--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F05339-EDF9-4D17-A6ED-18F8D03AC687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C28F1E2-5D9F-47A5-8BBC-DE131C2D9DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
@@ -4546,16 +4546,16 @@
         <v>1</v>
       </c>
       <c r="U30" s="21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" s="21">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="W30" s="21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" s="21">
-        <v>12000</v>
+        <v>7200</v>
       </c>
       <c r="Y30" s="21">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE4955E-EFC3-438E-8D1F-3DACCBCB0136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F05339-EDF9-4D17-A6ED-18F8D03AC687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
@@ -4546,16 +4546,16 @@
         <v>1</v>
       </c>
       <c r="U30" s="21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V30" s="21">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="W30" s="21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X30" s="21">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="Y30" s="21">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C28F1E2-5D9F-47A5-8BBC-DE131C2D9DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F05339-EDF9-4D17-A6ED-18F8D03AC687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
@@ -4546,16 +4546,16 @@
         <v>1</v>
       </c>
       <c r="U30" s="21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V30" s="21">
+        <v>20000</v>
+      </c>
+      <c r="W30" s="21">
+        <v>0</v>
+      </c>
+      <c r="X30" s="21">
         <v>12000</v>
-      </c>
-      <c r="W30" s="21">
-        <v>5</v>
-      </c>
-      <c r="X30" s="21">
-        <v>7200</v>
       </c>
       <c r="Y30" s="21">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F05339-EDF9-4D17-A6ED-18F8D03AC687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04FC212-D0B1-4530-9E46-1D26952C6008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -271,7 +271,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
+    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0-没有直接效果
+1-直接伤害：根据释放者的攻击力万分比
+2-直接回血：根据释放者的攻击力万分比
+3-直接回血：根据目标的生命最大值计算，百万分比</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
       <text>
         <r>
           <rPr>
@@ -302,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
+    <comment ref="AD4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
       <text>
         <r>
           <rPr>
@@ -338,7 +355,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="303">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1355,6 +1372,33 @@
   </si>
   <si>
     <t>击杀回血效果提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成，永久</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage_element</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S_C</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参与伤害计算的攻击元素类型（0-物理、1-冰、2-火、3-毒、4-电）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4,0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1362,7 +1406,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1516,6 +1560,20 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1650,7 +1708,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1717,6 +1775,16 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="4" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2017,7 +2085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2035,24 +2103,25 @@
     <col min="18" max="18" width="12.5" style="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.5" style="5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="28.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="5"/>
+    <col min="21" max="21" width="60" style="5" customWidth="1"/>
+    <col min="22" max="22" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="28.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2113,35 +2182,38 @@
       <c r="T2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U2" s="5" t="s">
-        <v>75</v>
+      <c r="U2" s="33" t="s">
+        <v>300</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="5" t="s">
         <v>75</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Y2" s="5" t="s">
-        <v>78</v>
+      <c r="Y2" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>78</v>
       </c>
       <c r="AA2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB2" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="AD2" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2202,35 +2274,38 @@
       <c r="T3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AA3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AB3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2291,35 +2366,38 @@
       <c r="T4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="U4" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="X4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Y4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="AA4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10101</v>
       </c>
@@ -2369,42 +2447,47 @@
       <c r="Q5" s="9">
         <v>2</v>
       </c>
-      <c r="R5" s="9"/>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
       <c r="S5" s="9">
         <v>1</v>
       </c>
       <c r="T5" s="9">
         <v>0</v>
       </c>
-      <c r="U5" s="9">
+      <c r="U5" s="34">
         <v>0</v>
       </c>
       <c r="V5" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W5" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X5" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>0</v>
       </c>
       <c r="AB5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC5" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC5" s="10" t="s">
+      <c r="AD5" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10102</v>
       </c>
@@ -2454,42 +2537,47 @@
       <c r="Q6" s="9">
         <v>2</v>
       </c>
-      <c r="R6" s="9"/>
+      <c r="R6" s="9">
+        <v>0</v>
+      </c>
       <c r="S6" s="9">
         <v>1</v>
       </c>
       <c r="T6" s="9">
         <v>0</v>
       </c>
-      <c r="U6" s="9">
+      <c r="U6" s="34">
         <v>0</v>
       </c>
       <c r="V6" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W6" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X6" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>0</v>
       </c>
       <c r="AB6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC6" s="10" t="s">
+      <c r="AD6" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10201</v>
       </c>
@@ -2539,42 +2627,47 @@
       <c r="Q7" s="9">
         <v>2</v>
       </c>
-      <c r="R7" s="9"/>
+      <c r="R7" s="9">
+        <v>0</v>
+      </c>
       <c r="S7" s="9">
         <v>1</v>
       </c>
       <c r="T7" s="9">
         <v>0</v>
       </c>
-      <c r="U7" s="9">
+      <c r="U7" s="34">
         <v>0</v>
       </c>
       <c r="V7" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X7" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
       </c>
       <c r="AB7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC7" s="10" t="s">
+      <c r="AD7" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10202</v>
       </c>
@@ -2624,42 +2717,47 @@
       <c r="Q8" s="9">
         <v>2</v>
       </c>
-      <c r="R8" s="9"/>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
       <c r="S8" s="9">
         <v>1</v>
       </c>
       <c r="T8" s="9">
         <v>0</v>
       </c>
-      <c r="U8" s="9">
+      <c r="U8" s="34">
         <v>0</v>
       </c>
       <c r="V8" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X8" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>0</v>
       </c>
       <c r="AB8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC8" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC8" s="10" t="s">
+      <c r="AD8" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10301</v>
       </c>
@@ -2709,42 +2807,47 @@
       <c r="Q9" s="9">
         <v>2</v>
       </c>
-      <c r="R9" s="9"/>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
       <c r="S9" s="9">
         <v>1</v>
       </c>
       <c r="T9" s="9">
         <v>0</v>
       </c>
-      <c r="U9" s="9">
+      <c r="U9" s="34">
         <v>0</v>
       </c>
       <c r="V9" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X9" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>0</v>
       </c>
       <c r="AB9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC9" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC9" s="10" t="s">
+      <c r="AD9" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10302</v>
       </c>
@@ -2794,42 +2897,47 @@
       <c r="Q10" s="9">
         <v>2</v>
       </c>
-      <c r="R10" s="9"/>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
       <c r="S10" s="9">
         <v>1</v>
       </c>
       <c r="T10" s="9">
         <v>0</v>
       </c>
-      <c r="U10" s="9">
+      <c r="U10" s="34">
         <v>0</v>
       </c>
       <c r="V10" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X10" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>0</v>
       </c>
       <c r="AB10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC10" s="10" t="s">
+      <c r="AD10" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>20001</v>
       </c>
@@ -2881,42 +2989,47 @@
       <c r="Q11" s="2">
         <v>2</v>
       </c>
-      <c r="R11" s="2"/>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
       <c r="S11" s="2">
         <v>1</v>
       </c>
       <c r="T11" s="2">
         <v>1</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="35">
         <v>0</v>
       </c>
       <c r="V11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z11" s="2">
         <v>0</v>
       </c>
-      <c r="AA11" s="2" t="s">
-        <v>34</v>
+      <c r="AA11" s="2">
+        <v>0</v>
       </c>
       <c r="AB11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC11" s="2" t="s">
+      <c r="AD11" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>20010001</v>
       </c>
@@ -2968,42 +3081,47 @@
       <c r="Q12" s="2">
         <v>2</v>
       </c>
-      <c r="R12" s="2"/>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
       <c r="S12" s="2">
         <v>1</v>
       </c>
       <c r="T12" s="2">
         <v>1</v>
       </c>
-      <c r="U12" s="2">
+      <c r="U12" s="35">
         <v>0</v>
       </c>
       <c r="V12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z12" s="2">
         <v>0</v>
       </c>
-      <c r="AA12" s="2" t="s">
-        <v>34</v>
+      <c r="AA12" s="2">
+        <v>0</v>
       </c>
       <c r="AB12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC12" s="2" t="s">
+      <c r="AD12" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>20020001</v>
       </c>
@@ -3055,42 +3173,47 @@
       <c r="Q13" s="2">
         <v>2</v>
       </c>
-      <c r="R13" s="2"/>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
       <c r="S13" s="2">
         <v>1</v>
       </c>
       <c r="T13" s="2">
         <v>1</v>
       </c>
-      <c r="U13" s="2">
+      <c r="U13" s="35">
         <v>0</v>
       </c>
       <c r="V13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z13" s="2">
         <v>0</v>
       </c>
-      <c r="AA13" s="2" t="s">
-        <v>34</v>
+      <c r="AA13" s="2">
+        <v>0</v>
       </c>
       <c r="AB13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC13" s="2" t="s">
+      <c r="AD13" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>20030001</v>
       </c>
@@ -3119,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3142,42 +3265,47 @@
       <c r="Q14" s="2">
         <v>2</v>
       </c>
-      <c r="R14" s="2"/>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
       <c r="S14" s="2">
         <v>1</v>
       </c>
       <c r="T14" s="2">
         <v>1</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="35">
         <v>0</v>
       </c>
       <c r="V14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z14" s="2">
         <v>0</v>
       </c>
-      <c r="AA14" s="2" t="s">
-        <v>34</v>
+      <c r="AA14" s="2">
+        <v>0</v>
       </c>
       <c r="AB14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC14" s="2" t="s">
+      <c r="AD14" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>20040001</v>
       </c>
@@ -3229,42 +3357,47 @@
       <c r="Q15" s="2">
         <v>2</v>
       </c>
-      <c r="R15" s="2"/>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
       <c r="S15" s="2">
         <v>1</v>
       </c>
       <c r="T15" s="2">
         <v>1</v>
       </c>
-      <c r="U15" s="2">
+      <c r="U15" s="35">
         <v>0</v>
       </c>
       <c r="V15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z15" s="2">
         <v>0</v>
       </c>
-      <c r="AA15" s="2" t="s">
-        <v>34</v>
+      <c r="AA15" s="2">
+        <v>0</v>
       </c>
       <c r="AB15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC15" s="2" t="s">
+      <c r="AD15" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>20050001</v>
       </c>
@@ -3316,42 +3449,47 @@
       <c r="Q16" s="2">
         <v>2</v>
       </c>
-      <c r="R16" s="2"/>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
       <c r="S16" s="2">
         <v>1</v>
       </c>
       <c r="T16" s="2">
         <v>1</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="35">
         <v>0</v>
       </c>
       <c r="V16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z16" s="2">
         <v>0</v>
       </c>
-      <c r="AA16" s="2" t="s">
-        <v>34</v>
+      <c r="AA16" s="2">
+        <v>0</v>
       </c>
       <c r="AB16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC16" s="2" t="s">
+      <c r="AD16" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>20060001</v>
       </c>
@@ -3403,42 +3541,47 @@
       <c r="Q17" s="2">
         <v>2</v>
       </c>
-      <c r="R17" s="2"/>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
       <c r="S17" s="2">
         <v>1</v>
       </c>
       <c r="T17" s="2">
         <v>1</v>
       </c>
-      <c r="U17" s="2">
+      <c r="U17" s="35">
         <v>0</v>
       </c>
       <c r="V17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z17" s="2">
         <v>0</v>
       </c>
-      <c r="AA17" s="2" t="s">
-        <v>34</v>
+      <c r="AA17" s="2">
+        <v>0</v>
       </c>
       <c r="AB17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC17" s="2" t="s">
+      <c r="AD17" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>20070001</v>
       </c>
@@ -3490,42 +3633,47 @@
       <c r="Q18" s="2">
         <v>2</v>
       </c>
-      <c r="R18" s="2"/>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
       <c r="S18" s="2">
         <v>1</v>
       </c>
       <c r="T18" s="2">
         <v>1</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="35">
         <v>0</v>
       </c>
       <c r="V18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z18" s="2">
         <v>0</v>
       </c>
-      <c r="AA18" s="2" t="s">
-        <v>34</v>
+      <c r="AA18" s="2">
+        <v>0</v>
       </c>
       <c r="AB18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC18" s="2" t="s">
+      <c r="AD18" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>20080001</v>
       </c>
@@ -3577,7 +3725,9 @@
       <c r="Q19" s="2">
         <v>2</v>
       </c>
-      <c r="R19" s="2"/>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
       <c r="S19" s="2">
         <v>1</v>
       </c>
@@ -3588,31 +3738,34 @@
         <v>0</v>
       </c>
       <c r="V19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z19" s="2">
         <v>0</v>
       </c>
-      <c r="AA19" s="2" t="s">
-        <v>34</v>
+      <c r="AA19" s="2">
+        <v>0</v>
       </c>
       <c r="AB19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC19" s="2" t="s">
+      <c r="AD19" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20090001</v>
       </c>
@@ -3664,7 +3817,9 @@
       <c r="Q20" s="2">
         <v>2</v>
       </c>
-      <c r="R20" s="2"/>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
       <c r="S20" s="2">
         <v>1</v>
       </c>
@@ -3675,31 +3830,34 @@
         <v>0</v>
       </c>
       <c r="V20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z20" s="2">
         <v>0</v>
       </c>
-      <c r="AA20" s="2" t="s">
-        <v>34</v>
+      <c r="AA20" s="2">
+        <v>0</v>
       </c>
       <c r="AB20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC20" s="2" t="s">
+      <c r="AD20" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20100001</v>
       </c>
@@ -3751,7 +3909,9 @@
       <c r="Q21" s="2">
         <v>2</v>
       </c>
-      <c r="R21" s="2"/>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
       <c r="S21" s="2">
         <v>1</v>
       </c>
@@ -3762,31 +3922,34 @@
         <v>0</v>
       </c>
       <c r="V21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z21" s="2">
         <v>0</v>
       </c>
-      <c r="AA21" s="2" t="s">
-        <v>34</v>
+      <c r="AA21" s="2">
+        <v>0</v>
       </c>
       <c r="AB21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC21" s="2" t="s">
+      <c r="AD21" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20110001</v>
       </c>
@@ -3838,7 +4001,9 @@
       <c r="Q22" s="2">
         <v>2</v>
       </c>
-      <c r="R22" s="2"/>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
       <c r="S22" s="2">
         <v>1</v>
       </c>
@@ -3849,31 +4014,34 @@
         <v>0</v>
       </c>
       <c r="V22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z22" s="2">
         <v>0</v>
       </c>
-      <c r="AA22" s="2" t="s">
-        <v>34</v>
+      <c r="AA22" s="2">
+        <v>0</v>
       </c>
       <c r="AB22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC22" s="2" t="s">
+      <c r="AD22" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20120001</v>
       </c>
@@ -3925,7 +4093,9 @@
       <c r="Q23" s="2">
         <v>2</v>
       </c>
-      <c r="R23" s="2"/>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
       <c r="S23" s="2">
         <v>1</v>
       </c>
@@ -3936,31 +4106,34 @@
         <v>0</v>
       </c>
       <c r="V23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z23" s="2">
         <v>0</v>
       </c>
-      <c r="AA23" s="2" t="s">
-        <v>34</v>
+      <c r="AA23" s="2">
+        <v>0</v>
       </c>
       <c r="AB23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC23" s="2" t="s">
+      <c r="AD23" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20130001</v>
       </c>
@@ -4012,7 +4185,9 @@
       <c r="Q24" s="2">
         <v>2</v>
       </c>
-      <c r="R24" s="2"/>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
       <c r="S24" s="2">
         <v>1</v>
       </c>
@@ -4023,31 +4198,34 @@
         <v>0</v>
       </c>
       <c r="V24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z24" s="2">
         <v>0</v>
       </c>
-      <c r="AA24" s="2" t="s">
-        <v>34</v>
+      <c r="AA24" s="2">
+        <v>0</v>
       </c>
       <c r="AB24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC24" s="2" t="s">
+      <c r="AD24" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20140001</v>
       </c>
@@ -4099,7 +4277,9 @@
       <c r="Q25" s="2">
         <v>2</v>
       </c>
-      <c r="R25" s="2"/>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
       <c r="S25" s="2">
         <v>1</v>
       </c>
@@ -4110,31 +4290,34 @@
         <v>0</v>
       </c>
       <c r="V25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z25" s="2">
         <v>0</v>
       </c>
-      <c r="AA25" s="2" t="s">
-        <v>34</v>
+      <c r="AA25" s="2">
+        <v>0</v>
       </c>
       <c r="AB25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC25" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC25" s="2" t="s">
+      <c r="AD25" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>20150001</v>
       </c>
@@ -4186,7 +4369,9 @@
       <c r="Q26" s="2">
         <v>2</v>
       </c>
-      <c r="R26" s="2"/>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
       <c r="S26" s="2">
         <v>1</v>
       </c>
@@ -4197,31 +4382,34 @@
         <v>0</v>
       </c>
       <c r="V26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z26" s="2">
         <v>0</v>
       </c>
-      <c r="AA26" s="2" t="s">
-        <v>34</v>
+      <c r="AA26" s="2">
+        <v>0</v>
       </c>
       <c r="AB26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC26" s="2" t="s">
+      <c r="AD26" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>20160001</v>
       </c>
@@ -4273,7 +4461,9 @@
       <c r="Q27" s="2">
         <v>2</v>
       </c>
-      <c r="R27" s="2"/>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
       <c r="S27" s="2">
         <v>1</v>
       </c>
@@ -4284,400 +4474,419 @@
         <v>0</v>
       </c>
       <c r="V27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z27" s="2">
         <v>0</v>
       </c>
-      <c r="AA27" s="2" t="s">
-        <v>34</v>
+      <c r="AA27" s="2">
+        <v>0</v>
       </c>
       <c r="AB27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC27" s="2" t="s">
+      <c r="AD27" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A28" s="23">
+        <v>25010001</v>
+      </c>
+      <c r="B28" s="23">
+        <v>2</v>
+      </c>
+      <c r="C28" s="23">
+        <v>2501</v>
+      </c>
+      <c r="D28" s="23">
+        <v>1</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="I28" s="23">
+        <v>0</v>
+      </c>
+      <c r="J28" s="23">
+        <v>1000</v>
+      </c>
+      <c r="K28" s="23">
+        <v>1000</v>
+      </c>
+      <c r="L28" s="23">
+        <v>0</v>
+      </c>
+      <c r="M28" s="23">
+        <v>10000</v>
+      </c>
+      <c r="N28" s="23">
+        <v>0</v>
+      </c>
+      <c r="O28" s="23">
+        <v>0</v>
+      </c>
+      <c r="P28" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="23">
+        <v>1</v>
+      </c>
+      <c r="R28" s="23">
+        <v>0</v>
+      </c>
+      <c r="S28" s="23">
+        <v>1</v>
+      </c>
+      <c r="T28" s="23">
+        <v>0</v>
+      </c>
+      <c r="U28" s="23">
+        <v>0</v>
+      </c>
+      <c r="V28" s="23">
+        <v>0</v>
+      </c>
+      <c r="W28" s="23">
+        <v>0</v>
+      </c>
+      <c r="X28" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="23">
+        <v>54150001</v>
+      </c>
+      <c r="AA28" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC28" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD28" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
         <v>30001</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>3</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C29" s="3">
         <v>3</v>
       </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>20000</v>
       </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N28" s="3">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3">
-        <v>1</v>
-      </c>
-      <c r="P28" s="3">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1</v>
+      </c>
+      <c r="P29" s="3">
         <v>2</v>
       </c>
-      <c r="Q28" s="3">
-        <v>1</v>
-      </c>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3">
-        <v>1</v>
-      </c>
-      <c r="T28" s="3">
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>1</v>
+      </c>
+      <c r="T29" s="3">
         <v>3</v>
       </c>
-      <c r="U28" s="3">
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <v>0</v>
-      </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>1000001</v>
       </c>
-      <c r="Z28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB28" s="3" t="s">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC29" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AC28" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
         <v>4000001</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>4</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C30" s="3">
         <v>400</v>
       </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
         <v>2000001</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AD30" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21">
+    <row r="31" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21">
         <v>5000001</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B31" s="21">
         <v>5</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C31" s="21">
         <v>500</v>
       </c>
-      <c r="D30" s="21">
-        <v>1</v>
-      </c>
-      <c r="E30" s="22" t="s">
+      <c r="D31" s="21">
+        <v>1</v>
+      </c>
+      <c r="E31" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F31" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="G31" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H31" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I31" s="21">
         <v>8000</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J31" s="21">
         <v>800</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K31" s="21">
         <v>8000</v>
       </c>
-      <c r="L30" s="21">
-        <v>0</v>
-      </c>
-      <c r="M30" s="21">
-        <v>10000</v>
-      </c>
-      <c r="N30" s="21">
-        <v>0</v>
-      </c>
-      <c r="O30" s="21">
-        <v>0</v>
-      </c>
-      <c r="P30" s="21">
+      <c r="L31" s="21">
+        <v>0</v>
+      </c>
+      <c r="M31" s="21">
+        <v>10000</v>
+      </c>
+      <c r="N31" s="21">
+        <v>0</v>
+      </c>
+      <c r="O31" s="21">
+        <v>0</v>
+      </c>
+      <c r="P31" s="21">
         <v>3</v>
       </c>
-      <c r="Q30" s="21">
+      <c r="Q31" s="21">
         <v>2</v>
       </c>
-      <c r="R30" s="21">
+      <c r="R31" s="21">
         <v>5000</v>
       </c>
-      <c r="S30" s="21">
+      <c r="S31" s="21">
         <v>9</v>
       </c>
-      <c r="T30" s="21">
-        <v>1</v>
-      </c>
-      <c r="U30" s="21">
-        <v>0</v>
-      </c>
-      <c r="V30" s="21">
-        <v>20000</v>
-      </c>
-      <c r="W30" s="21">
-        <v>0</v>
-      </c>
-      <c r="X30" s="21">
+      <c r="T31" s="21">
+        <v>1</v>
+      </c>
+      <c r="U31" s="21">
+        <v>1</v>
+      </c>
+      <c r="V31" s="21">
+        <v>0</v>
+      </c>
+      <c r="W31" s="21">
         <v>12000</v>
       </c>
-      <c r="Y30" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="21">
+      <c r="X31" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="21">
+        <v>8000</v>
+      </c>
+      <c r="Z31" s="21">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="21">
         <v>55010001</v>
       </c>
-      <c r="AA30" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB30" s="21" t="s">
+      <c r="AB31" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC31" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="AC30" s="21" t="s">
+      <c r="AD31" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="17">
+    <row r="32" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="17">
         <v>6000001</v>
-      </c>
-      <c r="B31" s="17">
-        <v>5</v>
-      </c>
-      <c r="C31" s="17">
-        <v>600</v>
-      </c>
-      <c r="D31" s="17">
-        <v>1</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17">
-        <v>100</v>
-      </c>
-      <c r="J31" s="17">
-        <v>100</v>
-      </c>
-      <c r="K31" s="17">
-        <v>100</v>
-      </c>
-      <c r="L31" s="17">
-        <v>0</v>
-      </c>
-      <c r="M31" s="17">
-        <v>10000</v>
-      </c>
-      <c r="N31" s="17">
-        <v>0</v>
-      </c>
-      <c r="O31" s="17">
-        <v>0</v>
-      </c>
-      <c r="P31" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="17">
-        <v>2</v>
-      </c>
-      <c r="R31" s="17">
-        <v>0</v>
-      </c>
-      <c r="S31" s="17">
-        <v>9</v>
-      </c>
-      <c r="T31" s="17">
-        <v>0</v>
-      </c>
-      <c r="U31" s="17">
-        <v>150</v>
-      </c>
-      <c r="V31" s="17">
-        <v>15000</v>
-      </c>
-      <c r="W31" s="17">
-        <v>120</v>
-      </c>
-      <c r="X31" s="17">
-        <v>12000</v>
-      </c>
-      <c r="Y31" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="17">
-        <v>56010001</v>
-      </c>
-      <c r="AA31" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB31" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC31" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="17">
-        <v>6010001</v>
       </c>
       <c r="B32" s="17">
         <v>5</v>
       </c>
       <c r="C32" s="17">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D32" s="17">
         <v>1</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>34</v>
@@ -4702,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="17">
         <v>3</v>
@@ -4720,138 +4929,144 @@
         <v>0</v>
       </c>
       <c r="U32" s="17">
+        <v>2</v>
+      </c>
+      <c r="V32" s="17">
         <v>150</v>
       </c>
-      <c r="V32" s="17">
+      <c r="W32" s="17">
         <v>15000</v>
       </c>
-      <c r="W32" s="17">
+      <c r="X32" s="17">
         <v>120</v>
       </c>
-      <c r="X32" s="17">
+      <c r="Y32" s="17">
         <v>12000</v>
       </c>
-      <c r="Y32" s="17">
-        <v>0</v>
-      </c>
       <c r="Z32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="17">
         <v>56010001</v>
       </c>
-      <c r="AA32" s="17" t="s">
-        <v>34</v>
-      </c>
       <c r="AB32" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC32" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AC32" s="17" t="s">
+      <c r="AD32" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="19">
+    <row r="33" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="17">
+        <v>6010001</v>
+      </c>
+      <c r="B33" s="17">
+        <v>5</v>
+      </c>
+      <c r="C33" s="17">
+        <v>601</v>
+      </c>
+      <c r="D33" s="17">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17">
+        <v>100</v>
+      </c>
+      <c r="J33" s="17">
+        <v>100</v>
+      </c>
+      <c r="K33" s="17">
+        <v>100</v>
+      </c>
+      <c r="L33" s="17">
+        <v>0</v>
+      </c>
+      <c r="M33" s="17">
+        <v>10000</v>
+      </c>
+      <c r="N33" s="17">
+        <v>0</v>
+      </c>
+      <c r="O33" s="17">
+        <v>1</v>
+      </c>
+      <c r="P33" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="17">
+        <v>2</v>
+      </c>
+      <c r="R33" s="17">
+        <v>0</v>
+      </c>
+      <c r="S33" s="17">
+        <v>9</v>
+      </c>
+      <c r="T33" s="17">
+        <v>0</v>
+      </c>
+      <c r="U33" s="17">
+        <v>2</v>
+      </c>
+      <c r="V33" s="17">
+        <v>150</v>
+      </c>
+      <c r="W33" s="17">
+        <v>15000</v>
+      </c>
+      <c r="X33" s="17">
+        <v>120</v>
+      </c>
+      <c r="Y33" s="17">
+        <v>12000</v>
+      </c>
+      <c r="Z33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="17">
+        <v>56010001</v>
+      </c>
+      <c r="AB33" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC33" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD33" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="19">
         <v>7000001</v>
-      </c>
-      <c r="B33" s="19">
-        <v>5</v>
-      </c>
-      <c r="C33" s="19">
-        <v>700</v>
-      </c>
-      <c r="D33" s="19">
-        <v>1</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19">
-        <v>100</v>
-      </c>
-      <c r="J33" s="19">
-        <v>100</v>
-      </c>
-      <c r="K33" s="19">
-        <v>100</v>
-      </c>
-      <c r="L33" s="19">
-        <v>0</v>
-      </c>
-      <c r="M33" s="19">
-        <v>10000</v>
-      </c>
-      <c r="N33" s="19">
-        <v>0</v>
-      </c>
-      <c r="O33" s="19">
-        <v>0</v>
-      </c>
-      <c r="P33" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="19">
-        <v>2</v>
-      </c>
-      <c r="R33" s="19">
-        <v>0</v>
-      </c>
-      <c r="S33" s="19">
-        <v>1</v>
-      </c>
-      <c r="T33" s="19">
-        <v>0</v>
-      </c>
-      <c r="U33" s="19">
-        <v>150</v>
-      </c>
-      <c r="V33" s="19">
-        <v>15000</v>
-      </c>
-      <c r="W33" s="19">
-        <v>120</v>
-      </c>
-      <c r="X33" s="19">
-        <v>12000</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="19">
-        <v>57010001</v>
-      </c>
-      <c r="AA33" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB33" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC33" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="19">
-        <v>7010001</v>
       </c>
       <c r="B34" s="19">
         <v>5</v>
       </c>
       <c r="C34" s="19">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D34" s="19">
         <v>1</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>34</v>
@@ -4876,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="19">
         <v>3</v>
@@ -4888,144 +5103,150 @@
         <v>0</v>
       </c>
       <c r="S34" s="19">
+        <v>1</v>
+      </c>
+      <c r="T34" s="19">
+        <v>0</v>
+      </c>
+      <c r="U34" s="19">
+        <v>4</v>
+      </c>
+      <c r="V34" s="19">
+        <v>150</v>
+      </c>
+      <c r="W34" s="19">
+        <v>15000</v>
+      </c>
+      <c r="X34" s="19">
+        <v>120</v>
+      </c>
+      <c r="Y34" s="19">
+        <v>12000</v>
+      </c>
+      <c r="Z34" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="19">
+        <v>57010001</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC34" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD34" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="19">
+        <v>7010001</v>
+      </c>
+      <c r="B35" s="19">
+        <v>5</v>
+      </c>
+      <c r="C35" s="19">
+        <v>701</v>
+      </c>
+      <c r="D35" s="19">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19">
+        <v>100</v>
+      </c>
+      <c r="J35" s="19">
+        <v>100</v>
+      </c>
+      <c r="K35" s="19">
+        <v>100</v>
+      </c>
+      <c r="L35" s="19">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19">
+        <v>10000</v>
+      </c>
+      <c r="N35" s="19">
+        <v>0</v>
+      </c>
+      <c r="O35" s="19">
+        <v>1</v>
+      </c>
+      <c r="P35" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="19">
+        <v>2</v>
+      </c>
+      <c r="R35" s="19">
+        <v>0</v>
+      </c>
+      <c r="S35" s="19">
         <v>9</v>
       </c>
-      <c r="T34" s="19">
-        <v>0</v>
-      </c>
-      <c r="U34" s="19">
+      <c r="T35" s="19">
+        <v>0</v>
+      </c>
+      <c r="U35" s="19">
+        <v>4</v>
+      </c>
+      <c r="V35" s="19">
         <v>150</v>
       </c>
-      <c r="V34" s="19">
+      <c r="W35" s="19">
         <v>15000</v>
       </c>
-      <c r="W34" s="19">
+      <c r="X35" s="19">
         <v>120</v>
       </c>
-      <c r="X34" s="19">
+      <c r="Y35" s="19">
         <v>12000</v>
       </c>
-      <c r="Y34" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="19">
+      <c r="Z35" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="19">
         <v>57010001</v>
       </c>
-      <c r="AA34" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB34" s="19" t="s">
+      <c r="AB35" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC35" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="AC34" s="19" t="s">
+      <c r="AD35" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="20">
+    <row r="36" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="20">
         <v>8000001</v>
-      </c>
-      <c r="B35" s="20">
-        <v>5</v>
-      </c>
-      <c r="C35" s="20">
-        <v>800</v>
-      </c>
-      <c r="D35" s="20">
-        <v>1</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20">
-        <v>100</v>
-      </c>
-      <c r="J35" s="20">
-        <v>100</v>
-      </c>
-      <c r="K35" s="20">
-        <v>100</v>
-      </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20">
-        <v>10000</v>
-      </c>
-      <c r="N35" s="20">
-        <v>0</v>
-      </c>
-      <c r="O35" s="20">
-        <v>0</v>
-      </c>
-      <c r="P35" s="20">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="20">
-        <v>2</v>
-      </c>
-      <c r="R35" s="20">
-        <v>0</v>
-      </c>
-      <c r="S35" s="20">
-        <v>9</v>
-      </c>
-      <c r="T35" s="20">
-        <v>0</v>
-      </c>
-      <c r="U35" s="20">
-        <v>150</v>
-      </c>
-      <c r="V35" s="20">
-        <v>15000</v>
-      </c>
-      <c r="W35" s="20">
-        <v>120</v>
-      </c>
-      <c r="X35" s="20">
-        <v>12000</v>
-      </c>
-      <c r="Y35" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="20">
-        <v>58010001</v>
-      </c>
-      <c r="AA35" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB35" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC35" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="20">
-        <v>8010001</v>
       </c>
       <c r="B36" s="20">
         <v>5</v>
       </c>
       <c r="C36" s="20">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D36" s="20">
         <v>1</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G36" s="20" t="s">
         <v>34</v>
@@ -5050,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" s="20">
         <v>3</v>
@@ -5068,225 +5289,234 @@
         <v>0</v>
       </c>
       <c r="U36" s="20">
+        <v>3</v>
+      </c>
+      <c r="V36" s="20">
         <v>150</v>
       </c>
-      <c r="V36" s="20">
+      <c r="W36" s="20">
         <v>15000</v>
       </c>
-      <c r="W36" s="20">
+      <c r="X36" s="20">
         <v>120</v>
       </c>
-      <c r="X36" s="20">
+      <c r="Y36" s="20">
         <v>12000</v>
       </c>
-      <c r="Y36" s="20">
-        <v>0</v>
-      </c>
       <c r="Z36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="20">
+        <v>58010001</v>
+      </c>
+      <c r="AB36" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC36" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD36" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="20">
+        <v>8010001</v>
+      </c>
+      <c r="B37" s="20">
+        <v>5</v>
+      </c>
+      <c r="C37" s="20">
+        <v>801</v>
+      </c>
+      <c r="D37" s="20">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20">
+        <v>100</v>
+      </c>
+      <c r="J37" s="20">
+        <v>100</v>
+      </c>
+      <c r="K37" s="20">
+        <v>100</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>10000</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20">
+        <v>1</v>
+      </c>
+      <c r="P37" s="20">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="20">
+        <v>2</v>
+      </c>
+      <c r="R37" s="20">
+        <v>0</v>
+      </c>
+      <c r="S37" s="20">
+        <v>9</v>
+      </c>
+      <c r="T37" s="20">
+        <v>0</v>
+      </c>
+      <c r="U37" s="20">
+        <v>3</v>
+      </c>
+      <c r="V37" s="20">
+        <v>150</v>
+      </c>
+      <c r="W37" s="20">
+        <v>15000</v>
+      </c>
+      <c r="X37" s="20">
+        <v>120</v>
+      </c>
+      <c r="Y37" s="20">
+        <v>12000</v>
+      </c>
+      <c r="Z37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="20">
         <v>58050001</v>
       </c>
-      <c r="AA36" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB36" s="20" t="s">
+      <c r="AB37" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC37" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AC36" s="20" t="s">
+      <c r="AD37" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="28">
+    <row r="38" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="28">
         <v>9000001</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B38" s="28">
         <v>5</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C38" s="28">
         <v>900</v>
       </c>
-      <c r="D37" s="28">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18" t="s">
+      <c r="D38" s="28">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F38" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28">
+      <c r="G38" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28">
         <v>100</v>
       </c>
-      <c r="J37" s="28">
+      <c r="J38" s="28">
         <v>100</v>
       </c>
-      <c r="K37" s="28">
+      <c r="K38" s="28">
         <v>100</v>
       </c>
-      <c r="L37" s="28">
-        <v>0</v>
-      </c>
-      <c r="M37" s="28">
-        <v>10000</v>
-      </c>
-      <c r="N37" s="28">
-        <v>0</v>
-      </c>
-      <c r="O37" s="28">
-        <v>1</v>
-      </c>
-      <c r="P37" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="28">
-        <v>0</v>
-      </c>
-      <c r="R37" s="28">
-        <v>0</v>
-      </c>
-      <c r="S37" s="28">
-        <v>1</v>
-      </c>
-      <c r="T37" s="28">
-        <v>0</v>
-      </c>
-      <c r="U37" s="28">
+      <c r="L38" s="28">
+        <v>0</v>
+      </c>
+      <c r="M38" s="28">
+        <v>10000</v>
+      </c>
+      <c r="N38" s="28">
+        <v>0</v>
+      </c>
+      <c r="O38" s="28">
+        <v>1</v>
+      </c>
+      <c r="P38" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="28">
+        <v>0</v>
+      </c>
+      <c r="R38" s="28">
+        <v>0</v>
+      </c>
+      <c r="S38" s="28">
+        <v>1</v>
+      </c>
+      <c r="T38" s="28">
+        <v>0</v>
+      </c>
+      <c r="U38" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="V38" s="28">
         <v>150</v>
       </c>
-      <c r="V37" s="28">
+      <c r="W38" s="28">
         <v>15000</v>
       </c>
-      <c r="W37" s="28">
+      <c r="X38" s="28">
         <v>120</v>
       </c>
-      <c r="X37" s="28">
+      <c r="Y38" s="28">
         <v>12000</v>
       </c>
-      <c r="Y37" s="28">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB37" s="28">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="28">
+      <c r="Z38" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="28">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC38" s="28">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="28">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="30">
+    <row r="39" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="30">
         <v>10010001</v>
-      </c>
-      <c r="B38" s="30">
-        <v>5</v>
-      </c>
-      <c r="C38" s="30">
-        <v>1001</v>
-      </c>
-      <c r="D38" s="30">
-        <v>1</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="F38" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="G38" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30">
-        <v>100</v>
-      </c>
-      <c r="J38" s="30">
-        <v>100</v>
-      </c>
-      <c r="K38" s="30">
-        <v>100</v>
-      </c>
-      <c r="L38" s="30">
-        <v>0</v>
-      </c>
-      <c r="M38" s="30">
-        <v>10000</v>
-      </c>
-      <c r="N38" s="30">
-        <v>0</v>
-      </c>
-      <c r="O38" s="30">
-        <v>0</v>
-      </c>
-      <c r="P38" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="30">
-        <v>2</v>
-      </c>
-      <c r="R38" s="30">
-        <v>0</v>
-      </c>
-      <c r="S38" s="30">
-        <v>9</v>
-      </c>
-      <c r="T38" s="30">
-        <v>0</v>
-      </c>
-      <c r="U38" s="30">
-        <v>150</v>
-      </c>
-      <c r="V38" s="30">
-        <v>15000</v>
-      </c>
-      <c r="W38" s="30">
-        <v>120</v>
-      </c>
-      <c r="X38" s="30">
-        <v>12000</v>
-      </c>
-      <c r="Y38" s="30">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB38" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC38" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="30">
-        <v>10020001</v>
       </c>
       <c r="B39" s="30">
         <v>5</v>
       </c>
       <c r="C39" s="30">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D39" s="30">
         <v>1</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G39" s="30" t="s">
         <v>100</v>
@@ -5329,233 +5559,240 @@
         <v>0</v>
       </c>
       <c r="U39" s="30">
+        <v>0</v>
+      </c>
+      <c r="V39" s="30">
         <v>150</v>
       </c>
-      <c r="V39" s="30">
+      <c r="W39" s="30">
         <v>15000</v>
       </c>
-      <c r="W39" s="30">
+      <c r="X39" s="30">
         <v>120</v>
       </c>
-      <c r="X39" s="30">
+      <c r="Y39" s="30">
         <v>12000</v>
       </c>
-      <c r="Y39" s="30">
-        <v>0</v>
-      </c>
       <c r="Z39" s="30">
         <v>0</v>
       </c>
-      <c r="AA39" s="30" t="s">
+      <c r="AA39" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="AB39" s="30" t="s">
+      <c r="AC39" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="AC39" s="30" t="s">
+      <c r="AD39" s="30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="31">
+    <row r="40" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="30">
+        <v>10020001</v>
+      </c>
+      <c r="B40" s="30">
+        <v>5</v>
+      </c>
+      <c r="C40" s="30">
+        <v>1002</v>
+      </c>
+      <c r="D40" s="30">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30">
+        <v>100</v>
+      </c>
+      <c r="J40" s="30">
+        <v>100</v>
+      </c>
+      <c r="K40" s="30">
+        <v>100</v>
+      </c>
+      <c r="L40" s="30">
+        <v>0</v>
+      </c>
+      <c r="M40" s="30">
+        <v>10000</v>
+      </c>
+      <c r="N40" s="30">
+        <v>0</v>
+      </c>
+      <c r="O40" s="30">
+        <v>0</v>
+      </c>
+      <c r="P40" s="30">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="30">
+        <v>2</v>
+      </c>
+      <c r="R40" s="30">
+        <v>0</v>
+      </c>
+      <c r="S40" s="30">
+        <v>9</v>
+      </c>
+      <c r="T40" s="30">
+        <v>0</v>
+      </c>
+      <c r="U40" s="30">
+        <v>0</v>
+      </c>
+      <c r="V40" s="30">
+        <v>150</v>
+      </c>
+      <c r="W40" s="30">
+        <v>15000</v>
+      </c>
+      <c r="X40" s="30">
+        <v>120</v>
+      </c>
+      <c r="Y40" s="30">
+        <v>12000</v>
+      </c>
+      <c r="Z40" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC40" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD40" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="31">
         <v>11010001</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B41" s="31">
         <v>5</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C41" s="31">
         <v>1101</v>
       </c>
-      <c r="D40" s="31">
-        <v>1</v>
-      </c>
-      <c r="E40" s="18" t="s">
+      <c r="D41" s="31">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F41" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="G40" s="31" t="s">
+      <c r="G41" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31">
+      <c r="H41" s="31"/>
+      <c r="I41" s="31">
         <v>100</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J41" s="31">
         <v>100</v>
       </c>
-      <c r="K40" s="31">
+      <c r="K41" s="31">
         <v>100</v>
       </c>
-      <c r="L40" s="31">
-        <v>0</v>
-      </c>
-      <c r="M40" s="31">
-        <v>10000</v>
-      </c>
-      <c r="N40" s="31">
-        <v>0</v>
-      </c>
-      <c r="O40" s="31">
-        <v>0</v>
-      </c>
-      <c r="P40" s="31">
+      <c r="L41" s="31">
+        <v>0</v>
+      </c>
+      <c r="M41" s="31">
+        <v>10000</v>
+      </c>
+      <c r="N41" s="31">
+        <v>0</v>
+      </c>
+      <c r="O41" s="31">
+        <v>0</v>
+      </c>
+      <c r="P41" s="31">
         <v>3</v>
       </c>
-      <c r="Q40" s="31">
+      <c r="Q41" s="31">
         <v>2</v>
       </c>
-      <c r="R40" s="31">
-        <v>0</v>
-      </c>
-      <c r="S40" s="31">
+      <c r="R41" s="31">
+        <v>0</v>
+      </c>
+      <c r="S41" s="31">
         <v>9</v>
       </c>
-      <c r="T40" s="31">
-        <v>0</v>
-      </c>
-      <c r="U40" s="31">
+      <c r="T41" s="31">
+        <v>0</v>
+      </c>
+      <c r="U41" s="31">
+        <v>0</v>
+      </c>
+      <c r="V41" s="31">
         <v>150</v>
       </c>
-      <c r="V40" s="31">
+      <c r="W41" s="31">
         <v>15000</v>
       </c>
-      <c r="W40" s="31">
+      <c r="X41" s="31">
         <v>120</v>
       </c>
-      <c r="X40" s="31">
+      <c r="Y41" s="31">
         <v>12000</v>
       </c>
-      <c r="Y40" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="31" t="s">
+      <c r="Z41" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AB40" s="31" t="s">
+      <c r="AC41" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="AC40" s="31" t="s">
+      <c r="AD41" s="31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A41" s="23">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A42" s="23">
         <v>54010001</v>
-      </c>
-      <c r="B41" s="23">
-        <v>4</v>
-      </c>
-      <c r="C41" s="23">
-        <v>5401</v>
-      </c>
-      <c r="D41" s="23">
-        <v>1</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="I41" s="23">
-        <v>0</v>
-      </c>
-      <c r="J41" s="23">
-        <v>0</v>
-      </c>
-      <c r="K41" s="23">
-        <v>0</v>
-      </c>
-      <c r="L41" s="23">
-        <v>0</v>
-      </c>
-      <c r="M41" s="23">
-        <v>0</v>
-      </c>
-      <c r="N41" s="23">
-        <v>0</v>
-      </c>
-      <c r="O41" s="23">
-        <v>0</v>
-      </c>
-      <c r="P41" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="23">
-        <v>0</v>
-      </c>
-      <c r="R41" s="23">
-        <v>0</v>
-      </c>
-      <c r="S41" s="23">
-        <v>0</v>
-      </c>
-      <c r="T41" s="23">
-        <v>0</v>
-      </c>
-      <c r="U41" s="23">
-        <v>0</v>
-      </c>
-      <c r="V41" s="23">
-        <v>0</v>
-      </c>
-      <c r="W41" s="23">
-        <v>0</v>
-      </c>
-      <c r="X41" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="23">
-        <v>54010001</v>
-      </c>
-      <c r="Z41" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB41" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC41" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A42" s="23">
-        <v>54030001</v>
       </c>
       <c r="B42" s="23">
         <v>4</v>
       </c>
       <c r="C42" s="23">
-        <v>5403</v>
+        <v>5401</v>
       </c>
       <c r="D42" s="23">
         <v>1</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I42" s="23">
         <v>0</v>
@@ -5606,45 +5843,48 @@
         <v>0</v>
       </c>
       <c r="Y42" s="23">
-        <v>54020001</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="23" t="s">
-        <v>34</v>
+        <v>54010001</v>
+      </c>
+      <c r="AA42" s="23">
+        <v>0</v>
       </c>
       <c r="AB42" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC42" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC42" s="23" t="s">
+      <c r="AD42" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A43" s="23">
-        <v>54050001</v>
+        <v>54030001</v>
       </c>
       <c r="B43" s="23">
         <v>4</v>
       </c>
       <c r="C43" s="23">
-        <v>5405</v>
+        <v>5403</v>
       </c>
       <c r="D43" s="23">
         <v>1</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I43" s="23">
         <v>0</v>
@@ -5695,45 +5935,48 @@
         <v>0</v>
       </c>
       <c r="Y43" s="23">
-        <v>54030001</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="23" t="s">
-        <v>34</v>
+        <v>54020001</v>
+      </c>
+      <c r="AA43" s="23">
+        <v>0</v>
       </c>
       <c r="AB43" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC43" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC43" s="23" t="s">
+      <c r="AD43" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A44" s="23">
-        <v>54070001</v>
+        <v>54050001</v>
       </c>
       <c r="B44" s="23">
         <v>4</v>
       </c>
       <c r="C44" s="23">
-        <v>5407</v>
+        <v>5405</v>
       </c>
       <c r="D44" s="23">
         <v>1</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I44" s="23">
         <v>0</v>
@@ -5784,45 +6027,48 @@
         <v>0</v>
       </c>
       <c r="Y44" s="23">
-        <v>54040001</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="23" t="s">
-        <v>34</v>
+        <v>54030001</v>
+      </c>
+      <c r="AA44" s="23">
+        <v>0</v>
       </c>
       <c r="AB44" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC44" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC44" s="23" t="s">
+      <c r="AD44" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A45" s="23">
-        <v>54090001</v>
+        <v>54070001</v>
       </c>
       <c r="B45" s="23">
         <v>4</v>
       </c>
       <c r="C45" s="23">
-        <v>5409</v>
+        <v>5407</v>
       </c>
       <c r="D45" s="23">
         <v>1</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G45" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I45" s="23">
         <v>0</v>
@@ -5873,45 +6119,48 @@
         <v>0</v>
       </c>
       <c r="Y45" s="23">
-        <v>54050001</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="23" t="s">
-        <v>34</v>
+        <v>54040001</v>
+      </c>
+      <c r="AA45" s="23">
+        <v>0</v>
       </c>
       <c r="AB45" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC45" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC45" s="23" t="s">
+      <c r="AD45" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A46" s="23">
-        <v>54110001</v>
+        <v>54090001</v>
       </c>
       <c r="B46" s="23">
         <v>4</v>
       </c>
       <c r="C46" s="23">
-        <v>5411</v>
+        <v>5409</v>
       </c>
       <c r="D46" s="23">
         <v>1</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G46" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I46" s="23">
         <v>0</v>
@@ -5962,45 +6211,48 @@
         <v>0</v>
       </c>
       <c r="Y46" s="23">
-        <v>54060001</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="23" t="s">
-        <v>34</v>
+        <v>54050001</v>
+      </c>
+      <c r="AA46" s="23">
+        <v>0</v>
       </c>
       <c r="AB46" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC46" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC46" s="23" t="s">
+      <c r="AD46" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A47" s="23">
-        <v>54130001</v>
+        <v>54110001</v>
       </c>
       <c r="B47" s="23">
         <v>4</v>
       </c>
       <c r="C47" s="23">
-        <v>5413</v>
+        <v>5411</v>
       </c>
       <c r="D47" s="23">
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G47" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I47" s="23">
         <v>0</v>
@@ -6051,45 +6303,48 @@
         <v>0</v>
       </c>
       <c r="Y47" s="23">
-        <v>54070001</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="23" t="s">
-        <v>34</v>
+        <v>54060001</v>
+      </c>
+      <c r="AA47" s="23">
+        <v>0</v>
       </c>
       <c r="AB47" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC47" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC47" s="23" t="s">
+      <c r="AD47" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A48" s="23">
-        <v>54150001</v>
+        <v>54130001</v>
       </c>
       <c r="B48" s="23">
         <v>4</v>
       </c>
       <c r="C48" s="23">
-        <v>5415</v>
+        <v>5413</v>
       </c>
       <c r="D48" s="23">
         <v>1</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G48" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I48" s="23">
         <v>0</v>
@@ -6140,45 +6395,48 @@
         <v>0</v>
       </c>
       <c r="Y48" s="23">
-        <v>54080001</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="23" t="s">
-        <v>34</v>
+        <v>54070001</v>
+      </c>
+      <c r="AA48" s="23">
+        <v>0</v>
       </c>
       <c r="AB48" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC48" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC48" s="23" t="s">
+      <c r="AD48" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A49" s="23">
-        <v>54170001</v>
+        <v>54150001</v>
       </c>
       <c r="B49" s="23">
         <v>4</v>
       </c>
       <c r="C49" s="23">
-        <v>5417</v>
+        <v>5415</v>
       </c>
       <c r="D49" s="23">
         <v>1</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G49" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="I49" s="23">
         <v>0</v>
@@ -6232,42 +6490,45 @@
         <v>0</v>
       </c>
       <c r="Z49" s="23">
-        <v>54090001</v>
-      </c>
-      <c r="AA49" s="23" t="s">
-        <v>34</v>
+        <v>54080001</v>
+      </c>
+      <c r="AA49" s="23">
+        <v>0</v>
       </c>
       <c r="AB49" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC49" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC49" s="23" t="s">
+      <c r="AD49" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A50" s="23">
-        <v>54190001</v>
+        <v>54170001</v>
       </c>
       <c r="B50" s="23">
         <v>4</v>
       </c>
       <c r="C50" s="23">
-        <v>5419</v>
+        <v>5417</v>
       </c>
       <c r="D50" s="23">
         <v>1</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G50" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="I50" s="23">
         <v>0</v>
@@ -6318,45 +6579,48 @@
         <v>0</v>
       </c>
       <c r="Y50" s="23">
-        <v>54100001</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="23">
         <v>0</v>
       </c>
-      <c r="AA50" s="23" t="s">
-        <v>34</v>
+      <c r="AA50" s="23">
+        <v>54090001</v>
       </c>
       <c r="AB50" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC50" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC50" s="23" t="s">
+      <c r="AD50" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A51" s="23">
-        <v>54210001</v>
+        <v>54190001</v>
       </c>
       <c r="B51" s="23">
         <v>4</v>
       </c>
       <c r="C51" s="23">
-        <v>5421</v>
+        <v>5419</v>
       </c>
       <c r="D51" s="23">
         <v>1</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I51" s="23">
         <v>0</v>
@@ -6410,42 +6674,45 @@
         <v>0</v>
       </c>
       <c r="Z51" s="23">
-        <v>54110001</v>
-      </c>
-      <c r="AA51" s="23" t="s">
-        <v>34</v>
+        <v>54100001</v>
+      </c>
+      <c r="AA51" s="23">
+        <v>0</v>
       </c>
       <c r="AB51" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC51" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC51" s="23" t="s">
+      <c r="AD51" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A52" s="23">
-        <v>54230001</v>
+        <v>54210001</v>
       </c>
       <c r="B52" s="23">
         <v>4</v>
       </c>
       <c r="C52" s="23">
-        <v>5423</v>
+        <v>5421</v>
       </c>
       <c r="D52" s="23">
         <v>1</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G52" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I52" s="23">
         <v>0</v>
@@ -6496,30 +6763,33 @@
         <v>0</v>
       </c>
       <c r="Y52" s="23">
-        <v>54120001</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="23">
         <v>0</v>
       </c>
-      <c r="AA52" s="23" t="s">
-        <v>34</v>
+      <c r="AA52" s="23">
+        <v>54110001</v>
       </c>
       <c r="AB52" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC52" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC52" s="23" t="s">
+      <c r="AD52" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A53" s="23">
-        <v>54250001</v>
+        <v>54230001</v>
       </c>
       <c r="B53" s="23">
         <v>4</v>
       </c>
       <c r="C53" s="23">
-        <v>5425</v>
+        <v>5423</v>
       </c>
       <c r="D53" s="23">
         <v>1</v>
@@ -6528,191 +6798,197 @@
         <v>157</v>
       </c>
       <c r="F53" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" s="23">
+        <v>0</v>
+      </c>
+      <c r="J53" s="23">
+        <v>0</v>
+      </c>
+      <c r="K53" s="23">
+        <v>0</v>
+      </c>
+      <c r="L53" s="23">
+        <v>0</v>
+      </c>
+      <c r="M53" s="23">
+        <v>0</v>
+      </c>
+      <c r="N53" s="23">
+        <v>0</v>
+      </c>
+      <c r="O53" s="23">
+        <v>0</v>
+      </c>
+      <c r="P53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="23">
+        <v>0</v>
+      </c>
+      <c r="R53" s="23">
+        <v>0</v>
+      </c>
+      <c r="S53" s="23">
+        <v>0</v>
+      </c>
+      <c r="T53" s="23">
+        <v>0</v>
+      </c>
+      <c r="U53" s="23">
+        <v>0</v>
+      </c>
+      <c r="V53" s="23">
+        <v>0</v>
+      </c>
+      <c r="W53" s="23">
+        <v>0</v>
+      </c>
+      <c r="X53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="23">
+        <v>54120001</v>
+      </c>
+      <c r="AA53" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC53" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD53" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A54" s="23">
+        <v>54250001</v>
+      </c>
+      <c r="B54" s="23">
+        <v>4</v>
+      </c>
+      <c r="C54" s="23">
+        <v>5425</v>
+      </c>
+      <c r="D54" s="23">
+        <v>1</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F54" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="G53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H53" s="23" t="s">
+      <c r="G54" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="I53" s="23">
-        <v>0</v>
-      </c>
-      <c r="J53" s="23">
-        <v>0</v>
-      </c>
-      <c r="K53" s="23">
-        <v>0</v>
-      </c>
-      <c r="L53" s="23">
-        <v>0</v>
-      </c>
-      <c r="M53" s="23">
-        <v>0</v>
-      </c>
-      <c r="N53" s="23">
-        <v>0</v>
-      </c>
-      <c r="O53" s="23">
-        <v>0</v>
-      </c>
-      <c r="P53" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="23">
-        <v>0</v>
-      </c>
-      <c r="R53" s="23">
-        <v>0</v>
-      </c>
-      <c r="S53" s="23">
-        <v>0</v>
-      </c>
-      <c r="T53" s="23">
-        <v>0</v>
-      </c>
-      <c r="U53" s="23">
-        <v>0</v>
-      </c>
-      <c r="V53" s="23">
-        <v>0</v>
-      </c>
-      <c r="W53" s="23">
-        <v>0</v>
-      </c>
-      <c r="X53" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="23">
+      <c r="I54" s="23">
+        <v>0</v>
+      </c>
+      <c r="J54" s="23">
+        <v>0</v>
+      </c>
+      <c r="K54" s="23">
+        <v>0</v>
+      </c>
+      <c r="L54" s="23">
+        <v>0</v>
+      </c>
+      <c r="M54" s="23">
+        <v>0</v>
+      </c>
+      <c r="N54" s="23">
+        <v>0</v>
+      </c>
+      <c r="O54" s="23">
+        <v>0</v>
+      </c>
+      <c r="P54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="23">
+        <v>0</v>
+      </c>
+      <c r="R54" s="23">
+        <v>0</v>
+      </c>
+      <c r="S54" s="23">
+        <v>0</v>
+      </c>
+      <c r="T54" s="23">
+        <v>0</v>
+      </c>
+      <c r="U54" s="23">
+        <v>0</v>
+      </c>
+      <c r="V54" s="23">
+        <v>0</v>
+      </c>
+      <c r="W54" s="23">
+        <v>0</v>
+      </c>
+      <c r="X54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="23">
         <v>54130001</v>
       </c>
-      <c r="Z53" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB53" s="23" t="s">
+      <c r="AA54" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC54" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC53" s="23" t="s">
+      <c r="AD54" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A54" s="13">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A55" s="13">
         <v>55010001</v>
-      </c>
-      <c r="B54" s="13">
-        <v>4</v>
-      </c>
-      <c r="C54" s="13">
-        <v>5501</v>
-      </c>
-      <c r="D54" s="13">
-        <v>1</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="I54" s="13">
-        <v>0</v>
-      </c>
-      <c r="J54" s="13">
-        <v>0</v>
-      </c>
-      <c r="K54" s="13">
-        <v>0</v>
-      </c>
-      <c r="L54" s="13">
-        <v>0</v>
-      </c>
-      <c r="M54" s="13">
-        <v>0</v>
-      </c>
-      <c r="N54" s="13">
-        <v>0</v>
-      </c>
-      <c r="O54" s="13">
-        <v>0</v>
-      </c>
-      <c r="P54" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="13">
-        <v>0</v>
-      </c>
-      <c r="R54" s="13">
-        <v>0</v>
-      </c>
-      <c r="S54" s="13">
-        <v>0</v>
-      </c>
-      <c r="T54" s="13">
-        <v>0</v>
-      </c>
-      <c r="U54" s="13">
-        <v>0</v>
-      </c>
-      <c r="V54" s="13">
-        <v>10000</v>
-      </c>
-      <c r="W54" s="13">
-        <v>0</v>
-      </c>
-      <c r="X54" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Y54" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="13">
-        <v>55010001</v>
-      </c>
-      <c r="AA54" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB54" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC54" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A55" s="13">
-        <v>55020001</v>
       </c>
       <c r="B55" s="13">
         <v>4</v>
       </c>
       <c r="C55" s="13">
-        <v>5502</v>
+        <v>5501</v>
       </c>
       <c r="D55" s="13">
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
@@ -6751,57 +7027,60 @@
         <v>0</v>
       </c>
       <c r="U55" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W55" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X55" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y55" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="13">
+        <v>55010001</v>
+      </c>
+      <c r="AB55" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC55" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD55" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A56" s="13">
         <v>55020001</v>
-      </c>
-      <c r="Z55" s="13">
-        <v>55010001</v>
-      </c>
-      <c r="AA55" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB55" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC55" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A56" s="13">
-        <v>55030001</v>
       </c>
       <c r="B56" s="13">
         <v>4</v>
       </c>
       <c r="C56" s="13">
-        <v>5503</v>
+        <v>5502</v>
       </c>
       <c r="D56" s="13">
         <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I56" s="13">
         <v>0</v>
@@ -6840,57 +7119,60 @@
         <v>0</v>
       </c>
       <c r="U56" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W56" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X56" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z56" s="13">
+        <v>55020001</v>
+      </c>
+      <c r="AA56" s="13">
+        <v>55010001</v>
+      </c>
+      <c r="AB56" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC56" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD56" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A57" s="13">
         <v>55030001</v>
-      </c>
-      <c r="Z56" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB56" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC56" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A57" s="13">
-        <v>55040001</v>
       </c>
       <c r="B57" s="13">
         <v>4</v>
       </c>
       <c r="C57" s="13">
-        <v>5504</v>
+        <v>5503</v>
       </c>
       <c r="D57" s="13">
         <v>1</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -6929,57 +7211,60 @@
         <v>0</v>
       </c>
       <c r="U57" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W57" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X57" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z57" s="13">
+        <v>55030001</v>
+      </c>
+      <c r="AA57" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC57" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD57" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A58" s="13">
         <v>55040001</v>
-      </c>
-      <c r="Z57" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB57" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC57" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A58" s="13">
-        <v>55050001</v>
       </c>
       <c r="B58" s="13">
         <v>4</v>
       </c>
       <c r="C58" s="13">
-        <v>5505</v>
+        <v>5504</v>
       </c>
       <c r="D58" s="13">
         <v>1</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I58" s="13">
         <v>0</v>
@@ -7018,57 +7303,60 @@
         <v>0</v>
       </c>
       <c r="U58" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W58" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X58" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z58" s="13">
+        <v>55040001</v>
+      </c>
+      <c r="AA58" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC58" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD58" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A59" s="13">
         <v>55050001</v>
-      </c>
-      <c r="AA58" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB58" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC58" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A59" s="13">
-        <v>55060001</v>
       </c>
       <c r="B59" s="13">
         <v>4</v>
       </c>
       <c r="C59" s="13">
-        <v>5506</v>
+        <v>5505</v>
       </c>
       <c r="D59" s="13">
         <v>1</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="I59" s="13">
         <v>0</v>
@@ -7107,235 +7395,244 @@
         <v>0</v>
       </c>
       <c r="U59" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W59" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X59" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z59" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="13">
+        <v>55050001</v>
+      </c>
+      <c r="AB59" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC59" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD59" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A60" s="13">
         <v>55060001</v>
-      </c>
-      <c r="Z59" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB59" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC59" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A60" s="13">
-        <v>55070001</v>
       </c>
       <c r="B60" s="13">
         <v>4</v>
       </c>
       <c r="C60" s="13">
+        <v>5506</v>
+      </c>
+      <c r="D60" s="13">
+        <v>1</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="I60" s="13">
+        <v>0</v>
+      </c>
+      <c r="J60" s="13">
+        <v>0</v>
+      </c>
+      <c r="K60" s="13">
+        <v>0</v>
+      </c>
+      <c r="L60" s="13">
+        <v>0</v>
+      </c>
+      <c r="M60" s="13">
+        <v>0</v>
+      </c>
+      <c r="N60" s="13">
+        <v>0</v>
+      </c>
+      <c r="O60" s="13">
+        <v>0</v>
+      </c>
+      <c r="P60" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="13">
+        <v>0</v>
+      </c>
+      <c r="R60" s="13">
+        <v>0</v>
+      </c>
+      <c r="S60" s="13">
+        <v>0</v>
+      </c>
+      <c r="T60" s="13">
+        <v>0</v>
+      </c>
+      <c r="U60" s="13">
+        <v>1</v>
+      </c>
+      <c r="V60" s="13">
+        <v>0</v>
+      </c>
+      <c r="W60" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X60" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z60" s="13">
+        <v>55060001</v>
+      </c>
+      <c r="AA60" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC60" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD60" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A61" s="13">
+        <v>55070001</v>
+      </c>
+      <c r="B61" s="13">
+        <v>4</v>
+      </c>
+      <c r="C61" s="13">
         <v>5507</v>
       </c>
-      <c r="D60" s="13">
-        <v>1</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="D61" s="13">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="13" t="s">
+      <c r="F61" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="G60" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H60" s="13" t="s">
+      <c r="G61" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="I60" s="13">
-        <v>0</v>
-      </c>
-      <c r="J60" s="13">
-        <v>0</v>
-      </c>
-      <c r="K60" s="13">
-        <v>0</v>
-      </c>
-      <c r="L60" s="13">
-        <v>0</v>
-      </c>
-      <c r="M60" s="13">
-        <v>0</v>
-      </c>
-      <c r="N60" s="13">
-        <v>0</v>
-      </c>
-      <c r="O60" s="13">
-        <v>0</v>
-      </c>
-      <c r="P60" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="13">
-        <v>0</v>
-      </c>
-      <c r="R60" s="13">
-        <v>0</v>
-      </c>
-      <c r="S60" s="13">
-        <v>0</v>
-      </c>
-      <c r="T60" s="13">
-        <v>0</v>
-      </c>
-      <c r="U60" s="13">
-        <v>0</v>
-      </c>
-      <c r="V60" s="13">
-        <v>10000</v>
-      </c>
-      <c r="W60" s="13">
-        <v>0</v>
-      </c>
-      <c r="X60" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Y60" s="13">
+      <c r="I61" s="13">
+        <v>0</v>
+      </c>
+      <c r="J61" s="13">
+        <v>0</v>
+      </c>
+      <c r="K61" s="13">
+        <v>0</v>
+      </c>
+      <c r="L61" s="13">
+        <v>0</v>
+      </c>
+      <c r="M61" s="13">
+        <v>0</v>
+      </c>
+      <c r="N61" s="13">
+        <v>0</v>
+      </c>
+      <c r="O61" s="13">
+        <v>0</v>
+      </c>
+      <c r="P61" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="13">
+        <v>0</v>
+      </c>
+      <c r="R61" s="13">
+        <v>0</v>
+      </c>
+      <c r="S61" s="13">
+        <v>0</v>
+      </c>
+      <c r="T61" s="13">
+        <v>0</v>
+      </c>
+      <c r="U61" s="13">
+        <v>1</v>
+      </c>
+      <c r="V61" s="13">
+        <v>0</v>
+      </c>
+      <c r="W61" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X61" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z61" s="13">
         <v>55070001</v>
       </c>
-      <c r="Z60" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB60" s="13" t="s">
+      <c r="AA61" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC61" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="AC60" s="13" t="s">
+      <c r="AD61" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A61" s="14">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A62" s="14">
         <v>56010001</v>
-      </c>
-      <c r="B61" s="14">
-        <v>4</v>
-      </c>
-      <c r="C61" s="14">
-        <v>5601</v>
-      </c>
-      <c r="D61" s="14">
-        <v>1</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I61" s="14">
-        <v>0</v>
-      </c>
-      <c r="J61" s="14">
-        <v>0</v>
-      </c>
-      <c r="K61" s="14">
-        <v>0</v>
-      </c>
-      <c r="L61" s="14">
-        <v>0</v>
-      </c>
-      <c r="M61" s="14">
-        <v>0</v>
-      </c>
-      <c r="N61" s="14">
-        <v>0</v>
-      </c>
-      <c r="O61" s="14">
-        <v>0</v>
-      </c>
-      <c r="P61" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="14">
-        <v>0</v>
-      </c>
-      <c r="R61" s="14">
-        <v>0</v>
-      </c>
-      <c r="S61" s="14">
-        <v>0</v>
-      </c>
-      <c r="T61" s="14">
-        <v>0</v>
-      </c>
-      <c r="U61" s="14">
-        <v>0</v>
-      </c>
-      <c r="V61" s="14">
-        <v>10000</v>
-      </c>
-      <c r="W61" s="14">
-        <v>0</v>
-      </c>
-      <c r="X61" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Y61" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="14">
-        <v>56010001</v>
-      </c>
-      <c r="AA61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB61" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC61" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A62" s="14">
-        <v>56040001</v>
       </c>
       <c r="B62" s="14">
         <v>4</v>
       </c>
       <c r="C62" s="14">
-        <v>5604</v>
+        <v>5601</v>
       </c>
       <c r="D62" s="14">
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I62" s="14">
         <v>0</v>
@@ -7374,57 +7671,60 @@
         <v>0</v>
       </c>
       <c r="U62" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V62" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W62" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X62" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z62" s="14">
         <v>0</v>
       </c>
-      <c r="AA62" s="14" t="s">
-        <v>34</v>
+      <c r="AA62" s="14">
+        <v>56010001</v>
       </c>
       <c r="AB62" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC62" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC62" s="14" t="s">
+      <c r="AD62" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A63" s="14">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B63" s="14">
         <v>4</v>
       </c>
       <c r="C63" s="14">
-        <v>5606</v>
+        <v>5604</v>
       </c>
       <c r="D63" s="14">
         <v>1</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I63" s="14">
         <v>0</v>
@@ -7463,57 +7763,60 @@
         <v>0</v>
       </c>
       <c r="U63" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V63" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W63" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X63" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y63" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z63" s="14">
-        <v>56030001</v>
-      </c>
-      <c r="AA63" s="14" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="AA63" s="14">
+        <v>0</v>
       </c>
       <c r="AB63" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC63" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC63" s="14" t="s">
+      <c r="AD63" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A64" s="14">
-        <v>56080001</v>
+        <v>56060001</v>
       </c>
       <c r="B64" s="14">
         <v>4</v>
       </c>
       <c r="C64" s="14">
-        <v>5608</v>
+        <v>5606</v>
       </c>
       <c r="D64" s="14">
         <v>1</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G64" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I64" s="14">
         <v>0</v>
@@ -7552,57 +7855,60 @@
         <v>0</v>
       </c>
       <c r="U64" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V64" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W64" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X64" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="14">
-        <v>56040001</v>
+        <v>10000</v>
       </c>
       <c r="Z64" s="14">
         <v>0</v>
       </c>
-      <c r="AA64" s="14" t="s">
-        <v>34</v>
+      <c r="AA64" s="14">
+        <v>56030001</v>
       </c>
       <c r="AB64" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC64" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC64" s="14" t="s">
+      <c r="AD64" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A65" s="14">
-        <v>56100001</v>
+        <v>56080001</v>
       </c>
       <c r="B65" s="14">
         <v>4</v>
       </c>
       <c r="C65" s="14">
-        <v>5610</v>
+        <v>5608</v>
       </c>
       <c r="D65" s="14">
         <v>1</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>291</v>
+        <v>228</v>
       </c>
       <c r="G65" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="I65" s="14">
         <v>0</v>
@@ -7641,42 +7947,45 @@
         <v>0</v>
       </c>
       <c r="U65" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V65" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W65" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X65" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y65" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z65" s="14">
-        <v>56050001</v>
-      </c>
-      <c r="AA65" s="14" t="s">
-        <v>34</v>
+        <v>56040001</v>
+      </c>
+      <c r="AA65" s="14">
+        <v>0</v>
       </c>
       <c r="AB65" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC65" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC65" s="14" t="s">
+      <c r="AD65" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A66" s="14">
-        <v>56130001</v>
+        <v>56100001</v>
       </c>
       <c r="B66" s="14">
         <v>4</v>
       </c>
       <c r="C66" s="14">
-        <v>5613</v>
+        <v>5610</v>
       </c>
       <c r="D66" s="14">
         <v>1</v>
@@ -7685,191 +7994,197 @@
         <v>140</v>
       </c>
       <c r="F66" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="I66" s="14">
+        <v>0</v>
+      </c>
+      <c r="J66" s="14">
+        <v>0</v>
+      </c>
+      <c r="K66" s="14">
+        <v>0</v>
+      </c>
+      <c r="L66" s="14">
+        <v>0</v>
+      </c>
+      <c r="M66" s="14">
+        <v>0</v>
+      </c>
+      <c r="N66" s="14">
+        <v>0</v>
+      </c>
+      <c r="O66" s="14">
+        <v>0</v>
+      </c>
+      <c r="P66" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="14">
+        <v>0</v>
+      </c>
+      <c r="R66" s="14">
+        <v>0</v>
+      </c>
+      <c r="S66" s="14">
+        <v>0</v>
+      </c>
+      <c r="T66" s="14">
+        <v>0</v>
+      </c>
+      <c r="U66" s="14">
+        <v>2</v>
+      </c>
+      <c r="V66" s="14">
+        <v>0</v>
+      </c>
+      <c r="W66" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X66" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="14">
+        <v>56050001</v>
+      </c>
+      <c r="AB66" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC66" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD66" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A67" s="14">
+        <v>56130001</v>
+      </c>
+      <c r="B67" s="14">
+        <v>4</v>
+      </c>
+      <c r="C67" s="14">
+        <v>5613</v>
+      </c>
+      <c r="D67" s="14">
+        <v>1</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="G66" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H66" s="14" t="s">
+      <c r="G67" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="I66" s="14">
-        <v>0</v>
-      </c>
-      <c r="J66" s="14">
-        <v>0</v>
-      </c>
-      <c r="K66" s="14">
-        <v>0</v>
-      </c>
-      <c r="L66" s="14">
-        <v>0</v>
-      </c>
-      <c r="M66" s="14">
-        <v>0</v>
-      </c>
-      <c r="N66" s="14">
-        <v>0</v>
-      </c>
-      <c r="O66" s="14">
-        <v>0</v>
-      </c>
-      <c r="P66" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="14">
-        <v>0</v>
-      </c>
-      <c r="R66" s="14">
-        <v>0</v>
-      </c>
-      <c r="S66" s="14">
-        <v>0</v>
-      </c>
-      <c r="T66" s="14">
-        <v>0</v>
-      </c>
-      <c r="U66" s="14">
-        <v>0</v>
-      </c>
-      <c r="V66" s="14">
-        <v>10000</v>
-      </c>
-      <c r="W66" s="14">
-        <v>0</v>
-      </c>
-      <c r="X66" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Y66" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="14">
+      <c r="I67" s="14">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14">
+        <v>0</v>
+      </c>
+      <c r="K67" s="14">
+        <v>0</v>
+      </c>
+      <c r="L67" s="14">
+        <v>0</v>
+      </c>
+      <c r="M67" s="14">
+        <v>0</v>
+      </c>
+      <c r="N67" s="14">
+        <v>0</v>
+      </c>
+      <c r="O67" s="14">
+        <v>0</v>
+      </c>
+      <c r="P67" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="14">
+        <v>0</v>
+      </c>
+      <c r="R67" s="14">
+        <v>0</v>
+      </c>
+      <c r="S67" s="14">
+        <v>0</v>
+      </c>
+      <c r="T67" s="14">
+        <v>0</v>
+      </c>
+      <c r="U67" s="14">
+        <v>2</v>
+      </c>
+      <c r="V67" s="14">
+        <v>0</v>
+      </c>
+      <c r="W67" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X67" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="14">
         <v>56060001</v>
       </c>
-      <c r="AA66" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB66" s="14" t="s">
+      <c r="AB67" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC67" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC66" s="14" t="s">
+      <c r="AD67" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A67" s="15">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A68" s="15">
         <v>57010001</v>
-      </c>
-      <c r="B67" s="15">
-        <v>4</v>
-      </c>
-      <c r="C67" s="15">
-        <v>5701</v>
-      </c>
-      <c r="D67" s="15">
-        <v>1</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="G67" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="I67" s="15">
-        <v>0</v>
-      </c>
-      <c r="J67" s="15">
-        <v>0</v>
-      </c>
-      <c r="K67" s="15">
-        <v>0</v>
-      </c>
-      <c r="L67" s="15">
-        <v>0</v>
-      </c>
-      <c r="M67" s="15">
-        <v>0</v>
-      </c>
-      <c r="N67" s="15">
-        <v>0</v>
-      </c>
-      <c r="O67" s="15">
-        <v>0</v>
-      </c>
-      <c r="P67" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="15">
-        <v>0</v>
-      </c>
-      <c r="R67" s="15">
-        <v>0</v>
-      </c>
-      <c r="S67" s="15">
-        <v>0</v>
-      </c>
-      <c r="T67" s="15">
-        <v>0</v>
-      </c>
-      <c r="U67" s="15">
-        <v>0</v>
-      </c>
-      <c r="V67" s="15">
-        <v>10000</v>
-      </c>
-      <c r="W67" s="15">
-        <v>0</v>
-      </c>
-      <c r="X67" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Y67" s="15">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="15">
-        <v>57010001</v>
-      </c>
-      <c r="AA67" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB67" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC67" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A68" s="15">
-        <v>57040001</v>
       </c>
       <c r="B68" s="15">
         <v>4</v>
       </c>
       <c r="C68" s="15">
-        <v>5704</v>
+        <v>5701</v>
       </c>
       <c r="D68" s="15">
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G68" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I68" s="15">
         <v>0</v>
@@ -7908,57 +8223,60 @@
         <v>0</v>
       </c>
       <c r="U68" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V68" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W68" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X68" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="15">
-        <v>57020001</v>
+        <v>10000</v>
       </c>
       <c r="Z68" s="15">
         <v>0</v>
       </c>
-      <c r="AA68" s="15" t="s">
-        <v>34</v>
+      <c r="AA68" s="15">
+        <v>57010001</v>
       </c>
       <c r="AB68" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC68" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC68" s="15" t="s">
+      <c r="AD68" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B69" s="15">
         <v>4</v>
       </c>
       <c r="C69" s="15">
-        <v>5706</v>
+        <v>5704</v>
       </c>
       <c r="D69" s="15">
         <v>1</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G69" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I69" s="15">
         <v>0</v>
@@ -7997,57 +8315,60 @@
         <v>0</v>
       </c>
       <c r="U69" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V69" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W69" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X69" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y69" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z69" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="15" t="s">
-        <v>34</v>
+        <v>57020001</v>
+      </c>
+      <c r="AA69" s="15">
+        <v>0</v>
       </c>
       <c r="AB69" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC69" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC69" s="15" t="s">
+      <c r="AD69" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A70" s="15">
-        <v>57080001</v>
+        <v>57060001</v>
       </c>
       <c r="B70" s="15">
         <v>4</v>
       </c>
       <c r="C70" s="15">
-        <v>5708</v>
+        <v>5706</v>
       </c>
       <c r="D70" s="15">
         <v>1</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>293</v>
+        <v>231</v>
       </c>
       <c r="G70" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
@@ -8086,57 +8407,60 @@
         <v>0</v>
       </c>
       <c r="U70" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V70" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X70" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z70" s="15">
-        <v>57040001</v>
-      </c>
-      <c r="AA70" s="15" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="AA70" s="15">
+        <v>0</v>
       </c>
       <c r="AB70" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC70" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC70" s="15" t="s">
+      <c r="AD70" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A71" s="15">
-        <v>57100001</v>
+        <v>57080001</v>
       </c>
       <c r="B71" s="15">
         <v>4</v>
       </c>
       <c r="C71" s="15">
-        <v>5710</v>
+        <v>5708</v>
       </c>
       <c r="D71" s="15">
         <v>1</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -8175,235 +8499,244 @@
         <v>0</v>
       </c>
       <c r="U71" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V71" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W71" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X71" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y71" s="15">
-        <v>57050001</v>
+        <v>10000</v>
       </c>
       <c r="Z71" s="15">
         <v>0</v>
       </c>
-      <c r="AA71" s="15" t="s">
-        <v>34</v>
+      <c r="AA71" s="15">
+        <v>57040001</v>
       </c>
       <c r="AB71" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC71" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC71" s="15" t="s">
+      <c r="AD71" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A72" s="15">
-        <v>57120001</v>
+        <v>57100001</v>
       </c>
       <c r="B72" s="15">
         <v>4</v>
       </c>
       <c r="C72" s="15">
+        <v>5710</v>
+      </c>
+      <c r="D72" s="15">
+        <v>1</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="I72" s="15">
+        <v>0</v>
+      </c>
+      <c r="J72" s="15">
+        <v>0</v>
+      </c>
+      <c r="K72" s="15">
+        <v>0</v>
+      </c>
+      <c r="L72" s="15">
+        <v>0</v>
+      </c>
+      <c r="M72" s="15">
+        <v>0</v>
+      </c>
+      <c r="N72" s="15">
+        <v>0</v>
+      </c>
+      <c r="O72" s="15">
+        <v>0</v>
+      </c>
+      <c r="P72" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="15">
+        <v>0</v>
+      </c>
+      <c r="R72" s="15">
+        <v>0</v>
+      </c>
+      <c r="S72" s="15">
+        <v>0</v>
+      </c>
+      <c r="T72" s="15">
+        <v>0</v>
+      </c>
+      <c r="U72" s="15">
+        <v>3</v>
+      </c>
+      <c r="V72" s="15">
+        <v>0</v>
+      </c>
+      <c r="W72" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X72" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z72" s="15">
+        <v>57050001</v>
+      </c>
+      <c r="AA72" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC72" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD72" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A73" s="15">
+        <v>57120001</v>
+      </c>
+      <c r="B73" s="15">
+        <v>4</v>
+      </c>
+      <c r="C73" s="15">
         <v>5712</v>
       </c>
-      <c r="D72" s="15">
-        <v>1</v>
-      </c>
-      <c r="E72" s="12" t="s">
+      <c r="D73" s="15">
+        <v>1</v>
+      </c>
+      <c r="E73" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F72" s="15" t="s">
+      <c r="F73" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="G72" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H72" s="15" t="s">
+      <c r="G73" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="I72" s="15">
-        <v>0</v>
-      </c>
-      <c r="J72" s="15">
-        <v>0</v>
-      </c>
-      <c r="K72" s="15">
-        <v>0</v>
-      </c>
-      <c r="L72" s="15">
-        <v>0</v>
-      </c>
-      <c r="M72" s="15">
-        <v>0</v>
-      </c>
-      <c r="N72" s="15">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15">
-        <v>0</v>
-      </c>
-      <c r="P72" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="15">
-        <v>0</v>
-      </c>
-      <c r="R72" s="15">
-        <v>0</v>
-      </c>
-      <c r="S72" s="15">
-        <v>0</v>
-      </c>
-      <c r="T72" s="15">
-        <v>0</v>
-      </c>
-      <c r="U72" s="15">
-        <v>0</v>
-      </c>
-      <c r="V72" s="15">
-        <v>10000</v>
-      </c>
-      <c r="W72" s="15">
-        <v>0</v>
-      </c>
-      <c r="X72" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Y72" s="15">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="15">
+      <c r="I73" s="15">
+        <v>0</v>
+      </c>
+      <c r="J73" s="15">
+        <v>0</v>
+      </c>
+      <c r="K73" s="15">
+        <v>0</v>
+      </c>
+      <c r="L73" s="15">
+        <v>0</v>
+      </c>
+      <c r="M73" s="15">
+        <v>0</v>
+      </c>
+      <c r="N73" s="15">
+        <v>0</v>
+      </c>
+      <c r="O73" s="15">
+        <v>0</v>
+      </c>
+      <c r="P73" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="15">
+        <v>0</v>
+      </c>
+      <c r="R73" s="15">
+        <v>0</v>
+      </c>
+      <c r="S73" s="15">
+        <v>0</v>
+      </c>
+      <c r="T73" s="15">
+        <v>0</v>
+      </c>
+      <c r="U73" s="15">
+        <v>3</v>
+      </c>
+      <c r="V73" s="15">
+        <v>0</v>
+      </c>
+      <c r="W73" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X73" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z73" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="15">
         <v>57060001</v>
       </c>
-      <c r="AA72" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB72" s="15" t="s">
+      <c r="AB73" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC73" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC72" s="15" t="s">
+      <c r="AD73" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A73" s="16">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A74" s="16">
         <v>58010001</v>
-      </c>
-      <c r="B73" s="16">
-        <v>4</v>
-      </c>
-      <c r="C73" s="16">
-        <v>5801</v>
-      </c>
-      <c r="D73" s="16">
-        <v>1</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="F73" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H73" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="I73" s="16">
-        <v>0</v>
-      </c>
-      <c r="J73" s="16">
-        <v>0</v>
-      </c>
-      <c r="K73" s="16">
-        <v>0</v>
-      </c>
-      <c r="L73" s="16">
-        <v>0</v>
-      </c>
-      <c r="M73" s="16">
-        <v>0</v>
-      </c>
-      <c r="N73" s="16">
-        <v>0</v>
-      </c>
-      <c r="O73" s="16">
-        <v>0</v>
-      </c>
-      <c r="P73" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="16">
-        <v>0</v>
-      </c>
-      <c r="R73" s="16">
-        <v>0</v>
-      </c>
-      <c r="S73" s="16">
-        <v>0</v>
-      </c>
-      <c r="T73" s="16">
-        <v>0</v>
-      </c>
-      <c r="U73" s="16">
-        <v>0</v>
-      </c>
-      <c r="V73" s="16">
-        <v>10000</v>
-      </c>
-      <c r="W73" s="16">
-        <v>0</v>
-      </c>
-      <c r="X73" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Y73" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z73" s="16">
-        <v>58010001</v>
-      </c>
-      <c r="AA73" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB73" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC73" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A74" s="16">
-        <v>58040001</v>
       </c>
       <c r="B74" s="16">
         <v>4</v>
       </c>
       <c r="C74" s="16">
-        <v>5804</v>
+        <v>5801</v>
       </c>
       <c r="D74" s="16">
         <v>1</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G74" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I74" s="16">
         <v>0</v>
@@ -8442,57 +8775,60 @@
         <v>0</v>
       </c>
       <c r="U74" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V74" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W74" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X74" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z74" s="16">
         <v>0</v>
       </c>
-      <c r="AA74" s="16" t="s">
-        <v>34</v>
+      <c r="AA74" s="16">
+        <v>58010001</v>
       </c>
       <c r="AB74" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC74" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC74" s="16" t="s">
+      <c r="AD74" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A75" s="16">
-        <v>58060001</v>
+        <v>58040001</v>
       </c>
       <c r="B75" s="16">
         <v>4</v>
       </c>
       <c r="C75" s="16">
-        <v>5806</v>
+        <v>5804</v>
       </c>
       <c r="D75" s="16">
         <v>1</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I75" s="16">
         <v>0</v>
@@ -8531,57 +8867,60 @@
         <v>0</v>
       </c>
       <c r="U75" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V75" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W75" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X75" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y75" s="16">
-        <v>58030001</v>
+        <v>10000</v>
       </c>
       <c r="Z75" s="16">
         <v>0</v>
       </c>
-      <c r="AA75" s="16" t="s">
-        <v>34</v>
+      <c r="AA75" s="16">
+        <v>0</v>
       </c>
       <c r="AB75" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC75" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC75" s="16" t="s">
+      <c r="AD75" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A76" s="16">
-        <v>58080001</v>
+        <v>58060001</v>
       </c>
       <c r="B76" s="16">
         <v>4</v>
       </c>
       <c r="C76" s="16">
-        <v>5808</v>
+        <v>5806</v>
       </c>
       <c r="D76" s="16">
         <v>1</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I76" s="16">
         <v>0</v>
@@ -8620,235 +8959,244 @@
         <v>0</v>
       </c>
       <c r="U76" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V76" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W76" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X76" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z76" s="16">
-        <v>58040001</v>
-      </c>
-      <c r="AA76" s="16" t="s">
-        <v>34</v>
+        <v>58030001</v>
+      </c>
+      <c r="AA76" s="16">
+        <v>0</v>
       </c>
       <c r="AB76" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC76" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC76" s="16" t="s">
+      <c r="AD76" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A77" s="16">
-        <v>58110001</v>
+        <v>58080001</v>
       </c>
       <c r="B77" s="16">
         <v>4</v>
       </c>
       <c r="C77" s="16">
+        <v>5808</v>
+      </c>
+      <c r="D77" s="16">
+        <v>1</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="I77" s="16">
+        <v>0</v>
+      </c>
+      <c r="J77" s="16">
+        <v>0</v>
+      </c>
+      <c r="K77" s="16">
+        <v>0</v>
+      </c>
+      <c r="L77" s="16">
+        <v>0</v>
+      </c>
+      <c r="M77" s="16">
+        <v>0</v>
+      </c>
+      <c r="N77" s="16">
+        <v>0</v>
+      </c>
+      <c r="O77" s="16">
+        <v>0</v>
+      </c>
+      <c r="P77" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="16">
+        <v>0</v>
+      </c>
+      <c r="R77" s="16">
+        <v>0</v>
+      </c>
+      <c r="S77" s="16">
+        <v>0</v>
+      </c>
+      <c r="T77" s="16">
+        <v>0</v>
+      </c>
+      <c r="U77" s="16">
+        <v>4</v>
+      </c>
+      <c r="V77" s="16">
+        <v>0</v>
+      </c>
+      <c r="W77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X77" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z77" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="16">
+        <v>58040001</v>
+      </c>
+      <c r="AB77" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD77" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A78" s="16">
+        <v>58110001</v>
+      </c>
+      <c r="B78" s="16">
+        <v>4</v>
+      </c>
+      <c r="C78" s="16">
         <v>5811</v>
       </c>
-      <c r="D77" s="16">
-        <v>1</v>
-      </c>
-      <c r="E77" s="12" t="s">
+      <c r="D78" s="16">
+        <v>1</v>
+      </c>
+      <c r="E78" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F77" s="16" t="s">
+      <c r="F78" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="G77" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H77" s="16" t="s">
+      <c r="G78" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="I77" s="16">
-        <v>0</v>
-      </c>
-      <c r="J77" s="16">
-        <v>0</v>
-      </c>
-      <c r="K77" s="16">
-        <v>0</v>
-      </c>
-      <c r="L77" s="16">
-        <v>0</v>
-      </c>
-      <c r="M77" s="16">
-        <v>0</v>
-      </c>
-      <c r="N77" s="16">
-        <v>0</v>
-      </c>
-      <c r="O77" s="16">
-        <v>0</v>
-      </c>
-      <c r="P77" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="16">
-        <v>0</v>
-      </c>
-      <c r="R77" s="16">
-        <v>0</v>
-      </c>
-      <c r="S77" s="16">
-        <v>0</v>
-      </c>
-      <c r="T77" s="16">
-        <v>0</v>
-      </c>
-      <c r="U77" s="16">
-        <v>0</v>
-      </c>
-      <c r="V77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="W77" s="16">
-        <v>0</v>
-      </c>
-      <c r="X77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Y77" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="16">
+      <c r="I78" s="16">
+        <v>0</v>
+      </c>
+      <c r="J78" s="16">
+        <v>0</v>
+      </c>
+      <c r="K78" s="16">
+        <v>0</v>
+      </c>
+      <c r="L78" s="16">
+        <v>0</v>
+      </c>
+      <c r="M78" s="16">
+        <v>0</v>
+      </c>
+      <c r="N78" s="16">
+        <v>0</v>
+      </c>
+      <c r="O78" s="16">
+        <v>0</v>
+      </c>
+      <c r="P78" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="16">
+        <v>0</v>
+      </c>
+      <c r="R78" s="16">
+        <v>0</v>
+      </c>
+      <c r="S78" s="16">
+        <v>0</v>
+      </c>
+      <c r="T78" s="16">
+        <v>0</v>
+      </c>
+      <c r="U78" s="16">
+        <v>4</v>
+      </c>
+      <c r="V78" s="16">
+        <v>0</v>
+      </c>
+      <c r="W78" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X78" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z78" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="16">
         <v>58050001</v>
       </c>
-      <c r="AA77" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB77" s="16" t="s">
+      <c r="AB78" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC78" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC77" s="16" t="s">
+      <c r="AD78" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A78" s="24">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A79" s="24">
         <v>59010001</v>
-      </c>
-      <c r="B78" s="24">
-        <v>4</v>
-      </c>
-      <c r="C78" s="24">
-        <v>5901</v>
-      </c>
-      <c r="D78" s="24">
-        <v>1</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F78" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="G78" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="I78" s="24">
-        <v>0</v>
-      </c>
-      <c r="J78" s="24">
-        <v>0</v>
-      </c>
-      <c r="K78" s="24">
-        <v>0</v>
-      </c>
-      <c r="L78" s="24">
-        <v>0</v>
-      </c>
-      <c r="M78" s="24">
-        <v>0</v>
-      </c>
-      <c r="N78" s="24">
-        <v>0</v>
-      </c>
-      <c r="O78" s="24">
-        <v>0</v>
-      </c>
-      <c r="P78" s="24">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="24">
-        <v>0</v>
-      </c>
-      <c r="R78" s="24">
-        <v>0</v>
-      </c>
-      <c r="S78" s="24">
-        <v>0</v>
-      </c>
-      <c r="T78" s="24">
-        <v>0</v>
-      </c>
-      <c r="U78" s="24">
-        <v>0</v>
-      </c>
-      <c r="V78" s="24">
-        <v>10000</v>
-      </c>
-      <c r="W78" s="24">
-        <v>0</v>
-      </c>
-      <c r="X78" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Y78" s="24">
-        <v>59010001</v>
-      </c>
-      <c r="Z78" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB78" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC78" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A79" s="24">
-        <v>59030001</v>
       </c>
       <c r="B79" s="24">
         <v>4</v>
       </c>
       <c r="C79" s="24">
-        <v>5903</v>
+        <v>5901</v>
       </c>
       <c r="D79" s="24">
         <v>1</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G79" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I79" s="24">
         <v>0</v>
@@ -8890,54 +9238,57 @@
         <v>0</v>
       </c>
       <c r="V79" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W79" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X79" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="24">
-        <v>59020001</v>
+        <v>10000</v>
       </c>
       <c r="Z79" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="24" t="s">
-        <v>34</v>
+        <v>59010001</v>
+      </c>
+      <c r="AA79" s="24">
+        <v>0</v>
       </c>
       <c r="AB79" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC79" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC79" s="24" t="s">
+      <c r="AD79" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A80" s="24">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B80" s="24">
         <v>4</v>
       </c>
       <c r="C80" s="24">
-        <v>5905</v>
+        <v>5903</v>
       </c>
       <c r="D80" s="24">
         <v>1</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G80" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>265</v>
+        <v>115</v>
       </c>
       <c r="I80" s="24">
         <v>0</v>
@@ -8979,54 +9330,57 @@
         <v>0</v>
       </c>
       <c r="V80" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W80" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X80" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="24">
-        <v>59030001</v>
+        <v>10000</v>
       </c>
       <c r="Z80" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="24" t="s">
-        <v>34</v>
+        <v>59020001</v>
+      </c>
+      <c r="AA80" s="24">
+        <v>0</v>
       </c>
       <c r="AB80" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC80" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC80" s="24" t="s">
+      <c r="AD80" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A81" s="24">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B81" s="24">
         <v>4</v>
       </c>
       <c r="C81" s="24">
-        <v>5907</v>
+        <v>5905</v>
       </c>
       <c r="D81" s="24">
         <v>1</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G81" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>183</v>
+        <v>265</v>
       </c>
       <c r="I81" s="24">
         <v>0</v>
@@ -9068,54 +9422,57 @@
         <v>0</v>
       </c>
       <c r="V81" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W81" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X81" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="24">
-        <v>59040001</v>
+        <v>10000</v>
       </c>
       <c r="Z81" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="24" t="s">
-        <v>34</v>
+        <v>59030001</v>
+      </c>
+      <c r="AA81" s="24">
+        <v>0</v>
       </c>
       <c r="AB81" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC81" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC81" s="24" t="s">
+      <c r="AD81" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A82" s="24">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B82" s="24">
         <v>4</v>
       </c>
       <c r="C82" s="24">
-        <v>5909</v>
+        <v>5907</v>
       </c>
       <c r="D82" s="24">
         <v>1</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G82" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I82" s="24">
         <v>0</v>
@@ -9157,54 +9514,57 @@
         <v>0</v>
       </c>
       <c r="V82" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W82" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X82" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y82" s="24">
-        <v>59050001</v>
+        <v>10000</v>
       </c>
       <c r="Z82" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="24" t="s">
-        <v>34</v>
+        <v>59040001</v>
+      </c>
+      <c r="AA82" s="24">
+        <v>0</v>
       </c>
       <c r="AB82" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC82" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC82" s="24" t="s">
+      <c r="AD82" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A83" s="24">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B83" s="24">
         <v>4</v>
       </c>
       <c r="C83" s="24">
-        <v>5911</v>
+        <v>5909</v>
       </c>
       <c r="D83" s="24">
         <v>1</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G83" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I83" s="24">
         <v>0</v>
@@ -9246,54 +9606,57 @@
         <v>0</v>
       </c>
       <c r="V83" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W83" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X83" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="24">
-        <v>59060001</v>
+        <v>10000</v>
       </c>
       <c r="Z83" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="24" t="s">
-        <v>34</v>
+        <v>59050001</v>
+      </c>
+      <c r="AA83" s="24">
+        <v>0</v>
       </c>
       <c r="AB83" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC83" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC83" s="24" t="s">
+      <c r="AD83" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A84" s="24">
-        <v>59130001</v>
+        <v>59110001</v>
       </c>
       <c r="B84" s="24">
         <v>4</v>
       </c>
       <c r="C84" s="24">
-        <v>5913</v>
+        <v>5911</v>
       </c>
       <c r="D84" s="24">
         <v>1</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G84" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I84" s="24">
         <v>0</v>
@@ -9335,54 +9698,57 @@
         <v>0</v>
       </c>
       <c r="V84" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W84" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X84" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y84" s="24">
-        <v>59070001</v>
+        <v>10000</v>
       </c>
       <c r="Z84" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="24" t="s">
-        <v>34</v>
+        <v>59060001</v>
+      </c>
+      <c r="AA84" s="24">
+        <v>0</v>
       </c>
       <c r="AB84" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC84" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC84" s="24" t="s">
+      <c r="AD84" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A85" s="24">
-        <v>59150001</v>
+        <v>59130001</v>
       </c>
       <c r="B85" s="24">
         <v>4</v>
       </c>
       <c r="C85" s="24">
-        <v>5915</v>
+        <v>5913</v>
       </c>
       <c r="D85" s="24">
         <v>1</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G85" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I85" s="24">
         <v>0</v>
@@ -9424,54 +9790,57 @@
         <v>0</v>
       </c>
       <c r="V85" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W85" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X85" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y85" s="24">
-        <v>59080001</v>
+        <v>10000</v>
       </c>
       <c r="Z85" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA85" s="24" t="s">
-        <v>34</v>
+        <v>59070001</v>
+      </c>
+      <c r="AA85" s="24">
+        <v>0</v>
       </c>
       <c r="AB85" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC85" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC85" s="24" t="s">
+      <c r="AD85" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A86" s="24">
-        <v>59180001</v>
+        <v>59150001</v>
       </c>
       <c r="B86" s="24">
         <v>4</v>
       </c>
       <c r="C86" s="24">
-        <v>5918</v>
+        <v>5915</v>
       </c>
       <c r="D86" s="24">
         <v>1</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G86" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I86" s="24">
         <v>0</v>
@@ -9513,54 +9882,57 @@
         <v>0</v>
       </c>
       <c r="V86" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W86" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X86" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y86" s="24">
-        <v>59090001</v>
+        <v>10000</v>
       </c>
       <c r="Z86" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA86" s="24" t="s">
-        <v>34</v>
+        <v>59080001</v>
+      </c>
+      <c r="AA86" s="24">
+        <v>0</v>
       </c>
       <c r="AB86" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC86" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC86" s="24" t="s">
+      <c r="AD86" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A87" s="24">
-        <v>59200001</v>
+        <v>59180001</v>
       </c>
       <c r="B87" s="24">
         <v>4</v>
       </c>
       <c r="C87" s="24">
-        <v>5920</v>
+        <v>5918</v>
       </c>
       <c r="D87" s="24">
         <v>1</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G87" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="I87" s="24">
         <v>0</v>
@@ -9602,54 +9974,57 @@
         <v>0</v>
       </c>
       <c r="V87" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W87" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X87" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y87" s="24">
-        <v>59100001</v>
+        <v>10000</v>
       </c>
       <c r="Z87" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="24" t="s">
-        <v>34</v>
+        <v>59090001</v>
+      </c>
+      <c r="AA87" s="24">
+        <v>0</v>
       </c>
       <c r="AB87" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC87" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC87" s="24" t="s">
+      <c r="AD87" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A88" s="24">
-        <v>59220001</v>
+        <v>59200001</v>
       </c>
       <c r="B88" s="24">
         <v>4</v>
       </c>
       <c r="C88" s="24">
-        <v>5922</v>
+        <v>5920</v>
       </c>
       <c r="D88" s="24">
         <v>1</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G88" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I88" s="24">
         <v>0</v>
@@ -9691,232 +10066,241 @@
         <v>0</v>
       </c>
       <c r="V88" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W88" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X88" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y88" s="24">
-        <v>59110001</v>
+        <v>10000</v>
       </c>
       <c r="Z88" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA88" s="24" t="s">
-        <v>34</v>
+        <v>59100001</v>
+      </c>
+      <c r="AA88" s="24">
+        <v>0</v>
       </c>
       <c r="AB88" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC88" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC88" s="24" t="s">
+      <c r="AD88" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A89" s="24">
-        <v>59240001</v>
+        <v>59220001</v>
       </c>
       <c r="B89" s="24">
         <v>4</v>
       </c>
       <c r="C89" s="24">
+        <v>5922</v>
+      </c>
+      <c r="D89" s="24">
+        <v>1</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F89" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G89" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="I89" s="24">
+        <v>0</v>
+      </c>
+      <c r="J89" s="24">
+        <v>0</v>
+      </c>
+      <c r="K89" s="24">
+        <v>0</v>
+      </c>
+      <c r="L89" s="24">
+        <v>0</v>
+      </c>
+      <c r="M89" s="24">
+        <v>0</v>
+      </c>
+      <c r="N89" s="24">
+        <v>0</v>
+      </c>
+      <c r="O89" s="24">
+        <v>0</v>
+      </c>
+      <c r="P89" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="24">
+        <v>0</v>
+      </c>
+      <c r="R89" s="24">
+        <v>0</v>
+      </c>
+      <c r="S89" s="24">
+        <v>0</v>
+      </c>
+      <c r="T89" s="24">
+        <v>0</v>
+      </c>
+      <c r="U89" s="24">
+        <v>0</v>
+      </c>
+      <c r="V89" s="24">
+        <v>0</v>
+      </c>
+      <c r="W89" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X89" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z89" s="24">
+        <v>59110001</v>
+      </c>
+      <c r="AA89" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC89" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD89" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A90" s="24">
+        <v>59240001</v>
+      </c>
+      <c r="B90" s="24">
+        <v>4</v>
+      </c>
+      <c r="C90" s="24">
         <v>5924</v>
       </c>
-      <c r="D89" s="24">
-        <v>1</v>
-      </c>
-      <c r="E89" s="12" t="s">
+      <c r="D90" s="24">
+        <v>1</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="F89" s="24" t="s">
+      <c r="F90" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="G89" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="H89" s="24" t="s">
+      <c r="G90" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="I89" s="24">
-        <v>0</v>
-      </c>
-      <c r="J89" s="24">
-        <v>0</v>
-      </c>
-      <c r="K89" s="24">
-        <v>0</v>
-      </c>
-      <c r="L89" s="24">
-        <v>0</v>
-      </c>
-      <c r="M89" s="24">
-        <v>0</v>
-      </c>
-      <c r="N89" s="24">
-        <v>0</v>
-      </c>
-      <c r="O89" s="24">
-        <v>0</v>
-      </c>
-      <c r="P89" s="24">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="24">
-        <v>0</v>
-      </c>
-      <c r="R89" s="24">
-        <v>0</v>
-      </c>
-      <c r="S89" s="24">
-        <v>0</v>
-      </c>
-      <c r="T89" s="24">
-        <v>0</v>
-      </c>
-      <c r="U89" s="24">
-        <v>0</v>
-      </c>
-      <c r="V89" s="24">
-        <v>10000</v>
-      </c>
-      <c r="W89" s="24">
-        <v>0</v>
-      </c>
-      <c r="X89" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Y89" s="24">
+      <c r="I90" s="24">
+        <v>0</v>
+      </c>
+      <c r="J90" s="24">
+        <v>0</v>
+      </c>
+      <c r="K90" s="24">
+        <v>0</v>
+      </c>
+      <c r="L90" s="24">
+        <v>0</v>
+      </c>
+      <c r="M90" s="24">
+        <v>0</v>
+      </c>
+      <c r="N90" s="24">
+        <v>0</v>
+      </c>
+      <c r="O90" s="24">
+        <v>0</v>
+      </c>
+      <c r="P90" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="24">
+        <v>0</v>
+      </c>
+      <c r="R90" s="24">
+        <v>0</v>
+      </c>
+      <c r="S90" s="24">
+        <v>0</v>
+      </c>
+      <c r="T90" s="24">
+        <v>0</v>
+      </c>
+      <c r="U90" s="24">
+        <v>0</v>
+      </c>
+      <c r="V90" s="24">
+        <v>0</v>
+      </c>
+      <c r="W90" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X90" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z90" s="24">
         <v>59120001</v>
       </c>
-      <c r="Z89" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB89" s="24" t="s">
+      <c r="AA90" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC90" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC89" s="24" t="s">
+      <c r="AD90" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A90" s="25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A91" s="25">
         <v>60010001</v>
-      </c>
-      <c r="B90" s="25">
-        <v>4</v>
-      </c>
-      <c r="C90" s="25">
-        <v>6001</v>
-      </c>
-      <c r="D90" s="25">
-        <v>1</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="F90" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="G90" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="H90" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="I90" s="25">
-        <v>0</v>
-      </c>
-      <c r="J90" s="25">
-        <v>0</v>
-      </c>
-      <c r="K90" s="25">
-        <v>0</v>
-      </c>
-      <c r="L90" s="25">
-        <v>0</v>
-      </c>
-      <c r="M90" s="25">
-        <v>0</v>
-      </c>
-      <c r="N90" s="25">
-        <v>0</v>
-      </c>
-      <c r="O90" s="25">
-        <v>0</v>
-      </c>
-      <c r="P90" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="25">
-        <v>0</v>
-      </c>
-      <c r="R90" s="25">
-        <v>0</v>
-      </c>
-      <c r="S90" s="25">
-        <v>0</v>
-      </c>
-      <c r="T90" s="25">
-        <v>0</v>
-      </c>
-      <c r="U90" s="25">
-        <v>0</v>
-      </c>
-      <c r="V90" s="25">
-        <v>10000</v>
-      </c>
-      <c r="W90" s="25">
-        <v>0</v>
-      </c>
-      <c r="X90" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Y90" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="Z90" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA90" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB90" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC90" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A91" s="25">
-        <v>60030001</v>
       </c>
       <c r="B91" s="25">
         <v>4</v>
       </c>
       <c r="C91" s="25">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="D91" s="25">
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G91" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>266</v>
+        <v>197</v>
       </c>
       <c r="I91" s="25">
         <v>0</v>
@@ -9958,54 +10342,57 @@
         <v>0</v>
       </c>
       <c r="V91" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W91" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X91" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="25">
-        <v>60020001</v>
+        <v>10000</v>
       </c>
       <c r="Z91" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="25" t="s">
+        <v>60010001</v>
+      </c>
+      <c r="AA91" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB91" s="25" t="s">
+      <c r="AC91" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC91" s="25" t="s">
+      <c r="AD91" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A92" s="25">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B92" s="25">
         <v>4</v>
       </c>
       <c r="C92" s="25">
-        <v>6006</v>
+        <v>6003</v>
       </c>
       <c r="D92" s="25">
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G92" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="I92" s="25">
         <v>0</v>
@@ -10047,54 +10434,57 @@
         <v>0</v>
       </c>
       <c r="V92" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W92" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X92" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="25">
-        <v>60030001</v>
+        <v>10000</v>
       </c>
       <c r="Z92" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA92" s="25" t="s">
+        <v>60020001</v>
+      </c>
+      <c r="AA92" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB92" s="25" t="s">
+      <c r="AC92" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC92" s="25" t="s">
+      <c r="AD92" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B93" s="25">
         <v>4</v>
       </c>
       <c r="C93" s="25">
-        <v>6009</v>
+        <v>6006</v>
       </c>
       <c r="D93" s="25">
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G93" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -10136,232 +10526,241 @@
         <v>0</v>
       </c>
       <c r="V93" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W93" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X93" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y93" s="25">
-        <v>60040001</v>
+        <v>10000</v>
       </c>
       <c r="Z93" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="25" t="s">
+        <v>60030001</v>
+      </c>
+      <c r="AA93" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB93" s="25" t="s">
+      <c r="AC93" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC93" s="25" t="s">
+      <c r="AD93" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B94" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C94" s="25">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="D94" s="25">
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H94" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="I94" s="25">
+        <v>0</v>
+      </c>
+      <c r="J94" s="25">
+        <v>0</v>
+      </c>
+      <c r="K94" s="25">
+        <v>0</v>
+      </c>
+      <c r="L94" s="25">
+        <v>0</v>
+      </c>
+      <c r="M94" s="25">
+        <v>0</v>
+      </c>
+      <c r="N94" s="25">
+        <v>0</v>
+      </c>
+      <c r="O94" s="25">
+        <v>0</v>
+      </c>
+      <c r="P94" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="25">
+        <v>0</v>
+      </c>
+      <c r="R94" s="25">
+        <v>0</v>
+      </c>
+      <c r="S94" s="25">
+        <v>0</v>
+      </c>
+      <c r="T94" s="25">
+        <v>0</v>
+      </c>
+      <c r="U94" s="25">
+        <v>0</v>
+      </c>
+      <c r="V94" s="25">
+        <v>0</v>
+      </c>
+      <c r="W94" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X94" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z94" s="25">
+        <v>60040001</v>
+      </c>
+      <c r="AA94" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC94" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD94" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A95" s="25">
+        <v>60110001</v>
+      </c>
+      <c r="B95" s="25">
+        <v>6</v>
+      </c>
+      <c r="C95" s="25">
+        <v>6011</v>
+      </c>
+      <c r="D95" s="25">
+        <v>1</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G95" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H95" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="I94" s="25">
-        <v>0</v>
-      </c>
-      <c r="J94" s="25">
-        <v>0</v>
-      </c>
-      <c r="K94" s="25">
-        <v>0</v>
-      </c>
-      <c r="L94" s="25">
-        <v>0</v>
-      </c>
-      <c r="M94" s="25">
-        <v>0</v>
-      </c>
-      <c r="N94" s="25">
-        <v>0</v>
-      </c>
-      <c r="O94" s="25">
-        <v>0</v>
-      </c>
-      <c r="P94" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="25">
-        <v>0</v>
-      </c>
-      <c r="R94" s="25">
-        <v>0</v>
-      </c>
-      <c r="S94" s="25">
-        <v>0</v>
-      </c>
-      <c r="T94" s="25">
-        <v>0</v>
-      </c>
-      <c r="U94" s="25">
-        <v>0</v>
-      </c>
-      <c r="V94" s="25">
-        <v>10000</v>
-      </c>
-      <c r="W94" s="25">
-        <v>0</v>
-      </c>
-      <c r="X94" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Y94" s="25">
+      <c r="I95" s="25">
+        <v>0</v>
+      </c>
+      <c r="J95" s="25">
+        <v>0</v>
+      </c>
+      <c r="K95" s="25">
+        <v>0</v>
+      </c>
+      <c r="L95" s="25">
+        <v>0</v>
+      </c>
+      <c r="M95" s="25">
+        <v>0</v>
+      </c>
+      <c r="N95" s="25">
+        <v>0</v>
+      </c>
+      <c r="O95" s="25">
+        <v>0</v>
+      </c>
+      <c r="P95" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="25">
+        <v>0</v>
+      </c>
+      <c r="R95" s="25">
+        <v>0</v>
+      </c>
+      <c r="S95" s="25">
+        <v>0</v>
+      </c>
+      <c r="T95" s="25">
+        <v>0</v>
+      </c>
+      <c r="U95" s="25">
+        <v>0</v>
+      </c>
+      <c r="V95" s="25">
+        <v>0</v>
+      </c>
+      <c r="W95" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X95" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z95" s="25">
         <v>60070001</v>
       </c>
-      <c r="Z94" s="26" t="s">
+      <c r="AA95" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="AA94" s="25" t="s">
+      <c r="AB95" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB94" s="25" t="s">
+      <c r="AC95" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC94" s="25" t="s">
+      <c r="AD95" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A95" s="27">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A96" s="27">
         <v>61020001</v>
-      </c>
-      <c r="B95" s="27">
-        <v>4</v>
-      </c>
-      <c r="C95" s="27">
-        <v>6102</v>
-      </c>
-      <c r="D95" s="27">
-        <v>1</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F95" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="G95" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H95" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="I95" s="27">
-        <v>0</v>
-      </c>
-      <c r="J95" s="27">
-        <v>0</v>
-      </c>
-      <c r="K95" s="27">
-        <v>0</v>
-      </c>
-      <c r="L95" s="27">
-        <v>0</v>
-      </c>
-      <c r="M95" s="27">
-        <v>0</v>
-      </c>
-      <c r="N95" s="27">
-        <v>0</v>
-      </c>
-      <c r="O95" s="27">
-        <v>0</v>
-      </c>
-      <c r="P95" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="27">
-        <v>0</v>
-      </c>
-      <c r="R95" s="27">
-        <v>0</v>
-      </c>
-      <c r="S95" s="27">
-        <v>0</v>
-      </c>
-      <c r="T95" s="27">
-        <v>0</v>
-      </c>
-      <c r="U95" s="27">
-        <v>0</v>
-      </c>
-      <c r="V95" s="27">
-        <v>10000</v>
-      </c>
-      <c r="W95" s="27">
-        <v>0</v>
-      </c>
-      <c r="X95" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Y95" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="Z95" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA95" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB95" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC95" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A96" s="27">
-        <v>61040001</v>
       </c>
       <c r="B96" s="27">
         <v>4</v>
       </c>
       <c r="C96" s="27">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="D96" s="27">
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G96" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H96" s="27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I96" s="27">
         <v>0</v>
@@ -10403,54 +10802,57 @@
         <v>0</v>
       </c>
       <c r="V96" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W96" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X96" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="27">
-        <v>61020001</v>
+        <v>10000</v>
       </c>
       <c r="Z96" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="27" t="s">
-        <v>34</v>
+        <v>61010001</v>
+      </c>
+      <c r="AA96" s="27">
+        <v>0</v>
       </c>
       <c r="AB96" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC96" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC96" s="27" t="s">
+      <c r="AD96" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A97" s="27">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B97" s="27">
         <v>4</v>
       </c>
       <c r="C97" s="27">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="D97" s="27">
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>270</v>
+        <v>208</v>
       </c>
       <c r="G97" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H97" s="27" t="s">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="I97" s="27">
         <v>0</v>
@@ -10492,54 +10894,57 @@
         <v>0</v>
       </c>
       <c r="V97" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W97" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X97" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y97" s="27">
-        <v>61030001</v>
+        <v>10000</v>
       </c>
       <c r="Z97" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA97" s="27" t="s">
-        <v>34</v>
+        <v>61020001</v>
+      </c>
+      <c r="AA97" s="27">
+        <v>0</v>
       </c>
       <c r="AB97" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC97" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC97" s="27" t="s">
+      <c r="AD97" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B98" s="27">
         <v>4</v>
       </c>
       <c r="C98" s="27">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="D98" s="27">
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>95</v>
+        <v>270</v>
       </c>
       <c r="G98" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>95</v>
+        <v>271</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -10581,54 +10986,57 @@
         <v>0</v>
       </c>
       <c r="V98" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W98" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X98" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y98" s="27">
-        <v>61040001</v>
+        <v>10000</v>
       </c>
       <c r="Z98" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA98" s="27" t="s">
-        <v>34</v>
+        <v>61030001</v>
+      </c>
+      <c r="AA98" s="27">
+        <v>0</v>
       </c>
       <c r="AB98" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC98" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC98" s="27" t="s">
+      <c r="AD98" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B99" s="27">
         <v>4</v>
       </c>
       <c r="C99" s="27">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="D99" s="27">
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>212</v>
+        <v>95</v>
       </c>
       <c r="G99" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>212</v>
+        <v>95</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -10670,54 +11078,57 @@
         <v>0</v>
       </c>
       <c r="V99" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W99" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X99" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y99" s="27">
-        <v>61050001</v>
+        <v>10000</v>
       </c>
       <c r="Z99" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA99" s="27" t="s">
-        <v>34</v>
+        <v>61040001</v>
+      </c>
+      <c r="AA99" s="27">
+        <v>0</v>
       </c>
       <c r="AB99" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC99" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC99" s="27" t="s">
+      <c r="AD99" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B100" s="27">
         <v>4</v>
       </c>
       <c r="C100" s="27">
-        <v>6112</v>
+        <v>6110</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="G100" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>273</v>
+        <v>212</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -10759,54 +11170,57 @@
         <v>0</v>
       </c>
       <c r="V100" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W100" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X100" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="27">
-        <v>61060001</v>
+        <v>10000</v>
       </c>
       <c r="Z100" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="27" t="s">
-        <v>34</v>
+        <v>61050001</v>
+      </c>
+      <c r="AA100" s="27">
+        <v>0</v>
       </c>
       <c r="AB100" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC100" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC100" s="27" t="s">
+      <c r="AD100" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B101" s="27">
         <v>4</v>
       </c>
       <c r="C101" s="27">
-        <v>6114</v>
+        <v>6112</v>
       </c>
       <c r="D101" s="27">
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G101" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -10848,54 +11262,57 @@
         <v>0</v>
       </c>
       <c r="V101" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W101" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X101" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="27">
-        <v>61070001</v>
+        <v>10000</v>
       </c>
       <c r="Z101" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="27" t="s">
-        <v>34</v>
+        <v>61060001</v>
+      </c>
+      <c r="AA101" s="27">
+        <v>0</v>
       </c>
       <c r="AB101" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC101" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC101" s="27" t="s">
+      <c r="AD101" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B102" s="27">
         <v>4</v>
       </c>
       <c r="C102" s="27">
-        <v>6116</v>
+        <v>6114</v>
       </c>
       <c r="D102" s="27">
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G102" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10937,121 +11354,219 @@
         <v>0</v>
       </c>
       <c r="V102" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W102" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X102" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="27">
-        <v>61080001</v>
+        <v>10000</v>
       </c>
       <c r="Z102" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="27" t="s">
-        <v>34</v>
+        <v>61070001</v>
+      </c>
+      <c r="AA102" s="27">
+        <v>0</v>
       </c>
       <c r="AB102" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC102" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC102" s="27" t="s">
+      <c r="AD102" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
-        <v>61180001</v>
+        <v>61160001</v>
       </c>
       <c r="B103" s="27">
         <v>4</v>
       </c>
       <c r="C103" s="27">
+        <v>6116</v>
+      </c>
+      <c r="D103" s="27">
+        <v>1</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F103" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="G103" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="I103" s="27">
+        <v>0</v>
+      </c>
+      <c r="J103" s="27">
+        <v>0</v>
+      </c>
+      <c r="K103" s="27">
+        <v>0</v>
+      </c>
+      <c r="L103" s="27">
+        <v>0</v>
+      </c>
+      <c r="M103" s="27">
+        <v>0</v>
+      </c>
+      <c r="N103" s="27">
+        <v>0</v>
+      </c>
+      <c r="O103" s="27">
+        <v>0</v>
+      </c>
+      <c r="P103" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="27">
+        <v>0</v>
+      </c>
+      <c r="R103" s="27">
+        <v>0</v>
+      </c>
+      <c r="S103" s="27">
+        <v>0</v>
+      </c>
+      <c r="T103" s="27">
+        <v>0</v>
+      </c>
+      <c r="U103" s="27">
+        <v>0</v>
+      </c>
+      <c r="V103" s="27">
+        <v>0</v>
+      </c>
+      <c r="W103" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X103" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z103" s="27">
+        <v>61080001</v>
+      </c>
+      <c r="AA103" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC103" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD103" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A104" s="27">
+        <v>61180001</v>
+      </c>
+      <c r="B104" s="27">
+        <v>4</v>
+      </c>
+      <c r="C104" s="27">
         <v>6118</v>
       </c>
-      <c r="D103" s="27">
-        <v>1</v>
-      </c>
-      <c r="E103" s="12" t="s">
+      <c r="D104" s="27">
+        <v>1</v>
+      </c>
+      <c r="E104" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="F103" s="27" t="s">
+      <c r="F104" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="G103" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H103" s="27" t="s">
+      <c r="G104" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="I103" s="27">
-        <v>0</v>
-      </c>
-      <c r="J103" s="27">
-        <v>0</v>
-      </c>
-      <c r="K103" s="27">
-        <v>0</v>
-      </c>
-      <c r="L103" s="27">
-        <v>0</v>
-      </c>
-      <c r="M103" s="27">
-        <v>0</v>
-      </c>
-      <c r="N103" s="27">
-        <v>0</v>
-      </c>
-      <c r="O103" s="27">
-        <v>0</v>
-      </c>
-      <c r="P103" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="27">
-        <v>0</v>
-      </c>
-      <c r="R103" s="27">
-        <v>0</v>
-      </c>
-      <c r="S103" s="27">
-        <v>0</v>
-      </c>
-      <c r="T103" s="27">
-        <v>0</v>
-      </c>
-      <c r="U103" s="27">
-        <v>0</v>
-      </c>
-      <c r="V103" s="27">
-        <v>10000</v>
-      </c>
-      <c r="W103" s="27">
-        <v>0</v>
-      </c>
-      <c r="X103" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Y103" s="27">
+      <c r="I104" s="27">
+        <v>0</v>
+      </c>
+      <c r="J104" s="27">
+        <v>0</v>
+      </c>
+      <c r="K104" s="27">
+        <v>0</v>
+      </c>
+      <c r="L104" s="27">
+        <v>0</v>
+      </c>
+      <c r="M104" s="27">
+        <v>0</v>
+      </c>
+      <c r="N104" s="27">
+        <v>0</v>
+      </c>
+      <c r="O104" s="27">
+        <v>0</v>
+      </c>
+      <c r="P104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="27">
+        <v>0</v>
+      </c>
+      <c r="R104" s="27">
+        <v>0</v>
+      </c>
+      <c r="S104" s="27">
+        <v>0</v>
+      </c>
+      <c r="T104" s="27">
+        <v>0</v>
+      </c>
+      <c r="U104" s="27">
+        <v>0</v>
+      </c>
+      <c r="V104" s="27">
+        <v>0</v>
+      </c>
+      <c r="W104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z104" s="27">
         <v>61090001</v>
       </c>
-      <c r="Z103" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA103" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB103" s="27" t="s">
+      <c r="AA104" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC104" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC103" s="27" t="s">
+      <c r="AD104" s="27" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AB104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04FC212-D0B1-4530-9E46-1D26952C6008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F05339-EDF9-4D17-A6ED-18F8D03AC687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -271,24 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0-没有直接效果
-1-直接伤害：根据释放者的攻击力万分比
-2-直接回血：根据释放者的攻击力万分比
-3-直接回血：根据目标的生命最大值计算，百万分比</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
+    <comment ref="AB4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
       <text>
         <r>
           <rPr>
@@ -319,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
+    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
       <text>
         <r>
           <rPr>
@@ -355,7 +338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="296">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1372,33 +1355,6 @@
   </si>
   <si>
     <t>击杀回血效果提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成，永久</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage_element</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S_C</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>参与伤害计算的攻击元素类型（0-物理、1-冰、2-火、3-毒、4-电）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4,0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1406,7 +1362,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1560,20 +1516,6 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1708,7 +1650,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1775,16 +1717,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="4" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2085,7 +2017,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2103,25 +2035,24 @@
     <col min="18" max="18" width="12.5" style="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.5" style="5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="60" style="5" customWidth="1"/>
-    <col min="22" max="22" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="28.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="5"/>
+    <col min="21" max="21" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="28.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2182,38 +2113,35 @@
       <c r="T2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U2" s="33" t="s">
-        <v>300</v>
+      <c r="U2" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="1" t="s">
         <v>75</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>75</v>
+      <c r="Y2" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>78</v>
       </c>
       <c r="AA2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AD2" s="1" t="s">
-        <v>78</v>
-      </c>
     </row>
-    <row r="3" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2274,38 +2202,35 @@
       <c r="T3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="33" t="s">
-        <v>299</v>
+      <c r="U3" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="W3" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="X3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y3" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="Y3" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="Z3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB3" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="AB3" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="AC3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD3" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2366,38 +2291,35 @@
       <c r="T4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="U4" s="33" t="s">
-        <v>301</v>
+      <c r="U4" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AB4" s="5" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="AC4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD4" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10101</v>
       </c>
@@ -2447,47 +2369,42 @@
       <c r="Q5" s="9">
         <v>2</v>
       </c>
-      <c r="R5" s="9">
-        <v>0</v>
-      </c>
+      <c r="R5" s="9"/>
       <c r="S5" s="9">
         <v>1</v>
       </c>
       <c r="T5" s="9">
         <v>0</v>
       </c>
-      <c r="U5" s="34">
+      <c r="U5" s="9">
         <v>0</v>
       </c>
       <c r="V5" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W5" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X5" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y5" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="AB5" s="10" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="AC5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD5" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10102</v>
       </c>
@@ -2537,47 +2454,42 @@
       <c r="Q6" s="9">
         <v>2</v>
       </c>
-      <c r="R6" s="9">
-        <v>0</v>
-      </c>
+      <c r="R6" s="9"/>
       <c r="S6" s="9">
         <v>1</v>
       </c>
       <c r="T6" s="9">
         <v>0</v>
       </c>
-      <c r="U6" s="34">
+      <c r="U6" s="9">
         <v>0</v>
       </c>
       <c r="V6" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W6" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X6" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y6" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="AB6" s="10" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="AC6" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD6" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10201</v>
       </c>
@@ -2627,47 +2539,42 @@
       <c r="Q7" s="9">
         <v>2</v>
       </c>
-      <c r="R7" s="9">
-        <v>0</v>
-      </c>
+      <c r="R7" s="9"/>
       <c r="S7" s="9">
         <v>1</v>
       </c>
       <c r="T7" s="9">
         <v>0</v>
       </c>
-      <c r="U7" s="34">
+      <c r="U7" s="9">
         <v>0</v>
       </c>
       <c r="V7" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W7" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X7" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y7" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="AB7" s="10" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD7" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10202</v>
       </c>
@@ -2717,47 +2624,42 @@
       <c r="Q8" s="9">
         <v>2</v>
       </c>
-      <c r="R8" s="9">
-        <v>0</v>
-      </c>
+      <c r="R8" s="9"/>
       <c r="S8" s="9">
         <v>1</v>
       </c>
       <c r="T8" s="9">
         <v>0</v>
       </c>
-      <c r="U8" s="34">
+      <c r="U8" s="9">
         <v>0</v>
       </c>
       <c r="V8" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W8" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X8" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y8" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD8" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10301</v>
       </c>
@@ -2807,47 +2709,42 @@
       <c r="Q9" s="9">
         <v>2</v>
       </c>
-      <c r="R9" s="9">
-        <v>0</v>
-      </c>
+      <c r="R9" s="9"/>
       <c r="S9" s="9">
         <v>1</v>
       </c>
       <c r="T9" s="9">
         <v>0</v>
       </c>
-      <c r="U9" s="34">
+      <c r="U9" s="9">
         <v>0</v>
       </c>
       <c r="V9" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W9" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X9" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y9" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="AB9" s="10" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD9" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10302</v>
       </c>
@@ -2897,47 +2794,42 @@
       <c r="Q10" s="9">
         <v>2</v>
       </c>
-      <c r="R10" s="9">
-        <v>0</v>
-      </c>
+      <c r="R10" s="9"/>
       <c r="S10" s="9">
         <v>1</v>
       </c>
       <c r="T10" s="9">
         <v>0</v>
       </c>
-      <c r="U10" s="34">
+      <c r="U10" s="9">
         <v>0</v>
       </c>
       <c r="V10" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W10" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X10" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y10" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="AB10" s="10" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD10" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>20001</v>
       </c>
@@ -2989,47 +2881,42 @@
       <c r="Q11" s="2">
         <v>2</v>
       </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
+      <c r="R11" s="2"/>
       <c r="S11" s="2">
         <v>1</v>
       </c>
       <c r="T11" s="2">
         <v>1</v>
       </c>
-      <c r="U11" s="35">
+      <c r="U11" s="2">
         <v>0</v>
       </c>
       <c r="V11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="2">
         <v>0</v>
       </c>
-      <c r="AA11" s="2">
-        <v>0</v>
+      <c r="AA11" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD11" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>20010001</v>
       </c>
@@ -3081,47 +2968,42 @@
       <c r="Q12" s="2">
         <v>2</v>
       </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
+      <c r="R12" s="2"/>
       <c r="S12" s="2">
         <v>1</v>
       </c>
       <c r="T12" s="2">
         <v>1</v>
       </c>
-      <c r="U12" s="35">
+      <c r="U12" s="2">
         <v>0</v>
       </c>
       <c r="V12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="2">
         <v>0</v>
       </c>
-      <c r="AA12" s="2">
-        <v>0</v>
+      <c r="AA12" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD12" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>20020001</v>
       </c>
@@ -3173,47 +3055,42 @@
       <c r="Q13" s="2">
         <v>2</v>
       </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
+      <c r="R13" s="2"/>
       <c r="S13" s="2">
         <v>1</v>
       </c>
       <c r="T13" s="2">
         <v>1</v>
       </c>
-      <c r="U13" s="35">
+      <c r="U13" s="2">
         <v>0</v>
       </c>
       <c r="V13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="2">
         <v>0</v>
       </c>
-      <c r="AA13" s="2">
-        <v>0</v>
+      <c r="AA13" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD13" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>20030001</v>
       </c>
@@ -3242,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3265,47 +3142,42 @@
       <c r="Q14" s="2">
         <v>2</v>
       </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
+      <c r="R14" s="2"/>
       <c r="S14" s="2">
         <v>1</v>
       </c>
       <c r="T14" s="2">
         <v>1</v>
       </c>
-      <c r="U14" s="35">
+      <c r="U14" s="2">
         <v>0</v>
       </c>
       <c r="V14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="2">
         <v>0</v>
       </c>
-      <c r="AA14" s="2">
-        <v>0</v>
+      <c r="AA14" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD14" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>20040001</v>
       </c>
@@ -3357,47 +3229,42 @@
       <c r="Q15" s="2">
         <v>2</v>
       </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
+      <c r="R15" s="2"/>
       <c r="S15" s="2">
         <v>1</v>
       </c>
       <c r="T15" s="2">
         <v>1</v>
       </c>
-      <c r="U15" s="35">
+      <c r="U15" s="2">
         <v>0</v>
       </c>
       <c r="V15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="2">
         <v>0</v>
       </c>
-      <c r="AA15" s="2">
-        <v>0</v>
+      <c r="AA15" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD15" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>20050001</v>
       </c>
@@ -3449,47 +3316,42 @@
       <c r="Q16" s="2">
         <v>2</v>
       </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
+      <c r="R16" s="2"/>
       <c r="S16" s="2">
         <v>1</v>
       </c>
       <c r="T16" s="2">
         <v>1</v>
       </c>
-      <c r="U16" s="35">
+      <c r="U16" s="2">
         <v>0</v>
       </c>
       <c r="V16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="2">
         <v>0</v>
       </c>
-      <c r="AA16" s="2">
-        <v>0</v>
+      <c r="AA16" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD16" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>20060001</v>
       </c>
@@ -3541,47 +3403,42 @@
       <c r="Q17" s="2">
         <v>2</v>
       </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
+      <c r="R17" s="2"/>
       <c r="S17" s="2">
         <v>1</v>
       </c>
       <c r="T17" s="2">
         <v>1</v>
       </c>
-      <c r="U17" s="35">
+      <c r="U17" s="2">
         <v>0</v>
       </c>
       <c r="V17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="2">
         <v>0</v>
       </c>
-      <c r="AA17" s="2">
-        <v>0</v>
+      <c r="AA17" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD17" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>20070001</v>
       </c>
@@ -3633,47 +3490,42 @@
       <c r="Q18" s="2">
         <v>2</v>
       </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
+      <c r="R18" s="2"/>
       <c r="S18" s="2">
         <v>1</v>
       </c>
       <c r="T18" s="2">
         <v>1</v>
       </c>
-      <c r="U18" s="35">
+      <c r="U18" s="2">
         <v>0</v>
       </c>
       <c r="V18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="2">
         <v>0</v>
       </c>
-      <c r="AA18" s="2">
-        <v>0</v>
+      <c r="AA18" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD18" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>20080001</v>
       </c>
@@ -3725,9 +3577,7 @@
       <c r="Q19" s="2">
         <v>2</v>
       </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
+      <c r="R19" s="2"/>
       <c r="S19" s="2">
         <v>1</v>
       </c>
@@ -3738,34 +3588,31 @@
         <v>0</v>
       </c>
       <c r="V19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="2">
         <v>0</v>
       </c>
-      <c r="AA19" s="2">
-        <v>0</v>
+      <c r="AA19" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD19" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20090001</v>
       </c>
@@ -3817,9 +3664,7 @@
       <c r="Q20" s="2">
         <v>2</v>
       </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
+      <c r="R20" s="2"/>
       <c r="S20" s="2">
         <v>1</v>
       </c>
@@ -3830,34 +3675,31 @@
         <v>0</v>
       </c>
       <c r="V20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="2">
         <v>0</v>
       </c>
-      <c r="AA20" s="2">
-        <v>0</v>
+      <c r="AA20" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD20" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20100001</v>
       </c>
@@ -3909,9 +3751,7 @@
       <c r="Q21" s="2">
         <v>2</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
+      <c r="R21" s="2"/>
       <c r="S21" s="2">
         <v>1</v>
       </c>
@@ -3922,34 +3762,31 @@
         <v>0</v>
       </c>
       <c r="V21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="2">
         <v>0</v>
       </c>
-      <c r="AA21" s="2">
-        <v>0</v>
+      <c r="AA21" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD21" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20110001</v>
       </c>
@@ -4001,9 +3838,7 @@
       <c r="Q22" s="2">
         <v>2</v>
       </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
+      <c r="R22" s="2"/>
       <c r="S22" s="2">
         <v>1</v>
       </c>
@@ -4014,34 +3849,31 @@
         <v>0</v>
       </c>
       <c r="V22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="2">
         <v>0</v>
       </c>
-      <c r="AA22" s="2">
-        <v>0</v>
+      <c r="AA22" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD22" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20120001</v>
       </c>
@@ -4093,9 +3925,7 @@
       <c r="Q23" s="2">
         <v>2</v>
       </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
+      <c r="R23" s="2"/>
       <c r="S23" s="2">
         <v>1</v>
       </c>
@@ -4106,34 +3936,31 @@
         <v>0</v>
       </c>
       <c r="V23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="2">
         <v>0</v>
       </c>
-      <c r="AA23" s="2">
-        <v>0</v>
+      <c r="AA23" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD23" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20130001</v>
       </c>
@@ -4185,9 +4012,7 @@
       <c r="Q24" s="2">
         <v>2</v>
       </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
+      <c r="R24" s="2"/>
       <c r="S24" s="2">
         <v>1</v>
       </c>
@@ -4198,34 +4023,31 @@
         <v>0</v>
       </c>
       <c r="V24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="2">
         <v>0</v>
       </c>
-      <c r="AA24" s="2">
-        <v>0</v>
+      <c r="AA24" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD24" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20140001</v>
       </c>
@@ -4277,9 +4099,7 @@
       <c r="Q25" s="2">
         <v>2</v>
       </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
+      <c r="R25" s="2"/>
       <c r="S25" s="2">
         <v>1</v>
       </c>
@@ -4290,34 +4110,31 @@
         <v>0</v>
       </c>
       <c r="V25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="2">
         <v>0</v>
       </c>
-      <c r="AA25" s="2">
-        <v>0</v>
+      <c r="AA25" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD25" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>20150001</v>
       </c>
@@ -4369,9 +4186,7 @@
       <c r="Q26" s="2">
         <v>2</v>
       </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
+      <c r="R26" s="2"/>
       <c r="S26" s="2">
         <v>1</v>
       </c>
@@ -4382,34 +4197,31 @@
         <v>0</v>
       </c>
       <c r="V26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="2">
         <v>0</v>
       </c>
-      <c r="AA26" s="2">
-        <v>0</v>
+      <c r="AA26" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD26" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>20160001</v>
       </c>
@@ -4461,9 +4273,7 @@
       <c r="Q27" s="2">
         <v>2</v>
       </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
+      <c r="R27" s="2"/>
       <c r="S27" s="2">
         <v>1</v>
       </c>
@@ -4474,419 +4284,400 @@
         <v>0</v>
       </c>
       <c r="V27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="2">
         <v>0</v>
       </c>
-      <c r="AA27" s="2">
-        <v>0</v>
+      <c r="AA27" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC27" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>30001</v>
+      </c>
+      <c r="B28" s="3">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>1</v>
+      </c>
+      <c r="P28" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3">
+        <v>1</v>
+      </c>
+      <c r="T28" s="3">
+        <v>3</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>1000001</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB28" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AD27" s="2" t="s">
+      <c r="AC28" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A28" s="23">
-        <v>25010001</v>
-      </c>
-      <c r="B28" s="23">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>4000001</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3">
+        <v>400</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>2000001</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="21">
+        <v>5000001</v>
+      </c>
+      <c r="B30" s="21">
+        <v>5</v>
+      </c>
+      <c r="C30" s="21">
+        <v>500</v>
+      </c>
+      <c r="D30" s="21">
+        <v>1</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="I30" s="21">
+        <v>8000</v>
+      </c>
+      <c r="J30" s="21">
+        <v>800</v>
+      </c>
+      <c r="K30" s="21">
+        <v>8000</v>
+      </c>
+      <c r="L30" s="21">
+        <v>0</v>
+      </c>
+      <c r="M30" s="21">
+        <v>10000</v>
+      </c>
+      <c r="N30" s="21">
+        <v>0</v>
+      </c>
+      <c r="O30" s="21">
+        <v>0</v>
+      </c>
+      <c r="P30" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="21">
         <v>2</v>
       </c>
-      <c r="C28" s="23">
-        <v>2501</v>
-      </c>
-      <c r="D28" s="23">
-        <v>1</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="I28" s="23">
-        <v>0</v>
-      </c>
-      <c r="J28" s="23">
-        <v>1000</v>
-      </c>
-      <c r="K28" s="23">
-        <v>1000</v>
-      </c>
-      <c r="L28" s="23">
-        <v>0</v>
-      </c>
-      <c r="M28" s="23">
-        <v>10000</v>
-      </c>
-      <c r="N28" s="23">
-        <v>0</v>
-      </c>
-      <c r="O28" s="23">
-        <v>0</v>
-      </c>
-      <c r="P28" s="23">
+      <c r="R30" s="21">
+        <v>5000</v>
+      </c>
+      <c r="S30" s="21">
+        <v>9</v>
+      </c>
+      <c r="T30" s="21">
+        <v>1</v>
+      </c>
+      <c r="U30" s="21">
+        <v>0</v>
+      </c>
+      <c r="V30" s="21">
+        <v>20000</v>
+      </c>
+      <c r="W30" s="21">
+        <v>0</v>
+      </c>
+      <c r="X30" s="21">
+        <v>12000</v>
+      </c>
+      <c r="Y30" s="21">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="21">
+        <v>55010001</v>
+      </c>
+      <c r="AA30" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC30" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="17">
+        <v>6000001</v>
+      </c>
+      <c r="B31" s="17">
+        <v>5</v>
+      </c>
+      <c r="C31" s="17">
+        <v>600</v>
+      </c>
+      <c r="D31" s="17">
+        <v>1</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17">
+        <v>100</v>
+      </c>
+      <c r="J31" s="17">
+        <v>100</v>
+      </c>
+      <c r="K31" s="17">
+        <v>100</v>
+      </c>
+      <c r="L31" s="17">
+        <v>0</v>
+      </c>
+      <c r="M31" s="17">
+        <v>10000</v>
+      </c>
+      <c r="N31" s="17">
+        <v>0</v>
+      </c>
+      <c r="O31" s="17">
+        <v>0</v>
+      </c>
+      <c r="P31" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="17">
         <v>2</v>
       </c>
-      <c r="Q28" s="23">
-        <v>1</v>
-      </c>
-      <c r="R28" s="23">
-        <v>0</v>
-      </c>
-      <c r="S28" s="23">
-        <v>1</v>
-      </c>
-      <c r="T28" s="23">
-        <v>0</v>
-      </c>
-      <c r="U28" s="23">
-        <v>0</v>
-      </c>
-      <c r="V28" s="23">
-        <v>0</v>
-      </c>
-      <c r="W28" s="23">
-        <v>0</v>
-      </c>
-      <c r="X28" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="23">
-        <v>54150001</v>
-      </c>
-      <c r="AA28" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC28" s="23" t="s">
+      <c r="R31" s="17">
+        <v>0</v>
+      </c>
+      <c r="S31" s="17">
+        <v>9</v>
+      </c>
+      <c r="T31" s="17">
+        <v>0</v>
+      </c>
+      <c r="U31" s="17">
+        <v>150</v>
+      </c>
+      <c r="V31" s="17">
+        <v>15000</v>
+      </c>
+      <c r="W31" s="17">
+        <v>120</v>
+      </c>
+      <c r="X31" s="17">
+        <v>12000</v>
+      </c>
+      <c r="Y31" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="17">
+        <v>56010001</v>
+      </c>
+      <c r="AA31" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB31" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AD28" s="23" t="s">
+      <c r="AC31" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
-        <v>30001</v>
-      </c>
-      <c r="B29" s="3">
-        <v>3</v>
-      </c>
-      <c r="C29" s="3">
-        <v>3</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>20000</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>1</v>
-      </c>
-      <c r="P29" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>1</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>1</v>
-      </c>
-      <c r="T29" s="3">
-        <v>3</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>4000001</v>
-      </c>
-      <c r="B30" s="3">
-        <v>4</v>
-      </c>
-      <c r="C30" s="3">
-        <v>400</v>
-      </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I30" s="3">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3">
-        <v>0</v>
-      </c>
-      <c r="O30" s="3">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="3">
-        <v>0</v>
-      </c>
-      <c r="R30" s="3">
-        <v>0</v>
-      </c>
-      <c r="S30" s="3">
-        <v>0</v>
-      </c>
-      <c r="T30" s="3">
-        <v>0</v>
-      </c>
-      <c r="U30" s="3">
-        <v>0</v>
-      </c>
-      <c r="V30" s="3">
-        <v>0</v>
-      </c>
-      <c r="W30" s="3">
-        <v>0</v>
-      </c>
-      <c r="X30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="3">
-        <v>2000001</v>
-      </c>
-      <c r="AA30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD30" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21">
-        <v>5000001</v>
-      </c>
-      <c r="B31" s="21">
-        <v>5</v>
-      </c>
-      <c r="C31" s="21">
-        <v>500</v>
-      </c>
-      <c r="D31" s="21">
-        <v>1</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="I31" s="21">
-        <v>8000</v>
-      </c>
-      <c r="J31" s="21">
-        <v>800</v>
-      </c>
-      <c r="K31" s="21">
-        <v>8000</v>
-      </c>
-      <c r="L31" s="21">
-        <v>0</v>
-      </c>
-      <c r="M31" s="21">
-        <v>10000</v>
-      </c>
-      <c r="N31" s="21">
-        <v>0</v>
-      </c>
-      <c r="O31" s="21">
-        <v>0</v>
-      </c>
-      <c r="P31" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="21">
-        <v>2</v>
-      </c>
-      <c r="R31" s="21">
-        <v>5000</v>
-      </c>
-      <c r="S31" s="21">
-        <v>9</v>
-      </c>
-      <c r="T31" s="21">
-        <v>1</v>
-      </c>
-      <c r="U31" s="21">
-        <v>1</v>
-      </c>
-      <c r="V31" s="21">
-        <v>0</v>
-      </c>
-      <c r="W31" s="21">
-        <v>12000</v>
-      </c>
-      <c r="X31" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="21">
-        <v>8000</v>
-      </c>
-      <c r="Z31" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="21">
-        <v>55010001</v>
-      </c>
-      <c r="AB31" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC31" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD31" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A32" s="17">
-        <v>6000001</v>
+        <v>6010001</v>
       </c>
       <c r="B32" s="17">
         <v>5</v>
       </c>
       <c r="C32" s="17">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D32" s="17">
         <v>1</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>34</v>
@@ -4911,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="17">
         <v>3</v>
@@ -4929,144 +4720,138 @@
         <v>0</v>
       </c>
       <c r="U32" s="17">
+        <v>150</v>
+      </c>
+      <c r="V32" s="17">
+        <v>15000</v>
+      </c>
+      <c r="W32" s="17">
+        <v>120</v>
+      </c>
+      <c r="X32" s="17">
+        <v>12000</v>
+      </c>
+      <c r="Y32" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="17">
+        <v>56010001</v>
+      </c>
+      <c r="AA32" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB32" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC32" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="19">
+        <v>7000001</v>
+      </c>
+      <c r="B33" s="19">
+        <v>5</v>
+      </c>
+      <c r="C33" s="19">
+        <v>700</v>
+      </c>
+      <c r="D33" s="19">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19">
+        <v>100</v>
+      </c>
+      <c r="J33" s="19">
+        <v>100</v>
+      </c>
+      <c r="K33" s="19">
+        <v>100</v>
+      </c>
+      <c r="L33" s="19">
+        <v>0</v>
+      </c>
+      <c r="M33" s="19">
+        <v>10000</v>
+      </c>
+      <c r="N33" s="19">
+        <v>0</v>
+      </c>
+      <c r="O33" s="19">
+        <v>0</v>
+      </c>
+      <c r="P33" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="19">
         <v>2</v>
       </c>
-      <c r="V32" s="17">
+      <c r="R33" s="19">
+        <v>0</v>
+      </c>
+      <c r="S33" s="19">
+        <v>1</v>
+      </c>
+      <c r="T33" s="19">
+        <v>0</v>
+      </c>
+      <c r="U33" s="19">
         <v>150</v>
       </c>
-      <c r="W32" s="17">
+      <c r="V33" s="19">
         <v>15000</v>
       </c>
-      <c r="X32" s="17">
+      <c r="W33" s="19">
         <v>120</v>
       </c>
-      <c r="Y32" s="17">
+      <c r="X33" s="19">
         <v>12000</v>
       </c>
-      <c r="Z32" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="17">
-        <v>56010001</v>
-      </c>
-      <c r="AB32" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC32" s="17" t="s">
+      <c r="Y33" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="19">
+        <v>57010001</v>
+      </c>
+      <c r="AA33" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB33" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="AD32" s="17" t="s">
+      <c r="AC33" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="17">
-        <v>6010001</v>
-      </c>
-      <c r="B33" s="17">
-        <v>5</v>
-      </c>
-      <c r="C33" s="17">
-        <v>601</v>
-      </c>
-      <c r="D33" s="17">
-        <v>1</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17">
-        <v>100</v>
-      </c>
-      <c r="J33" s="17">
-        <v>100</v>
-      </c>
-      <c r="K33" s="17">
-        <v>100</v>
-      </c>
-      <c r="L33" s="17">
-        <v>0</v>
-      </c>
-      <c r="M33" s="17">
-        <v>10000</v>
-      </c>
-      <c r="N33" s="17">
-        <v>0</v>
-      </c>
-      <c r="O33" s="17">
-        <v>1</v>
-      </c>
-      <c r="P33" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="17">
-        <v>2</v>
-      </c>
-      <c r="R33" s="17">
-        <v>0</v>
-      </c>
-      <c r="S33" s="17">
-        <v>9</v>
-      </c>
-      <c r="T33" s="17">
-        <v>0</v>
-      </c>
-      <c r="U33" s="17">
-        <v>2</v>
-      </c>
-      <c r="V33" s="17">
-        <v>150</v>
-      </c>
-      <c r="W33" s="17">
-        <v>15000</v>
-      </c>
-      <c r="X33" s="17">
-        <v>120</v>
-      </c>
-      <c r="Y33" s="17">
-        <v>12000</v>
-      </c>
-      <c r="Z33" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="17">
-        <v>56010001</v>
-      </c>
-      <c r="AB33" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC33" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD33" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="19">
-        <v>7000001</v>
+        <v>7010001</v>
       </c>
       <c r="B34" s="19">
         <v>5</v>
       </c>
       <c r="C34" s="19">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D34" s="19">
         <v>1</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>34</v>
@@ -5091,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="19">
         <v>3</v>
@@ -5103,150 +4888,144 @@
         <v>0</v>
       </c>
       <c r="S34" s="19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T34" s="19">
         <v>0</v>
       </c>
       <c r="U34" s="19">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="V34" s="19">
+        <v>15000</v>
+      </c>
+      <c r="W34" s="19">
+        <v>120</v>
+      </c>
+      <c r="X34" s="19">
+        <v>12000</v>
+      </c>
+      <c r="Y34" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="19">
+        <v>57010001</v>
+      </c>
+      <c r="AA34" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC34" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="20">
+        <v>8000001</v>
+      </c>
+      <c r="B35" s="20">
+        <v>5</v>
+      </c>
+      <c r="C35" s="20">
+        <v>800</v>
+      </c>
+      <c r="D35" s="20">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20">
+        <v>100</v>
+      </c>
+      <c r="J35" s="20">
+        <v>100</v>
+      </c>
+      <c r="K35" s="20">
+        <v>100</v>
+      </c>
+      <c r="L35" s="20">
+        <v>0</v>
+      </c>
+      <c r="M35" s="20">
+        <v>10000</v>
+      </c>
+      <c r="N35" s="20">
+        <v>0</v>
+      </c>
+      <c r="O35" s="20">
+        <v>0</v>
+      </c>
+      <c r="P35" s="20">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="20">
+        <v>2</v>
+      </c>
+      <c r="R35" s="20">
+        <v>0</v>
+      </c>
+      <c r="S35" s="20">
+        <v>9</v>
+      </c>
+      <c r="T35" s="20">
+        <v>0</v>
+      </c>
+      <c r="U35" s="20">
         <v>150</v>
       </c>
-      <c r="W34" s="19">
+      <c r="V35" s="20">
         <v>15000</v>
       </c>
-      <c r="X34" s="19">
+      <c r="W35" s="20">
         <v>120</v>
       </c>
-      <c r="Y34" s="19">
+      <c r="X35" s="20">
         <v>12000</v>
       </c>
-      <c r="Z34" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="19">
-        <v>57010001</v>
-      </c>
-      <c r="AB34" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC34" s="19" t="s">
+      <c r="Y35" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="20">
+        <v>58010001</v>
+      </c>
+      <c r="AA35" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB35" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AD34" s="19" t="s">
+      <c r="AC35" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="19">
-        <v>7010001</v>
-      </c>
-      <c r="B35" s="19">
-        <v>5</v>
-      </c>
-      <c r="C35" s="19">
-        <v>701</v>
-      </c>
-      <c r="D35" s="19">
-        <v>1</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19">
-        <v>100</v>
-      </c>
-      <c r="J35" s="19">
-        <v>100</v>
-      </c>
-      <c r="K35" s="19">
-        <v>100</v>
-      </c>
-      <c r="L35" s="19">
-        <v>0</v>
-      </c>
-      <c r="M35" s="19">
-        <v>10000</v>
-      </c>
-      <c r="N35" s="19">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19">
-        <v>1</v>
-      </c>
-      <c r="P35" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="19">
-        <v>2</v>
-      </c>
-      <c r="R35" s="19">
-        <v>0</v>
-      </c>
-      <c r="S35" s="19">
-        <v>9</v>
-      </c>
-      <c r="T35" s="19">
-        <v>0</v>
-      </c>
-      <c r="U35" s="19">
-        <v>4</v>
-      </c>
-      <c r="V35" s="19">
-        <v>150</v>
-      </c>
-      <c r="W35" s="19">
-        <v>15000</v>
-      </c>
-      <c r="X35" s="19">
-        <v>120</v>
-      </c>
-      <c r="Y35" s="19">
-        <v>12000</v>
-      </c>
-      <c r="Z35" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="19">
-        <v>57010001</v>
-      </c>
-      <c r="AB35" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC35" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD35" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A36" s="20">
-        <v>8000001</v>
+        <v>8010001</v>
       </c>
       <c r="B36" s="20">
         <v>5</v>
       </c>
       <c r="C36" s="20">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D36" s="20">
         <v>1</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G36" s="20" t="s">
         <v>34</v>
@@ -5271,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" s="20">
         <v>3</v>
@@ -5289,234 +5068,225 @@
         <v>0</v>
       </c>
       <c r="U36" s="20">
+        <v>150</v>
+      </c>
+      <c r="V36" s="20">
+        <v>15000</v>
+      </c>
+      <c r="W36" s="20">
+        <v>120</v>
+      </c>
+      <c r="X36" s="20">
+        <v>12000</v>
+      </c>
+      <c r="Y36" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="20">
+        <v>58050001</v>
+      </c>
+      <c r="AA36" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB36" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC36" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="28">
+        <v>9000001</v>
+      </c>
+      <c r="B37" s="28">
+        <v>5</v>
+      </c>
+      <c r="C37" s="28">
+        <v>900</v>
+      </c>
+      <c r="D37" s="28">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28">
+        <v>100</v>
+      </c>
+      <c r="J37" s="28">
+        <v>100</v>
+      </c>
+      <c r="K37" s="28">
+        <v>100</v>
+      </c>
+      <c r="L37" s="28">
+        <v>0</v>
+      </c>
+      <c r="M37" s="28">
+        <v>10000</v>
+      </c>
+      <c r="N37" s="28">
+        <v>0</v>
+      </c>
+      <c r="O37" s="28">
+        <v>1</v>
+      </c>
+      <c r="P37" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="28">
+        <v>0</v>
+      </c>
+      <c r="R37" s="28">
+        <v>0</v>
+      </c>
+      <c r="S37" s="28">
+        <v>1</v>
+      </c>
+      <c r="T37" s="28">
+        <v>0</v>
+      </c>
+      <c r="U37" s="28">
+        <v>150</v>
+      </c>
+      <c r="V37" s="28">
+        <v>15000</v>
+      </c>
+      <c r="W37" s="28">
+        <v>120</v>
+      </c>
+      <c r="X37" s="28">
+        <v>12000</v>
+      </c>
+      <c r="Y37" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB37" s="28">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="30">
+        <v>10010001</v>
+      </c>
+      <c r="B38" s="30">
+        <v>5</v>
+      </c>
+      <c r="C38" s="30">
+        <v>1001</v>
+      </c>
+      <c r="D38" s="30">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G38" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30">
+        <v>100</v>
+      </c>
+      <c r="J38" s="30">
+        <v>100</v>
+      </c>
+      <c r="K38" s="30">
+        <v>100</v>
+      </c>
+      <c r="L38" s="30">
+        <v>0</v>
+      </c>
+      <c r="M38" s="30">
+        <v>10000</v>
+      </c>
+      <c r="N38" s="30">
+        <v>0</v>
+      </c>
+      <c r="O38" s="30">
+        <v>0</v>
+      </c>
+      <c r="P38" s="30">
         <v>3</v>
       </c>
-      <c r="V36" s="20">
+      <c r="Q38" s="30">
+        <v>2</v>
+      </c>
+      <c r="R38" s="30">
+        <v>0</v>
+      </c>
+      <c r="S38" s="30">
+        <v>9</v>
+      </c>
+      <c r="T38" s="30">
+        <v>0</v>
+      </c>
+      <c r="U38" s="30">
         <v>150</v>
       </c>
-      <c r="W36" s="20">
+      <c r="V38" s="30">
         <v>15000</v>
       </c>
-      <c r="X36" s="20">
+      <c r="W38" s="30">
         <v>120</v>
       </c>
-      <c r="Y36" s="20">
+      <c r="X38" s="30">
         <v>12000</v>
       </c>
-      <c r="Z36" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="20">
-        <v>58010001</v>
-      </c>
-      <c r="AB36" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC36" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD36" s="20" t="s">
-        <v>62</v>
+      <c r="Y38" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB38" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC38" s="30" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="20">
-        <v>8010001</v>
-      </c>
-      <c r="B37" s="20">
-        <v>5</v>
-      </c>
-      <c r="C37" s="20">
-        <v>801</v>
-      </c>
-      <c r="D37" s="20">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20">
-        <v>100</v>
-      </c>
-      <c r="J37" s="20">
-        <v>100</v>
-      </c>
-      <c r="K37" s="20">
-        <v>100</v>
-      </c>
-      <c r="L37" s="20">
-        <v>0</v>
-      </c>
-      <c r="M37" s="20">
-        <v>10000</v>
-      </c>
-      <c r="N37" s="20">
-        <v>0</v>
-      </c>
-      <c r="O37" s="20">
-        <v>1</v>
-      </c>
-      <c r="P37" s="20">
-        <v>3</v>
-      </c>
-      <c r="Q37" s="20">
-        <v>2</v>
-      </c>
-      <c r="R37" s="20">
-        <v>0</v>
-      </c>
-      <c r="S37" s="20">
-        <v>9</v>
-      </c>
-      <c r="T37" s="20">
-        <v>0</v>
-      </c>
-      <c r="U37" s="20">
-        <v>3</v>
-      </c>
-      <c r="V37" s="20">
-        <v>150</v>
-      </c>
-      <c r="W37" s="20">
-        <v>15000</v>
-      </c>
-      <c r="X37" s="20">
-        <v>120</v>
-      </c>
-      <c r="Y37" s="20">
-        <v>12000</v>
-      </c>
-      <c r="Z37" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="20">
-        <v>58050001</v>
-      </c>
-      <c r="AB37" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC37" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD37" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="28">
-        <v>9000001</v>
-      </c>
-      <c r="B38" s="28">
-        <v>5</v>
-      </c>
-      <c r="C38" s="28">
-        <v>900</v>
-      </c>
-      <c r="D38" s="28">
-        <v>1</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="F38" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28">
-        <v>100</v>
-      </c>
-      <c r="J38" s="28">
-        <v>100</v>
-      </c>
-      <c r="K38" s="28">
-        <v>100</v>
-      </c>
-      <c r="L38" s="28">
-        <v>0</v>
-      </c>
-      <c r="M38" s="28">
-        <v>10000</v>
-      </c>
-      <c r="N38" s="28">
-        <v>0</v>
-      </c>
-      <c r="O38" s="28">
-        <v>1</v>
-      </c>
-      <c r="P38" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="28">
-        <v>0</v>
-      </c>
-      <c r="R38" s="28">
-        <v>0</v>
-      </c>
-      <c r="S38" s="28">
-        <v>1</v>
-      </c>
-      <c r="T38" s="28">
-        <v>0</v>
-      </c>
-      <c r="U38" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="V38" s="28">
-        <v>150</v>
-      </c>
-      <c r="W38" s="28">
-        <v>15000</v>
-      </c>
-      <c r="X38" s="28">
-        <v>120</v>
-      </c>
-      <c r="Y38" s="28">
-        <v>12000</v>
-      </c>
-      <c r="Z38" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="28">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC38" s="28">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="30">
-        <v>10010001</v>
+        <v>10020001</v>
       </c>
       <c r="B39" s="30">
         <v>5</v>
       </c>
       <c r="C39" s="30">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D39" s="30">
         <v>1</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G39" s="30" t="s">
         <v>100</v>
@@ -5559,240 +5329,233 @@
         <v>0</v>
       </c>
       <c r="U39" s="30">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="V39" s="30">
+        <v>15000</v>
+      </c>
+      <c r="W39" s="30">
+        <v>120</v>
+      </c>
+      <c r="X39" s="30">
+        <v>12000</v>
+      </c>
+      <c r="Y39" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB39" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC39" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="31">
+        <v>11010001</v>
+      </c>
+      <c r="B40" s="31">
+        <v>5</v>
+      </c>
+      <c r="C40" s="31">
+        <v>1101</v>
+      </c>
+      <c r="D40" s="31">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="F40" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31">
+        <v>100</v>
+      </c>
+      <c r="J40" s="31">
+        <v>100</v>
+      </c>
+      <c r="K40" s="31">
+        <v>100</v>
+      </c>
+      <c r="L40" s="31">
+        <v>0</v>
+      </c>
+      <c r="M40" s="31">
+        <v>10000</v>
+      </c>
+      <c r="N40" s="31">
+        <v>0</v>
+      </c>
+      <c r="O40" s="31">
+        <v>0</v>
+      </c>
+      <c r="P40" s="31">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="31">
+        <v>2</v>
+      </c>
+      <c r="R40" s="31">
+        <v>0</v>
+      </c>
+      <c r="S40" s="31">
+        <v>9</v>
+      </c>
+      <c r="T40" s="31">
+        <v>0</v>
+      </c>
+      <c r="U40" s="31">
         <v>150</v>
       </c>
-      <c r="W39" s="30">
+      <c r="V40" s="31">
         <v>15000</v>
       </c>
-      <c r="X39" s="30">
+      <c r="W40" s="31">
         <v>120</v>
       </c>
-      <c r="Y39" s="30">
+      <c r="X40" s="31">
         <v>12000</v>
       </c>
-      <c r="Z39" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="30">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="30" t="s">
+      <c r="Y40" s="31">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AC39" s="30" t="s">
+      <c r="AB40" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="AD39" s="30" t="s">
+      <c r="AC40" s="31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="30">
-        <v>10020001</v>
-      </c>
-      <c r="B40" s="30">
-        <v>5</v>
-      </c>
-      <c r="C40" s="30">
-        <v>1002</v>
-      </c>
-      <c r="D40" s="30">
-        <v>1</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="F40" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="G40" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30">
-        <v>100</v>
-      </c>
-      <c r="J40" s="30">
-        <v>100</v>
-      </c>
-      <c r="K40" s="30">
-        <v>100</v>
-      </c>
-      <c r="L40" s="30">
-        <v>0</v>
-      </c>
-      <c r="M40" s="30">
-        <v>10000</v>
-      </c>
-      <c r="N40" s="30">
-        <v>0</v>
-      </c>
-      <c r="O40" s="30">
-        <v>0</v>
-      </c>
-      <c r="P40" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="30">
-        <v>2</v>
-      </c>
-      <c r="R40" s="30">
-        <v>0</v>
-      </c>
-      <c r="S40" s="30">
-        <v>9</v>
-      </c>
-      <c r="T40" s="30">
-        <v>0</v>
-      </c>
-      <c r="U40" s="30">
-        <v>0</v>
-      </c>
-      <c r="V40" s="30">
-        <v>150</v>
-      </c>
-      <c r="W40" s="30">
-        <v>15000</v>
-      </c>
-      <c r="X40" s="30">
-        <v>120</v>
-      </c>
-      <c r="Y40" s="30">
-        <v>12000</v>
-      </c>
-      <c r="Z40" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="30">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC40" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD40" s="30" t="s">
-        <v>64</v>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A41" s="23">
+        <v>54010001</v>
+      </c>
+      <c r="B41" s="23">
+        <v>4</v>
+      </c>
+      <c r="C41" s="23">
+        <v>5401</v>
+      </c>
+      <c r="D41" s="23">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="I41" s="23">
+        <v>0</v>
+      </c>
+      <c r="J41" s="23">
+        <v>0</v>
+      </c>
+      <c r="K41" s="23">
+        <v>0</v>
+      </c>
+      <c r="L41" s="23">
+        <v>0</v>
+      </c>
+      <c r="M41" s="23">
+        <v>0</v>
+      </c>
+      <c r="N41" s="23">
+        <v>0</v>
+      </c>
+      <c r="O41" s="23">
+        <v>0</v>
+      </c>
+      <c r="P41" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="23">
+        <v>0</v>
+      </c>
+      <c r="R41" s="23">
+        <v>0</v>
+      </c>
+      <c r="S41" s="23">
+        <v>0</v>
+      </c>
+      <c r="T41" s="23">
+        <v>0</v>
+      </c>
+      <c r="U41" s="23">
+        <v>0</v>
+      </c>
+      <c r="V41" s="23">
+        <v>0</v>
+      </c>
+      <c r="W41" s="23">
+        <v>0</v>
+      </c>
+      <c r="X41" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="23">
+        <v>54010001</v>
+      </c>
+      <c r="Z41" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB41" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC41" s="23" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="31">
-        <v>11010001</v>
-      </c>
-      <c r="B41" s="31">
-        <v>5</v>
-      </c>
-      <c r="C41" s="31">
-        <v>1101</v>
-      </c>
-      <c r="D41" s="31">
-        <v>1</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="G41" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31">
-        <v>100</v>
-      </c>
-      <c r="J41" s="31">
-        <v>100</v>
-      </c>
-      <c r="K41" s="31">
-        <v>100</v>
-      </c>
-      <c r="L41" s="31">
-        <v>0</v>
-      </c>
-      <c r="M41" s="31">
-        <v>10000</v>
-      </c>
-      <c r="N41" s="31">
-        <v>0</v>
-      </c>
-      <c r="O41" s="31">
-        <v>0</v>
-      </c>
-      <c r="P41" s="31">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="31">
-        <v>2</v>
-      </c>
-      <c r="R41" s="31">
-        <v>0</v>
-      </c>
-      <c r="S41" s="31">
-        <v>9</v>
-      </c>
-      <c r="T41" s="31">
-        <v>0</v>
-      </c>
-      <c r="U41" s="31">
-        <v>0</v>
-      </c>
-      <c r="V41" s="31">
-        <v>150</v>
-      </c>
-      <c r="W41" s="31">
-        <v>15000</v>
-      </c>
-      <c r="X41" s="31">
-        <v>120</v>
-      </c>
-      <c r="Y41" s="31">
-        <v>12000</v>
-      </c>
-      <c r="Z41" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC41" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD41" s="31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A42" s="23">
-        <v>54010001</v>
+        <v>54030001</v>
       </c>
       <c r="B42" s="23">
         <v>4</v>
       </c>
       <c r="C42" s="23">
-        <v>5401</v>
+        <v>5403</v>
       </c>
       <c r="D42" s="23">
         <v>1</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I42" s="23">
         <v>0</v>
@@ -5843,48 +5606,45 @@
         <v>0</v>
       </c>
       <c r="Y42" s="23">
-        <v>0</v>
+        <v>54020001</v>
       </c>
       <c r="Z42" s="23">
-        <v>54010001</v>
-      </c>
-      <c r="AA42" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA42" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB42" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC42" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD42" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A43" s="23">
-        <v>54030001</v>
+        <v>54050001</v>
       </c>
       <c r="B43" s="23">
         <v>4</v>
       </c>
       <c r="C43" s="23">
-        <v>5403</v>
+        <v>5405</v>
       </c>
       <c r="D43" s="23">
         <v>1</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I43" s="23">
         <v>0</v>
@@ -5935,48 +5695,45 @@
         <v>0</v>
       </c>
       <c r="Y43" s="23">
-        <v>0</v>
+        <v>54030001</v>
       </c>
       <c r="Z43" s="23">
-        <v>54020001</v>
-      </c>
-      <c r="AA43" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA43" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB43" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC43" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD43" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A44" s="23">
-        <v>54050001</v>
+        <v>54070001</v>
       </c>
       <c r="B44" s="23">
         <v>4</v>
       </c>
       <c r="C44" s="23">
-        <v>5405</v>
+        <v>5407</v>
       </c>
       <c r="D44" s="23">
         <v>1</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I44" s="23">
         <v>0</v>
@@ -6027,48 +5784,45 @@
         <v>0</v>
       </c>
       <c r="Y44" s="23">
-        <v>0</v>
+        <v>54040001</v>
       </c>
       <c r="Z44" s="23">
-        <v>54030001</v>
-      </c>
-      <c r="AA44" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA44" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB44" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC44" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD44" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A45" s="23">
-        <v>54070001</v>
+        <v>54090001</v>
       </c>
       <c r="B45" s="23">
         <v>4</v>
       </c>
       <c r="C45" s="23">
-        <v>5407</v>
+        <v>5409</v>
       </c>
       <c r="D45" s="23">
         <v>1</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G45" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I45" s="23">
         <v>0</v>
@@ -6119,48 +5873,45 @@
         <v>0</v>
       </c>
       <c r="Y45" s="23">
-        <v>0</v>
+        <v>54050001</v>
       </c>
       <c r="Z45" s="23">
-        <v>54040001</v>
-      </c>
-      <c r="AA45" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA45" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB45" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC45" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD45" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A46" s="23">
-        <v>54090001</v>
+        <v>54110001</v>
       </c>
       <c r="B46" s="23">
         <v>4</v>
       </c>
       <c r="C46" s="23">
-        <v>5409</v>
+        <v>5411</v>
       </c>
       <c r="D46" s="23">
         <v>1</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G46" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I46" s="23">
         <v>0</v>
@@ -6211,48 +5962,45 @@
         <v>0</v>
       </c>
       <c r="Y46" s="23">
-        <v>0</v>
+        <v>54060001</v>
       </c>
       <c r="Z46" s="23">
-        <v>54050001</v>
-      </c>
-      <c r="AA46" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB46" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC46" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD46" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A47" s="23">
-        <v>54110001</v>
+        <v>54130001</v>
       </c>
       <c r="B47" s="23">
         <v>4</v>
       </c>
       <c r="C47" s="23">
-        <v>5411</v>
+        <v>5413</v>
       </c>
       <c r="D47" s="23">
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G47" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I47" s="23">
         <v>0</v>
@@ -6303,48 +6051,45 @@
         <v>0</v>
       </c>
       <c r="Y47" s="23">
-        <v>0</v>
+        <v>54070001</v>
       </c>
       <c r="Z47" s="23">
-        <v>54060001</v>
-      </c>
-      <c r="AA47" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA47" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB47" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC47" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD47" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A48" s="23">
-        <v>54130001</v>
+        <v>54150001</v>
       </c>
       <c r="B48" s="23">
         <v>4</v>
       </c>
       <c r="C48" s="23">
-        <v>5413</v>
+        <v>5415</v>
       </c>
       <c r="D48" s="23">
         <v>1</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G48" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I48" s="23">
         <v>0</v>
@@ -6395,48 +6140,45 @@
         <v>0</v>
       </c>
       <c r="Y48" s="23">
-        <v>0</v>
+        <v>54080001</v>
       </c>
       <c r="Z48" s="23">
-        <v>54070001</v>
-      </c>
-      <c r="AA48" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA48" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB48" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC48" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD48" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A49" s="23">
-        <v>54150001</v>
+        <v>54170001</v>
       </c>
       <c r="B49" s="23">
         <v>4</v>
       </c>
       <c r="C49" s="23">
-        <v>5415</v>
+        <v>5417</v>
       </c>
       <c r="D49" s="23">
         <v>1</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G49" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="I49" s="23">
         <v>0</v>
@@ -6490,45 +6232,42 @@
         <v>0</v>
       </c>
       <c r="Z49" s="23">
-        <v>54080001</v>
-      </c>
-      <c r="AA49" s="23">
-        <v>0</v>
+        <v>54090001</v>
+      </c>
+      <c r="AA49" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB49" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC49" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD49" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A50" s="23">
-        <v>54170001</v>
+        <v>54190001</v>
       </c>
       <c r="B50" s="23">
         <v>4</v>
       </c>
       <c r="C50" s="23">
-        <v>5417</v>
+        <v>5419</v>
       </c>
       <c r="D50" s="23">
         <v>1</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G50" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="I50" s="23">
         <v>0</v>
@@ -6579,48 +6318,45 @@
         <v>0</v>
       </c>
       <c r="Y50" s="23">
-        <v>0</v>
+        <v>54100001</v>
       </c>
       <c r="Z50" s="23">
         <v>0</v>
       </c>
-      <c r="AA50" s="23">
-        <v>54090001</v>
+      <c r="AA50" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB50" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC50" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD50" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A51" s="23">
-        <v>54190001</v>
+        <v>54210001</v>
       </c>
       <c r="B51" s="23">
         <v>4</v>
       </c>
       <c r="C51" s="23">
-        <v>5419</v>
+        <v>5421</v>
       </c>
       <c r="D51" s="23">
         <v>1</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="I51" s="23">
         <v>0</v>
@@ -6674,45 +6410,42 @@
         <v>0</v>
       </c>
       <c r="Z51" s="23">
-        <v>54100001</v>
-      </c>
-      <c r="AA51" s="23">
-        <v>0</v>
+        <v>54110001</v>
+      </c>
+      <c r="AA51" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB51" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC51" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD51" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A52" s="23">
-        <v>54210001</v>
+        <v>54230001</v>
       </c>
       <c r="B52" s="23">
         <v>4</v>
       </c>
       <c r="C52" s="23">
-        <v>5421</v>
+        <v>5423</v>
       </c>
       <c r="D52" s="23">
         <v>1</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G52" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I52" s="23">
         <v>0</v>
@@ -6763,33 +6496,30 @@
         <v>0</v>
       </c>
       <c r="Y52" s="23">
-        <v>0</v>
+        <v>54120001</v>
       </c>
       <c r="Z52" s="23">
         <v>0</v>
       </c>
-      <c r="AA52" s="23">
-        <v>54110001</v>
+      <c r="AA52" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB52" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC52" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD52" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A53" s="23">
-        <v>54230001</v>
+        <v>54250001</v>
       </c>
       <c r="B53" s="23">
         <v>4</v>
       </c>
       <c r="C53" s="23">
-        <v>5423</v>
+        <v>5425</v>
       </c>
       <c r="D53" s="23">
         <v>1</v>
@@ -6798,13 +6528,13 @@
         <v>157</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G53" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>114</v>
+        <v>269</v>
       </c>
       <c r="I53" s="23">
         <v>0</v>
@@ -6855,140 +6585,134 @@
         <v>0</v>
       </c>
       <c r="Y53" s="23">
-        <v>0</v>
+        <v>54130001</v>
       </c>
       <c r="Z53" s="23">
-        <v>54120001</v>
-      </c>
-      <c r="AA53" s="23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA53" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="AB53" s="23" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC53" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A54" s="13">
+        <v>55010001</v>
+      </c>
+      <c r="B54" s="13">
+        <v>4</v>
+      </c>
+      <c r="C54" s="13">
+        <v>5501</v>
+      </c>
+      <c r="D54" s="13">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0</v>
+      </c>
+      <c r="J54" s="13">
+        <v>0</v>
+      </c>
+      <c r="K54" s="13">
+        <v>0</v>
+      </c>
+      <c r="L54" s="13">
+        <v>0</v>
+      </c>
+      <c r="M54" s="13">
+        <v>0</v>
+      </c>
+      <c r="N54" s="13">
+        <v>0</v>
+      </c>
+      <c r="O54" s="13">
+        <v>0</v>
+      </c>
+      <c r="P54" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="13">
+        <v>0</v>
+      </c>
+      <c r="R54" s="13">
+        <v>0</v>
+      </c>
+      <c r="S54" s="13">
+        <v>0</v>
+      </c>
+      <c r="T54" s="13">
+        <v>0</v>
+      </c>
+      <c r="U54" s="13">
+        <v>0</v>
+      </c>
+      <c r="V54" s="13">
+        <v>10000</v>
+      </c>
+      <c r="W54" s="13">
+        <v>0</v>
+      </c>
+      <c r="X54" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Y54" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="13">
+        <v>55010001</v>
+      </c>
+      <c r="AA54" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB54" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="AD53" s="23" t="s">
+      <c r="AC54" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A54" s="23">
-        <v>54250001</v>
-      </c>
-      <c r="B54" s="23">
-        <v>4</v>
-      </c>
-      <c r="C54" s="23">
-        <v>5425</v>
-      </c>
-      <c r="D54" s="23">
-        <v>1</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="G54" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="I54" s="23">
-        <v>0</v>
-      </c>
-      <c r="J54" s="23">
-        <v>0</v>
-      </c>
-      <c r="K54" s="23">
-        <v>0</v>
-      </c>
-      <c r="L54" s="23">
-        <v>0</v>
-      </c>
-      <c r="M54" s="23">
-        <v>0</v>
-      </c>
-      <c r="N54" s="23">
-        <v>0</v>
-      </c>
-      <c r="O54" s="23">
-        <v>0</v>
-      </c>
-      <c r="P54" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="23">
-        <v>0</v>
-      </c>
-      <c r="R54" s="23">
-        <v>0</v>
-      </c>
-      <c r="S54" s="23">
-        <v>0</v>
-      </c>
-      <c r="T54" s="23">
-        <v>0</v>
-      </c>
-      <c r="U54" s="23">
-        <v>0</v>
-      </c>
-      <c r="V54" s="23">
-        <v>0</v>
-      </c>
-      <c r="W54" s="23">
-        <v>0</v>
-      </c>
-      <c r="X54" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="23">
-        <v>54130001</v>
-      </c>
-      <c r="AA54" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC54" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD54" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A55" s="13">
-        <v>55010001</v>
+        <v>55020001</v>
       </c>
       <c r="B55" s="13">
         <v>4</v>
       </c>
       <c r="C55" s="13">
-        <v>5501</v>
+        <v>5502</v>
       </c>
       <c r="D55" s="13">
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
@@ -7027,60 +6751,57 @@
         <v>0</v>
       </c>
       <c r="U55" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V55" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W55" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X55" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y55" s="13">
-        <v>10000</v>
+        <v>55020001</v>
       </c>
       <c r="Z55" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="13">
         <v>55010001</v>
       </c>
+      <c r="AA55" s="13" t="s">
+        <v>34</v>
+      </c>
       <c r="AB55" s="13" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC55" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD55" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A56" s="13">
-        <v>55020001</v>
+        <v>55030001</v>
       </c>
       <c r="B56" s="13">
         <v>4</v>
       </c>
       <c r="C56" s="13">
-        <v>5502</v>
+        <v>5503</v>
       </c>
       <c r="D56" s="13">
         <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I56" s="13">
         <v>0</v>
@@ -7119,60 +6840,57 @@
         <v>0</v>
       </c>
       <c r="U56" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W56" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X56" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y56" s="13">
-        <v>10000</v>
+        <v>55030001</v>
       </c>
       <c r="Z56" s="13">
-        <v>55020001</v>
-      </c>
-      <c r="AA56" s="13">
-        <v>55010001</v>
+        <v>0</v>
+      </c>
+      <c r="AA56" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="AB56" s="13" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC56" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD56" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A57" s="13">
-        <v>55030001</v>
+        <v>55040001</v>
       </c>
       <c r="B57" s="13">
         <v>4</v>
       </c>
       <c r="C57" s="13">
-        <v>5503</v>
+        <v>5504</v>
       </c>
       <c r="D57" s="13">
         <v>1</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -7211,60 +6929,57 @@
         <v>0</v>
       </c>
       <c r="U57" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W57" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X57" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y57" s="13">
-        <v>10000</v>
+        <v>55040001</v>
       </c>
       <c r="Z57" s="13">
-        <v>55030001</v>
-      </c>
-      <c r="AA57" s="13">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA57" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="AB57" s="13" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC57" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD57" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A58" s="13">
-        <v>55040001</v>
+        <v>55050001</v>
       </c>
       <c r="B58" s="13">
         <v>4</v>
       </c>
       <c r="C58" s="13">
-        <v>5504</v>
+        <v>5505</v>
       </c>
       <c r="D58" s="13">
         <v>1</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I58" s="13">
         <v>0</v>
@@ -7303,60 +7018,57 @@
         <v>0</v>
       </c>
       <c r="U58" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W58" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X58" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y58" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="13">
-        <v>55040001</v>
-      </c>
-      <c r="AA58" s="13">
-        <v>0</v>
+        <v>55050001</v>
+      </c>
+      <c r="AA58" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="AB58" s="13" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC58" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD58" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59" s="13">
-        <v>55050001</v>
+        <v>55060001</v>
       </c>
       <c r="B59" s="13">
         <v>4</v>
       </c>
       <c r="C59" s="13">
-        <v>5505</v>
+        <v>5506</v>
       </c>
       <c r="D59" s="13">
         <v>1</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="I59" s="13">
         <v>0</v>
@@ -7395,60 +7107,57 @@
         <v>0</v>
       </c>
       <c r="U59" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W59" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X59" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y59" s="13">
-        <v>10000</v>
+        <v>55060001</v>
       </c>
       <c r="Z59" s="13">
         <v>0</v>
       </c>
-      <c r="AA59" s="13">
-        <v>55050001</v>
+      <c r="AA59" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="AB59" s="13" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC59" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD59" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="13">
-        <v>55060001</v>
+        <v>55070001</v>
       </c>
       <c r="B60" s="13">
         <v>4</v>
       </c>
       <c r="C60" s="13">
-        <v>5506</v>
+        <v>5507</v>
       </c>
       <c r="D60" s="13">
         <v>1</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I60" s="13">
         <v>0</v>
@@ -7487,152 +7196,146 @@
         <v>0</v>
       </c>
       <c r="U60" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V60" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W60" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X60" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y60" s="13">
-        <v>10000</v>
+        <v>55070001</v>
       </c>
       <c r="Z60" s="13">
-        <v>55060001</v>
-      </c>
-      <c r="AA60" s="13">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA60" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="AB60" s="13" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC60" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A61" s="14">
+        <v>56010001</v>
+      </c>
+      <c r="B61" s="14">
+        <v>4</v>
+      </c>
+      <c r="C61" s="14">
+        <v>5601</v>
+      </c>
+      <c r="D61" s="14">
+        <v>1</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="I61" s="14">
+        <v>0</v>
+      </c>
+      <c r="J61" s="14">
+        <v>0</v>
+      </c>
+      <c r="K61" s="14">
+        <v>0</v>
+      </c>
+      <c r="L61" s="14">
+        <v>0</v>
+      </c>
+      <c r="M61" s="14">
+        <v>0</v>
+      </c>
+      <c r="N61" s="14">
+        <v>0</v>
+      </c>
+      <c r="O61" s="14">
+        <v>0</v>
+      </c>
+      <c r="P61" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="14">
+        <v>0</v>
+      </c>
+      <c r="R61" s="14">
+        <v>0</v>
+      </c>
+      <c r="S61" s="14">
+        <v>0</v>
+      </c>
+      <c r="T61" s="14">
+        <v>0</v>
+      </c>
+      <c r="U61" s="14">
+        <v>0</v>
+      </c>
+      <c r="V61" s="14">
+        <v>10000</v>
+      </c>
+      <c r="W61" s="14">
+        <v>0</v>
+      </c>
+      <c r="X61" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Y61" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="14">
+        <v>56010001</v>
+      </c>
+      <c r="AA61" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB61" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AD60" s="13" t="s">
+      <c r="AC61" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A61" s="13">
-        <v>55070001</v>
-      </c>
-      <c r="B61" s="13">
-        <v>4</v>
-      </c>
-      <c r="C61" s="13">
-        <v>5507</v>
-      </c>
-      <c r="D61" s="13">
-        <v>1</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H61" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="I61" s="13">
-        <v>0</v>
-      </c>
-      <c r="J61" s="13">
-        <v>0</v>
-      </c>
-      <c r="K61" s="13">
-        <v>0</v>
-      </c>
-      <c r="L61" s="13">
-        <v>0</v>
-      </c>
-      <c r="M61" s="13">
-        <v>0</v>
-      </c>
-      <c r="N61" s="13">
-        <v>0</v>
-      </c>
-      <c r="O61" s="13">
-        <v>0</v>
-      </c>
-      <c r="P61" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="13">
-        <v>0</v>
-      </c>
-      <c r="R61" s="13">
-        <v>0</v>
-      </c>
-      <c r="S61" s="13">
-        <v>0</v>
-      </c>
-      <c r="T61" s="13">
-        <v>0</v>
-      </c>
-      <c r="U61" s="13">
-        <v>1</v>
-      </c>
-      <c r="V61" s="13">
-        <v>0</v>
-      </c>
-      <c r="W61" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X61" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z61" s="13">
-        <v>55070001</v>
-      </c>
-      <c r="AA61" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC61" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD61" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A62" s="14">
-        <v>56010001</v>
+        <v>56040001</v>
       </c>
       <c r="B62" s="14">
         <v>4</v>
       </c>
       <c r="C62" s="14">
-        <v>5601</v>
+        <v>5604</v>
       </c>
       <c r="D62" s="14">
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I62" s="14">
         <v>0</v>
@@ -7671,60 +7374,57 @@
         <v>0</v>
       </c>
       <c r="U62" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V62" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W62" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X62" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y62" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="14">
         <v>0</v>
       </c>
-      <c r="AA62" s="14">
-        <v>56010001</v>
+      <c r="AA62" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="AB62" s="14" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC62" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD62" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A63" s="14">
-        <v>56040001</v>
+        <v>56060001</v>
       </c>
       <c r="B63" s="14">
         <v>4</v>
       </c>
       <c r="C63" s="14">
-        <v>5604</v>
+        <v>5606</v>
       </c>
       <c r="D63" s="14">
         <v>1</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I63" s="14">
         <v>0</v>
@@ -7763,60 +7463,57 @@
         <v>0</v>
       </c>
       <c r="U63" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V63" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W63" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X63" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y63" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="14">
-        <v>0</v>
+        <v>56030001</v>
+      </c>
+      <c r="AA63" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="AB63" s="14" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC63" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD63" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A64" s="14">
-        <v>56060001</v>
+        <v>56080001</v>
       </c>
       <c r="B64" s="14">
         <v>4</v>
       </c>
       <c r="C64" s="14">
-        <v>5606</v>
+        <v>5608</v>
       </c>
       <c r="D64" s="14">
         <v>1</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G64" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I64" s="14">
         <v>0</v>
@@ -7855,60 +7552,57 @@
         <v>0</v>
       </c>
       <c r="U64" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V64" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W64" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X64" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y64" s="14">
-        <v>10000</v>
+        <v>56040001</v>
       </c>
       <c r="Z64" s="14">
         <v>0</v>
       </c>
-      <c r="AA64" s="14">
-        <v>56030001</v>
+      <c r="AA64" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="AB64" s="14" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC64" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD64" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A65" s="14">
-        <v>56080001</v>
+        <v>56100001</v>
       </c>
       <c r="B65" s="14">
         <v>4</v>
       </c>
       <c r="C65" s="14">
-        <v>5608</v>
+        <v>5610</v>
       </c>
       <c r="D65" s="14">
         <v>1</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="G65" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="I65" s="14">
         <v>0</v>
@@ -7947,45 +7641,42 @@
         <v>0</v>
       </c>
       <c r="U65" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V65" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W65" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X65" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y65" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z65" s="14">
-        <v>56040001</v>
-      </c>
-      <c r="AA65" s="14">
-        <v>0</v>
+        <v>56050001</v>
+      </c>
+      <c r="AA65" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="AB65" s="14" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC65" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD65" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A66" s="14">
-        <v>56100001</v>
+        <v>56130001</v>
       </c>
       <c r="B66" s="14">
         <v>4</v>
       </c>
       <c r="C66" s="14">
-        <v>5610</v>
+        <v>5613</v>
       </c>
       <c r="D66" s="14">
         <v>1</v>
@@ -7994,13 +7685,13 @@
         <v>140</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G66" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I66" s="14">
         <v>0</v>
@@ -8039,152 +7730,146 @@
         <v>0</v>
       </c>
       <c r="U66" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V66" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W66" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X66" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y66" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z66" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="14">
-        <v>56050001</v>
+        <v>56060001</v>
+      </c>
+      <c r="AA66" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="AB66" s="14" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC66" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A67" s="15">
+        <v>57010001</v>
+      </c>
+      <c r="B67" s="15">
+        <v>4</v>
+      </c>
+      <c r="C67" s="15">
+        <v>5701</v>
+      </c>
+      <c r="D67" s="15">
+        <v>1</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="I67" s="15">
+        <v>0</v>
+      </c>
+      <c r="J67" s="15">
+        <v>0</v>
+      </c>
+      <c r="K67" s="15">
+        <v>0</v>
+      </c>
+      <c r="L67" s="15">
+        <v>0</v>
+      </c>
+      <c r="M67" s="15">
+        <v>0</v>
+      </c>
+      <c r="N67" s="15">
+        <v>0</v>
+      </c>
+      <c r="O67" s="15">
+        <v>0</v>
+      </c>
+      <c r="P67" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="15">
+        <v>0</v>
+      </c>
+      <c r="R67" s="15">
+        <v>0</v>
+      </c>
+      <c r="S67" s="15">
+        <v>0</v>
+      </c>
+      <c r="T67" s="15">
+        <v>0</v>
+      </c>
+      <c r="U67" s="15">
+        <v>0</v>
+      </c>
+      <c r="V67" s="15">
+        <v>10000</v>
+      </c>
+      <c r="W67" s="15">
+        <v>0</v>
+      </c>
+      <c r="X67" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Y67" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="15">
+        <v>57010001</v>
+      </c>
+      <c r="AA67" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB67" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AD66" s="14" t="s">
+      <c r="AC67" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A67" s="14">
-        <v>56130001</v>
-      </c>
-      <c r="B67" s="14">
-        <v>4</v>
-      </c>
-      <c r="C67" s="14">
-        <v>5613</v>
-      </c>
-      <c r="D67" s="14">
-        <v>1</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="G67" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="I67" s="14">
-        <v>0</v>
-      </c>
-      <c r="J67" s="14">
-        <v>0</v>
-      </c>
-      <c r="K67" s="14">
-        <v>0</v>
-      </c>
-      <c r="L67" s="14">
-        <v>0</v>
-      </c>
-      <c r="M67" s="14">
-        <v>0</v>
-      </c>
-      <c r="N67" s="14">
-        <v>0</v>
-      </c>
-      <c r="O67" s="14">
-        <v>0</v>
-      </c>
-      <c r="P67" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="14">
-        <v>0</v>
-      </c>
-      <c r="R67" s="14">
-        <v>0</v>
-      </c>
-      <c r="S67" s="14">
-        <v>0</v>
-      </c>
-      <c r="T67" s="14">
-        <v>0</v>
-      </c>
-      <c r="U67" s="14">
-        <v>2</v>
-      </c>
-      <c r="V67" s="14">
-        <v>0</v>
-      </c>
-      <c r="W67" s="14">
-        <v>10000</v>
-      </c>
-      <c r="X67" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Z67" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="14">
-        <v>56060001</v>
-      </c>
-      <c r="AB67" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC67" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD67" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A68" s="15">
-        <v>57010001</v>
+        <v>57040001</v>
       </c>
       <c r="B68" s="15">
         <v>4</v>
       </c>
       <c r="C68" s="15">
-        <v>5701</v>
+        <v>5704</v>
       </c>
       <c r="D68" s="15">
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G68" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I68" s="15">
         <v>0</v>
@@ -8223,60 +7908,57 @@
         <v>0</v>
       </c>
       <c r="U68" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V68" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W68" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X68" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y68" s="15">
-        <v>10000</v>
+        <v>57020001</v>
       </c>
       <c r="Z68" s="15">
         <v>0</v>
       </c>
-      <c r="AA68" s="15">
-        <v>57010001</v>
+      <c r="AA68" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="AB68" s="15" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC68" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD68" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
-        <v>57040001</v>
+        <v>57060001</v>
       </c>
       <c r="B69" s="15">
         <v>4</v>
       </c>
       <c r="C69" s="15">
-        <v>5704</v>
+        <v>5706</v>
       </c>
       <c r="D69" s="15">
         <v>1</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G69" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I69" s="15">
         <v>0</v>
@@ -8315,60 +7997,57 @@
         <v>0</v>
       </c>
       <c r="U69" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V69" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W69" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X69" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y69" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="15">
-        <v>57020001</v>
-      </c>
-      <c r="AA69" s="15">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA69" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="AB69" s="15" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC69" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD69" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A70" s="15">
-        <v>57060001</v>
+        <v>57080001</v>
       </c>
       <c r="B70" s="15">
         <v>4</v>
       </c>
       <c r="C70" s="15">
-        <v>5706</v>
+        <v>5708</v>
       </c>
       <c r="D70" s="15">
         <v>1</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="G70" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
@@ -8407,60 +8086,57 @@
         <v>0</v>
       </c>
       <c r="U70" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V70" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W70" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X70" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y70" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="15">
-        <v>0</v>
+        <v>57040001</v>
+      </c>
+      <c r="AA70" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="AB70" s="15" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC70" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD70" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A71" s="15">
-        <v>57080001</v>
+        <v>57100001</v>
       </c>
       <c r="B71" s="15">
         <v>4</v>
       </c>
       <c r="C71" s="15">
-        <v>5708</v>
+        <v>5710</v>
       </c>
       <c r="D71" s="15">
         <v>1</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -8499,60 +8175,57 @@
         <v>0</v>
       </c>
       <c r="U71" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V71" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W71" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X71" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y71" s="15">
-        <v>10000</v>
+        <v>57050001</v>
       </c>
       <c r="Z71" s="15">
         <v>0</v>
       </c>
-      <c r="AA71" s="15">
-        <v>57040001</v>
+      <c r="AA71" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="AB71" s="15" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC71" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD71" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A72" s="15">
-        <v>57100001</v>
+        <v>57120001</v>
       </c>
       <c r="B72" s="15">
         <v>4</v>
       </c>
       <c r="C72" s="15">
-        <v>5710</v>
+        <v>5712</v>
       </c>
       <c r="D72" s="15">
         <v>1</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G72" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I72" s="15">
         <v>0</v>
@@ -8591,152 +8264,146 @@
         <v>0</v>
       </c>
       <c r="U72" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V72" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W72" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X72" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y72" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z72" s="15">
-        <v>57050001</v>
-      </c>
-      <c r="AA72" s="15">
-        <v>0</v>
+        <v>57060001</v>
+      </c>
+      <c r="AA72" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="AB72" s="15" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC72" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A73" s="16">
+        <v>58010001</v>
+      </c>
+      <c r="B73" s="16">
+        <v>4</v>
+      </c>
+      <c r="C73" s="16">
+        <v>5801</v>
+      </c>
+      <c r="D73" s="16">
+        <v>1</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="I73" s="16">
+        <v>0</v>
+      </c>
+      <c r="J73" s="16">
+        <v>0</v>
+      </c>
+      <c r="K73" s="16">
+        <v>0</v>
+      </c>
+      <c r="L73" s="16">
+        <v>0</v>
+      </c>
+      <c r="M73" s="16">
+        <v>0</v>
+      </c>
+      <c r="N73" s="16">
+        <v>0</v>
+      </c>
+      <c r="O73" s="16">
+        <v>0</v>
+      </c>
+      <c r="P73" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="16">
+        <v>0</v>
+      </c>
+      <c r="R73" s="16">
+        <v>0</v>
+      </c>
+      <c r="S73" s="16">
+        <v>0</v>
+      </c>
+      <c r="T73" s="16">
+        <v>0</v>
+      </c>
+      <c r="U73" s="16">
+        <v>0</v>
+      </c>
+      <c r="V73" s="16">
+        <v>10000</v>
+      </c>
+      <c r="W73" s="16">
+        <v>0</v>
+      </c>
+      <c r="X73" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Y73" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="16">
+        <v>58010001</v>
+      </c>
+      <c r="AA73" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB73" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AD72" s="15" t="s">
+      <c r="AC73" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A73" s="15">
-        <v>57120001</v>
-      </c>
-      <c r="B73" s="15">
-        <v>4</v>
-      </c>
-      <c r="C73" s="15">
-        <v>5712</v>
-      </c>
-      <c r="D73" s="15">
-        <v>1</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="G73" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="I73" s="15">
-        <v>0</v>
-      </c>
-      <c r="J73" s="15">
-        <v>0</v>
-      </c>
-      <c r="K73" s="15">
-        <v>0</v>
-      </c>
-      <c r="L73" s="15">
-        <v>0</v>
-      </c>
-      <c r="M73" s="15">
-        <v>0</v>
-      </c>
-      <c r="N73" s="15">
-        <v>0</v>
-      </c>
-      <c r="O73" s="15">
-        <v>0</v>
-      </c>
-      <c r="P73" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="15">
-        <v>0</v>
-      </c>
-      <c r="R73" s="15">
-        <v>0</v>
-      </c>
-      <c r="S73" s="15">
-        <v>0</v>
-      </c>
-      <c r="T73" s="15">
-        <v>0</v>
-      </c>
-      <c r="U73" s="15">
-        <v>3</v>
-      </c>
-      <c r="V73" s="15">
-        <v>0</v>
-      </c>
-      <c r="W73" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X73" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Z73" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="15">
-        <v>57060001</v>
-      </c>
-      <c r="AB73" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC73" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD73" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A74" s="16">
-        <v>58010001</v>
+        <v>58040001</v>
       </c>
       <c r="B74" s="16">
         <v>4</v>
       </c>
       <c r="C74" s="16">
-        <v>5801</v>
+        <v>5804</v>
       </c>
       <c r="D74" s="16">
         <v>1</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G74" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I74" s="16">
         <v>0</v>
@@ -8775,60 +8442,57 @@
         <v>0</v>
       </c>
       <c r="U74" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V74" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W74" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X74" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y74" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="16">
         <v>0</v>
       </c>
-      <c r="AA74" s="16">
-        <v>58010001</v>
+      <c r="AA74" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="AB74" s="16" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC74" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD74" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A75" s="16">
-        <v>58040001</v>
+        <v>58060001</v>
       </c>
       <c r="B75" s="16">
         <v>4</v>
       </c>
       <c r="C75" s="16">
-        <v>5804</v>
+        <v>5806</v>
       </c>
       <c r="D75" s="16">
         <v>1</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I75" s="16">
         <v>0</v>
@@ -8867,60 +8531,57 @@
         <v>0</v>
       </c>
       <c r="U75" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V75" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W75" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X75" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y75" s="16">
-        <v>10000</v>
+        <v>58030001</v>
       </c>
       <c r="Z75" s="16">
         <v>0</v>
       </c>
-      <c r="AA75" s="16">
-        <v>0</v>
+      <c r="AA75" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="AB75" s="16" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC75" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD75" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A76" s="16">
-        <v>58060001</v>
+        <v>58080001</v>
       </c>
       <c r="B76" s="16">
         <v>4</v>
       </c>
       <c r="C76" s="16">
-        <v>5806</v>
+        <v>5808</v>
       </c>
       <c r="D76" s="16">
         <v>1</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I76" s="16">
         <v>0</v>
@@ -8959,60 +8620,57 @@
         <v>0</v>
       </c>
       <c r="U76" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V76" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W76" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X76" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y76" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z76" s="16">
-        <v>58030001</v>
-      </c>
-      <c r="AA76" s="16">
-        <v>0</v>
+        <v>58040001</v>
+      </c>
+      <c r="AA76" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="AB76" s="16" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC76" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD76" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A77" s="16">
-        <v>58080001</v>
+        <v>58110001</v>
       </c>
       <c r="B77" s="16">
         <v>4</v>
       </c>
       <c r="C77" s="16">
-        <v>5808</v>
+        <v>5811</v>
       </c>
       <c r="D77" s="16">
         <v>1</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I77" s="16">
         <v>0</v>
@@ -9051,152 +8709,146 @@
         <v>0</v>
       </c>
       <c r="U77" s="16">
+        <v>0</v>
+      </c>
+      <c r="V77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="W77" s="16">
+        <v>0</v>
+      </c>
+      <c r="X77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Y77" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="16">
+        <v>58050001</v>
+      </c>
+      <c r="AA77" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC77" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A78" s="24">
+        <v>59010001</v>
+      </c>
+      <c r="B78" s="24">
         <v>4</v>
       </c>
-      <c r="V77" s="16">
-        <v>0</v>
-      </c>
-      <c r="W77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="X77" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Z77" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="16">
-        <v>58040001</v>
-      </c>
-      <c r="AB77" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC77" s="16" t="s">
+      <c r="C78" s="24">
+        <v>5901</v>
+      </c>
+      <c r="D78" s="24">
+        <v>1</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F78" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="I78" s="24">
+        <v>0</v>
+      </c>
+      <c r="J78" s="24">
+        <v>0</v>
+      </c>
+      <c r="K78" s="24">
+        <v>0</v>
+      </c>
+      <c r="L78" s="24">
+        <v>0</v>
+      </c>
+      <c r="M78" s="24">
+        <v>0</v>
+      </c>
+      <c r="N78" s="24">
+        <v>0</v>
+      </c>
+      <c r="O78" s="24">
+        <v>0</v>
+      </c>
+      <c r="P78" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="24">
+        <v>0</v>
+      </c>
+      <c r="R78" s="24">
+        <v>0</v>
+      </c>
+      <c r="S78" s="24">
+        <v>0</v>
+      </c>
+      <c r="T78" s="24">
+        <v>0</v>
+      </c>
+      <c r="U78" s="24">
+        <v>0</v>
+      </c>
+      <c r="V78" s="24">
+        <v>10000</v>
+      </c>
+      <c r="W78" s="24">
+        <v>0</v>
+      </c>
+      <c r="X78" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Y78" s="24">
+        <v>59010001</v>
+      </c>
+      <c r="Z78" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB78" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD77" s="16" t="s">
+      <c r="AC78" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A78" s="16">
-        <v>58110001</v>
-      </c>
-      <c r="B78" s="16">
-        <v>4</v>
-      </c>
-      <c r="C78" s="16">
-        <v>5811</v>
-      </c>
-      <c r="D78" s="16">
-        <v>1</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F78" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H78" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="I78" s="16">
-        <v>0</v>
-      </c>
-      <c r="J78" s="16">
-        <v>0</v>
-      </c>
-      <c r="K78" s="16">
-        <v>0</v>
-      </c>
-      <c r="L78" s="16">
-        <v>0</v>
-      </c>
-      <c r="M78" s="16">
-        <v>0</v>
-      </c>
-      <c r="N78" s="16">
-        <v>0</v>
-      </c>
-      <c r="O78" s="16">
-        <v>0</v>
-      </c>
-      <c r="P78" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="16">
-        <v>0</v>
-      </c>
-      <c r="R78" s="16">
-        <v>0</v>
-      </c>
-      <c r="S78" s="16">
-        <v>0</v>
-      </c>
-      <c r="T78" s="16">
-        <v>0</v>
-      </c>
-      <c r="U78" s="16">
-        <v>4</v>
-      </c>
-      <c r="V78" s="16">
-        <v>0</v>
-      </c>
-      <c r="W78" s="16">
-        <v>10000</v>
-      </c>
-      <c r="X78" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Z78" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="16">
-        <v>58050001</v>
-      </c>
-      <c r="AB78" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC78" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD78" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A79" s="24">
-        <v>59010001</v>
+        <v>59030001</v>
       </c>
       <c r="B79" s="24">
         <v>4</v>
       </c>
       <c r="C79" s="24">
-        <v>5901</v>
+        <v>5903</v>
       </c>
       <c r="D79" s="24">
         <v>1</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G79" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="I79" s="24">
         <v>0</v>
@@ -9238,57 +8890,54 @@
         <v>0</v>
       </c>
       <c r="V79" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W79" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X79" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y79" s="24">
-        <v>10000</v>
+        <v>59020001</v>
       </c>
       <c r="Z79" s="24">
-        <v>59010001</v>
-      </c>
-      <c r="AA79" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA79" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB79" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC79" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD79" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A80" s="24">
-        <v>59030001</v>
+        <v>59050001</v>
       </c>
       <c r="B80" s="24">
         <v>4</v>
       </c>
       <c r="C80" s="24">
-        <v>5903</v>
+        <v>5905</v>
       </c>
       <c r="D80" s="24">
         <v>1</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G80" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="I80" s="24">
         <v>0</v>
@@ -9330,57 +8979,54 @@
         <v>0</v>
       </c>
       <c r="V80" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W80" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X80" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y80" s="24">
-        <v>10000</v>
+        <v>59030001</v>
       </c>
       <c r="Z80" s="24">
-        <v>59020001</v>
-      </c>
-      <c r="AA80" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA80" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB80" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC80" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD80" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A81" s="24">
-        <v>59050001</v>
+        <v>59070001</v>
       </c>
       <c r="B81" s="24">
         <v>4</v>
       </c>
       <c r="C81" s="24">
-        <v>5905</v>
+        <v>5907</v>
       </c>
       <c r="D81" s="24">
         <v>1</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G81" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>265</v>
+        <v>183</v>
       </c>
       <c r="I81" s="24">
         <v>0</v>
@@ -9422,57 +9068,54 @@
         <v>0</v>
       </c>
       <c r="V81" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W81" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X81" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y81" s="24">
-        <v>10000</v>
+        <v>59040001</v>
       </c>
       <c r="Z81" s="24">
-        <v>59030001</v>
-      </c>
-      <c r="AA81" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA81" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB81" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC81" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD81" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A82" s="24">
-        <v>59070001</v>
+        <v>59090001</v>
       </c>
       <c r="B82" s="24">
         <v>4</v>
       </c>
       <c r="C82" s="24">
-        <v>5907</v>
+        <v>5909</v>
       </c>
       <c r="D82" s="24">
         <v>1</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G82" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I82" s="24">
         <v>0</v>
@@ -9514,57 +9157,54 @@
         <v>0</v>
       </c>
       <c r="V82" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W82" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X82" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y82" s="24">
-        <v>10000</v>
+        <v>59050001</v>
       </c>
       <c r="Z82" s="24">
-        <v>59040001</v>
-      </c>
-      <c r="AA82" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA82" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB82" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC82" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD82" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A83" s="24">
-        <v>59090001</v>
+        <v>59110001</v>
       </c>
       <c r="B83" s="24">
         <v>4</v>
       </c>
       <c r="C83" s="24">
-        <v>5909</v>
+        <v>5911</v>
       </c>
       <c r="D83" s="24">
         <v>1</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G83" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I83" s="24">
         <v>0</v>
@@ -9606,57 +9246,54 @@
         <v>0</v>
       </c>
       <c r="V83" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W83" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X83" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y83" s="24">
-        <v>10000</v>
+        <v>59060001</v>
       </c>
       <c r="Z83" s="24">
-        <v>59050001</v>
-      </c>
-      <c r="AA83" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA83" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB83" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC83" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD83" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A84" s="24">
-        <v>59110001</v>
+        <v>59130001</v>
       </c>
       <c r="B84" s="24">
         <v>4</v>
       </c>
       <c r="C84" s="24">
-        <v>5911</v>
+        <v>5913</v>
       </c>
       <c r="D84" s="24">
         <v>1</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G84" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I84" s="24">
         <v>0</v>
@@ -9698,57 +9335,54 @@
         <v>0</v>
       </c>
       <c r="V84" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W84" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X84" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y84" s="24">
-        <v>10000</v>
+        <v>59070001</v>
       </c>
       <c r="Z84" s="24">
-        <v>59060001</v>
-      </c>
-      <c r="AA84" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA84" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB84" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC84" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD84" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A85" s="24">
-        <v>59130001</v>
+        <v>59150001</v>
       </c>
       <c r="B85" s="24">
         <v>4</v>
       </c>
       <c r="C85" s="24">
-        <v>5913</v>
+        <v>5915</v>
       </c>
       <c r="D85" s="24">
         <v>1</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G85" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I85" s="24">
         <v>0</v>
@@ -9790,57 +9424,54 @@
         <v>0</v>
       </c>
       <c r="V85" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W85" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X85" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y85" s="24">
-        <v>10000</v>
+        <v>59080001</v>
       </c>
       <c r="Z85" s="24">
-        <v>59070001</v>
-      </c>
-      <c r="AA85" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA85" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB85" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC85" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD85" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A86" s="24">
-        <v>59150001</v>
+        <v>59180001</v>
       </c>
       <c r="B86" s="24">
         <v>4</v>
       </c>
       <c r="C86" s="24">
-        <v>5915</v>
+        <v>5918</v>
       </c>
       <c r="D86" s="24">
         <v>1</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G86" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I86" s="24">
         <v>0</v>
@@ -9882,57 +9513,54 @@
         <v>0</v>
       </c>
       <c r="V86" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W86" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X86" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y86" s="24">
-        <v>10000</v>
+        <v>59090001</v>
       </c>
       <c r="Z86" s="24">
-        <v>59080001</v>
-      </c>
-      <c r="AA86" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA86" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB86" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC86" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD86" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A87" s="24">
-        <v>59180001</v>
+        <v>59200001</v>
       </c>
       <c r="B87" s="24">
         <v>4</v>
       </c>
       <c r="C87" s="24">
-        <v>5918</v>
+        <v>5920</v>
       </c>
       <c r="D87" s="24">
         <v>1</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G87" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="I87" s="24">
         <v>0</v>
@@ -9974,57 +9602,54 @@
         <v>0</v>
       </c>
       <c r="V87" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W87" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X87" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y87" s="24">
-        <v>10000</v>
+        <v>59100001</v>
       </c>
       <c r="Z87" s="24">
-        <v>59090001</v>
-      </c>
-      <c r="AA87" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA87" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB87" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC87" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD87" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A88" s="24">
-        <v>59200001</v>
+        <v>59220001</v>
       </c>
       <c r="B88" s="24">
         <v>4</v>
       </c>
       <c r="C88" s="24">
-        <v>5920</v>
+        <v>5922</v>
       </c>
       <c r="D88" s="24">
         <v>1</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G88" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I88" s="24">
         <v>0</v>
@@ -10066,57 +9691,54 @@
         <v>0</v>
       </c>
       <c r="V88" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W88" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X88" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y88" s="24">
-        <v>10000</v>
+        <v>59110001</v>
       </c>
       <c r="Z88" s="24">
-        <v>59100001</v>
-      </c>
-      <c r="AA88" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA88" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB88" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC88" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD88" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A89" s="24">
-        <v>59220001</v>
+        <v>59240001</v>
       </c>
       <c r="B89" s="24">
         <v>4</v>
       </c>
       <c r="C89" s="24">
-        <v>5922</v>
+        <v>5924</v>
       </c>
       <c r="D89" s="24">
         <v>1</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="G89" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="I89" s="24">
         <v>0</v>
@@ -10158,149 +9780,143 @@
         <v>0</v>
       </c>
       <c r="V89" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W89" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X89" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y89" s="24">
-        <v>10000</v>
+        <v>59120001</v>
       </c>
       <c r="Z89" s="24">
-        <v>59110001</v>
-      </c>
-      <c r="AA89" s="24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA89" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="AB89" s="24" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC89" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD89" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A90" s="24">
-        <v>59240001</v>
-      </c>
-      <c r="B90" s="24">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A90" s="25">
+        <v>60010001</v>
+      </c>
+      <c r="B90" s="25">
         <v>4</v>
       </c>
-      <c r="C90" s="24">
-        <v>5924</v>
-      </c>
-      <c r="D90" s="24">
+      <c r="C90" s="25">
+        <v>6001</v>
+      </c>
+      <c r="D90" s="25">
         <v>1</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="F90" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="G90" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="H90" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="I90" s="24">
-        <v>0</v>
-      </c>
-      <c r="J90" s="24">
-        <v>0</v>
-      </c>
-      <c r="K90" s="24">
-        <v>0</v>
-      </c>
-      <c r="L90" s="24">
-        <v>0</v>
-      </c>
-      <c r="M90" s="24">
-        <v>0</v>
-      </c>
-      <c r="N90" s="24">
-        <v>0</v>
-      </c>
-      <c r="O90" s="24">
-        <v>0</v>
-      </c>
-      <c r="P90" s="24">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="24">
-        <v>0</v>
-      </c>
-      <c r="R90" s="24">
-        <v>0</v>
-      </c>
-      <c r="S90" s="24">
-        <v>0</v>
-      </c>
-      <c r="T90" s="24">
-        <v>0</v>
-      </c>
-      <c r="U90" s="24">
-        <v>0</v>
-      </c>
-      <c r="V90" s="24">
-        <v>0</v>
-      </c>
-      <c r="W90" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X90" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y90" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z90" s="24">
-        <v>59120001</v>
-      </c>
-      <c r="AA90" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB90" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC90" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD90" s="24" t="s">
-        <v>62</v>
+        <v>196</v>
+      </c>
+      <c r="F90" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="G90" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H90" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="I90" s="25">
+        <v>0</v>
+      </c>
+      <c r="J90" s="25">
+        <v>0</v>
+      </c>
+      <c r="K90" s="25">
+        <v>0</v>
+      </c>
+      <c r="L90" s="25">
+        <v>0</v>
+      </c>
+      <c r="M90" s="25">
+        <v>0</v>
+      </c>
+      <c r="N90" s="25">
+        <v>0</v>
+      </c>
+      <c r="O90" s="25">
+        <v>0</v>
+      </c>
+      <c r="P90" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="25">
+        <v>0</v>
+      </c>
+      <c r="R90" s="25">
+        <v>0</v>
+      </c>
+      <c r="S90" s="25">
+        <v>0</v>
+      </c>
+      <c r="T90" s="25">
+        <v>0</v>
+      </c>
+      <c r="U90" s="25">
+        <v>0</v>
+      </c>
+      <c r="V90" s="25">
+        <v>10000</v>
+      </c>
+      <c r="W90" s="25">
+        <v>0</v>
+      </c>
+      <c r="X90" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Y90" s="25">
+        <v>60010001</v>
+      </c>
+      <c r="Z90" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB90" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC90" s="25" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A91" s="25">
-        <v>60010001</v>
+        <v>60030001</v>
       </c>
       <c r="B91" s="25">
         <v>4</v>
       </c>
       <c r="C91" s="25">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="D91" s="25">
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G91" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>197</v>
+        <v>266</v>
       </c>
       <c r="I91" s="25">
         <v>0</v>
@@ -10342,57 +9958,54 @@
         <v>0</v>
       </c>
       <c r="V91" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W91" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X91" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y91" s="25">
-        <v>10000</v>
+        <v>60020001</v>
       </c>
       <c r="Z91" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="AA91" s="25">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA91" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="AB91" s="25" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="AC91" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD91" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A92" s="25">
-        <v>60030001</v>
+        <v>60060001</v>
       </c>
       <c r="B92" s="25">
         <v>4</v>
       </c>
       <c r="C92" s="25">
-        <v>6003</v>
+        <v>6006</v>
       </c>
       <c r="D92" s="25">
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G92" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
       <c r="I92" s="25">
         <v>0</v>
@@ -10434,57 +10047,54 @@
         <v>0</v>
       </c>
       <c r="V92" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W92" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X92" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y92" s="25">
-        <v>10000</v>
+        <v>60030001</v>
       </c>
       <c r="Z92" s="25">
-        <v>60020001</v>
-      </c>
-      <c r="AA92" s="25">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA92" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="AB92" s="25" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="AC92" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD92" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
-        <v>60060001</v>
+        <v>60090001</v>
       </c>
       <c r="B93" s="25">
         <v>4</v>
       </c>
       <c r="C93" s="25">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="D93" s="25">
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G93" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -10526,57 +10136,54 @@
         <v>0</v>
       </c>
       <c r="V93" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W93" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X93" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y93" s="25">
-        <v>10000</v>
+        <v>60040001</v>
       </c>
       <c r="Z93" s="25">
-        <v>60030001</v>
-      </c>
-      <c r="AA93" s="25">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA93" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="AB93" s="25" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="AC93" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD93" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
-        <v>60090001</v>
+        <v>60110001</v>
       </c>
       <c r="B94" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C94" s="25">
-        <v>6009</v>
+        <v>6011</v>
       </c>
       <c r="D94" s="25">
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="I94" s="25">
         <v>0</v>
@@ -10618,149 +10225,143 @@
         <v>0</v>
       </c>
       <c r="V94" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W94" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X94" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y94" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z94" s="25">
-        <v>60040001</v>
-      </c>
-      <c r="AA94" s="25">
-        <v>0</v>
+        <v>60070001</v>
+      </c>
+      <c r="Z94" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA94" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="AB94" s="25" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="AC94" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD94" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A95" s="25">
-        <v>60110001</v>
-      </c>
-      <c r="B95" s="25">
-        <v>6</v>
-      </c>
-      <c r="C95" s="25">
-        <v>6011</v>
-      </c>
-      <c r="D95" s="25">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A95" s="27">
+        <v>61020001</v>
+      </c>
+      <c r="B95" s="27">
+        <v>4</v>
+      </c>
+      <c r="C95" s="27">
+        <v>6102</v>
+      </c>
+      <c r="D95" s="27">
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="F95" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="G95" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="H95" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="I95" s="25">
-        <v>0</v>
-      </c>
-      <c r="J95" s="25">
-        <v>0</v>
-      </c>
-      <c r="K95" s="25">
-        <v>0</v>
-      </c>
-      <c r="L95" s="25">
-        <v>0</v>
-      </c>
-      <c r="M95" s="25">
-        <v>0</v>
-      </c>
-      <c r="N95" s="25">
-        <v>0</v>
-      </c>
-      <c r="O95" s="25">
-        <v>0</v>
-      </c>
-      <c r="P95" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="25">
-        <v>0</v>
-      </c>
-      <c r="R95" s="25">
-        <v>0</v>
-      </c>
-      <c r="S95" s="25">
-        <v>0</v>
-      </c>
-      <c r="T95" s="25">
-        <v>0</v>
-      </c>
-      <c r="U95" s="25">
-        <v>0</v>
-      </c>
-      <c r="V95" s="25">
-        <v>0</v>
-      </c>
-      <c r="W95" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X95" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y95" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z95" s="25">
-        <v>60070001</v>
-      </c>
-      <c r="AA95" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB95" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC95" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD95" s="25" t="s">
-        <v>64</v>
+        <v>205</v>
+      </c>
+      <c r="F95" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="G95" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="I95" s="27">
+        <v>0</v>
+      </c>
+      <c r="J95" s="27">
+        <v>0</v>
+      </c>
+      <c r="K95" s="27">
+        <v>0</v>
+      </c>
+      <c r="L95" s="27">
+        <v>0</v>
+      </c>
+      <c r="M95" s="27">
+        <v>0</v>
+      </c>
+      <c r="N95" s="27">
+        <v>0</v>
+      </c>
+      <c r="O95" s="27">
+        <v>0</v>
+      </c>
+      <c r="P95" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="27">
+        <v>0</v>
+      </c>
+      <c r="R95" s="27">
+        <v>0</v>
+      </c>
+      <c r="S95" s="27">
+        <v>0</v>
+      </c>
+      <c r="T95" s="27">
+        <v>0</v>
+      </c>
+      <c r="U95" s="27">
+        <v>0</v>
+      </c>
+      <c r="V95" s="27">
+        <v>10000</v>
+      </c>
+      <c r="W95" s="27">
+        <v>0</v>
+      </c>
+      <c r="X95" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Y95" s="27">
+        <v>61010001</v>
+      </c>
+      <c r="Z95" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB95" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC95" s="27" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A96" s="27">
-        <v>61020001</v>
+        <v>61040001</v>
       </c>
       <c r="B96" s="27">
         <v>4</v>
       </c>
       <c r="C96" s="27">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="D96" s="27">
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G96" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H96" s="27" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I96" s="27">
         <v>0</v>
@@ -10802,57 +10403,54 @@
         <v>0</v>
       </c>
       <c r="V96" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W96" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X96" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y96" s="27">
-        <v>10000</v>
+        <v>61020001</v>
       </c>
       <c r="Z96" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="AA96" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA96" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB96" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC96" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD96" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A97" s="27">
-        <v>61040001</v>
+        <v>61060001</v>
       </c>
       <c r="B97" s="27">
         <v>4</v>
       </c>
       <c r="C97" s="27">
-        <v>6104</v>
+        <v>6106</v>
       </c>
       <c r="D97" s="27">
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="G97" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H97" s="27" t="s">
-        <v>208</v>
+        <v>271</v>
       </c>
       <c r="I97" s="27">
         <v>0</v>
@@ -10894,57 +10492,54 @@
         <v>0</v>
       </c>
       <c r="V97" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W97" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X97" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y97" s="27">
-        <v>10000</v>
+        <v>61030001</v>
       </c>
       <c r="Z97" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="AA97" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA97" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB97" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC97" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD97" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
-        <v>61060001</v>
+        <v>61080001</v>
       </c>
       <c r="B98" s="27">
         <v>4</v>
       </c>
       <c r="C98" s="27">
-        <v>6106</v>
+        <v>6108</v>
       </c>
       <c r="D98" s="27">
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>270</v>
+        <v>95</v>
       </c>
       <c r="G98" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>271</v>
+        <v>95</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -10986,57 +10581,54 @@
         <v>0</v>
       </c>
       <c r="V98" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W98" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X98" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y98" s="27">
-        <v>10000</v>
+        <v>61040001</v>
       </c>
       <c r="Z98" s="27">
-        <v>61030001</v>
-      </c>
-      <c r="AA98" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA98" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB98" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC98" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD98" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
-        <v>61080001</v>
+        <v>61100001</v>
       </c>
       <c r="B99" s="27">
         <v>4</v>
       </c>
       <c r="C99" s="27">
-        <v>6108</v>
+        <v>6110</v>
       </c>
       <c r="D99" s="27">
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="G99" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -11078,57 +10670,54 @@
         <v>0</v>
       </c>
       <c r="V99" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W99" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X99" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y99" s="27">
-        <v>10000</v>
+        <v>61050001</v>
       </c>
       <c r="Z99" s="27">
-        <v>61040001</v>
-      </c>
-      <c r="AA99" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA99" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB99" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC99" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD99" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
-        <v>61100001</v>
+        <v>61120001</v>
       </c>
       <c r="B100" s="27">
         <v>4</v>
       </c>
       <c r="C100" s="27">
-        <v>6110</v>
+        <v>6112</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="G100" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -11170,57 +10759,54 @@
         <v>0</v>
       </c>
       <c r="V100" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W100" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X100" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y100" s="27">
-        <v>10000</v>
+        <v>61060001</v>
       </c>
       <c r="Z100" s="27">
-        <v>61050001</v>
-      </c>
-      <c r="AA100" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA100" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB100" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC100" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD100" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
-        <v>61120001</v>
+        <v>61140001</v>
       </c>
       <c r="B101" s="27">
         <v>4</v>
       </c>
       <c r="C101" s="27">
-        <v>6112</v>
+        <v>6114</v>
       </c>
       <c r="D101" s="27">
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G101" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -11262,57 +10848,54 @@
         <v>0</v>
       </c>
       <c r="V101" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W101" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X101" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y101" s="27">
-        <v>10000</v>
+        <v>61070001</v>
       </c>
       <c r="Z101" s="27">
-        <v>61060001</v>
-      </c>
-      <c r="AA101" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA101" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB101" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC101" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD101" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
-        <v>61140001</v>
+        <v>61160001</v>
       </c>
       <c r="B102" s="27">
         <v>4</v>
       </c>
       <c r="C102" s="27">
-        <v>6114</v>
+        <v>6116</v>
       </c>
       <c r="D102" s="27">
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G102" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -11354,57 +10937,54 @@
         <v>0</v>
       </c>
       <c r="V102" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W102" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X102" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y102" s="27">
-        <v>10000</v>
+        <v>61080001</v>
       </c>
       <c r="Z102" s="27">
-        <v>61070001</v>
-      </c>
-      <c r="AA102" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA102" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB102" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC102" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD102" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
-        <v>61160001</v>
+        <v>61180001</v>
       </c>
       <c r="B103" s="27">
         <v>4</v>
       </c>
       <c r="C103" s="27">
-        <v>6116</v>
+        <v>6118</v>
       </c>
       <c r="D103" s="27">
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G103" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -11446,127 +11026,32 @@
         <v>0</v>
       </c>
       <c r="V103" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W103" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X103" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y103" s="27">
-        <v>10000</v>
+        <v>61090001</v>
       </c>
       <c r="Z103" s="27">
-        <v>61080001</v>
-      </c>
-      <c r="AA103" s="27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA103" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="AB103" s="27" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AC103" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD103" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A104" s="27">
-        <v>61180001</v>
-      </c>
-      <c r="B104" s="27">
-        <v>4</v>
-      </c>
-      <c r="C104" s="27">
-        <v>6118</v>
-      </c>
-      <c r="D104" s="27">
-        <v>1</v>
-      </c>
-      <c r="E104" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="F104" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="G104" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H104" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="I104" s="27">
-        <v>0</v>
-      </c>
-      <c r="J104" s="27">
-        <v>0</v>
-      </c>
-      <c r="K104" s="27">
-        <v>0</v>
-      </c>
-      <c r="L104" s="27">
-        <v>0</v>
-      </c>
-      <c r="M104" s="27">
-        <v>0</v>
-      </c>
-      <c r="N104" s="27">
-        <v>0</v>
-      </c>
-      <c r="O104" s="27">
-        <v>0</v>
-      </c>
-      <c r="P104" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="27">
-        <v>0</v>
-      </c>
-      <c r="R104" s="27">
-        <v>0</v>
-      </c>
-      <c r="S104" s="27">
-        <v>0</v>
-      </c>
-      <c r="T104" s="27">
-        <v>0</v>
-      </c>
-      <c r="U104" s="27">
-        <v>0</v>
-      </c>
-      <c r="V104" s="27">
-        <v>0</v>
-      </c>
-      <c r="W104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X104" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z104" s="27">
-        <v>61090001</v>
-      </c>
-      <c r="AA104" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB104" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC104" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD104" s="27" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AB104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AA77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04FC212-D0B1-4530-9E46-1D26952C6008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0797EAF7-B638-4AEB-9F2B-E48BABD15539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -5,18 +5,18 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0797EAF7-B638-4AEB-9F2B-E48BABD15539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BB79B9-E9A1-4586-90ED-D7EE65E5CC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$X$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -179,68 +179,12 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1 目标单体
-2 自身单体
-3 目标为中心范围
-4 自身为中心范围
-</t>
+1 -允许无目标释放，无目标的时候以自身为目标释放
+0-不允许无目标释放</t>
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>李强:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 目标单体
-2 自身单体
-3 目标为中心范围
-4 自身为中心范围
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>李强:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 友方
-2 敌方 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
+    <comment ref="P4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
       <text>
         <r>
           <rPr>
@@ -254,7 +198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="Q4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
       <text>
         <r>
           <rPr>
@@ -271,24 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0-没有直接效果
-1-直接伤害：根据释放者的攻击力万分比
-2-直接回血：根据释放者的攻击力万分比
-3-直接回血：根据目标的生命最大值计算，百万分比</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
+    <comment ref="Y4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
       <text>
         <r>
           <rPr>
@@ -319,7 +246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
+    <comment ref="Z4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
       <text>
         <r>
           <rPr>
@@ -355,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="295">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -390,18 +317,9 @@
     <t>skill_cool_time</t>
   </si>
   <si>
-    <t>is_break</t>
-  </si>
-  <si>
     <t>is_no_target</t>
   </si>
   <si>
-    <t>target_type</t>
-  </si>
-  <si>
-    <t>damage_type</t>
-  </si>
-  <si>
     <t>main_target_damage</t>
   </si>
   <si>
@@ -435,18 +353,9 @@
     <t>技能释放冷却时间（豪秒）</t>
   </si>
   <si>
-    <t>是否打断当前动作（0-不 1-打断</t>
-  </si>
-  <si>
     <t>是否允许无目标释放（0-不允许 1-允许）</t>
   </si>
   <si>
-    <t>释放目标类型</t>
-  </si>
-  <si>
-    <t>伤害计算类型</t>
-  </si>
-  <si>
     <t>主目标直接伤害系数</t>
   </si>
   <si>
@@ -541,10 +450,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>scope_type</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>is_allow</t>
   </si>
   <si>
@@ -596,10 +501,6 @@
   </si>
   <si>
     <t>玩家3档技能1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标阵营</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -2085,7 +1986,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:Z104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2096,124 +1997,108 @@
     <col min="8" max="8" width="17.625" style="5" customWidth="1"/>
     <col min="9" max="11" width="22.5" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.75" style="5" customWidth="1"/>
-    <col min="15" max="15" width="19" style="5" customWidth="1"/>
-    <col min="16" max="16" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="60" style="5" customWidth="1"/>
-    <col min="22" max="22" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="28.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="5"/>
+    <col min="14" max="14" width="18" style="5" customWidth="1"/>
+    <col min="15" max="15" width="12.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="28.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:26" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="U2" s="33" t="s">
-        <v>300</v>
+        <v>67</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2224,7 +2109,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>6</v>
@@ -2239,165 +2124,141 @@
         <v>9</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q3" s="5" t="s">
+      <c r="T3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S3" s="1" t="s">
+      <c r="W3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="T3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="U3" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10101</v>
       </c>
@@ -2411,13 +2272,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9">
@@ -2442,52 +2303,40 @@
         <v>0</v>
       </c>
       <c r="P5" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="34">
+        <v>0</v>
       </c>
       <c r="R5" s="9">
         <v>0</v>
       </c>
       <c r="S5" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T5" s="9">
         <v>0</v>
       </c>
-      <c r="U5" s="34">
-        <v>0</v>
+      <c r="U5" s="9">
+        <v>10000</v>
       </c>
       <c r="V5" s="9">
         <v>0</v>
       </c>
-      <c r="W5" s="9">
-        <v>10000</v>
-      </c>
-      <c r="X5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD5" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="W5" s="10">
+        <v>0</v>
+      </c>
+      <c r="X5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z5" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10102</v>
       </c>
@@ -2501,13 +2350,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9">
@@ -2532,52 +2381,40 @@
         <v>0</v>
       </c>
       <c r="P6" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="34">
+        <v>0</v>
       </c>
       <c r="R6" s="9">
         <v>0</v>
       </c>
       <c r="S6" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T6" s="9">
         <v>0</v>
       </c>
-      <c r="U6" s="34">
-        <v>0</v>
+      <c r="U6" s="9">
+        <v>10000</v>
       </c>
       <c r="V6" s="9">
         <v>0</v>
       </c>
-      <c r="W6" s="9">
-        <v>10000</v>
-      </c>
-      <c r="X6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC6" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD6" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="W6" s="10">
+        <v>0</v>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z6" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10201</v>
       </c>
@@ -2591,13 +2428,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9">
@@ -2622,52 +2459,40 @@
         <v>0</v>
       </c>
       <c r="P7" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="34">
+        <v>0</v>
       </c>
       <c r="R7" s="9">
         <v>0</v>
       </c>
       <c r="S7" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T7" s="9">
         <v>0</v>
       </c>
-      <c r="U7" s="34">
-        <v>0</v>
+      <c r="U7" s="9">
+        <v>10000</v>
       </c>
       <c r="V7" s="9">
         <v>0</v>
       </c>
-      <c r="W7" s="9">
-        <v>10000</v>
-      </c>
-      <c r="X7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD7" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="W7" s="10">
+        <v>0</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z7" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10202</v>
       </c>
@@ -2681,13 +2506,13 @@
         <v>2</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9">
@@ -2712,52 +2537,40 @@
         <v>0</v>
       </c>
       <c r="P8" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="34">
+        <v>0</v>
       </c>
       <c r="R8" s="9">
         <v>0</v>
       </c>
       <c r="S8" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T8" s="9">
         <v>0</v>
       </c>
-      <c r="U8" s="34">
-        <v>0</v>
+      <c r="U8" s="9">
+        <v>10000</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
       </c>
-      <c r="W8" s="9">
-        <v>10000</v>
-      </c>
-      <c r="X8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD8" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="W8" s="10">
+        <v>0</v>
+      </c>
+      <c r="X8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z8" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10301</v>
       </c>
@@ -2771,13 +2584,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9">
@@ -2802,52 +2615,40 @@
         <v>0</v>
       </c>
       <c r="P9" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="34">
+        <v>0</v>
       </c>
       <c r="R9" s="9">
         <v>0</v>
       </c>
       <c r="S9" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T9" s="9">
         <v>0</v>
       </c>
-      <c r="U9" s="34">
-        <v>0</v>
+      <c r="U9" s="9">
+        <v>10000</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
       </c>
-      <c r="W9" s="9">
-        <v>10000</v>
-      </c>
-      <c r="X9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD9" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="W9" s="10">
+        <v>0</v>
+      </c>
+      <c r="X9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z9" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10302</v>
       </c>
@@ -2861,13 +2662,13 @@
         <v>3</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9">
@@ -2892,52 +2693,40 @@
         <v>0</v>
       </c>
       <c r="P10" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="34">
+        <v>0</v>
       </c>
       <c r="R10" s="9">
         <v>0</v>
       </c>
       <c r="S10" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T10" s="9">
         <v>0</v>
       </c>
-      <c r="U10" s="34">
-        <v>0</v>
+      <c r="U10" s="9">
+        <v>10000</v>
       </c>
       <c r="V10" s="9">
         <v>0</v>
       </c>
-      <c r="W10" s="9">
-        <v>10000</v>
-      </c>
-      <c r="X10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="9">
-        <v>10000</v>
-      </c>
-      <c r="Z10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD10" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="W10" s="10">
+        <v>0</v>
+      </c>
+      <c r="X10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z10" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>20001</v>
       </c>
@@ -2951,16 +2740,16 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -2978,58 +2767,46 @@
         <v>10000</v>
       </c>
       <c r="N11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="35">
+        <v>0</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
       </c>
       <c r="S11" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T11" s="2">
-        <v>1</v>
-      </c>
-      <c r="U11" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>10000</v>
       </c>
       <c r="V11" s="2">
         <v>0</v>
       </c>
       <c r="W11" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>20010001</v>
       </c>
@@ -3043,16 +2820,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -3070,58 +2847,46 @@
         <v>10000</v>
       </c>
       <c r="N12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="35">
+        <v>0</v>
       </c>
       <c r="R12" s="2">
         <v>0</v>
       </c>
       <c r="S12" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T12" s="2">
-        <v>1</v>
-      </c>
-      <c r="U12" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>10000</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
       </c>
       <c r="W12" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD12" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>20020001</v>
       </c>
@@ -3135,16 +2900,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
@@ -3162,58 +2927,46 @@
         <v>10000</v>
       </c>
       <c r="N13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="35">
+        <v>0</v>
       </c>
       <c r="R13" s="2">
         <v>0</v>
       </c>
       <c r="S13" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T13" s="2">
-        <v>1</v>
-      </c>
-      <c r="U13" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <v>10000</v>
       </c>
       <c r="V13" s="2">
         <v>0</v>
       </c>
       <c r="W13" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD13" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>20030001</v>
       </c>
@@ -3227,16 +2980,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -3254,58 +3007,46 @@
         <v>10000</v>
       </c>
       <c r="N14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="35">
+        <v>0</v>
       </c>
       <c r="R14" s="2">
         <v>0</v>
       </c>
       <c r="S14" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T14" s="2">
-        <v>1</v>
-      </c>
-      <c r="U14" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>10000</v>
       </c>
       <c r="V14" s="2">
         <v>0</v>
       </c>
       <c r="W14" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X14" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>20040001</v>
       </c>
@@ -3319,16 +3060,16 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -3346,58 +3087,46 @@
         <v>10000</v>
       </c>
       <c r="N15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="35">
+        <v>0</v>
       </c>
       <c r="R15" s="2">
         <v>0</v>
       </c>
       <c r="S15" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T15" s="2">
-        <v>1</v>
-      </c>
-      <c r="U15" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>10000</v>
       </c>
       <c r="V15" s="2">
         <v>0</v>
       </c>
       <c r="W15" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X15" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>20050001</v>
       </c>
@@ -3411,16 +3140,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I16" s="2">
         <v>2000</v>
@@ -3438,58 +3167,46 @@
         <v>10000</v>
       </c>
       <c r="N16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q16" s="35">
+        <v>0</v>
       </c>
       <c r="R16" s="2">
         <v>0</v>
       </c>
       <c r="S16" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T16" s="2">
-        <v>1</v>
-      </c>
-      <c r="U16" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>10000</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
       </c>
       <c r="W16" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X16" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD16" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>20060001</v>
       </c>
@@ -3503,16 +3220,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I17" s="2">
         <v>2000</v>
@@ -3530,58 +3247,46 @@
         <v>10000</v>
       </c>
       <c r="N17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="35">
+        <v>0</v>
       </c>
       <c r="R17" s="2">
         <v>0</v>
       </c>
       <c r="S17" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T17" s="2">
-        <v>1</v>
-      </c>
-      <c r="U17" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>10000</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
       </c>
       <c r="W17" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X17" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD17" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>20070001</v>
       </c>
@@ -3595,16 +3300,16 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I18" s="2">
         <v>2000</v>
@@ -3622,58 +3327,46 @@
         <v>10000</v>
       </c>
       <c r="N18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="35">
+        <v>0</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
       </c>
       <c r="S18" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T18" s="2">
-        <v>1</v>
-      </c>
-      <c r="U18" s="35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>10000</v>
       </c>
       <c r="V18" s="2">
         <v>0</v>
       </c>
       <c r="W18" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X18" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD18" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>20080001</v>
       </c>
@@ -3687,16 +3380,16 @@
         <v>1</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I19" s="2">
         <v>2000</v>
@@ -3714,58 +3407,46 @@
         <v>10000</v>
       </c>
       <c r="N19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" s="2">
         <v>0</v>
       </c>
       <c r="S19" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V19" s="2">
         <v>0</v>
       </c>
       <c r="W19" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X19" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD19" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20090001</v>
       </c>
@@ -3779,16 +3460,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I20" s="2">
         <v>2000</v>
@@ -3806,58 +3487,46 @@
         <v>10000</v>
       </c>
       <c r="N20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R20" s="2">
         <v>0</v>
       </c>
       <c r="S20" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V20" s="2">
         <v>0</v>
       </c>
       <c r="W20" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X20" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z20" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD20" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20100001</v>
       </c>
@@ -3871,16 +3540,16 @@
         <v>1</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I21" s="2">
         <v>2000</v>
@@ -3898,58 +3567,46 @@
         <v>10000</v>
       </c>
       <c r="N21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R21" s="2">
         <v>0</v>
       </c>
       <c r="S21" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V21" s="2">
         <v>0</v>
       </c>
       <c r="W21" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X21" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20110001</v>
       </c>
@@ -3963,16 +3620,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I22" s="2">
         <v>2000</v>
@@ -3990,58 +3647,46 @@
         <v>10000</v>
       </c>
       <c r="N22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R22" s="2">
         <v>0</v>
       </c>
       <c r="S22" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V22" s="2">
         <v>0</v>
       </c>
       <c r="W22" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X22" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD22" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20120001</v>
       </c>
@@ -4055,16 +3700,16 @@
         <v>1</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I23" s="2">
         <v>2000</v>
@@ -4082,58 +3727,46 @@
         <v>10000</v>
       </c>
       <c r="N23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R23" s="2">
         <v>0</v>
       </c>
       <c r="S23" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V23" s="2">
         <v>0</v>
       </c>
       <c r="W23" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X23" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD23" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20130001</v>
       </c>
@@ -4147,16 +3780,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I24" s="2">
         <v>2000</v>
@@ -4174,58 +3807,46 @@
         <v>10000</v>
       </c>
       <c r="N24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" s="2">
         <v>0</v>
       </c>
       <c r="S24" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V24" s="2">
         <v>0</v>
       </c>
       <c r="W24" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X24" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD24" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20140001</v>
       </c>
@@ -4239,16 +3860,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I25" s="2">
         <v>2000</v>
@@ -4266,58 +3887,46 @@
         <v>10000</v>
       </c>
       <c r="N25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" s="2">
         <v>0</v>
       </c>
       <c r="S25" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V25" s="2">
         <v>0</v>
       </c>
       <c r="W25" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X25" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z25" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>20150001</v>
       </c>
@@ -4331,16 +3940,16 @@
         <v>1</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I26" s="2">
         <v>2000</v>
@@ -4358,58 +3967,46 @@
         <v>10000</v>
       </c>
       <c r="N26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" s="2">
         <v>0</v>
       </c>
       <c r="S26" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V26" s="2">
         <v>0</v>
       </c>
       <c r="W26" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X26" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD26" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>20160001</v>
       </c>
@@ -4423,16 +4020,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I27" s="2">
         <v>2000</v>
@@ -4450,58 +4047,46 @@
         <v>10000</v>
       </c>
       <c r="N27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R27" s="2">
         <v>0</v>
       </c>
       <c r="S27" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="T27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V27" s="2">
         <v>0</v>
       </c>
       <c r="W27" s="2">
-        <v>10000</v>
-      </c>
-      <c r="X27" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="2">
-        <v>10000</v>
-      </c>
-      <c r="Z27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A28" s="23">
         <v>25010001</v>
       </c>
@@ -4515,16 +4100,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="I28" s="23">
         <v>0</v>
@@ -4548,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="P28" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" s="23">
         <v>0</v>
       </c>
       <c r="S28" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="23">
         <v>0</v>
@@ -4566,34 +4151,22 @@
         <v>0</v>
       </c>
       <c r="V28" s="23">
-        <v>0</v>
+        <v>54150001</v>
       </c>
       <c r="W28" s="23">
         <v>0</v>
       </c>
-      <c r="X28" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="23">
-        <v>54150001</v>
-      </c>
-      <c r="AA28" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC28" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD28" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X28" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y28" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z28" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>30001</v>
       </c>
@@ -4607,16 +4180,16 @@
         <v>1</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -4634,58 +4207,46 @@
         <v>10000</v>
       </c>
       <c r="N29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
       <c r="V29" s="3">
-        <v>0</v>
+        <v>1000001</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>4000001</v>
       </c>
@@ -4699,16 +4260,16 @@
         <v>1</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I30" s="3">
         <v>0</v>
@@ -4750,34 +4311,22 @@
         <v>0</v>
       </c>
       <c r="V30" s="3">
-        <v>0</v>
+        <v>2000001</v>
       </c>
       <c r="W30" s="3">
         <v>0</v>
       </c>
-      <c r="X30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="3">
-        <v>2000001</v>
-      </c>
-      <c r="AA30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD30" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z30" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21">
         <v>5000001</v>
       </c>
@@ -4791,16 +4340,16 @@
         <v>1</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="I31" s="21">
         <v>8000</v>
@@ -4821,55 +4370,43 @@
         <v>0</v>
       </c>
       <c r="O31" s="21">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="P31" s="21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q31" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31" s="21">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S31" s="21">
-        <v>9</v>
+        <v>12000</v>
       </c>
       <c r="T31" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" s="21">
-        <v>1</v>
+        <v>8000</v>
       </c>
       <c r="V31" s="21">
         <v>0</v>
       </c>
       <c r="W31" s="21">
-        <v>12000</v>
-      </c>
-      <c r="X31" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="21">
-        <v>8000</v>
-      </c>
-      <c r="Z31" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="21">
         <v>55010001</v>
       </c>
-      <c r="AB31" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC31" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD31" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="X31" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y31" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z31" s="21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A32" s="17">
         <v>6000001</v>
       </c>
@@ -4883,13 +4420,13 @@
         <v>1</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17">
@@ -4914,52 +4451,40 @@
         <v>0</v>
       </c>
       <c r="P32" s="17">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q32" s="17">
         <v>2</v>
       </c>
       <c r="R32" s="17">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S32" s="17">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T32" s="17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U32" s="17">
-        <v>2</v>
+        <v>12000</v>
       </c>
       <c r="V32" s="17">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W32" s="17">
-        <v>15000</v>
-      </c>
-      <c r="X32" s="17">
-        <v>120</v>
-      </c>
-      <c r="Y32" s="17">
-        <v>12000</v>
-      </c>
-      <c r="Z32" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="17">
         <v>56010001</v>
       </c>
-      <c r="AB32" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC32" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD32" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="X32" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y32" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z32" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A33" s="17">
         <v>6010001</v>
       </c>
@@ -4973,13 +4498,13 @@
         <v>1</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="17">
@@ -4998,58 +4523,46 @@
         <v>10000</v>
       </c>
       <c r="N33" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="17">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q33" s="17">
         <v>2</v>
       </c>
       <c r="R33" s="17">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S33" s="17">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T33" s="17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U33" s="17">
-        <v>2</v>
+        <v>12000</v>
       </c>
       <c r="V33" s="17">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W33" s="17">
-        <v>15000</v>
-      </c>
-      <c r="X33" s="17">
-        <v>120</v>
-      </c>
-      <c r="Y33" s="17">
-        <v>12000</v>
-      </c>
-      <c r="Z33" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="17">
         <v>56010001</v>
       </c>
-      <c r="AB33" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC33" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD33" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="X33" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y33" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z33" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="19">
         <v>7000001</v>
       </c>
@@ -5063,13 +4576,13 @@
         <v>1</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19">
@@ -5094,52 +4607,40 @@
         <v>0</v>
       </c>
       <c r="P34" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R34" s="19">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S34" s="19">
-        <v>1</v>
+        <v>15000</v>
       </c>
       <c r="T34" s="19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U34" s="19">
-        <v>4</v>
+        <v>12000</v>
       </c>
       <c r="V34" s="19">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W34" s="19">
-        <v>15000</v>
-      </c>
-      <c r="X34" s="19">
-        <v>120</v>
-      </c>
-      <c r="Y34" s="19">
-        <v>12000</v>
-      </c>
-      <c r="Z34" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="19">
         <v>57010001</v>
       </c>
-      <c r="AB34" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC34" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD34" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="X34" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y34" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z34" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A35" s="19">
         <v>7010001</v>
       </c>
@@ -5153,13 +4654,13 @@
         <v>1</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19">
@@ -5178,58 +4679,46 @@
         <v>10000</v>
       </c>
       <c r="N35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q35" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R35" s="19">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S35" s="19">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T35" s="19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U35" s="19">
-        <v>4</v>
+        <v>12000</v>
       </c>
       <c r="V35" s="19">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W35" s="19">
-        <v>15000</v>
-      </c>
-      <c r="X35" s="19">
-        <v>120</v>
-      </c>
-      <c r="Y35" s="19">
-        <v>12000</v>
-      </c>
-      <c r="Z35" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="19">
         <v>57010001</v>
       </c>
-      <c r="AB35" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC35" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD35" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="X35" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y35" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z35" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A36" s="20">
         <v>8000001</v>
       </c>
@@ -5243,13 +4732,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20">
@@ -5274,52 +4763,40 @@
         <v>0</v>
       </c>
       <c r="P36" s="20">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="20">
         <v>3</v>
       </c>
-      <c r="Q36" s="20">
-        <v>2</v>
-      </c>
       <c r="R36" s="20">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S36" s="20">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T36" s="20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U36" s="20">
-        <v>3</v>
+        <v>12000</v>
       </c>
       <c r="V36" s="20">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W36" s="20">
-        <v>15000</v>
-      </c>
-      <c r="X36" s="20">
-        <v>120</v>
-      </c>
-      <c r="Y36" s="20">
-        <v>12000</v>
-      </c>
-      <c r="Z36" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="20">
         <v>58010001</v>
       </c>
-      <c r="AB36" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC36" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD36" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="X36" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y36" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z36" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A37" s="20">
         <v>8010001</v>
       </c>
@@ -5333,13 +4810,13 @@
         <v>1</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20">
@@ -5358,58 +4835,46 @@
         <v>10000</v>
       </c>
       <c r="N37" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" s="20">
+        <v>9</v>
+      </c>
+      <c r="Q37" s="20">
         <v>3</v>
       </c>
-      <c r="Q37" s="20">
-        <v>2</v>
-      </c>
       <c r="R37" s="20">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S37" s="20">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T37" s="20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U37" s="20">
-        <v>3</v>
+        <v>12000</v>
       </c>
       <c r="V37" s="20">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W37" s="20">
-        <v>15000</v>
-      </c>
-      <c r="X37" s="20">
-        <v>120</v>
-      </c>
-      <c r="Y37" s="20">
-        <v>12000</v>
-      </c>
-      <c r="Z37" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="20">
         <v>58050001</v>
       </c>
-      <c r="AB37" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC37" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD37" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="X37" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y37" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z37" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A38" s="28">
         <v>9000001</v>
       </c>
@@ -5423,13 +4888,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H38" s="28"/>
       <c r="I38" s="28">
@@ -5448,58 +4913,46 @@
         <v>10000</v>
       </c>
       <c r="N38" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="28">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q38" s="32" t="s">
+        <v>294</v>
       </c>
       <c r="R38" s="28">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S38" s="28">
-        <v>1</v>
+        <v>15000</v>
       </c>
       <c r="T38" s="28">
-        <v>0</v>
-      </c>
-      <c r="U38" s="32" t="s">
-        <v>302</v>
+        <v>120</v>
+      </c>
+      <c r="U38" s="28">
+        <v>12000</v>
       </c>
       <c r="V38" s="28">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W38" s="28">
-        <v>15000</v>
-      </c>
-      <c r="X38" s="28">
-        <v>120</v>
+        <v>0</v>
+      </c>
+      <c r="X38" s="28" t="s">
+        <v>28</v>
       </c>
       <c r="Y38" s="28">
-        <v>12000</v>
+        <v>1</v>
       </c>
       <c r="Z38" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="28">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC38" s="28">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="30">
         <v>10010001</v>
       </c>
@@ -5513,13 +4966,13 @@
         <v>1</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H39" s="30"/>
       <c r="I39" s="30">
@@ -5544,52 +4997,40 @@
         <v>0</v>
       </c>
       <c r="P39" s="30">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q39" s="30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R39" s="30">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S39" s="30">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T39" s="30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U39" s="30">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="V39" s="30">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W39" s="30">
-        <v>15000</v>
-      </c>
-      <c r="X39" s="30">
-        <v>120</v>
-      </c>
-      <c r="Y39" s="30">
-        <v>12000</v>
-      </c>
-      <c r="Z39" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="30">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC39" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD39" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X39" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y39" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z39" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A40" s="30">
         <v>10020001</v>
       </c>
@@ -5603,13 +5044,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G40" s="30" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H40" s="30"/>
       <c r="I40" s="30">
@@ -5634,52 +5075,40 @@
         <v>0</v>
       </c>
       <c r="P40" s="30">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q40" s="30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R40" s="30">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S40" s="30">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T40" s="30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U40" s="30">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="V40" s="30">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W40" s="30">
-        <v>15000</v>
-      </c>
-      <c r="X40" s="30">
-        <v>120</v>
-      </c>
-      <c r="Y40" s="30">
-        <v>12000</v>
-      </c>
-      <c r="Z40" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="30">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC40" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD40" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X40" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y40" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z40" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A41" s="31">
         <v>11010001</v>
       </c>
@@ -5693,13 +5122,13 @@
         <v>1</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="31">
@@ -5724,52 +5153,40 @@
         <v>0</v>
       </c>
       <c r="P41" s="31">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q41" s="31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R41" s="31">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S41" s="31">
-        <v>9</v>
+        <v>15000</v>
       </c>
       <c r="T41" s="31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U41" s="31">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="V41" s="31">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="W41" s="31">
-        <v>15000</v>
-      </c>
-      <c r="X41" s="31">
-        <v>120</v>
-      </c>
-      <c r="Y41" s="31">
-        <v>12000</v>
-      </c>
-      <c r="Z41" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC41" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD41" s="31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X41" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y41" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z41" s="31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A42" s="23">
         <v>54010001</v>
       </c>
@@ -5783,16 +5200,16 @@
         <v>1</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I42" s="23">
         <v>0</v>
@@ -5834,34 +5251,22 @@
         <v>0</v>
       </c>
       <c r="V42" s="23">
-        <v>0</v>
+        <v>54010001</v>
       </c>
       <c r="W42" s="23">
         <v>0</v>
       </c>
-      <c r="X42" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="23">
-        <v>54010001</v>
-      </c>
-      <c r="AA42" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC42" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD42" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X42" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y42" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z42" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A43" s="23">
         <v>54030001</v>
       </c>
@@ -5875,16 +5280,16 @@
         <v>1</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I43" s="23">
         <v>0</v>
@@ -5926,34 +5331,22 @@
         <v>0</v>
       </c>
       <c r="V43" s="23">
-        <v>0</v>
+        <v>54020001</v>
       </c>
       <c r="W43" s="23">
         <v>0</v>
       </c>
-      <c r="X43" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="23">
-        <v>54020001</v>
-      </c>
-      <c r="AA43" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC43" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD43" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X43" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y43" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z43" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A44" s="23">
         <v>54050001</v>
       </c>
@@ -5967,16 +5360,16 @@
         <v>1</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I44" s="23">
         <v>0</v>
@@ -6018,34 +5411,22 @@
         <v>0</v>
       </c>
       <c r="V44" s="23">
-        <v>0</v>
+        <v>54030001</v>
       </c>
       <c r="W44" s="23">
         <v>0</v>
       </c>
-      <c r="X44" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="23">
-        <v>54030001</v>
-      </c>
-      <c r="AA44" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC44" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD44" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X44" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y44" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z44" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A45" s="23">
         <v>54070001</v>
       </c>
@@ -6059,16 +5440,16 @@
         <v>1</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I45" s="23">
         <v>0</v>
@@ -6110,34 +5491,22 @@
         <v>0</v>
       </c>
       <c r="V45" s="23">
-        <v>0</v>
+        <v>54040001</v>
       </c>
       <c r="W45" s="23">
         <v>0</v>
       </c>
-      <c r="X45" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="23">
-        <v>54040001</v>
-      </c>
-      <c r="AA45" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC45" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD45" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X45" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y45" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z45" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A46" s="23">
         <v>54090001</v>
       </c>
@@ -6151,16 +5520,16 @@
         <v>1</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I46" s="23">
         <v>0</v>
@@ -6202,34 +5571,22 @@
         <v>0</v>
       </c>
       <c r="V46" s="23">
-        <v>0</v>
+        <v>54050001</v>
       </c>
       <c r="W46" s="23">
         <v>0</v>
       </c>
-      <c r="X46" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="23">
-        <v>54050001</v>
-      </c>
-      <c r="AA46" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC46" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD46" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X46" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y46" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z46" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A47" s="23">
         <v>54110001</v>
       </c>
@@ -6243,16 +5600,16 @@
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I47" s="23">
         <v>0</v>
@@ -6294,34 +5651,22 @@
         <v>0</v>
       </c>
       <c r="V47" s="23">
-        <v>0</v>
+        <v>54060001</v>
       </c>
       <c r="W47" s="23">
         <v>0</v>
       </c>
-      <c r="X47" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="23">
-        <v>54060001</v>
-      </c>
-      <c r="AA47" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC47" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD47" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X47" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y47" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z47" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A48" s="23">
         <v>54130001</v>
       </c>
@@ -6335,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I48" s="23">
         <v>0</v>
@@ -6386,34 +5731,22 @@
         <v>0</v>
       </c>
       <c r="V48" s="23">
-        <v>0</v>
+        <v>54070001</v>
       </c>
       <c r="W48" s="23">
         <v>0</v>
       </c>
-      <c r="X48" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="23">
-        <v>54070001</v>
-      </c>
-      <c r="AA48" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC48" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD48" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X48" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y48" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z48" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A49" s="23">
         <v>54150001</v>
       </c>
@@ -6427,16 +5760,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I49" s="23">
         <v>0</v>
@@ -6478,34 +5811,22 @@
         <v>0</v>
       </c>
       <c r="V49" s="23">
-        <v>0</v>
+        <v>54080001</v>
       </c>
       <c r="W49" s="23">
         <v>0</v>
       </c>
-      <c r="X49" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="23">
-        <v>54080001</v>
-      </c>
-      <c r="AA49" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC49" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD49" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X49" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y49" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z49" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A50" s="23">
         <v>54170001</v>
       </c>
@@ -6519,16 +5840,16 @@
         <v>1</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I50" s="23">
         <v>0</v>
@@ -6573,31 +5894,19 @@
         <v>0</v>
       </c>
       <c r="W50" s="23">
-        <v>0</v>
-      </c>
-      <c r="X50" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="23">
         <v>54090001</v>
       </c>
-      <c r="AB50" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC50" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD50" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X50" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y50" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z50" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A51" s="23">
         <v>54190001</v>
       </c>
@@ -6611,16 +5920,16 @@
         <v>1</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I51" s="23">
         <v>0</v>
@@ -6662,34 +5971,22 @@
         <v>0</v>
       </c>
       <c r="V51" s="23">
-        <v>0</v>
+        <v>54100001</v>
       </c>
       <c r="W51" s="23">
         <v>0</v>
       </c>
-      <c r="X51" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="23">
-        <v>54100001</v>
-      </c>
-      <c r="AA51" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC51" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD51" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X51" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y51" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z51" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A52" s="23">
         <v>54210001</v>
       </c>
@@ -6703,16 +6000,16 @@
         <v>1</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I52" s="23">
         <v>0</v>
@@ -6757,31 +6054,19 @@
         <v>0</v>
       </c>
       <c r="W52" s="23">
-        <v>0</v>
-      </c>
-      <c r="X52" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="23">
         <v>54110001</v>
       </c>
-      <c r="AB52" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC52" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD52" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X52" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y52" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z52" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A53" s="23">
         <v>54230001</v>
       </c>
@@ -6795,16 +6080,16 @@
         <v>1</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="I53" s="23">
         <v>0</v>
@@ -6846,34 +6131,22 @@
         <v>0</v>
       </c>
       <c r="V53" s="23">
-        <v>0</v>
+        <v>54120001</v>
       </c>
       <c r="W53" s="23">
         <v>0</v>
       </c>
-      <c r="X53" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="23">
-        <v>54120001</v>
-      </c>
-      <c r="AA53" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC53" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD53" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X53" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y53" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z53" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A54" s="23">
         <v>54250001</v>
       </c>
@@ -6887,16 +6160,16 @@
         <v>1</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F54" s="23" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="I54" s="23">
         <v>0</v>
@@ -6938,34 +6211,22 @@
         <v>0</v>
       </c>
       <c r="V54" s="23">
-        <v>0</v>
+        <v>54130001</v>
       </c>
       <c r="W54" s="23">
         <v>0</v>
       </c>
-      <c r="X54" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="23">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="23">
-        <v>54130001</v>
-      </c>
-      <c r="AA54" s="23">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC54" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD54" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X54" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y54" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z54" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55" s="13">
         <v>55010001</v>
       </c>
@@ -6979,16 +6240,16 @@
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
@@ -7015,49 +6276,37 @@
         <v>0</v>
       </c>
       <c r="Q55" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="13">
         <v>0</v>
       </c>
       <c r="S55" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T55" s="13">
         <v>0</v>
       </c>
       <c r="U55" s="13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="V55" s="13">
         <v>0</v>
       </c>
       <c r="W55" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X55" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z55" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="13">
         <v>55010001</v>
       </c>
-      <c r="AB55" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC55" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD55" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X55" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y55" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z55" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A56" s="13">
         <v>55020001</v>
       </c>
@@ -7071,16 +6320,16 @@
         <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="I56" s="13">
         <v>0</v>
@@ -7107,49 +6356,37 @@
         <v>0</v>
       </c>
       <c r="Q56" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="13">
         <v>0</v>
       </c>
       <c r="S56" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T56" s="13">
         <v>0</v>
       </c>
       <c r="U56" s="13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="V56" s="13">
-        <v>0</v>
+        <v>55020001</v>
       </c>
       <c r="W56" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X56" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z56" s="13">
-        <v>55020001</v>
-      </c>
-      <c r="AA56" s="13">
         <v>55010001</v>
       </c>
-      <c r="AB56" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC56" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD56" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X56" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y56" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z56" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A57" s="13">
         <v>55030001</v>
       </c>
@@ -7163,16 +6400,16 @@
         <v>1</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -7199,49 +6436,37 @@
         <v>0</v>
       </c>
       <c r="Q57" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="13">
         <v>0</v>
       </c>
       <c r="S57" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T57" s="13">
         <v>0</v>
       </c>
       <c r="U57" s="13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="V57" s="13">
-        <v>0</v>
+        <v>55030001</v>
       </c>
       <c r="W57" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X57" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z57" s="13">
-        <v>55030001</v>
-      </c>
-      <c r="AA57" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC57" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD57" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X57" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y57" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z57" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A58" s="13">
         <v>55040001</v>
       </c>
@@ -7255,16 +6480,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I58" s="13">
         <v>0</v>
@@ -7291,49 +6516,37 @@
         <v>0</v>
       </c>
       <c r="Q58" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="13">
         <v>0</v>
       </c>
       <c r="S58" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T58" s="13">
         <v>0</v>
       </c>
       <c r="U58" s="13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="V58" s="13">
-        <v>0</v>
+        <v>55040001</v>
       </c>
       <c r="W58" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X58" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z58" s="13">
-        <v>55040001</v>
-      </c>
-      <c r="AA58" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC58" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD58" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X58" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y58" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z58" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A59" s="13">
         <v>55050001</v>
       </c>
@@ -7347,16 +6560,16 @@
         <v>1</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I59" s="13">
         <v>0</v>
@@ -7383,49 +6596,37 @@
         <v>0</v>
       </c>
       <c r="Q59" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="13">
         <v>0</v>
       </c>
       <c r="S59" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T59" s="13">
         <v>0</v>
       </c>
       <c r="U59" s="13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="V59" s="13">
         <v>0</v>
       </c>
       <c r="W59" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X59" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z59" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="13">
         <v>55050001</v>
       </c>
-      <c r="AB59" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC59" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD59" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X59" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y59" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z59" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A60" s="13">
         <v>55060001</v>
       </c>
@@ -7439,16 +6640,16 @@
         <v>1</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I60" s="13">
         <v>0</v>
@@ -7475,49 +6676,37 @@
         <v>0</v>
       </c>
       <c r="Q60" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="13">
         <v>0</v>
       </c>
       <c r="S60" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T60" s="13">
         <v>0</v>
       </c>
       <c r="U60" s="13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="V60" s="13">
-        <v>0</v>
+        <v>55060001</v>
       </c>
       <c r="W60" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X60" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z60" s="13">
-        <v>55060001</v>
-      </c>
-      <c r="AA60" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC60" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD60" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X60" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y60" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z60" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A61" s="13">
         <v>55070001</v>
       </c>
@@ -7531,16 +6720,16 @@
         <v>1</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="I61" s="13">
         <v>0</v>
@@ -7567,49 +6756,37 @@
         <v>0</v>
       </c>
       <c r="Q61" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="13">
         <v>0</v>
       </c>
       <c r="S61" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T61" s="13">
         <v>0</v>
       </c>
       <c r="U61" s="13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="V61" s="13">
-        <v>0</v>
+        <v>55070001</v>
       </c>
       <c r="W61" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X61" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Z61" s="13">
-        <v>55070001</v>
-      </c>
-      <c r="AA61" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC61" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD61" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X61" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y61" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z61" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A62" s="14">
         <v>56010001</v>
       </c>
@@ -7623,16 +6800,16 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I62" s="14">
         <v>0</v>
@@ -7659,49 +6836,37 @@
         <v>0</v>
       </c>
       <c r="Q62" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R62" s="14">
         <v>0</v>
       </c>
       <c r="S62" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T62" s="14">
         <v>0</v>
       </c>
       <c r="U62" s="14">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="V62" s="14">
         <v>0</v>
       </c>
       <c r="W62" s="14">
-        <v>10000</v>
-      </c>
-      <c r="X62" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Z62" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="14">
         <v>56010001</v>
       </c>
-      <c r="AB62" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC62" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD62" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X62" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y62" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z62" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A63" s="14">
         <v>56040001</v>
       </c>
@@ -7715,16 +6880,16 @@
         <v>1</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I63" s="14">
         <v>0</v>
@@ -7751,49 +6916,37 @@
         <v>0</v>
       </c>
       <c r="Q63" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R63" s="14">
         <v>0</v>
       </c>
       <c r="S63" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T63" s="14">
         <v>0</v>
       </c>
       <c r="U63" s="14">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="V63" s="14">
         <v>0</v>
       </c>
       <c r="W63" s="14">
-        <v>10000</v>
-      </c>
-      <c r="X63" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Z63" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC63" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD63" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X63" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y63" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z63" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A64" s="14">
         <v>56060001</v>
       </c>
@@ -7807,16 +6960,16 @@
         <v>1</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I64" s="14">
         <v>0</v>
@@ -7843,49 +6996,37 @@
         <v>0</v>
       </c>
       <c r="Q64" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R64" s="14">
         <v>0</v>
       </c>
       <c r="S64" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T64" s="14">
         <v>0</v>
       </c>
       <c r="U64" s="14">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="V64" s="14">
         <v>0</v>
       </c>
       <c r="W64" s="14">
-        <v>10000</v>
-      </c>
-      <c r="X64" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Z64" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="14">
         <v>56030001</v>
       </c>
-      <c r="AB64" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC64" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD64" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X64" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y64" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z64" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A65" s="14">
         <v>56080001</v>
       </c>
@@ -7899,16 +7040,16 @@
         <v>1</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="I65" s="14">
         <v>0</v>
@@ -7935,49 +7076,37 @@
         <v>0</v>
       </c>
       <c r="Q65" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65" s="14">
         <v>0</v>
       </c>
       <c r="S65" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T65" s="14">
         <v>0</v>
       </c>
       <c r="U65" s="14">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="V65" s="14">
-        <v>0</v>
+        <v>56040001</v>
       </c>
       <c r="W65" s="14">
-        <v>10000</v>
-      </c>
-      <c r="X65" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Z65" s="14">
-        <v>56040001</v>
-      </c>
-      <c r="AA65" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB65" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC65" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD65" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X65" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y65" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z65" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A66" s="14">
         <v>56100001</v>
       </c>
@@ -7991,16 +7120,16 @@
         <v>1</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="I66" s="14">
         <v>0</v>
@@ -8027,49 +7156,37 @@
         <v>0</v>
       </c>
       <c r="Q66" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R66" s="14">
         <v>0</v>
       </c>
       <c r="S66" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T66" s="14">
         <v>0</v>
       </c>
       <c r="U66" s="14">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="V66" s="14">
         <v>0</v>
       </c>
       <c r="W66" s="14">
-        <v>10000</v>
-      </c>
-      <c r="X66" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Z66" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="14">
         <v>56050001</v>
       </c>
-      <c r="AB66" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC66" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD66" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X66" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y66" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z66" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A67" s="14">
         <v>56130001</v>
       </c>
@@ -8083,16 +7200,16 @@
         <v>1</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I67" s="14">
         <v>0</v>
@@ -8119,49 +7236,37 @@
         <v>0</v>
       </c>
       <c r="Q67" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R67" s="14">
         <v>0</v>
       </c>
       <c r="S67" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T67" s="14">
         <v>0</v>
       </c>
       <c r="U67" s="14">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="V67" s="14">
         <v>0</v>
       </c>
       <c r="W67" s="14">
-        <v>10000</v>
-      </c>
-      <c r="X67" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Z67" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="14">
         <v>56060001</v>
       </c>
-      <c r="AB67" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC67" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD67" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X67" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y67" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z67" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A68" s="15">
         <v>57010001</v>
       </c>
@@ -8175,16 +7280,16 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="I68" s="15">
         <v>0</v>
@@ -8211,49 +7316,37 @@
         <v>0</v>
       </c>
       <c r="Q68" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R68" s="15">
         <v>0</v>
       </c>
       <c r="S68" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T68" s="15">
         <v>0</v>
       </c>
       <c r="U68" s="15">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="V68" s="15">
         <v>0</v>
       </c>
       <c r="W68" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X68" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Z68" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="15">
         <v>57010001</v>
       </c>
-      <c r="AB68" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC68" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD68" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X68" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y68" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z68" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
         <v>57040001</v>
       </c>
@@ -8267,16 +7360,16 @@
         <v>1</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I69" s="15">
         <v>0</v>
@@ -8303,49 +7396,37 @@
         <v>0</v>
       </c>
       <c r="Q69" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R69" s="15">
         <v>0</v>
       </c>
       <c r="S69" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T69" s="15">
         <v>0</v>
       </c>
       <c r="U69" s="15">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="V69" s="15">
-        <v>0</v>
+        <v>57020001</v>
       </c>
       <c r="W69" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X69" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Z69" s="15">
-        <v>57020001</v>
-      </c>
-      <c r="AA69" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB69" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC69" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD69" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X69" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y69" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z69" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A70" s="15">
         <v>57060001</v>
       </c>
@@ -8359,16 +7440,16 @@
         <v>1</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
@@ -8395,49 +7476,37 @@
         <v>0</v>
       </c>
       <c r="Q70" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R70" s="15">
         <v>0</v>
       </c>
       <c r="S70" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T70" s="15">
         <v>0</v>
       </c>
       <c r="U70" s="15">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="V70" s="15">
         <v>0</v>
       </c>
       <c r="W70" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X70" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Z70" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC70" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD70" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X70" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y70" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z70" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A71" s="15">
         <v>57080001</v>
       </c>
@@ -8451,16 +7520,16 @@
         <v>1</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -8487,49 +7556,37 @@
         <v>0</v>
       </c>
       <c r="Q71" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R71" s="15">
         <v>0</v>
       </c>
       <c r="S71" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T71" s="15">
         <v>0</v>
       </c>
       <c r="U71" s="15">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="V71" s="15">
         <v>0</v>
       </c>
       <c r="W71" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X71" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Z71" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="15">
         <v>57040001</v>
       </c>
-      <c r="AB71" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC71" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD71" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X71" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y71" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z71" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A72" s="15">
         <v>57100001</v>
       </c>
@@ -8543,16 +7600,16 @@
         <v>1</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I72" s="15">
         <v>0</v>
@@ -8579,49 +7636,37 @@
         <v>0</v>
       </c>
       <c r="Q72" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R72" s="15">
         <v>0</v>
       </c>
       <c r="S72" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T72" s="15">
         <v>0</v>
       </c>
       <c r="U72" s="15">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="V72" s="15">
-        <v>0</v>
+        <v>57050001</v>
       </c>
       <c r="W72" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X72" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Z72" s="15">
-        <v>57050001</v>
-      </c>
-      <c r="AA72" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC72" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD72" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X72" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y72" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z72" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A73" s="15">
         <v>57120001</v>
       </c>
@@ -8635,16 +7680,16 @@
         <v>1</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I73" s="15">
         <v>0</v>
@@ -8671,49 +7716,37 @@
         <v>0</v>
       </c>
       <c r="Q73" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R73" s="15">
         <v>0</v>
       </c>
       <c r="S73" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T73" s="15">
         <v>0</v>
       </c>
       <c r="U73" s="15">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="V73" s="15">
         <v>0</v>
       </c>
       <c r="W73" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X73" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Z73" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="15">
         <v>57060001</v>
       </c>
-      <c r="AB73" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC73" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD73" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X73" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y73" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z73" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A74" s="16">
         <v>58010001</v>
       </c>
@@ -8727,16 +7760,16 @@
         <v>1</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I74" s="16">
         <v>0</v>
@@ -8763,49 +7796,37 @@
         <v>0</v>
       </c>
       <c r="Q74" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R74" s="16">
         <v>0</v>
       </c>
       <c r="S74" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T74" s="16">
         <v>0</v>
       </c>
       <c r="U74" s="16">
-        <v>4</v>
+        <v>10000</v>
       </c>
       <c r="V74" s="16">
         <v>0</v>
       </c>
       <c r="W74" s="16">
-        <v>10000</v>
-      </c>
-      <c r="X74" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Z74" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="16">
         <v>58010001</v>
       </c>
-      <c r="AB74" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC74" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD74" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X74" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y74" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z74" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A75" s="16">
         <v>58040001</v>
       </c>
@@ -8819,16 +7840,16 @@
         <v>1</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I75" s="16">
         <v>0</v>
@@ -8855,49 +7876,37 @@
         <v>0</v>
       </c>
       <c r="Q75" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R75" s="16">
         <v>0</v>
       </c>
       <c r="S75" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T75" s="16">
         <v>0</v>
       </c>
       <c r="U75" s="16">
-        <v>4</v>
+        <v>10000</v>
       </c>
       <c r="V75" s="16">
         <v>0</v>
       </c>
       <c r="W75" s="16">
-        <v>10000</v>
-      </c>
-      <c r="X75" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Z75" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC75" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD75" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X75" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y75" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z75" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A76" s="16">
         <v>58060001</v>
       </c>
@@ -8911,16 +7920,16 @@
         <v>1</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I76" s="16">
         <v>0</v>
@@ -8947,49 +7956,37 @@
         <v>0</v>
       </c>
       <c r="Q76" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R76" s="16">
         <v>0</v>
       </c>
       <c r="S76" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T76" s="16">
         <v>0</v>
       </c>
       <c r="U76" s="16">
-        <v>4</v>
+        <v>10000</v>
       </c>
       <c r="V76" s="16">
-        <v>0</v>
+        <v>58030001</v>
       </c>
       <c r="W76" s="16">
-        <v>10000</v>
-      </c>
-      <c r="X76" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Z76" s="16">
-        <v>58030001</v>
-      </c>
-      <c r="AA76" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC76" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD76" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X76" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y76" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z76" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A77" s="16">
         <v>58080001</v>
       </c>
@@ -9003,16 +8000,16 @@
         <v>1</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="I77" s="16">
         <v>0</v>
@@ -9039,49 +8036,37 @@
         <v>0</v>
       </c>
       <c r="Q77" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R77" s="16">
         <v>0</v>
       </c>
       <c r="S77" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T77" s="16">
         <v>0</v>
       </c>
       <c r="U77" s="16">
-        <v>4</v>
+        <v>10000</v>
       </c>
       <c r="V77" s="16">
         <v>0</v>
       </c>
       <c r="W77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="X77" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Z77" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="16">
         <v>58040001</v>
       </c>
-      <c r="AB77" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC77" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD77" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X77" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y77" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z77" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A78" s="16">
         <v>58110001</v>
       </c>
@@ -9095,16 +8080,16 @@
         <v>1</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I78" s="16">
         <v>0</v>
@@ -9131,49 +8116,37 @@
         <v>0</v>
       </c>
       <c r="Q78" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R78" s="16">
         <v>0</v>
       </c>
       <c r="S78" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T78" s="16">
         <v>0</v>
       </c>
       <c r="U78" s="16">
-        <v>4</v>
+        <v>10000</v>
       </c>
       <c r="V78" s="16">
         <v>0</v>
       </c>
       <c r="W78" s="16">
-        <v>10000</v>
-      </c>
-      <c r="X78" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Z78" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="16">
         <v>58050001</v>
       </c>
-      <c r="AB78" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC78" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD78" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="X78" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y78" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z78" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A79" s="24">
         <v>59010001</v>
       </c>
@@ -9187,16 +8160,16 @@
         <v>1</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I79" s="24">
         <v>0</v>
@@ -9229,43 +8202,31 @@
         <v>0</v>
       </c>
       <c r="S79" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T79" s="24">
         <v>0</v>
       </c>
       <c r="U79" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V79" s="24">
-        <v>0</v>
+        <v>59010001</v>
       </c>
       <c r="W79" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X79" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y79" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z79" s="24">
-        <v>59010001</v>
-      </c>
-      <c r="AA79" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC79" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD79" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X79" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y79" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z79" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A80" s="24">
         <v>59030001</v>
       </c>
@@ -9279,16 +8240,16 @@
         <v>1</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="I80" s="24">
         <v>0</v>
@@ -9321,43 +8282,31 @@
         <v>0</v>
       </c>
       <c r="S80" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T80" s="24">
         <v>0</v>
       </c>
       <c r="U80" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V80" s="24">
-        <v>0</v>
+        <v>59020001</v>
       </c>
       <c r="W80" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X80" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z80" s="24">
-        <v>59020001</v>
-      </c>
-      <c r="AA80" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC80" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD80" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X80" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y80" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z80" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A81" s="24">
         <v>59050001</v>
       </c>
@@ -9371,16 +8320,16 @@
         <v>1</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="I81" s="24">
         <v>0</v>
@@ -9413,43 +8362,31 @@
         <v>0</v>
       </c>
       <c r="S81" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T81" s="24">
         <v>0</v>
       </c>
       <c r="U81" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V81" s="24">
-        <v>0</v>
+        <v>59030001</v>
       </c>
       <c r="W81" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X81" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z81" s="24">
-        <v>59030001</v>
-      </c>
-      <c r="AA81" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC81" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD81" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X81" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y81" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z81" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A82" s="24">
         <v>59070001</v>
       </c>
@@ -9463,16 +8400,16 @@
         <v>1</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I82" s="24">
         <v>0</v>
@@ -9505,43 +8442,31 @@
         <v>0</v>
       </c>
       <c r="S82" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T82" s="24">
         <v>0</v>
       </c>
       <c r="U82" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V82" s="24">
-        <v>0</v>
+        <v>59040001</v>
       </c>
       <c r="W82" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X82" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z82" s="24">
-        <v>59040001</v>
-      </c>
-      <c r="AA82" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC82" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD82" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X82" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y82" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z82" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A83" s="24">
         <v>59090001</v>
       </c>
@@ -9555,16 +8480,16 @@
         <v>1</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I83" s="24">
         <v>0</v>
@@ -9597,43 +8522,31 @@
         <v>0</v>
       </c>
       <c r="S83" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T83" s="24">
         <v>0</v>
       </c>
       <c r="U83" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V83" s="24">
-        <v>0</v>
+        <v>59050001</v>
       </c>
       <c r="W83" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X83" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z83" s="24">
-        <v>59050001</v>
-      </c>
-      <c r="AA83" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC83" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD83" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X83" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y83" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z83" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A84" s="24">
         <v>59110001</v>
       </c>
@@ -9647,16 +8560,16 @@
         <v>1</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I84" s="24">
         <v>0</v>
@@ -9689,43 +8602,31 @@
         <v>0</v>
       </c>
       <c r="S84" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T84" s="24">
         <v>0</v>
       </c>
       <c r="U84" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V84" s="24">
-        <v>0</v>
+        <v>59060001</v>
       </c>
       <c r="W84" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X84" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z84" s="24">
-        <v>59060001</v>
-      </c>
-      <c r="AA84" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB84" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC84" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD84" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X84" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y84" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z84" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A85" s="24">
         <v>59130001</v>
       </c>
@@ -9739,16 +8640,16 @@
         <v>1</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I85" s="24">
         <v>0</v>
@@ -9781,43 +8682,31 @@
         <v>0</v>
       </c>
       <c r="S85" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T85" s="24">
         <v>0</v>
       </c>
       <c r="U85" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V85" s="24">
-        <v>0</v>
+        <v>59070001</v>
       </c>
       <c r="W85" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X85" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y85" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z85" s="24">
-        <v>59070001</v>
-      </c>
-      <c r="AA85" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB85" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC85" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD85" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X85" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y85" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z85" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A86" s="24">
         <v>59150001</v>
       </c>
@@ -9831,16 +8720,16 @@
         <v>1</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I86" s="24">
         <v>0</v>
@@ -9873,43 +8762,31 @@
         <v>0</v>
       </c>
       <c r="S86" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T86" s="24">
         <v>0</v>
       </c>
       <c r="U86" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V86" s="24">
-        <v>0</v>
+        <v>59080001</v>
       </c>
       <c r="W86" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X86" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y86" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z86" s="24">
-        <v>59080001</v>
-      </c>
-      <c r="AA86" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB86" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC86" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD86" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X86" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y86" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z86" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A87" s="24">
         <v>59180001</v>
       </c>
@@ -9923,16 +8800,16 @@
         <v>1</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I87" s="24">
         <v>0</v>
@@ -9965,43 +8842,31 @@
         <v>0</v>
       </c>
       <c r="S87" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T87" s="24">
         <v>0</v>
       </c>
       <c r="U87" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V87" s="24">
-        <v>0</v>
+        <v>59090001</v>
       </c>
       <c r="W87" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X87" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y87" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z87" s="24">
-        <v>59090001</v>
-      </c>
-      <c r="AA87" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB87" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC87" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD87" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X87" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y87" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z87" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A88" s="24">
         <v>59200001</v>
       </c>
@@ -10015,16 +8880,16 @@
         <v>1</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I88" s="24">
         <v>0</v>
@@ -10057,43 +8922,31 @@
         <v>0</v>
       </c>
       <c r="S88" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T88" s="24">
         <v>0</v>
       </c>
       <c r="U88" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V88" s="24">
-        <v>0</v>
+        <v>59100001</v>
       </c>
       <c r="W88" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X88" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z88" s="24">
-        <v>59100001</v>
-      </c>
-      <c r="AA88" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB88" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC88" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD88" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X88" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y88" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z88" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A89" s="24">
         <v>59220001</v>
       </c>
@@ -10107,16 +8960,16 @@
         <v>1</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I89" s="24">
         <v>0</v>
@@ -10149,43 +9002,31 @@
         <v>0</v>
       </c>
       <c r="S89" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T89" s="24">
         <v>0</v>
       </c>
       <c r="U89" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V89" s="24">
-        <v>0</v>
+        <v>59110001</v>
       </c>
       <c r="W89" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X89" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z89" s="24">
-        <v>59110001</v>
-      </c>
-      <c r="AA89" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC89" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD89" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X89" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y89" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z89" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A90" s="24">
         <v>59240001</v>
       </c>
@@ -10199,16 +9040,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I90" s="24">
         <v>0</v>
@@ -10241,43 +9082,31 @@
         <v>0</v>
       </c>
       <c r="S90" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T90" s="24">
         <v>0</v>
       </c>
       <c r="U90" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V90" s="24">
-        <v>0</v>
+        <v>59120001</v>
       </c>
       <c r="W90" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X90" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y90" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Z90" s="24">
-        <v>59120001</v>
-      </c>
-      <c r="AA90" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB90" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC90" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD90" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X90" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y90" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z90" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A91" s="25">
         <v>60010001</v>
       </c>
@@ -10291,16 +9120,16 @@
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="G91" s="25" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I91" s="25">
         <v>0</v>
@@ -10333,43 +9162,31 @@
         <v>0</v>
       </c>
       <c r="S91" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T91" s="25">
         <v>0</v>
       </c>
       <c r="U91" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V91" s="25">
-        <v>0</v>
+        <v>60010001</v>
       </c>
       <c r="W91" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X91" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z91" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="AA91" s="25">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC91" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD91" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X91" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y91" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z91" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A92" s="25">
         <v>60030001</v>
       </c>
@@ -10383,16 +9200,16 @@
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="G92" s="25" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="I92" s="25">
         <v>0</v>
@@ -10425,43 +9242,31 @@
         <v>0</v>
       </c>
       <c r="S92" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T92" s="25">
         <v>0</v>
       </c>
       <c r="U92" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V92" s="25">
-        <v>0</v>
+        <v>60020001</v>
       </c>
       <c r="W92" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X92" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y92" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z92" s="25">
-        <v>60020001</v>
-      </c>
-      <c r="AA92" s="25">
-        <v>0</v>
-      </c>
-      <c r="AB92" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC92" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD92" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X92" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y92" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z92" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
         <v>60060001</v>
       </c>
@@ -10475,16 +9280,16 @@
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="G93" s="25" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -10517,43 +9322,31 @@
         <v>0</v>
       </c>
       <c r="S93" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T93" s="25">
         <v>0</v>
       </c>
       <c r="U93" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V93" s="25">
-        <v>0</v>
+        <v>60030001</v>
       </c>
       <c r="W93" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X93" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z93" s="25">
-        <v>60030001</v>
-      </c>
-      <c r="AA93" s="25">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC93" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD93" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X93" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y93" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z93" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
         <v>60090001</v>
       </c>
@@ -10567,16 +9360,16 @@
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G94" s="25" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I94" s="25">
         <v>0</v>
@@ -10609,43 +9402,31 @@
         <v>0</v>
       </c>
       <c r="S94" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T94" s="25">
         <v>0</v>
       </c>
       <c r="U94" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V94" s="25">
-        <v>0</v>
+        <v>60040001</v>
       </c>
       <c r="W94" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X94" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z94" s="25">
-        <v>60040001</v>
-      </c>
-      <c r="AA94" s="25">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC94" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD94" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X94" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y94" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z94" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A95" s="25">
         <v>60110001</v>
       </c>
@@ -10659,16 +9440,16 @@
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I95" s="25">
         <v>0</v>
@@ -10701,43 +9482,31 @@
         <v>0</v>
       </c>
       <c r="S95" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T95" s="25">
         <v>0</v>
       </c>
       <c r="U95" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V95" s="25">
-        <v>0</v>
-      </c>
-      <c r="W95" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X95" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y95" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z95" s="25">
         <v>60070001</v>
       </c>
-      <c r="AA95" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB95" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC95" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD95" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="W95" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="X95" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y95" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z95" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A96" s="27">
         <v>61020001</v>
       </c>
@@ -10751,16 +9520,16 @@
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G96" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H96" s="27" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="I96" s="27">
         <v>0</v>
@@ -10793,43 +9562,31 @@
         <v>0</v>
       </c>
       <c r="S96" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T96" s="27">
         <v>0</v>
       </c>
       <c r="U96" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V96" s="27">
-        <v>0</v>
+        <v>61010001</v>
       </c>
       <c r="W96" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X96" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z96" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="AA96" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC96" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD96" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X96" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y96" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z96" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A97" s="27">
         <v>61040001</v>
       </c>
@@ -10843,16 +9600,16 @@
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G97" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H97" s="27" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I97" s="27">
         <v>0</v>
@@ -10885,43 +9642,31 @@
         <v>0</v>
       </c>
       <c r="S97" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T97" s="27">
         <v>0</v>
       </c>
       <c r="U97" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V97" s="27">
-        <v>0</v>
+        <v>61020001</v>
       </c>
       <c r="W97" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X97" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y97" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z97" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="AA97" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB97" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC97" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD97" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X97" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y97" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z97" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
         <v>61060001</v>
       </c>
@@ -10935,16 +9680,16 @@
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="G98" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -10977,43 +9722,31 @@
         <v>0</v>
       </c>
       <c r="S98" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T98" s="27">
         <v>0</v>
       </c>
       <c r="U98" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V98" s="27">
-        <v>0</v>
+        <v>61030001</v>
       </c>
       <c r="W98" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X98" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y98" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z98" s="27">
-        <v>61030001</v>
-      </c>
-      <c r="AA98" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB98" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC98" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD98" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X98" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y98" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z98" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
         <v>61080001</v>
       </c>
@@ -11027,16 +9760,16 @@
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G99" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -11069,43 +9802,31 @@
         <v>0</v>
       </c>
       <c r="S99" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T99" s="27">
         <v>0</v>
       </c>
       <c r="U99" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V99" s="27">
-        <v>0</v>
+        <v>61040001</v>
       </c>
       <c r="W99" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X99" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y99" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z99" s="27">
-        <v>61040001</v>
-      </c>
-      <c r="AA99" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB99" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC99" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD99" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X99" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y99" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z99" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
         <v>61100001</v>
       </c>
@@ -11119,16 +9840,16 @@
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G100" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -11161,43 +9882,31 @@
         <v>0</v>
       </c>
       <c r="S100" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T100" s="27">
         <v>0</v>
       </c>
       <c r="U100" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V100" s="27">
-        <v>0</v>
+        <v>61050001</v>
       </c>
       <c r="W100" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X100" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z100" s="27">
-        <v>61050001</v>
-      </c>
-      <c r="AA100" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC100" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD100" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X100" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y100" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z100" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
         <v>61120001</v>
       </c>
@@ -11211,16 +9920,16 @@
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G101" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -11253,43 +9962,31 @@
         <v>0</v>
       </c>
       <c r="S101" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T101" s="27">
         <v>0</v>
       </c>
       <c r="U101" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V101" s="27">
-        <v>0</v>
+        <v>61060001</v>
       </c>
       <c r="W101" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X101" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z101" s="27">
-        <v>61060001</v>
-      </c>
-      <c r="AA101" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC101" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD101" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X101" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y101" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z101" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
         <v>61140001</v>
       </c>
@@ -11303,16 +10000,16 @@
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="G102" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -11345,43 +10042,31 @@
         <v>0</v>
       </c>
       <c r="S102" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T102" s="27">
         <v>0</v>
       </c>
       <c r="U102" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V102" s="27">
-        <v>0</v>
+        <v>61070001</v>
       </c>
       <c r="W102" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X102" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z102" s="27">
-        <v>61070001</v>
-      </c>
-      <c r="AA102" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC102" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD102" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X102" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y102" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z102" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
         <v>61160001</v>
       </c>
@@ -11395,16 +10080,16 @@
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G103" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -11437,43 +10122,31 @@
         <v>0</v>
       </c>
       <c r="S103" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T103" s="27">
         <v>0</v>
       </c>
       <c r="U103" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V103" s="27">
-        <v>0</v>
+        <v>61080001</v>
       </c>
       <c r="W103" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X103" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y103" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z103" s="27">
-        <v>61080001</v>
-      </c>
-      <c r="AA103" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB103" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC103" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD103" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X103" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y103" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z103" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A104" s="27">
         <v>61180001</v>
       </c>
@@ -11487,16 +10160,16 @@
         <v>1</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G104" s="27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H104" s="27" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I104" s="27">
         <v>0</v>
@@ -11529,44 +10202,32 @@
         <v>0</v>
       </c>
       <c r="S104" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T104" s="27">
         <v>0</v>
       </c>
       <c r="U104" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V104" s="27">
-        <v>0</v>
+        <v>61090001</v>
       </c>
       <c r="W104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X104" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z104" s="27">
-        <v>61090001</v>
-      </c>
-      <c r="AA104" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB104" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC104" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD104" s="27" t="s">
-        <v>62</v>
+        <v>0</v>
+      </c>
+      <c r="X104" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y104" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z104" s="27" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AB104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:X104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BB79B9-E9A1-4586-90ED-D7EE65E5CC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B942E6D-D462-4F5B-A59A-6B86D1DB3208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$X$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -179,12 +179,68 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1 -允许无目标释放，无目标的时候以自身为目标释放
-0-不允许无目标释放</t>
+1 目标单体
+2 自身单体
+3 目标为中心范围
+4 自身为中心范围
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
+    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>李强:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 目标单体
+2 自身单体
+3 目标为中心范围
+4 自身为中心范围
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>李强:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 友方
+2 敌方 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
       <text>
         <r>
           <rPr>
@@ -198,7 +254,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
+    <comment ref="T4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -215,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
+    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
       <text>
         <r>
           <rPr>
@@ -225,55 +281,10 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>1 死亡
-2 非死亡
-3 安全
-4 非安全
-5 无敌
-6 非无敌
-7 隐身
-8 非隐身
-9 定身
-10 非定身
-11 混乱
-12 非混乱
-13 在水面
-14 不在水面
-15 麻痹
-16 非麻痹
-17 眩晕
-18 非眩晕</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Z4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1 死亡
-2 非死亡
-3 安全
-4 非安全
-5 无敌
-6 非无敌
-7 隐身
-8 非隐身
-9 定身
-10 非定身
-11 混乱
-12 非混乱
-13 在水面
-14 不在水面
-15 麻痹
-16 非麻痹
-17 眩晕
-18 非眩晕</t>
+          <t>0-没有直接效果
+1-直接伤害：根据释放者的攻击力万分比
+2-直接回血：根据释放者的攻击力万分比
+3-直接回血：根据目标的生命最大值计算，百万分比</t>
         </r>
       </text>
     </comment>
@@ -282,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="292">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -317,9 +328,18 @@
     <t>skill_cool_time</t>
   </si>
   <si>
+    <t>is_break</t>
+  </si>
+  <si>
     <t>is_no_target</t>
   </si>
   <si>
+    <t>target_type</t>
+  </si>
+  <si>
+    <t>damage_type</t>
+  </si>
+  <si>
     <t>main_target_damage</t>
   </si>
   <si>
@@ -329,9 +349,6 @@
     <t>target_effect</t>
   </si>
   <si>
-    <t>target_effect_pro</t>
-  </si>
-  <si>
     <t>技能id</t>
   </si>
   <si>
@@ -353,9 +370,18 @@
     <t>技能释放冷却时间（豪秒）</t>
   </si>
   <si>
+    <t>是否打断当前动作（0-不 1-打断</t>
+  </si>
+  <si>
     <t>是否允许无目标释放（0-不允许 1-允许）</t>
   </si>
   <si>
+    <t>释放目标类型</t>
+  </si>
+  <si>
+    <t>伤害计算类型</t>
+  </si>
+  <si>
     <t>主目标直接伤害系数</t>
   </si>
   <si>
@@ -365,9 +391,6 @@
     <t>释放后对目标效果</t>
   </si>
   <si>
-    <t>效果同组几率</t>
-  </si>
-  <si>
     <t>0:0</t>
   </si>
   <si>
@@ -450,29 +473,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>is_allow</t>
-  </si>
-  <si>
-    <t>is_target</t>
-  </si>
-  <si>
-    <t>允许释放状态</t>
-  </si>
-  <si>
-    <t>能被选中的目标状态</t>
-  </si>
-  <si>
-    <t>2,4,5,6,7,8,9,10,12,14,16,18</t>
-  </si>
-  <si>
-    <t>2,4,6,8,9,10,11,12,14,15,16,17,18</t>
-  </si>
-  <si>
-    <t>2,4,5,6,7,8,9,10,12,14,16,18</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4,6,8,9,10,11,12,14,15,16,17,18</t>
+    <t>scope_type</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -504,6 +505,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>目标阵营</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>小怪-平A</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -518,9 +523,6 @@
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S_C</t>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S_C</t>
   </si>
   <si>
     <t>属性id-击中回血</t>
@@ -1986,7 +1988,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z104"/>
+  <dimension ref="A1:AA104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -1997,108 +1999,112 @@
     <col min="8" max="8" width="17.625" style="5" customWidth="1"/>
     <col min="9" max="11" width="22.5" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18" style="5" customWidth="1"/>
-    <col min="15" max="15" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.375" style="5" customWidth="1"/>
-    <col min="18" max="18" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="28.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="5"/>
+    <col min="14" max="14" width="12.75" style="5" customWidth="1"/>
+    <col min="15" max="15" width="19" style="5" customWidth="1"/>
+    <col min="16" max="16" width="12.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="60" style="5" customWidth="1"/>
+    <col min="22" max="22" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q2" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>70</v>
-      </c>
     </row>
-    <row r="3" spans="1:26" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2109,7 +2115,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>6</v>
@@ -2124,141 +2130,147 @@
         <v>9</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U3" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="J4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="R3" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>51</v>
+      <c r="AA4" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10101</v>
       </c>
@@ -2272,13 +2284,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9">
@@ -2303,40 +2315,43 @@
         <v>0</v>
       </c>
       <c r="P5" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="34">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>2</v>
       </c>
       <c r="R5" s="9">
         <v>0</v>
       </c>
       <c r="S5" s="9">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T5" s="9">
         <v>0</v>
       </c>
-      <c r="U5" s="9">
-        <v>10000</v>
+      <c r="U5" s="34">
+        <v>0</v>
       </c>
       <c r="V5" s="9">
         <v>0</v>
       </c>
-      <c r="W5" s="10">
-        <v>0</v>
-      </c>
-      <c r="X5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z5" s="10" t="s">
-        <v>57</v>
+      <c r="W5" s="9">
+        <v>10000</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>10000</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10102</v>
       </c>
@@ -2350,13 +2365,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9">
@@ -2381,40 +2396,43 @@
         <v>0</v>
       </c>
       <c r="P6" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="34">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>2</v>
       </c>
       <c r="R6" s="9">
         <v>0</v>
       </c>
       <c r="S6" s="9">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T6" s="9">
         <v>0</v>
       </c>
-      <c r="U6" s="9">
-        <v>10000</v>
+      <c r="U6" s="34">
+        <v>0</v>
       </c>
       <c r="V6" s="9">
         <v>0</v>
       </c>
-      <c r="W6" s="10">
-        <v>0</v>
-      </c>
-      <c r="X6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z6" s="10" t="s">
-        <v>57</v>
+      <c r="W6" s="9">
+        <v>10000</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>10000</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10201</v>
       </c>
@@ -2428,13 +2446,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9">
@@ -2459,40 +2477,43 @@
         <v>0</v>
       </c>
       <c r="P7" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="34">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>2</v>
       </c>
       <c r="R7" s="9">
         <v>0</v>
       </c>
       <c r="S7" s="9">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T7" s="9">
         <v>0</v>
       </c>
-      <c r="U7" s="9">
-        <v>10000</v>
+      <c r="U7" s="34">
+        <v>0</v>
       </c>
       <c r="V7" s="9">
         <v>0</v>
       </c>
-      <c r="W7" s="10">
-        <v>0</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y7" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z7" s="10" t="s">
-        <v>57</v>
+      <c r="W7" s="9">
+        <v>10000</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>10000</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10202</v>
       </c>
@@ -2506,13 +2527,13 @@
         <v>2</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9">
@@ -2537,40 +2558,43 @@
         <v>0</v>
       </c>
       <c r="P8" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="34">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>2</v>
       </c>
       <c r="R8" s="9">
         <v>0</v>
       </c>
       <c r="S8" s="9">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T8" s="9">
         <v>0</v>
       </c>
-      <c r="U8" s="9">
-        <v>10000</v>
+      <c r="U8" s="34">
+        <v>0</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
       </c>
-      <c r="W8" s="10">
-        <v>0</v>
-      </c>
-      <c r="X8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z8" s="10" t="s">
-        <v>57</v>
+      <c r="W8" s="9">
+        <v>10000</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>10000</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10301</v>
       </c>
@@ -2584,13 +2608,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9">
@@ -2615,40 +2639,43 @@
         <v>0</v>
       </c>
       <c r="P9" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="34">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>2</v>
       </c>
       <c r="R9" s="9">
         <v>0</v>
       </c>
       <c r="S9" s="9">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T9" s="9">
         <v>0</v>
       </c>
-      <c r="U9" s="9">
-        <v>10000</v>
+      <c r="U9" s="34">
+        <v>0</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
       </c>
-      <c r="W9" s="10">
-        <v>0</v>
-      </c>
-      <c r="X9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y9" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z9" s="10" t="s">
-        <v>57</v>
+      <c r="W9" s="9">
+        <v>10000</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>10000</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10302</v>
       </c>
@@ -2662,13 +2689,13 @@
         <v>3</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9">
@@ -2693,40 +2720,43 @@
         <v>0</v>
       </c>
       <c r="P10" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="34">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>2</v>
       </c>
       <c r="R10" s="9">
         <v>0</v>
       </c>
       <c r="S10" s="9">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T10" s="9">
         <v>0</v>
       </c>
-      <c r="U10" s="9">
-        <v>10000</v>
+      <c r="U10" s="34">
+        <v>0</v>
       </c>
       <c r="V10" s="9">
         <v>0</v>
       </c>
-      <c r="W10" s="10">
-        <v>0</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z10" s="10" t="s">
-        <v>57</v>
+      <c r="W10" s="9">
+        <v>10000</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>10000</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>20001</v>
       </c>
@@ -2740,17 +2770,17 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
@@ -2767,46 +2797,49 @@
         <v>10000</v>
       </c>
       <c r="N11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
       </c>
       <c r="S11" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T11" s="2">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="35">
+        <v>0</v>
       </c>
       <c r="V11" s="2">
         <v>0</v>
       </c>
       <c r="W11" s="2">
-        <v>0</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>20010001</v>
       </c>
@@ -2820,16 +2853,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -2847,46 +2880,49 @@
         <v>10000</v>
       </c>
       <c r="N12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>2</v>
       </c>
       <c r="R12" s="2">
         <v>0</v>
       </c>
       <c r="S12" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T12" s="2">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="35">
+        <v>0</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
       </c>
       <c r="W12" s="2">
-        <v>0</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>20020001</v>
       </c>
@@ -2900,16 +2936,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
@@ -2927,46 +2963,49 @@
         <v>10000</v>
       </c>
       <c r="N13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>2</v>
       </c>
       <c r="R13" s="2">
         <v>0</v>
       </c>
       <c r="S13" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T13" s="2">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U13" s="35">
+        <v>0</v>
       </c>
       <c r="V13" s="2">
         <v>0</v>
       </c>
       <c r="W13" s="2">
-        <v>0</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>20030001</v>
       </c>
@@ -2980,16 +3019,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -3007,46 +3046,49 @@
         <v>10000</v>
       </c>
       <c r="N14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>2</v>
       </c>
       <c r="R14" s="2">
         <v>0</v>
       </c>
       <c r="S14" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T14" s="2">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U14" s="35">
+        <v>0</v>
       </c>
       <c r="V14" s="2">
         <v>0</v>
       </c>
       <c r="W14" s="2">
-        <v>0</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>20040001</v>
       </c>
@@ -3060,16 +3102,16 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -3087,46 +3129,49 @@
         <v>10000</v>
       </c>
       <c r="N15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>2</v>
       </c>
       <c r="R15" s="2">
         <v>0</v>
       </c>
       <c r="S15" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T15" s="2">
-        <v>0</v>
-      </c>
-      <c r="U15" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U15" s="35">
+        <v>0</v>
       </c>
       <c r="V15" s="2">
         <v>0</v>
       </c>
       <c r="W15" s="2">
-        <v>0</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>20050001</v>
       </c>
@@ -3140,16 +3185,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I16" s="2">
         <v>2000</v>
@@ -3167,46 +3212,49 @@
         <v>10000</v>
       </c>
       <c r="N16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>2</v>
       </c>
       <c r="R16" s="2">
         <v>0</v>
       </c>
       <c r="S16" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T16" s="2">
-        <v>0</v>
-      </c>
-      <c r="U16" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U16" s="35">
+        <v>0</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
       </c>
       <c r="W16" s="2">
-        <v>0</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>20060001</v>
       </c>
@@ -3220,16 +3268,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I17" s="2">
         <v>2000</v>
@@ -3247,46 +3295,49 @@
         <v>10000</v>
       </c>
       <c r="N17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>2</v>
       </c>
       <c r="R17" s="2">
         <v>0</v>
       </c>
       <c r="S17" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T17" s="2">
-        <v>0</v>
-      </c>
-      <c r="U17" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="35">
+        <v>0</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
       </c>
       <c r="W17" s="2">
-        <v>0</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>20070001</v>
       </c>
@@ -3300,16 +3351,16 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I18" s="2">
         <v>2000</v>
@@ -3327,46 +3378,49 @@
         <v>10000</v>
       </c>
       <c r="N18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="35">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>2</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
       </c>
       <c r="S18" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T18" s="2">
-        <v>0</v>
-      </c>
-      <c r="U18" s="2">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="35">
+        <v>0</v>
       </c>
       <c r="V18" s="2">
         <v>0</v>
       </c>
       <c r="W18" s="2">
-        <v>0</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>20080001</v>
       </c>
@@ -3380,16 +3434,16 @@
         <v>1</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I19" s="2">
         <v>2000</v>
@@ -3407,46 +3461,49 @@
         <v>10000</v>
       </c>
       <c r="N19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" s="2">
         <v>0</v>
       </c>
       <c r="S19" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2">
         <v>0</v>
       </c>
       <c r="W19" s="2">
-        <v>0</v>
-      </c>
-      <c r="X19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z19" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20090001</v>
       </c>
@@ -3460,16 +3517,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I20" s="2">
         <v>2000</v>
@@ -3487,46 +3544,49 @@
         <v>10000</v>
       </c>
       <c r="N20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" s="2">
         <v>0</v>
       </c>
       <c r="S20" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2">
         <v>0</v>
       </c>
       <c r="W20" s="2">
-        <v>0</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20100001</v>
       </c>
@@ -3540,16 +3600,16 @@
         <v>1</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I21" s="2">
         <v>2000</v>
@@ -3567,46 +3627,49 @@
         <v>10000</v>
       </c>
       <c r="N21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R21" s="2">
         <v>0</v>
       </c>
       <c r="S21" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2">
         <v>0</v>
       </c>
       <c r="W21" s="2">
-        <v>0</v>
-      </c>
-      <c r="X21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z21" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20110001</v>
       </c>
@@ -3620,16 +3683,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I22" s="2">
         <v>2000</v>
@@ -3647,46 +3710,49 @@
         <v>10000</v>
       </c>
       <c r="N22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" s="2">
         <v>0</v>
       </c>
       <c r="S22" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2">
         <v>0</v>
       </c>
       <c r="W22" s="2">
-        <v>0</v>
-      </c>
-      <c r="X22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z22" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20120001</v>
       </c>
@@ -3700,16 +3766,16 @@
         <v>1</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I23" s="2">
         <v>2000</v>
@@ -3727,46 +3793,49 @@
         <v>10000</v>
       </c>
       <c r="N23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" s="2">
         <v>0</v>
       </c>
       <c r="S23" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2">
         <v>0</v>
       </c>
       <c r="W23" s="2">
-        <v>0</v>
-      </c>
-      <c r="X23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z23" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20130001</v>
       </c>
@@ -3780,16 +3849,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I24" s="2">
         <v>2000</v>
@@ -3807,46 +3876,49 @@
         <v>10000</v>
       </c>
       <c r="N24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24" s="2">
         <v>0</v>
       </c>
       <c r="S24" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2">
         <v>0</v>
       </c>
       <c r="W24" s="2">
-        <v>0</v>
-      </c>
-      <c r="X24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y24" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z24" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20140001</v>
       </c>
@@ -3860,16 +3932,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I25" s="2">
         <v>2000</v>
@@ -3887,46 +3959,49 @@
         <v>10000</v>
       </c>
       <c r="N25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" s="2">
         <v>0</v>
       </c>
       <c r="S25" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2">
         <v>0</v>
       </c>
       <c r="W25" s="2">
-        <v>0</v>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z25" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>20150001</v>
       </c>
@@ -3940,16 +4015,16 @@
         <v>1</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I26" s="2">
         <v>2000</v>
@@ -3967,46 +4042,49 @@
         <v>10000</v>
       </c>
       <c r="N26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26" s="2">
         <v>0</v>
       </c>
       <c r="S26" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2">
         <v>0</v>
       </c>
       <c r="W26" s="2">
-        <v>0</v>
-      </c>
-      <c r="X26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z26" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>20160001</v>
       </c>
@@ -4020,16 +4098,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I27" s="2">
         <v>2000</v>
@@ -4047,46 +4125,49 @@
         <v>10000</v>
       </c>
       <c r="N27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R27" s="2">
         <v>0</v>
       </c>
       <c r="S27" s="2">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="T27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2">
         <v>0</v>
       </c>
       <c r="W27" s="2">
-        <v>0</v>
-      </c>
-      <c r="X27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z27" s="2" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A28" s="23">
         <v>25010001</v>
       </c>
@@ -4100,16 +4181,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I28" s="23">
         <v>0</v>
@@ -4133,16 +4214,16 @@
         <v>0</v>
       </c>
       <c r="P28" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="23">
         <v>0</v>
       </c>
       <c r="S28" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="23">
         <v>0</v>
@@ -4151,22 +4232,25 @@
         <v>0</v>
       </c>
       <c r="V28" s="23">
+        <v>0</v>
+      </c>
+      <c r="W28" s="23">
+        <v>0</v>
+      </c>
+      <c r="X28" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="23">
         <v>54150001</v>
       </c>
-      <c r="W28" s="23">
-        <v>0</v>
-      </c>
-      <c r="X28" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y28" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z28" s="23" t="s">
-        <v>55</v>
+      <c r="AA28" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>30001</v>
       </c>
@@ -4180,16 +4264,16 @@
         <v>1</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -4207,46 +4291,49 @@
         <v>10000</v>
       </c>
       <c r="N29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>1000001</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>55</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>4000001</v>
       </c>
@@ -4260,16 +4347,16 @@
         <v>1</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I30" s="3">
         <v>0</v>
@@ -4311,22 +4398,25 @@
         <v>0</v>
       </c>
       <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
         <v>2000001</v>
       </c>
-      <c r="W30" s="3">
-        <v>0</v>
-      </c>
-      <c r="X30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z30" s="3" t="s">
-        <v>55</v>
+      <c r="AA30" s="3">
+        <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21">
         <v>5000001</v>
       </c>
@@ -4340,16 +4430,16 @@
         <v>1</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I31" s="21">
         <v>8000</v>
@@ -4370,43 +4460,46 @@
         <v>0</v>
       </c>
       <c r="O31" s="21">
+        <v>0</v>
+      </c>
+      <c r="P31" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="21">
+        <v>2</v>
+      </c>
+      <c r="R31" s="21">
         <v>5000</v>
       </c>
-      <c r="P31" s="21">
+      <c r="S31" s="21">
         <v>9</v>
       </c>
-      <c r="Q31" s="21">
-        <v>1</v>
-      </c>
-      <c r="R31" s="21">
-        <v>0</v>
-      </c>
-      <c r="S31" s="21">
+      <c r="T31" s="21">
+        <v>1</v>
+      </c>
+      <c r="U31" s="21">
+        <v>1</v>
+      </c>
+      <c r="V31" s="21">
+        <v>0</v>
+      </c>
+      <c r="W31" s="21">
         <v>12000</v>
       </c>
-      <c r="T31" s="21">
-        <v>0</v>
-      </c>
-      <c r="U31" s="21">
+      <c r="X31" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="21">
         <v>8000</v>
       </c>
-      <c r="V31" s="21">
-        <v>0</v>
-      </c>
-      <c r="W31" s="21">
+      <c r="Z31" s="21">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="21">
         <v>55010001</v>
       </c>
-      <c r="X31" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y31" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z31" s="21" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="32" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A32" s="17">
         <v>6000001</v>
       </c>
@@ -4420,13 +4513,13 @@
         <v>1</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17">
@@ -4451,40 +4544,43 @@
         <v>0</v>
       </c>
       <c r="P32" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="17">
         <v>2</v>
       </c>
       <c r="R32" s="17">
+        <v>0</v>
+      </c>
+      <c r="S32" s="17">
+        <v>9</v>
+      </c>
+      <c r="T32" s="17">
+        <v>0</v>
+      </c>
+      <c r="U32" s="17">
+        <v>2</v>
+      </c>
+      <c r="V32" s="17">
         <v>150</v>
       </c>
-      <c r="S32" s="17">
+      <c r="W32" s="17">
         <v>15000</v>
       </c>
-      <c r="T32" s="17">
+      <c r="X32" s="17">
         <v>120</v>
       </c>
-      <c r="U32" s="17">
+      <c r="Y32" s="17">
         <v>12000</v>
       </c>
-      <c r="V32" s="17">
-        <v>0</v>
-      </c>
-      <c r="W32" s="17">
+      <c r="Z32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="17">
         <v>56010001</v>
       </c>
-      <c r="X32" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y32" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z32" s="17" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="33" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A33" s="17">
         <v>6010001</v>
       </c>
@@ -4498,13 +4594,13 @@
         <v>1</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="17">
@@ -4523,46 +4619,49 @@
         <v>10000</v>
       </c>
       <c r="N33" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="17">
         <v>2</v>
       </c>
       <c r="R33" s="17">
+        <v>0</v>
+      </c>
+      <c r="S33" s="17">
+        <v>9</v>
+      </c>
+      <c r="T33" s="17">
+        <v>0</v>
+      </c>
+      <c r="U33" s="17">
+        <v>2</v>
+      </c>
+      <c r="V33" s="17">
         <v>150</v>
       </c>
-      <c r="S33" s="17">
+      <c r="W33" s="17">
         <v>15000</v>
       </c>
-      <c r="T33" s="17">
+      <c r="X33" s="17">
         <v>120</v>
       </c>
-      <c r="U33" s="17">
+      <c r="Y33" s="17">
         <v>12000</v>
       </c>
-      <c r="V33" s="17">
-        <v>0</v>
-      </c>
-      <c r="W33" s="17">
+      <c r="Z33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="17">
         <v>56010001</v>
       </c>
-      <c r="X33" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y33" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z33" s="17" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="34" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="19">
         <v>7000001</v>
       </c>
@@ -4576,13 +4675,13 @@
         <v>1</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19">
@@ -4607,40 +4706,43 @@
         <v>0</v>
       </c>
       <c r="P34" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="19">
+        <v>2</v>
+      </c>
+      <c r="R34" s="19">
+        <v>0</v>
+      </c>
+      <c r="S34" s="19">
+        <v>1</v>
+      </c>
+      <c r="T34" s="19">
+        <v>0</v>
+      </c>
+      <c r="U34" s="19">
         <v>4</v>
       </c>
-      <c r="R34" s="19">
+      <c r="V34" s="19">
         <v>150</v>
       </c>
-      <c r="S34" s="19">
+      <c r="W34" s="19">
         <v>15000</v>
       </c>
-      <c r="T34" s="19">
+      <c r="X34" s="19">
         <v>120</v>
       </c>
-      <c r="U34" s="19">
+      <c r="Y34" s="19">
         <v>12000</v>
       </c>
-      <c r="V34" s="19">
-        <v>0</v>
-      </c>
-      <c r="W34" s="19">
+      <c r="Z34" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="19">
         <v>57010001</v>
       </c>
-      <c r="X34" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y34" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z34" s="19" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="35" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A35" s="19">
         <v>7010001</v>
       </c>
@@ -4654,13 +4756,13 @@
         <v>1</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19">
@@ -4679,46 +4781,49 @@
         <v>10000</v>
       </c>
       <c r="N35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="19">
+        <v>2</v>
+      </c>
+      <c r="R35" s="19">
+        <v>0</v>
+      </c>
+      <c r="S35" s="19">
         <v>9</v>
       </c>
-      <c r="Q35" s="19">
+      <c r="T35" s="19">
+        <v>0</v>
+      </c>
+      <c r="U35" s="19">
         <v>4</v>
       </c>
-      <c r="R35" s="19">
+      <c r="V35" s="19">
         <v>150</v>
       </c>
-      <c r="S35" s="19">
+      <c r="W35" s="19">
         <v>15000</v>
       </c>
-      <c r="T35" s="19">
+      <c r="X35" s="19">
         <v>120</v>
       </c>
-      <c r="U35" s="19">
+      <c r="Y35" s="19">
         <v>12000</v>
       </c>
-      <c r="V35" s="19">
-        <v>0</v>
-      </c>
-      <c r="W35" s="19">
+      <c r="Z35" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="19">
         <v>57010001</v>
       </c>
-      <c r="X35" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y35" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z35" s="19" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="36" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A36" s="20">
         <v>8000001</v>
       </c>
@@ -4732,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20">
@@ -4763,40 +4868,43 @@
         <v>0</v>
       </c>
       <c r="P36" s="20">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="20">
+        <v>2</v>
+      </c>
+      <c r="R36" s="20">
+        <v>0</v>
+      </c>
+      <c r="S36" s="20">
         <v>9</v>
       </c>
-      <c r="Q36" s="20">
+      <c r="T36" s="20">
+        <v>0</v>
+      </c>
+      <c r="U36" s="20">
         <v>3</v>
       </c>
-      <c r="R36" s="20">
+      <c r="V36" s="20">
         <v>150</v>
       </c>
-      <c r="S36" s="20">
+      <c r="W36" s="20">
         <v>15000</v>
       </c>
-      <c r="T36" s="20">
+      <c r="X36" s="20">
         <v>120</v>
       </c>
-      <c r="U36" s="20">
+      <c r="Y36" s="20">
         <v>12000</v>
       </c>
-      <c r="V36" s="20">
-        <v>0</v>
-      </c>
-      <c r="W36" s="20">
+      <c r="Z36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="20">
         <v>58010001</v>
       </c>
-      <c r="X36" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y36" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z36" s="20" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="37" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A37" s="20">
         <v>8010001</v>
       </c>
@@ -4810,13 +4918,13 @@
         <v>1</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20">
@@ -4835,46 +4943,49 @@
         <v>10000</v>
       </c>
       <c r="N37" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="20">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="20">
+        <v>2</v>
+      </c>
+      <c r="R37" s="20">
+        <v>0</v>
+      </c>
+      <c r="S37" s="20">
         <v>9</v>
       </c>
-      <c r="Q37" s="20">
+      <c r="T37" s="20">
+        <v>0</v>
+      </c>
+      <c r="U37" s="20">
         <v>3</v>
       </c>
-      <c r="R37" s="20">
+      <c r="V37" s="20">
         <v>150</v>
       </c>
-      <c r="S37" s="20">
+      <c r="W37" s="20">
         <v>15000</v>
       </c>
-      <c r="T37" s="20">
+      <c r="X37" s="20">
         <v>120</v>
       </c>
-      <c r="U37" s="20">
+      <c r="Y37" s="20">
         <v>12000</v>
       </c>
-      <c r="V37" s="20">
-        <v>0</v>
-      </c>
-      <c r="W37" s="20">
+      <c r="Z37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="20">
         <v>58050001</v>
       </c>
-      <c r="X37" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z37" s="20" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="38" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A38" s="28">
         <v>9000001</v>
       </c>
@@ -4888,13 +4999,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H38" s="28"/>
       <c r="I38" s="28">
@@ -4913,46 +5024,49 @@
         <v>10000</v>
       </c>
       <c r="N38" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="28">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="32" t="s">
-        <v>294</v>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="28">
+        <v>0</v>
       </c>
       <c r="R38" s="28">
+        <v>0</v>
+      </c>
+      <c r="S38" s="28">
+        <v>1</v>
+      </c>
+      <c r="T38" s="28">
+        <v>0</v>
+      </c>
+      <c r="U38" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="V38" s="28">
         <v>150</v>
       </c>
-      <c r="S38" s="28">
+      <c r="W38" s="28">
         <v>15000</v>
       </c>
-      <c r="T38" s="28">
+      <c r="X38" s="28">
         <v>120</v>
       </c>
-      <c r="U38" s="28">
+      <c r="Y38" s="28">
         <v>12000</v>
       </c>
-      <c r="V38" s="28">
-        <v>0</v>
-      </c>
-      <c r="W38" s="28">
-        <v>0</v>
-      </c>
-      <c r="X38" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y38" s="28">
-        <v>1</v>
-      </c>
       <c r="Z38" s="28">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA38" s="28">
+        <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="30">
         <v>10010001</v>
       </c>
@@ -4966,13 +5080,13 @@
         <v>1</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H39" s="30"/>
       <c r="I39" s="30">
@@ -4997,40 +5111,43 @@
         <v>0</v>
       </c>
       <c r="P39" s="30">
+        <v>3</v>
+      </c>
+      <c r="Q39" s="30">
+        <v>2</v>
+      </c>
+      <c r="R39" s="30">
+        <v>0</v>
+      </c>
+      <c r="S39" s="30">
         <v>9</v>
       </c>
-      <c r="Q39" s="30">
-        <v>0</v>
-      </c>
-      <c r="R39" s="30">
+      <c r="T39" s="30">
+        <v>0</v>
+      </c>
+      <c r="U39" s="30">
+        <v>0</v>
+      </c>
+      <c r="V39" s="30">
         <v>150</v>
       </c>
-      <c r="S39" s="30">
+      <c r="W39" s="30">
         <v>15000</v>
       </c>
-      <c r="T39" s="30">
+      <c r="X39" s="30">
         <v>120</v>
       </c>
-      <c r="U39" s="30">
+      <c r="Y39" s="30">
         <v>12000</v>
       </c>
-      <c r="V39" s="30">
-        <v>0</v>
-      </c>
-      <c r="W39" s="30">
-        <v>0</v>
-      </c>
-      <c r="X39" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y39" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z39" s="30" t="s">
-        <v>57</v>
+      <c r="Z39" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="30">
+        <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A40" s="30">
         <v>10020001</v>
       </c>
@@ -5044,13 +5161,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G40" s="30" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H40" s="30"/>
       <c r="I40" s="30">
@@ -5075,40 +5192,43 @@
         <v>0</v>
       </c>
       <c r="P40" s="30">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="30">
+        <v>2</v>
+      </c>
+      <c r="R40" s="30">
+        <v>0</v>
+      </c>
+      <c r="S40" s="30">
         <v>9</v>
       </c>
-      <c r="Q40" s="30">
-        <v>0</v>
-      </c>
-      <c r="R40" s="30">
+      <c r="T40" s="30">
+        <v>0</v>
+      </c>
+      <c r="U40" s="30">
+        <v>0</v>
+      </c>
+      <c r="V40" s="30">
         <v>150</v>
       </c>
-      <c r="S40" s="30">
+      <c r="W40" s="30">
         <v>15000</v>
       </c>
-      <c r="T40" s="30">
+      <c r="X40" s="30">
         <v>120</v>
       </c>
-      <c r="U40" s="30">
+      <c r="Y40" s="30">
         <v>12000</v>
       </c>
-      <c r="V40" s="30">
-        <v>0</v>
-      </c>
-      <c r="W40" s="30">
-        <v>0</v>
-      </c>
-      <c r="X40" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y40" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z40" s="30" t="s">
-        <v>57</v>
+      <c r="Z40" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="30">
+        <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:26" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A41" s="31">
         <v>11010001</v>
       </c>
@@ -5122,13 +5242,13 @@
         <v>1</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="31">
@@ -5153,40 +5273,43 @@
         <v>0</v>
       </c>
       <c r="P41" s="31">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="31">
+        <v>2</v>
+      </c>
+      <c r="R41" s="31">
+        <v>0</v>
+      </c>
+      <c r="S41" s="31">
         <v>9</v>
       </c>
-      <c r="Q41" s="31">
-        <v>0</v>
-      </c>
-      <c r="R41" s="31">
+      <c r="T41" s="31">
+        <v>0</v>
+      </c>
+      <c r="U41" s="31">
+        <v>0</v>
+      </c>
+      <c r="V41" s="31">
         <v>150</v>
       </c>
-      <c r="S41" s="31">
+      <c r="W41" s="31">
         <v>15000</v>
       </c>
-      <c r="T41" s="31">
+      <c r="X41" s="31">
         <v>120</v>
       </c>
-      <c r="U41" s="31">
+      <c r="Y41" s="31">
         <v>12000</v>
       </c>
-      <c r="V41" s="31">
-        <v>0</v>
-      </c>
-      <c r="W41" s="31">
-        <v>0</v>
-      </c>
-      <c r="X41" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y41" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z41" s="31" t="s">
-        <v>57</v>
+      <c r="Z41" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="31">
+        <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A42" s="23">
         <v>54010001</v>
       </c>
@@ -5200,16 +5323,16 @@
         <v>1</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I42" s="23">
         <v>0</v>
@@ -5251,22 +5374,25 @@
         <v>0</v>
       </c>
       <c r="V42" s="23">
+        <v>0</v>
+      </c>
+      <c r="W42" s="23">
+        <v>0</v>
+      </c>
+      <c r="X42" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="23">
         <v>54010001</v>
       </c>
-      <c r="W42" s="23">
-        <v>0</v>
-      </c>
-      <c r="X42" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y42" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z42" s="23" t="s">
-        <v>55</v>
+      <c r="AA42" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A43" s="23">
         <v>54030001</v>
       </c>
@@ -5280,16 +5406,16 @@
         <v>1</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I43" s="23">
         <v>0</v>
@@ -5331,22 +5457,25 @@
         <v>0</v>
       </c>
       <c r="V43" s="23">
+        <v>0</v>
+      </c>
+      <c r="W43" s="23">
+        <v>0</v>
+      </c>
+      <c r="X43" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="23">
         <v>54020001</v>
       </c>
-      <c r="W43" s="23">
-        <v>0</v>
-      </c>
-      <c r="X43" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y43" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z43" s="23" t="s">
-        <v>55</v>
+      <c r="AA43" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A44" s="23">
         <v>54050001</v>
       </c>
@@ -5360,16 +5489,16 @@
         <v>1</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I44" s="23">
         <v>0</v>
@@ -5411,22 +5540,25 @@
         <v>0</v>
       </c>
       <c r="V44" s="23">
+        <v>0</v>
+      </c>
+      <c r="W44" s="23">
+        <v>0</v>
+      </c>
+      <c r="X44" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="23">
         <v>54030001</v>
       </c>
-      <c r="W44" s="23">
-        <v>0</v>
-      </c>
-      <c r="X44" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y44" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z44" s="23" t="s">
-        <v>55</v>
+      <c r="AA44" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A45" s="23">
         <v>54070001</v>
       </c>
@@ -5440,16 +5572,16 @@
         <v>1</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I45" s="23">
         <v>0</v>
@@ -5491,22 +5623,25 @@
         <v>0</v>
       </c>
       <c r="V45" s="23">
+        <v>0</v>
+      </c>
+      <c r="W45" s="23">
+        <v>0</v>
+      </c>
+      <c r="X45" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="23">
         <v>54040001</v>
       </c>
-      <c r="W45" s="23">
-        <v>0</v>
-      </c>
-      <c r="X45" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y45" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z45" s="23" t="s">
-        <v>55</v>
+      <c r="AA45" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A46" s="23">
         <v>54090001</v>
       </c>
@@ -5520,16 +5655,16 @@
         <v>1</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I46" s="23">
         <v>0</v>
@@ -5571,22 +5706,25 @@
         <v>0</v>
       </c>
       <c r="V46" s="23">
+        <v>0</v>
+      </c>
+      <c r="W46" s="23">
+        <v>0</v>
+      </c>
+      <c r="X46" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="23">
         <v>54050001</v>
       </c>
-      <c r="W46" s="23">
-        <v>0</v>
-      </c>
-      <c r="X46" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y46" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z46" s="23" t="s">
-        <v>55</v>
+      <c r="AA46" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A47" s="23">
         <v>54110001</v>
       </c>
@@ -5600,16 +5738,16 @@
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I47" s="23">
         <v>0</v>
@@ -5651,22 +5789,25 @@
         <v>0</v>
       </c>
       <c r="V47" s="23">
+        <v>0</v>
+      </c>
+      <c r="W47" s="23">
+        <v>0</v>
+      </c>
+      <c r="X47" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="23">
         <v>54060001</v>
       </c>
-      <c r="W47" s="23">
-        <v>0</v>
-      </c>
-      <c r="X47" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y47" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z47" s="23" t="s">
-        <v>55</v>
+      <c r="AA47" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A48" s="23">
         <v>54130001</v>
       </c>
@@ -5680,16 +5821,16 @@
         <v>1</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I48" s="23">
         <v>0</v>
@@ -5731,22 +5872,25 @@
         <v>0</v>
       </c>
       <c r="V48" s="23">
+        <v>0</v>
+      </c>
+      <c r="W48" s="23">
+        <v>0</v>
+      </c>
+      <c r="X48" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="23">
         <v>54070001</v>
       </c>
-      <c r="W48" s="23">
-        <v>0</v>
-      </c>
-      <c r="X48" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y48" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z48" s="23" t="s">
-        <v>55</v>
+      <c r="AA48" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A49" s="23">
         <v>54150001</v>
       </c>
@@ -5760,16 +5904,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I49" s="23">
         <v>0</v>
@@ -5811,22 +5955,25 @@
         <v>0</v>
       </c>
       <c r="V49" s="23">
+        <v>0</v>
+      </c>
+      <c r="W49" s="23">
+        <v>0</v>
+      </c>
+      <c r="X49" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="23">
         <v>54080001</v>
       </c>
-      <c r="W49" s="23">
-        <v>0</v>
-      </c>
-      <c r="X49" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y49" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z49" s="23" t="s">
-        <v>55</v>
+      <c r="AA49" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A50" s="23">
         <v>54170001</v>
       </c>
@@ -5840,17 +5987,17 @@
         <v>1</v>
       </c>
       <c r="E50" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F50" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>104</v>
-      </c>
       <c r="I50" s="23">
         <v>0</v>
       </c>
@@ -5894,19 +6041,22 @@
         <v>0</v>
       </c>
       <c r="W50" s="23">
+        <v>0</v>
+      </c>
+      <c r="X50" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="23">
         <v>54090001</v>
       </c>
-      <c r="X50" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y50" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z50" s="23" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A51" s="23">
         <v>54190001</v>
       </c>
@@ -5920,16 +6070,16 @@
         <v>1</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I51" s="23">
         <v>0</v>
@@ -5971,22 +6121,25 @@
         <v>0</v>
       </c>
       <c r="V51" s="23">
+        <v>0</v>
+      </c>
+      <c r="W51" s="23">
+        <v>0</v>
+      </c>
+      <c r="X51" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="23">
         <v>54100001</v>
       </c>
-      <c r="W51" s="23">
-        <v>0</v>
-      </c>
-      <c r="X51" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y51" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z51" s="23" t="s">
-        <v>55</v>
+      <c r="AA51" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A52" s="23">
         <v>54210001</v>
       </c>
@@ -6000,16 +6153,16 @@
         <v>1</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I52" s="23">
         <v>0</v>
@@ -6054,19 +6207,22 @@
         <v>0</v>
       </c>
       <c r="W52" s="23">
+        <v>0</v>
+      </c>
+      <c r="X52" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="23">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="23">
         <v>54110001</v>
       </c>
-      <c r="X52" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y52" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z52" s="23" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A53" s="23">
         <v>54230001</v>
       </c>
@@ -6080,16 +6236,16 @@
         <v>1</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I53" s="23">
         <v>0</v>
@@ -6131,22 +6287,25 @@
         <v>0</v>
       </c>
       <c r="V53" s="23">
+        <v>0</v>
+      </c>
+      <c r="W53" s="23">
+        <v>0</v>
+      </c>
+      <c r="X53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="23">
         <v>54120001</v>
       </c>
-      <c r="W53" s="23">
-        <v>0</v>
-      </c>
-      <c r="X53" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y53" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z53" s="23" t="s">
-        <v>55</v>
+      <c r="AA53" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A54" s="23">
         <v>54250001</v>
       </c>
@@ -6160,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F54" s="23" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I54" s="23">
         <v>0</v>
@@ -6211,22 +6370,25 @@
         <v>0</v>
       </c>
       <c r="V54" s="23">
+        <v>0</v>
+      </c>
+      <c r="W54" s="23">
+        <v>0</v>
+      </c>
+      <c r="X54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="23">
         <v>54130001</v>
       </c>
-      <c r="W54" s="23">
-        <v>0</v>
-      </c>
-      <c r="X54" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y54" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z54" s="23" t="s">
-        <v>55</v>
+      <c r="AA54" s="23">
+        <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="13">
         <v>55010001</v>
       </c>
@@ -6240,16 +6402,16 @@
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
@@ -6276,37 +6438,40 @@
         <v>0</v>
       </c>
       <c r="Q55" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="13">
         <v>0</v>
       </c>
       <c r="S55" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T55" s="13">
         <v>0</v>
       </c>
       <c r="U55" s="13">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V55" s="13">
         <v>0</v>
       </c>
       <c r="W55" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X55" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="13">
         <v>55010001</v>
       </c>
-      <c r="X55" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y55" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z55" s="13" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="13">
         <v>55020001</v>
       </c>
@@ -6320,16 +6485,16 @@
         <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I56" s="13">
         <v>0</v>
@@ -6356,37 +6521,40 @@
         <v>0</v>
       </c>
       <c r="Q56" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="13">
         <v>0</v>
       </c>
       <c r="S56" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T56" s="13">
         <v>0</v>
       </c>
       <c r="U56" s="13">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V56" s="13">
+        <v>0</v>
+      </c>
+      <c r="W56" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X56" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z56" s="13">
         <v>55020001</v>
       </c>
-      <c r="W56" s="13">
+      <c r="AA56" s="13">
         <v>55010001</v>
       </c>
-      <c r="X56" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y56" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z56" s="13" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57" s="13">
         <v>55030001</v>
       </c>
@@ -6400,16 +6568,16 @@
         <v>1</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -6436,37 +6604,40 @@
         <v>0</v>
       </c>
       <c r="Q57" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" s="13">
         <v>0</v>
       </c>
       <c r="S57" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T57" s="13">
         <v>0</v>
       </c>
       <c r="U57" s="13">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V57" s="13">
+        <v>0</v>
+      </c>
+      <c r="W57" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X57" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z57" s="13">
         <v>55030001</v>
       </c>
-      <c r="W57" s="13">
-        <v>0</v>
-      </c>
-      <c r="X57" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y57" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z57" s="13" t="s">
-        <v>55</v>
+      <c r="AA57" s="13">
+        <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="13">
         <v>55040001</v>
       </c>
@@ -6480,16 +6651,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I58" s="13">
         <v>0</v>
@@ -6516,37 +6687,40 @@
         <v>0</v>
       </c>
       <c r="Q58" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" s="13">
         <v>0</v>
       </c>
       <c r="S58" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T58" s="13">
         <v>0</v>
       </c>
       <c r="U58" s="13">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V58" s="13">
+        <v>0</v>
+      </c>
+      <c r="W58" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X58" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z58" s="13">
         <v>55040001</v>
       </c>
-      <c r="W58" s="13">
-        <v>0</v>
-      </c>
-      <c r="X58" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y58" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z58" s="13" t="s">
-        <v>55</v>
+      <c r="AA58" s="13">
+        <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="13">
         <v>55050001</v>
       </c>
@@ -6560,16 +6734,16 @@
         <v>1</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I59" s="13">
         <v>0</v>
@@ -6596,37 +6770,40 @@
         <v>0</v>
       </c>
       <c r="Q59" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" s="13">
         <v>0</v>
       </c>
       <c r="S59" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T59" s="13">
         <v>0</v>
       </c>
       <c r="U59" s="13">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V59" s="13">
         <v>0</v>
       </c>
       <c r="W59" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X59" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z59" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="13">
         <v>55050001</v>
       </c>
-      <c r="X59" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y59" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z59" s="13" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="13">
         <v>55060001</v>
       </c>
@@ -6640,16 +6817,16 @@
         <v>1</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I60" s="13">
         <v>0</v>
@@ -6676,37 +6853,40 @@
         <v>0</v>
       </c>
       <c r="Q60" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" s="13">
         <v>0</v>
       </c>
       <c r="S60" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T60" s="13">
         <v>0</v>
       </c>
       <c r="U60" s="13">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V60" s="13">
+        <v>0</v>
+      </c>
+      <c r="W60" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X60" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z60" s="13">
         <v>55060001</v>
       </c>
-      <c r="W60" s="13">
-        <v>0</v>
-      </c>
-      <c r="X60" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y60" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z60" s="13" t="s">
-        <v>55</v>
+      <c r="AA60" s="13">
+        <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="13">
         <v>55070001</v>
       </c>
@@ -6720,16 +6900,16 @@
         <v>1</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I61" s="13">
         <v>0</v>
@@ -6756,37 +6936,40 @@
         <v>0</v>
       </c>
       <c r="Q61" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" s="13">
         <v>0</v>
       </c>
       <c r="S61" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T61" s="13">
         <v>0</v>
       </c>
       <c r="U61" s="13">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V61" s="13">
+        <v>0</v>
+      </c>
+      <c r="W61" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X61" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z61" s="13">
         <v>55070001</v>
       </c>
-      <c r="W61" s="13">
-        <v>0</v>
-      </c>
-      <c r="X61" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y61" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z61" s="13" t="s">
-        <v>55</v>
+      <c r="AA61" s="13">
+        <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A62" s="14">
         <v>56010001</v>
       </c>
@@ -6800,16 +6983,16 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I62" s="14">
         <v>0</v>
@@ -6836,37 +7019,40 @@
         <v>0</v>
       </c>
       <c r="Q62" s="14">
+        <v>0</v>
+      </c>
+      <c r="R62" s="14">
+        <v>0</v>
+      </c>
+      <c r="S62" s="14">
+        <v>0</v>
+      </c>
+      <c r="T62" s="14">
+        <v>0</v>
+      </c>
+      <c r="U62" s="14">
         <v>2</v>
       </c>
-      <c r="R62" s="14">
-        <v>0</v>
-      </c>
-      <c r="S62" s="14">
-        <v>10000</v>
-      </c>
-      <c r="T62" s="14">
-        <v>0</v>
-      </c>
-      <c r="U62" s="14">
-        <v>10000</v>
-      </c>
       <c r="V62" s="14">
         <v>0</v>
       </c>
       <c r="W62" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X62" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="14">
         <v>56010001</v>
       </c>
-      <c r="X62" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y62" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z62" s="14" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A63" s="14">
         <v>56040001</v>
       </c>
@@ -6880,16 +7066,16 @@
         <v>1</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I63" s="14">
         <v>0</v>
@@ -6916,37 +7102,40 @@
         <v>0</v>
       </c>
       <c r="Q63" s="14">
+        <v>0</v>
+      </c>
+      <c r="R63" s="14">
+        <v>0</v>
+      </c>
+      <c r="S63" s="14">
+        <v>0</v>
+      </c>
+      <c r="T63" s="14">
+        <v>0</v>
+      </c>
+      <c r="U63" s="14">
         <v>2</v>
       </c>
-      <c r="R63" s="14">
-        <v>0</v>
-      </c>
-      <c r="S63" s="14">
-        <v>10000</v>
-      </c>
-      <c r="T63" s="14">
-        <v>0</v>
-      </c>
-      <c r="U63" s="14">
-        <v>10000</v>
-      </c>
       <c r="V63" s="14">
         <v>0</v>
       </c>
       <c r="W63" s="14">
-        <v>0</v>
-      </c>
-      <c r="X63" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y63" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z63" s="14" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X63" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="14">
+        <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A64" s="14">
         <v>56060001</v>
       </c>
@@ -6960,16 +7149,16 @@
         <v>1</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I64" s="14">
         <v>0</v>
@@ -6996,37 +7185,40 @@
         <v>0</v>
       </c>
       <c r="Q64" s="14">
+        <v>0</v>
+      </c>
+      <c r="R64" s="14">
+        <v>0</v>
+      </c>
+      <c r="S64" s="14">
+        <v>0</v>
+      </c>
+      <c r="T64" s="14">
+        <v>0</v>
+      </c>
+      <c r="U64" s="14">
         <v>2</v>
       </c>
-      <c r="R64" s="14">
-        <v>0</v>
-      </c>
-      <c r="S64" s="14">
-        <v>10000</v>
-      </c>
-      <c r="T64" s="14">
-        <v>0</v>
-      </c>
-      <c r="U64" s="14">
-        <v>10000</v>
-      </c>
       <c r="V64" s="14">
         <v>0</v>
       </c>
       <c r="W64" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X64" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="14">
         <v>56030001</v>
       </c>
-      <c r="X64" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y64" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z64" s="14" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A65" s="14">
         <v>56080001</v>
       </c>
@@ -7040,16 +7232,16 @@
         <v>1</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I65" s="14">
         <v>0</v>
@@ -7076,37 +7268,40 @@
         <v>0</v>
       </c>
       <c r="Q65" s="14">
+        <v>0</v>
+      </c>
+      <c r="R65" s="14">
+        <v>0</v>
+      </c>
+      <c r="S65" s="14">
+        <v>0</v>
+      </c>
+      <c r="T65" s="14">
+        <v>0</v>
+      </c>
+      <c r="U65" s="14">
         <v>2</v>
       </c>
-      <c r="R65" s="14">
-        <v>0</v>
-      </c>
-      <c r="S65" s="14">
-        <v>10000</v>
-      </c>
-      <c r="T65" s="14">
-        <v>0</v>
-      </c>
-      <c r="U65" s="14">
-        <v>10000</v>
-      </c>
       <c r="V65" s="14">
+        <v>0</v>
+      </c>
+      <c r="W65" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X65" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z65" s="14">
         <v>56040001</v>
       </c>
-      <c r="W65" s="14">
-        <v>0</v>
-      </c>
-      <c r="X65" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y65" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z65" s="14" t="s">
-        <v>55</v>
+      <c r="AA65" s="14">
+        <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A66" s="14">
         <v>56100001</v>
       </c>
@@ -7120,16 +7315,16 @@
         <v>1</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I66" s="14">
         <v>0</v>
@@ -7156,37 +7351,40 @@
         <v>0</v>
       </c>
       <c r="Q66" s="14">
+        <v>0</v>
+      </c>
+      <c r="R66" s="14">
+        <v>0</v>
+      </c>
+      <c r="S66" s="14">
+        <v>0</v>
+      </c>
+      <c r="T66" s="14">
+        <v>0</v>
+      </c>
+      <c r="U66" s="14">
         <v>2</v>
       </c>
-      <c r="R66" s="14">
-        <v>0</v>
-      </c>
-      <c r="S66" s="14">
-        <v>10000</v>
-      </c>
-      <c r="T66" s="14">
-        <v>0</v>
-      </c>
-      <c r="U66" s="14">
-        <v>10000</v>
-      </c>
       <c r="V66" s="14">
         <v>0</v>
       </c>
       <c r="W66" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X66" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="14">
         <v>56050001</v>
       </c>
-      <c r="X66" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y66" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z66" s="14" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A67" s="14">
         <v>56130001</v>
       </c>
@@ -7200,16 +7398,16 @@
         <v>1</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I67" s="14">
         <v>0</v>
@@ -7236,37 +7434,40 @@
         <v>0</v>
       </c>
       <c r="Q67" s="14">
+        <v>0</v>
+      </c>
+      <c r="R67" s="14">
+        <v>0</v>
+      </c>
+      <c r="S67" s="14">
+        <v>0</v>
+      </c>
+      <c r="T67" s="14">
+        <v>0</v>
+      </c>
+      <c r="U67" s="14">
         <v>2</v>
       </c>
-      <c r="R67" s="14">
-        <v>0</v>
-      </c>
-      <c r="S67" s="14">
-        <v>10000</v>
-      </c>
-      <c r="T67" s="14">
-        <v>0</v>
-      </c>
-      <c r="U67" s="14">
-        <v>10000</v>
-      </c>
       <c r="V67" s="14">
         <v>0</v>
       </c>
       <c r="W67" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X67" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="14">
         <v>56060001</v>
       </c>
-      <c r="X67" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y67" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z67" s="14" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A68" s="15">
         <v>57010001</v>
       </c>
@@ -7280,16 +7481,16 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I68" s="15">
         <v>0</v>
@@ -7316,37 +7517,40 @@
         <v>0</v>
       </c>
       <c r="Q68" s="15">
+        <v>0</v>
+      </c>
+      <c r="R68" s="15">
+        <v>0</v>
+      </c>
+      <c r="S68" s="15">
+        <v>0</v>
+      </c>
+      <c r="T68" s="15">
+        <v>0</v>
+      </c>
+      <c r="U68" s="15">
         <v>3</v>
       </c>
-      <c r="R68" s="15">
-        <v>0</v>
-      </c>
-      <c r="S68" s="15">
-        <v>10000</v>
-      </c>
-      <c r="T68" s="15">
-        <v>0</v>
-      </c>
-      <c r="U68" s="15">
-        <v>10000</v>
-      </c>
       <c r="V68" s="15">
         <v>0</v>
       </c>
       <c r="W68" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X68" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z68" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="15">
         <v>57010001</v>
       </c>
-      <c r="X68" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y68" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z68" s="15" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
         <v>57040001</v>
       </c>
@@ -7360,16 +7564,16 @@
         <v>1</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I69" s="15">
         <v>0</v>
@@ -7396,37 +7600,40 @@
         <v>0</v>
       </c>
       <c r="Q69" s="15">
+        <v>0</v>
+      </c>
+      <c r="R69" s="15">
+        <v>0</v>
+      </c>
+      <c r="S69" s="15">
+        <v>0</v>
+      </c>
+      <c r="T69" s="15">
+        <v>0</v>
+      </c>
+      <c r="U69" s="15">
         <v>3</v>
       </c>
-      <c r="R69" s="15">
-        <v>0</v>
-      </c>
-      <c r="S69" s="15">
-        <v>10000</v>
-      </c>
-      <c r="T69" s="15">
-        <v>0</v>
-      </c>
-      <c r="U69" s="15">
-        <v>10000</v>
-      </c>
       <c r="V69" s="15">
+        <v>0</v>
+      </c>
+      <c r="W69" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X69" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z69" s="15">
         <v>57020001</v>
       </c>
-      <c r="W69" s="15">
-        <v>0</v>
-      </c>
-      <c r="X69" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y69" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z69" s="15" t="s">
-        <v>55</v>
+      <c r="AA69" s="15">
+        <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A70" s="15">
         <v>57060001</v>
       </c>
@@ -7440,16 +7647,16 @@
         <v>1</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
@@ -7476,37 +7683,40 @@
         <v>0</v>
       </c>
       <c r="Q70" s="15">
+        <v>0</v>
+      </c>
+      <c r="R70" s="15">
+        <v>0</v>
+      </c>
+      <c r="S70" s="15">
+        <v>0</v>
+      </c>
+      <c r="T70" s="15">
+        <v>0</v>
+      </c>
+      <c r="U70" s="15">
         <v>3</v>
       </c>
-      <c r="R70" s="15">
-        <v>0</v>
-      </c>
-      <c r="S70" s="15">
-        <v>10000</v>
-      </c>
-      <c r="T70" s="15">
-        <v>0</v>
-      </c>
-      <c r="U70" s="15">
-        <v>10000</v>
-      </c>
       <c r="V70" s="15">
         <v>0</v>
       </c>
       <c r="W70" s="15">
-        <v>0</v>
-      </c>
-      <c r="X70" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y70" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z70" s="15" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X70" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z70" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="15">
+        <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A71" s="15">
         <v>57080001</v>
       </c>
@@ -7520,16 +7730,16 @@
         <v>1</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -7556,37 +7766,40 @@
         <v>0</v>
       </c>
       <c r="Q71" s="15">
+        <v>0</v>
+      </c>
+      <c r="R71" s="15">
+        <v>0</v>
+      </c>
+      <c r="S71" s="15">
+        <v>0</v>
+      </c>
+      <c r="T71" s="15">
+        <v>0</v>
+      </c>
+      <c r="U71" s="15">
         <v>3</v>
       </c>
-      <c r="R71" s="15">
-        <v>0</v>
-      </c>
-      <c r="S71" s="15">
-        <v>10000</v>
-      </c>
-      <c r="T71" s="15">
-        <v>0</v>
-      </c>
-      <c r="U71" s="15">
-        <v>10000</v>
-      </c>
       <c r="V71" s="15">
         <v>0</v>
       </c>
       <c r="W71" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X71" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z71" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="15">
         <v>57040001</v>
       </c>
-      <c r="X71" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y71" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z71" s="15" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A72" s="15">
         <v>57100001</v>
       </c>
@@ -7600,16 +7813,16 @@
         <v>1</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I72" s="15">
         <v>0</v>
@@ -7636,37 +7849,40 @@
         <v>0</v>
       </c>
       <c r="Q72" s="15">
+        <v>0</v>
+      </c>
+      <c r="R72" s="15">
+        <v>0</v>
+      </c>
+      <c r="S72" s="15">
+        <v>0</v>
+      </c>
+      <c r="T72" s="15">
+        <v>0</v>
+      </c>
+      <c r="U72" s="15">
         <v>3</v>
       </c>
-      <c r="R72" s="15">
-        <v>0</v>
-      </c>
-      <c r="S72" s="15">
-        <v>10000</v>
-      </c>
-      <c r="T72" s="15">
-        <v>0</v>
-      </c>
-      <c r="U72" s="15">
-        <v>10000</v>
-      </c>
       <c r="V72" s="15">
+        <v>0</v>
+      </c>
+      <c r="W72" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X72" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z72" s="15">
         <v>57050001</v>
       </c>
-      <c r="W72" s="15">
-        <v>0</v>
-      </c>
-      <c r="X72" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y72" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z72" s="15" t="s">
-        <v>55</v>
+      <c r="AA72" s="15">
+        <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A73" s="15">
         <v>57120001</v>
       </c>
@@ -7680,16 +7896,16 @@
         <v>1</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I73" s="15">
         <v>0</v>
@@ -7716,37 +7932,40 @@
         <v>0</v>
       </c>
       <c r="Q73" s="15">
+        <v>0</v>
+      </c>
+      <c r="R73" s="15">
+        <v>0</v>
+      </c>
+      <c r="S73" s="15">
+        <v>0</v>
+      </c>
+      <c r="T73" s="15">
+        <v>0</v>
+      </c>
+      <c r="U73" s="15">
         <v>3</v>
       </c>
-      <c r="R73" s="15">
-        <v>0</v>
-      </c>
-      <c r="S73" s="15">
-        <v>10000</v>
-      </c>
-      <c r="T73" s="15">
-        <v>0</v>
-      </c>
-      <c r="U73" s="15">
-        <v>10000</v>
-      </c>
       <c r="V73" s="15">
         <v>0</v>
       </c>
       <c r="W73" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X73" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z73" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="15">
         <v>57060001</v>
       </c>
-      <c r="X73" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y73" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z73" s="15" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A74" s="16">
         <v>58010001</v>
       </c>
@@ -7760,16 +7979,16 @@
         <v>1</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I74" s="16">
         <v>0</v>
@@ -7796,37 +8015,40 @@
         <v>0</v>
       </c>
       <c r="Q74" s="16">
+        <v>0</v>
+      </c>
+      <c r="R74" s="16">
+        <v>0</v>
+      </c>
+      <c r="S74" s="16">
+        <v>0</v>
+      </c>
+      <c r="T74" s="16">
+        <v>0</v>
+      </c>
+      <c r="U74" s="16">
         <v>4</v>
       </c>
-      <c r="R74" s="16">
-        <v>0</v>
-      </c>
-      <c r="S74" s="16">
-        <v>10000</v>
-      </c>
-      <c r="T74" s="16">
-        <v>0</v>
-      </c>
-      <c r="U74" s="16">
-        <v>10000</v>
-      </c>
       <c r="V74" s="16">
         <v>0</v>
       </c>
       <c r="W74" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X74" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z74" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="16">
         <v>58010001</v>
       </c>
-      <c r="X74" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y74" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z74" s="16" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A75" s="16">
         <v>58040001</v>
       </c>
@@ -7840,16 +8062,16 @@
         <v>1</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I75" s="16">
         <v>0</v>
@@ -7876,37 +8098,40 @@
         <v>0</v>
       </c>
       <c r="Q75" s="16">
+        <v>0</v>
+      </c>
+      <c r="R75" s="16">
+        <v>0</v>
+      </c>
+      <c r="S75" s="16">
+        <v>0</v>
+      </c>
+      <c r="T75" s="16">
+        <v>0</v>
+      </c>
+      <c r="U75" s="16">
         <v>4</v>
       </c>
-      <c r="R75" s="16">
-        <v>0</v>
-      </c>
-      <c r="S75" s="16">
-        <v>10000</v>
-      </c>
-      <c r="T75" s="16">
-        <v>0</v>
-      </c>
-      <c r="U75" s="16">
-        <v>10000</v>
-      </c>
       <c r="V75" s="16">
         <v>0</v>
       </c>
       <c r="W75" s="16">
-        <v>0</v>
-      </c>
-      <c r="X75" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y75" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z75" s="16" t="s">
-        <v>55</v>
+        <v>10000</v>
+      </c>
+      <c r="X75" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z75" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="16">
+        <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A76" s="16">
         <v>58060001</v>
       </c>
@@ -7920,16 +8145,16 @@
         <v>1</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I76" s="16">
         <v>0</v>
@@ -7956,37 +8181,40 @@
         <v>0</v>
       </c>
       <c r="Q76" s="16">
+        <v>0</v>
+      </c>
+      <c r="R76" s="16">
+        <v>0</v>
+      </c>
+      <c r="S76" s="16">
+        <v>0</v>
+      </c>
+      <c r="T76" s="16">
+        <v>0</v>
+      </c>
+      <c r="U76" s="16">
         <v>4</v>
       </c>
-      <c r="R76" s="16">
-        <v>0</v>
-      </c>
-      <c r="S76" s="16">
-        <v>10000</v>
-      </c>
-      <c r="T76" s="16">
-        <v>0</v>
-      </c>
-      <c r="U76" s="16">
-        <v>10000</v>
-      </c>
       <c r="V76" s="16">
+        <v>0</v>
+      </c>
+      <c r="W76" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X76" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z76" s="16">
         <v>58030001</v>
       </c>
-      <c r="W76" s="16">
-        <v>0</v>
-      </c>
-      <c r="X76" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y76" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z76" s="16" t="s">
-        <v>55</v>
+      <c r="AA76" s="16">
+        <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A77" s="16">
         <v>58080001</v>
       </c>
@@ -8000,16 +8228,16 @@
         <v>1</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I77" s="16">
         <v>0</v>
@@ -8036,37 +8264,40 @@
         <v>0</v>
       </c>
       <c r="Q77" s="16">
+        <v>0</v>
+      </c>
+      <c r="R77" s="16">
+        <v>0</v>
+      </c>
+      <c r="S77" s="16">
+        <v>0</v>
+      </c>
+      <c r="T77" s="16">
+        <v>0</v>
+      </c>
+      <c r="U77" s="16">
         <v>4</v>
       </c>
-      <c r="R77" s="16">
-        <v>0</v>
-      </c>
-      <c r="S77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="T77" s="16">
-        <v>0</v>
-      </c>
-      <c r="U77" s="16">
-        <v>10000</v>
-      </c>
       <c r="V77" s="16">
         <v>0</v>
       </c>
       <c r="W77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X77" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z77" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="16">
         <v>58040001</v>
       </c>
-      <c r="X77" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y77" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z77" s="16" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A78" s="16">
         <v>58110001</v>
       </c>
@@ -8080,16 +8311,16 @@
         <v>1</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I78" s="16">
         <v>0</v>
@@ -8116,37 +8347,40 @@
         <v>0</v>
       </c>
       <c r="Q78" s="16">
+        <v>0</v>
+      </c>
+      <c r="R78" s="16">
+        <v>0</v>
+      </c>
+      <c r="S78" s="16">
+        <v>0</v>
+      </c>
+      <c r="T78" s="16">
+        <v>0</v>
+      </c>
+      <c r="U78" s="16">
         <v>4</v>
       </c>
-      <c r="R78" s="16">
-        <v>0</v>
-      </c>
-      <c r="S78" s="16">
-        <v>10000</v>
-      </c>
-      <c r="T78" s="16">
-        <v>0</v>
-      </c>
-      <c r="U78" s="16">
-        <v>10000</v>
-      </c>
       <c r="V78" s="16">
         <v>0</v>
       </c>
       <c r="W78" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X78" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z78" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="16">
         <v>58050001</v>
       </c>
-      <c r="X78" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y78" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z78" s="16" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A79" s="24">
         <v>59010001</v>
       </c>
@@ -8160,16 +8394,16 @@
         <v>1</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I79" s="24">
         <v>0</v>
@@ -8202,31 +8436,34 @@
         <v>0</v>
       </c>
       <c r="S79" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T79" s="24">
         <v>0</v>
       </c>
       <c r="U79" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V79" s="24">
+        <v>0</v>
+      </c>
+      <c r="W79" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X79" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z79" s="24">
         <v>59010001</v>
       </c>
-      <c r="W79" s="24">
-        <v>0</v>
-      </c>
-      <c r="X79" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y79" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z79" s="24" t="s">
-        <v>55</v>
+      <c r="AA79" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A80" s="24">
         <v>59030001</v>
       </c>
@@ -8240,16 +8477,16 @@
         <v>1</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I80" s="24">
         <v>0</v>
@@ -8282,31 +8519,34 @@
         <v>0</v>
       </c>
       <c r="S80" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T80" s="24">
         <v>0</v>
       </c>
       <c r="U80" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V80" s="24">
+        <v>0</v>
+      </c>
+      <c r="W80" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X80" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z80" s="24">
         <v>59020001</v>
       </c>
-      <c r="W80" s="24">
-        <v>0</v>
-      </c>
-      <c r="X80" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y80" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z80" s="24" t="s">
-        <v>55</v>
+      <c r="AA80" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A81" s="24">
         <v>59050001</v>
       </c>
@@ -8320,16 +8560,16 @@
         <v>1</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I81" s="24">
         <v>0</v>
@@ -8362,31 +8602,34 @@
         <v>0</v>
       </c>
       <c r="S81" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T81" s="24">
         <v>0</v>
       </c>
       <c r="U81" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V81" s="24">
+        <v>0</v>
+      </c>
+      <c r="W81" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X81" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z81" s="24">
         <v>59030001</v>
       </c>
-      <c r="W81" s="24">
-        <v>0</v>
-      </c>
-      <c r="X81" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y81" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z81" s="24" t="s">
-        <v>55</v>
+      <c r="AA81" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A82" s="24">
         <v>59070001</v>
       </c>
@@ -8400,16 +8643,16 @@
         <v>1</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I82" s="24">
         <v>0</v>
@@ -8442,31 +8685,34 @@
         <v>0</v>
       </c>
       <c r="S82" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T82" s="24">
         <v>0</v>
       </c>
       <c r="U82" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V82" s="24">
+        <v>0</v>
+      </c>
+      <c r="W82" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X82" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z82" s="24">
         <v>59040001</v>
       </c>
-      <c r="W82" s="24">
-        <v>0</v>
-      </c>
-      <c r="X82" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y82" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z82" s="24" t="s">
-        <v>55</v>
+      <c r="AA82" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A83" s="24">
         <v>59090001</v>
       </c>
@@ -8480,16 +8726,16 @@
         <v>1</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I83" s="24">
         <v>0</v>
@@ -8522,31 +8768,34 @@
         <v>0</v>
       </c>
       <c r="S83" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T83" s="24">
         <v>0</v>
       </c>
       <c r="U83" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V83" s="24">
+        <v>0</v>
+      </c>
+      <c r="W83" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X83" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z83" s="24">
         <v>59050001</v>
       </c>
-      <c r="W83" s="24">
-        <v>0</v>
-      </c>
-      <c r="X83" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y83" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z83" s="24" t="s">
-        <v>55</v>
+      <c r="AA83" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A84" s="24">
         <v>59110001</v>
       </c>
@@ -8560,16 +8809,16 @@
         <v>1</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I84" s="24">
         <v>0</v>
@@ -8602,31 +8851,34 @@
         <v>0</v>
       </c>
       <c r="S84" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T84" s="24">
         <v>0</v>
       </c>
       <c r="U84" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V84" s="24">
+        <v>0</v>
+      </c>
+      <c r="W84" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X84" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z84" s="24">
         <v>59060001</v>
       </c>
-      <c r="W84" s="24">
-        <v>0</v>
-      </c>
-      <c r="X84" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y84" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z84" s="24" t="s">
-        <v>55</v>
+      <c r="AA84" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A85" s="24">
         <v>59130001</v>
       </c>
@@ -8640,16 +8892,16 @@
         <v>1</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I85" s="24">
         <v>0</v>
@@ -8682,31 +8934,34 @@
         <v>0</v>
       </c>
       <c r="S85" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T85" s="24">
         <v>0</v>
       </c>
       <c r="U85" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V85" s="24">
+        <v>0</v>
+      </c>
+      <c r="W85" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X85" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z85" s="24">
         <v>59070001</v>
       </c>
-      <c r="W85" s="24">
-        <v>0</v>
-      </c>
-      <c r="X85" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y85" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z85" s="24" t="s">
-        <v>55</v>
+      <c r="AA85" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A86" s="24">
         <v>59150001</v>
       </c>
@@ -8720,16 +8975,16 @@
         <v>1</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I86" s="24">
         <v>0</v>
@@ -8762,31 +9017,34 @@
         <v>0</v>
       </c>
       <c r="S86" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T86" s="24">
         <v>0</v>
       </c>
       <c r="U86" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V86" s="24">
+        <v>0</v>
+      </c>
+      <c r="W86" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X86" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z86" s="24">
         <v>59080001</v>
       </c>
-      <c r="W86" s="24">
-        <v>0</v>
-      </c>
-      <c r="X86" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y86" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z86" s="24" t="s">
-        <v>55</v>
+      <c r="AA86" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A87" s="24">
         <v>59180001</v>
       </c>
@@ -8800,16 +9058,16 @@
         <v>1</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I87" s="24">
         <v>0</v>
@@ -8842,31 +9100,34 @@
         <v>0</v>
       </c>
       <c r="S87" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T87" s="24">
         <v>0</v>
       </c>
       <c r="U87" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V87" s="24">
+        <v>0</v>
+      </c>
+      <c r="W87" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X87" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z87" s="24">
         <v>59090001</v>
       </c>
-      <c r="W87" s="24">
-        <v>0</v>
-      </c>
-      <c r="X87" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y87" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z87" s="24" t="s">
-        <v>55</v>
+      <c r="AA87" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A88" s="24">
         <v>59200001</v>
       </c>
@@ -8880,16 +9141,16 @@
         <v>1</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I88" s="24">
         <v>0</v>
@@ -8922,31 +9183,34 @@
         <v>0</v>
       </c>
       <c r="S88" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T88" s="24">
         <v>0</v>
       </c>
       <c r="U88" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V88" s="24">
+        <v>0</v>
+      </c>
+      <c r="W88" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X88" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z88" s="24">
         <v>59100001</v>
       </c>
-      <c r="W88" s="24">
-        <v>0</v>
-      </c>
-      <c r="X88" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y88" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z88" s="24" t="s">
-        <v>55</v>
+      <c r="AA88" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A89" s="24">
         <v>59220001</v>
       </c>
@@ -8960,16 +9224,16 @@
         <v>1</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I89" s="24">
         <v>0</v>
@@ -9002,31 +9266,34 @@
         <v>0</v>
       </c>
       <c r="S89" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T89" s="24">
         <v>0</v>
       </c>
       <c r="U89" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V89" s="24">
+        <v>0</v>
+      </c>
+      <c r="W89" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X89" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z89" s="24">
         <v>59110001</v>
       </c>
-      <c r="W89" s="24">
-        <v>0</v>
-      </c>
-      <c r="X89" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y89" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z89" s="24" t="s">
-        <v>55</v>
+      <c r="AA89" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A90" s="24">
         <v>59240001</v>
       </c>
@@ -9040,16 +9307,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I90" s="24">
         <v>0</v>
@@ -9082,31 +9349,34 @@
         <v>0</v>
       </c>
       <c r="S90" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T90" s="24">
         <v>0</v>
       </c>
       <c r="U90" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V90" s="24">
+        <v>0</v>
+      </c>
+      <c r="W90" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X90" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z90" s="24">
         <v>59120001</v>
       </c>
-      <c r="W90" s="24">
-        <v>0</v>
-      </c>
-      <c r="X90" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y90" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z90" s="24" t="s">
-        <v>55</v>
+      <c r="AA90" s="24">
+        <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A91" s="25">
         <v>60010001</v>
       </c>
@@ -9120,16 +9390,16 @@
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G91" s="25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I91" s="25">
         <v>0</v>
@@ -9162,31 +9432,34 @@
         <v>0</v>
       </c>
       <c r="S91" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T91" s="25">
         <v>0</v>
       </c>
       <c r="U91" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V91" s="25">
+        <v>0</v>
+      </c>
+      <c r="W91" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X91" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z91" s="25">
         <v>60010001</v>
       </c>
-      <c r="W91" s="25">
-        <v>0</v>
-      </c>
-      <c r="X91" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y91" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z91" s="25" t="s">
-        <v>57</v>
+      <c r="AA91" s="25">
+        <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A92" s="25">
         <v>60030001</v>
       </c>
@@ -9200,16 +9473,16 @@
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G92" s="25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I92" s="25">
         <v>0</v>
@@ -9242,31 +9515,34 @@
         <v>0</v>
       </c>
       <c r="S92" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T92" s="25">
         <v>0</v>
       </c>
       <c r="U92" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V92" s="25">
+        <v>0</v>
+      </c>
+      <c r="W92" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X92" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z92" s="25">
         <v>60020001</v>
       </c>
-      <c r="W92" s="25">
-        <v>0</v>
-      </c>
-      <c r="X92" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y92" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z92" s="25" t="s">
-        <v>57</v>
+      <c r="AA92" s="25">
+        <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
         <v>60060001</v>
       </c>
@@ -9280,16 +9556,16 @@
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G93" s="25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -9322,31 +9598,34 @@
         <v>0</v>
       </c>
       <c r="S93" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T93" s="25">
         <v>0</v>
       </c>
       <c r="U93" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V93" s="25">
+        <v>0</v>
+      </c>
+      <c r="W93" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X93" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z93" s="25">
         <v>60030001</v>
       </c>
-      <c r="W93" s="25">
-        <v>0</v>
-      </c>
-      <c r="X93" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y93" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z93" s="25" t="s">
-        <v>57</v>
+      <c r="AA93" s="25">
+        <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
         <v>60090001</v>
       </c>
@@ -9360,16 +9639,16 @@
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G94" s="25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I94" s="25">
         <v>0</v>
@@ -9402,31 +9681,34 @@
         <v>0</v>
       </c>
       <c r="S94" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T94" s="25">
         <v>0</v>
       </c>
       <c r="U94" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V94" s="25">
+        <v>0</v>
+      </c>
+      <c r="W94" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X94" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z94" s="25">
         <v>60040001</v>
       </c>
-      <c r="W94" s="25">
-        <v>0</v>
-      </c>
-      <c r="X94" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y94" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z94" s="25" t="s">
-        <v>57</v>
+      <c r="AA94" s="25">
+        <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A95" s="25">
         <v>60110001</v>
       </c>
@@ -9440,16 +9722,16 @@
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I95" s="25">
         <v>0</v>
@@ -9482,31 +9764,34 @@
         <v>0</v>
       </c>
       <c r="S95" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T95" s="25">
         <v>0</v>
       </c>
       <c r="U95" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V95" s="25">
+        <v>0</v>
+      </c>
+      <c r="W95" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X95" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z95" s="25">
         <v>60070001</v>
       </c>
-      <c r="W95" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="X95" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y95" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z95" s="25" t="s">
-        <v>57</v>
+      <c r="AA95" s="26" t="s">
+        <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A96" s="27">
         <v>61020001</v>
       </c>
@@ -9520,16 +9805,16 @@
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G96" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H96" s="27" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I96" s="27">
         <v>0</v>
@@ -9562,31 +9847,34 @@
         <v>0</v>
       </c>
       <c r="S96" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T96" s="27">
         <v>0</v>
       </c>
       <c r="U96" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V96" s="27">
+        <v>0</v>
+      </c>
+      <c r="W96" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X96" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z96" s="27">
         <v>61010001</v>
       </c>
-      <c r="W96" s="27">
-        <v>0</v>
-      </c>
-      <c r="X96" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y96" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z96" s="27" t="s">
-        <v>55</v>
+      <c r="AA96" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A97" s="27">
         <v>61040001</v>
       </c>
@@ -9600,16 +9888,16 @@
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G97" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H97" s="27" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I97" s="27">
         <v>0</v>
@@ -9642,31 +9930,34 @@
         <v>0</v>
       </c>
       <c r="S97" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T97" s="27">
         <v>0</v>
       </c>
       <c r="U97" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V97" s="27">
+        <v>0</v>
+      </c>
+      <c r="W97" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X97" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z97" s="27">
         <v>61020001</v>
       </c>
-      <c r="W97" s="27">
-        <v>0</v>
-      </c>
-      <c r="X97" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y97" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z97" s="27" t="s">
-        <v>55</v>
+      <c r="AA97" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
         <v>61060001</v>
       </c>
@@ -9680,16 +9971,16 @@
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G98" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -9722,31 +10013,34 @@
         <v>0</v>
       </c>
       <c r="S98" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T98" s="27">
         <v>0</v>
       </c>
       <c r="U98" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V98" s="27">
+        <v>0</v>
+      </c>
+      <c r="W98" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X98" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z98" s="27">
         <v>61030001</v>
       </c>
-      <c r="W98" s="27">
-        <v>0</v>
-      </c>
-      <c r="X98" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y98" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z98" s="27" t="s">
-        <v>55</v>
+      <c r="AA98" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
         <v>61080001</v>
       </c>
@@ -9760,16 +10054,16 @@
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G99" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -9802,31 +10096,34 @@
         <v>0</v>
       </c>
       <c r="S99" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T99" s="27">
         <v>0</v>
       </c>
       <c r="U99" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V99" s="27">
+        <v>0</v>
+      </c>
+      <c r="W99" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X99" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z99" s="27">
         <v>61040001</v>
       </c>
-      <c r="W99" s="27">
-        <v>0</v>
-      </c>
-      <c r="X99" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y99" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z99" s="27" t="s">
-        <v>55</v>
+      <c r="AA99" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
         <v>61100001</v>
       </c>
@@ -9840,16 +10137,16 @@
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G100" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -9882,31 +10179,34 @@
         <v>0</v>
       </c>
       <c r="S100" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T100" s="27">
         <v>0</v>
       </c>
       <c r="U100" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V100" s="27">
+        <v>0</v>
+      </c>
+      <c r="W100" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X100" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z100" s="27">
         <v>61050001</v>
       </c>
-      <c r="W100" s="27">
-        <v>0</v>
-      </c>
-      <c r="X100" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y100" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z100" s="27" t="s">
-        <v>55</v>
+      <c r="AA100" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
         <v>61120001</v>
       </c>
@@ -9920,16 +10220,16 @@
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G101" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -9962,31 +10262,34 @@
         <v>0</v>
       </c>
       <c r="S101" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T101" s="27">
         <v>0</v>
       </c>
       <c r="U101" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V101" s="27">
+        <v>0</v>
+      </c>
+      <c r="W101" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X101" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z101" s="27">
         <v>61060001</v>
       </c>
-      <c r="W101" s="27">
-        <v>0</v>
-      </c>
-      <c r="X101" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y101" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z101" s="27" t="s">
-        <v>55</v>
+      <c r="AA101" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
         <v>61140001</v>
       </c>
@@ -10000,16 +10303,16 @@
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G102" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10042,31 +10345,34 @@
         <v>0</v>
       </c>
       <c r="S102" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T102" s="27">
         <v>0</v>
       </c>
       <c r="U102" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V102" s="27">
+        <v>0</v>
+      </c>
+      <c r="W102" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X102" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z102" s="27">
         <v>61070001</v>
       </c>
-      <c r="W102" s="27">
-        <v>0</v>
-      </c>
-      <c r="X102" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y102" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z102" s="27" t="s">
-        <v>55</v>
+      <c r="AA102" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
         <v>61160001</v>
       </c>
@@ -10080,16 +10386,16 @@
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G103" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -10122,31 +10428,34 @@
         <v>0</v>
       </c>
       <c r="S103" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T103" s="27">
         <v>0</v>
       </c>
       <c r="U103" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V103" s="27">
+        <v>0</v>
+      </c>
+      <c r="W103" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X103" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z103" s="27">
         <v>61080001</v>
       </c>
-      <c r="W103" s="27">
-        <v>0</v>
-      </c>
-      <c r="X103" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y103" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z103" s="27" t="s">
-        <v>55</v>
+      <c r="AA103" s="27">
+        <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" s="27">
         <v>61180001</v>
       </c>
@@ -10160,16 +10469,16 @@
         <v>1</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G104" s="27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H104" s="27" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I104" s="27">
         <v>0</v>
@@ -10202,32 +10511,35 @@
         <v>0</v>
       </c>
       <c r="S104" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T104" s="27">
         <v>0</v>
       </c>
       <c r="U104" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V104" s="27">
+        <v>0</v>
+      </c>
+      <c r="W104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z104" s="27">
         <v>61090001</v>
       </c>
-      <c r="W104" s="27">
-        <v>0</v>
-      </c>
-      <c r="X104" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y104" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z104" s="27" t="s">
-        <v>55</v>
+      <c r="AA104" s="27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:X104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AA104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B942E6D-D462-4F5B-A59A-6B86D1DB3208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28465B04-19DD-41AD-875D-2B6DFCA8A82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2327,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="34">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="34">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="T7" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="34">
         <v>0</v>
@@ -2570,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="34">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="34">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="34">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" s="23">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" s="3">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>9</v>
       </c>
       <c r="T32" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" s="17">
         <v>2</v>
@@ -4637,7 +4637,7 @@
         <v>9</v>
       </c>
       <c r="T33" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" s="17">
         <v>2</v>
@@ -4718,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" s="19">
         <v>4</v>
@@ -4799,7 +4799,7 @@
         <v>9</v>
       </c>
       <c r="T35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" s="19">
         <v>4</v>
@@ -4880,7 +4880,7 @@
         <v>9</v>
       </c>
       <c r="T36" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" s="20">
         <v>3</v>
@@ -4961,7 +4961,7 @@
         <v>9</v>
       </c>
       <c r="T37" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" s="20">
         <v>3</v>
@@ -5042,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="T38" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" s="32" t="s">
         <v>291</v>
@@ -5123,7 +5123,7 @@
         <v>9</v>
       </c>
       <c r="T39" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="30">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>9</v>
       </c>
       <c r="T40" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" s="30">
         <v>0</v>
@@ -5285,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="T41" s="31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" s="31">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28465B04-19DD-41AD-875D-2B6DFCA8A82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9E04A4-209C-4931-A5C5-F020B6F92D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="296">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1174,10 +1174,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>光环技能-自身效果：光环范围提高-范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>获取护盾提高</t>
   </si>
   <si>
@@ -1302,6 +1298,26 @@
   </si>
   <si>
     <t>1,2,3,4,0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-自身效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-敌人效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-自身效果：光环范围提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-敌人效果：范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>正义光环</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1988,7 +2004,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA104"/>
+  <dimension ref="A1:AA106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2083,7 +2099,7 @@
         <v>65</v>
       </c>
       <c r="U2" s="33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>65</v>
@@ -2166,7 +2182,7 @@
         <v>14</v>
       </c>
       <c r="U3" s="33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V3" s="5" t="s">
         <v>34</v>
@@ -2249,7 +2265,7 @@
         <v>28</v>
       </c>
       <c r="U4" s="33" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="V4" s="5" t="s">
         <v>35</v>
@@ -4172,7 +4188,7 @@
         <v>25010001</v>
       </c>
       <c r="B28" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" s="23">
         <v>2501</v>
@@ -4181,16 +4197,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>285</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>286</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I28" s="23">
         <v>0</v>
@@ -5045,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="U38" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V38" s="28">
         <v>150</v>
@@ -6328,7 +6344,7 @@
         <v>32</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I54" s="23">
         <v>0</v>
@@ -6405,7 +6421,7 @@
         <v>70</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>32</v>
@@ -6488,7 +6504,7 @@
         <v>110</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>32</v>
@@ -6571,7 +6587,7 @@
         <v>112</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>32</v>
@@ -6654,7 +6670,7 @@
         <v>74</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>32</v>
@@ -6737,7 +6753,7 @@
         <v>75</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>32</v>
@@ -6820,7 +6836,7 @@
         <v>115</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>32</v>
@@ -6903,7 +6919,7 @@
         <v>116</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>32</v>
@@ -7318,13 +7334,13 @@
         <v>129</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G66" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I66" s="14">
         <v>0</v>
@@ -7401,13 +7417,13 @@
         <v>129</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G67" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I67" s="14">
         <v>0</v>
@@ -7733,13 +7749,13 @@
         <v>135</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>32</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -7816,7 +7832,7 @@
         <v>136</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G72" s="15" t="s">
         <v>32</v>
@@ -7899,7 +7915,7 @@
         <v>137</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G73" s="15" t="s">
         <v>32</v>
@@ -8314,7 +8330,7 @@
         <v>144</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>32</v>
@@ -9307,16 +9323,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G90" s="24" t="s">
         <v>32</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I90" s="24">
         <v>0</v>
@@ -9713,7 +9729,7 @@
         <v>60110001</v>
       </c>
       <c r="B95" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C95" s="25">
         <v>6011</v>
@@ -9722,16 +9738,16 @@
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F95" s="25" t="s">
         <v>192</v>
-      </c>
-      <c r="F95" s="25" t="s">
-        <v>257</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="I95" s="25">
         <v>0</v>
@@ -9785,202 +9801,202 @@
         <v>10000</v>
       </c>
       <c r="Z95" s="25">
-        <v>60070001</v>
-      </c>
-      <c r="AA95" s="26" t="s">
-        <v>193</v>
+        <v>60080001</v>
+      </c>
+      <c r="AA95" s="26">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A96" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="B96" s="27">
+      <c r="A96" s="25">
+        <v>60120001</v>
+      </c>
+      <c r="B96" s="25">
+        <v>5</v>
+      </c>
+      <c r="C96" s="25">
+        <v>6012</v>
+      </c>
+      <c r="D96" s="25">
+        <v>1</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="G96" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H96" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I96" s="25">
+        <v>0</v>
+      </c>
+      <c r="J96" s="25">
+        <v>0</v>
+      </c>
+      <c r="K96" s="25">
+        <v>0</v>
+      </c>
+      <c r="L96" s="25">
+        <v>0</v>
+      </c>
+      <c r="M96" s="25">
+        <v>0</v>
+      </c>
+      <c r="N96" s="25">
+        <v>0</v>
+      </c>
+      <c r="O96" s="25">
+        <v>0</v>
+      </c>
+      <c r="P96" s="25">
         <v>4</v>
       </c>
-      <c r="C96" s="27">
-        <v>6102</v>
-      </c>
-      <c r="D96" s="27">
-        <v>1</v>
-      </c>
-      <c r="E96" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="F96" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="G96" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H96" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I96" s="27">
-        <v>0</v>
-      </c>
-      <c r="J96" s="27">
-        <v>0</v>
-      </c>
-      <c r="K96" s="27">
-        <v>0</v>
-      </c>
-      <c r="L96" s="27">
-        <v>0</v>
-      </c>
-      <c r="M96" s="27">
-        <v>0</v>
-      </c>
-      <c r="N96" s="27">
-        <v>0</v>
-      </c>
-      <c r="O96" s="27">
-        <v>0</v>
-      </c>
-      <c r="P96" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="27">
-        <v>0</v>
-      </c>
-      <c r="R96" s="27">
-        <v>0</v>
-      </c>
-      <c r="S96" s="27">
-        <v>0</v>
-      </c>
-      <c r="T96" s="27">
-        <v>0</v>
-      </c>
-      <c r="U96" s="27">
-        <v>0</v>
-      </c>
-      <c r="V96" s="27">
-        <v>0</v>
-      </c>
-      <c r="W96" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X96" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z96" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="AA96" s="27">
+      <c r="Q96" s="25">
+        <v>1</v>
+      </c>
+      <c r="R96" s="25">
+        <v>10000</v>
+      </c>
+      <c r="S96" s="25">
+        <v>0</v>
+      </c>
+      <c r="T96" s="25">
+        <v>0</v>
+      </c>
+      <c r="U96" s="25">
+        <v>0</v>
+      </c>
+      <c r="V96" s="25">
+        <v>0</v>
+      </c>
+      <c r="W96" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X96" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z96" s="25">
+        <v>60070001</v>
+      </c>
+      <c r="AA96" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A97" s="27">
-        <v>61040001</v>
-      </c>
-      <c r="B97" s="27">
+      <c r="A97" s="25">
+        <v>60130001</v>
+      </c>
+      <c r="B97" s="25">
+        <v>5</v>
+      </c>
+      <c r="C97" s="25">
+        <v>6013</v>
+      </c>
+      <c r="D97" s="25">
+        <v>1</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="G97" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H97" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I97" s="25">
+        <v>0</v>
+      </c>
+      <c r="J97" s="25">
+        <v>0</v>
+      </c>
+      <c r="K97" s="25">
+        <v>0</v>
+      </c>
+      <c r="L97" s="25">
+        <v>0</v>
+      </c>
+      <c r="M97" s="25">
+        <v>0</v>
+      </c>
+      <c r="N97" s="25">
+        <v>0</v>
+      </c>
+      <c r="O97" s="25">
+        <v>0</v>
+      </c>
+      <c r="P97" s="25">
         <v>4</v>
       </c>
-      <c r="C97" s="27">
-        <v>6104</v>
-      </c>
-      <c r="D97" s="27">
-        <v>1</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="F97" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="G97" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H97" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="I97" s="27">
-        <v>0</v>
-      </c>
-      <c r="J97" s="27">
-        <v>0</v>
-      </c>
-      <c r="K97" s="27">
-        <v>0</v>
-      </c>
-      <c r="L97" s="27">
-        <v>0</v>
-      </c>
-      <c r="M97" s="27">
-        <v>0</v>
-      </c>
-      <c r="N97" s="27">
-        <v>0</v>
-      </c>
-      <c r="O97" s="27">
-        <v>0</v>
-      </c>
-      <c r="P97" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="27">
-        <v>0</v>
-      </c>
-      <c r="R97" s="27">
-        <v>0</v>
-      </c>
-      <c r="S97" s="27">
-        <v>0</v>
-      </c>
-      <c r="T97" s="27">
-        <v>0</v>
-      </c>
-      <c r="U97" s="27">
-        <v>0</v>
-      </c>
-      <c r="V97" s="27">
-        <v>0</v>
-      </c>
-      <c r="W97" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X97" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y97" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z97" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="AA97" s="27">
-        <v>0</v>
+      <c r="Q97" s="25">
+        <v>2</v>
+      </c>
+      <c r="R97" s="25">
+        <v>10000</v>
+      </c>
+      <c r="S97" s="25">
+        <v>0</v>
+      </c>
+      <c r="T97" s="25">
+        <v>0</v>
+      </c>
+      <c r="U97" s="25">
+        <v>0</v>
+      </c>
+      <c r="V97" s="25">
+        <v>0</v>
+      </c>
+      <c r="W97" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X97" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z97" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="26" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
-        <v>61060001</v>
+        <v>61020001</v>
       </c>
       <c r="B98" s="27">
         <v>4</v>
       </c>
       <c r="C98" s="27">
-        <v>6106</v>
+        <v>6102</v>
       </c>
       <c r="D98" s="27">
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>259</v>
+        <v>195</v>
       </c>
       <c r="G98" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -10034,7 +10050,7 @@
         <v>10000</v>
       </c>
       <c r="Z98" s="27">
-        <v>61030001</v>
+        <v>61010001</v>
       </c>
       <c r="AA98" s="27">
         <v>0</v>
@@ -10042,28 +10058,28 @@
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
-        <v>61080001</v>
+        <v>61040001</v>
       </c>
       <c r="B99" s="27">
         <v>4</v>
       </c>
       <c r="C99" s="27">
-        <v>6108</v>
+        <v>6104</v>
       </c>
       <c r="D99" s="27">
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="G99" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -10117,7 +10133,7 @@
         <v>10000</v>
       </c>
       <c r="Z99" s="27">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="AA99" s="27">
         <v>0</v>
@@ -10125,28 +10141,28 @@
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
-        <v>61100001</v>
+        <v>61060001</v>
       </c>
       <c r="B100" s="27">
         <v>4</v>
       </c>
       <c r="C100" s="27">
-        <v>6110</v>
+        <v>6106</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="G100" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -10200,7 +10216,7 @@
         <v>10000</v>
       </c>
       <c r="Z100" s="27">
-        <v>61050001</v>
+        <v>61030001</v>
       </c>
       <c r="AA100" s="27">
         <v>0</v>
@@ -10208,28 +10224,28 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
-        <v>61120001</v>
+        <v>61080001</v>
       </c>
       <c r="B101" s="27">
         <v>4</v>
       </c>
       <c r="C101" s="27">
-        <v>6112</v>
+        <v>6108</v>
       </c>
       <c r="D101" s="27">
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="G101" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -10283,7 +10299,7 @@
         <v>10000</v>
       </c>
       <c r="Z101" s="27">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="AA101" s="27">
         <v>0</v>
@@ -10291,28 +10307,28 @@
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
-        <v>61140001</v>
+        <v>61100001</v>
       </c>
       <c r="B102" s="27">
         <v>4</v>
       </c>
       <c r="C102" s="27">
-        <v>6114</v>
+        <v>6110</v>
       </c>
       <c r="D102" s="27">
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="G102" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10366,7 +10382,7 @@
         <v>10000</v>
       </c>
       <c r="Z102" s="27">
-        <v>61070001</v>
+        <v>61050001</v>
       </c>
       <c r="AA102" s="27">
         <v>0</v>
@@ -10374,28 +10390,28 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
-        <v>61160001</v>
+        <v>61120001</v>
       </c>
       <c r="B103" s="27">
         <v>4</v>
       </c>
       <c r="C103" s="27">
-        <v>6116</v>
+        <v>6112</v>
       </c>
       <c r="D103" s="27">
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G103" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -10449,7 +10465,7 @@
         <v>10000</v>
       </c>
       <c r="Z103" s="27">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="AA103" s="27">
         <v>0</v>
@@ -10457,89 +10473,255 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" s="27">
-        <v>61180001</v>
+        <v>61140001</v>
       </c>
       <c r="B104" s="27">
         <v>4</v>
       </c>
       <c r="C104" s="27">
-        <v>6118</v>
+        <v>6114</v>
       </c>
       <c r="D104" s="27">
         <v>1</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G104" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H104" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="I104" s="27">
+        <v>0</v>
+      </c>
+      <c r="J104" s="27">
+        <v>0</v>
+      </c>
+      <c r="K104" s="27">
+        <v>0</v>
+      </c>
+      <c r="L104" s="27">
+        <v>0</v>
+      </c>
+      <c r="M104" s="27">
+        <v>0</v>
+      </c>
+      <c r="N104" s="27">
+        <v>0</v>
+      </c>
+      <c r="O104" s="27">
+        <v>0</v>
+      </c>
+      <c r="P104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="27">
+        <v>0</v>
+      </c>
+      <c r="R104" s="27">
+        <v>0</v>
+      </c>
+      <c r="S104" s="27">
+        <v>0</v>
+      </c>
+      <c r="T104" s="27">
+        <v>0</v>
+      </c>
+      <c r="U104" s="27">
+        <v>0</v>
+      </c>
+      <c r="V104" s="27">
+        <v>0</v>
+      </c>
+      <c r="W104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z104" s="27">
+        <v>61070001</v>
+      </c>
+      <c r="AA104" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A105" s="27">
+        <v>61160001</v>
+      </c>
+      <c r="B105" s="27">
+        <v>4</v>
+      </c>
+      <c r="C105" s="27">
+        <v>6116</v>
+      </c>
+      <c r="D105" s="27">
+        <v>1</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F105" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="G105" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H105" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="I105" s="27">
+        <v>0</v>
+      </c>
+      <c r="J105" s="27">
+        <v>0</v>
+      </c>
+      <c r="K105" s="27">
+        <v>0</v>
+      </c>
+      <c r="L105" s="27">
+        <v>0</v>
+      </c>
+      <c r="M105" s="27">
+        <v>0</v>
+      </c>
+      <c r="N105" s="27">
+        <v>0</v>
+      </c>
+      <c r="O105" s="27">
+        <v>0</v>
+      </c>
+      <c r="P105" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="27">
+        <v>0</v>
+      </c>
+      <c r="R105" s="27">
+        <v>0</v>
+      </c>
+      <c r="S105" s="27">
+        <v>0</v>
+      </c>
+      <c r="T105" s="27">
+        <v>0</v>
+      </c>
+      <c r="U105" s="27">
+        <v>0</v>
+      </c>
+      <c r="V105" s="27">
+        <v>0</v>
+      </c>
+      <c r="W105" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X105" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z105" s="27">
+        <v>61080001</v>
+      </c>
+      <c r="AA105" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A106" s="27">
+        <v>61180001</v>
+      </c>
+      <c r="B106" s="27">
+        <v>4</v>
+      </c>
+      <c r="C106" s="27">
+        <v>6118</v>
+      </c>
+      <c r="D106" s="27">
+        <v>1</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F106" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="I104" s="27">
-        <v>0</v>
-      </c>
-      <c r="J104" s="27">
-        <v>0</v>
-      </c>
-      <c r="K104" s="27">
-        <v>0</v>
-      </c>
-      <c r="L104" s="27">
-        <v>0</v>
-      </c>
-      <c r="M104" s="27">
-        <v>0</v>
-      </c>
-      <c r="N104" s="27">
-        <v>0</v>
-      </c>
-      <c r="O104" s="27">
-        <v>0</v>
-      </c>
-      <c r="P104" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="27">
-        <v>0</v>
-      </c>
-      <c r="R104" s="27">
-        <v>0</v>
-      </c>
-      <c r="S104" s="27">
-        <v>0</v>
-      </c>
-      <c r="T104" s="27">
-        <v>0</v>
-      </c>
-      <c r="U104" s="27">
-        <v>0</v>
-      </c>
-      <c r="V104" s="27">
-        <v>0</v>
-      </c>
-      <c r="W104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X104" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z104" s="27">
+      <c r="G106" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="I106" s="27">
+        <v>0</v>
+      </c>
+      <c r="J106" s="27">
+        <v>0</v>
+      </c>
+      <c r="K106" s="27">
+        <v>0</v>
+      </c>
+      <c r="L106" s="27">
+        <v>0</v>
+      </c>
+      <c r="M106" s="27">
+        <v>0</v>
+      </c>
+      <c r="N106" s="27">
+        <v>0</v>
+      </c>
+      <c r="O106" s="27">
+        <v>0</v>
+      </c>
+      <c r="P106" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="27">
+        <v>0</v>
+      </c>
+      <c r="R106" s="27">
+        <v>0</v>
+      </c>
+      <c r="S106" s="27">
+        <v>0</v>
+      </c>
+      <c r="T106" s="27">
+        <v>0</v>
+      </c>
+      <c r="U106" s="27">
+        <v>0</v>
+      </c>
+      <c r="V106" s="27">
+        <v>0</v>
+      </c>
+      <c r="W106" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X106" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z106" s="27">
         <v>61090001</v>
       </c>
-      <c r="AA104" s="27">
+      <c r="AA106" s="27">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AA106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9E04A4-209C-4931-A5C5-F020B6F92D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DE34AF-DEAE-4EDE-93F1-8384081D8D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DE34AF-DEAE-4EDE-93F1-8384081D8D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FB6CC5-EBDB-44D8-A101-6EE506E72E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="298">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1318,6 +1318,14 @@
   </si>
   <si>
     <t>正义光环</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能-每X秒获得最大生命值的护盾</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能-自身效果</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2004,7 +2012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA106"/>
+  <dimension ref="A1:AA108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -10720,6 +10728,169 @@
         <v>0</v>
       </c>
     </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A107" s="5">
+        <v>955001001</v>
+      </c>
+      <c r="B107" s="5">
+        <v>4</v>
+      </c>
+      <c r="C107" s="5">
+        <v>7001</v>
+      </c>
+      <c r="D107" s="5">
+        <v>1</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="G107" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" s="27">
+        <v>0</v>
+      </c>
+      <c r="I107" s="27">
+        <v>0</v>
+      </c>
+      <c r="J107" s="27">
+        <v>0</v>
+      </c>
+      <c r="K107" s="27">
+        <v>0</v>
+      </c>
+      <c r="L107" s="27">
+        <v>0</v>
+      </c>
+      <c r="M107" s="27">
+        <v>0</v>
+      </c>
+      <c r="N107" s="27">
+        <v>0</v>
+      </c>
+      <c r="O107" s="27">
+        <v>0</v>
+      </c>
+      <c r="P107" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="27">
+        <v>0</v>
+      </c>
+      <c r="R107" s="27">
+        <v>0</v>
+      </c>
+      <c r="S107" s="27">
+        <v>0</v>
+      </c>
+      <c r="T107" s="27">
+        <v>0</v>
+      </c>
+      <c r="U107" s="27">
+        <v>0</v>
+      </c>
+      <c r="V107" s="27">
+        <v>0</v>
+      </c>
+      <c r="W107" s="27">
+        <v>0</v>
+      </c>
+      <c r="X107" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="27">
+        <v>855001001</v>
+      </c>
+      <c r="AA107" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A108" s="5">
+        <v>955001002</v>
+      </c>
+      <c r="B108" s="5">
+        <v>5</v>
+      </c>
+      <c r="C108" s="5">
+        <v>7002</v>
+      </c>
+      <c r="D108" s="5">
+        <v>1</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G108" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="H108" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="I108" s="27">
+        <v>0</v>
+      </c>
+      <c r="J108" s="27">
+        <v>0</v>
+      </c>
+      <c r="K108" s="27">
+        <v>0</v>
+      </c>
+      <c r="L108" s="27">
+        <v>0</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0</v>
+      </c>
+      <c r="N108" s="27">
+        <v>0</v>
+      </c>
+      <c r="O108" s="27">
+        <v>0</v>
+      </c>
+      <c r="P108" s="27">
+        <v>4</v>
+      </c>
+      <c r="Q108" s="27">
+        <v>1</v>
+      </c>
+      <c r="R108" s="27">
+        <v>0</v>
+      </c>
+      <c r="S108" s="27">
+        <v>0</v>
+      </c>
+      <c r="T108" s="27">
+        <v>0</v>
+      </c>
+      <c r="U108" s="27">
+        <v>0</v>
+      </c>
+      <c r="V108" s="27">
+        <v>0</v>
+      </c>
+      <c r="W108" s="27">
+        <v>0</v>
+      </c>
+      <c r="X108" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="27">
+        <v>855001002</v>
+      </c>
+      <c r="AA108" s="27">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:AA106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FB6CC5-EBDB-44D8-A101-6EE506E72E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08237993-AD29-4BEC-9073-FFEE3E23B95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="390" windowWidth="21600" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="307">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1326,6 +1326,42 @@
   </si>
   <si>
     <t>护盾技能-自身效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放4道雷击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）雷击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）冰弹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放冰弹攻击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）陨石</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放陨石攻击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1502,7 +1538,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1578,6 +1614,12 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1635,7 +1677,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1712,6 +1754,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2012,7 +2059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA108"/>
+  <dimension ref="A1:AA114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2030,7 +2077,7 @@
     <col min="18" max="18" width="12.5" style="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.5" style="5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="60" style="5" customWidth="1"/>
+    <col min="21" max="21" width="58" style="5" customWidth="1"/>
     <col min="22" max="22" width="19.25" style="5" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17.5" style="5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="20.875" style="5" bestFit="1" customWidth="1"/>
@@ -10891,6 +10938,504 @@
         <v>0</v>
       </c>
     </row>
+    <row r="109" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="36">
+        <v>955001003</v>
+      </c>
+      <c r="B109" s="36">
+        <v>4</v>
+      </c>
+      <c r="C109" s="36">
+        <v>7003</v>
+      </c>
+      <c r="D109" s="36">
+        <v>1</v>
+      </c>
+      <c r="E109" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="F109" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="G109" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H109" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="I109" s="36">
+        <v>0</v>
+      </c>
+      <c r="J109" s="36">
+        <v>0</v>
+      </c>
+      <c r="K109" s="36">
+        <v>0</v>
+      </c>
+      <c r="L109" s="36">
+        <v>0</v>
+      </c>
+      <c r="M109" s="36">
+        <v>0</v>
+      </c>
+      <c r="N109" s="36">
+        <v>0</v>
+      </c>
+      <c r="O109" s="36">
+        <v>0</v>
+      </c>
+      <c r="P109" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="36">
+        <v>0</v>
+      </c>
+      <c r="R109" s="36">
+        <v>0</v>
+      </c>
+      <c r="S109" s="36">
+        <v>0</v>
+      </c>
+      <c r="T109" s="36">
+        <v>0</v>
+      </c>
+      <c r="U109" s="36">
+        <v>0</v>
+      </c>
+      <c r="V109" s="36">
+        <v>0</v>
+      </c>
+      <c r="W109" s="36">
+        <v>0</v>
+      </c>
+      <c r="X109" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="36">
+        <v>855001003</v>
+      </c>
+      <c r="AA109" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="36">
+        <v>955001004</v>
+      </c>
+      <c r="B110" s="36">
+        <v>5</v>
+      </c>
+      <c r="C110" s="36">
+        <v>7004</v>
+      </c>
+      <c r="D110" s="36">
+        <v>1</v>
+      </c>
+      <c r="E110" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="F110" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="G110" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H110" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="I110" s="36">
+        <v>0</v>
+      </c>
+      <c r="J110" s="36">
+        <v>0</v>
+      </c>
+      <c r="K110" s="36">
+        <v>0</v>
+      </c>
+      <c r="L110" s="36">
+        <v>0</v>
+      </c>
+      <c r="M110" s="36">
+        <v>0</v>
+      </c>
+      <c r="N110" s="36">
+        <v>0</v>
+      </c>
+      <c r="O110" s="36">
+        <v>0</v>
+      </c>
+      <c r="P110" s="36">
+        <v>4</v>
+      </c>
+      <c r="Q110" s="36">
+        <v>2</v>
+      </c>
+      <c r="R110" s="36">
+        <v>4000</v>
+      </c>
+      <c r="S110" s="36">
+        <v>4</v>
+      </c>
+      <c r="T110" s="36">
+        <v>1</v>
+      </c>
+      <c r="U110" s="36">
+        <v>4</v>
+      </c>
+      <c r="V110" s="36">
+        <v>0</v>
+      </c>
+      <c r="W110" s="36">
+        <v>15000</v>
+      </c>
+      <c r="X110" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="36">
+        <v>15000</v>
+      </c>
+      <c r="Z110" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A111" s="36">
+        <v>955001005</v>
+      </c>
+      <c r="B111" s="36">
+        <v>4</v>
+      </c>
+      <c r="C111" s="36">
+        <v>7005</v>
+      </c>
+      <c r="D111" s="36">
+        <v>1</v>
+      </c>
+      <c r="E111" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="F111" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="G111" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H111" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="I111" s="36">
+        <v>0</v>
+      </c>
+      <c r="J111" s="36">
+        <v>0</v>
+      </c>
+      <c r="K111" s="36">
+        <v>0</v>
+      </c>
+      <c r="L111" s="36">
+        <v>0</v>
+      </c>
+      <c r="M111" s="36">
+        <v>0</v>
+      </c>
+      <c r="N111" s="36">
+        <v>0</v>
+      </c>
+      <c r="O111" s="36">
+        <v>0</v>
+      </c>
+      <c r="P111" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="36">
+        <v>0</v>
+      </c>
+      <c r="R111" s="36">
+        <v>0</v>
+      </c>
+      <c r="S111" s="36">
+        <v>0</v>
+      </c>
+      <c r="T111" s="36">
+        <v>0</v>
+      </c>
+      <c r="U111" s="36">
+        <v>0</v>
+      </c>
+      <c r="V111" s="36">
+        <v>0</v>
+      </c>
+      <c r="W111" s="36">
+        <v>0</v>
+      </c>
+      <c r="X111" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="36">
+        <v>855001004</v>
+      </c>
+      <c r="AA111" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="36">
+        <v>955001006</v>
+      </c>
+      <c r="B112" s="36">
+        <v>5</v>
+      </c>
+      <c r="C112" s="36">
+        <v>7006</v>
+      </c>
+      <c r="D112" s="36">
+        <v>1</v>
+      </c>
+      <c r="E112" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="F112" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="G112" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H112" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="I112" s="36">
+        <v>0</v>
+      </c>
+      <c r="J112" s="36">
+        <v>0</v>
+      </c>
+      <c r="K112" s="36">
+        <v>0</v>
+      </c>
+      <c r="L112" s="36">
+        <v>0</v>
+      </c>
+      <c r="M112" s="36">
+        <v>1000</v>
+      </c>
+      <c r="N112" s="36">
+        <v>0</v>
+      </c>
+      <c r="O112" s="36">
+        <v>0</v>
+      </c>
+      <c r="P112" s="36">
+        <v>4</v>
+      </c>
+      <c r="Q112" s="36">
+        <v>2</v>
+      </c>
+      <c r="R112" s="36">
+        <v>0</v>
+      </c>
+      <c r="S112" s="36">
+        <v>0</v>
+      </c>
+      <c r="T112" s="36">
+        <v>0</v>
+      </c>
+      <c r="U112" s="36">
+        <v>1</v>
+      </c>
+      <c r="V112" s="36">
+        <v>0</v>
+      </c>
+      <c r="W112" s="36">
+        <v>15000</v>
+      </c>
+      <c r="X112" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="36">
+        <v>15000</v>
+      </c>
+      <c r="Z112" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="36">
+        <v>955001007</v>
+      </c>
+      <c r="B113" s="36">
+        <v>4</v>
+      </c>
+      <c r="C113" s="36">
+        <v>7007</v>
+      </c>
+      <c r="D113" s="36">
+        <v>1</v>
+      </c>
+      <c r="E113" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="F113" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="G113" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H113" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="I113" s="36">
+        <v>0</v>
+      </c>
+      <c r="J113" s="36">
+        <v>0</v>
+      </c>
+      <c r="K113" s="36">
+        <v>0</v>
+      </c>
+      <c r="L113" s="36">
+        <v>0</v>
+      </c>
+      <c r="M113" s="36">
+        <v>0</v>
+      </c>
+      <c r="N113" s="36">
+        <v>0</v>
+      </c>
+      <c r="O113" s="36">
+        <v>0</v>
+      </c>
+      <c r="P113" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="36">
+        <v>0</v>
+      </c>
+      <c r="R113" s="36">
+        <v>0</v>
+      </c>
+      <c r="S113" s="36">
+        <v>0</v>
+      </c>
+      <c r="T113" s="36">
+        <v>0</v>
+      </c>
+      <c r="U113" s="36">
+        <v>0</v>
+      </c>
+      <c r="V113" s="36">
+        <v>0</v>
+      </c>
+      <c r="W113" s="36">
+        <v>0</v>
+      </c>
+      <c r="X113" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="36">
+        <v>855001005</v>
+      </c>
+      <c r="AA113" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="36">
+        <v>955001008</v>
+      </c>
+      <c r="B114" s="36">
+        <v>5</v>
+      </c>
+      <c r="C114" s="36">
+        <v>7008</v>
+      </c>
+      <c r="D114" s="36">
+        <v>1</v>
+      </c>
+      <c r="E114" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="F114" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="G114" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H114" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="I114" s="36">
+        <v>0</v>
+      </c>
+      <c r="J114" s="36">
+        <v>0</v>
+      </c>
+      <c r="K114" s="36">
+        <v>0</v>
+      </c>
+      <c r="L114" s="36">
+        <v>0</v>
+      </c>
+      <c r="M114" s="36">
+        <v>1000</v>
+      </c>
+      <c r="N114" s="36">
+        <v>0</v>
+      </c>
+      <c r="O114" s="36">
+        <v>0</v>
+      </c>
+      <c r="P114" s="36">
+        <v>4</v>
+      </c>
+      <c r="Q114" s="36">
+        <v>2</v>
+      </c>
+      <c r="R114" s="36">
+        <v>10000</v>
+      </c>
+      <c r="S114" s="36">
+        <v>4</v>
+      </c>
+      <c r="T114" s="36">
+        <v>1</v>
+      </c>
+      <c r="U114" s="36">
+        <v>2</v>
+      </c>
+      <c r="V114" s="36">
+        <v>0</v>
+      </c>
+      <c r="W114" s="36">
+        <v>15000</v>
+      </c>
+      <c r="X114" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="36">
+        <v>15000</v>
+      </c>
+      <c r="Z114" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="36">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:AA106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -5,18 +5,18 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08237993-AD29-4BEC-9073-FFEE3E23B95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F25196A-BB4A-4612-BB6D-F38FC5232AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="390" windowWidth="21600" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="310">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1362,6 +1362,17 @@
   </si>
   <si>
     <t>陨石</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血效果提高</t>
+  </si>
+  <si>
+    <t>普攻击中回血效果提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血效果提高</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2059,7 +2070,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA114"/>
+  <dimension ref="A1:AA115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -9448,112 +9459,112 @@
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A91" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="B91" s="25">
+      <c r="A91" s="24">
+        <v>59260001</v>
+      </c>
+      <c r="B91" s="24">
         <v>4</v>
       </c>
-      <c r="C91" s="25">
-        <v>6001</v>
-      </c>
-      <c r="D91" s="25">
+      <c r="C91" s="24">
+        <v>5926</v>
+      </c>
+      <c r="D91" s="24">
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="F91" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="G91" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="H91" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="I91" s="25">
-        <v>0</v>
-      </c>
-      <c r="J91" s="25">
-        <v>0</v>
-      </c>
-      <c r="K91" s="25">
-        <v>0</v>
-      </c>
-      <c r="L91" s="25">
-        <v>0</v>
-      </c>
-      <c r="M91" s="25">
-        <v>0</v>
-      </c>
-      <c r="N91" s="25">
-        <v>0</v>
-      </c>
-      <c r="O91" s="25">
-        <v>0</v>
-      </c>
-      <c r="P91" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="25">
-        <v>0</v>
-      </c>
-      <c r="R91" s="25">
-        <v>0</v>
-      </c>
-      <c r="S91" s="25">
-        <v>0</v>
-      </c>
-      <c r="T91" s="25">
-        <v>0</v>
-      </c>
-      <c r="U91" s="25">
-        <v>0</v>
-      </c>
-      <c r="V91" s="25">
-        <v>0</v>
-      </c>
-      <c r="W91" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X91" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z91" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="AA91" s="25">
+        <v>308</v>
+      </c>
+      <c r="F91" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="G91" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="I91" s="24">
+        <v>0</v>
+      </c>
+      <c r="J91" s="24">
+        <v>0</v>
+      </c>
+      <c r="K91" s="24">
+        <v>0</v>
+      </c>
+      <c r="L91" s="24">
+        <v>0</v>
+      </c>
+      <c r="M91" s="24">
+        <v>0</v>
+      </c>
+      <c r="N91" s="24">
+        <v>0</v>
+      </c>
+      <c r="O91" s="24">
+        <v>0</v>
+      </c>
+      <c r="P91" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="24">
+        <v>0</v>
+      </c>
+      <c r="R91" s="24">
+        <v>0</v>
+      </c>
+      <c r="S91" s="24">
+        <v>0</v>
+      </c>
+      <c r="T91" s="24">
+        <v>0</v>
+      </c>
+      <c r="U91" s="24">
+        <v>0</v>
+      </c>
+      <c r="V91" s="24">
+        <v>0</v>
+      </c>
+      <c r="W91" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X91" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z91" s="24">
+        <v>59140001</v>
+      </c>
+      <c r="AA91" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A92" s="25">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B92" s="25">
         <v>4</v>
       </c>
       <c r="C92" s="25">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="D92" s="25">
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G92" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="I92" s="25">
         <v>0</v>
@@ -9607,7 +9618,7 @@
         <v>10000</v>
       </c>
       <c r="Z92" s="25">
-        <v>60020001</v>
+        <v>60010001</v>
       </c>
       <c r="AA92" s="25">
         <v>0</v>
@@ -9615,28 +9626,28 @@
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B93" s="25">
         <v>4</v>
       </c>
       <c r="C93" s="25">
-        <v>6006</v>
+        <v>6003</v>
       </c>
       <c r="D93" s="25">
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G93" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -9690,7 +9701,7 @@
         <v>10000</v>
       </c>
       <c r="Z93" s="25">
-        <v>60030001</v>
+        <v>60020001</v>
       </c>
       <c r="AA93" s="25">
         <v>0</v>
@@ -9698,28 +9709,28 @@
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B94" s="25">
         <v>4</v>
       </c>
       <c r="C94" s="25">
-        <v>6009</v>
+        <v>6006</v>
       </c>
       <c r="D94" s="25">
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I94" s="25">
         <v>0</v>
@@ -9773,7 +9784,7 @@
         <v>10000</v>
       </c>
       <c r="Z94" s="25">
-        <v>60040001</v>
+        <v>60030001</v>
       </c>
       <c r="AA94" s="25">
         <v>0</v>
@@ -9781,28 +9792,28 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A95" s="25">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B95" s="25">
         <v>4</v>
       </c>
       <c r="C95" s="25">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="D95" s="25">
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>295</v>
+        <v>190</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I95" s="25">
         <v>0</v>
@@ -9856,36 +9867,36 @@
         <v>10000</v>
       </c>
       <c r="Z95" s="25">
-        <v>60080001</v>
-      </c>
-      <c r="AA95" s="26">
+        <v>60040001</v>
+      </c>
+      <c r="AA95" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A96" s="25">
-        <v>60120001</v>
+        <v>60110001</v>
       </c>
       <c r="B96" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96" s="25">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="D96" s="25">
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>293</v>
+        <v>192</v>
       </c>
       <c r="G96" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="I96" s="25">
         <v>0</v>
@@ -9909,13 +9920,13 @@
         <v>0</v>
       </c>
       <c r="P96" s="25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="S96" s="25">
         <v>0</v>
@@ -9939,7 +9950,7 @@
         <v>10000</v>
       </c>
       <c r="Z96" s="25">
-        <v>60070001</v>
+        <v>60080001</v>
       </c>
       <c r="AA96" s="26">
         <v>0</v>
@@ -9947,22 +9958,22 @@
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A97" s="25">
-        <v>60130001</v>
+        <v>60120001</v>
       </c>
       <c r="B97" s="25">
         <v>5</v>
       </c>
       <c r="C97" s="25">
-        <v>6013</v>
+        <v>6012</v>
       </c>
       <c r="D97" s="25">
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G97" s="25" t="s">
         <v>89</v>
@@ -9995,7 +10006,7 @@
         <v>4</v>
       </c>
       <c r="Q97" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R97" s="25">
         <v>10000</v>
@@ -10022,119 +10033,119 @@
         <v>10000</v>
       </c>
       <c r="Z97" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA97" s="26" t="s">
-        <v>193</v>
+        <v>60070001</v>
+      </c>
+      <c r="AA97" s="26">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A98" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="B98" s="27">
+      <c r="A98" s="25">
+        <v>60130001</v>
+      </c>
+      <c r="B98" s="25">
+        <v>5</v>
+      </c>
+      <c r="C98" s="25">
+        <v>6013</v>
+      </c>
+      <c r="D98" s="25">
+        <v>1</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F98" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="G98" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H98" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I98" s="25">
+        <v>0</v>
+      </c>
+      <c r="J98" s="25">
+        <v>0</v>
+      </c>
+      <c r="K98" s="25">
+        <v>0</v>
+      </c>
+      <c r="L98" s="25">
+        <v>0</v>
+      </c>
+      <c r="M98" s="25">
+        <v>0</v>
+      </c>
+      <c r="N98" s="25">
+        <v>0</v>
+      </c>
+      <c r="O98" s="25">
+        <v>0</v>
+      </c>
+      <c r="P98" s="25">
         <v>4</v>
       </c>
-      <c r="C98" s="27">
-        <v>6102</v>
-      </c>
-      <c r="D98" s="27">
-        <v>1</v>
-      </c>
-      <c r="E98" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="F98" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="G98" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H98" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I98" s="27">
-        <v>0</v>
-      </c>
-      <c r="J98" s="27">
-        <v>0</v>
-      </c>
-      <c r="K98" s="27">
-        <v>0</v>
-      </c>
-      <c r="L98" s="27">
-        <v>0</v>
-      </c>
-      <c r="M98" s="27">
-        <v>0</v>
-      </c>
-      <c r="N98" s="27">
-        <v>0</v>
-      </c>
-      <c r="O98" s="27">
-        <v>0</v>
-      </c>
-      <c r="P98" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="27">
-        <v>0</v>
-      </c>
-      <c r="R98" s="27">
-        <v>0</v>
-      </c>
-      <c r="S98" s="27">
-        <v>0</v>
-      </c>
-      <c r="T98" s="27">
-        <v>0</v>
-      </c>
-      <c r="U98" s="27">
-        <v>0</v>
-      </c>
-      <c r="V98" s="27">
-        <v>0</v>
-      </c>
-      <c r="W98" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X98" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y98" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z98" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="AA98" s="27">
-        <v>0</v>
+      <c r="Q98" s="25">
+        <v>2</v>
+      </c>
+      <c r="R98" s="25">
+        <v>10000</v>
+      </c>
+      <c r="S98" s="25">
+        <v>0</v>
+      </c>
+      <c r="T98" s="25">
+        <v>0</v>
+      </c>
+      <c r="U98" s="25">
+        <v>0</v>
+      </c>
+      <c r="V98" s="25">
+        <v>0</v>
+      </c>
+      <c r="W98" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X98" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z98" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="26" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B99" s="27">
         <v>4</v>
       </c>
       <c r="C99" s="27">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="D99" s="27">
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G99" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -10188,7 +10199,7 @@
         <v>10000</v>
       </c>
       <c r="Z99" s="27">
-        <v>61020001</v>
+        <v>61010001</v>
       </c>
       <c r="AA99" s="27">
         <v>0</v>
@@ -10196,28 +10207,28 @@
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B100" s="27">
         <v>4</v>
       </c>
       <c r="C100" s="27">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="G100" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -10271,7 +10282,7 @@
         <v>10000</v>
       </c>
       <c r="Z100" s="27">
-        <v>61030001</v>
+        <v>61020001</v>
       </c>
       <c r="AA100" s="27">
         <v>0</v>
@@ -10279,28 +10290,28 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B101" s="27">
         <v>4</v>
       </c>
       <c r="C101" s="27">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="D101" s="27">
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>84</v>
+        <v>258</v>
       </c>
       <c r="G101" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>84</v>
+        <v>259</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -10354,7 +10365,7 @@
         <v>10000</v>
       </c>
       <c r="Z101" s="27">
-        <v>61040001</v>
+        <v>61030001</v>
       </c>
       <c r="AA101" s="27">
         <v>0</v>
@@ -10362,28 +10373,28 @@
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B102" s="27">
         <v>4</v>
       </c>
       <c r="C102" s="27">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="D102" s="27">
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="G102" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10437,7 +10448,7 @@
         <v>10000</v>
       </c>
       <c r="Z102" s="27">
-        <v>61050001</v>
+        <v>61040001</v>
       </c>
       <c r="AA102" s="27">
         <v>0</v>
@@ -10445,28 +10456,28 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B103" s="27">
         <v>4</v>
       </c>
       <c r="C103" s="27">
-        <v>6112</v>
+        <v>6110</v>
       </c>
       <c r="D103" s="27">
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="G103" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -10520,7 +10531,7 @@
         <v>10000</v>
       </c>
       <c r="Z103" s="27">
-        <v>61060001</v>
+        <v>61050001</v>
       </c>
       <c r="AA103" s="27">
         <v>0</v>
@@ -10528,28 +10539,28 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" s="27">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B104" s="27">
         <v>4</v>
       </c>
       <c r="C104" s="27">
-        <v>6114</v>
+        <v>6112</v>
       </c>
       <c r="D104" s="27">
         <v>1</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G104" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H104" s="27" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="I104" s="27">
         <v>0</v>
@@ -10603,7 +10614,7 @@
         <v>10000</v>
       </c>
       <c r="Z104" s="27">
-        <v>61070001</v>
+        <v>61060001</v>
       </c>
       <c r="AA104" s="27">
         <v>0</v>
@@ -10611,28 +10622,28 @@
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A105" s="27">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B105" s="27">
         <v>4</v>
       </c>
       <c r="C105" s="27">
-        <v>6116</v>
+        <v>6114</v>
       </c>
       <c r="D105" s="27">
         <v>1</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F105" s="27" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G105" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H105" s="27" t="s">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="I105" s="27">
         <v>0</v>
@@ -10686,7 +10697,7 @@
         <v>10000</v>
       </c>
       <c r="Z105" s="27">
-        <v>61080001</v>
+        <v>61070001</v>
       </c>
       <c r="AA105" s="27">
         <v>0</v>
@@ -10694,28 +10705,28 @@
     </row>
     <row r="106" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A106" s="27">
-        <v>61180001</v>
+        <v>61160001</v>
       </c>
       <c r="B106" s="27">
         <v>4</v>
       </c>
       <c r="C106" s="27">
-        <v>6118</v>
+        <v>6116</v>
       </c>
       <c r="D106" s="27">
         <v>1</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F106" s="27" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G106" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H106" s="27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I106" s="27">
         <v>0</v>
@@ -10769,33 +10780,36 @@
         <v>10000</v>
       </c>
       <c r="Z106" s="27">
-        <v>61090001</v>
+        <v>61080001</v>
       </c>
       <c r="AA106" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A107" s="5">
-        <v>955001001</v>
-      </c>
-      <c r="B107" s="5">
+      <c r="A107" s="27">
+        <v>61180001</v>
+      </c>
+      <c r="B107" s="27">
         <v>4</v>
       </c>
-      <c r="C107" s="5">
-        <v>7001</v>
-      </c>
-      <c r="D107" s="5">
-        <v>1</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>296</v>
+      <c r="C107" s="27">
+        <v>6118</v>
+      </c>
+      <c r="D107" s="27">
+        <v>1</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F107" s="27" t="s">
+        <v>266</v>
       </c>
       <c r="G107" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H107" s="27">
-        <v>0</v>
+      <c r="H107" s="27" t="s">
+        <v>265</v>
       </c>
       <c r="I107" s="27">
         <v>0</v>
@@ -10840,16 +10854,16 @@
         <v>0</v>
       </c>
       <c r="W107" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X107" s="27">
         <v>0</v>
       </c>
       <c r="Y107" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z107" s="27">
-        <v>855001001</v>
+        <v>61090001</v>
       </c>
       <c r="AA107" s="27">
         <v>0</v>
@@ -10857,360 +10871,357 @@
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A108" s="5">
+        <v>955001001</v>
+      </c>
+      <c r="B108" s="5">
+        <v>4</v>
+      </c>
+      <c r="C108" s="5">
+        <v>7001</v>
+      </c>
+      <c r="D108" s="5">
+        <v>1</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="G108" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" s="27">
+        <v>0</v>
+      </c>
+      <c r="I108" s="27">
+        <v>0</v>
+      </c>
+      <c r="J108" s="27">
+        <v>0</v>
+      </c>
+      <c r="K108" s="27">
+        <v>0</v>
+      </c>
+      <c r="L108" s="27">
+        <v>0</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0</v>
+      </c>
+      <c r="N108" s="27">
+        <v>0</v>
+      </c>
+      <c r="O108" s="27">
+        <v>0</v>
+      </c>
+      <c r="P108" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="27">
+        <v>0</v>
+      </c>
+      <c r="R108" s="27">
+        <v>0</v>
+      </c>
+      <c r="S108" s="27">
+        <v>0</v>
+      </c>
+      <c r="T108" s="27">
+        <v>0</v>
+      </c>
+      <c r="U108" s="27">
+        <v>0</v>
+      </c>
+      <c r="V108" s="27">
+        <v>0</v>
+      </c>
+      <c r="W108" s="27">
+        <v>0</v>
+      </c>
+      <c r="X108" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="27">
+        <v>855001001</v>
+      </c>
+      <c r="AA108" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A109" s="5">
         <v>955001002</v>
       </c>
-      <c r="B108" s="5">
+      <c r="B109" s="5">
         <v>5</v>
       </c>
-      <c r="C108" s="5">
+      <c r="C109" s="5">
         <v>7002</v>
       </c>
-      <c r="D108" s="5">
-        <v>1</v>
-      </c>
-      <c r="E108" s="5" t="s">
+      <c r="D109" s="5">
+        <v>1</v>
+      </c>
+      <c r="E109" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="F109" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="G108" s="27" t="s">
+      <c r="G109" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="H108" s="27" t="s">
+      <c r="H109" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="I108" s="27">
-        <v>0</v>
-      </c>
-      <c r="J108" s="27">
-        <v>0</v>
-      </c>
-      <c r="K108" s="27">
-        <v>0</v>
-      </c>
-      <c r="L108" s="27">
-        <v>0</v>
-      </c>
-      <c r="M108" s="27">
-        <v>0</v>
-      </c>
-      <c r="N108" s="27">
-        <v>0</v>
-      </c>
-      <c r="O108" s="27">
-        <v>0</v>
-      </c>
-      <c r="P108" s="27">
+      <c r="I109" s="27">
+        <v>0</v>
+      </c>
+      <c r="J109" s="27">
+        <v>0</v>
+      </c>
+      <c r="K109" s="27">
+        <v>0</v>
+      </c>
+      <c r="L109" s="27">
+        <v>0</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0</v>
+      </c>
+      <c r="N109" s="27">
+        <v>0</v>
+      </c>
+      <c r="O109" s="27">
+        <v>0</v>
+      </c>
+      <c r="P109" s="27">
         <v>4</v>
       </c>
-      <c r="Q108" s="27">
-        <v>1</v>
-      </c>
-      <c r="R108" s="27">
-        <v>0</v>
-      </c>
-      <c r="S108" s="27">
-        <v>0</v>
-      </c>
-      <c r="T108" s="27">
-        <v>0</v>
-      </c>
-      <c r="U108" s="27">
-        <v>0</v>
-      </c>
-      <c r="V108" s="27">
-        <v>0</v>
-      </c>
-      <c r="W108" s="27">
-        <v>0</v>
-      </c>
-      <c r="X108" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y108" s="27">
-        <v>0</v>
-      </c>
-      <c r="Z108" s="27">
+      <c r="Q109" s="27">
+        <v>1</v>
+      </c>
+      <c r="R109" s="27">
+        <v>0</v>
+      </c>
+      <c r="S109" s="27">
+        <v>0</v>
+      </c>
+      <c r="T109" s="27">
+        <v>0</v>
+      </c>
+      <c r="U109" s="27">
+        <v>0</v>
+      </c>
+      <c r="V109" s="27">
+        <v>0</v>
+      </c>
+      <c r="W109" s="27">
+        <v>0</v>
+      </c>
+      <c r="X109" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="27">
         <v>855001002</v>
       </c>
-      <c r="AA108" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="36">
-        <v>955001003</v>
-      </c>
-      <c r="B109" s="36">
-        <v>4</v>
-      </c>
-      <c r="C109" s="36">
-        <v>7003</v>
-      </c>
-      <c r="D109" s="36">
-        <v>1</v>
-      </c>
-      <c r="E109" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="F109" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="G109" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="H109" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="I109" s="36">
-        <v>0</v>
-      </c>
-      <c r="J109" s="36">
-        <v>0</v>
-      </c>
-      <c r="K109" s="36">
-        <v>0</v>
-      </c>
-      <c r="L109" s="36">
-        <v>0</v>
-      </c>
-      <c r="M109" s="36">
-        <v>0</v>
-      </c>
-      <c r="N109" s="36">
-        <v>0</v>
-      </c>
-      <c r="O109" s="36">
-        <v>0</v>
-      </c>
-      <c r="P109" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="36">
-        <v>0</v>
-      </c>
-      <c r="R109" s="36">
-        <v>0</v>
-      </c>
-      <c r="S109" s="36">
-        <v>0</v>
-      </c>
-      <c r="T109" s="36">
-        <v>0</v>
-      </c>
-      <c r="U109" s="36">
-        <v>0</v>
-      </c>
-      <c r="V109" s="36">
-        <v>0</v>
-      </c>
-      <c r="W109" s="36">
-        <v>0</v>
-      </c>
-      <c r="X109" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y109" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z109" s="36">
-        <v>855001003</v>
-      </c>
-      <c r="AA109" s="36">
+      <c r="AA109" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A110" s="36">
-        <v>955001004</v>
+        <v>955001003</v>
       </c>
       <c r="B110" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" s="36">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="D110" s="36">
         <v>1</v>
       </c>
       <c r="E110" s="36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F110" s="36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G110" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H110" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="I110" s="36">
+        <v>0</v>
+      </c>
+      <c r="J110" s="36">
+        <v>0</v>
+      </c>
+      <c r="K110" s="36">
+        <v>0</v>
+      </c>
+      <c r="L110" s="36">
+        <v>0</v>
+      </c>
+      <c r="M110" s="36">
+        <v>0</v>
+      </c>
+      <c r="N110" s="36">
+        <v>0</v>
+      </c>
+      <c r="O110" s="36">
+        <v>0</v>
+      </c>
+      <c r="P110" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="36">
+        <v>0</v>
+      </c>
+      <c r="R110" s="36">
+        <v>0</v>
+      </c>
+      <c r="S110" s="36">
+        <v>0</v>
+      </c>
+      <c r="T110" s="36">
+        <v>0</v>
+      </c>
+      <c r="U110" s="36">
+        <v>0</v>
+      </c>
+      <c r="V110" s="36">
+        <v>0</v>
+      </c>
+      <c r="W110" s="36">
+        <v>0</v>
+      </c>
+      <c r="X110" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="36">
+        <v>855001003</v>
+      </c>
+      <c r="AA110" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="36">
+        <v>955001004</v>
+      </c>
+      <c r="B111" s="36">
+        <v>5</v>
+      </c>
+      <c r="C111" s="36">
+        <v>7004</v>
+      </c>
+      <c r="D111" s="36">
+        <v>1</v>
+      </c>
+      <c r="E111" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="F111" s="36" t="s">
         <v>299</v>
-      </c>
-      <c r="I110" s="36">
-        <v>0</v>
-      </c>
-      <c r="J110" s="36">
-        <v>0</v>
-      </c>
-      <c r="K110" s="36">
-        <v>0</v>
-      </c>
-      <c r="L110" s="36">
-        <v>0</v>
-      </c>
-      <c r="M110" s="36">
-        <v>0</v>
-      </c>
-      <c r="N110" s="36">
-        <v>0</v>
-      </c>
-      <c r="O110" s="36">
-        <v>0</v>
-      </c>
-      <c r="P110" s="36">
-        <v>4</v>
-      </c>
-      <c r="Q110" s="36">
-        <v>2</v>
-      </c>
-      <c r="R110" s="36">
-        <v>4000</v>
-      </c>
-      <c r="S110" s="36">
-        <v>4</v>
-      </c>
-      <c r="T110" s="36">
-        <v>1</v>
-      </c>
-      <c r="U110" s="36">
-        <v>4</v>
-      </c>
-      <c r="V110" s="36">
-        <v>0</v>
-      </c>
-      <c r="W110" s="36">
-        <v>15000</v>
-      </c>
-      <c r="X110" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y110" s="36">
-        <v>15000</v>
-      </c>
-      <c r="Z110" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA110" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:27" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A111" s="36">
-        <v>955001005</v>
-      </c>
-      <c r="B111" s="36">
-        <v>4</v>
-      </c>
-      <c r="C111" s="36">
-        <v>7005</v>
-      </c>
-      <c r="D111" s="36">
-        <v>1</v>
-      </c>
-      <c r="E111" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="F111" s="38" t="s">
-        <v>301</v>
       </c>
       <c r="G111" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H111" s="38" t="s">
+      <c r="H111" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="I111" s="36">
+        <v>0</v>
+      </c>
+      <c r="J111" s="36">
+        <v>0</v>
+      </c>
+      <c r="K111" s="36">
+        <v>0</v>
+      </c>
+      <c r="L111" s="36">
+        <v>0</v>
+      </c>
+      <c r="M111" s="36">
+        <v>0</v>
+      </c>
+      <c r="N111" s="36">
+        <v>0</v>
+      </c>
+      <c r="O111" s="36">
+        <v>0</v>
+      </c>
+      <c r="P111" s="36">
+        <v>4</v>
+      </c>
+      <c r="Q111" s="36">
+        <v>2</v>
+      </c>
+      <c r="R111" s="36">
+        <v>4000</v>
+      </c>
+      <c r="S111" s="36">
+        <v>4</v>
+      </c>
+      <c r="T111" s="36">
+        <v>1</v>
+      </c>
+      <c r="U111" s="36">
+        <v>4</v>
+      </c>
+      <c r="V111" s="36">
+        <v>0</v>
+      </c>
+      <c r="W111" s="36">
+        <v>15000</v>
+      </c>
+      <c r="X111" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="36">
+        <v>15000</v>
+      </c>
+      <c r="Z111" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A112" s="36">
+        <v>955001005</v>
+      </c>
+      <c r="B112" s="36">
+        <v>4</v>
+      </c>
+      <c r="C112" s="36">
+        <v>7005</v>
+      </c>
+      <c r="D112" s="36">
+        <v>1</v>
+      </c>
+      <c r="E112" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="I111" s="36">
-        <v>0</v>
-      </c>
-      <c r="J111" s="36">
-        <v>0</v>
-      </c>
-      <c r="K111" s="36">
-        <v>0</v>
-      </c>
-      <c r="L111" s="36">
-        <v>0</v>
-      </c>
-      <c r="M111" s="36">
-        <v>0</v>
-      </c>
-      <c r="N111" s="36">
-        <v>0</v>
-      </c>
-      <c r="O111" s="36">
-        <v>0</v>
-      </c>
-      <c r="P111" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="36">
-        <v>0</v>
-      </c>
-      <c r="R111" s="36">
-        <v>0</v>
-      </c>
-      <c r="S111" s="36">
-        <v>0</v>
-      </c>
-      <c r="T111" s="36">
-        <v>0</v>
-      </c>
-      <c r="U111" s="36">
-        <v>0</v>
-      </c>
-      <c r="V111" s="36">
-        <v>0</v>
-      </c>
-      <c r="W111" s="36">
-        <v>0</v>
-      </c>
-      <c r="X111" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y111" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z111" s="36">
-        <v>855001004</v>
-      </c>
-      <c r="AA111" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="36">
-        <v>955001006</v>
-      </c>
-      <c r="B112" s="36">
-        <v>5</v>
-      </c>
-      <c r="C112" s="36">
-        <v>7006</v>
-      </c>
-      <c r="D112" s="36">
-        <v>1</v>
-      </c>
-      <c r="E112" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="F112" s="36" t="s">
-        <v>302</v>
+      <c r="F112" s="38" t="s">
+        <v>301</v>
       </c>
       <c r="G112" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H112" s="36" t="s">
-        <v>302</v>
+      <c r="H112" s="38" t="s">
+        <v>301</v>
       </c>
       <c r="I112" s="36">
         <v>0</v>
@@ -11225,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="36">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N112" s="36">
         <v>0</v>
@@ -11234,10 +11245,10 @@
         <v>0</v>
       </c>
       <c r="P112" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R112" s="36">
         <v>0</v>
@@ -11249,22 +11260,22 @@
         <v>0</v>
       </c>
       <c r="U112" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V112" s="36">
         <v>0</v>
       </c>
       <c r="W112" s="36">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X112" s="36">
         <v>0</v>
       </c>
       <c r="Y112" s="36">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="Z112" s="36">
-        <v>0</v>
+        <v>855001004</v>
       </c>
       <c r="AA112" s="36">
         <v>0</v>
@@ -11272,28 +11283,28 @@
     </row>
     <row r="113" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A113" s="36">
-        <v>955001007</v>
+        <v>955001006</v>
       </c>
       <c r="B113" s="36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C113" s="36">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="D113" s="36">
         <v>1</v>
       </c>
       <c r="E113" s="36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F113" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G113" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H113" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I113" s="36">
         <v>0</v>
@@ -11308,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N113" s="36">
         <v>0</v>
@@ -11317,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="P113" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q113" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R113" s="36">
         <v>0</v>
@@ -11332,22 +11343,22 @@
         <v>0</v>
       </c>
       <c r="U113" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V113" s="36">
         <v>0</v>
       </c>
       <c r="W113" s="36">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X113" s="36">
         <v>0</v>
       </c>
       <c r="Y113" s="36">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="Z113" s="36">
-        <v>855001005</v>
+        <v>0</v>
       </c>
       <c r="AA113" s="36">
         <v>0</v>
@@ -11355,89 +11366,172 @@
     </row>
     <row r="114" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A114" s="36">
-        <v>955001008</v>
+        <v>955001007</v>
       </c>
       <c r="B114" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" s="36">
-        <v>7008</v>
+        <v>7007</v>
       </c>
       <c r="D114" s="36">
         <v>1</v>
       </c>
       <c r="E114" s="36" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F114" s="36" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G114" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H114" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="I114" s="36">
+        <v>0</v>
+      </c>
+      <c r="J114" s="36">
+        <v>0</v>
+      </c>
+      <c r="K114" s="36">
+        <v>0</v>
+      </c>
+      <c r="L114" s="36">
+        <v>0</v>
+      </c>
+      <c r="M114" s="36">
+        <v>0</v>
+      </c>
+      <c r="N114" s="36">
+        <v>0</v>
+      </c>
+      <c r="O114" s="36">
+        <v>0</v>
+      </c>
+      <c r="P114" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="36">
+        <v>0</v>
+      </c>
+      <c r="R114" s="36">
+        <v>0</v>
+      </c>
+      <c r="S114" s="36">
+        <v>0</v>
+      </c>
+      <c r="T114" s="36">
+        <v>0</v>
+      </c>
+      <c r="U114" s="36">
+        <v>0</v>
+      </c>
+      <c r="V114" s="36">
+        <v>0</v>
+      </c>
+      <c r="W114" s="36">
+        <v>0</v>
+      </c>
+      <c r="X114" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="36">
+        <v>855001005</v>
+      </c>
+      <c r="AA114" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="36">
+        <v>955001008</v>
+      </c>
+      <c r="B115" s="36">
+        <v>5</v>
+      </c>
+      <c r="C115" s="36">
+        <v>7008</v>
+      </c>
+      <c r="D115" s="36">
+        <v>1</v>
+      </c>
+      <c r="E115" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="F115" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="I114" s="36">
-        <v>0</v>
-      </c>
-      <c r="J114" s="36">
-        <v>0</v>
-      </c>
-      <c r="K114" s="36">
-        <v>0</v>
-      </c>
-      <c r="L114" s="36">
-        <v>0</v>
-      </c>
-      <c r="M114" s="36">
+      <c r="G115" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H115" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="I115" s="36">
+        <v>0</v>
+      </c>
+      <c r="J115" s="36">
+        <v>0</v>
+      </c>
+      <c r="K115" s="36">
+        <v>0</v>
+      </c>
+      <c r="L115" s="36">
+        <v>0</v>
+      </c>
+      <c r="M115" s="36">
         <v>1000</v>
       </c>
-      <c r="N114" s="36">
-        <v>0</v>
-      </c>
-      <c r="O114" s="36">
-        <v>0</v>
-      </c>
-      <c r="P114" s="36">
+      <c r="N115" s="36">
+        <v>0</v>
+      </c>
+      <c r="O115" s="36">
+        <v>0</v>
+      </c>
+      <c r="P115" s="36">
         <v>4</v>
       </c>
-      <c r="Q114" s="36">
+      <c r="Q115" s="36">
         <v>2</v>
       </c>
-      <c r="R114" s="36">
-        <v>10000</v>
-      </c>
-      <c r="S114" s="36">
+      <c r="R115" s="36">
+        <v>10000</v>
+      </c>
+      <c r="S115" s="36">
         <v>4</v>
       </c>
-      <c r="T114" s="36">
-        <v>1</v>
-      </c>
-      <c r="U114" s="36">
+      <c r="T115" s="36">
+        <v>1</v>
+      </c>
+      <c r="U115" s="36">
         <v>2</v>
       </c>
-      <c r="V114" s="36">
-        <v>0</v>
-      </c>
-      <c r="W114" s="36">
+      <c r="V115" s="36">
+        <v>0</v>
+      </c>
+      <c r="W115" s="36">
         <v>15000</v>
       </c>
-      <c r="X114" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y114" s="36">
+      <c r="X115" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="36">
         <v>15000</v>
       </c>
-      <c r="Z114" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="36">
+      <c r="Z115" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="36">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AA107" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F25196A-BB4A-4612-BB6D-F38FC5232AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB2D93-6CA2-45D0-8D9B-AD98D0253BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="311">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1086,293 +1086,298 @@
     <t>拥有护盾时同时有受伤降低效果</t>
   </si>
   <si>
+    <t>击杀回血-回复量根据击中回血数值倍率</t>
+  </si>
+  <si>
+    <t>满血触发效果</t>
+  </si>
+  <si>
+    <t>低血时同时有受到伤害降低效果</t>
+  </si>
+  <si>
+    <t>死亡时触发释放复活</t>
+  </si>
+  <si>
+    <t>复活时回复血郞、触发间隔、每轮挑战最大次数</t>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放多重打击</t>
+  </si>
+  <si>
+    <t>提高多重打击的额外伤害</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放旋风斩</t>
+  </si>
+  <si>
+    <t>释放旋风斩触发释放半月斩</t>
+  </si>
+  <si>
+    <t>使目标陷入燃烧，每秒受到火元素持续伤害效果</t>
+  </si>
+  <si>
+    <t>若干次攻击后，自动对周围任意目标释放陨石</t>
+  </si>
+  <si>
+    <t>强化燃烧效果对敌人的伤害</t>
+  </si>
+  <si>
+    <t>陨石攻击必定附加燃烧效果</t>
+  </si>
+  <si>
+    <t>使目标触电，受到伤害时额外承受触电伤害</t>
+  </si>
+  <si>
+    <t>使闪电链技能可以弹射到其他目标</t>
+  </si>
+  <si>
+    <t>若干次攻击后，自动对周围任意目标释放闪电链</t>
+  </si>
+  <si>
+    <t>使目标触电时，立刻造成触电伤害</t>
+  </si>
+  <si>
+    <t>对目标造成触电伤害时，以目标为中心释放一次电磁爆炸</t>
+  </si>
+  <si>
+    <t>使目标中毒，每秒受到毒元素伤害</t>
+  </si>
+  <si>
+    <t>若干次攻击后，释放传染技能</t>
+  </si>
+  <si>
+    <t>对目标释放中毒效果并命中时，如果目标已经中毒则造成额外伤害</t>
+  </si>
+  <si>
+    <t>击败中毒目标时，以目标为中心释放瘟疫。</t>
+  </si>
+  <si>
+    <t>瘟疫状态，每秒承受毒元素伤害，最大可叠加10层</t>
+  </si>
+  <si>
+    <t>有护盾时触发技能受到全属性伤害降低</t>
+  </si>
+  <si>
+    <t>多重打击造成额外伤害</t>
+  </si>
+  <si>
+    <t>光环效果：自身-增加光环范围：敌人-造成伤害降低、受到伤害提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+  </si>
+  <si>
+    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
+  </si>
+  <si>
+    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命暴击状态触发技能攻击速度提高</t>
+  </si>
+  <si>
+    <t>致命暴击状态触发技能攻击速度提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+  </si>
+  <si>
+    <t>斩杀时暴击触发斩杀血线变化</t>
+  </si>
+  <si>
+    <t>斩杀时暴击触发斩杀血线变化</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀血线的值增加</t>
+  </si>
+  <si>
+    <t>斩杀血线的值增加</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击几率使目标冰冻</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数触发释放冰霜新星</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星触发释放冰霜新星</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>使冰冻目标再次冰冻时触发额外伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标冰冻时造成额外伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星必定使目标冰冻</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘟疫状态</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成触电时立刻触发触电伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发触电伤害时触发释放电磁爆炸</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被击败会使其发生爆炸，爆炸会点燃被波及的敌人</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击受到额外伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，死亡触发释放死亡爆炸</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成，永久</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage_element</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S_C</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参与伤害计算的攻击元素类型（0-物理、1-冰、2-火、3-毒、4-电）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4,0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-自身效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-敌人效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-自身效果：光环范围提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-敌人效果：范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>正义光环</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能-每X秒获得最大生命值的护盾</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能-自身效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放4道雷击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）雷击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）冰弹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放冰弹攻击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）陨石</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放陨石攻击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血效果提高</t>
+  </si>
+  <si>
+    <t>普攻击中回血效果提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血效果提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>击杀怪物触发击杀回血效果</t>
-  </si>
-  <si>
-    <t>击杀回血-回复量根据击中回血数值倍率</t>
-  </si>
-  <si>
-    <t>满血触发效果</t>
-  </si>
-  <si>
-    <t>低血时同时有受到伤害降低效果</t>
-  </si>
-  <si>
-    <t>死亡时触发释放复活</t>
-  </si>
-  <si>
-    <t>复活时回复血郞、触发间隔、每轮挑战最大次数</t>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放多重打击</t>
-  </si>
-  <si>
-    <t>提高多重打击的额外伤害</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放旋风斩</t>
-  </si>
-  <si>
-    <t>释放旋风斩触发释放半月斩</t>
-  </si>
-  <si>
-    <t>使目标陷入燃烧，每秒受到火元素持续伤害效果</t>
-  </si>
-  <si>
-    <t>若干次攻击后，自动对周围任意目标释放陨石</t>
-  </si>
-  <si>
-    <t>强化燃烧效果对敌人的伤害</t>
-  </si>
-  <si>
-    <t>陨石攻击必定附加燃烧效果</t>
-  </si>
-  <si>
-    <t>使目标触电，受到伤害时额外承受触电伤害</t>
-  </si>
-  <si>
-    <t>使闪电链技能可以弹射到其他目标</t>
-  </si>
-  <si>
-    <t>若干次攻击后，自动对周围任意目标释放闪电链</t>
-  </si>
-  <si>
-    <t>使目标触电时，立刻造成触电伤害</t>
-  </si>
-  <si>
-    <t>对目标造成触电伤害时，以目标为中心释放一次电磁爆炸</t>
-  </si>
-  <si>
-    <t>使目标中毒，每秒受到毒元素伤害</t>
-  </si>
-  <si>
-    <t>若干次攻击后，释放传染技能</t>
-  </si>
-  <si>
-    <t>对目标释放中毒效果并命中时，如果目标已经中毒则造成额外伤害</t>
-  </si>
-  <si>
-    <t>击败中毒目标时，以目标为中心释放瘟疫。</t>
-  </si>
-  <si>
-    <t>瘟疫状态，每秒承受毒元素伤害，最大可叠加10层</t>
-  </si>
-  <si>
-    <t>有护盾时触发技能受到全属性伤害降低</t>
-  </si>
-  <si>
-    <t>多重打击造成额外伤害</t>
-  </si>
-  <si>
-    <t>光环效果：自身-增加光环范围：敌人-造成伤害降低、受到伤害提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-  </si>
-  <si>
-    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
-  </si>
-  <si>
-    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命暴击状态触发技能攻击速度提高</t>
-  </si>
-  <si>
-    <t>致命暴击状态触发技能攻击速度提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-  </si>
-  <si>
-    <t>斩杀时暴击触发斩杀血线变化</t>
-  </si>
-  <si>
-    <t>斩杀时暴击触发斩杀血线变化</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀血线的值增加</t>
-  </si>
-  <si>
-    <t>斩杀血线的值增加</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击几率使目标冰冻</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数触发释放冰霜新星</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星触发释放冰霜新星</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>使冰冻目标再次冰冻时触发额外伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>使目标冰冻时造成额外伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星必定使目标冰冻</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>瘟疫状态</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成触电时立刻触发触电伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发触电伤害时触发释放电磁爆炸</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被击败会使其发生爆炸，爆炸会点燃被波及的敌人</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击受到额外伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，死亡触发释放死亡爆炸</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成，永久</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage_element</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S_C</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>参与伤害计算的攻击元素类型（0-物理、1-冰、2-火、3-毒、4-电）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4,0</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能-自身效果</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能-敌人效果</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能-自身效果：光环范围提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能-敌人效果：范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>正义光环</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾技能-每X秒获得最大生命值的护盾</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾技能-自身效果</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷击</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放4道雷击敌方</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>（获得）雷击</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>（获得）冰弹</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放冰弹攻击敌方</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>（获得）陨石</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放陨石攻击敌方</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰弹</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻击中回血效果提高</t>
-  </si>
-  <si>
-    <t>普攻击中回血效果提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻击中回血效果提高</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2070,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA115"/>
+  <dimension ref="A1:AA116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2165,7 +2170,7 @@
         <v>65</v>
       </c>
       <c r="U2" s="33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>65</v>
@@ -2248,7 +2253,7 @@
         <v>14</v>
       </c>
       <c r="U3" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="V3" s="5" t="s">
         <v>34</v>
@@ -2331,7 +2336,7 @@
         <v>28</v>
       </c>
       <c r="U4" s="33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V4" s="5" t="s">
         <v>35</v>
@@ -4263,16 +4268,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>284</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>285</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I28" s="23">
         <v>0</v>
@@ -5127,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="U38" s="32" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="V38" s="28">
         <v>150</v>
@@ -6410,7 +6415,7 @@
         <v>32</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I54" s="23">
         <v>0</v>
@@ -6487,7 +6492,7 @@
         <v>70</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>32</v>
@@ -6570,7 +6575,7 @@
         <v>110</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>32</v>
@@ -6653,7 +6658,7 @@
         <v>112</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>32</v>
@@ -6736,7 +6741,7 @@
         <v>74</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>32</v>
@@ -6819,7 +6824,7 @@
         <v>75</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>32</v>
@@ -6902,7 +6907,7 @@
         <v>115</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>32</v>
@@ -6985,7 +6990,7 @@
         <v>116</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>32</v>
@@ -7074,7 +7079,7 @@
         <v>32</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I62" s="14">
         <v>0</v>
@@ -7157,7 +7162,7 @@
         <v>32</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I63" s="14">
         <v>0</v>
@@ -7240,7 +7245,7 @@
         <v>32</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I64" s="14">
         <v>0</v>
@@ -7323,7 +7328,7 @@
         <v>32</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I65" s="14">
         <v>0</v>
@@ -7400,13 +7405,13 @@
         <v>129</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G66" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I66" s="14">
         <v>0</v>
@@ -7483,13 +7488,13 @@
         <v>129</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G67" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I67" s="14">
         <v>0</v>
@@ -7572,7 +7577,7 @@
         <v>32</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I68" s="15">
         <v>0</v>
@@ -7655,7 +7660,7 @@
         <v>32</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I69" s="15">
         <v>0</v>
@@ -7738,7 +7743,7 @@
         <v>32</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
@@ -7815,13 +7820,13 @@
         <v>135</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>32</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -7898,13 +7903,13 @@
         <v>136</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G72" s="15" t="s">
         <v>32</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I72" s="15">
         <v>0</v>
@@ -7981,13 +7986,13 @@
         <v>137</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G73" s="15" t="s">
         <v>32</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I73" s="15">
         <v>0</v>
@@ -8070,7 +8075,7 @@
         <v>32</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I74" s="16">
         <v>0</v>
@@ -8153,7 +8158,7 @@
         <v>32</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I75" s="16">
         <v>0</v>
@@ -8236,7 +8241,7 @@
         <v>32</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I76" s="16">
         <v>0</v>
@@ -8319,7 +8324,7 @@
         <v>32</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I77" s="16">
         <v>0</v>
@@ -8396,13 +8401,13 @@
         <v>144</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>32</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I78" s="16">
         <v>0</v>
@@ -8651,7 +8656,7 @@
         <v>32</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I81" s="24">
         <v>0</v>
@@ -8728,7 +8733,7 @@
         <v>171</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>228</v>
+        <v>310</v>
       </c>
       <c r="G82" s="24" t="s">
         <v>32</v>
@@ -8811,7 +8816,7 @@
         <v>173</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G83" s="24" t="s">
         <v>32</v>
@@ -8894,7 +8899,7 @@
         <v>175</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G84" s="24" t="s">
         <v>32</v>
@@ -8977,7 +8982,7 @@
         <v>177</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G85" s="24" t="s">
         <v>32</v>
@@ -9060,7 +9065,7 @@
         <v>179</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G86" s="24" t="s">
         <v>32</v>
@@ -9143,7 +9148,7 @@
         <v>181</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G87" s="24" t="s">
         <v>32</v>
@@ -9226,13 +9231,13 @@
         <v>183</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G88" s="24" t="s">
         <v>32</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I88" s="24">
         <v>0</v>
@@ -9309,13 +9314,13 @@
         <v>184</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G89" s="24" t="s">
         <v>32</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I89" s="24">
         <v>0</v>
@@ -9389,16 +9394,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G90" s="24" t="s">
         <v>32</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I90" s="24">
         <v>0</v>
@@ -9472,7 +9477,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F91" s="24" t="s">
         <v>309</v>
@@ -9481,7 +9486,7 @@
         <v>32</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I91" s="24">
         <v>0</v>
@@ -9535,119 +9540,119 @@
         <v>10000</v>
       </c>
       <c r="Z91" s="24">
-        <v>59140001</v>
+        <v>59130001</v>
       </c>
       <c r="AA91" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A92" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="B92" s="25">
+      <c r="A92" s="24">
+        <v>59280001</v>
+      </c>
+      <c r="B92" s="24">
         <v>4</v>
       </c>
-      <c r="C92" s="25">
-        <v>6001</v>
-      </c>
-      <c r="D92" s="25">
+      <c r="C92" s="24">
+        <v>5928</v>
+      </c>
+      <c r="D92" s="24">
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="F92" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="G92" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="H92" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="I92" s="25">
-        <v>0</v>
-      </c>
-      <c r="J92" s="25">
-        <v>0</v>
-      </c>
-      <c r="K92" s="25">
-        <v>0</v>
-      </c>
-      <c r="L92" s="25">
-        <v>0</v>
-      </c>
-      <c r="M92" s="25">
-        <v>0</v>
-      </c>
-      <c r="N92" s="25">
-        <v>0</v>
-      </c>
-      <c r="O92" s="25">
-        <v>0</v>
-      </c>
-      <c r="P92" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="25">
-        <v>0</v>
-      </c>
-      <c r="R92" s="25">
-        <v>0</v>
-      </c>
-      <c r="S92" s="25">
-        <v>0</v>
-      </c>
-      <c r="T92" s="25">
-        <v>0</v>
-      </c>
-      <c r="U92" s="25">
-        <v>0</v>
-      </c>
-      <c r="V92" s="25">
-        <v>0</v>
-      </c>
-      <c r="W92" s="25">
-        <v>10000</v>
-      </c>
-      <c r="X92" s="25">
-        <v>0</v>
-      </c>
-      <c r="Y92" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Z92" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="AA92" s="25">
+        <v>307</v>
+      </c>
+      <c r="F92" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="G92" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H92" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="I92" s="24">
+        <v>0</v>
+      </c>
+      <c r="J92" s="24">
+        <v>0</v>
+      </c>
+      <c r="K92" s="24">
+        <v>0</v>
+      </c>
+      <c r="L92" s="24">
+        <v>0</v>
+      </c>
+      <c r="M92" s="24">
+        <v>0</v>
+      </c>
+      <c r="N92" s="24">
+        <v>0</v>
+      </c>
+      <c r="O92" s="24">
+        <v>0</v>
+      </c>
+      <c r="P92" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="24">
+        <v>0</v>
+      </c>
+      <c r="R92" s="24">
+        <v>0</v>
+      </c>
+      <c r="S92" s="24">
+        <v>0</v>
+      </c>
+      <c r="T92" s="24">
+        <v>0</v>
+      </c>
+      <c r="U92" s="24">
+        <v>0</v>
+      </c>
+      <c r="V92" s="24">
+        <v>0</v>
+      </c>
+      <c r="W92" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X92" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z92" s="24">
+        <v>59140001</v>
+      </c>
+      <c r="AA92" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B93" s="25">
         <v>4</v>
       </c>
       <c r="C93" s="25">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="D93" s="25">
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G93" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -9701,7 +9706,7 @@
         <v>10000</v>
       </c>
       <c r="Z93" s="25">
-        <v>60020001</v>
+        <v>60010001</v>
       </c>
       <c r="AA93" s="25">
         <v>0</v>
@@ -9709,28 +9714,28 @@
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B94" s="25">
         <v>4</v>
       </c>
       <c r="C94" s="25">
-        <v>6006</v>
+        <v>6003</v>
       </c>
       <c r="D94" s="25">
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="I94" s="25">
         <v>0</v>
@@ -9784,7 +9789,7 @@
         <v>10000</v>
       </c>
       <c r="Z94" s="25">
-        <v>60030001</v>
+        <v>60020001</v>
       </c>
       <c r="AA94" s="25">
         <v>0</v>
@@ -9792,28 +9797,28 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A95" s="25">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B95" s="25">
         <v>4</v>
       </c>
       <c r="C95" s="25">
-        <v>6009</v>
+        <v>6006</v>
       </c>
       <c r="D95" s="25">
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I95" s="25">
         <v>0</v>
@@ -9867,7 +9872,7 @@
         <v>10000</v>
       </c>
       <c r="Z95" s="25">
-        <v>60040001</v>
+        <v>60030001</v>
       </c>
       <c r="AA95" s="25">
         <v>0</v>
@@ -9875,28 +9880,28 @@
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A96" s="25">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B96" s="25">
         <v>4</v>
       </c>
       <c r="C96" s="25">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="D96" s="25">
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>295</v>
+        <v>190</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="G96" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I96" s="25">
         <v>0</v>
@@ -9950,36 +9955,36 @@
         <v>10000</v>
       </c>
       <c r="Z96" s="25">
-        <v>60080001</v>
-      </c>
-      <c r="AA96" s="26">
+        <v>60040001</v>
+      </c>
+      <c r="AA96" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A97" s="25">
-        <v>60120001</v>
+        <v>60110001</v>
       </c>
       <c r="B97" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97" s="25">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="D97" s="25">
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>293</v>
+        <v>192</v>
       </c>
       <c r="G97" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H97" s="25" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="I97" s="25">
         <v>0</v>
@@ -10003,13 +10008,13 @@
         <v>0</v>
       </c>
       <c r="P97" s="25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="S97" s="25">
         <v>0</v>
@@ -10033,7 +10038,7 @@
         <v>10000</v>
       </c>
       <c r="Z97" s="25">
-        <v>60070001</v>
+        <v>60080001</v>
       </c>
       <c r="AA97" s="26">
         <v>0</v>
@@ -10041,28 +10046,28 @@
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A98" s="25">
-        <v>60130001</v>
+        <v>60120001</v>
       </c>
       <c r="B98" s="25">
         <v>5</v>
       </c>
       <c r="C98" s="25">
-        <v>6013</v>
+        <v>6012</v>
       </c>
       <c r="D98" s="25">
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F98" s="25" t="s">
         <v>292</v>
-      </c>
-      <c r="F98" s="25" t="s">
-        <v>294</v>
       </c>
       <c r="G98" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I98" s="25">
         <v>0</v>
@@ -10089,7 +10094,7 @@
         <v>4</v>
       </c>
       <c r="Q98" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R98" s="25">
         <v>10000</v>
@@ -10116,119 +10121,119 @@
         <v>10000</v>
       </c>
       <c r="Z98" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA98" s="26" t="s">
-        <v>193</v>
+        <v>60070001</v>
+      </c>
+      <c r="AA98" s="26">
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A99" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="B99" s="27">
+      <c r="A99" s="25">
+        <v>60130001</v>
+      </c>
+      <c r="B99" s="25">
+        <v>5</v>
+      </c>
+      <c r="C99" s="25">
+        <v>6013</v>
+      </c>
+      <c r="D99" s="25">
+        <v>1</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F99" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="G99" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H99" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="I99" s="25">
+        <v>0</v>
+      </c>
+      <c r="J99" s="25">
+        <v>0</v>
+      </c>
+      <c r="K99" s="25">
+        <v>0</v>
+      </c>
+      <c r="L99" s="25">
+        <v>0</v>
+      </c>
+      <c r="M99" s="25">
+        <v>0</v>
+      </c>
+      <c r="N99" s="25">
+        <v>0</v>
+      </c>
+      <c r="O99" s="25">
+        <v>0</v>
+      </c>
+      <c r="P99" s="25">
         <v>4</v>
       </c>
-      <c r="C99" s="27">
-        <v>6102</v>
-      </c>
-      <c r="D99" s="27">
-        <v>1</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="F99" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="G99" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H99" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I99" s="27">
-        <v>0</v>
-      </c>
-      <c r="J99" s="27">
-        <v>0</v>
-      </c>
-      <c r="K99" s="27">
-        <v>0</v>
-      </c>
-      <c r="L99" s="27">
-        <v>0</v>
-      </c>
-      <c r="M99" s="27">
-        <v>0</v>
-      </c>
-      <c r="N99" s="27">
-        <v>0</v>
-      </c>
-      <c r="O99" s="27">
-        <v>0</v>
-      </c>
-      <c r="P99" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="27">
-        <v>0</v>
-      </c>
-      <c r="R99" s="27">
-        <v>0</v>
-      </c>
-      <c r="S99" s="27">
-        <v>0</v>
-      </c>
-      <c r="T99" s="27">
-        <v>0</v>
-      </c>
-      <c r="U99" s="27">
-        <v>0</v>
-      </c>
-      <c r="V99" s="27">
-        <v>0</v>
-      </c>
-      <c r="W99" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X99" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y99" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z99" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="AA99" s="27">
-        <v>0</v>
+      <c r="Q99" s="25">
+        <v>2</v>
+      </c>
+      <c r="R99" s="25">
+        <v>10000</v>
+      </c>
+      <c r="S99" s="25">
+        <v>0</v>
+      </c>
+      <c r="T99" s="25">
+        <v>0</v>
+      </c>
+      <c r="U99" s="25">
+        <v>0</v>
+      </c>
+      <c r="V99" s="25">
+        <v>0</v>
+      </c>
+      <c r="W99" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X99" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z99" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="26" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B100" s="27">
         <v>4</v>
       </c>
       <c r="C100" s="27">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G100" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -10282,7 +10287,7 @@
         <v>10000</v>
       </c>
       <c r="Z100" s="27">
-        <v>61020001</v>
+        <v>61010001</v>
       </c>
       <c r="AA100" s="27">
         <v>0</v>
@@ -10290,28 +10295,28 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B101" s="27">
         <v>4</v>
       </c>
       <c r="C101" s="27">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="D101" s="27">
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="G101" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -10365,7 +10370,7 @@
         <v>10000</v>
       </c>
       <c r="Z101" s="27">
-        <v>61030001</v>
+        <v>61020001</v>
       </c>
       <c r="AA101" s="27">
         <v>0</v>
@@ -10373,28 +10378,28 @@
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B102" s="27">
         <v>4</v>
       </c>
       <c r="C102" s="27">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="D102" s="27">
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>84</v>
+        <v>257</v>
       </c>
       <c r="G102" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>84</v>
+        <v>258</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10448,7 +10453,7 @@
         <v>10000</v>
       </c>
       <c r="Z102" s="27">
-        <v>61040001</v>
+        <v>61030001</v>
       </c>
       <c r="AA102" s="27">
         <v>0</v>
@@ -10456,28 +10461,28 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B103" s="27">
         <v>4</v>
       </c>
       <c r="C103" s="27">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="D103" s="27">
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="G103" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -10531,7 +10536,7 @@
         <v>10000</v>
       </c>
       <c r="Z103" s="27">
-        <v>61050001</v>
+        <v>61040001</v>
       </c>
       <c r="AA103" s="27">
         <v>0</v>
@@ -10539,28 +10544,28 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" s="27">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B104" s="27">
         <v>4</v>
       </c>
       <c r="C104" s="27">
-        <v>6112</v>
+        <v>6110</v>
       </c>
       <c r="D104" s="27">
         <v>1</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="G104" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H104" s="27" t="s">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="I104" s="27">
         <v>0</v>
@@ -10614,7 +10619,7 @@
         <v>10000</v>
       </c>
       <c r="Z104" s="27">
-        <v>61060001</v>
+        <v>61050001</v>
       </c>
       <c r="AA104" s="27">
         <v>0</v>
@@ -10622,28 +10627,28 @@
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A105" s="27">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B105" s="27">
         <v>4</v>
       </c>
       <c r="C105" s="27">
-        <v>6114</v>
+        <v>6112</v>
       </c>
       <c r="D105" s="27">
         <v>1</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F105" s="27" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G105" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H105" s="27" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="I105" s="27">
         <v>0</v>
@@ -10697,7 +10702,7 @@
         <v>10000</v>
       </c>
       <c r="Z105" s="27">
-        <v>61070001</v>
+        <v>61060001</v>
       </c>
       <c r="AA105" s="27">
         <v>0</v>
@@ -10705,28 +10710,28 @@
     </row>
     <row r="106" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A106" s="27">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B106" s="27">
         <v>4</v>
       </c>
       <c r="C106" s="27">
-        <v>6116</v>
+        <v>6114</v>
       </c>
       <c r="D106" s="27">
         <v>1</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F106" s="27" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G106" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H106" s="27" t="s">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="I106" s="27">
         <v>0</v>
@@ -10780,7 +10785,7 @@
         <v>10000</v>
       </c>
       <c r="Z106" s="27">
-        <v>61080001</v>
+        <v>61070001</v>
       </c>
       <c r="AA106" s="27">
         <v>0</v>
@@ -10788,28 +10793,28 @@
     </row>
     <row r="107" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A107" s="27">
-        <v>61180001</v>
+        <v>61160001</v>
       </c>
       <c r="B107" s="27">
         <v>4</v>
       </c>
       <c r="C107" s="27">
-        <v>6118</v>
+        <v>6116</v>
       </c>
       <c r="D107" s="27">
         <v>1</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F107" s="27" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G107" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H107" s="27" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I107" s="27">
         <v>0</v>
@@ -10863,33 +10868,36 @@
         <v>10000</v>
       </c>
       <c r="Z107" s="27">
-        <v>61090001</v>
+        <v>61080001</v>
       </c>
       <c r="AA107" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A108" s="5">
-        <v>955001001</v>
-      </c>
-      <c r="B108" s="5">
+      <c r="A108" s="27">
+        <v>61180001</v>
+      </c>
+      <c r="B108" s="27">
         <v>4</v>
       </c>
-      <c r="C108" s="5">
-        <v>7001</v>
-      </c>
-      <c r="D108" s="5">
-        <v>1</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>296</v>
+      <c r="C108" s="27">
+        <v>6118</v>
+      </c>
+      <c r="D108" s="27">
+        <v>1</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F108" s="27" t="s">
+        <v>265</v>
       </c>
       <c r="G108" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H108" s="27">
-        <v>0</v>
+      <c r="H108" s="27" t="s">
+        <v>264</v>
       </c>
       <c r="I108" s="27">
         <v>0</v>
@@ -10934,16 +10942,16 @@
         <v>0</v>
       </c>
       <c r="W108" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X108" s="27">
         <v>0</v>
       </c>
       <c r="Y108" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z108" s="27">
-        <v>855001001</v>
+        <v>61090001</v>
       </c>
       <c r="AA108" s="27">
         <v>0</v>
@@ -10951,185 +10959,182 @@
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A109" s="5">
+        <v>955001001</v>
+      </c>
+      <c r="B109" s="5">
+        <v>4</v>
+      </c>
+      <c r="C109" s="5">
+        <v>7001</v>
+      </c>
+      <c r="D109" s="5">
+        <v>1</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="G109" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H109" s="27">
+        <v>0</v>
+      </c>
+      <c r="I109" s="27">
+        <v>0</v>
+      </c>
+      <c r="J109" s="27">
+        <v>0</v>
+      </c>
+      <c r="K109" s="27">
+        <v>0</v>
+      </c>
+      <c r="L109" s="27">
+        <v>0</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0</v>
+      </c>
+      <c r="N109" s="27">
+        <v>0</v>
+      </c>
+      <c r="O109" s="27">
+        <v>0</v>
+      </c>
+      <c r="P109" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="27">
+        <v>0</v>
+      </c>
+      <c r="R109" s="27">
+        <v>0</v>
+      </c>
+      <c r="S109" s="27">
+        <v>0</v>
+      </c>
+      <c r="T109" s="27">
+        <v>0</v>
+      </c>
+      <c r="U109" s="27">
+        <v>0</v>
+      </c>
+      <c r="V109" s="27">
+        <v>0</v>
+      </c>
+      <c r="W109" s="27">
+        <v>0</v>
+      </c>
+      <c r="X109" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="27">
+        <v>855001001</v>
+      </c>
+      <c r="AA109" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A110" s="5">
         <v>955001002</v>
       </c>
-      <c r="B109" s="5">
+      <c r="B110" s="5">
         <v>5</v>
       </c>
-      <c r="C109" s="5">
+      <c r="C110" s="5">
         <v>7002</v>
       </c>
-      <c r="D109" s="5">
-        <v>1</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G109" s="27" t="s">
+      <c r="D110" s="5">
+        <v>1</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G110" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="H109" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="I109" s="27">
-        <v>0</v>
-      </c>
-      <c r="J109" s="27">
-        <v>0</v>
-      </c>
-      <c r="K109" s="27">
-        <v>0</v>
-      </c>
-      <c r="L109" s="27">
-        <v>0</v>
-      </c>
-      <c r="M109" s="27">
-        <v>0</v>
-      </c>
-      <c r="N109" s="27">
-        <v>0</v>
-      </c>
-      <c r="O109" s="27">
-        <v>0</v>
-      </c>
-      <c r="P109" s="27">
+      <c r="H110" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="I110" s="27">
+        <v>0</v>
+      </c>
+      <c r="J110" s="27">
+        <v>0</v>
+      </c>
+      <c r="K110" s="27">
+        <v>0</v>
+      </c>
+      <c r="L110" s="27">
+        <v>0</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0</v>
+      </c>
+      <c r="N110" s="27">
+        <v>0</v>
+      </c>
+      <c r="O110" s="27">
+        <v>0</v>
+      </c>
+      <c r="P110" s="27">
         <v>4</v>
       </c>
-      <c r="Q109" s="27">
-        <v>1</v>
-      </c>
-      <c r="R109" s="27">
-        <v>0</v>
-      </c>
-      <c r="S109" s="27">
-        <v>0</v>
-      </c>
-      <c r="T109" s="27">
-        <v>0</v>
-      </c>
-      <c r="U109" s="27">
-        <v>0</v>
-      </c>
-      <c r="V109" s="27">
-        <v>0</v>
-      </c>
-      <c r="W109" s="27">
-        <v>0</v>
-      </c>
-      <c r="X109" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y109" s="27">
-        <v>0</v>
-      </c>
-      <c r="Z109" s="27">
+      <c r="Q110" s="27">
+        <v>1</v>
+      </c>
+      <c r="R110" s="27">
+        <v>0</v>
+      </c>
+      <c r="S110" s="27">
+        <v>0</v>
+      </c>
+      <c r="T110" s="27">
+        <v>0</v>
+      </c>
+      <c r="U110" s="27">
+        <v>0</v>
+      </c>
+      <c r="V110" s="27">
+        <v>0</v>
+      </c>
+      <c r="W110" s="27">
+        <v>0</v>
+      </c>
+      <c r="X110" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="27">
         <v>855001002</v>
       </c>
-      <c r="AA109" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="36">
-        <v>955001003</v>
-      </c>
-      <c r="B110" s="36">
-        <v>4</v>
-      </c>
-      <c r="C110" s="36">
-        <v>7003</v>
-      </c>
-      <c r="D110" s="36">
-        <v>1</v>
-      </c>
-      <c r="E110" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="F110" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="G110" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="H110" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="I110" s="36">
-        <v>0</v>
-      </c>
-      <c r="J110" s="36">
-        <v>0</v>
-      </c>
-      <c r="K110" s="36">
-        <v>0</v>
-      </c>
-      <c r="L110" s="36">
-        <v>0</v>
-      </c>
-      <c r="M110" s="36">
-        <v>0</v>
-      </c>
-      <c r="N110" s="36">
-        <v>0</v>
-      </c>
-      <c r="O110" s="36">
-        <v>0</v>
-      </c>
-      <c r="P110" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="36">
-        <v>0</v>
-      </c>
-      <c r="R110" s="36">
-        <v>0</v>
-      </c>
-      <c r="S110" s="36">
-        <v>0</v>
-      </c>
-      <c r="T110" s="36">
-        <v>0</v>
-      </c>
-      <c r="U110" s="36">
-        <v>0</v>
-      </c>
-      <c r="V110" s="36">
-        <v>0</v>
-      </c>
-      <c r="W110" s="36">
-        <v>0</v>
-      </c>
-      <c r="X110" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y110" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z110" s="36">
-        <v>855001003</v>
-      </c>
-      <c r="AA110" s="36">
+      <c r="AA110" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A111" s="36">
-        <v>955001004</v>
+        <v>955001003</v>
       </c>
       <c r="B111" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C111" s="36">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="D111" s="36">
         <v>1</v>
       </c>
       <c r="E111" s="36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F111" s="36" t="s">
         <v>299</v>
@@ -11162,66 +11167,66 @@
         <v>0</v>
       </c>
       <c r="P111" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R111" s="36">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="S111" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T111" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U111" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V111" s="36">
         <v>0</v>
       </c>
       <c r="W111" s="36">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X111" s="36">
         <v>0</v>
       </c>
       <c r="Y111" s="36">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="Z111" s="36">
-        <v>0</v>
+        <v>855001003</v>
       </c>
       <c r="AA111" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A112" s="36">
-        <v>955001005</v>
+        <v>955001004</v>
       </c>
       <c r="B112" s="36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C112" s="36">
-        <v>7005</v>
+        <v>7004</v>
       </c>
       <c r="D112" s="36">
         <v>1</v>
       </c>
-      <c r="E112" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="F112" s="38" t="s">
-        <v>301</v>
+      <c r="E112" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="F112" s="36" t="s">
+        <v>298</v>
       </c>
       <c r="G112" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H112" s="38" t="s">
-        <v>301</v>
+      <c r="H112" s="36" t="s">
+        <v>298</v>
       </c>
       <c r="I112" s="36">
         <v>0</v>
@@ -11245,66 +11250,66 @@
         <v>0</v>
       </c>
       <c r="P112" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q112" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R112" s="36">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="S112" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T112" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U112" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V112" s="36">
         <v>0</v>
       </c>
       <c r="W112" s="36">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X112" s="36">
         <v>0</v>
       </c>
       <c r="Y112" s="36">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="Z112" s="36">
-        <v>855001004</v>
+        <v>0</v>
       </c>
       <c r="AA112" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:27" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A113" s="36">
-        <v>955001006</v>
+        <v>955001005</v>
       </c>
       <c r="B113" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113" s="36">
-        <v>7006</v>
+        <v>7005</v>
       </c>
       <c r="D113" s="36">
         <v>1</v>
       </c>
-      <c r="E113" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="F113" s="36" t="s">
-        <v>302</v>
+      <c r="E113" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="F113" s="38" t="s">
+        <v>300</v>
       </c>
       <c r="G113" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H113" s="36" t="s">
-        <v>302</v>
+      <c r="H113" s="38" t="s">
+        <v>300</v>
       </c>
       <c r="I113" s="36">
         <v>0</v>
@@ -11319,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="36">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N113" s="36">
         <v>0</v>
@@ -11328,10 +11333,10 @@
         <v>0</v>
       </c>
       <c r="P113" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R113" s="36">
         <v>0</v>
@@ -11343,22 +11348,22 @@
         <v>0</v>
       </c>
       <c r="U113" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V113" s="36">
         <v>0</v>
       </c>
       <c r="W113" s="36">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X113" s="36">
         <v>0</v>
       </c>
       <c r="Y113" s="36">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="Z113" s="36">
-        <v>0</v>
+        <v>855001004</v>
       </c>
       <c r="AA113" s="36">
         <v>0</v>
@@ -11366,28 +11371,28 @@
     </row>
     <row r="114" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A114" s="36">
-        <v>955001007</v>
+        <v>955001006</v>
       </c>
       <c r="B114" s="36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C114" s="36">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="D114" s="36">
         <v>1</v>
       </c>
       <c r="E114" s="36" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F114" s="36" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G114" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H114" s="36" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I114" s="36">
         <v>0</v>
@@ -11402,7 +11407,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N114" s="36">
         <v>0</v>
@@ -11411,10 +11416,10 @@
         <v>0</v>
       </c>
       <c r="P114" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q114" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R114" s="36">
         <v>0</v>
@@ -11426,22 +11431,22 @@
         <v>0</v>
       </c>
       <c r="U114" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V114" s="36">
         <v>0</v>
       </c>
       <c r="W114" s="36">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X114" s="36">
         <v>0</v>
       </c>
       <c r="Y114" s="36">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="Z114" s="36">
-        <v>855001005</v>
+        <v>0</v>
       </c>
       <c r="AA114" s="36">
         <v>0</v>
@@ -11449,28 +11454,28 @@
     </row>
     <row r="115" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A115" s="36">
-        <v>955001008</v>
+        <v>955001007</v>
       </c>
       <c r="B115" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" s="36">
-        <v>7008</v>
+        <v>7007</v>
       </c>
       <c r="D115" s="36">
         <v>1</v>
       </c>
       <c r="E115" s="36" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F115" s="36" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G115" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H115" s="36" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I115" s="36">
         <v>0</v>
@@ -11485,53 +11490,136 @@
         <v>0</v>
       </c>
       <c r="M115" s="36">
+        <v>0</v>
+      </c>
+      <c r="N115" s="36">
+        <v>0</v>
+      </c>
+      <c r="O115" s="36">
+        <v>0</v>
+      </c>
+      <c r="P115" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="36">
+        <v>0</v>
+      </c>
+      <c r="R115" s="36">
+        <v>0</v>
+      </c>
+      <c r="S115" s="36">
+        <v>0</v>
+      </c>
+      <c r="T115" s="36">
+        <v>0</v>
+      </c>
+      <c r="U115" s="36">
+        <v>0</v>
+      </c>
+      <c r="V115" s="36">
+        <v>0</v>
+      </c>
+      <c r="W115" s="36">
+        <v>0</v>
+      </c>
+      <c r="X115" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="36">
+        <v>855001005</v>
+      </c>
+      <c r="AA115" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A116" s="36">
+        <v>955001008</v>
+      </c>
+      <c r="B116" s="36">
+        <v>5</v>
+      </c>
+      <c r="C116" s="36">
+        <v>7008</v>
+      </c>
+      <c r="D116" s="36">
+        <v>1</v>
+      </c>
+      <c r="E116" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="F116" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="G116" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H116" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="I116" s="36">
+        <v>0</v>
+      </c>
+      <c r="J116" s="36">
+        <v>0</v>
+      </c>
+      <c r="K116" s="36">
+        <v>0</v>
+      </c>
+      <c r="L116" s="36">
+        <v>0</v>
+      </c>
+      <c r="M116" s="36">
         <v>1000</v>
       </c>
-      <c r="N115" s="36">
-        <v>0</v>
-      </c>
-      <c r="O115" s="36">
-        <v>0</v>
-      </c>
-      <c r="P115" s="36">
+      <c r="N116" s="36">
+        <v>0</v>
+      </c>
+      <c r="O116" s="36">
+        <v>0</v>
+      </c>
+      <c r="P116" s="36">
         <v>4</v>
       </c>
-      <c r="Q115" s="36">
+      <c r="Q116" s="36">
         <v>2</v>
       </c>
-      <c r="R115" s="36">
-        <v>10000</v>
-      </c>
-      <c r="S115" s="36">
+      <c r="R116" s="36">
+        <v>10000</v>
+      </c>
+      <c r="S116" s="36">
         <v>4</v>
       </c>
-      <c r="T115" s="36">
-        <v>1</v>
-      </c>
-      <c r="U115" s="36">
+      <c r="T116" s="36">
+        <v>1</v>
+      </c>
+      <c r="U116" s="36">
         <v>2</v>
       </c>
-      <c r="V115" s="36">
-        <v>0</v>
-      </c>
-      <c r="W115" s="36">
+      <c r="V116" s="36">
+        <v>0</v>
+      </c>
+      <c r="W116" s="36">
         <v>15000</v>
       </c>
-      <c r="X115" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y115" s="36">
+      <c r="X116" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="36">
         <v>15000</v>
       </c>
-      <c r="Z115" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA115" s="36">
+      <c r="Z116" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="36">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA107" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AA108" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB2D93-6CA2-45D0-8D9B-AD98D0253BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9C549B-1C19-43BB-AC38-117E07DDA205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="315">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1378,6 +1378,20 @@
   </si>
   <si>
     <t>击杀怪物触发击杀回血效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击目标数量</t>
+  </si>
+  <si>
+    <t>雷击伤害</t>
+  </si>
+  <si>
+    <t>雷击目标数量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击伤害</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2075,7 +2089,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA116"/>
+  <dimension ref="A1:AA118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -8804,7 +8818,7 @@
         <v>59090001</v>
       </c>
       <c r="B83" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C83" s="24">
         <v>5909</v>
@@ -8843,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83" s="24">
         <v>0</v>
@@ -9468,7 +9482,7 @@
         <v>59260001</v>
       </c>
       <c r="B91" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C91" s="24">
         <v>5926</v>
@@ -9507,7 +9521,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P91" s="24">
         <v>0</v>
@@ -11120,30 +11134,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:27" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A111" s="36">
-        <v>955001003</v>
+        <v>95000100</v>
       </c>
       <c r="B111" s="36">
         <v>4</v>
       </c>
       <c r="C111" s="36">
-        <v>7003</v>
+        <v>7005</v>
       </c>
       <c r="D111" s="36">
         <v>1</v>
       </c>
-      <c r="E111" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="F111" s="36" t="s">
-        <v>299</v>
+      <c r="E111" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="F111" s="38" t="s">
+        <v>300</v>
       </c>
       <c r="G111" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H111" s="36" t="s">
-        <v>299</v>
+      <c r="H111" s="38" t="s">
+        <v>300</v>
       </c>
       <c r="I111" s="36">
         <v>0</v>
@@ -11197,7 +11211,7 @@
         <v>0</v>
       </c>
       <c r="Z111" s="36">
-        <v>855001003</v>
+        <v>85001000</v>
       </c>
       <c r="AA111" s="36">
         <v>0</v>
@@ -11205,28 +11219,28 @@
     </row>
     <row r="112" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A112" s="36">
-        <v>955001004</v>
+        <v>95000101</v>
       </c>
       <c r="B112" s="36">
         <v>5</v>
       </c>
       <c r="C112" s="36">
-        <v>7004</v>
+        <v>7006</v>
       </c>
       <c r="D112" s="36">
         <v>1</v>
       </c>
       <c r="E112" s="36" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F112" s="36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G112" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H112" s="36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I112" s="36">
         <v>0</v>
@@ -11241,7 +11255,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N112" s="36">
         <v>0</v>
@@ -11256,22 +11270,22 @@
         <v>2</v>
       </c>
       <c r="R112" s="36">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="S112" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T112" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U112" s="36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V112" s="36">
         <v>0</v>
       </c>
       <c r="W112" s="36">
-        <v>15000</v>
+        <v>21000</v>
       </c>
       <c r="X112" s="36">
         <v>0</v>
@@ -11286,30 +11300,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A113" s="36">
-        <v>955001005</v>
+        <v>95100100</v>
       </c>
       <c r="B113" s="36">
         <v>4</v>
       </c>
       <c r="C113" s="36">
-        <v>7005</v>
+        <v>7007</v>
       </c>
       <c r="D113" s="36">
         <v>1</v>
       </c>
-      <c r="E113" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="F113" s="38" t="s">
-        <v>300</v>
+      <c r="E113" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="F113" s="36" t="s">
+        <v>302</v>
       </c>
       <c r="G113" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H113" s="38" t="s">
-        <v>300</v>
+      <c r="H113" s="36" t="s">
+        <v>302</v>
       </c>
       <c r="I113" s="36">
         <v>0</v>
@@ -11363,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="Z113" s="36">
-        <v>855001004</v>
+        <v>85100100</v>
       </c>
       <c r="AA113" s="36">
         <v>0</v>
@@ -11371,28 +11385,28 @@
     </row>
     <row r="114" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A114" s="36">
-        <v>955001006</v>
+        <v>95100101</v>
       </c>
       <c r="B114" s="36">
         <v>5</v>
       </c>
       <c r="C114" s="36">
-        <v>7006</v>
+        <v>7008</v>
       </c>
       <c r="D114" s="36">
         <v>1</v>
       </c>
       <c r="E114" s="36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F114" s="36" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G114" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H114" s="36" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I114" s="36">
         <v>0</v>
@@ -11422,22 +11436,22 @@
         <v>2</v>
       </c>
       <c r="R114" s="36">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="S114" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T114" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U114" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V114" s="36">
         <v>0</v>
       </c>
       <c r="W114" s="36">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="X114" s="36">
         <v>0</v>
@@ -11454,28 +11468,28 @@
     </row>
     <row r="115" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A115" s="36">
-        <v>955001007</v>
+        <v>95200100</v>
       </c>
       <c r="B115" s="36">
         <v>4</v>
       </c>
       <c r="C115" s="36">
-        <v>7007</v>
+        <v>7003</v>
       </c>
       <c r="D115" s="36">
         <v>1</v>
       </c>
       <c r="E115" s="36" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F115" s="36" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G115" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H115" s="36" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I115" s="36">
         <v>0</v>
@@ -11529,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="Z115" s="36">
-        <v>855001005</v>
+        <v>85200100</v>
       </c>
       <c r="AA115" s="36">
         <v>0</v>
@@ -11537,28 +11551,28 @@
     </row>
     <row r="116" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A116" s="36">
-        <v>955001008</v>
+        <v>95200101</v>
       </c>
       <c r="B116" s="36">
         <v>5</v>
       </c>
       <c r="C116" s="36">
-        <v>7008</v>
+        <v>7004</v>
       </c>
       <c r="D116" s="36">
         <v>1</v>
       </c>
       <c r="E116" s="36" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F116" s="36" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G116" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H116" s="36" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I116" s="36">
         <v>0</v>
@@ -11573,7 +11587,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="36">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N116" s="36">
         <v>0</v>
@@ -11588,7 +11602,7 @@
         <v>2</v>
       </c>
       <c r="R116" s="36">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="S116" s="36">
         <v>4</v>
@@ -11597,13 +11611,13 @@
         <v>1</v>
       </c>
       <c r="U116" s="36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V116" s="36">
         <v>0</v>
       </c>
       <c r="W116" s="36">
-        <v>15000</v>
+        <v>24000</v>
       </c>
       <c r="X116" s="36">
         <v>0</v>
@@ -11615,6 +11629,172 @@
         <v>0</v>
       </c>
       <c r="AA116" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A117" s="5">
+        <v>95200300</v>
+      </c>
+      <c r="B117" s="5">
+        <v>4</v>
+      </c>
+      <c r="C117" s="5">
+        <v>7009</v>
+      </c>
+      <c r="D117" s="5">
+        <v>1</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G117" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H117" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="I117" s="36">
+        <v>0</v>
+      </c>
+      <c r="J117" s="36">
+        <v>0</v>
+      </c>
+      <c r="K117" s="36">
+        <v>0</v>
+      </c>
+      <c r="L117" s="36">
+        <v>0</v>
+      </c>
+      <c r="M117" s="36">
+        <v>0</v>
+      </c>
+      <c r="N117" s="36">
+        <v>0</v>
+      </c>
+      <c r="O117" s="36">
+        <v>0</v>
+      </c>
+      <c r="P117" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="36">
+        <v>0</v>
+      </c>
+      <c r="R117" s="36">
+        <v>0</v>
+      </c>
+      <c r="S117" s="36">
+        <v>0</v>
+      </c>
+      <c r="T117" s="36">
+        <v>0</v>
+      </c>
+      <c r="U117" s="36">
+        <v>0</v>
+      </c>
+      <c r="V117" s="36">
+        <v>0</v>
+      </c>
+      <c r="W117" s="36">
+        <v>0</v>
+      </c>
+      <c r="X117" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z117" s="36">
+        <v>85200300</v>
+      </c>
+      <c r="AA117" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A118" s="5">
+        <v>95200500</v>
+      </c>
+      <c r="B118" s="5">
+        <v>4</v>
+      </c>
+      <c r="C118" s="5">
+        <v>7010</v>
+      </c>
+      <c r="D118" s="5">
+        <v>1</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G118" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H118" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="I118" s="36">
+        <v>0</v>
+      </c>
+      <c r="J118" s="36">
+        <v>0</v>
+      </c>
+      <c r="K118" s="36">
+        <v>0</v>
+      </c>
+      <c r="L118" s="36">
+        <v>0</v>
+      </c>
+      <c r="M118" s="36">
+        <v>0</v>
+      </c>
+      <c r="N118" s="36">
+        <v>0</v>
+      </c>
+      <c r="O118" s="36">
+        <v>0</v>
+      </c>
+      <c r="P118" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="36">
+        <v>0</v>
+      </c>
+      <c r="R118" s="36">
+        <v>0</v>
+      </c>
+      <c r="S118" s="36">
+        <v>0</v>
+      </c>
+      <c r="T118" s="36">
+        <v>0</v>
+      </c>
+      <c r="U118" s="36">
+        <v>0</v>
+      </c>
+      <c r="V118" s="36">
+        <v>0</v>
+      </c>
+      <c r="W118" s="36">
+        <v>0</v>
+      </c>
+      <c r="X118" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="36">
+        <v>85200500</v>
+      </c>
+      <c r="AA118" s="36">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9C549B-1C19-43BB-AC38-117E07DDA205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EE12D4-E1E2-4AE5-867C-62FA9F5B89F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EE12D4-E1E2-4AE5-867C-62FA9F5B89F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D22CA80-938D-4672-B899-A8A0772F71F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="319">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1393,6 +1393,18 @@
   <si>
     <t>雷击伤害</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹数量</t>
+  </si>
+  <si>
+    <t>冰弹伤害</t>
+  </si>
+  <si>
+    <t>冰弹范围</t>
+  </si>
+  <si>
+    <t>追加冰弹次数&amp;伤害</t>
   </si>
 </sst>
 </file>
@@ -2089,7 +2101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA118"/>
+  <dimension ref="A1:AA122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -11300,30 +11312,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="36">
-        <v>95100100</v>
-      </c>
-      <c r="B113" s="36">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A113" s="5">
+        <v>95000300</v>
+      </c>
+      <c r="B113" s="5">
         <v>4</v>
       </c>
-      <c r="C113" s="36">
-        <v>7007</v>
-      </c>
-      <c r="D113" s="36">
-        <v>1</v>
-      </c>
-      <c r="E113" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="F113" s="36" t="s">
-        <v>302</v>
+      <c r="C113" s="5">
+        <v>7011</v>
+      </c>
+      <c r="D113" s="5">
+        <v>1</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>315</v>
       </c>
       <c r="G113" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H113" s="36" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="I113" s="36">
         <v>0</v>
@@ -11377,36 +11389,36 @@
         <v>0</v>
       </c>
       <c r="Z113" s="36">
-        <v>85100100</v>
+        <v>85000300</v>
       </c>
       <c r="AA113" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="36">
-        <v>95100101</v>
-      </c>
-      <c r="B114" s="36">
-        <v>5</v>
-      </c>
-      <c r="C114" s="36">
-        <v>7008</v>
-      </c>
-      <c r="D114" s="36">
-        <v>1</v>
-      </c>
-      <c r="E114" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="F114" s="36" t="s">
-        <v>303</v>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A114" s="5">
+        <v>95000500</v>
+      </c>
+      <c r="B114" s="5">
+        <v>4</v>
+      </c>
+      <c r="C114" s="5">
+        <v>7012</v>
+      </c>
+      <c r="D114" s="5">
+        <v>1</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>316</v>
       </c>
       <c r="G114" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H114" s="36" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="I114" s="36">
         <v>0</v>
@@ -11421,7 +11433,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="36">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N114" s="36">
         <v>0</v>
@@ -11430,66 +11442,66 @@
         <v>0</v>
       </c>
       <c r="P114" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="36">
+        <v>0</v>
+      </c>
+      <c r="R114" s="36">
+        <v>0</v>
+      </c>
+      <c r="S114" s="36">
+        <v>0</v>
+      </c>
+      <c r="T114" s="36">
+        <v>0</v>
+      </c>
+      <c r="U114" s="36">
+        <v>0</v>
+      </c>
+      <c r="V114" s="36">
+        <v>0</v>
+      </c>
+      <c r="W114" s="36">
+        <v>0</v>
+      </c>
+      <c r="X114" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="36">
+        <v>85000500</v>
+      </c>
+      <c r="AA114" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A115" s="5">
+        <v>95000700</v>
+      </c>
+      <c r="B115" s="5">
         <v>4</v>
       </c>
-      <c r="Q114" s="36">
-        <v>2</v>
-      </c>
-      <c r="R114" s="36">
-        <v>10000</v>
-      </c>
-      <c r="S114" s="36">
-        <v>4</v>
-      </c>
-      <c r="T114" s="36">
-        <v>1</v>
-      </c>
-      <c r="U114" s="36">
-        <v>2</v>
-      </c>
-      <c r="V114" s="36">
-        <v>0</v>
-      </c>
-      <c r="W114" s="36">
-        <v>20000</v>
-      </c>
-      <c r="X114" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y114" s="36">
-        <v>15000</v>
-      </c>
-      <c r="Z114" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="36">
-        <v>95200100</v>
-      </c>
-      <c r="B115" s="36">
-        <v>4</v>
-      </c>
-      <c r="C115" s="36">
-        <v>7003</v>
-      </c>
-      <c r="D115" s="36">
-        <v>1</v>
-      </c>
-      <c r="E115" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="F115" s="36" t="s">
-        <v>299</v>
+      <c r="C115" s="5">
+        <v>7013</v>
+      </c>
+      <c r="D115" s="5">
+        <v>1</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>317</v>
       </c>
       <c r="G115" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H115" s="36" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="I115" s="36">
         <v>0</v>
@@ -11543,36 +11555,36 @@
         <v>0</v>
       </c>
       <c r="Z115" s="36">
-        <v>85200100</v>
+        <v>85000700</v>
       </c>
       <c r="AA115" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="36">
-        <v>95200101</v>
-      </c>
-      <c r="B116" s="36">
-        <v>5</v>
-      </c>
-      <c r="C116" s="36">
-        <v>7004</v>
-      </c>
-      <c r="D116" s="36">
-        <v>1</v>
-      </c>
-      <c r="E116" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="F116" s="36" t="s">
-        <v>298</v>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A116" s="5">
+        <v>95000900</v>
+      </c>
+      <c r="B116" s="5">
+        <v>4</v>
+      </c>
+      <c r="C116" s="5">
+        <v>7014</v>
+      </c>
+      <c r="D116" s="5">
+        <v>1</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>318</v>
       </c>
       <c r="G116" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H116" s="36" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="I116" s="36">
         <v>0</v>
@@ -11596,66 +11608,66 @@
         <v>0</v>
       </c>
       <c r="P116" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="36">
+        <v>0</v>
+      </c>
+      <c r="R116" s="36">
+        <v>0</v>
+      </c>
+      <c r="S116" s="36">
+        <v>0</v>
+      </c>
+      <c r="T116" s="36">
+        <v>0</v>
+      </c>
+      <c r="U116" s="36">
+        <v>0</v>
+      </c>
+      <c r="V116" s="36">
+        <v>0</v>
+      </c>
+      <c r="W116" s="36">
+        <v>0</v>
+      </c>
+      <c r="X116" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="36">
+        <v>85000900</v>
+      </c>
+      <c r="AA116" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A117" s="36">
+        <v>95100100</v>
+      </c>
+      <c r="B117" s="36">
         <v>4</v>
       </c>
-      <c r="Q116" s="36">
-        <v>2</v>
-      </c>
-      <c r="R116" s="36">
-        <v>4000</v>
-      </c>
-      <c r="S116" s="36">
-        <v>4</v>
-      </c>
-      <c r="T116" s="36">
-        <v>1</v>
-      </c>
-      <c r="U116" s="36">
-        <v>4</v>
-      </c>
-      <c r="V116" s="36">
-        <v>0</v>
-      </c>
-      <c r="W116" s="36">
-        <v>24000</v>
-      </c>
-      <c r="X116" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y116" s="36">
-        <v>15000</v>
-      </c>
-      <c r="Z116" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A117" s="5">
-        <v>95200300</v>
-      </c>
-      <c r="B117" s="5">
-        <v>4</v>
-      </c>
-      <c r="C117" s="5">
-        <v>7009</v>
-      </c>
-      <c r="D117" s="5">
-        <v>1</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>311</v>
+      <c r="C117" s="36">
+        <v>7007</v>
+      </c>
+      <c r="D117" s="36">
+        <v>1</v>
+      </c>
+      <c r="E117" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="F117" s="36" t="s">
+        <v>302</v>
       </c>
       <c r="G117" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H117" s="36" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="I117" s="36">
         <v>0</v>
@@ -11709,92 +11721,424 @@
         <v>0</v>
       </c>
       <c r="Z117" s="36">
-        <v>85200300</v>
+        <v>85100100</v>
       </c>
       <c r="AA117" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A118" s="5">
-        <v>95200500</v>
-      </c>
-      <c r="B118" s="5">
-        <v>4</v>
-      </c>
-      <c r="C118" s="5">
-        <v>7010</v>
-      </c>
-      <c r="D118" s="5">
-        <v>1</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>312</v>
+    <row r="118" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A118" s="36">
+        <v>95100101</v>
+      </c>
+      <c r="B118" s="36">
+        <v>5</v>
+      </c>
+      <c r="C118" s="36">
+        <v>7008</v>
+      </c>
+      <c r="D118" s="36">
+        <v>1</v>
+      </c>
+      <c r="E118" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="F118" s="36" t="s">
+        <v>303</v>
       </c>
       <c r="G118" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H118" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="I118" s="36">
+        <v>0</v>
+      </c>
+      <c r="J118" s="36">
+        <v>0</v>
+      </c>
+      <c r="K118" s="36">
+        <v>0</v>
+      </c>
+      <c r="L118" s="36">
+        <v>0</v>
+      </c>
+      <c r="M118" s="36">
+        <v>1000</v>
+      </c>
+      <c r="N118" s="36">
+        <v>0</v>
+      </c>
+      <c r="O118" s="36">
+        <v>0</v>
+      </c>
+      <c r="P118" s="36">
+        <v>4</v>
+      </c>
+      <c r="Q118" s="36">
+        <v>2</v>
+      </c>
+      <c r="R118" s="36">
+        <v>10000</v>
+      </c>
+      <c r="S118" s="36">
+        <v>4</v>
+      </c>
+      <c r="T118" s="36">
+        <v>1</v>
+      </c>
+      <c r="U118" s="36">
+        <v>2</v>
+      </c>
+      <c r="V118" s="36">
+        <v>0</v>
+      </c>
+      <c r="W118" s="36">
+        <v>20000</v>
+      </c>
+      <c r="X118" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="36">
+        <v>15000</v>
+      </c>
+      <c r="Z118" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="36">
+        <v>95200100</v>
+      </c>
+      <c r="B119" s="36">
+        <v>4</v>
+      </c>
+      <c r="C119" s="36">
+        <v>7003</v>
+      </c>
+      <c r="D119" s="36">
+        <v>1</v>
+      </c>
+      <c r="E119" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="F119" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="G119" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H119" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="I119" s="36">
+        <v>0</v>
+      </c>
+      <c r="J119" s="36">
+        <v>0</v>
+      </c>
+      <c r="K119" s="36">
+        <v>0</v>
+      </c>
+      <c r="L119" s="36">
+        <v>0</v>
+      </c>
+      <c r="M119" s="36">
+        <v>0</v>
+      </c>
+      <c r="N119" s="36">
+        <v>0</v>
+      </c>
+      <c r="O119" s="36">
+        <v>0</v>
+      </c>
+      <c r="P119" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="36">
+        <v>0</v>
+      </c>
+      <c r="R119" s="36">
+        <v>0</v>
+      </c>
+      <c r="S119" s="36">
+        <v>0</v>
+      </c>
+      <c r="T119" s="36">
+        <v>0</v>
+      </c>
+      <c r="U119" s="36">
+        <v>0</v>
+      </c>
+      <c r="V119" s="36">
+        <v>0</v>
+      </c>
+      <c r="W119" s="36">
+        <v>0</v>
+      </c>
+      <c r="X119" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="36">
+        <v>85200100</v>
+      </c>
+      <c r="AA119" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="36">
+        <v>95200101</v>
+      </c>
+      <c r="B120" s="36">
+        <v>5</v>
+      </c>
+      <c r="C120" s="36">
+        <v>7004</v>
+      </c>
+      <c r="D120" s="36">
+        <v>1</v>
+      </c>
+      <c r="E120" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="F120" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="G120" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H120" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="I120" s="36">
+        <v>0</v>
+      </c>
+      <c r="J120" s="36">
+        <v>0</v>
+      </c>
+      <c r="K120" s="36">
+        <v>0</v>
+      </c>
+      <c r="L120" s="36">
+        <v>0</v>
+      </c>
+      <c r="M120" s="36">
+        <v>0</v>
+      </c>
+      <c r="N120" s="36">
+        <v>0</v>
+      </c>
+      <c r="O120" s="36">
+        <v>0</v>
+      </c>
+      <c r="P120" s="36">
+        <v>4</v>
+      </c>
+      <c r="Q120" s="36">
+        <v>2</v>
+      </c>
+      <c r="R120" s="36">
+        <v>4000</v>
+      </c>
+      <c r="S120" s="36">
+        <v>4</v>
+      </c>
+      <c r="T120" s="36">
+        <v>1</v>
+      </c>
+      <c r="U120" s="36">
+        <v>4</v>
+      </c>
+      <c r="V120" s="36">
+        <v>0</v>
+      </c>
+      <c r="W120" s="36">
+        <v>24000</v>
+      </c>
+      <c r="X120" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y120" s="36">
+        <v>15000</v>
+      </c>
+      <c r="Z120" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A121" s="5">
+        <v>95200300</v>
+      </c>
+      <c r="B121" s="5">
+        <v>4</v>
+      </c>
+      <c r="C121" s="5">
+        <v>7009</v>
+      </c>
+      <c r="D121" s="5">
+        <v>1</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G121" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H121" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="I121" s="36">
+        <v>0</v>
+      </c>
+      <c r="J121" s="36">
+        <v>0</v>
+      </c>
+      <c r="K121" s="36">
+        <v>0</v>
+      </c>
+      <c r="L121" s="36">
+        <v>0</v>
+      </c>
+      <c r="M121" s="36">
+        <v>0</v>
+      </c>
+      <c r="N121" s="36">
+        <v>0</v>
+      </c>
+      <c r="O121" s="36">
+        <v>0</v>
+      </c>
+      <c r="P121" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="36">
+        <v>0</v>
+      </c>
+      <c r="R121" s="36">
+        <v>0</v>
+      </c>
+      <c r="S121" s="36">
+        <v>0</v>
+      </c>
+      <c r="T121" s="36">
+        <v>0</v>
+      </c>
+      <c r="U121" s="36">
+        <v>0</v>
+      </c>
+      <c r="V121" s="36">
+        <v>0</v>
+      </c>
+      <c r="W121" s="36">
+        <v>0</v>
+      </c>
+      <c r="X121" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="36">
+        <v>85200300</v>
+      </c>
+      <c r="AA121" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A122" s="5">
+        <v>95200500</v>
+      </c>
+      <c r="B122" s="5">
+        <v>4</v>
+      </c>
+      <c r="C122" s="5">
+        <v>7010</v>
+      </c>
+      <c r="D122" s="5">
+        <v>1</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G122" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H122" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="I118" s="36">
-        <v>0</v>
-      </c>
-      <c r="J118" s="36">
-        <v>0</v>
-      </c>
-      <c r="K118" s="36">
-        <v>0</v>
-      </c>
-      <c r="L118" s="36">
-        <v>0</v>
-      </c>
-      <c r="M118" s="36">
-        <v>0</v>
-      </c>
-      <c r="N118" s="36">
-        <v>0</v>
-      </c>
-      <c r="O118" s="36">
-        <v>0</v>
-      </c>
-      <c r="P118" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="36">
-        <v>0</v>
-      </c>
-      <c r="R118" s="36">
-        <v>0</v>
-      </c>
-      <c r="S118" s="36">
-        <v>0</v>
-      </c>
-      <c r="T118" s="36">
-        <v>0</v>
-      </c>
-      <c r="U118" s="36">
-        <v>0</v>
-      </c>
-      <c r="V118" s="36">
-        <v>0</v>
-      </c>
-      <c r="W118" s="36">
-        <v>0</v>
-      </c>
-      <c r="X118" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y118" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z118" s="36">
+      <c r="I122" s="36">
+        <v>0</v>
+      </c>
+      <c r="J122" s="36">
+        <v>0</v>
+      </c>
+      <c r="K122" s="36">
+        <v>0</v>
+      </c>
+      <c r="L122" s="36">
+        <v>0</v>
+      </c>
+      <c r="M122" s="36">
+        <v>0</v>
+      </c>
+      <c r="N122" s="36">
+        <v>0</v>
+      </c>
+      <c r="O122" s="36">
+        <v>0</v>
+      </c>
+      <c r="P122" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="36">
+        <v>0</v>
+      </c>
+      <c r="R122" s="36">
+        <v>0</v>
+      </c>
+      <c r="S122" s="36">
+        <v>0</v>
+      </c>
+      <c r="T122" s="36">
+        <v>0</v>
+      </c>
+      <c r="U122" s="36">
+        <v>0</v>
+      </c>
+      <c r="V122" s="36">
+        <v>0</v>
+      </c>
+      <c r="W122" s="36">
+        <v>0</v>
+      </c>
+      <c r="X122" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y122" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="36">
         <v>85200500</v>
       </c>
-      <c r="AA118" s="36">
+      <c r="AA122" s="36">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0751FD-ED1D-4531-86DC-4326E60B5284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F794EE41-58B6-41C1-AFEE-F806CFABB97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$140</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7273,7 +7273,7 @@
         <v>54090051</v>
       </c>
       <c r="B64" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" s="23">
         <v>5409</v>
@@ -7356,7 +7356,7 @@
         <v>54110051</v>
       </c>
       <c r="B65" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" s="23">
         <v>5411</v>
@@ -7439,7 +7439,7 @@
         <v>54130051</v>
       </c>
       <c r="B66" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" s="23">
         <v>5413</v>
@@ -7522,7 +7522,7 @@
         <v>54150051</v>
       </c>
       <c r="B67" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" s="23">
         <v>5415</v>
@@ -7605,7 +7605,7 @@
         <v>54170051</v>
       </c>
       <c r="B68" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" s="23">
         <v>5417</v>
@@ -7688,7 +7688,7 @@
         <v>54190051</v>
       </c>
       <c r="B69" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69" s="23">
         <v>5419</v>
@@ -7771,7 +7771,7 @@
         <v>54210051</v>
       </c>
       <c r="B70" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C70" s="23">
         <v>5421</v>
@@ -7854,7 +7854,7 @@
         <v>54230051</v>
       </c>
       <c r="B71" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" s="23">
         <v>5423</v>
@@ -7937,7 +7937,7 @@
         <v>54250051</v>
       </c>
       <c r="B72" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72" s="23">
         <v>5425</v>
@@ -13657,7 +13657,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F794EE41-58B6-41C1-AFEE-F806CFABB97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E9A6CE-52C5-4EA0-8796-22BB1F70CDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1404,9 +1404,6 @@
     <t>冰弹范围</t>
   </si>
   <si>
-    <t>追加冰弹次数&amp;伤害</t>
-  </si>
-  <si>
     <t>骷髅怪等级1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1424,6 +1421,10 @@
   </si>
   <si>
     <t>僵尸等级2精英</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加冰弹次数</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -4314,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>163</v>
@@ -4397,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>163</v>
@@ -4480,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>163</v>
@@ -4563,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>163</v>
@@ -4646,7 +4647,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>163</v>
@@ -12737,7 +12738,7 @@
         <v>0</v>
       </c>
       <c r="Z129" s="36">
-        <v>85001000</v>
+        <v>85000100</v>
       </c>
       <c r="AA129" s="36">
         <v>0</v>
@@ -12817,10 +12818,10 @@
         <v>0</v>
       </c>
       <c r="Y130" s="36">
-        <v>15000</v>
+        <v>21000</v>
       </c>
       <c r="Z130" s="36">
-        <v>0</v>
+        <v>85001100</v>
       </c>
       <c r="AA130" s="36">
         <v>0</v>
@@ -13089,16 +13090,16 @@
         <v>1</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G134" s="37" t="s">
         <v>89</v>
       </c>
       <c r="H134" s="36" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="I134" s="36">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B327493B-1F09-4D7C-9370-99B371E2890B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA59FBEB-529D-43FE-899F-04D499B810A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="337">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1487,6 +1487,9 @@
   <si>
     <t>冰弹命中后产生冰爆</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击概率附加麻痹</t>
   </si>
 </sst>
 </file>
@@ -2183,7 +2186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AF141"/>
+  <dimension ref="A1:AF142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -15904,6 +15907,104 @@
         <v>0</v>
       </c>
     </row>
+    <row r="142" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A142" s="5">
+        <v>95200700</v>
+      </c>
+      <c r="B142" s="5">
+        <v>4</v>
+      </c>
+      <c r="C142" s="5">
+        <v>0</v>
+      </c>
+      <c r="D142" s="5">
+        <v>7016</v>
+      </c>
+      <c r="E142" s="5">
+        <v>1</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H142" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I142" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J142" s="36">
+        <v>0</v>
+      </c>
+      <c r="K142" s="36">
+        <v>0</v>
+      </c>
+      <c r="L142" s="36">
+        <v>0</v>
+      </c>
+      <c r="M142" s="36">
+        <v>0</v>
+      </c>
+      <c r="N142" s="36">
+        <v>0</v>
+      </c>
+      <c r="O142" s="36">
+        <v>0</v>
+      </c>
+      <c r="P142" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="36">
+        <v>0</v>
+      </c>
+      <c r="R142" s="36">
+        <v>0</v>
+      </c>
+      <c r="S142" s="36">
+        <v>0</v>
+      </c>
+      <c r="T142" s="36">
+        <v>0</v>
+      </c>
+      <c r="U142" s="36">
+        <v>0</v>
+      </c>
+      <c r="V142" s="36">
+        <v>0</v>
+      </c>
+      <c r="W142" s="36">
+        <v>0</v>
+      </c>
+      <c r="X142" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="36">
+        <v>85200700</v>
+      </c>
+      <c r="AB142" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF142" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA59FBEB-529D-43FE-899F-04D499B810A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD62C603-F29A-4B48-B424-9C001412A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="341">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1490,6 +1490,18 @@
   </si>
   <si>
     <t>雷击概率附加麻痹</t>
+  </si>
+  <si>
+    <t>陨石额外范围</t>
+  </si>
+  <si>
+    <t>陨石伤害</t>
+  </si>
+  <si>
+    <t>陨石数量</t>
+  </si>
+  <si>
+    <t>陨石落地后产生冲击波</t>
   </si>
 </sst>
 </file>
@@ -2186,7 +2198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AF142"/>
+  <dimension ref="A1:AF146"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -14643,8 +14655,8 @@
       <c r="C129" s="36">
         <v>0</v>
       </c>
-      <c r="D129" s="36">
-        <v>7005</v>
+      <c r="D129" s="5">
+        <v>7003</v>
       </c>
       <c r="E129" s="36">
         <v>1</v>
@@ -14741,8 +14753,8 @@
       <c r="C130" s="36">
         <v>1</v>
       </c>
-      <c r="D130" s="36">
-        <v>7006</v>
+      <c r="D130" s="5">
+        <v>7004</v>
       </c>
       <c r="E130" s="36">
         <v>1</v>
@@ -14840,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="5">
-        <v>7011</v>
+        <v>7005</v>
       </c>
       <c r="E131" s="5">
         <v>1</v>
@@ -14938,7 +14950,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="5">
-        <v>7012</v>
+        <v>7006</v>
       </c>
       <c r="E132" s="5">
         <v>1</v>
@@ -15036,7 +15048,7 @@
         <v>0</v>
       </c>
       <c r="D133" s="5">
-        <v>7013</v>
+        <v>7007</v>
       </c>
       <c r="E133" s="5">
         <v>1</v>
@@ -15134,7 +15146,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="5">
-        <v>7014</v>
+        <v>7008</v>
       </c>
       <c r="E134" s="5">
         <v>1</v>
@@ -15232,7 +15244,7 @@
         <v>0</v>
       </c>
       <c r="D135" s="5">
-        <v>7015</v>
+        <v>7009</v>
       </c>
       <c r="E135" s="5">
         <v>1</v>
@@ -15329,8 +15341,8 @@
       <c r="C136" s="36">
         <v>0</v>
       </c>
-      <c r="D136" s="36">
-        <v>7007</v>
+      <c r="D136" s="5">
+        <v>7010</v>
       </c>
       <c r="E136" s="36">
         <v>1</v>
@@ -15427,8 +15439,8 @@
       <c r="C137" s="36">
         <v>1</v>
       </c>
-      <c r="D137" s="36">
-        <v>7008</v>
+      <c r="D137" s="5">
+        <v>7011</v>
       </c>
       <c r="E137" s="36">
         <v>1</v>
@@ -15494,7 +15506,7 @@
         <v>0</v>
       </c>
       <c r="Z137" s="36">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="AA137" s="36">
         <v>0</v>
@@ -15515,33 +15527,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A138" s="36">
-        <v>95200100</v>
-      </c>
-      <c r="B138" s="36">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A138" s="5">
+        <v>95100300</v>
+      </c>
+      <c r="B138" s="5">
         <v>4</v>
       </c>
-      <c r="C138" s="36">
-        <v>0</v>
-      </c>
-      <c r="D138" s="36">
-        <v>7003</v>
-      </c>
-      <c r="E138" s="36">
-        <v>1</v>
-      </c>
-      <c r="F138" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="G138" s="36" t="s">
-        <v>299</v>
+      <c r="C138" s="5">
+        <v>0</v>
+      </c>
+      <c r="D138" s="5">
+        <v>7012</v>
+      </c>
+      <c r="E138" s="5">
+        <v>1</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>337</v>
       </c>
       <c r="H138" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I138" s="36" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="J138" s="36">
         <v>0</v>
@@ -15595,7 +15607,7 @@
         <v>0</v>
       </c>
       <c r="AA138" s="36">
-        <v>85200100</v>
+        <v>85100300</v>
       </c>
       <c r="AB138" s="36">
         <v>0</v>
@@ -15613,33 +15625,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A139" s="36">
-        <v>95200101</v>
-      </c>
-      <c r="B139" s="36">
-        <v>5</v>
-      </c>
-      <c r="C139" s="36">
-        <v>1</v>
-      </c>
-      <c r="D139" s="36">
-        <v>7004</v>
-      </c>
-      <c r="E139" s="36">
-        <v>1</v>
-      </c>
-      <c r="F139" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="G139" s="36" t="s">
-        <v>298</v>
+    <row r="139" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A139" s="5">
+        <v>95100500</v>
+      </c>
+      <c r="B139" s="5">
+        <v>4</v>
+      </c>
+      <c r="C139" s="5">
+        <v>0</v>
+      </c>
+      <c r="D139" s="5">
+        <v>7013</v>
+      </c>
+      <c r="E139" s="5">
+        <v>1</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="H139" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I139" s="36" t="s">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="J139" s="36">
         <v>0</v>
@@ -15648,7 +15660,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="36">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="M139" s="36">
         <v>0</v>
@@ -15663,37 +15675,37 @@
         <v>0</v>
       </c>
       <c r="Q139" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R139" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S139" s="36">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T139" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U139" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V139" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W139" s="36">
         <v>0</v>
       </c>
       <c r="X139" s="36">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="Y139" s="36">
         <v>0</v>
       </c>
       <c r="Z139" s="36">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="36">
-        <v>0</v>
+        <v>85100500</v>
       </c>
       <c r="AB139" s="36">
         <v>0</v>
@@ -15713,7 +15725,7 @@
     </row>
     <row r="140" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A140" s="5">
-        <v>95200300</v>
+        <v>95100700</v>
       </c>
       <c r="B140" s="5">
         <v>4</v>
@@ -15722,22 +15734,22 @@
         <v>0</v>
       </c>
       <c r="D140" s="5">
-        <v>7009</v>
+        <v>7014</v>
       </c>
       <c r="E140" s="5">
         <v>1</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="H140" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I140" s="36" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="J140" s="36">
         <v>0</v>
@@ -15791,7 +15803,7 @@
         <v>0</v>
       </c>
       <c r="AA140" s="36">
-        <v>85200300</v>
+        <v>85100700</v>
       </c>
       <c r="AB140" s="36">
         <v>0</v>
@@ -15811,7 +15823,7 @@
     </row>
     <row r="141" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A141" s="5">
-        <v>95200500</v>
+        <v>95100900</v>
       </c>
       <c r="B141" s="5">
         <v>4</v>
@@ -15820,22 +15832,22 @@
         <v>0</v>
       </c>
       <c r="D141" s="5">
-        <v>7010</v>
+        <v>7015</v>
       </c>
       <c r="E141" s="5">
         <v>1</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="H141" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I141" s="36" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="J141" s="36">
         <v>0</v>
@@ -15889,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AA141" s="36">
-        <v>85200500</v>
+        <v>85100900</v>
       </c>
       <c r="AB141" s="36">
         <v>0</v>
@@ -15907,101 +15919,493 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A142" s="5">
-        <v>95200700</v>
-      </c>
-      <c r="B142" s="5">
+    <row r="142" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="36">
+        <v>95200100</v>
+      </c>
+      <c r="B142" s="36">
         <v>4</v>
       </c>
-      <c r="C142" s="5">
+      <c r="C142" s="36">
         <v>0</v>
       </c>
       <c r="D142" s="5">
         <v>7016</v>
       </c>
-      <c r="E142" s="5">
-        <v>1</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>336</v>
+      <c r="E142" s="36">
+        <v>1</v>
+      </c>
+      <c r="F142" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="G142" s="36" t="s">
+        <v>299</v>
       </c>
       <c r="H142" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I142" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="J142" s="36">
+        <v>0</v>
+      </c>
+      <c r="K142" s="36">
+        <v>0</v>
+      </c>
+      <c r="L142" s="36">
+        <v>0</v>
+      </c>
+      <c r="M142" s="36">
+        <v>0</v>
+      </c>
+      <c r="N142" s="36">
+        <v>0</v>
+      </c>
+      <c r="O142" s="36">
+        <v>0</v>
+      </c>
+      <c r="P142" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="36">
+        <v>0</v>
+      </c>
+      <c r="R142" s="36">
+        <v>0</v>
+      </c>
+      <c r="S142" s="36">
+        <v>0</v>
+      </c>
+      <c r="T142" s="36">
+        <v>0</v>
+      </c>
+      <c r="U142" s="36">
+        <v>0</v>
+      </c>
+      <c r="V142" s="36">
+        <v>0</v>
+      </c>
+      <c r="W142" s="36">
+        <v>0</v>
+      </c>
+      <c r="X142" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="36">
+        <v>85200100</v>
+      </c>
+      <c r="AB142" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF142" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A143" s="36">
+        <v>95200101</v>
+      </c>
+      <c r="B143" s="36">
+        <v>5</v>
+      </c>
+      <c r="C143" s="36">
+        <v>1</v>
+      </c>
+      <c r="D143" s="5">
+        <v>7017</v>
+      </c>
+      <c r="E143" s="36">
+        <v>1</v>
+      </c>
+      <c r="F143" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="G143" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="H143" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I143" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="J143" s="36">
+        <v>0</v>
+      </c>
+      <c r="K143" s="36">
+        <v>0</v>
+      </c>
+      <c r="L143" s="36">
+        <v>6000</v>
+      </c>
+      <c r="M143" s="36">
+        <v>0</v>
+      </c>
+      <c r="N143" s="36">
+        <v>0</v>
+      </c>
+      <c r="O143" s="36">
+        <v>0</v>
+      </c>
+      <c r="P143" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="36">
+        <v>4</v>
+      </c>
+      <c r="R143" s="36">
+        <v>2</v>
+      </c>
+      <c r="S143" s="36">
+        <v>5000</v>
+      </c>
+      <c r="T143" s="36">
+        <v>4</v>
+      </c>
+      <c r="U143" s="36">
+        <v>1</v>
+      </c>
+      <c r="V143" s="36">
+        <v>4</v>
+      </c>
+      <c r="W143" s="36">
+        <v>0</v>
+      </c>
+      <c r="X143" s="36">
+        <v>24000</v>
+      </c>
+      <c r="Y143" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="36">
+        <v>24000</v>
+      </c>
+      <c r="AA143" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB143" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF143" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A144" s="5">
+        <v>95200300</v>
+      </c>
+      <c r="B144" s="5">
+        <v>4</v>
+      </c>
+      <c r="C144" s="5">
+        <v>0</v>
+      </c>
+      <c r="D144" s="5">
+        <v>7018</v>
+      </c>
+      <c r="E144" s="5">
+        <v>1</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H144" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I144" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="J144" s="36">
+        <v>0</v>
+      </c>
+      <c r="K144" s="36">
+        <v>0</v>
+      </c>
+      <c r="L144" s="36">
+        <v>0</v>
+      </c>
+      <c r="M144" s="36">
+        <v>0</v>
+      </c>
+      <c r="N144" s="36">
+        <v>0</v>
+      </c>
+      <c r="O144" s="36">
+        <v>0</v>
+      </c>
+      <c r="P144" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="36">
+        <v>0</v>
+      </c>
+      <c r="R144" s="36">
+        <v>0</v>
+      </c>
+      <c r="S144" s="36">
+        <v>0</v>
+      </c>
+      <c r="T144" s="36">
+        <v>0</v>
+      </c>
+      <c r="U144" s="36">
+        <v>0</v>
+      </c>
+      <c r="V144" s="36">
+        <v>0</v>
+      </c>
+      <c r="W144" s="36">
+        <v>0</v>
+      </c>
+      <c r="X144" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="36">
+        <v>85200300</v>
+      </c>
+      <c r="AB144" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD144" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE144" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF144" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A145" s="5">
+        <v>95200500</v>
+      </c>
+      <c r="B145" s="5">
+        <v>4</v>
+      </c>
+      <c r="C145" s="5">
+        <v>0</v>
+      </c>
+      <c r="D145" s="5">
+        <v>7019</v>
+      </c>
+      <c r="E145" s="5">
+        <v>1</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H145" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I145" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="J145" s="36">
+        <v>0</v>
+      </c>
+      <c r="K145" s="36">
+        <v>0</v>
+      </c>
+      <c r="L145" s="36">
+        <v>0</v>
+      </c>
+      <c r="M145" s="36">
+        <v>0</v>
+      </c>
+      <c r="N145" s="36">
+        <v>0</v>
+      </c>
+      <c r="O145" s="36">
+        <v>0</v>
+      </c>
+      <c r="P145" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="36">
+        <v>0</v>
+      </c>
+      <c r="R145" s="36">
+        <v>0</v>
+      </c>
+      <c r="S145" s="36">
+        <v>0</v>
+      </c>
+      <c r="T145" s="36">
+        <v>0</v>
+      </c>
+      <c r="U145" s="36">
+        <v>0</v>
+      </c>
+      <c r="V145" s="36">
+        <v>0</v>
+      </c>
+      <c r="W145" s="36">
+        <v>0</v>
+      </c>
+      <c r="X145" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="36">
+        <v>85200500</v>
+      </c>
+      <c r="AB145" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF145" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A146" s="5">
+        <v>95200700</v>
+      </c>
+      <c r="B146" s="5">
+        <v>4</v>
+      </c>
+      <c r="C146" s="5">
+        <v>0</v>
+      </c>
+      <c r="D146" s="5">
+        <v>7020</v>
+      </c>
+      <c r="E146" s="5">
+        <v>1</v>
+      </c>
+      <c r="F146" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="J142" s="36">
-        <v>0</v>
-      </c>
-      <c r="K142" s="36">
-        <v>0</v>
-      </c>
-      <c r="L142" s="36">
-        <v>0</v>
-      </c>
-      <c r="M142" s="36">
-        <v>0</v>
-      </c>
-      <c r="N142" s="36">
-        <v>0</v>
-      </c>
-      <c r="O142" s="36">
-        <v>0</v>
-      </c>
-      <c r="P142" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="36">
-        <v>0</v>
-      </c>
-      <c r="R142" s="36">
-        <v>0</v>
-      </c>
-      <c r="S142" s="36">
-        <v>0</v>
-      </c>
-      <c r="T142" s="36">
-        <v>0</v>
-      </c>
-      <c r="U142" s="36">
-        <v>0</v>
-      </c>
-      <c r="V142" s="36">
-        <v>0</v>
-      </c>
-      <c r="W142" s="36">
-        <v>0</v>
-      </c>
-      <c r="X142" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y142" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z142" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA142" s="36">
+      <c r="G146" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H146" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I146" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J146" s="36">
+        <v>0</v>
+      </c>
+      <c r="K146" s="36">
+        <v>0</v>
+      </c>
+      <c r="L146" s="36">
+        <v>0</v>
+      </c>
+      <c r="M146" s="36">
+        <v>0</v>
+      </c>
+      <c r="N146" s="36">
+        <v>0</v>
+      </c>
+      <c r="O146" s="36">
+        <v>0</v>
+      </c>
+      <c r="P146" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="36">
+        <v>0</v>
+      </c>
+      <c r="R146" s="36">
+        <v>0</v>
+      </c>
+      <c r="S146" s="36">
+        <v>0</v>
+      </c>
+      <c r="T146" s="36">
+        <v>0</v>
+      </c>
+      <c r="U146" s="36">
+        <v>0</v>
+      </c>
+      <c r="V146" s="36">
+        <v>0</v>
+      </c>
+      <c r="W146" s="36">
+        <v>0</v>
+      </c>
+      <c r="X146" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="36">
         <v>85200700</v>
       </c>
-      <c r="AB142" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC142" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD142" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE142" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF142" s="5">
+      <c r="AB146" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="5">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD62C603-F29A-4B48-B424-9C001412A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2583D073-4AA5-4CC2-B5C6-B8DF55D66DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$147</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="346">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1502,6 +1502,23 @@
   </si>
   <si>
     <t>陨石落地后产生冲击波</t>
+  </si>
+  <si>
+    <t>冰弹CD</t>
+  </si>
+  <si>
+    <t>冰弹CD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石CD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击CD</t>
+  </si>
+  <si>
+    <t>普攻伤害</t>
   </si>
 </sst>
 </file>
@@ -2198,7 +2215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AF146"/>
+  <dimension ref="A1:AF150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -14811,7 +14828,7 @@
         <v>1</v>
       </c>
       <c r="W130" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X130" s="36">
         <v>21000</v>
@@ -15295,13 +15312,13 @@
         <v>0</v>
       </c>
       <c r="U135" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V135" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X135" s="36">
         <v>0</v>
@@ -15331,33 +15348,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A136" s="36">
-        <v>95100100</v>
-      </c>
-      <c r="B136" s="36">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A136" s="5">
+        <v>95020300</v>
+      </c>
+      <c r="B136" s="5">
         <v>4</v>
       </c>
-      <c r="C136" s="36">
+      <c r="C136" s="5">
         <v>0</v>
       </c>
       <c r="D136" s="5">
         <v>7010</v>
       </c>
-      <c r="E136" s="36">
-        <v>1</v>
-      </c>
-      <c r="F136" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="G136" s="36" t="s">
-        <v>302</v>
+      <c r="E136" s="5">
+        <v>1</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="H136" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I136" s="36" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="J136" s="36">
         <v>0</v>
@@ -15411,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="AA136" s="36">
-        <v>85100100</v>
+        <v>85020300</v>
       </c>
       <c r="AB136" s="36">
         <v>0</v>
@@ -15431,13 +15448,13 @@
     </row>
     <row r="137" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A137" s="36">
-        <v>95100101</v>
+        <v>95100100</v>
       </c>
       <c r="B137" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C137" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D137" s="5">
         <v>7011</v>
@@ -15446,16 +15463,16 @@
         <v>1</v>
       </c>
       <c r="F137" s="36" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G137" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H137" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I137" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J137" s="36">
         <v>0</v>
@@ -15464,13 +15481,13 @@
         <v>0</v>
       </c>
       <c r="L137" s="36">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M137" s="36">
         <v>0</v>
       </c>
       <c r="N137" s="36">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="O137" s="36">
         <v>0</v>
@@ -15479,37 +15496,37 @@
         <v>0</v>
       </c>
       <c r="Q137" s="36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R137" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S137" s="36">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="T137" s="36">
         <v>0</v>
       </c>
       <c r="U137" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V137" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W137" s="36">
         <v>0</v>
       </c>
       <c r="X137" s="36">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="Y137" s="36">
         <v>0</v>
       </c>
       <c r="Z137" s="36">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AA137" s="36">
-        <v>0</v>
+        <v>85100100</v>
       </c>
       <c r="AB137" s="36">
         <v>0</v>
@@ -15527,33 +15544,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A138" s="5">
-        <v>95100300</v>
-      </c>
-      <c r="B138" s="5">
-        <v>4</v>
-      </c>
-      <c r="C138" s="5">
-        <v>0</v>
+    <row r="138" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="36">
+        <v>95100101</v>
+      </c>
+      <c r="B138" s="36">
+        <v>5</v>
+      </c>
+      <c r="C138" s="36">
+        <v>1</v>
       </c>
       <c r="D138" s="5">
         <v>7012</v>
       </c>
-      <c r="E138" s="5">
-        <v>1</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G138" s="5" t="s">
-        <v>337</v>
+      <c r="E138" s="36">
+        <v>1</v>
+      </c>
+      <c r="F138" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="G138" s="36" t="s">
+        <v>303</v>
       </c>
       <c r="H138" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I138" s="36" t="s">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="J138" s="36">
         <v>0</v>
@@ -15562,13 +15579,13 @@
         <v>0</v>
       </c>
       <c r="L138" s="36">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="M138" s="36">
         <v>0</v>
       </c>
       <c r="N138" s="36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O138" s="36">
         <v>0</v>
@@ -15577,37 +15594,37 @@
         <v>0</v>
       </c>
       <c r="Q138" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R138" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S138" s="36">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="T138" s="36">
         <v>0</v>
       </c>
       <c r="U138" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V138" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W138" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X138" s="36">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Y138" s="36">
         <v>0</v>
       </c>
       <c r="Z138" s="36">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AA138" s="36">
-        <v>85100300</v>
+        <v>0</v>
       </c>
       <c r="AB138" s="36">
         <v>0</v>
@@ -15627,7 +15644,7 @@
     </row>
     <row r="139" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A139" s="5">
-        <v>95100500</v>
+        <v>95100300</v>
       </c>
       <c r="B139" s="5">
         <v>4</v>
@@ -15642,16 +15659,16 @@
         <v>1</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H139" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I139" s="36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J139" s="36">
         <v>0</v>
@@ -15705,7 +15722,7 @@
         <v>0</v>
       </c>
       <c r="AA139" s="36">
-        <v>85100500</v>
+        <v>85100300</v>
       </c>
       <c r="AB139" s="36">
         <v>0</v>
@@ -15725,7 +15742,7 @@
     </row>
     <row r="140" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A140" s="5">
-        <v>95100700</v>
+        <v>95100500</v>
       </c>
       <c r="B140" s="5">
         <v>4</v>
@@ -15740,16 +15757,16 @@
         <v>1</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H140" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I140" s="36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J140" s="36">
         <v>0</v>
@@ -15803,7 +15820,7 @@
         <v>0</v>
       </c>
       <c r="AA140" s="36">
-        <v>85100700</v>
+        <v>85100500</v>
       </c>
       <c r="AB140" s="36">
         <v>0</v>
@@ -15823,7 +15840,7 @@
     </row>
     <row r="141" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A141" s="5">
-        <v>95100900</v>
+        <v>95100700</v>
       </c>
       <c r="B141" s="5">
         <v>4</v>
@@ -15838,16 +15855,16 @@
         <v>1</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H141" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I141" s="36" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J141" s="36">
         <v>0</v>
@@ -15901,7 +15918,7 @@
         <v>0</v>
       </c>
       <c r="AA141" s="36">
-        <v>85100900</v>
+        <v>85100700</v>
       </c>
       <c r="AB141" s="36">
         <v>0</v>
@@ -15919,33 +15936,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="36">
-        <v>95200100</v>
-      </c>
-      <c r="B142" s="36">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A142" s="5">
+        <v>95100900</v>
+      </c>
+      <c r="B142" s="5">
         <v>4</v>
       </c>
-      <c r="C142" s="36">
+      <c r="C142" s="5">
         <v>0</v>
       </c>
       <c r="D142" s="5">
         <v>7016</v>
       </c>
-      <c r="E142" s="36">
-        <v>1</v>
-      </c>
-      <c r="F142" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="G142" s="36" t="s">
-        <v>299</v>
+      <c r="E142" s="5">
+        <v>1</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="H142" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I142" s="36" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="J142" s="36">
         <v>0</v>
@@ -15981,13 +15998,13 @@
         <v>0</v>
       </c>
       <c r="U142" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V142" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W142" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X142" s="36">
         <v>0</v>
@@ -15999,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="AA142" s="36">
-        <v>85200100</v>
+        <v>85100900</v>
       </c>
       <c r="AB142" s="36">
         <v>0</v>
@@ -16017,33 +16034,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A143" s="36">
-        <v>95200101</v>
-      </c>
-      <c r="B143" s="36">
-        <v>5</v>
-      </c>
-      <c r="C143" s="36">
-        <v>1</v>
+    <row r="143" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A143" s="5">
+        <v>95120300</v>
+      </c>
+      <c r="B143" s="5">
+        <v>4</v>
+      </c>
+      <c r="C143" s="5">
+        <v>0</v>
       </c>
       <c r="D143" s="5">
         <v>7017</v>
       </c>
-      <c r="E143" s="36">
-        <v>1</v>
-      </c>
-      <c r="F143" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="G143" s="36" t="s">
-        <v>298</v>
+      <c r="E143" s="5">
+        <v>1</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>343</v>
       </c>
       <c r="H143" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I143" s="36" t="s">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="J143" s="36">
         <v>0</v>
@@ -16052,7 +16069,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="36">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="M143" s="36">
         <v>0</v>
@@ -16067,81 +16084,81 @@
         <v>0</v>
       </c>
       <c r="Q143" s="36">
+        <v>0</v>
+      </c>
+      <c r="R143" s="36">
+        <v>0</v>
+      </c>
+      <c r="S143" s="36">
+        <v>0</v>
+      </c>
+      <c r="T143" s="36">
+        <v>0</v>
+      </c>
+      <c r="U143" s="36">
+        <v>0</v>
+      </c>
+      <c r="V143" s="36">
+        <v>0</v>
+      </c>
+      <c r="W143" s="36">
+        <v>0</v>
+      </c>
+      <c r="X143" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y143" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="36">
+        <v>85120300</v>
+      </c>
+      <c r="AB143" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF143" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A144" s="36">
+        <v>95200100</v>
+      </c>
+      <c r="B144" s="36">
         <v>4</v>
       </c>
-      <c r="R143" s="36">
-        <v>2</v>
-      </c>
-      <c r="S143" s="36">
-        <v>5000</v>
-      </c>
-      <c r="T143" s="36">
-        <v>4</v>
-      </c>
-      <c r="U143" s="36">
-        <v>1</v>
-      </c>
-      <c r="V143" s="36">
-        <v>4</v>
-      </c>
-      <c r="W143" s="36">
-        <v>0</v>
-      </c>
-      <c r="X143" s="36">
-        <v>24000</v>
-      </c>
-      <c r="Y143" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z143" s="36">
-        <v>24000</v>
-      </c>
-      <c r="AA143" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB143" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC143" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD143" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE143" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF143" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A144" s="5">
-        <v>95200300</v>
-      </c>
-      <c r="B144" s="5">
-        <v>4</v>
-      </c>
-      <c r="C144" s="5">
+      <c r="C144" s="36">
         <v>0</v>
       </c>
       <c r="D144" s="5">
         <v>7018</v>
       </c>
-      <c r="E144" s="5">
-        <v>1</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>311</v>
+      <c r="E144" s="36">
+        <v>1</v>
+      </c>
+      <c r="F144" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="G144" s="36" t="s">
+        <v>299</v>
       </c>
       <c r="H144" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I144" s="36" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="J144" s="36">
         <v>0</v>
@@ -16195,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="AA144" s="36">
-        <v>85200300</v>
+        <v>85200100</v>
       </c>
       <c r="AB144" s="36">
         <v>0</v>
@@ -16213,33 +16230,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A145" s="5">
-        <v>95200500</v>
-      </c>
-      <c r="B145" s="5">
-        <v>4</v>
-      </c>
-      <c r="C145" s="5">
-        <v>0</v>
+    <row r="145" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="36">
+        <v>95200101</v>
+      </c>
+      <c r="B145" s="36">
+        <v>5</v>
+      </c>
+      <c r="C145" s="36">
+        <v>1</v>
       </c>
       <c r="D145" s="5">
         <v>7019</v>
       </c>
-      <c r="E145" s="5">
-        <v>1</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>312</v>
+      <c r="E145" s="36">
+        <v>1</v>
+      </c>
+      <c r="F145" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="G145" s="36" t="s">
+        <v>298</v>
       </c>
       <c r="H145" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I145" s="36" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="J145" s="36">
         <v>0</v>
@@ -16248,7 +16265,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="36">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="M145" s="36">
         <v>0</v>
@@ -16263,37 +16280,37 @@
         <v>0</v>
       </c>
       <c r="Q145" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R145" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S145" s="36">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T145" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U145" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V145" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W145" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X145" s="36">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="Y145" s="36">
         <v>0</v>
       </c>
       <c r="Z145" s="36">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="AA145" s="36">
-        <v>85200500</v>
+        <v>0</v>
       </c>
       <c r="AB145" s="36">
         <v>0</v>
@@ -16313,7 +16330,7 @@
     </row>
     <row r="146" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A146" s="5">
-        <v>95200700</v>
+        <v>95200300</v>
       </c>
       <c r="B146" s="5">
         <v>4</v>
@@ -16328,84 +16345,476 @@
         <v>1</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="H146" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I146" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="J146" s="36">
+        <v>0</v>
+      </c>
+      <c r="K146" s="36">
+        <v>0</v>
+      </c>
+      <c r="L146" s="36">
+        <v>0</v>
+      </c>
+      <c r="M146" s="36">
+        <v>0</v>
+      </c>
+      <c r="N146" s="36">
+        <v>0</v>
+      </c>
+      <c r="O146" s="36">
+        <v>0</v>
+      </c>
+      <c r="P146" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="36">
+        <v>0</v>
+      </c>
+      <c r="R146" s="36">
+        <v>0</v>
+      </c>
+      <c r="S146" s="36">
+        <v>0</v>
+      </c>
+      <c r="T146" s="36">
+        <v>0</v>
+      </c>
+      <c r="U146" s="36">
+        <v>0</v>
+      </c>
+      <c r="V146" s="36">
+        <v>0</v>
+      </c>
+      <c r="W146" s="36">
+        <v>0</v>
+      </c>
+      <c r="X146" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="36">
+        <v>85200300</v>
+      </c>
+      <c r="AB146" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A147" s="5">
+        <v>95200500</v>
+      </c>
+      <c r="B147" s="5">
+        <v>4</v>
+      </c>
+      <c r="C147" s="5">
+        <v>0</v>
+      </c>
+      <c r="D147" s="5">
+        <v>7021</v>
+      </c>
+      <c r="E147" s="5">
+        <v>1</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H147" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I147" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="J147" s="36">
+        <v>0</v>
+      </c>
+      <c r="K147" s="36">
+        <v>0</v>
+      </c>
+      <c r="L147" s="36">
+        <v>0</v>
+      </c>
+      <c r="M147" s="36">
+        <v>0</v>
+      </c>
+      <c r="N147" s="36">
+        <v>0</v>
+      </c>
+      <c r="O147" s="36">
+        <v>0</v>
+      </c>
+      <c r="P147" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="36">
+        <v>0</v>
+      </c>
+      <c r="R147" s="36">
+        <v>0</v>
+      </c>
+      <c r="S147" s="36">
+        <v>0</v>
+      </c>
+      <c r="T147" s="36">
+        <v>0</v>
+      </c>
+      <c r="U147" s="36">
+        <v>0</v>
+      </c>
+      <c r="V147" s="36">
+        <v>0</v>
+      </c>
+      <c r="W147" s="36">
+        <v>0</v>
+      </c>
+      <c r="X147" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="36">
+        <v>85200500</v>
+      </c>
+      <c r="AB147" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD147" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE147" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF147" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A148" s="5">
+        <v>95200700</v>
+      </c>
+      <c r="B148" s="5">
+        <v>4</v>
+      </c>
+      <c r="C148" s="5">
+        <v>0</v>
+      </c>
+      <c r="D148" s="5">
+        <v>7022</v>
+      </c>
+      <c r="E148" s="5">
+        <v>1</v>
+      </c>
+      <c r="F148" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="J146" s="36">
-        <v>0</v>
-      </c>
-      <c r="K146" s="36">
-        <v>0</v>
-      </c>
-      <c r="L146" s="36">
-        <v>0</v>
-      </c>
-      <c r="M146" s="36">
-        <v>0</v>
-      </c>
-      <c r="N146" s="36">
-        <v>0</v>
-      </c>
-      <c r="O146" s="36">
-        <v>0</v>
-      </c>
-      <c r="P146" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q146" s="36">
-        <v>0</v>
-      </c>
-      <c r="R146" s="36">
-        <v>0</v>
-      </c>
-      <c r="S146" s="36">
-        <v>0</v>
-      </c>
-      <c r="T146" s="36">
-        <v>0</v>
-      </c>
-      <c r="U146" s="36">
-        <v>0</v>
-      </c>
-      <c r="V146" s="36">
-        <v>0</v>
-      </c>
-      <c r="W146" s="36">
-        <v>0</v>
-      </c>
-      <c r="X146" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y146" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z146" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="36">
+      <c r="G148" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H148" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I148" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J148" s="36">
+        <v>0</v>
+      </c>
+      <c r="K148" s="36">
+        <v>0</v>
+      </c>
+      <c r="L148" s="36">
+        <v>0</v>
+      </c>
+      <c r="M148" s="36">
+        <v>0</v>
+      </c>
+      <c r="N148" s="36">
+        <v>0</v>
+      </c>
+      <c r="O148" s="36">
+        <v>0</v>
+      </c>
+      <c r="P148" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="36">
+        <v>0</v>
+      </c>
+      <c r="R148" s="36">
+        <v>0</v>
+      </c>
+      <c r="S148" s="36">
+        <v>0</v>
+      </c>
+      <c r="T148" s="36">
+        <v>0</v>
+      </c>
+      <c r="U148" s="36">
+        <v>0</v>
+      </c>
+      <c r="V148" s="36">
+        <v>0</v>
+      </c>
+      <c r="W148" s="36">
+        <v>0</v>
+      </c>
+      <c r="X148" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="36">
         <v>85200700</v>
       </c>
-      <c r="AB146" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC146" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD146" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE146" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF146" s="5">
+      <c r="AB148" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD148" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE148" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF148" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A149" s="5">
+        <v>95220300</v>
+      </c>
+      <c r="B149" s="5">
+        <v>4</v>
+      </c>
+      <c r="C149" s="5">
+        <v>0</v>
+      </c>
+      <c r="D149" s="5">
+        <v>7023</v>
+      </c>
+      <c r="E149" s="5">
+        <v>1</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H149" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I149" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="J149" s="36">
+        <v>0</v>
+      </c>
+      <c r="K149" s="36">
+        <v>0</v>
+      </c>
+      <c r="L149" s="36">
+        <v>0</v>
+      </c>
+      <c r="M149" s="36">
+        <v>0</v>
+      </c>
+      <c r="N149" s="36">
+        <v>0</v>
+      </c>
+      <c r="O149" s="36">
+        <v>0</v>
+      </c>
+      <c r="P149" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="36">
+        <v>0</v>
+      </c>
+      <c r="R149" s="36">
+        <v>0</v>
+      </c>
+      <c r="S149" s="36">
+        <v>0</v>
+      </c>
+      <c r="T149" s="36">
+        <v>0</v>
+      </c>
+      <c r="U149" s="36">
+        <v>0</v>
+      </c>
+      <c r="V149" s="36">
+        <v>0</v>
+      </c>
+      <c r="W149" s="36">
+        <v>0</v>
+      </c>
+      <c r="X149" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="36">
+        <v>85220300</v>
+      </c>
+      <c r="AB149" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD149" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE149" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF149" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A150" s="5">
+        <v>97000100</v>
+      </c>
+      <c r="B150" s="5">
+        <v>4</v>
+      </c>
+      <c r="C150" s="5">
+        <v>0</v>
+      </c>
+      <c r="D150" s="5">
+        <v>7024</v>
+      </c>
+      <c r="E150" s="5">
+        <v>1</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H150" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I150" s="36" t="s">
+        <v>345</v>
+      </c>
+      <c r="J150" s="36">
+        <v>0</v>
+      </c>
+      <c r="K150" s="36">
+        <v>0</v>
+      </c>
+      <c r="L150" s="36">
+        <v>0</v>
+      </c>
+      <c r="M150" s="36">
+        <v>0</v>
+      </c>
+      <c r="N150" s="36">
+        <v>0</v>
+      </c>
+      <c r="O150" s="36">
+        <v>0</v>
+      </c>
+      <c r="P150" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="36">
+        <v>0</v>
+      </c>
+      <c r="R150" s="36">
+        <v>0</v>
+      </c>
+      <c r="S150" s="36">
+        <v>0</v>
+      </c>
+      <c r="T150" s="36">
+        <v>0</v>
+      </c>
+      <c r="U150" s="36">
+        <v>0</v>
+      </c>
+      <c r="V150" s="36">
+        <v>0</v>
+      </c>
+      <c r="W150" s="36">
+        <v>0</v>
+      </c>
+      <c r="X150" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="36">
+        <v>87000100</v>
+      </c>
+      <c r="AB150" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="5">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2583D073-4AA5-4CC2-B5C6-B8DF55D66DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABF6CD1-86F2-48E6-981D-6CA173C7F87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="N130" s="36">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O130" s="36">
         <v>0</v>
@@ -14810,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="Q130" s="36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R130" s="36">
         <v>2</v>
@@ -14849,13 +14849,13 @@
         <v>0</v>
       </c>
       <c r="AD130" s="5">
-        <v>0</v>
+        <v>95001300</v>
       </c>
       <c r="AE130" s="5">
         <v>0</v>
       </c>
       <c r="AF130" s="5">
-        <v>95001300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:32" x14ac:dyDescent="0.15">
@@ -15291,16 +15291,16 @@
         <v>0</v>
       </c>
       <c r="N135" s="36">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="O135" s="36">
         <v>0</v>
       </c>
       <c r="P135" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R135" s="36">
         <v>0</v>
@@ -15585,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="N138" s="36">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O138" s="36">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q138" s="36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R138" s="36">
         <v>2</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="AD138" s="5">
-        <v>0</v>
+        <v>95100900</v>
       </c>
       <c r="AE138" s="5">
         <v>0</v>
@@ -15977,22 +15977,22 @@
         <v>0</v>
       </c>
       <c r="N142" s="36">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="O142" s="36">
         <v>0</v>
       </c>
       <c r="P142" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R142" s="36">
         <v>0</v>
       </c>
       <c r="S142" s="36">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="T142" s="36">
         <v>0</v>
@@ -16271,7 +16271,7 @@
         <v>0</v>
       </c>
       <c r="N145" s="36">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O145" s="36">
         <v>0</v>
@@ -16280,13 +16280,13 @@
         <v>0</v>
       </c>
       <c r="Q145" s="36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R145" s="36">
         <v>2</v>
       </c>
       <c r="S145" s="36">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T145" s="36">
         <v>4</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABF6CD1-86F2-48E6-981D-6CA173C7F87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0C1BB6-5AD2-4AB5-8C9A-52113428C3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15303,7 +15303,7 @@
         <v>3</v>
       </c>
       <c r="R135" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S135" s="36">
         <v>1400</v>
@@ -15989,7 +15989,7 @@
         <v>3</v>
       </c>
       <c r="R142" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S142" s="36">
         <v>1600</v>
@@ -16280,13 +16280,13 @@
         <v>0</v>
       </c>
       <c r="Q145" s="36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R145" s="36">
         <v>2</v>
       </c>
       <c r="S145" s="36">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T145" s="36">
         <v>4</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0C1BB6-5AD2-4AB5-8C9A-52113428C3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB47906-4B0F-4B42-B157-2267DEE0C2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -16325,7 +16325,7 @@
         <v>0</v>
       </c>
       <c r="AF145" s="5">
-        <v>0</v>
+        <v>95200700</v>
       </c>
     </row>
     <row r="146" spans="1:32" x14ac:dyDescent="0.15">
@@ -16604,10 +16604,10 @@
         <v>0</v>
       </c>
       <c r="AA148" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="36">
         <v>85200700</v>
-      </c>
-      <c r="AB148" s="36">
-        <v>0</v>
       </c>
       <c r="AC148" s="5">
         <v>0</v>
@@ -16633,7 +16633,7 @@
         <v>0</v>
       </c>
       <c r="D149" s="5">
-        <v>7023</v>
+        <v>7024</v>
       </c>
       <c r="E149" s="5">
         <v>1</v>
@@ -16731,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="D150" s="5">
-        <v>7024</v>
+        <v>7025</v>
       </c>
       <c r="E150" s="5">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB47906-4B0F-4B42-B157-2267DEE0C2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A4B3C2-F034-4B34-B15D-09BB4CDF9BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$149</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="350">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1519,6 +1519,20 @@
   </si>
   <si>
     <t>普攻伤害</t>
+  </si>
+  <si>
+    <t>冰弹概率附加冰冻</t>
+  </si>
+  <si>
+    <t>冰弹概率附加冰冻</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石概率附加燃烧</t>
+  </si>
+  <si>
+    <t>陨石概率附加燃烧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2215,7 +2229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AF150"/>
+  <dimension ref="A1:AF152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -14855,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="AF130" s="5">
-        <v>0</v>
+        <v>95001500</v>
       </c>
     </row>
     <row r="131" spans="1:32" x14ac:dyDescent="0.15">
@@ -15350,7 +15364,7 @@
     </row>
     <row r="136" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A136" s="5">
-        <v>95020300</v>
+        <v>95001500</v>
       </c>
       <c r="B136" s="5">
         <v>4</v>
@@ -15365,16 +15379,16 @@
         <v>1</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="H136" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I136" s="36" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J136" s="36">
         <v>0</v>
@@ -15428,10 +15442,10 @@
         <v>0</v>
       </c>
       <c r="AA136" s="36">
-        <v>85020300</v>
+        <v>0</v>
       </c>
       <c r="AB136" s="36">
-        <v>0</v>
+        <v>85001500</v>
       </c>
       <c r="AC136" s="5">
         <v>0</v>
@@ -15446,33 +15460,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A137" s="36">
-        <v>95100100</v>
-      </c>
-      <c r="B137" s="36">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A137" s="5">
+        <v>95020300</v>
+      </c>
+      <c r="B137" s="5">
         <v>4</v>
       </c>
-      <c r="C137" s="36">
+      <c r="C137" s="5">
         <v>0</v>
       </c>
       <c r="D137" s="5">
         <v>7011</v>
       </c>
-      <c r="E137" s="36">
-        <v>1</v>
-      </c>
-      <c r="F137" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="G137" s="36" t="s">
-        <v>302</v>
+      <c r="E137" s="5">
+        <v>1</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="H137" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I137" s="36" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="J137" s="36">
         <v>0</v>
@@ -15526,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="AA137" s="36">
-        <v>85100100</v>
+        <v>85020300</v>
       </c>
       <c r="AB137" s="36">
         <v>0</v>
@@ -15546,13 +15560,13 @@
     </row>
     <row r="138" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A138" s="36">
-        <v>95100101</v>
+        <v>95100100</v>
       </c>
       <c r="B138" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C138" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" s="5">
         <v>7012</v>
@@ -15561,16 +15575,16 @@
         <v>1</v>
       </c>
       <c r="F138" s="36" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G138" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H138" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I138" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J138" s="36">
         <v>0</v>
@@ -15579,13 +15593,13 @@
         <v>0</v>
       </c>
       <c r="L138" s="36">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M138" s="36">
         <v>0</v>
       </c>
       <c r="N138" s="36">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="O138" s="36">
         <v>0</v>
@@ -15594,37 +15608,37 @@
         <v>0</v>
       </c>
       <c r="Q138" s="36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R138" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S138" s="36">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="T138" s="36">
         <v>0</v>
       </c>
       <c r="U138" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V138" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W138" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X138" s="36">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="Y138" s="36">
         <v>0</v>
       </c>
       <c r="Z138" s="36">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="36">
-        <v>0</v>
+        <v>85100100</v>
       </c>
       <c r="AB138" s="36">
         <v>0</v>
@@ -15633,7 +15647,7 @@
         <v>0</v>
       </c>
       <c r="AD138" s="5">
-        <v>95100900</v>
+        <v>0</v>
       </c>
       <c r="AE138" s="5">
         <v>0</v>
@@ -15642,33 +15656,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A139" s="5">
-        <v>95100300</v>
-      </c>
-      <c r="B139" s="5">
-        <v>4</v>
-      </c>
-      <c r="C139" s="5">
-        <v>0</v>
+    <row r="139" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="36">
+        <v>95100101</v>
+      </c>
+      <c r="B139" s="36">
+        <v>5</v>
+      </c>
+      <c r="C139" s="36">
+        <v>1</v>
       </c>
       <c r="D139" s="5">
         <v>7013</v>
       </c>
-      <c r="E139" s="5">
-        <v>1</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>337</v>
+      <c r="E139" s="36">
+        <v>1</v>
+      </c>
+      <c r="F139" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="G139" s="36" t="s">
+        <v>303</v>
       </c>
       <c r="H139" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I139" s="36" t="s">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="J139" s="36">
         <v>0</v>
@@ -15677,13 +15691,13 @@
         <v>0</v>
       </c>
       <c r="L139" s="36">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="M139" s="36">
         <v>0</v>
       </c>
       <c r="N139" s="36">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O139" s="36">
         <v>0</v>
@@ -15692,37 +15706,37 @@
         <v>0</v>
       </c>
       <c r="Q139" s="36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R139" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S139" s="36">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="T139" s="36">
         <v>0</v>
       </c>
       <c r="U139" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V139" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W139" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X139" s="36">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Y139" s="36">
         <v>0</v>
       </c>
       <c r="Z139" s="36">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AA139" s="36">
-        <v>85100300</v>
+        <v>0</v>
       </c>
       <c r="AB139" s="36">
         <v>0</v>
@@ -15731,18 +15745,18 @@
         <v>0</v>
       </c>
       <c r="AD139" s="5">
-        <v>0</v>
+        <v>95100900</v>
       </c>
       <c r="AE139" s="5">
         <v>0</v>
       </c>
       <c r="AF139" s="5">
-        <v>0</v>
+        <v>95101100</v>
       </c>
     </row>
     <row r="140" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A140" s="5">
-        <v>95100500</v>
+        <v>95100300</v>
       </c>
       <c r="B140" s="5">
         <v>4</v>
@@ -15757,16 +15771,16 @@
         <v>1</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H140" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I140" s="36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J140" s="36">
         <v>0</v>
@@ -15820,7 +15834,7 @@
         <v>0</v>
       </c>
       <c r="AA140" s="36">
-        <v>85100500</v>
+        <v>85100300</v>
       </c>
       <c r="AB140" s="36">
         <v>0</v>
@@ -15840,7 +15854,7 @@
     </row>
     <row r="141" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A141" s="5">
-        <v>95100700</v>
+        <v>95100500</v>
       </c>
       <c r="B141" s="5">
         <v>4</v>
@@ -15855,16 +15869,16 @@
         <v>1</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H141" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I141" s="36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J141" s="36">
         <v>0</v>
@@ -15918,7 +15932,7 @@
         <v>0</v>
       </c>
       <c r="AA141" s="36">
-        <v>85100700</v>
+        <v>85100500</v>
       </c>
       <c r="AB141" s="36">
         <v>0</v>
@@ -15938,7 +15952,7 @@
     </row>
     <row r="142" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A142" s="5">
-        <v>95100900</v>
+        <v>95100700</v>
       </c>
       <c r="B142" s="5">
         <v>4</v>
@@ -15953,16 +15967,16 @@
         <v>1</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H142" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I142" s="36" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J142" s="36">
         <v>0</v>
@@ -15977,34 +15991,34 @@
         <v>0</v>
       </c>
       <c r="N142" s="36">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="O142" s="36">
         <v>0</v>
       </c>
       <c r="P142" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q142" s="36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R142" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S142" s="36">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="T142" s="36">
         <v>0</v>
       </c>
       <c r="U142" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V142" s="36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W142" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X142" s="36">
         <v>0</v>
@@ -16016,7 +16030,7 @@
         <v>0</v>
       </c>
       <c r="AA142" s="36">
-        <v>85100900</v>
+        <v>85100700</v>
       </c>
       <c r="AB142" s="36">
         <v>0</v>
@@ -16036,7 +16050,7 @@
     </row>
     <row r="143" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A143" s="5">
-        <v>95120300</v>
+        <v>95100900</v>
       </c>
       <c r="B143" s="5">
         <v>4</v>
@@ -16051,16 +16065,16 @@
         <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H143" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I143" s="36" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J143" s="36">
         <v>0</v>
@@ -16075,34 +16089,34 @@
         <v>0</v>
       </c>
       <c r="N143" s="36">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="O143" s="36">
         <v>0</v>
       </c>
       <c r="P143" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q143" s="36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R143" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S143" s="36">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="T143" s="36">
         <v>0</v>
       </c>
       <c r="U143" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V143" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W143" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X143" s="36">
         <v>0</v>
@@ -16114,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="AA143" s="36">
-        <v>85120300</v>
+        <v>85100900</v>
       </c>
       <c r="AB143" s="36">
         <v>0</v>
@@ -16132,33 +16146,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A144" s="36">
-        <v>95200100</v>
-      </c>
-      <c r="B144" s="36">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A144" s="5">
+        <v>95101100</v>
+      </c>
+      <c r="B144" s="5">
         <v>4</v>
       </c>
-      <c r="C144" s="36">
+      <c r="C144" s="5">
         <v>0</v>
       </c>
       <c r="D144" s="5">
         <v>7018</v>
       </c>
-      <c r="E144" s="36">
-        <v>1</v>
-      </c>
-      <c r="F144" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="G144" s="36" t="s">
-        <v>299</v>
+      <c r="E144" s="5">
+        <v>1</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>349</v>
       </c>
       <c r="H144" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I144" s="36" t="s">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="J144" s="36">
         <v>0</v>
@@ -16212,10 +16226,10 @@
         <v>0</v>
       </c>
       <c r="AA144" s="36">
-        <v>85200100</v>
+        <v>0</v>
       </c>
       <c r="AB144" s="36">
-        <v>0</v>
+        <v>85101100</v>
       </c>
       <c r="AC144" s="5">
         <v>0</v>
@@ -16230,33 +16244,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A145" s="36">
-        <v>95200101</v>
-      </c>
-      <c r="B145" s="36">
-        <v>5</v>
-      </c>
-      <c r="C145" s="36">
-        <v>1</v>
+    <row r="145" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A145" s="5">
+        <v>95120300</v>
+      </c>
+      <c r="B145" s="5">
+        <v>4</v>
+      </c>
+      <c r="C145" s="5">
+        <v>0</v>
       </c>
       <c r="D145" s="5">
         <v>7019</v>
       </c>
-      <c r="E145" s="36">
-        <v>1</v>
-      </c>
-      <c r="F145" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="G145" s="36" t="s">
-        <v>298</v>
+      <c r="E145" s="5">
+        <v>1</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>343</v>
       </c>
       <c r="H145" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I145" s="36" t="s">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="J145" s="36">
         <v>0</v>
@@ -16265,13 +16279,13 @@
         <v>0</v>
       </c>
       <c r="L145" s="36">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="M145" s="36">
         <v>0</v>
       </c>
       <c r="N145" s="36">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="O145" s="36">
         <v>0</v>
@@ -16280,81 +16294,81 @@
         <v>0</v>
       </c>
       <c r="Q145" s="36">
+        <v>0</v>
+      </c>
+      <c r="R145" s="36">
+        <v>0</v>
+      </c>
+      <c r="S145" s="36">
+        <v>0</v>
+      </c>
+      <c r="T145" s="36">
+        <v>0</v>
+      </c>
+      <c r="U145" s="36">
+        <v>0</v>
+      </c>
+      <c r="V145" s="36">
+        <v>0</v>
+      </c>
+      <c r="W145" s="36">
+        <v>0</v>
+      </c>
+      <c r="X145" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="36">
+        <v>85120300</v>
+      </c>
+      <c r="AB145" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF145" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="36">
+        <v>95200100</v>
+      </c>
+      <c r="B146" s="36">
         <v>4</v>
       </c>
-      <c r="R145" s="36">
-        <v>2</v>
-      </c>
-      <c r="S145" s="36">
-        <v>5000</v>
-      </c>
-      <c r="T145" s="36">
-        <v>4</v>
-      </c>
-      <c r="U145" s="36">
-        <v>1</v>
-      </c>
-      <c r="V145" s="36">
-        <v>4</v>
-      </c>
-      <c r="W145" s="36">
-        <v>1</v>
-      </c>
-      <c r="X145" s="36">
-        <v>24000</v>
-      </c>
-      <c r="Y145" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z145" s="36">
-        <v>24000</v>
-      </c>
-      <c r="AA145" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB145" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC145" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD145" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE145" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF145" s="5">
-        <v>95200700</v>
-      </c>
-    </row>
-    <row r="146" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A146" s="5">
-        <v>95200300</v>
-      </c>
-      <c r="B146" s="5">
-        <v>4</v>
-      </c>
-      <c r="C146" s="5">
+      <c r="C146" s="36">
         <v>0</v>
       </c>
       <c r="D146" s="5">
         <v>7020</v>
       </c>
-      <c r="E146" s="5">
-        <v>1</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>311</v>
+      <c r="E146" s="36">
+        <v>1</v>
+      </c>
+      <c r="F146" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="G146" s="36" t="s">
+        <v>299</v>
       </c>
       <c r="H146" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I146" s="36" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="J146" s="36">
         <v>0</v>
@@ -16408,7 +16422,7 @@
         <v>0</v>
       </c>
       <c r="AA146" s="36">
-        <v>85200300</v>
+        <v>85200100</v>
       </c>
       <c r="AB146" s="36">
         <v>0</v>
@@ -16426,33 +16440,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A147" s="5">
-        <v>95200500</v>
-      </c>
-      <c r="B147" s="5">
-        <v>4</v>
-      </c>
-      <c r="C147" s="5">
-        <v>0</v>
+    <row r="147" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A147" s="36">
+        <v>95200101</v>
+      </c>
+      <c r="B147" s="36">
+        <v>5</v>
+      </c>
+      <c r="C147" s="36">
+        <v>1</v>
       </c>
       <c r="D147" s="5">
         <v>7021</v>
       </c>
-      <c r="E147" s="5">
-        <v>1</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>312</v>
+      <c r="E147" s="36">
+        <v>1</v>
+      </c>
+      <c r="F147" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="G147" s="36" t="s">
+        <v>298</v>
       </c>
       <c r="H147" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I147" s="36" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="J147" s="36">
         <v>0</v>
@@ -16461,13 +16475,13 @@
         <v>0</v>
       </c>
       <c r="L147" s="36">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="M147" s="36">
         <v>0</v>
       </c>
       <c r="N147" s="36">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O147" s="36">
         <v>0</v>
@@ -16476,37 +16490,37 @@
         <v>0</v>
       </c>
       <c r="Q147" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R147" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S147" s="36">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T147" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U147" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V147" s="36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W147" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X147" s="36">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="Y147" s="36">
         <v>0</v>
       </c>
       <c r="Z147" s="36">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="AA147" s="36">
-        <v>85200500</v>
+        <v>0</v>
       </c>
       <c r="AB147" s="36">
         <v>0</v>
@@ -16521,12 +16535,12 @@
         <v>0</v>
       </c>
       <c r="AF147" s="5">
-        <v>0</v>
+        <v>95200700</v>
       </c>
     </row>
     <row r="148" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A148" s="5">
-        <v>95200700</v>
+        <v>95200300</v>
       </c>
       <c r="B148" s="5">
         <v>4</v>
@@ -16541,16 +16555,16 @@
         <v>1</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="H148" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I148" s="36" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="J148" s="36">
         <v>0</v>
@@ -16604,10 +16618,10 @@
         <v>0</v>
       </c>
       <c r="AA148" s="36">
-        <v>0</v>
+        <v>85200300</v>
       </c>
       <c r="AB148" s="36">
-        <v>85200700</v>
+        <v>0</v>
       </c>
       <c r="AC148" s="5">
         <v>0</v>
@@ -16624,7 +16638,7 @@
     </row>
     <row r="149" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A149" s="5">
-        <v>95220300</v>
+        <v>95200500</v>
       </c>
       <c r="B149" s="5">
         <v>4</v>
@@ -16633,22 +16647,22 @@
         <v>0</v>
       </c>
       <c r="D149" s="5">
-        <v>7024</v>
+        <v>7023</v>
       </c>
       <c r="E149" s="5">
         <v>1</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="H149" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I149" s="36" t="s">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="J149" s="36">
         <v>0</v>
@@ -16702,7 +16716,7 @@
         <v>0</v>
       </c>
       <c r="AA149" s="36">
-        <v>85220300</v>
+        <v>85200500</v>
       </c>
       <c r="AB149" s="36">
         <v>0</v>
@@ -16722,7 +16736,7 @@
     </row>
     <row r="150" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A150" s="5">
-        <v>97000100</v>
+        <v>95200700</v>
       </c>
       <c r="B150" s="5">
         <v>4</v>
@@ -16731,90 +16745,286 @@
         <v>0</v>
       </c>
       <c r="D150" s="5">
-        <v>7025</v>
+        <v>7024</v>
       </c>
       <c r="E150" s="5">
         <v>1</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="H150" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I150" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J150" s="36">
+        <v>0</v>
+      </c>
+      <c r="K150" s="36">
+        <v>0</v>
+      </c>
+      <c r="L150" s="36">
+        <v>0</v>
+      </c>
+      <c r="M150" s="36">
+        <v>0</v>
+      </c>
+      <c r="N150" s="36">
+        <v>0</v>
+      </c>
+      <c r="O150" s="36">
+        <v>0</v>
+      </c>
+      <c r="P150" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="36">
+        <v>0</v>
+      </c>
+      <c r="R150" s="36">
+        <v>0</v>
+      </c>
+      <c r="S150" s="36">
+        <v>0</v>
+      </c>
+      <c r="T150" s="36">
+        <v>0</v>
+      </c>
+      <c r="U150" s="36">
+        <v>0</v>
+      </c>
+      <c r="V150" s="36">
+        <v>0</v>
+      </c>
+      <c r="W150" s="36">
+        <v>0</v>
+      </c>
+      <c r="X150" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="36">
+        <v>85200700</v>
+      </c>
+      <c r="AC150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A151" s="5">
+        <v>95220300</v>
+      </c>
+      <c r="B151" s="5">
+        <v>4</v>
+      </c>
+      <c r="C151" s="5">
+        <v>0</v>
+      </c>
+      <c r="D151" s="5">
+        <v>7025</v>
+      </c>
+      <c r="E151" s="5">
+        <v>1</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H151" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I151" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="J151" s="36">
+        <v>0</v>
+      </c>
+      <c r="K151" s="36">
+        <v>0</v>
+      </c>
+      <c r="L151" s="36">
+        <v>0</v>
+      </c>
+      <c r="M151" s="36">
+        <v>0</v>
+      </c>
+      <c r="N151" s="36">
+        <v>0</v>
+      </c>
+      <c r="O151" s="36">
+        <v>0</v>
+      </c>
+      <c r="P151" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q151" s="36">
+        <v>0</v>
+      </c>
+      <c r="R151" s="36">
+        <v>0</v>
+      </c>
+      <c r="S151" s="36">
+        <v>0</v>
+      </c>
+      <c r="T151" s="36">
+        <v>0</v>
+      </c>
+      <c r="U151" s="36">
+        <v>0</v>
+      </c>
+      <c r="V151" s="36">
+        <v>0</v>
+      </c>
+      <c r="W151" s="36">
+        <v>0</v>
+      </c>
+      <c r="X151" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="36">
+        <v>85220300</v>
+      </c>
+      <c r="AB151" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE151" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF151" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A152" s="5">
+        <v>97000100</v>
+      </c>
+      <c r="B152" s="5">
+        <v>4</v>
+      </c>
+      <c r="C152" s="5">
+        <v>0</v>
+      </c>
+      <c r="D152" s="5">
+        <v>7026</v>
+      </c>
+      <c r="E152" s="5">
+        <v>1</v>
+      </c>
+      <c r="F152" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="J150" s="36">
-        <v>0</v>
-      </c>
-      <c r="K150" s="36">
-        <v>0</v>
-      </c>
-      <c r="L150" s="36">
-        <v>0</v>
-      </c>
-      <c r="M150" s="36">
-        <v>0</v>
-      </c>
-      <c r="N150" s="36">
-        <v>0</v>
-      </c>
-      <c r="O150" s="36">
-        <v>0</v>
-      </c>
-      <c r="P150" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q150" s="36">
-        <v>0</v>
-      </c>
-      <c r="R150" s="36">
-        <v>0</v>
-      </c>
-      <c r="S150" s="36">
-        <v>0</v>
-      </c>
-      <c r="T150" s="36">
-        <v>0</v>
-      </c>
-      <c r="U150" s="36">
-        <v>0</v>
-      </c>
-      <c r="V150" s="36">
-        <v>0</v>
-      </c>
-      <c r="W150" s="36">
-        <v>0</v>
-      </c>
-      <c r="X150" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y150" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z150" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA150" s="36">
+      <c r="G152" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H152" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I152" s="36" t="s">
+        <v>345</v>
+      </c>
+      <c r="J152" s="36">
+        <v>0</v>
+      </c>
+      <c r="K152" s="36">
+        <v>0</v>
+      </c>
+      <c r="L152" s="36">
+        <v>0</v>
+      </c>
+      <c r="M152" s="36">
+        <v>0</v>
+      </c>
+      <c r="N152" s="36">
+        <v>0</v>
+      </c>
+      <c r="O152" s="36">
+        <v>0</v>
+      </c>
+      <c r="P152" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q152" s="36">
+        <v>0</v>
+      </c>
+      <c r="R152" s="36">
+        <v>0</v>
+      </c>
+      <c r="S152" s="36">
+        <v>0</v>
+      </c>
+      <c r="T152" s="36">
+        <v>0</v>
+      </c>
+      <c r="U152" s="36">
+        <v>0</v>
+      </c>
+      <c r="V152" s="36">
+        <v>0</v>
+      </c>
+      <c r="W152" s="36">
+        <v>0</v>
+      </c>
+      <c r="X152" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="36">
         <v>87000100</v>
       </c>
-      <c r="AB150" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC150" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD150" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE150" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF150" s="5">
+      <c r="AB152" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC152" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD152" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE152" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF152" s="5">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A4B3C2-F034-4B34-B15D-09BB4CDF9BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5423F5E-7BBF-4207-9C47-9E8948991DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15367,10 +15367,10 @@
         <v>95001500</v>
       </c>
       <c r="B136" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C136" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="5">
         <v>7010</v>
@@ -15412,10 +15412,10 @@
         <v>0</v>
       </c>
       <c r="Q136" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S136" s="36">
         <v>0</v>
@@ -16151,10 +16151,10 @@
         <v>95101100</v>
       </c>
       <c r="B144" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C144" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" s="5">
         <v>7018</v>
@@ -16196,10 +16196,10 @@
         <v>0</v>
       </c>
       <c r="Q144" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S144" s="36">
         <v>0</v>
@@ -16739,7 +16739,7 @@
         <v>95200700</v>
       </c>
       <c r="B150" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C150" s="5">
         <v>0</v>
@@ -16784,10 +16784,10 @@
         <v>0</v>
       </c>
       <c r="Q150" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S150" s="36">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5423F5E-7BBF-4207-9C47-9E8948991DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC82337-38AF-4417-A253-1E97062541B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -5296,7 +5296,7 @@
         <v>25010001</v>
       </c>
       <c r="B33" s="23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" s="23">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC82337-38AF-4417-A253-1E97062541B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C97378-8305-4931-9A19-78ACC0102862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14848,7 +14848,7 @@
         <v>21000</v>
       </c>
       <c r="Y130" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z130" s="36">
         <v>21000</v>
@@ -15730,7 +15730,7 @@
         <v>20000</v>
       </c>
       <c r="Y139" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z139" s="36">
         <v>20000</v>
@@ -16514,7 +16514,7 @@
         <v>24000</v>
       </c>
       <c r="Y147" s="36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z147" s="36">
         <v>24000</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C97378-8305-4931-9A19-78ACC0102862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7990C25C-3E21-40E8-9753-9B1D82B28C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14815,7 +14815,7 @@
         <v>0</v>
       </c>
       <c r="N130" s="36">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="O130" s="36">
         <v>0</v>
@@ -15697,7 +15697,7 @@
         <v>0</v>
       </c>
       <c r="N139" s="36">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="O139" s="36">
         <v>0</v>
@@ -15712,7 +15712,7 @@
         <v>2</v>
       </c>
       <c r="S139" s="36">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="T139" s="36">
         <v>0</v>
@@ -16089,7 +16089,7 @@
         <v>0</v>
       </c>
       <c r="N143" s="36">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="O143" s="36">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>2</v>
       </c>
       <c r="S143" s="36">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="T143" s="36">
         <v>0</v>
@@ -16481,7 +16481,7 @@
         <v>0</v>
       </c>
       <c r="N147" s="36">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="O147" s="36">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7990C25C-3E21-40E8-9753-9B1D82B28C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C276D5F4-15CA-4851-861D-1B531218EE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14842,13 +14842,13 @@
         <v>1</v>
       </c>
       <c r="W130" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X130" s="36">
         <v>21000</v>
       </c>
       <c r="Y130" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z130" s="36">
         <v>21000</v>
@@ -15332,7 +15332,7 @@
         <v>1</v>
       </c>
       <c r="W135" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X135" s="36">
         <v>0</v>
@@ -15724,13 +15724,13 @@
         <v>2</v>
       </c>
       <c r="W139" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X139" s="36">
         <v>20000</v>
       </c>
       <c r="Y139" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="36">
         <v>20000</v>
@@ -16116,7 +16116,7 @@
         <v>2</v>
       </c>
       <c r="W143" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X143" s="36">
         <v>0</v>
@@ -16508,13 +16508,13 @@
         <v>4</v>
       </c>
       <c r="W147" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X147" s="36">
         <v>24000</v>
       </c>
       <c r="Y147" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z147" s="36">
         <v>24000</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C276D5F4-15CA-4851-861D-1B531218EE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE66CA2-4432-4106-A213-98FB45631724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14845,13 +14845,13 @@
         <v>0</v>
       </c>
       <c r="X130" s="36">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="Y130" s="36">
         <v>0</v>
       </c>
       <c r="Z130" s="36">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="AA130" s="36">
         <v>85001100</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE66CA2-4432-4106-A213-98FB45631724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416B5521-2C8C-4703-B336-038447C76567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AC$149</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,6 +38,7 @@
   <authors>
     <author>李强</author>
     <author>pe</author>
+    <author>cltx</author>
   </authors>
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -302,12 +303,39 @@
         </r>
       </text>
     </comment>
+    <comment ref="W4" authorId="2" shapeId="0" xr:uid="{3BCFFE37-A88F-4166-8915-9D540B7CC094}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">如果关联属性ID为0，则使用默认值；如果非0，则主副目标伤害系数均乘以对应属性id的值/10000（备注：对应属性id的值为0时，伤害系数最终结果为0）
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="353">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1532,6 +1560,18 @@
   </si>
   <si>
     <t>陨石概率附加燃烧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage_element_adjust</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素伤害系数调整关联属性id（按顺序：物理、冰、火、毒、电，万分比）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,7000301,7000302,7000303,7000304</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1539,7 +1579,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1703,6 +1743,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2229,7 +2284,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AF152"/>
+  <dimension ref="A1:AG152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2250,22 +2305,23 @@
     <col min="20" max="20" width="9.5" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.5" style="5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="58" style="5" customWidth="1"/>
-    <col min="23" max="23" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="17.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="5"/>
+    <col min="23" max="23" width="61" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="17.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:33" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2332,20 +2388,20 @@
       <c r="V2" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="W2" s="5" t="s">
-        <v>65</v>
+      <c r="W2" s="33" t="s">
+        <v>287</v>
       </c>
       <c r="X2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="5" t="s">
         <v>65</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AA2" s="5" t="s">
-        <v>68</v>
+      <c r="AA2" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="AB2" s="5" t="s">
         <v>68</v>
@@ -2362,8 +2418,11 @@
       <c r="AF2" s="5" t="s">
         <v>68</v>
       </c>
+      <c r="AG2" s="5" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="3" spans="1:32" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2430,38 +2489,41 @@
       <c r="V3" s="33" t="s">
         <v>286</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="33" t="s">
+        <v>350</v>
+      </c>
+      <c r="X3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AB3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="5" t="s">
+      <c r="AC3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AD3" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="AD3" s="5" t="s">
+      <c r="AE3" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AF3" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="AF3" s="5" t="s">
+      <c r="AG3" s="5" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
@@ -2528,38 +2590,41 @@
       <c r="V4" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="X4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Y4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="AA4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AE4" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10101</v>
       </c>
@@ -2624,25 +2689,25 @@
       <c r="V5" s="34">
         <v>0</v>
       </c>
-      <c r="W5" s="9">
-        <v>0</v>
+      <c r="W5" s="34" t="s">
+        <v>352</v>
       </c>
       <c r="X5" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z5" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="10">
         <v>0</v>
       </c>
       <c r="AD5" s="5">
@@ -2654,8 +2719,11 @@
       <c r="AF5" s="5">
         <v>0</v>
       </c>
+      <c r="AG5" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10102</v>
       </c>
@@ -2720,25 +2788,25 @@
       <c r="V6" s="34">
         <v>0</v>
       </c>
-      <c r="W6" s="9">
-        <v>0</v>
+      <c r="W6" s="34" t="s">
+        <v>352</v>
       </c>
       <c r="X6" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z6" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="10">
         <v>0</v>
       </c>
       <c r="AD6" s="5">
@@ -2750,8 +2818,11 @@
       <c r="AF6" s="5">
         <v>0</v>
       </c>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10201</v>
       </c>
@@ -2816,25 +2887,25 @@
       <c r="V7" s="34">
         <v>0</v>
       </c>
-      <c r="W7" s="9">
-        <v>0</v>
+      <c r="W7" s="34" t="s">
+        <v>352</v>
       </c>
       <c r="X7" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z7" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="10">
         <v>0</v>
       </c>
       <c r="AD7" s="5">
@@ -2846,8 +2917,11 @@
       <c r="AF7" s="5">
         <v>0</v>
       </c>
+      <c r="AG7" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10202</v>
       </c>
@@ -2912,25 +2986,25 @@
       <c r="V8" s="34">
         <v>0</v>
       </c>
-      <c r="W8" s="9">
-        <v>0</v>
+      <c r="W8" s="34" t="s">
+        <v>352</v>
       </c>
       <c r="X8" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z8" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="10">
         <v>0</v>
       </c>
       <c r="AD8" s="5">
@@ -2942,8 +3016,11 @@
       <c r="AF8" s="5">
         <v>0</v>
       </c>
+      <c r="AG8" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10301</v>
       </c>
@@ -3008,25 +3085,25 @@
       <c r="V9" s="34">
         <v>0</v>
       </c>
-      <c r="W9" s="9">
-        <v>0</v>
+      <c r="W9" s="34" t="s">
+        <v>352</v>
       </c>
       <c r="X9" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z9" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10">
         <v>0</v>
       </c>
       <c r="AD9" s="5">
@@ -3038,8 +3115,11 @@
       <c r="AF9" s="5">
         <v>0</v>
       </c>
+      <c r="AG9" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10302</v>
       </c>
@@ -3104,25 +3184,25 @@
       <c r="V10" s="34">
         <v>0</v>
       </c>
-      <c r="W10" s="9">
-        <v>0</v>
+      <c r="W10" s="34" t="s">
+        <v>352</v>
       </c>
       <c r="X10" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z10" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="10">
         <v>0</v>
       </c>
       <c r="AD10" s="5">
@@ -3134,8 +3214,11 @@
       <c r="AF10" s="5">
         <v>0</v>
       </c>
+      <c r="AG10" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>20001</v>
       </c>
@@ -3202,25 +3285,25 @@
       <c r="V11" s="35">
         <v>0</v>
       </c>
-      <c r="W11" s="2">
+      <c r="W11" s="35">
         <v>0</v>
       </c>
       <c r="X11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB11" s="2">
         <v>0</v>
       </c>
-      <c r="AC11" s="5">
+      <c r="AC11" s="2">
         <v>0</v>
       </c>
       <c r="AD11" s="5">
@@ -3232,8 +3315,11 @@
       <c r="AF11" s="5">
         <v>0</v>
       </c>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>20010001</v>
       </c>
@@ -3300,25 +3386,25 @@
       <c r="V12" s="35">
         <v>0</v>
       </c>
-      <c r="W12" s="2">
+      <c r="W12" s="35">
         <v>0</v>
       </c>
       <c r="X12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB12" s="2">
         <v>0</v>
       </c>
-      <c r="AC12" s="5">
+      <c r="AC12" s="2">
         <v>0</v>
       </c>
       <c r="AD12" s="5">
@@ -3330,8 +3416,11 @@
       <c r="AF12" s="5">
         <v>0</v>
       </c>
+      <c r="AG12" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>20020001</v>
       </c>
@@ -3398,25 +3487,25 @@
       <c r="V13" s="35">
         <v>0</v>
       </c>
-      <c r="W13" s="2">
+      <c r="W13" s="35">
         <v>0</v>
       </c>
       <c r="X13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB13" s="2">
         <v>0</v>
       </c>
-      <c r="AC13" s="5">
+      <c r="AC13" s="2">
         <v>0</v>
       </c>
       <c r="AD13" s="5">
@@ -3428,8 +3517,11 @@
       <c r="AF13" s="5">
         <v>0</v>
       </c>
+      <c r="AG13" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>20030001</v>
       </c>
@@ -3496,25 +3588,25 @@
       <c r="V14" s="35">
         <v>0</v>
       </c>
-      <c r="W14" s="2">
+      <c r="W14" s="35">
         <v>0</v>
       </c>
       <c r="X14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB14" s="2">
         <v>0</v>
       </c>
-      <c r="AC14" s="5">
+      <c r="AC14" s="2">
         <v>0</v>
       </c>
       <c r="AD14" s="5">
@@ -3526,8 +3618,11 @@
       <c r="AF14" s="5">
         <v>0</v>
       </c>
+      <c r="AG14" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>20040001</v>
       </c>
@@ -3594,25 +3689,25 @@
       <c r="V15" s="35">
         <v>0</v>
       </c>
-      <c r="W15" s="2">
+      <c r="W15" s="35">
         <v>0</v>
       </c>
       <c r="X15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB15" s="2">
         <v>0</v>
       </c>
-      <c r="AC15" s="5">
+      <c r="AC15" s="2">
         <v>0</v>
       </c>
       <c r="AD15" s="5">
@@ -3624,8 +3719,11 @@
       <c r="AF15" s="5">
         <v>0</v>
       </c>
+      <c r="AG15" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>20050001</v>
       </c>
@@ -3692,25 +3790,25 @@
       <c r="V16" s="35">
         <v>0</v>
       </c>
-      <c r="W16" s="2">
+      <c r="W16" s="35">
         <v>0</v>
       </c>
       <c r="X16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB16" s="2">
         <v>0</v>
       </c>
-      <c r="AC16" s="5">
+      <c r="AC16" s="2">
         <v>0</v>
       </c>
       <c r="AD16" s="5">
@@ -3722,8 +3820,11 @@
       <c r="AF16" s="5">
         <v>0</v>
       </c>
+      <c r="AG16" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>20060001</v>
       </c>
@@ -3790,25 +3891,25 @@
       <c r="V17" s="35">
         <v>0</v>
       </c>
-      <c r="W17" s="2">
+      <c r="W17" s="35">
         <v>0</v>
       </c>
       <c r="X17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB17" s="2">
         <v>0</v>
       </c>
-      <c r="AC17" s="5">
+      <c r="AC17" s="2">
         <v>0</v>
       </c>
       <c r="AD17" s="5">
@@ -3820,8 +3921,11 @@
       <c r="AF17" s="5">
         <v>0</v>
       </c>
+      <c r="AG17" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>20070001</v>
       </c>
@@ -3888,25 +3992,25 @@
       <c r="V18" s="35">
         <v>0</v>
       </c>
-      <c r="W18" s="2">
+      <c r="W18" s="35">
         <v>0</v>
       </c>
       <c r="X18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB18" s="2">
         <v>0</v>
       </c>
-      <c r="AC18" s="5">
+      <c r="AC18" s="2">
         <v>0</v>
       </c>
       <c r="AD18" s="5">
@@ -3918,8 +4022,11 @@
       <c r="AF18" s="5">
         <v>0</v>
       </c>
+      <c r="AG18" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>20080001</v>
       </c>
@@ -3990,21 +4097,21 @@
         <v>0</v>
       </c>
       <c r="X19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB19" s="2">
         <v>0</v>
       </c>
-      <c r="AC19" s="5">
+      <c r="AC19" s="2">
         <v>0</v>
       </c>
       <c r="AD19" s="5">
@@ -4016,8 +4123,11 @@
       <c r="AF19" s="5">
         <v>0</v>
       </c>
+      <c r="AG19" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20090001</v>
       </c>
@@ -4088,21 +4198,21 @@
         <v>0</v>
       </c>
       <c r="X20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB20" s="2">
         <v>0</v>
       </c>
-      <c r="AC20" s="5">
+      <c r="AC20" s="2">
         <v>0</v>
       </c>
       <c r="AD20" s="5">
@@ -4114,8 +4224,11 @@
       <c r="AF20" s="5">
         <v>0</v>
       </c>
+      <c r="AG20" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20100001</v>
       </c>
@@ -4186,21 +4299,21 @@
         <v>0</v>
       </c>
       <c r="X21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB21" s="2">
         <v>0</v>
       </c>
-      <c r="AC21" s="5">
+      <c r="AC21" s="2">
         <v>0</v>
       </c>
       <c r="AD21" s="5">
@@ -4212,8 +4325,11 @@
       <c r="AF21" s="5">
         <v>0</v>
       </c>
+      <c r="AG21" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20110001</v>
       </c>
@@ -4284,21 +4400,21 @@
         <v>0</v>
       </c>
       <c r="X22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB22" s="2">
         <v>0</v>
       </c>
-      <c r="AC22" s="5">
+      <c r="AC22" s="2">
         <v>0</v>
       </c>
       <c r="AD22" s="5">
@@ -4310,8 +4426,11 @@
       <c r="AF22" s="5">
         <v>0</v>
       </c>
+      <c r="AG22" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20120001</v>
       </c>
@@ -4382,21 +4501,21 @@
         <v>0</v>
       </c>
       <c r="X23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB23" s="2">
         <v>0</v>
       </c>
-      <c r="AC23" s="5">
+      <c r="AC23" s="2">
         <v>0</v>
       </c>
       <c r="AD23" s="5">
@@ -4408,8 +4527,11 @@
       <c r="AF23" s="5">
         <v>0</v>
       </c>
+      <c r="AG23" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20130001</v>
       </c>
@@ -4480,21 +4602,21 @@
         <v>0</v>
       </c>
       <c r="X24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB24" s="2">
         <v>0</v>
       </c>
-      <c r="AC24" s="5">
+      <c r="AC24" s="2">
         <v>0</v>
       </c>
       <c r="AD24" s="5">
@@ -4506,8 +4628,11 @@
       <c r="AF24" s="5">
         <v>0</v>
       </c>
+      <c r="AG24" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20140001</v>
       </c>
@@ -4578,21 +4703,21 @@
         <v>0</v>
       </c>
       <c r="X25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB25" s="2">
         <v>0</v>
       </c>
-      <c r="AC25" s="5">
+      <c r="AC25" s="2">
         <v>0</v>
       </c>
       <c r="AD25" s="5">
@@ -4604,8 +4729,11 @@
       <c r="AF25" s="5">
         <v>0</v>
       </c>
+      <c r="AG25" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>20150001</v>
       </c>
@@ -4676,21 +4804,21 @@
         <v>0</v>
       </c>
       <c r="X26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB26" s="2">
         <v>0</v>
       </c>
-      <c r="AC26" s="5">
+      <c r="AC26" s="2">
         <v>0</v>
       </c>
       <c r="AD26" s="5">
@@ -4702,8 +4830,11 @@
       <c r="AF26" s="5">
         <v>0</v>
       </c>
+      <c r="AG26" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>20160001</v>
       </c>
@@ -4774,21 +4905,21 @@
         <v>0</v>
       </c>
       <c r="X27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB27" s="2">
         <v>0</v>
       </c>
-      <c r="AC27" s="5">
+      <c r="AC27" s="2">
         <v>0</v>
       </c>
       <c r="AD27" s="5">
@@ -4800,8 +4931,11 @@
       <c r="AF27" s="5">
         <v>0</v>
       </c>
+      <c r="AG27" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>201001011</v>
       </c>
@@ -4868,25 +5002,25 @@
       <c r="V28" s="35">
         <v>0</v>
       </c>
-      <c r="W28" s="2">
+      <c r="W28" s="35">
         <v>0</v>
       </c>
       <c r="X28" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z28" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB28" s="2">
         <v>0</v>
       </c>
-      <c r="AC28" s="5">
+      <c r="AC28" s="2">
         <v>0</v>
       </c>
       <c r="AD28" s="5">
@@ -4898,8 +5032,11 @@
       <c r="AF28" s="5">
         <v>0</v>
       </c>
+      <c r="AG28" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>201002011</v>
       </c>
@@ -4966,25 +5103,25 @@
       <c r="V29" s="35">
         <v>0</v>
       </c>
-      <c r="W29" s="2">
+      <c r="W29" s="35">
         <v>0</v>
       </c>
       <c r="X29" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z29" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB29" s="2">
         <v>0</v>
       </c>
-      <c r="AC29" s="5">
+      <c r="AC29" s="2">
         <v>0</v>
       </c>
       <c r="AD29" s="5">
@@ -4996,8 +5133,11 @@
       <c r="AF29" s="5">
         <v>0</v>
       </c>
+      <c r="AG29" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>201004011</v>
       </c>
@@ -5064,25 +5204,25 @@
       <c r="V30" s="35">
         <v>0</v>
       </c>
-      <c r="W30" s="2">
+      <c r="W30" s="35">
         <v>0</v>
       </c>
       <c r="X30" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z30" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB30" s="2">
         <v>0</v>
       </c>
-      <c r="AC30" s="5">
+      <c r="AC30" s="2">
         <v>0</v>
       </c>
       <c r="AD30" s="5">
@@ -5094,8 +5234,11 @@
       <c r="AF30" s="5">
         <v>0</v>
       </c>
+      <c r="AG30" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>214001011</v>
       </c>
@@ -5162,25 +5305,25 @@
       <c r="V31" s="35">
         <v>0</v>
       </c>
-      <c r="W31" s="2">
+      <c r="W31" s="35">
         <v>0</v>
       </c>
       <c r="X31" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z31" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB31" s="2">
         <v>0</v>
       </c>
-      <c r="AC31" s="5">
+      <c r="AC31" s="2">
         <v>0</v>
       </c>
       <c r="AD31" s="5">
@@ -5192,8 +5335,11 @@
       <c r="AF31" s="5">
         <v>0</v>
       </c>
+      <c r="AG31" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>203002011</v>
       </c>
@@ -5260,25 +5406,25 @@
       <c r="V32" s="35">
         <v>0</v>
       </c>
-      <c r="W32" s="2">
+      <c r="W32" s="35">
         <v>0</v>
       </c>
       <c r="X32" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z32" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB32" s="2">
         <v>0</v>
       </c>
-      <c r="AC32" s="5">
+      <c r="AC32" s="2">
         <v>0</v>
       </c>
       <c r="AD32" s="5">
@@ -5290,8 +5436,11 @@
       <c r="AF32" s="5">
         <v>0</v>
       </c>
+      <c r="AG32" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A33" s="23">
         <v>25010001</v>
       </c>
@@ -5371,12 +5520,12 @@
         <v>0</v>
       </c>
       <c r="AA33" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="23">
         <v>54150001</v>
       </c>
-      <c r="AB33" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="5">
+      <c r="AC33" s="23">
         <v>0</v>
       </c>
       <c r="AD33" s="5">
@@ -5388,8 +5537,11 @@
       <c r="AF33" s="5">
         <v>0</v>
       </c>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>30001</v>
       </c>
@@ -5469,12 +5621,12 @@
         <v>0</v>
       </c>
       <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
         <v>1000001</v>
       </c>
-      <c r="AB34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="5">
+      <c r="AC34" s="3">
         <v>0</v>
       </c>
       <c r="AD34" s="5">
@@ -5486,8 +5638,11 @@
       <c r="AF34" s="5">
         <v>0</v>
       </c>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>4000001</v>
       </c>
@@ -5567,12 +5722,12 @@
         <v>0</v>
       </c>
       <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
         <v>2000001</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="5">
+      <c r="AC35" s="3">
         <v>0</v>
       </c>
       <c r="AD35" s="5">
@@ -5584,8 +5739,11 @@
       <c r="AF35" s="5">
         <v>0</v>
       </c>
+      <c r="AG35" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:32" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="21">
         <v>5000001</v>
       </c>
@@ -5656,23 +5814,23 @@
         <v>0</v>
       </c>
       <c r="X36" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="21">
         <v>12000</v>
       </c>
-      <c r="Y36" s="21">
-        <v>0</v>
-      </c>
       <c r="Z36" s="21">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="21">
         <v>8000</v>
       </c>
-      <c r="AA36" s="21">
-        <v>0</v>
-      </c>
       <c r="AB36" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="21">
         <v>55010001</v>
       </c>
-      <c r="AC36" s="5">
-        <v>0</v>
-      </c>
       <c r="AD36" s="5">
         <v>0</v>
       </c>
@@ -5682,8 +5840,11 @@
       <c r="AF36" s="5">
         <v>0</v>
       </c>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A37" s="17">
         <v>6000001</v>
       </c>
@@ -5749,26 +5910,26 @@
         <v>2</v>
       </c>
       <c r="W37" s="17">
+        <v>0</v>
+      </c>
+      <c r="X37" s="17">
         <v>150</v>
       </c>
-      <c r="X37" s="17">
+      <c r="Y37" s="17">
         <v>15000</v>
       </c>
-      <c r="Y37" s="17">
+      <c r="Z37" s="17">
         <v>120</v>
       </c>
-      <c r="Z37" s="17">
+      <c r="AA37" s="17">
         <v>12000</v>
       </c>
-      <c r="AA37" s="17">
-        <v>0</v>
-      </c>
       <c r="AB37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="17">
         <v>56010001</v>
       </c>
-      <c r="AC37" s="5">
-        <v>0</v>
-      </c>
       <c r="AD37" s="5">
         <v>0</v>
       </c>
@@ -5778,8 +5939,11 @@
       <c r="AF37" s="5">
         <v>0</v>
       </c>
+      <c r="AG37" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A38" s="17">
         <v>6010001</v>
       </c>
@@ -5845,26 +6009,26 @@
         <v>2</v>
       </c>
       <c r="W38" s="17">
+        <v>0</v>
+      </c>
+      <c r="X38" s="17">
         <v>150</v>
       </c>
-      <c r="X38" s="17">
+      <c r="Y38" s="17">
         <v>15000</v>
       </c>
-      <c r="Y38" s="17">
+      <c r="Z38" s="17">
         <v>120</v>
       </c>
-      <c r="Z38" s="17">
+      <c r="AA38" s="17">
         <v>12000</v>
       </c>
-      <c r="AA38" s="17">
-        <v>0</v>
-      </c>
       <c r="AB38" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="17">
         <v>56010001</v>
       </c>
-      <c r="AC38" s="5">
-        <v>0</v>
-      </c>
       <c r="AD38" s="5">
         <v>0</v>
       </c>
@@ -5874,8 +6038,11 @@
       <c r="AF38" s="5">
         <v>0</v>
       </c>
+      <c r="AG38" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="19">
         <v>7000001</v>
       </c>
@@ -5941,26 +6108,26 @@
         <v>4</v>
       </c>
       <c r="W39" s="19">
+        <v>0</v>
+      </c>
+      <c r="X39" s="19">
         <v>150</v>
       </c>
-      <c r="X39" s="19">
+      <c r="Y39" s="19">
         <v>15000</v>
       </c>
-      <c r="Y39" s="19">
+      <c r="Z39" s="19">
         <v>120</v>
       </c>
-      <c r="Z39" s="19">
+      <c r="AA39" s="19">
         <v>12000</v>
       </c>
-      <c r="AA39" s="19">
-        <v>0</v>
-      </c>
       <c r="AB39" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="19">
         <v>57010001</v>
       </c>
-      <c r="AC39" s="5">
-        <v>0</v>
-      </c>
       <c r="AD39" s="5">
         <v>0</v>
       </c>
@@ -5970,8 +6137,11 @@
       <c r="AF39" s="5">
         <v>0</v>
       </c>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A40" s="19">
         <v>7010001</v>
       </c>
@@ -6037,26 +6207,26 @@
         <v>4</v>
       </c>
       <c r="W40" s="19">
+        <v>0</v>
+      </c>
+      <c r="X40" s="19">
         <v>150</v>
       </c>
-      <c r="X40" s="19">
+      <c r="Y40" s="19">
         <v>15000</v>
       </c>
-      <c r="Y40" s="19">
+      <c r="Z40" s="19">
         <v>120</v>
       </c>
-      <c r="Z40" s="19">
+      <c r="AA40" s="19">
         <v>12000</v>
       </c>
-      <c r="AA40" s="19">
-        <v>0</v>
-      </c>
       <c r="AB40" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="19">
         <v>57010001</v>
       </c>
-      <c r="AC40" s="5">
-        <v>0</v>
-      </c>
       <c r="AD40" s="5">
         <v>0</v>
       </c>
@@ -6066,8 +6236,11 @@
       <c r="AF40" s="5">
         <v>0</v>
       </c>
+      <c r="AG40" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A41" s="20">
         <v>8000001</v>
       </c>
@@ -6133,26 +6306,26 @@
         <v>3</v>
       </c>
       <c r="W41" s="20">
+        <v>0</v>
+      </c>
+      <c r="X41" s="20">
         <v>150</v>
       </c>
-      <c r="X41" s="20">
+      <c r="Y41" s="20">
         <v>15000</v>
       </c>
-      <c r="Y41" s="20">
+      <c r="Z41" s="20">
         <v>120</v>
       </c>
-      <c r="Z41" s="20">
+      <c r="AA41" s="20">
         <v>12000</v>
       </c>
-      <c r="AA41" s="20">
-        <v>0</v>
-      </c>
       <c r="AB41" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="20">
         <v>58010001</v>
       </c>
-      <c r="AC41" s="5">
-        <v>0</v>
-      </c>
       <c r="AD41" s="5">
         <v>0</v>
       </c>
@@ -6162,8 +6335,11 @@
       <c r="AF41" s="5">
         <v>0</v>
       </c>
+      <c r="AG41" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A42" s="20">
         <v>8010001</v>
       </c>
@@ -6229,26 +6405,26 @@
         <v>3</v>
       </c>
       <c r="W42" s="20">
+        <v>0</v>
+      </c>
+      <c r="X42" s="20">
         <v>150</v>
       </c>
-      <c r="X42" s="20">
+      <c r="Y42" s="20">
         <v>15000</v>
       </c>
-      <c r="Y42" s="20">
+      <c r="Z42" s="20">
         <v>120</v>
       </c>
-      <c r="Z42" s="20">
+      <c r="AA42" s="20">
         <v>12000</v>
       </c>
-      <c r="AA42" s="20">
-        <v>0</v>
-      </c>
       <c r="AB42" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="20">
         <v>58050001</v>
       </c>
-      <c r="AC42" s="5">
-        <v>0</v>
-      </c>
       <c r="AD42" s="5">
         <v>0</v>
       </c>
@@ -6258,8 +6434,11 @@
       <c r="AF42" s="5">
         <v>0</v>
       </c>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A43" s="28">
         <v>9000001</v>
       </c>
@@ -6324,25 +6503,25 @@
       <c r="V43" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="W43" s="28">
+      <c r="W43" s="32">
+        <v>0</v>
+      </c>
+      <c r="X43" s="28">
         <v>150</v>
       </c>
-      <c r="X43" s="28">
+      <c r="Y43" s="28">
         <v>15000</v>
       </c>
-      <c r="Y43" s="28">
+      <c r="Z43" s="28">
         <v>120</v>
       </c>
-      <c r="Z43" s="28">
+      <c r="AA43" s="28">
         <v>12000</v>
       </c>
-      <c r="AA43" s="28">
-        <v>0</v>
-      </c>
       <c r="AB43" s="28">
         <v>0</v>
       </c>
-      <c r="AC43" s="5">
+      <c r="AC43" s="28">
         <v>0</v>
       </c>
       <c r="AD43" s="5">
@@ -6354,8 +6533,11 @@
       <c r="AF43" s="5">
         <v>0</v>
       </c>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A44" s="30">
         <v>10010001</v>
       </c>
@@ -6421,24 +6603,24 @@
         <v>0</v>
       </c>
       <c r="W44" s="30">
+        <v>0</v>
+      </c>
+      <c r="X44" s="30">
         <v>150</v>
       </c>
-      <c r="X44" s="30">
+      <c r="Y44" s="30">
         <v>15000</v>
       </c>
-      <c r="Y44" s="30">
+      <c r="Z44" s="30">
         <v>120</v>
       </c>
-      <c r="Z44" s="30">
+      <c r="AA44" s="30">
         <v>12000</v>
       </c>
-      <c r="AA44" s="30">
-        <v>0</v>
-      </c>
       <c r="AB44" s="30">
         <v>0</v>
       </c>
-      <c r="AC44" s="5">
+      <c r="AC44" s="30">
         <v>0</v>
       </c>
       <c r="AD44" s="5">
@@ -6450,8 +6632,11 @@
       <c r="AF44" s="5">
         <v>0</v>
       </c>
+      <c r="AG44" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A45" s="30">
         <v>10020001</v>
       </c>
@@ -6517,24 +6702,24 @@
         <v>0</v>
       </c>
       <c r="W45" s="30">
+        <v>0</v>
+      </c>
+      <c r="X45" s="30">
         <v>150</v>
       </c>
-      <c r="X45" s="30">
+      <c r="Y45" s="30">
         <v>15000</v>
       </c>
-      <c r="Y45" s="30">
+      <c r="Z45" s="30">
         <v>120</v>
       </c>
-      <c r="Z45" s="30">
+      <c r="AA45" s="30">
         <v>12000</v>
       </c>
-      <c r="AA45" s="30">
-        <v>0</v>
-      </c>
       <c r="AB45" s="30">
         <v>0</v>
       </c>
-      <c r="AC45" s="5">
+      <c r="AC45" s="30">
         <v>0</v>
       </c>
       <c r="AD45" s="5">
@@ -6546,8 +6731,11 @@
       <c r="AF45" s="5">
         <v>0</v>
       </c>
+      <c r="AG45" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:33" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A46" s="31">
         <v>11010001</v>
       </c>
@@ -6613,24 +6801,24 @@
         <v>0</v>
       </c>
       <c r="W46" s="31">
+        <v>0</v>
+      </c>
+      <c r="X46" s="31">
         <v>150</v>
       </c>
-      <c r="X46" s="31">
+      <c r="Y46" s="31">
         <v>15000</v>
       </c>
-      <c r="Y46" s="31">
+      <c r="Z46" s="31">
         <v>120</v>
       </c>
-      <c r="Z46" s="31">
+      <c r="AA46" s="31">
         <v>12000</v>
       </c>
-      <c r="AA46" s="31">
-        <v>0</v>
-      </c>
       <c r="AB46" s="31">
         <v>0</v>
       </c>
-      <c r="AC46" s="5">
+      <c r="AC46" s="31">
         <v>0</v>
       </c>
       <c r="AD46" s="5">
@@ -6642,8 +6830,11 @@
       <c r="AF46" s="5">
         <v>0</v>
       </c>
+      <c r="AG46" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A47" s="23">
         <v>54010001</v>
       </c>
@@ -6723,12 +6914,12 @@
         <v>0</v>
       </c>
       <c r="AA47" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="23">
         <v>54010001</v>
       </c>
-      <c r="AB47" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="5">
+      <c r="AC47" s="23">
         <v>0</v>
       </c>
       <c r="AD47" s="5">
@@ -6740,8 +6931,11 @@
       <c r="AF47" s="5">
         <v>0</v>
       </c>
+      <c r="AG47" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A48" s="23">
         <v>54030001</v>
       </c>
@@ -6821,12 +7015,12 @@
         <v>0</v>
       </c>
       <c r="AA48" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="23">
         <v>54020001</v>
       </c>
-      <c r="AB48" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="5">
+      <c r="AC48" s="23">
         <v>0</v>
       </c>
       <c r="AD48" s="5">
@@ -6838,8 +7032,11 @@
       <c r="AF48" s="5">
         <v>0</v>
       </c>
+      <c r="AG48" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A49" s="23">
         <v>54050001</v>
       </c>
@@ -6919,12 +7116,12 @@
         <v>0</v>
       </c>
       <c r="AA49" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="23">
         <v>54030001</v>
       </c>
-      <c r="AB49" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="5">
+      <c r="AC49" s="23">
         <v>0</v>
       </c>
       <c r="AD49" s="5">
@@ -6936,8 +7133,11 @@
       <c r="AF49" s="5">
         <v>0</v>
       </c>
+      <c r="AG49" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A50" s="23">
         <v>54070001</v>
       </c>
@@ -7017,12 +7217,12 @@
         <v>0</v>
       </c>
       <c r="AA50" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="23">
         <v>54040001</v>
       </c>
-      <c r="AB50" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="5">
+      <c r="AC50" s="23">
         <v>0</v>
       </c>
       <c r="AD50" s="5">
@@ -7034,8 +7234,11 @@
       <c r="AF50" s="5">
         <v>0</v>
       </c>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A51" s="23">
         <v>54090001</v>
       </c>
@@ -7115,12 +7318,12 @@
         <v>0</v>
       </c>
       <c r="AA51" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="23">
         <v>54050001</v>
       </c>
-      <c r="AB51" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="5">
+      <c r="AC51" s="23">
         <v>0</v>
       </c>
       <c r="AD51" s="5">
@@ -7132,8 +7335,11 @@
       <c r="AF51" s="5">
         <v>0</v>
       </c>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A52" s="23">
         <v>54110001</v>
       </c>
@@ -7213,12 +7419,12 @@
         <v>0</v>
       </c>
       <c r="AA52" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="23">
         <v>54060001</v>
       </c>
-      <c r="AB52" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="5">
+      <c r="AC52" s="23">
         <v>0</v>
       </c>
       <c r="AD52" s="5">
@@ -7230,8 +7436,11 @@
       <c r="AF52" s="5">
         <v>0</v>
       </c>
+      <c r="AG52" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A53" s="23">
         <v>54130001</v>
       </c>
@@ -7311,12 +7520,12 @@
         <v>0</v>
       </c>
       <c r="AA53" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="23">
         <v>54070001</v>
       </c>
-      <c r="AB53" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="5">
+      <c r="AC53" s="23">
         <v>0</v>
       </c>
       <c r="AD53" s="5">
@@ -7328,8 +7537,11 @@
       <c r="AF53" s="5">
         <v>0</v>
       </c>
+      <c r="AG53" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A54" s="23">
         <v>54150001</v>
       </c>
@@ -7409,12 +7621,12 @@
         <v>0</v>
       </c>
       <c r="AA54" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="23">
         <v>54080001</v>
       </c>
-      <c r="AB54" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="5">
+      <c r="AC54" s="23">
         <v>0</v>
       </c>
       <c r="AD54" s="5">
@@ -7426,8 +7638,11 @@
       <c r="AF54" s="5">
         <v>0</v>
       </c>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A55" s="23">
         <v>54170001</v>
       </c>
@@ -7510,11 +7725,11 @@
         <v>0</v>
       </c>
       <c r="AB55" s="23">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="23">
         <v>54090001</v>
       </c>
-      <c r="AC55" s="5">
-        <v>0</v>
-      </c>
       <c r="AD55" s="5">
         <v>0</v>
       </c>
@@ -7524,8 +7739,11 @@
       <c r="AF55" s="5">
         <v>0</v>
       </c>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A56" s="23">
         <v>54190001</v>
       </c>
@@ -7605,12 +7823,12 @@
         <v>0</v>
       </c>
       <c r="AA56" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="23">
         <v>54100001</v>
       </c>
-      <c r="AB56" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="5">
+      <c r="AC56" s="23">
         <v>0</v>
       </c>
       <c r="AD56" s="5">
@@ -7622,8 +7840,11 @@
       <c r="AF56" s="5">
         <v>0</v>
       </c>
+      <c r="AG56" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A57" s="23">
         <v>54210001</v>
       </c>
@@ -7706,11 +7927,11 @@
         <v>0</v>
       </c>
       <c r="AB57" s="23">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="23">
         <v>54110001</v>
       </c>
-      <c r="AC57" s="5">
-        <v>0</v>
-      </c>
       <c r="AD57" s="5">
         <v>0</v>
       </c>
@@ -7720,8 +7941,11 @@
       <c r="AF57" s="5">
         <v>0</v>
       </c>
+      <c r="AG57" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A58" s="23">
         <v>54230001</v>
       </c>
@@ -7801,12 +8025,12 @@
         <v>0</v>
       </c>
       <c r="AA58" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="23">
         <v>54120001</v>
       </c>
-      <c r="AB58" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="5">
+      <c r="AC58" s="23">
         <v>0</v>
       </c>
       <c r="AD58" s="5">
@@ -7818,8 +8042,11 @@
       <c r="AF58" s="5">
         <v>0</v>
       </c>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A59" s="23">
         <v>54250001</v>
       </c>
@@ -7899,12 +8126,12 @@
         <v>0</v>
       </c>
       <c r="AA59" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="23">
         <v>54130001</v>
       </c>
-      <c r="AB59" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="5">
+      <c r="AC59" s="23">
         <v>0</v>
       </c>
       <c r="AD59" s="5">
@@ -7916,8 +8143,11 @@
       <c r="AF59" s="5">
         <v>0</v>
       </c>
+      <c r="AG59" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A60" s="23">
         <v>54010051</v>
       </c>
@@ -7997,12 +8227,12 @@
         <v>0</v>
       </c>
       <c r="AA60" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="23">
         <v>54010001</v>
       </c>
-      <c r="AB60" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="5">
+      <c r="AC60" s="23">
         <v>0</v>
       </c>
       <c r="AD60" s="5">
@@ -8014,8 +8244,11 @@
       <c r="AF60" s="5">
         <v>0</v>
       </c>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A61" s="23">
         <v>54030051</v>
       </c>
@@ -8095,12 +8328,12 @@
         <v>0</v>
       </c>
       <c r="AA61" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="23">
         <v>54020001</v>
       </c>
-      <c r="AB61" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="5">
+      <c r="AC61" s="23">
         <v>0</v>
       </c>
       <c r="AD61" s="5">
@@ -8112,8 +8345,11 @@
       <c r="AF61" s="5">
         <v>0</v>
       </c>
+      <c r="AG61" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A62" s="23">
         <v>54050051</v>
       </c>
@@ -8193,12 +8429,12 @@
         <v>0</v>
       </c>
       <c r="AA62" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="23">
         <v>54030001</v>
       </c>
-      <c r="AB62" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="5">
+      <c r="AC62" s="23">
         <v>0</v>
       </c>
       <c r="AD62" s="5">
@@ -8210,8 +8446,11 @@
       <c r="AF62" s="5">
         <v>0</v>
       </c>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A63" s="23">
         <v>54070051</v>
       </c>
@@ -8291,12 +8530,12 @@
         <v>0</v>
       </c>
       <c r="AA63" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="23">
         <v>54040001</v>
       </c>
-      <c r="AB63" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="5">
+      <c r="AC63" s="23">
         <v>0</v>
       </c>
       <c r="AD63" s="5">
@@ -8308,8 +8547,11 @@
       <c r="AF63" s="5">
         <v>0</v>
       </c>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A64" s="23">
         <v>54090051</v>
       </c>
@@ -8389,12 +8631,12 @@
         <v>0</v>
       </c>
       <c r="AA64" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="23">
         <v>54050001</v>
       </c>
-      <c r="AB64" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="5">
+      <c r="AC64" s="23">
         <v>0</v>
       </c>
       <c r="AD64" s="5">
@@ -8406,8 +8648,11 @@
       <c r="AF64" s="5">
         <v>0</v>
       </c>
+      <c r="AG64" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A65" s="23">
         <v>54110051</v>
       </c>
@@ -8487,12 +8732,12 @@
         <v>0</v>
       </c>
       <c r="AA65" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="23">
         <v>54060001</v>
       </c>
-      <c r="AB65" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="5">
+      <c r="AC65" s="23">
         <v>0</v>
       </c>
       <c r="AD65" s="5">
@@ -8504,8 +8749,11 @@
       <c r="AF65" s="5">
         <v>0</v>
       </c>
+      <c r="AG65" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A66" s="23">
         <v>54130051</v>
       </c>
@@ -8585,12 +8833,12 @@
         <v>0</v>
       </c>
       <c r="AA66" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="23">
         <v>54070001</v>
       </c>
-      <c r="AB66" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC66" s="5">
+      <c r="AC66" s="23">
         <v>0</v>
       </c>
       <c r="AD66" s="5">
@@ -8602,8 +8850,11 @@
       <c r="AF66" s="5">
         <v>0</v>
       </c>
+      <c r="AG66" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A67" s="23">
         <v>54150051</v>
       </c>
@@ -8683,12 +8934,12 @@
         <v>0</v>
       </c>
       <c r="AA67" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="23">
         <v>54080001</v>
       </c>
-      <c r="AB67" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="5">
+      <c r="AC67" s="23">
         <v>0</v>
       </c>
       <c r="AD67" s="5">
@@ -8700,8 +8951,11 @@
       <c r="AF67" s="5">
         <v>0</v>
       </c>
+      <c r="AG67" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A68" s="23">
         <v>54170051</v>
       </c>
@@ -8784,11 +9038,11 @@
         <v>0</v>
       </c>
       <c r="AB68" s="23">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="23">
         <v>54090001</v>
       </c>
-      <c r="AC68" s="5">
-        <v>0</v>
-      </c>
       <c r="AD68" s="5">
         <v>0</v>
       </c>
@@ -8798,8 +9052,11 @@
       <c r="AF68" s="5">
         <v>0</v>
       </c>
+      <c r="AG68" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A69" s="23">
         <v>54190051</v>
       </c>
@@ -8879,12 +9136,12 @@
         <v>0</v>
       </c>
       <c r="AA69" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="23">
         <v>54100001</v>
       </c>
-      <c r="AB69" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC69" s="5">
+      <c r="AC69" s="23">
         <v>0</v>
       </c>
       <c r="AD69" s="5">
@@ -8896,8 +9153,11 @@
       <c r="AF69" s="5">
         <v>0</v>
       </c>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A70" s="23">
         <v>54210051</v>
       </c>
@@ -8980,11 +9240,11 @@
         <v>0</v>
       </c>
       <c r="AB70" s="23">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="23">
         <v>54110001</v>
       </c>
-      <c r="AC70" s="5">
-        <v>0</v>
-      </c>
       <c r="AD70" s="5">
         <v>0</v>
       </c>
@@ -8994,8 +9254,11 @@
       <c r="AF70" s="5">
         <v>0</v>
       </c>
+      <c r="AG70" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A71" s="23">
         <v>54230051</v>
       </c>
@@ -9075,12 +9338,12 @@
         <v>0</v>
       </c>
       <c r="AA71" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="23">
         <v>54120001</v>
       </c>
-      <c r="AB71" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC71" s="5">
+      <c r="AC71" s="23">
         <v>0</v>
       </c>
       <c r="AD71" s="5">
@@ -9092,8 +9355,11 @@
       <c r="AF71" s="5">
         <v>0</v>
       </c>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A72" s="23">
         <v>54250051</v>
       </c>
@@ -9173,12 +9439,12 @@
         <v>0</v>
       </c>
       <c r="AA72" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="23">
         <v>54130001</v>
       </c>
-      <c r="AB72" s="23">
-        <v>0</v>
-      </c>
-      <c r="AC72" s="5">
+      <c r="AC72" s="23">
         <v>0</v>
       </c>
       <c r="AD72" s="5">
@@ -9190,8 +9456,11 @@
       <c r="AF72" s="5">
         <v>0</v>
       </c>
+      <c r="AG72" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A73" s="13">
         <v>55010001</v>
       </c>
@@ -9262,23 +9531,23 @@
         <v>0</v>
       </c>
       <c r="X73" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y73" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z73" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA73" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB73" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="13">
         <v>55010001</v>
       </c>
-      <c r="AC73" s="5">
-        <v>0</v>
-      </c>
       <c r="AD73" s="5">
         <v>0</v>
       </c>
@@ -9288,8 +9557,11 @@
       <c r="AF73" s="5">
         <v>0</v>
       </c>
+      <c r="AG73" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A74" s="13">
         <v>55020001</v>
       </c>
@@ -9360,23 +9632,23 @@
         <v>0</v>
       </c>
       <c r="X74" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z74" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA74" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AB74" s="13">
         <v>55020001</v>
       </c>
-      <c r="AB74" s="13">
+      <c r="AC74" s="13">
         <v>55010001</v>
       </c>
-      <c r="AC74" s="5">
-        <v>0</v>
-      </c>
       <c r="AD74" s="5">
         <v>0</v>
       </c>
@@ -9386,8 +9658,11 @@
       <c r="AF74" s="5">
         <v>0</v>
       </c>
+      <c r="AG74" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A75" s="13">
         <v>55030001</v>
       </c>
@@ -9458,21 +9733,21 @@
         <v>0</v>
       </c>
       <c r="X75" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y75" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z75" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA75" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AB75" s="13">
         <v>55030001</v>
       </c>
-      <c r="AB75" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC75" s="5">
+      <c r="AC75" s="13">
         <v>0</v>
       </c>
       <c r="AD75" s="5">
@@ -9484,8 +9759,11 @@
       <c r="AF75" s="5">
         <v>0</v>
       </c>
+      <c r="AG75" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A76" s="13">
         <v>55040001</v>
       </c>
@@ -9556,21 +9834,21 @@
         <v>0</v>
       </c>
       <c r="X76" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z76" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA76" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AB76" s="13">
         <v>55040001</v>
       </c>
-      <c r="AB76" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC76" s="5">
+      <c r="AC76" s="13">
         <v>0</v>
       </c>
       <c r="AD76" s="5">
@@ -9582,8 +9860,11 @@
       <c r="AF76" s="5">
         <v>0</v>
       </c>
+      <c r="AG76" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A77" s="13">
         <v>55050001</v>
       </c>
@@ -9654,23 +9935,23 @@
         <v>0</v>
       </c>
       <c r="X77" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y77" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z77" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA77" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB77" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="13">
         <v>55050001</v>
       </c>
-      <c r="AC77" s="5">
-        <v>0</v>
-      </c>
       <c r="AD77" s="5">
         <v>0</v>
       </c>
@@ -9680,8 +9961,11 @@
       <c r="AF77" s="5">
         <v>0</v>
       </c>
+      <c r="AG77" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A78" s="13">
         <v>55060001</v>
       </c>
@@ -9752,21 +10036,21 @@
         <v>0</v>
       </c>
       <c r="X78" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y78" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z78" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA78" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AB78" s="13">
         <v>55060001</v>
       </c>
-      <c r="AB78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="5">
+      <c r="AC78" s="13">
         <v>0</v>
       </c>
       <c r="AD78" s="5">
@@ -9778,8 +10062,11 @@
       <c r="AF78" s="5">
         <v>0</v>
       </c>
+      <c r="AG78" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A79" s="13">
         <v>55070001</v>
       </c>
@@ -9850,21 +10137,21 @@
         <v>0</v>
       </c>
       <c r="X79" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z79" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA79" s="13">
+        <v>10000</v>
+      </c>
+      <c r="AB79" s="13">
         <v>55070001</v>
       </c>
-      <c r="AB79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC79" s="5">
+      <c r="AC79" s="13">
         <v>0</v>
       </c>
       <c r="AD79" s="5">
@@ -9876,8 +10163,11 @@
       <c r="AF79" s="5">
         <v>0</v>
       </c>
+      <c r="AG79" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A80" s="14">
         <v>56010001</v>
       </c>
@@ -9948,23 +10238,23 @@
         <v>0</v>
       </c>
       <c r="X80" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z80" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA80" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="14">
         <v>56010001</v>
       </c>
-      <c r="AC80" s="5">
-        <v>0</v>
-      </c>
       <c r="AD80" s="5">
         <v>0</v>
       </c>
@@ -9974,8 +10264,11 @@
       <c r="AF80" s="5">
         <v>0</v>
       </c>
+      <c r="AG80" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A81" s="14">
         <v>56040001</v>
       </c>
@@ -10046,21 +10339,21 @@
         <v>0</v>
       </c>
       <c r="X81" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z81" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA81" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB81" s="14">
         <v>0</v>
       </c>
-      <c r="AC81" s="5">
+      <c r="AC81" s="14">
         <v>0</v>
       </c>
       <c r="AD81" s="5">
@@ -10072,8 +10365,11 @@
       <c r="AF81" s="5">
         <v>0</v>
       </c>
+      <c r="AG81" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A82" s="14">
         <v>56060001</v>
       </c>
@@ -10144,23 +10440,23 @@
         <v>0</v>
       </c>
       <c r="X82" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y82" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z82" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="14">
         <v>56030001</v>
       </c>
-      <c r="AC82" s="5">
-        <v>0</v>
-      </c>
       <c r="AD82" s="5">
         <v>0</v>
       </c>
@@ -10170,8 +10466,11 @@
       <c r="AF82" s="5">
         <v>0</v>
       </c>
+      <c r="AG82" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A83" s="14">
         <v>56080001</v>
       </c>
@@ -10242,21 +10541,21 @@
         <v>0</v>
       </c>
       <c r="X83" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z83" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="14">
+        <v>10000</v>
+      </c>
+      <c r="AB83" s="14">
         <v>56040001</v>
       </c>
-      <c r="AB83" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="5">
+      <c r="AC83" s="14">
         <v>0</v>
       </c>
       <c r="AD83" s="5">
@@ -10268,8 +10567,11 @@
       <c r="AF83" s="5">
         <v>0</v>
       </c>
+      <c r="AG83" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A84" s="14">
         <v>56100001</v>
       </c>
@@ -10340,23 +10642,23 @@
         <v>0</v>
       </c>
       <c r="X84" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y84" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z84" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA84" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB84" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="14">
         <v>56050001</v>
       </c>
-      <c r="AC84" s="5">
-        <v>0</v>
-      </c>
       <c r="AD84" s="5">
         <v>0</v>
       </c>
@@ -10366,8 +10668,11 @@
       <c r="AF84" s="5">
         <v>0</v>
       </c>
+      <c r="AG84" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A85" s="14">
         <v>56130001</v>
       </c>
@@ -10438,23 +10743,23 @@
         <v>0</v>
       </c>
       <c r="X85" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y85" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z85" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA85" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB85" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="14">
         <v>56060001</v>
       </c>
-      <c r="AC85" s="5">
-        <v>0</v>
-      </c>
       <c r="AD85" s="5">
         <v>0</v>
       </c>
@@ -10464,8 +10769,11 @@
       <c r="AF85" s="5">
         <v>0</v>
       </c>
+      <c r="AG85" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A86" s="15">
         <v>57010001</v>
       </c>
@@ -10536,23 +10844,23 @@
         <v>0</v>
       </c>
       <c r="X86" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y86" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z86" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA86" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB86" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="15">
         <v>57010001</v>
       </c>
-      <c r="AC86" s="5">
-        <v>0</v>
-      </c>
       <c r="AD86" s="5">
         <v>0</v>
       </c>
@@ -10562,8 +10870,11 @@
       <c r="AF86" s="5">
         <v>0</v>
       </c>
+      <c r="AG86" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A87" s="15">
         <v>57040001</v>
       </c>
@@ -10634,21 +10945,21 @@
         <v>0</v>
       </c>
       <c r="X87" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y87" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z87" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA87" s="15">
+        <v>10000</v>
+      </c>
+      <c r="AB87" s="15">
         <v>57020001</v>
       </c>
-      <c r="AB87" s="15">
-        <v>0</v>
-      </c>
-      <c r="AC87" s="5">
+      <c r="AC87" s="15">
         <v>0</v>
       </c>
       <c r="AD87" s="5">
@@ -10660,8 +10971,11 @@
       <c r="AF87" s="5">
         <v>0</v>
       </c>
+      <c r="AG87" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
         <v>57060001</v>
       </c>
@@ -10732,21 +11046,21 @@
         <v>0</v>
       </c>
       <c r="X88" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y88" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z88" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA88" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB88" s="15">
         <v>0</v>
       </c>
-      <c r="AC88" s="5">
+      <c r="AC88" s="15">
         <v>0</v>
       </c>
       <c r="AD88" s="5">
@@ -10758,8 +11072,11 @@
       <c r="AF88" s="5">
         <v>0</v>
       </c>
+      <c r="AG88" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A89" s="15">
         <v>57080001</v>
       </c>
@@ -10830,23 +11147,23 @@
         <v>0</v>
       </c>
       <c r="X89" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z89" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA89" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB89" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="15">
         <v>57040001</v>
       </c>
-      <c r="AC89" s="5">
-        <v>0</v>
-      </c>
       <c r="AD89" s="5">
         <v>0</v>
       </c>
@@ -10856,8 +11173,11 @@
       <c r="AF89" s="5">
         <v>0</v>
       </c>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A90" s="15">
         <v>57100001</v>
       </c>
@@ -10928,21 +11248,21 @@
         <v>0</v>
       </c>
       <c r="X90" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y90" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z90" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA90" s="15">
+        <v>10000</v>
+      </c>
+      <c r="AB90" s="15">
         <v>57050001</v>
       </c>
-      <c r="AB90" s="15">
-        <v>0</v>
-      </c>
-      <c r="AC90" s="5">
+      <c r="AC90" s="15">
         <v>0</v>
       </c>
       <c r="AD90" s="5">
@@ -10954,8 +11274,11 @@
       <c r="AF90" s="5">
         <v>0</v>
       </c>
+      <c r="AG90" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A91" s="15">
         <v>57120001</v>
       </c>
@@ -11026,23 +11349,23 @@
         <v>0</v>
       </c>
       <c r="X91" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z91" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB91" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="15">
         <v>57060001</v>
       </c>
-      <c r="AC91" s="5">
-        <v>0</v>
-      </c>
       <c r="AD91" s="5">
         <v>0</v>
       </c>
@@ -11052,8 +11375,11 @@
       <c r="AF91" s="5">
         <v>0</v>
       </c>
+      <c r="AG91" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A92" s="16">
         <v>58010001</v>
       </c>
@@ -11124,23 +11450,23 @@
         <v>0</v>
       </c>
       <c r="X92" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z92" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA92" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB92" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="16">
         <v>58010001</v>
       </c>
-      <c r="AC92" s="5">
-        <v>0</v>
-      </c>
       <c r="AD92" s="5">
         <v>0</v>
       </c>
@@ -11150,8 +11476,11 @@
       <c r="AF92" s="5">
         <v>0</v>
       </c>
+      <c r="AG92" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A93" s="16">
         <v>58040001</v>
       </c>
@@ -11222,21 +11551,21 @@
         <v>0</v>
       </c>
       <c r="X93" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y93" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z93" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA93" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB93" s="16">
         <v>0</v>
       </c>
-      <c r="AC93" s="5">
+      <c r="AC93" s="16">
         <v>0</v>
       </c>
       <c r="AD93" s="5">
@@ -11248,8 +11577,11 @@
       <c r="AF93" s="5">
         <v>0</v>
       </c>
+      <c r="AG93" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A94" s="16">
         <v>58060001</v>
       </c>
@@ -11320,21 +11652,21 @@
         <v>0</v>
       </c>
       <c r="X94" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y94" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z94" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="16">
+        <v>10000</v>
+      </c>
+      <c r="AB94" s="16">
         <v>58030001</v>
       </c>
-      <c r="AB94" s="16">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="5">
+      <c r="AC94" s="16">
         <v>0</v>
       </c>
       <c r="AD94" s="5">
@@ -11346,8 +11678,11 @@
       <c r="AF94" s="5">
         <v>0</v>
       </c>
+      <c r="AG94" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A95" s="16">
         <v>58080001</v>
       </c>
@@ -11418,23 +11753,23 @@
         <v>0</v>
       </c>
       <c r="X95" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y95" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z95" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA95" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB95" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="16">
         <v>58040001</v>
       </c>
-      <c r="AC95" s="5">
-        <v>0</v>
-      </c>
       <c r="AD95" s="5">
         <v>0</v>
       </c>
@@ -11444,8 +11779,11 @@
       <c r="AF95" s="5">
         <v>0</v>
       </c>
+      <c r="AG95" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A96" s="16">
         <v>58110001</v>
       </c>
@@ -11516,23 +11854,23 @@
         <v>0</v>
       </c>
       <c r="X96" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z96" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA96" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB96" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="16">
         <v>58050001</v>
       </c>
-      <c r="AC96" s="5">
-        <v>0</v>
-      </c>
       <c r="AD96" s="5">
         <v>0</v>
       </c>
@@ -11542,8 +11880,11 @@
       <c r="AF96" s="5">
         <v>0</v>
       </c>
+      <c r="AG96" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A97" s="24">
         <v>59010001</v>
       </c>
@@ -11614,21 +11955,21 @@
         <v>0</v>
       </c>
       <c r="X97" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y97" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z97" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA97" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB97" s="24">
         <v>59010001</v>
       </c>
-      <c r="AB97" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC97" s="5">
+      <c r="AC97" s="24">
         <v>0</v>
       </c>
       <c r="AD97" s="5">
@@ -11640,8 +11981,11 @@
       <c r="AF97" s="5">
         <v>0</v>
       </c>
+      <c r="AG97" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A98" s="24">
         <v>59030001</v>
       </c>
@@ -11712,21 +12056,21 @@
         <v>0</v>
       </c>
       <c r="X98" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y98" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z98" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB98" s="24">
         <v>59020001</v>
       </c>
-      <c r="AB98" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC98" s="5">
+      <c r="AC98" s="24">
         <v>0</v>
       </c>
       <c r="AD98" s="5">
@@ -11738,8 +12082,11 @@
       <c r="AF98" s="5">
         <v>0</v>
       </c>
+      <c r="AG98" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A99" s="24">
         <v>59050001</v>
       </c>
@@ -11810,21 +12157,21 @@
         <v>0</v>
       </c>
       <c r="X99" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y99" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z99" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA99" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB99" s="24">
         <v>59030001</v>
       </c>
-      <c r="AB99" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC99" s="5">
+      <c r="AC99" s="24">
         <v>0</v>
       </c>
       <c r="AD99" s="5">
@@ -11836,8 +12183,11 @@
       <c r="AF99" s="5">
         <v>0</v>
       </c>
+      <c r="AG99" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A100" s="24">
         <v>59070001</v>
       </c>
@@ -11908,21 +12258,21 @@
         <v>0</v>
       </c>
       <c r="X100" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z100" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA100" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB100" s="24">
         <v>59040001</v>
       </c>
-      <c r="AB100" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="5">
+      <c r="AC100" s="24">
         <v>0</v>
       </c>
       <c r="AD100" s="5">
@@ -11934,8 +12284,11 @@
       <c r="AF100" s="5">
         <v>0</v>
       </c>
+      <c r="AG100" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A101" s="24">
         <v>59090001</v>
       </c>
@@ -12006,21 +12359,21 @@
         <v>0</v>
       </c>
       <c r="X101" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z101" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA101" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB101" s="24">
         <v>59050001</v>
       </c>
-      <c r="AB101" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="5">
+      <c r="AC101" s="24">
         <v>0</v>
       </c>
       <c r="AD101" s="5">
@@ -12032,8 +12385,11 @@
       <c r="AF101" s="5">
         <v>0</v>
       </c>
+      <c r="AG101" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A102" s="24">
         <v>59110001</v>
       </c>
@@ -12104,21 +12460,21 @@
         <v>0</v>
       </c>
       <c r="X102" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z102" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB102" s="24">
         <v>59060001</v>
       </c>
-      <c r="AB102" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="5">
+      <c r="AC102" s="24">
         <v>0</v>
       </c>
       <c r="AD102" s="5">
@@ -12130,8 +12486,11 @@
       <c r="AF102" s="5">
         <v>0</v>
       </c>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A103" s="24">
         <v>59130001</v>
       </c>
@@ -12202,21 +12561,21 @@
         <v>0</v>
       </c>
       <c r="X103" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y103" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z103" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA103" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB103" s="24">
         <v>59070001</v>
       </c>
-      <c r="AB103" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="5">
+      <c r="AC103" s="24">
         <v>0</v>
       </c>
       <c r="AD103" s="5">
@@ -12228,8 +12587,11 @@
       <c r="AF103" s="5">
         <v>0</v>
       </c>
+      <c r="AG103" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A104" s="24">
         <v>59150001</v>
       </c>
@@ -12300,21 +12662,21 @@
         <v>0</v>
       </c>
       <c r="X104" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y104" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z104" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA104" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB104" s="24">
         <v>59080001</v>
       </c>
-      <c r="AB104" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC104" s="5">
+      <c r="AC104" s="24">
         <v>0</v>
       </c>
       <c r="AD104" s="5">
@@ -12326,8 +12688,11 @@
       <c r="AF104" s="5">
         <v>0</v>
       </c>
+      <c r="AG104" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A105" s="24">
         <v>59180001</v>
       </c>
@@ -12398,21 +12763,21 @@
         <v>0</v>
       </c>
       <c r="X105" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y105" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z105" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA105" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB105" s="24">
         <v>59090001</v>
       </c>
-      <c r="AB105" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC105" s="5">
+      <c r="AC105" s="24">
         <v>0</v>
       </c>
       <c r="AD105" s="5">
@@ -12424,8 +12789,11 @@
       <c r="AF105" s="5">
         <v>0</v>
       </c>
+      <c r="AG105" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A106" s="24">
         <v>59200001</v>
       </c>
@@ -12496,21 +12864,21 @@
         <v>0</v>
       </c>
       <c r="X106" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y106" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z106" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA106" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB106" s="24">
         <v>59100001</v>
       </c>
-      <c r="AB106" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC106" s="5">
+      <c r="AC106" s="24">
         <v>0</v>
       </c>
       <c r="AD106" s="5">
@@ -12522,8 +12890,11 @@
       <c r="AF106" s="5">
         <v>0</v>
       </c>
+      <c r="AG106" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A107" s="24">
         <v>59220001</v>
       </c>
@@ -12594,21 +12965,21 @@
         <v>0</v>
       </c>
       <c r="X107" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y107" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z107" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA107" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB107" s="24">
         <v>59110001</v>
       </c>
-      <c r="AB107" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC107" s="5">
+      <c r="AC107" s="24">
         <v>0</v>
       </c>
       <c r="AD107" s="5">
@@ -12620,8 +12991,11 @@
       <c r="AF107" s="5">
         <v>0</v>
       </c>
+      <c r="AG107" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A108" s="24">
         <v>59240001</v>
       </c>
@@ -12692,21 +13066,21 @@
         <v>0</v>
       </c>
       <c r="X108" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y108" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z108" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA108" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB108" s="24">
         <v>59120001</v>
       </c>
-      <c r="AB108" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC108" s="5">
+      <c r="AC108" s="24">
         <v>0</v>
       </c>
       <c r="AD108" s="5">
@@ -12718,8 +13092,11 @@
       <c r="AF108" s="5">
         <v>0</v>
       </c>
+      <c r="AG108" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A109" s="24">
         <v>59260001</v>
       </c>
@@ -12790,21 +13167,21 @@
         <v>0</v>
       </c>
       <c r="X109" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y109" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z109" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA109" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB109" s="24">
         <v>59130001</v>
       </c>
-      <c r="AB109" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC109" s="5">
+      <c r="AC109" s="24">
         <v>0</v>
       </c>
       <c r="AD109" s="5">
@@ -12816,8 +13193,11 @@
       <c r="AF109" s="5">
         <v>0</v>
       </c>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A110" s="24">
         <v>59280001</v>
       </c>
@@ -12888,21 +13268,21 @@
         <v>0</v>
       </c>
       <c r="X110" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y110" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z110" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA110" s="24">
+        <v>10000</v>
+      </c>
+      <c r="AB110" s="24">
         <v>59140001</v>
       </c>
-      <c r="AB110" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC110" s="5">
+      <c r="AC110" s="24">
         <v>0</v>
       </c>
       <c r="AD110" s="5">
@@ -12914,8 +13294,11 @@
       <c r="AF110" s="5">
         <v>0</v>
       </c>
+      <c r="AG110" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A111" s="25">
         <v>60010001</v>
       </c>
@@ -12986,21 +13369,21 @@
         <v>0</v>
       </c>
       <c r="X111" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y111" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z111" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA111" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AB111" s="25">
         <v>60010001</v>
       </c>
-      <c r="AB111" s="25">
-        <v>0</v>
-      </c>
-      <c r="AC111" s="5">
+      <c r="AC111" s="25">
         <v>0</v>
       </c>
       <c r="AD111" s="5">
@@ -13012,8 +13395,11 @@
       <c r="AF111" s="5">
         <v>0</v>
       </c>
+      <c r="AG111" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A112" s="25">
         <v>60030001</v>
       </c>
@@ -13084,21 +13470,21 @@
         <v>0</v>
       </c>
       <c r="X112" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y112" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z112" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA112" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AB112" s="25">
         <v>60020001</v>
       </c>
-      <c r="AB112" s="25">
-        <v>0</v>
-      </c>
-      <c r="AC112" s="5">
+      <c r="AC112" s="25">
         <v>0</v>
       </c>
       <c r="AD112" s="5">
@@ -13110,8 +13496,11 @@
       <c r="AF112" s="5">
         <v>0</v>
       </c>
+      <c r="AG112" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A113" s="25">
         <v>60060001</v>
       </c>
@@ -13182,21 +13571,21 @@
         <v>0</v>
       </c>
       <c r="X113" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y113" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z113" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA113" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AB113" s="25">
         <v>60030001</v>
       </c>
-      <c r="AB113" s="25">
-        <v>0</v>
-      </c>
-      <c r="AC113" s="5">
+      <c r="AC113" s="25">
         <v>0</v>
       </c>
       <c r="AD113" s="5">
@@ -13208,8 +13597,11 @@
       <c r="AF113" s="5">
         <v>0</v>
       </c>
+      <c r="AG113" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A114" s="25">
         <v>60090001</v>
       </c>
@@ -13280,21 +13672,21 @@
         <v>0</v>
       </c>
       <c r="X114" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y114" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z114" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA114" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AB114" s="25">
         <v>60040001</v>
       </c>
-      <c r="AB114" s="25">
-        <v>0</v>
-      </c>
-      <c r="AC114" s="5">
+      <c r="AC114" s="25">
         <v>0</v>
       </c>
       <c r="AD114" s="5">
@@ -13306,8 +13698,11 @@
       <c r="AF114" s="5">
         <v>0</v>
       </c>
+      <c r="AG114" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A115" s="25">
         <v>60110001</v>
       </c>
@@ -13378,21 +13773,21 @@
         <v>0</v>
       </c>
       <c r="X115" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y115" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z115" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA115" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AB115" s="25">
         <v>60080001</v>
       </c>
-      <c r="AB115" s="26">
-        <v>0</v>
-      </c>
-      <c r="AC115" s="5">
+      <c r="AC115" s="26">
         <v>0</v>
       </c>
       <c r="AD115" s="5">
@@ -13404,8 +13799,11 @@
       <c r="AF115" s="5">
         <v>0</v>
       </c>
+      <c r="AG115" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A116" s="25">
         <v>60120001</v>
       </c>
@@ -13476,21 +13874,21 @@
         <v>0</v>
       </c>
       <c r="X116" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y116" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z116" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="25">
+        <v>10000</v>
+      </c>
+      <c r="AB116" s="25">
         <v>60070001</v>
       </c>
-      <c r="AB116" s="26">
-        <v>0</v>
-      </c>
-      <c r="AC116" s="5">
+      <c r="AC116" s="26">
         <v>0</v>
       </c>
       <c r="AD116" s="5">
@@ -13502,8 +13900,11 @@
       <c r="AF116" s="5">
         <v>0</v>
       </c>
+      <c r="AG116" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A117" s="25">
         <v>60130001</v>
       </c>
@@ -13574,23 +13975,23 @@
         <v>0</v>
       </c>
       <c r="X117" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y117" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z117" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA117" s="25">
-        <v>0</v>
-      </c>
-      <c r="AB117" s="26" t="s">
+        <v>10000</v>
+      </c>
+      <c r="AB117" s="25">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="AC117" s="5">
-        <v>0</v>
-      </c>
       <c r="AD117" s="5">
         <v>0</v>
       </c>
@@ -13600,8 +14001,11 @@
       <c r="AF117" s="5">
         <v>0</v>
       </c>
+      <c r="AG117" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A118" s="27">
         <v>61020001</v>
       </c>
@@ -13672,21 +14076,21 @@
         <v>0</v>
       </c>
       <c r="X118" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y118" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z118" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA118" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB118" s="27">
         <v>61010001</v>
       </c>
-      <c r="AB118" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC118" s="5">
+      <c r="AC118" s="27">
         <v>0</v>
       </c>
       <c r="AD118" s="5">
@@ -13698,8 +14102,11 @@
       <c r="AF118" s="5">
         <v>0</v>
       </c>
+      <c r="AG118" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A119" s="27">
         <v>61040001</v>
       </c>
@@ -13770,21 +14177,21 @@
         <v>0</v>
       </c>
       <c r="X119" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y119" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z119" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA119" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB119" s="27">
         <v>61020001</v>
       </c>
-      <c r="AB119" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC119" s="5">
+      <c r="AC119" s="27">
         <v>0</v>
       </c>
       <c r="AD119" s="5">
@@ -13796,8 +14203,11 @@
       <c r="AF119" s="5">
         <v>0</v>
       </c>
+      <c r="AG119" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A120" s="27">
         <v>61060001</v>
       </c>
@@ -13868,21 +14278,21 @@
         <v>0</v>
       </c>
       <c r="X120" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y120" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z120" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA120" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB120" s="27">
         <v>61030001</v>
       </c>
-      <c r="AB120" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC120" s="5">
+      <c r="AC120" s="27">
         <v>0</v>
       </c>
       <c r="AD120" s="5">
@@ -13894,8 +14304,11 @@
       <c r="AF120" s="5">
         <v>0</v>
       </c>
+      <c r="AG120" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A121" s="27">
         <v>61080001</v>
       </c>
@@ -13966,21 +14379,21 @@
         <v>0</v>
       </c>
       <c r="X121" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y121" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z121" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA121" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB121" s="27">
         <v>61040001</v>
       </c>
-      <c r="AB121" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC121" s="5">
+      <c r="AC121" s="27">
         <v>0</v>
       </c>
       <c r="AD121" s="5">
@@ -13992,8 +14405,11 @@
       <c r="AF121" s="5">
         <v>0</v>
       </c>
+      <c r="AG121" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A122" s="27">
         <v>61100001</v>
       </c>
@@ -14064,21 +14480,21 @@
         <v>0</v>
       </c>
       <c r="X122" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y122" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z122" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA122" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB122" s="27">
         <v>61050001</v>
       </c>
-      <c r="AB122" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC122" s="5">
+      <c r="AC122" s="27">
         <v>0</v>
       </c>
       <c r="AD122" s="5">
@@ -14090,8 +14506,11 @@
       <c r="AF122" s="5">
         <v>0</v>
       </c>
+      <c r="AG122" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A123" s="27">
         <v>61120001</v>
       </c>
@@ -14162,21 +14581,21 @@
         <v>0</v>
       </c>
       <c r="X123" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y123" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z123" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA123" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB123" s="27">
         <v>61060001</v>
       </c>
-      <c r="AB123" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC123" s="5">
+      <c r="AC123" s="27">
         <v>0</v>
       </c>
       <c r="AD123" s="5">
@@ -14188,8 +14607,11 @@
       <c r="AF123" s="5">
         <v>0</v>
       </c>
+      <c r="AG123" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A124" s="27">
         <v>61140001</v>
       </c>
@@ -14260,21 +14682,21 @@
         <v>0</v>
       </c>
       <c r="X124" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y124" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z124" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA124" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB124" s="27">
         <v>61070001</v>
       </c>
-      <c r="AB124" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC124" s="5">
+      <c r="AC124" s="27">
         <v>0</v>
       </c>
       <c r="AD124" s="5">
@@ -14286,8 +14708,11 @@
       <c r="AF124" s="5">
         <v>0</v>
       </c>
+      <c r="AG124" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A125" s="27">
         <v>61160001</v>
       </c>
@@ -14358,21 +14783,21 @@
         <v>0</v>
       </c>
       <c r="X125" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y125" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z125" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA125" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB125" s="27">
         <v>61080001</v>
       </c>
-      <c r="AB125" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC125" s="5">
+      <c r="AC125" s="27">
         <v>0</v>
       </c>
       <c r="AD125" s="5">
@@ -14384,8 +14809,11 @@
       <c r="AF125" s="5">
         <v>0</v>
       </c>
+      <c r="AG125" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A126" s="27">
         <v>61180001</v>
       </c>
@@ -14456,21 +14884,21 @@
         <v>0</v>
       </c>
       <c r="X126" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y126" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z126" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA126" s="27">
+        <v>10000</v>
+      </c>
+      <c r="AB126" s="27">
         <v>61090001</v>
       </c>
-      <c r="AB126" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC126" s="5">
+      <c r="AC126" s="27">
         <v>0</v>
       </c>
       <c r="AD126" s="5">
@@ -14482,8 +14910,11 @@
       <c r="AF126" s="5">
         <v>0</v>
       </c>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A127" s="5">
         <v>955001001</v>
       </c>
@@ -14560,12 +14991,12 @@
         <v>0</v>
       </c>
       <c r="AA127" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB127" s="27">
         <v>855001001</v>
       </c>
-      <c r="AB127" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC127" s="5">
+      <c r="AC127" s="27">
         <v>0</v>
       </c>
       <c r="AD127" s="5">
@@ -14577,8 +15008,11 @@
       <c r="AF127" s="5">
         <v>0</v>
       </c>
+      <c r="AG127" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A128" s="5">
         <v>955001002</v>
       </c>
@@ -14658,12 +15092,12 @@
         <v>0</v>
       </c>
       <c r="AA128" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB128" s="27">
         <v>855001002</v>
       </c>
-      <c r="AB128" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC128" s="5">
+      <c r="AC128" s="27">
         <v>0</v>
       </c>
       <c r="AD128" s="5">
@@ -14675,8 +15109,11 @@
       <c r="AF128" s="5">
         <v>0</v>
       </c>
+      <c r="AG128" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="129" spans="1:32" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A129" s="36">
         <v>95000100</v>
       </c>
@@ -14756,12 +15193,12 @@
         <v>0</v>
       </c>
       <c r="AA129" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB129" s="36">
         <v>85000100</v>
       </c>
-      <c r="AB129" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC129" s="5">
+      <c r="AC129" s="36">
         <v>0</v>
       </c>
       <c r="AD129" s="5">
@@ -14773,8 +15210,11 @@
       <c r="AF129" s="5">
         <v>0</v>
       </c>
+      <c r="AG129" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="130" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A130" s="36">
         <v>95000101</v>
       </c>
@@ -14845,34 +15285,37 @@
         <v>0</v>
       </c>
       <c r="X130" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="36">
         <v>27000</v>
       </c>
-      <c r="Y130" s="36">
-        <v>0</v>
-      </c>
       <c r="Z130" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="36">
         <v>27000</v>
       </c>
-      <c r="AA130" s="36">
+      <c r="AB130" s="36">
         <v>85001100</v>
       </c>
-      <c r="AB130" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC130" s="5">
+      <c r="AC130" s="36">
         <v>0</v>
       </c>
       <c r="AD130" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE130" s="5">
         <v>95001300</v>
       </c>
-      <c r="AE130" s="5">
-        <v>0</v>
-      </c>
       <c r="AF130" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG130" s="5">
         <v>95001500</v>
       </c>
     </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A131" s="5">
         <v>95000300</v>
       </c>
@@ -14952,12 +15395,12 @@
         <v>0</v>
       </c>
       <c r="AA131" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="36">
         <v>85000300</v>
       </c>
-      <c r="AB131" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC131" s="5">
+      <c r="AC131" s="36">
         <v>0</v>
       </c>
       <c r="AD131" s="5">
@@ -14969,8 +15412,11 @@
       <c r="AF131" s="5">
         <v>0</v>
       </c>
+      <c r="AG131" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A132" s="5">
         <v>95000500</v>
       </c>
@@ -15050,12 +15496,12 @@
         <v>0</v>
       </c>
       <c r="AA132" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="36">
         <v>85000500</v>
       </c>
-      <c r="AB132" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC132" s="5">
+      <c r="AC132" s="36">
         <v>0</v>
       </c>
       <c r="AD132" s="5">
@@ -15067,8 +15513,11 @@
       <c r="AF132" s="5">
         <v>0</v>
       </c>
+      <c r="AG132" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A133" s="5">
         <v>95000700</v>
       </c>
@@ -15148,12 +15597,12 @@
         <v>0</v>
       </c>
       <c r="AA133" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="36">
         <v>85000700</v>
       </c>
-      <c r="AB133" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC133" s="5">
+      <c r="AC133" s="36">
         <v>0</v>
       </c>
       <c r="AD133" s="5">
@@ -15165,8 +15614,11 @@
       <c r="AF133" s="5">
         <v>0</v>
       </c>
+      <c r="AG133" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A134" s="5">
         <v>95000900</v>
       </c>
@@ -15246,12 +15698,12 @@
         <v>0</v>
       </c>
       <c r="AA134" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB134" s="36">
         <v>85000900</v>
       </c>
-      <c r="AB134" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC134" s="5">
+      <c r="AC134" s="36">
         <v>0</v>
       </c>
       <c r="AD134" s="5">
@@ -15263,8 +15715,11 @@
       <c r="AF134" s="5">
         <v>0</v>
       </c>
+      <c r="AG134" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A135" s="5">
         <v>95001300</v>
       </c>
@@ -15344,12 +15799,12 @@
         <v>0</v>
       </c>
       <c r="AA135" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB135" s="36">
         <v>85001300</v>
       </c>
-      <c r="AB135" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC135" s="5">
+      <c r="AC135" s="36">
         <v>0</v>
       </c>
       <c r="AD135" s="5">
@@ -15361,8 +15816,11 @@
       <c r="AF135" s="5">
         <v>0</v>
       </c>
+      <c r="AG135" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="136" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A136" s="5">
         <v>95001500</v>
       </c>
@@ -15445,11 +15903,11 @@
         <v>0</v>
       </c>
       <c r="AB136" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="36">
         <v>85001500</v>
       </c>
-      <c r="AC136" s="5">
-        <v>0</v>
-      </c>
       <c r="AD136" s="5">
         <v>0</v>
       </c>
@@ -15459,8 +15917,11 @@
       <c r="AF136" s="5">
         <v>0</v>
       </c>
+      <c r="AG136" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A137" s="5">
         <v>95020300</v>
       </c>
@@ -15540,12 +16001,12 @@
         <v>0</v>
       </c>
       <c r="AA137" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="36">
         <v>85020300</v>
       </c>
-      <c r="AB137" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC137" s="5">
+      <c r="AC137" s="36">
         <v>0</v>
       </c>
       <c r="AD137" s="5">
@@ -15557,8 +16018,11 @@
       <c r="AF137" s="5">
         <v>0</v>
       </c>
+      <c r="AG137" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="138" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A138" s="36">
         <v>95100100</v>
       </c>
@@ -15638,12 +16102,12 @@
         <v>0</v>
       </c>
       <c r="AA138" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="36">
         <v>85100100</v>
       </c>
-      <c r="AB138" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC138" s="5">
+      <c r="AC138" s="36">
         <v>0</v>
       </c>
       <c r="AD138" s="5">
@@ -15655,8 +16119,11 @@
       <c r="AF138" s="5">
         <v>0</v>
       </c>
+      <c r="AG138" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="139" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A139" s="36">
         <v>95100101</v>
       </c>
@@ -15727,34 +16194,37 @@
         <v>0</v>
       </c>
       <c r="X139" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="36">
         <v>20000</v>
       </c>
-      <c r="Y139" s="36">
-        <v>0</v>
-      </c>
       <c r="Z139" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="36">
         <v>20000</v>
       </c>
-      <c r="AA139" s="36">
-        <v>0</v>
-      </c>
       <c r="AB139" s="36">
         <v>0</v>
       </c>
-      <c r="AC139" s="5">
+      <c r="AC139" s="36">
         <v>0</v>
       </c>
       <c r="AD139" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE139" s="5">
         <v>95100900</v>
       </c>
-      <c r="AE139" s="5">
-        <v>0</v>
-      </c>
       <c r="AF139" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG139" s="5">
         <v>95101100</v>
       </c>
     </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A140" s="5">
         <v>95100300</v>
       </c>
@@ -15834,12 +16304,12 @@
         <v>0</v>
       </c>
       <c r="AA140" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB140" s="36">
         <v>85100300</v>
       </c>
-      <c r="AB140" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC140" s="5">
+      <c r="AC140" s="36">
         <v>0</v>
       </c>
       <c r="AD140" s="5">
@@ -15851,8 +16321,11 @@
       <c r="AF140" s="5">
         <v>0</v>
       </c>
+      <c r="AG140" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A141" s="5">
         <v>95100500</v>
       </c>
@@ -15932,12 +16405,12 @@
         <v>0</v>
       </c>
       <c r="AA141" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="36">
         <v>85100500</v>
       </c>
-      <c r="AB141" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC141" s="5">
+      <c r="AC141" s="36">
         <v>0</v>
       </c>
       <c r="AD141" s="5">
@@ -15949,8 +16422,11 @@
       <c r="AF141" s="5">
         <v>0</v>
       </c>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A142" s="5">
         <v>95100700</v>
       </c>
@@ -16030,12 +16506,12 @@
         <v>0</v>
       </c>
       <c r="AA142" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="36">
         <v>85100700</v>
       </c>
-      <c r="AB142" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC142" s="5">
+      <c r="AC142" s="36">
         <v>0</v>
       </c>
       <c r="AD142" s="5">
@@ -16047,8 +16523,11 @@
       <c r="AF142" s="5">
         <v>0</v>
       </c>
+      <c r="AG142" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A143" s="5">
         <v>95100900</v>
       </c>
@@ -16128,12 +16607,12 @@
         <v>0</v>
       </c>
       <c r="AA143" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB143" s="36">
         <v>85100900</v>
       </c>
-      <c r="AB143" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC143" s="5">
+      <c r="AC143" s="36">
         <v>0</v>
       </c>
       <c r="AD143" s="5">
@@ -16145,8 +16624,11 @@
       <c r="AF143" s="5">
         <v>0</v>
       </c>
+      <c r="AG143" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A144" s="5">
         <v>95101100</v>
       </c>
@@ -16229,11 +16711,11 @@
         <v>0</v>
       </c>
       <c r="AB144" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="36">
         <v>85101100</v>
       </c>
-      <c r="AC144" s="5">
-        <v>0</v>
-      </c>
       <c r="AD144" s="5">
         <v>0</v>
       </c>
@@ -16243,8 +16725,11 @@
       <c r="AF144" s="5">
         <v>0</v>
       </c>
+      <c r="AG144" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A145" s="5">
         <v>95120300</v>
       </c>
@@ -16324,12 +16809,12 @@
         <v>0</v>
       </c>
       <c r="AA145" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="36">
         <v>85120300</v>
       </c>
-      <c r="AB145" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC145" s="5">
+      <c r="AC145" s="36">
         <v>0</v>
       </c>
       <c r="AD145" s="5">
@@ -16341,8 +16826,11 @@
       <c r="AF145" s="5">
         <v>0</v>
       </c>
+      <c r="AG145" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="146" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A146" s="36">
         <v>95200100</v>
       </c>
@@ -16422,12 +16910,12 @@
         <v>0</v>
       </c>
       <c r="AA146" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="36">
         <v>85200100</v>
       </c>
-      <c r="AB146" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC146" s="5">
+      <c r="AC146" s="36">
         <v>0</v>
       </c>
       <c r="AD146" s="5">
@@ -16439,8 +16927,11 @@
       <c r="AF146" s="5">
         <v>0</v>
       </c>
+      <c r="AG146" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="147" spans="1:32" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A147" s="36">
         <v>95200101</v>
       </c>
@@ -16511,21 +17002,21 @@
         <v>0</v>
       </c>
       <c r="X147" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="36">
         <v>24000</v>
       </c>
-      <c r="Y147" s="36">
-        <v>0</v>
-      </c>
       <c r="Z147" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="36">
         <v>24000</v>
       </c>
-      <c r="AA147" s="36">
-        <v>0</v>
-      </c>
       <c r="AB147" s="36">
         <v>0</v>
       </c>
-      <c r="AC147" s="5">
+      <c r="AC147" s="36">
         <v>0</v>
       </c>
       <c r="AD147" s="5">
@@ -16535,10 +17026,13 @@
         <v>0</v>
       </c>
       <c r="AF147" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG147" s="5">
         <v>95200700</v>
       </c>
     </row>
-    <row r="148" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A148" s="5">
         <v>95200300</v>
       </c>
@@ -16618,12 +17112,12 @@
         <v>0</v>
       </c>
       <c r="AA148" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="36">
         <v>85200300</v>
       </c>
-      <c r="AB148" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC148" s="5">
+      <c r="AC148" s="36">
         <v>0</v>
       </c>
       <c r="AD148" s="5">
@@ -16635,8 +17129,11 @@
       <c r="AF148" s="5">
         <v>0</v>
       </c>
+      <c r="AG148" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="149" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A149" s="5">
         <v>95200500</v>
       </c>
@@ -16716,12 +17213,12 @@
         <v>0</v>
       </c>
       <c r="AA149" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="36">
         <v>85200500</v>
       </c>
-      <c r="AB149" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC149" s="5">
+      <c r="AC149" s="36">
         <v>0</v>
       </c>
       <c r="AD149" s="5">
@@ -16733,8 +17230,11 @@
       <c r="AF149" s="5">
         <v>0</v>
       </c>
+      <c r="AG149" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="150" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A150" s="5">
         <v>95200700</v>
       </c>
@@ -16817,11 +17317,11 @@
         <v>0</v>
       </c>
       <c r="AB150" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="36">
         <v>85200700</v>
       </c>
-      <c r="AC150" s="5">
-        <v>0</v>
-      </c>
       <c r="AD150" s="5">
         <v>0</v>
       </c>
@@ -16831,8 +17331,11 @@
       <c r="AF150" s="5">
         <v>0</v>
       </c>
+      <c r="AG150" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="151" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A151" s="5">
         <v>95220300</v>
       </c>
@@ -16912,12 +17415,12 @@
         <v>0</v>
       </c>
       <c r="AA151" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="36">
         <v>85220300</v>
       </c>
-      <c r="AB151" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC151" s="5">
+      <c r="AC151" s="36">
         <v>0</v>
       </c>
       <c r="AD151" s="5">
@@ -16929,8 +17432,11 @@
       <c r="AF151" s="5">
         <v>0</v>
       </c>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="152" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A152" s="5">
         <v>97000100</v>
       </c>
@@ -17010,12 +17516,12 @@
         <v>0</v>
       </c>
       <c r="AA152" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="36">
         <v>87000100</v>
       </c>
-      <c r="AB152" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC152" s="5">
+      <c r="AC152" s="36">
         <v>0</v>
       </c>
       <c r="AD152" s="5">
@@ -17025,6 +17531,9 @@
         <v>0</v>
       </c>
       <c r="AF152" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG152" s="5">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416B5521-2C8C-4703-B336-038447C76567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFB7411-248E-4F9D-AF55-1D95B392A406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1571,7 +1571,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>0,7000301,7000302,7000303,7000304</t>
+    <t>7000305,7000301,7000302,7000303,7000304</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1902,7 +1902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1984,6 +1984,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2689,7 +2692,7 @@
       <c r="V5" s="34">
         <v>0</v>
       </c>
-      <c r="W5" s="34" t="s">
+      <c r="W5" s="39" t="s">
         <v>352</v>
       </c>
       <c r="X5" s="9">
@@ -2788,7 +2791,7 @@
       <c r="V6" s="34">
         <v>0</v>
       </c>
-      <c r="W6" s="34" t="s">
+      <c r="W6" s="39" t="s">
         <v>352</v>
       </c>
       <c r="X6" s="9">
@@ -2887,7 +2890,7 @@
       <c r="V7" s="34">
         <v>0</v>
       </c>
-      <c r="W7" s="34" t="s">
+      <c r="W7" s="39" t="s">
         <v>352</v>
       </c>
       <c r="X7" s="9">
@@ -2986,7 +2989,7 @@
       <c r="V8" s="34">
         <v>0</v>
       </c>
-      <c r="W8" s="34" t="s">
+      <c r="W8" s="39" t="s">
         <v>352</v>
       </c>
       <c r="X8" s="9">
@@ -3085,7 +3088,7 @@
       <c r="V9" s="34">
         <v>0</v>
       </c>
-      <c r="W9" s="34" t="s">
+      <c r="W9" s="39" t="s">
         <v>352</v>
       </c>
       <c r="X9" s="9">
@@ -3184,7 +3187,7 @@
       <c r="V10" s="34">
         <v>0</v>
       </c>
-      <c r="W10" s="34" t="s">
+      <c r="W10" s="39" t="s">
         <v>352</v>
       </c>
       <c r="X10" s="9">

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFB7411-248E-4F9D-AF55-1D95B392A406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30AFB09F-0592-44E0-8EC2-628F5F36B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="355">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1572,6 +1572,13 @@
   </si>
   <si>
     <t>7000305,7000301,7000302,7000303,7000304</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1902,7 +1909,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1985,6 +1992,9 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3288,8 +3298,8 @@
       <c r="V11" s="35">
         <v>0</v>
       </c>
-      <c r="W11" s="35">
-        <v>0</v>
+      <c r="W11" s="40" t="s">
+        <v>354</v>
       </c>
       <c r="X11" s="2">
         <v>0</v>
@@ -3389,8 +3399,8 @@
       <c r="V12" s="35">
         <v>0</v>
       </c>
-      <c r="W12" s="35">
-        <v>0</v>
+      <c r="W12" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X12" s="2">
         <v>0</v>
@@ -3490,8 +3500,8 @@
       <c r="V13" s="35">
         <v>0</v>
       </c>
-      <c r="W13" s="35">
-        <v>0</v>
+      <c r="W13" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
@@ -3591,8 +3601,8 @@
       <c r="V14" s="35">
         <v>0</v>
       </c>
-      <c r="W14" s="35">
-        <v>0</v>
+      <c r="W14" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
@@ -3692,8 +3702,8 @@
       <c r="V15" s="35">
         <v>0</v>
       </c>
-      <c r="W15" s="35">
-        <v>0</v>
+      <c r="W15" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
@@ -3793,8 +3803,8 @@
       <c r="V16" s="35">
         <v>0</v>
       </c>
-      <c r="W16" s="35">
-        <v>0</v>
+      <c r="W16" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X16" s="2">
         <v>0</v>
@@ -3894,8 +3904,8 @@
       <c r="V17" s="35">
         <v>0</v>
       </c>
-      <c r="W17" s="35">
-        <v>0</v>
+      <c r="W17" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
@@ -3995,8 +4005,8 @@
       <c r="V18" s="35">
         <v>0</v>
       </c>
-      <c r="W18" s="35">
-        <v>0</v>
+      <c r="W18" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X18" s="2">
         <v>0</v>
@@ -4096,8 +4106,8 @@
       <c r="V19" s="2">
         <v>0</v>
       </c>
-      <c r="W19" s="2">
-        <v>0</v>
+      <c r="W19" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X19" s="2">
         <v>0</v>
@@ -4197,8 +4207,8 @@
       <c r="V20" s="2">
         <v>0</v>
       </c>
-      <c r="W20" s="2">
-        <v>0</v>
+      <c r="W20" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X20" s="2">
         <v>0</v>
@@ -4298,8 +4308,8 @@
       <c r="V21" s="2">
         <v>0</v>
       </c>
-      <c r="W21" s="2">
-        <v>0</v>
+      <c r="W21" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X21" s="2">
         <v>0</v>
@@ -4399,8 +4409,8 @@
       <c r="V22" s="2">
         <v>0</v>
       </c>
-      <c r="W22" s="2">
-        <v>0</v>
+      <c r="W22" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X22" s="2">
         <v>0</v>
@@ -4500,8 +4510,8 @@
       <c r="V23" s="2">
         <v>0</v>
       </c>
-      <c r="W23" s="2">
-        <v>0</v>
+      <c r="W23" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X23" s="2">
         <v>0</v>
@@ -4601,8 +4611,8 @@
       <c r="V24" s="2">
         <v>0</v>
       </c>
-      <c r="W24" s="2">
-        <v>0</v>
+      <c r="W24" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X24" s="2">
         <v>0</v>
@@ -4702,8 +4712,8 @@
       <c r="V25" s="2">
         <v>0</v>
       </c>
-      <c r="W25" s="2">
-        <v>0</v>
+      <c r="W25" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X25" s="2">
         <v>0</v>
@@ -4803,8 +4813,8 @@
       <c r="V26" s="2">
         <v>0</v>
       </c>
-      <c r="W26" s="2">
-        <v>0</v>
+      <c r="W26" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X26" s="2">
         <v>0</v>
@@ -4904,8 +4914,8 @@
       <c r="V27" s="2">
         <v>0</v>
       </c>
-      <c r="W27" s="2">
-        <v>0</v>
+      <c r="W27" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="X27" s="2">
         <v>0</v>
@@ -5005,8 +5015,8 @@
       <c r="V28" s="35">
         <v>0</v>
       </c>
-      <c r="W28" s="35">
-        <v>0</v>
+      <c r="W28" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X28" s="2">
         <v>0</v>
@@ -5106,8 +5116,8 @@
       <c r="V29" s="35">
         <v>0</v>
       </c>
-      <c r="W29" s="35">
-        <v>0</v>
+      <c r="W29" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X29" s="2">
         <v>0</v>
@@ -5207,8 +5217,8 @@
       <c r="V30" s="35">
         <v>0</v>
       </c>
-      <c r="W30" s="35">
-        <v>0</v>
+      <c r="W30" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>
@@ -5308,8 +5318,8 @@
       <c r="V31" s="35">
         <v>0</v>
       </c>
-      <c r="W31" s="35">
-        <v>0</v>
+      <c r="W31" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X31" s="2">
         <v>0</v>
@@ -5409,8 +5419,8 @@
       <c r="V32" s="35">
         <v>0</v>
       </c>
-      <c r="W32" s="35">
-        <v>0</v>
+      <c r="W32" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="X32" s="2">
         <v>0</v>
@@ -5510,8 +5520,8 @@
       <c r="V33" s="23">
         <v>0</v>
       </c>
-      <c r="W33" s="23">
-        <v>0</v>
+      <c r="W33" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X33" s="23">
         <v>0</v>
@@ -5611,8 +5621,8 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-      <c r="W34" s="3">
-        <v>0</v>
+      <c r="W34" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="X34" s="3">
         <v>0</v>
@@ -5712,8 +5722,8 @@
       <c r="V35" s="3">
         <v>0</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
+      <c r="W35" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="X35" s="3">
         <v>0</v>
@@ -5813,8 +5823,8 @@
       <c r="V36" s="21">
         <v>1</v>
       </c>
-      <c r="W36" s="21">
-        <v>0</v>
+      <c r="W36" s="21" t="s">
+        <v>353</v>
       </c>
       <c r="X36" s="21">
         <v>0</v>
@@ -5912,8 +5922,8 @@
       <c r="V37" s="17">
         <v>2</v>
       </c>
-      <c r="W37" s="17">
-        <v>0</v>
+      <c r="W37" s="17" t="s">
+        <v>353</v>
       </c>
       <c r="X37" s="17">
         <v>150</v>
@@ -6011,8 +6021,8 @@
       <c r="V38" s="17">
         <v>2</v>
       </c>
-      <c r="W38" s="17">
-        <v>0</v>
+      <c r="W38" s="17" t="s">
+        <v>353</v>
       </c>
       <c r="X38" s="17">
         <v>150</v>
@@ -6110,8 +6120,8 @@
       <c r="V39" s="19">
         <v>4</v>
       </c>
-      <c r="W39" s="19">
-        <v>0</v>
+      <c r="W39" s="19" t="s">
+        <v>353</v>
       </c>
       <c r="X39" s="19">
         <v>150</v>
@@ -6209,8 +6219,8 @@
       <c r="V40" s="19">
         <v>4</v>
       </c>
-      <c r="W40" s="19">
-        <v>0</v>
+      <c r="W40" s="19" t="s">
+        <v>353</v>
       </c>
       <c r="X40" s="19">
         <v>150</v>
@@ -6308,8 +6318,8 @@
       <c r="V41" s="20">
         <v>3</v>
       </c>
-      <c r="W41" s="20">
-        <v>0</v>
+      <c r="W41" s="20" t="s">
+        <v>353</v>
       </c>
       <c r="X41" s="20">
         <v>150</v>
@@ -6407,8 +6417,8 @@
       <c r="V42" s="20">
         <v>3</v>
       </c>
-      <c r="W42" s="20">
-        <v>0</v>
+      <c r="W42" s="20" t="s">
+        <v>353</v>
       </c>
       <c r="X42" s="20">
         <v>150</v>
@@ -6506,8 +6516,8 @@
       <c r="V43" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="W43" s="32">
-        <v>0</v>
+      <c r="W43" s="32" t="s">
+        <v>353</v>
       </c>
       <c r="X43" s="28">
         <v>150</v>
@@ -6605,8 +6615,8 @@
       <c r="V44" s="30">
         <v>0</v>
       </c>
-      <c r="W44" s="30">
-        <v>0</v>
+      <c r="W44" s="30" t="s">
+        <v>353</v>
       </c>
       <c r="X44" s="30">
         <v>150</v>
@@ -6704,8 +6714,8 @@
       <c r="V45" s="30">
         <v>0</v>
       </c>
-      <c r="W45" s="30">
-        <v>0</v>
+      <c r="W45" s="30" t="s">
+        <v>353</v>
       </c>
       <c r="X45" s="30">
         <v>150</v>
@@ -6803,8 +6813,8 @@
       <c r="V46" s="31">
         <v>0</v>
       </c>
-      <c r="W46" s="31">
-        <v>0</v>
+      <c r="W46" s="31" t="s">
+        <v>353</v>
       </c>
       <c r="X46" s="31">
         <v>150</v>
@@ -6904,8 +6914,8 @@
       <c r="V47" s="23">
         <v>0</v>
       </c>
-      <c r="W47" s="23">
-        <v>0</v>
+      <c r="W47" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X47" s="23">
         <v>0</v>
@@ -7005,8 +7015,8 @@
       <c r="V48" s="23">
         <v>0</v>
       </c>
-      <c r="W48" s="23">
-        <v>0</v>
+      <c r="W48" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X48" s="23">
         <v>0</v>
@@ -7106,8 +7116,8 @@
       <c r="V49" s="23">
         <v>0</v>
       </c>
-      <c r="W49" s="23">
-        <v>0</v>
+      <c r="W49" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X49" s="23">
         <v>0</v>
@@ -7207,8 +7217,8 @@
       <c r="V50" s="23">
         <v>0</v>
       </c>
-      <c r="W50" s="23">
-        <v>0</v>
+      <c r="W50" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X50" s="23">
         <v>0</v>
@@ -7308,8 +7318,8 @@
       <c r="V51" s="23">
         <v>0</v>
       </c>
-      <c r="W51" s="23">
-        <v>0</v>
+      <c r="W51" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X51" s="23">
         <v>0</v>
@@ -7409,8 +7419,8 @@
       <c r="V52" s="23">
         <v>0</v>
       </c>
-      <c r="W52" s="23">
-        <v>0</v>
+      <c r="W52" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X52" s="23">
         <v>0</v>
@@ -7510,8 +7520,8 @@
       <c r="V53" s="23">
         <v>0</v>
       </c>
-      <c r="W53" s="23">
-        <v>0</v>
+      <c r="W53" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X53" s="23">
         <v>0</v>
@@ -7611,8 +7621,8 @@
       <c r="V54" s="23">
         <v>0</v>
       </c>
-      <c r="W54" s="23">
-        <v>0</v>
+      <c r="W54" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X54" s="23">
         <v>0</v>
@@ -7712,8 +7722,8 @@
       <c r="V55" s="23">
         <v>0</v>
       </c>
-      <c r="W55" s="23">
-        <v>0</v>
+      <c r="W55" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X55" s="23">
         <v>0</v>
@@ -7813,8 +7823,8 @@
       <c r="V56" s="23">
         <v>0</v>
       </c>
-      <c r="W56" s="23">
-        <v>0</v>
+      <c r="W56" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X56" s="23">
         <v>0</v>
@@ -7914,8 +7924,8 @@
       <c r="V57" s="23">
         <v>0</v>
       </c>
-      <c r="W57" s="23">
-        <v>0</v>
+      <c r="W57" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X57" s="23">
         <v>0</v>
@@ -8015,8 +8025,8 @@
       <c r="V58" s="23">
         <v>0</v>
       </c>
-      <c r="W58" s="23">
-        <v>0</v>
+      <c r="W58" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X58" s="23">
         <v>0</v>
@@ -8116,8 +8126,8 @@
       <c r="V59" s="23">
         <v>0</v>
       </c>
-      <c r="W59" s="23">
-        <v>0</v>
+      <c r="W59" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X59" s="23">
         <v>0</v>
@@ -8217,8 +8227,8 @@
       <c r="V60" s="23">
         <v>0</v>
       </c>
-      <c r="W60" s="23">
-        <v>0</v>
+      <c r="W60" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X60" s="23">
         <v>0</v>
@@ -8318,8 +8328,8 @@
       <c r="V61" s="23">
         <v>0</v>
       </c>
-      <c r="W61" s="23">
-        <v>0</v>
+      <c r="W61" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X61" s="23">
         <v>0</v>
@@ -8419,8 +8429,8 @@
       <c r="V62" s="23">
         <v>0</v>
       </c>
-      <c r="W62" s="23">
-        <v>0</v>
+      <c r="W62" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X62" s="23">
         <v>0</v>
@@ -8520,8 +8530,8 @@
       <c r="V63" s="23">
         <v>0</v>
       </c>
-      <c r="W63" s="23">
-        <v>0</v>
+      <c r="W63" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X63" s="23">
         <v>0</v>
@@ -8621,8 +8631,8 @@
       <c r="V64" s="23">
         <v>0</v>
       </c>
-      <c r="W64" s="23">
-        <v>0</v>
+      <c r="W64" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X64" s="23">
         <v>0</v>
@@ -8722,8 +8732,8 @@
       <c r="V65" s="23">
         <v>0</v>
       </c>
-      <c r="W65" s="23">
-        <v>0</v>
+      <c r="W65" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X65" s="23">
         <v>0</v>
@@ -8823,8 +8833,8 @@
       <c r="V66" s="23">
         <v>0</v>
       </c>
-      <c r="W66" s="23">
-        <v>0</v>
+      <c r="W66" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X66" s="23">
         <v>0</v>
@@ -8924,8 +8934,8 @@
       <c r="V67" s="23">
         <v>0</v>
       </c>
-      <c r="W67" s="23">
-        <v>0</v>
+      <c r="W67" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X67" s="23">
         <v>0</v>
@@ -9025,8 +9035,8 @@
       <c r="V68" s="23">
         <v>0</v>
       </c>
-      <c r="W68" s="23">
-        <v>0</v>
+      <c r="W68" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X68" s="23">
         <v>0</v>
@@ -9126,8 +9136,8 @@
       <c r="V69" s="23">
         <v>0</v>
       </c>
-      <c r="W69" s="23">
-        <v>0</v>
+      <c r="W69" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X69" s="23">
         <v>0</v>
@@ -9227,8 +9237,8 @@
       <c r="V70" s="23">
         <v>0</v>
       </c>
-      <c r="W70" s="23">
-        <v>0</v>
+      <c r="W70" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X70" s="23">
         <v>0</v>
@@ -9328,8 +9338,8 @@
       <c r="V71" s="23">
         <v>0</v>
       </c>
-      <c r="W71" s="23">
-        <v>0</v>
+      <c r="W71" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X71" s="23">
         <v>0</v>
@@ -9429,8 +9439,8 @@
       <c r="V72" s="23">
         <v>0</v>
       </c>
-      <c r="W72" s="23">
-        <v>0</v>
+      <c r="W72" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="X72" s="23">
         <v>0</v>
@@ -9530,8 +9540,8 @@
       <c r="V73" s="13">
         <v>1</v>
       </c>
-      <c r="W73" s="13">
-        <v>0</v>
+      <c r="W73" s="13" t="s">
+        <v>353</v>
       </c>
       <c r="X73" s="13">
         <v>0</v>
@@ -9631,8 +9641,8 @@
       <c r="V74" s="13">
         <v>1</v>
       </c>
-      <c r="W74" s="13">
-        <v>0</v>
+      <c r="W74" s="13" t="s">
+        <v>353</v>
       </c>
       <c r="X74" s="13">
         <v>0</v>
@@ -9732,8 +9742,8 @@
       <c r="V75" s="13">
         <v>1</v>
       </c>
-      <c r="W75" s="13">
-        <v>0</v>
+      <c r="W75" s="13" t="s">
+        <v>353</v>
       </c>
       <c r="X75" s="13">
         <v>0</v>
@@ -9833,8 +9843,8 @@
       <c r="V76" s="13">
         <v>1</v>
       </c>
-      <c r="W76" s="13">
-        <v>0</v>
+      <c r="W76" s="13" t="s">
+        <v>353</v>
       </c>
       <c r="X76" s="13">
         <v>0</v>
@@ -9934,8 +9944,8 @@
       <c r="V77" s="13">
         <v>1</v>
       </c>
-      <c r="W77" s="13">
-        <v>0</v>
+      <c r="W77" s="13" t="s">
+        <v>353</v>
       </c>
       <c r="X77" s="13">
         <v>0</v>
@@ -10035,8 +10045,8 @@
       <c r="V78" s="13">
         <v>1</v>
       </c>
-      <c r="W78" s="13">
-        <v>0</v>
+      <c r="W78" s="13" t="s">
+        <v>353</v>
       </c>
       <c r="X78" s="13">
         <v>0</v>
@@ -10136,8 +10146,8 @@
       <c r="V79" s="13">
         <v>1</v>
       </c>
-      <c r="W79" s="13">
-        <v>0</v>
+      <c r="W79" s="13" t="s">
+        <v>353</v>
       </c>
       <c r="X79" s="13">
         <v>0</v>
@@ -10237,8 +10247,8 @@
       <c r="V80" s="14">
         <v>2</v>
       </c>
-      <c r="W80" s="14">
-        <v>0</v>
+      <c r="W80" s="14" t="s">
+        <v>353</v>
       </c>
       <c r="X80" s="14">
         <v>0</v>
@@ -10338,8 +10348,8 @@
       <c r="V81" s="14">
         <v>2</v>
       </c>
-      <c r="W81" s="14">
-        <v>0</v>
+      <c r="W81" s="14" t="s">
+        <v>353</v>
       </c>
       <c r="X81" s="14">
         <v>0</v>
@@ -10439,8 +10449,8 @@
       <c r="V82" s="14">
         <v>2</v>
       </c>
-      <c r="W82" s="14">
-        <v>0</v>
+      <c r="W82" s="14" t="s">
+        <v>353</v>
       </c>
       <c r="X82" s="14">
         <v>0</v>
@@ -10540,8 +10550,8 @@
       <c r="V83" s="14">
         <v>2</v>
       </c>
-      <c r="W83" s="14">
-        <v>0</v>
+      <c r="W83" s="14" t="s">
+        <v>353</v>
       </c>
       <c r="X83" s="14">
         <v>0</v>
@@ -10641,8 +10651,8 @@
       <c r="V84" s="14">
         <v>2</v>
       </c>
-      <c r="W84" s="14">
-        <v>0</v>
+      <c r="W84" s="14" t="s">
+        <v>353</v>
       </c>
       <c r="X84" s="14">
         <v>0</v>
@@ -10742,8 +10752,8 @@
       <c r="V85" s="14">
         <v>2</v>
       </c>
-      <c r="W85" s="14">
-        <v>0</v>
+      <c r="W85" s="14" t="s">
+        <v>353</v>
       </c>
       <c r="X85" s="14">
         <v>0</v>
@@ -10843,8 +10853,8 @@
       <c r="V86" s="15">
         <v>3</v>
       </c>
-      <c r="W86" s="15">
-        <v>0</v>
+      <c r="W86" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="X86" s="15">
         <v>0</v>
@@ -10944,8 +10954,8 @@
       <c r="V87" s="15">
         <v>3</v>
       </c>
-      <c r="W87" s="15">
-        <v>0</v>
+      <c r="W87" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="X87" s="15">
         <v>0</v>
@@ -11045,8 +11055,8 @@
       <c r="V88" s="15">
         <v>3</v>
       </c>
-      <c r="W88" s="15">
-        <v>0</v>
+      <c r="W88" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="X88" s="15">
         <v>0</v>
@@ -11146,8 +11156,8 @@
       <c r="V89" s="15">
         <v>3</v>
       </c>
-      <c r="W89" s="15">
-        <v>0</v>
+      <c r="W89" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="X89" s="15">
         <v>0</v>
@@ -11247,8 +11257,8 @@
       <c r="V90" s="15">
         <v>3</v>
       </c>
-      <c r="W90" s="15">
-        <v>0</v>
+      <c r="W90" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="X90" s="15">
         <v>0</v>
@@ -11348,8 +11358,8 @@
       <c r="V91" s="15">
         <v>3</v>
       </c>
-      <c r="W91" s="15">
-        <v>0</v>
+      <c r="W91" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="X91" s="15">
         <v>0</v>
@@ -11449,8 +11459,8 @@
       <c r="V92" s="16">
         <v>4</v>
       </c>
-      <c r="W92" s="16">
-        <v>0</v>
+      <c r="W92" s="16" t="s">
+        <v>353</v>
       </c>
       <c r="X92" s="16">
         <v>0</v>
@@ -11550,8 +11560,8 @@
       <c r="V93" s="16">
         <v>4</v>
       </c>
-      <c r="W93" s="16">
-        <v>0</v>
+      <c r="W93" s="16" t="s">
+        <v>353</v>
       </c>
       <c r="X93" s="16">
         <v>0</v>
@@ -11651,8 +11661,8 @@
       <c r="V94" s="16">
         <v>4</v>
       </c>
-      <c r="W94" s="16">
-        <v>0</v>
+      <c r="W94" s="16" t="s">
+        <v>353</v>
       </c>
       <c r="X94" s="16">
         <v>0</v>
@@ -11752,8 +11762,8 @@
       <c r="V95" s="16">
         <v>4</v>
       </c>
-      <c r="W95" s="16">
-        <v>0</v>
+      <c r="W95" s="16" t="s">
+        <v>353</v>
       </c>
       <c r="X95" s="16">
         <v>0</v>
@@ -11853,8 +11863,8 @@
       <c r="V96" s="16">
         <v>4</v>
       </c>
-      <c r="W96" s="16">
-        <v>0</v>
+      <c r="W96" s="16" t="s">
+        <v>353</v>
       </c>
       <c r="X96" s="16">
         <v>0</v>
@@ -11954,8 +11964,8 @@
       <c r="V97" s="24">
         <v>0</v>
       </c>
-      <c r="W97" s="24">
-        <v>0</v>
+      <c r="W97" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X97" s="24">
         <v>0</v>
@@ -12055,8 +12065,8 @@
       <c r="V98" s="24">
         <v>0</v>
       </c>
-      <c r="W98" s="24">
-        <v>0</v>
+      <c r="W98" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X98" s="24">
         <v>0</v>
@@ -12156,8 +12166,8 @@
       <c r="V99" s="24">
         <v>0</v>
       </c>
-      <c r="W99" s="24">
-        <v>0</v>
+      <c r="W99" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X99" s="24">
         <v>0</v>
@@ -12257,8 +12267,8 @@
       <c r="V100" s="24">
         <v>0</v>
       </c>
-      <c r="W100" s="24">
-        <v>0</v>
+      <c r="W100" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X100" s="24">
         <v>0</v>
@@ -12358,8 +12368,8 @@
       <c r="V101" s="24">
         <v>0</v>
       </c>
-      <c r="W101" s="24">
-        <v>0</v>
+      <c r="W101" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X101" s="24">
         <v>0</v>
@@ -12459,8 +12469,8 @@
       <c r="V102" s="24">
         <v>0</v>
       </c>
-      <c r="W102" s="24">
-        <v>0</v>
+      <c r="W102" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X102" s="24">
         <v>0</v>
@@ -12560,8 +12570,8 @@
       <c r="V103" s="24">
         <v>0</v>
       </c>
-      <c r="W103" s="24">
-        <v>0</v>
+      <c r="W103" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X103" s="24">
         <v>0</v>
@@ -12661,8 +12671,8 @@
       <c r="V104" s="24">
         <v>0</v>
       </c>
-      <c r="W104" s="24">
-        <v>0</v>
+      <c r="W104" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X104" s="24">
         <v>0</v>
@@ -12762,8 +12772,8 @@
       <c r="V105" s="24">
         <v>0</v>
       </c>
-      <c r="W105" s="24">
-        <v>0</v>
+      <c r="W105" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X105" s="24">
         <v>0</v>
@@ -12863,8 +12873,8 @@
       <c r="V106" s="24">
         <v>0</v>
       </c>
-      <c r="W106" s="24">
-        <v>0</v>
+      <c r="W106" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X106" s="24">
         <v>0</v>
@@ -12964,8 +12974,8 @@
       <c r="V107" s="24">
         <v>0</v>
       </c>
-      <c r="W107" s="24">
-        <v>0</v>
+      <c r="W107" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X107" s="24">
         <v>0</v>
@@ -13065,8 +13075,8 @@
       <c r="V108" s="24">
         <v>0</v>
       </c>
-      <c r="W108" s="24">
-        <v>0</v>
+      <c r="W108" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X108" s="24">
         <v>0</v>
@@ -13166,8 +13176,8 @@
       <c r="V109" s="24">
         <v>0</v>
       </c>
-      <c r="W109" s="24">
-        <v>0</v>
+      <c r="W109" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X109" s="24">
         <v>0</v>
@@ -13267,8 +13277,8 @@
       <c r="V110" s="24">
         <v>0</v>
       </c>
-      <c r="W110" s="24">
-        <v>0</v>
+      <c r="W110" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="X110" s="24">
         <v>0</v>
@@ -13368,8 +13378,8 @@
       <c r="V111" s="25">
         <v>0</v>
       </c>
-      <c r="W111" s="25">
-        <v>0</v>
+      <c r="W111" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X111" s="25">
         <v>0</v>
@@ -13469,8 +13479,8 @@
       <c r="V112" s="25">
         <v>0</v>
       </c>
-      <c r="W112" s="25">
-        <v>0</v>
+      <c r="W112" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X112" s="25">
         <v>0</v>
@@ -13570,8 +13580,8 @@
       <c r="V113" s="25">
         <v>0</v>
       </c>
-      <c r="W113" s="25">
-        <v>0</v>
+      <c r="W113" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X113" s="25">
         <v>0</v>
@@ -13671,8 +13681,8 @@
       <c r="V114" s="25">
         <v>0</v>
       </c>
-      <c r="W114" s="25">
-        <v>0</v>
+      <c r="W114" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X114" s="25">
         <v>0</v>
@@ -13772,8 +13782,8 @@
       <c r="V115" s="25">
         <v>0</v>
       </c>
-      <c r="W115" s="25">
-        <v>0</v>
+      <c r="W115" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X115" s="25">
         <v>0</v>
@@ -13873,8 +13883,8 @@
       <c r="V116" s="25">
         <v>0</v>
       </c>
-      <c r="W116" s="25">
-        <v>0</v>
+      <c r="W116" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X116" s="25">
         <v>0</v>
@@ -13974,8 +13984,8 @@
       <c r="V117" s="25">
         <v>0</v>
       </c>
-      <c r="W117" s="25">
-        <v>0</v>
+      <c r="W117" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X117" s="25">
         <v>0</v>
@@ -14075,8 +14085,8 @@
       <c r="V118" s="27">
         <v>0</v>
       </c>
-      <c r="W118" s="27">
-        <v>0</v>
+      <c r="W118" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X118" s="27">
         <v>0</v>
@@ -14176,8 +14186,8 @@
       <c r="V119" s="27">
         <v>0</v>
       </c>
-      <c r="W119" s="27">
-        <v>0</v>
+      <c r="W119" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X119" s="27">
         <v>0</v>
@@ -14277,8 +14287,8 @@
       <c r="V120" s="27">
         <v>0</v>
       </c>
-      <c r="W120" s="27">
-        <v>0</v>
+      <c r="W120" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X120" s="27">
         <v>0</v>
@@ -14378,8 +14388,8 @@
       <c r="V121" s="27">
         <v>0</v>
       </c>
-      <c r="W121" s="27">
-        <v>0</v>
+      <c r="W121" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X121" s="27">
         <v>0</v>
@@ -14479,8 +14489,8 @@
       <c r="V122" s="27">
         <v>0</v>
       </c>
-      <c r="W122" s="27">
-        <v>0</v>
+      <c r="W122" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X122" s="27">
         <v>0</v>
@@ -14580,8 +14590,8 @@
       <c r="V123" s="27">
         <v>0</v>
       </c>
-      <c r="W123" s="27">
-        <v>0</v>
+      <c r="W123" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X123" s="27">
         <v>0</v>
@@ -14681,8 +14691,8 @@
       <c r="V124" s="27">
         <v>0</v>
       </c>
-      <c r="W124" s="27">
-        <v>0</v>
+      <c r="W124" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X124" s="27">
         <v>0</v>
@@ -14782,8 +14792,8 @@
       <c r="V125" s="27">
         <v>0</v>
       </c>
-      <c r="W125" s="27">
-        <v>0</v>
+      <c r="W125" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X125" s="27">
         <v>0</v>
@@ -14883,8 +14893,8 @@
       <c r="V126" s="27">
         <v>0</v>
       </c>
-      <c r="W126" s="27">
-        <v>0</v>
+      <c r="W126" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X126" s="27">
         <v>0</v>
@@ -14981,8 +14991,8 @@
       <c r="V127" s="27">
         <v>0</v>
       </c>
-      <c r="W127" s="27">
-        <v>0</v>
+      <c r="W127" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X127" s="27">
         <v>0</v>
@@ -15082,8 +15092,8 @@
       <c r="V128" s="27">
         <v>0</v>
       </c>
-      <c r="W128" s="27">
-        <v>0</v>
+      <c r="W128" s="27" t="s">
+        <v>353</v>
       </c>
       <c r="X128" s="27">
         <v>0</v>
@@ -15183,8 +15193,8 @@
       <c r="V129" s="36">
         <v>0</v>
       </c>
-      <c r="W129" s="36">
-        <v>0</v>
+      <c r="W129" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X129" s="36">
         <v>0</v>
@@ -15284,8 +15294,8 @@
       <c r="V130" s="36">
         <v>1</v>
       </c>
-      <c r="W130" s="36">
-        <v>0</v>
+      <c r="W130" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X130" s="36">
         <v>0</v>
@@ -15385,8 +15395,8 @@
       <c r="V131" s="36">
         <v>0</v>
       </c>
-      <c r="W131" s="36">
-        <v>0</v>
+      <c r="W131" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X131" s="36">
         <v>0</v>
@@ -15486,8 +15496,8 @@
       <c r="V132" s="36">
         <v>0</v>
       </c>
-      <c r="W132" s="36">
-        <v>0</v>
+      <c r="W132" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X132" s="36">
         <v>0</v>
@@ -15587,8 +15597,8 @@
       <c r="V133" s="36">
         <v>0</v>
       </c>
-      <c r="W133" s="36">
-        <v>0</v>
+      <c r="W133" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X133" s="36">
         <v>0</v>
@@ -15688,8 +15698,8 @@
       <c r="V134" s="36">
         <v>0</v>
       </c>
-      <c r="W134" s="36">
-        <v>0</v>
+      <c r="W134" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X134" s="36">
         <v>0</v>
@@ -15789,8 +15799,8 @@
       <c r="V135" s="36">
         <v>1</v>
       </c>
-      <c r="W135" s="36">
-        <v>0</v>
+      <c r="W135" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X135" s="36">
         <v>0</v>
@@ -15890,8 +15900,8 @@
       <c r="V136" s="36">
         <v>0</v>
       </c>
-      <c r="W136" s="36">
-        <v>0</v>
+      <c r="W136" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X136" s="36">
         <v>0</v>
@@ -15991,8 +16001,8 @@
       <c r="V137" s="36">
         <v>0</v>
       </c>
-      <c r="W137" s="36">
-        <v>0</v>
+      <c r="W137" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X137" s="36">
         <v>0</v>
@@ -16092,8 +16102,8 @@
       <c r="V138" s="36">
         <v>0</v>
       </c>
-      <c r="W138" s="36">
-        <v>0</v>
+      <c r="W138" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X138" s="36">
         <v>0</v>
@@ -16193,8 +16203,8 @@
       <c r="V139" s="36">
         <v>2</v>
       </c>
-      <c r="W139" s="36">
-        <v>0</v>
+      <c r="W139" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X139" s="36">
         <v>0</v>
@@ -16294,8 +16304,8 @@
       <c r="V140" s="36">
         <v>0</v>
       </c>
-      <c r="W140" s="36">
-        <v>0</v>
+      <c r="W140" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X140" s="36">
         <v>0</v>
@@ -16395,8 +16405,8 @@
       <c r="V141" s="36">
         <v>0</v>
       </c>
-      <c r="W141" s="36">
-        <v>0</v>
+      <c r="W141" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X141" s="36">
         <v>0</v>
@@ -16496,8 +16506,8 @@
       <c r="V142" s="36">
         <v>0</v>
       </c>
-      <c r="W142" s="36">
-        <v>0</v>
+      <c r="W142" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X142" s="36">
         <v>0</v>
@@ -16597,8 +16607,8 @@
       <c r="V143" s="36">
         <v>2</v>
       </c>
-      <c r="W143" s="36">
-        <v>0</v>
+      <c r="W143" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X143" s="36">
         <v>0</v>
@@ -16698,8 +16708,8 @@
       <c r="V144" s="36">
         <v>0</v>
       </c>
-      <c r="W144" s="36">
-        <v>0</v>
+      <c r="W144" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X144" s="36">
         <v>0</v>
@@ -16799,8 +16809,8 @@
       <c r="V145" s="36">
         <v>0</v>
       </c>
-      <c r="W145" s="36">
-        <v>0</v>
+      <c r="W145" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X145" s="36">
         <v>0</v>
@@ -16900,8 +16910,8 @@
       <c r="V146" s="36">
         <v>0</v>
       </c>
-      <c r="W146" s="36">
-        <v>0</v>
+      <c r="W146" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X146" s="36">
         <v>0</v>
@@ -17001,8 +17011,8 @@
       <c r="V147" s="36">
         <v>4</v>
       </c>
-      <c r="W147" s="36">
-        <v>0</v>
+      <c r="W147" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X147" s="36">
         <v>0</v>
@@ -17102,8 +17112,8 @@
       <c r="V148" s="36">
         <v>0</v>
       </c>
-      <c r="W148" s="36">
-        <v>0</v>
+      <c r="W148" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X148" s="36">
         <v>0</v>
@@ -17203,8 +17213,8 @@
       <c r="V149" s="36">
         <v>0</v>
       </c>
-      <c r="W149" s="36">
-        <v>0</v>
+      <c r="W149" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X149" s="36">
         <v>0</v>
@@ -17304,8 +17314,8 @@
       <c r="V150" s="36">
         <v>0</v>
       </c>
-      <c r="W150" s="36">
-        <v>0</v>
+      <c r="W150" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X150" s="36">
         <v>0</v>
@@ -17405,8 +17415,8 @@
       <c r="V151" s="36">
         <v>0</v>
       </c>
-      <c r="W151" s="36">
-        <v>0</v>
+      <c r="W151" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X151" s="36">
         <v>0</v>
@@ -17506,8 +17516,8 @@
       <c r="V152" s="36">
         <v>0</v>
       </c>
-      <c r="W152" s="36">
-        <v>0</v>
+      <c r="W152" s="36" t="s">
+        <v>353</v>
       </c>
       <c r="X152" s="36">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30AFB09F-0592-44E0-8EC2-628F5F36B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837022DA-D3CB-4597-AA8A-0A1F7EC2F3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="356">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1579,6 +1579,10 @@
   </si>
   <si>
     <t>0,0,0,0,0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3,4</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1909,7 +1913,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1978,9 +1982,6 @@
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="4" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
@@ -2699,10 +2700,10 @@
       <c r="U5" s="9">
         <v>1</v>
       </c>
-      <c r="V5" s="34">
-        <v>0</v>
-      </c>
-      <c r="W5" s="39" t="s">
+      <c r="V5" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="W5" s="38" t="s">
         <v>352</v>
       </c>
       <c r="X5" s="9">
@@ -2798,10 +2799,10 @@
       <c r="U6" s="9">
         <v>1</v>
       </c>
-      <c r="V6" s="34">
-        <v>0</v>
-      </c>
-      <c r="W6" s="39" t="s">
+      <c r="V6" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="W6" s="38" t="s">
         <v>352</v>
       </c>
       <c r="X6" s="9">
@@ -2897,10 +2898,10 @@
       <c r="U7" s="9">
         <v>1</v>
       </c>
-      <c r="V7" s="34">
-        <v>0</v>
-      </c>
-      <c r="W7" s="39" t="s">
+      <c r="V7" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="W7" s="38" t="s">
         <v>352</v>
       </c>
       <c r="X7" s="9">
@@ -2996,10 +2997,10 @@
       <c r="U8" s="9">
         <v>1</v>
       </c>
-      <c r="V8" s="34">
-        <v>0</v>
-      </c>
-      <c r="W8" s="39" t="s">
+      <c r="V8" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="W8" s="38" t="s">
         <v>352</v>
       </c>
       <c r="X8" s="9">
@@ -3095,10 +3096,10 @@
       <c r="U9" s="9">
         <v>1</v>
       </c>
-      <c r="V9" s="34">
-        <v>0</v>
-      </c>
-      <c r="W9" s="39" t="s">
+      <c r="V9" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="W9" s="38" t="s">
         <v>352</v>
       </c>
       <c r="X9" s="9">
@@ -3194,10 +3195,10 @@
       <c r="U10" s="9">
         <v>1</v>
       </c>
-      <c r="V10" s="34">
-        <v>0</v>
-      </c>
-      <c r="W10" s="39" t="s">
+      <c r="V10" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="W10" s="38" t="s">
         <v>352</v>
       </c>
       <c r="X10" s="9">
@@ -3295,10 +3296,10 @@
       <c r="U11" s="2">
         <v>1</v>
       </c>
-      <c r="V11" s="35">
-        <v>0</v>
-      </c>
-      <c r="W11" s="40" t="s">
+      <c r="V11" s="34">
+        <v>0</v>
+      </c>
+      <c r="W11" s="39" t="s">
         <v>354</v>
       </c>
       <c r="X11" s="2">
@@ -3396,10 +3397,10 @@
       <c r="U12" s="2">
         <v>1</v>
       </c>
-      <c r="V12" s="35">
-        <v>0</v>
-      </c>
-      <c r="W12" s="35" t="s">
+      <c r="V12" s="34">
+        <v>0</v>
+      </c>
+      <c r="W12" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X12" s="2">
@@ -3497,10 +3498,10 @@
       <c r="U13" s="2">
         <v>1</v>
       </c>
-      <c r="V13" s="35">
-        <v>0</v>
-      </c>
-      <c r="W13" s="35" t="s">
+      <c r="V13" s="34">
+        <v>0</v>
+      </c>
+      <c r="W13" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X13" s="2">
@@ -3598,10 +3599,10 @@
       <c r="U14" s="2">
         <v>1</v>
       </c>
-      <c r="V14" s="35">
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="s">
+      <c r="V14" s="34">
+        <v>0</v>
+      </c>
+      <c r="W14" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X14" s="2">
@@ -3699,10 +3700,10 @@
       <c r="U15" s="2">
         <v>1</v>
       </c>
-      <c r="V15" s="35">
-        <v>0</v>
-      </c>
-      <c r="W15" s="35" t="s">
+      <c r="V15" s="34">
+        <v>0</v>
+      </c>
+      <c r="W15" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X15" s="2">
@@ -3800,10 +3801,10 @@
       <c r="U16" s="2">
         <v>1</v>
       </c>
-      <c r="V16" s="35">
-        <v>0</v>
-      </c>
-      <c r="W16" s="35" t="s">
+      <c r="V16" s="34">
+        <v>0</v>
+      </c>
+      <c r="W16" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X16" s="2">
@@ -3901,10 +3902,10 @@
       <c r="U17" s="2">
         <v>1</v>
       </c>
-      <c r="V17" s="35">
-        <v>0</v>
-      </c>
-      <c r="W17" s="35" t="s">
+      <c r="V17" s="34">
+        <v>0</v>
+      </c>
+      <c r="W17" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X17" s="2">
@@ -4002,10 +4003,10 @@
       <c r="U18" s="2">
         <v>1</v>
       </c>
-      <c r="V18" s="35">
-        <v>0</v>
-      </c>
-      <c r="W18" s="35" t="s">
+      <c r="V18" s="34">
+        <v>0</v>
+      </c>
+      <c r="W18" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X18" s="2">
@@ -5012,10 +5013,10 @@
       <c r="U28" s="2">
         <v>1</v>
       </c>
-      <c r="V28" s="35">
-        <v>0</v>
-      </c>
-      <c r="W28" s="35" t="s">
+      <c r="V28" s="34">
+        <v>0</v>
+      </c>
+      <c r="W28" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X28" s="2">
@@ -5113,10 +5114,10 @@
       <c r="U29" s="2">
         <v>1</v>
       </c>
-      <c r="V29" s="35">
-        <v>0</v>
-      </c>
-      <c r="W29" s="35" t="s">
+      <c r="V29" s="34">
+        <v>0</v>
+      </c>
+      <c r="W29" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X29" s="2">
@@ -5214,10 +5215,10 @@
       <c r="U30" s="2">
         <v>1</v>
       </c>
-      <c r="V30" s="35">
-        <v>0</v>
-      </c>
-      <c r="W30" s="35" t="s">
+      <c r="V30" s="34">
+        <v>0</v>
+      </c>
+      <c r="W30" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X30" s="2">
@@ -5315,10 +5316,10 @@
       <c r="U31" s="2">
         <v>1</v>
       </c>
-      <c r="V31" s="35">
-        <v>0</v>
-      </c>
-      <c r="W31" s="35" t="s">
+      <c r="V31" s="34">
+        <v>0</v>
+      </c>
+      <c r="W31" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X31" s="2">
@@ -5416,10 +5417,10 @@
       <c r="U32" s="2">
         <v>1</v>
       </c>
-      <c r="V32" s="35">
-        <v>0</v>
-      </c>
-      <c r="W32" s="35" t="s">
+      <c r="V32" s="34">
+        <v>0</v>
+      </c>
+      <c r="W32" s="34" t="s">
         <v>353</v>
       </c>
       <c r="X32" s="2">
@@ -15126,92 +15127,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:33" s="36" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A129" s="36">
+    <row r="129" spans="1:33" s="35" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A129" s="35">
         <v>95000100</v>
       </c>
-      <c r="B129" s="36">
+      <c r="B129" s="35">
         <v>4</v>
       </c>
-      <c r="C129" s="36">
+      <c r="C129" s="35">
         <v>0</v>
       </c>
       <c r="D129" s="5">
         <v>7003</v>
       </c>
-      <c r="E129" s="36">
-        <v>1</v>
-      </c>
-      <c r="F129" s="38" t="s">
+      <c r="E129" s="35">
+        <v>1</v>
+      </c>
+      <c r="F129" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="G129" s="38" t="s">
+      <c r="G129" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="H129" s="37" t="s">
+      <c r="H129" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I129" s="38" t="s">
+      <c r="I129" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="J129" s="36">
-        <v>0</v>
-      </c>
-      <c r="K129" s="36">
-        <v>0</v>
-      </c>
-      <c r="L129" s="36">
-        <v>0</v>
-      </c>
-      <c r="M129" s="36">
-        <v>0</v>
-      </c>
-      <c r="N129" s="36">
-        <v>0</v>
-      </c>
-      <c r="O129" s="36">
-        <v>0</v>
-      </c>
-      <c r="P129" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="36">
-        <v>0</v>
-      </c>
-      <c r="R129" s="36">
-        <v>0</v>
-      </c>
-      <c r="S129" s="36">
-        <v>0</v>
-      </c>
-      <c r="T129" s="36">
-        <v>0</v>
-      </c>
-      <c r="U129" s="36">
-        <v>0</v>
-      </c>
-      <c r="V129" s="36">
-        <v>0</v>
-      </c>
-      <c r="W129" s="36" t="s">
+      <c r="J129" s="35">
+        <v>0</v>
+      </c>
+      <c r="K129" s="35">
+        <v>0</v>
+      </c>
+      <c r="L129" s="35">
+        <v>0</v>
+      </c>
+      <c r="M129" s="35">
+        <v>0</v>
+      </c>
+      <c r="N129" s="35">
+        <v>0</v>
+      </c>
+      <c r="O129" s="35">
+        <v>0</v>
+      </c>
+      <c r="P129" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="35">
+        <v>0</v>
+      </c>
+      <c r="R129" s="35">
+        <v>0</v>
+      </c>
+      <c r="S129" s="35">
+        <v>0</v>
+      </c>
+      <c r="T129" s="35">
+        <v>0</v>
+      </c>
+      <c r="U129" s="35">
+        <v>0</v>
+      </c>
+      <c r="V129" s="35">
+        <v>0</v>
+      </c>
+      <c r="W129" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X129" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y129" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB129" s="36">
+      <c r="X129" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y129" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA129" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB129" s="35">
         <v>85000100</v>
       </c>
-      <c r="AC129" s="36">
+      <c r="AC129" s="35">
         <v>0</v>
       </c>
       <c r="AD129" s="5">
@@ -15227,92 +15228,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A130" s="36">
+    <row r="130" spans="1:33" s="35" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="35">
         <v>95000101</v>
       </c>
-      <c r="B130" s="36">
+      <c r="B130" s="35">
         <v>5</v>
       </c>
-      <c r="C130" s="36">
+      <c r="C130" s="35">
         <v>1</v>
       </c>
       <c r="D130" s="5">
         <v>7004</v>
       </c>
-      <c r="E130" s="36">
-        <v>1</v>
-      </c>
-      <c r="F130" s="36" t="s">
+      <c r="E130" s="35">
+        <v>1</v>
+      </c>
+      <c r="F130" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="G130" s="36" t="s">
+      <c r="G130" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="H130" s="37" t="s">
+      <c r="H130" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I130" s="36" t="s">
+      <c r="I130" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="J130" s="36">
-        <v>0</v>
-      </c>
-      <c r="K130" s="36">
-        <v>0</v>
-      </c>
-      <c r="L130" s="36">
+      <c r="J130" s="35">
+        <v>0</v>
+      </c>
+      <c r="K130" s="35">
+        <v>0</v>
+      </c>
+      <c r="L130" s="35">
         <v>7000</v>
       </c>
-      <c r="M130" s="36">
-        <v>0</v>
-      </c>
-      <c r="N130" s="36">
+      <c r="M130" s="35">
+        <v>0</v>
+      </c>
+      <c r="N130" s="35">
         <v>7500</v>
       </c>
-      <c r="O130" s="36">
-        <v>0</v>
-      </c>
-      <c r="P130" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q130" s="36">
-        <v>1</v>
-      </c>
-      <c r="R130" s="36">
+      <c r="O130" s="35">
+        <v>0</v>
+      </c>
+      <c r="P130" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="35">
+        <v>1</v>
+      </c>
+      <c r="R130" s="35">
         <v>2</v>
       </c>
-      <c r="S130" s="36">
-        <v>0</v>
-      </c>
-      <c r="T130" s="36">
-        <v>0</v>
-      </c>
-      <c r="U130" s="36">
-        <v>1</v>
-      </c>
-      <c r="V130" s="36">
-        <v>1</v>
-      </c>
-      <c r="W130" s="36" t="s">
+      <c r="S130" s="35">
+        <v>0</v>
+      </c>
+      <c r="T130" s="35">
+        <v>0</v>
+      </c>
+      <c r="U130" s="35">
+        <v>1</v>
+      </c>
+      <c r="V130" s="35">
+        <v>1</v>
+      </c>
+      <c r="W130" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X130" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y130" s="36">
+      <c r="X130" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="35">
         <v>27000</v>
       </c>
-      <c r="Z130" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="36">
+      <c r="Z130" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="35">
         <v>27000</v>
       </c>
-      <c r="AB130" s="36">
+      <c r="AB130" s="35">
         <v>85001100</v>
       </c>
-      <c r="AC130" s="36">
+      <c r="AC130" s="35">
         <v>0</v>
       </c>
       <c r="AD130" s="5">
@@ -15350,70 +15351,70 @@
       <c r="G131" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H131" s="37" t="s">
+      <c r="H131" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I131" s="36" t="s">
+      <c r="I131" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="J131" s="36">
-        <v>0</v>
-      </c>
-      <c r="K131" s="36">
-        <v>0</v>
-      </c>
-      <c r="L131" s="36">
-        <v>0</v>
-      </c>
-      <c r="M131" s="36">
-        <v>0</v>
-      </c>
-      <c r="N131" s="36">
-        <v>0</v>
-      </c>
-      <c r="O131" s="36">
-        <v>0</v>
-      </c>
-      <c r="P131" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q131" s="36">
-        <v>0</v>
-      </c>
-      <c r="R131" s="36">
-        <v>0</v>
-      </c>
-      <c r="S131" s="36">
-        <v>0</v>
-      </c>
-      <c r="T131" s="36">
-        <v>0</v>
-      </c>
-      <c r="U131" s="36">
-        <v>0</v>
-      </c>
-      <c r="V131" s="36">
-        <v>0</v>
-      </c>
-      <c r="W131" s="36" t="s">
+      <c r="J131" s="35">
+        <v>0</v>
+      </c>
+      <c r="K131" s="35">
+        <v>0</v>
+      </c>
+      <c r="L131" s="35">
+        <v>0</v>
+      </c>
+      <c r="M131" s="35">
+        <v>0</v>
+      </c>
+      <c r="N131" s="35">
+        <v>0</v>
+      </c>
+      <c r="O131" s="35">
+        <v>0</v>
+      </c>
+      <c r="P131" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="35">
+        <v>0</v>
+      </c>
+      <c r="R131" s="35">
+        <v>0</v>
+      </c>
+      <c r="S131" s="35">
+        <v>0</v>
+      </c>
+      <c r="T131" s="35">
+        <v>0</v>
+      </c>
+      <c r="U131" s="35">
+        <v>0</v>
+      </c>
+      <c r="V131" s="35">
+        <v>0</v>
+      </c>
+      <c r="W131" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X131" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y131" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z131" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA131" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB131" s="36">
+      <c r="X131" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="35">
         <v>85000300</v>
       </c>
-      <c r="AC131" s="36">
+      <c r="AC131" s="35">
         <v>0</v>
       </c>
       <c r="AD131" s="5">
@@ -15451,70 +15452,70 @@
       <c r="G132" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="H132" s="37" t="s">
+      <c r="H132" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I132" s="36" t="s">
+      <c r="I132" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="J132" s="36">
-        <v>0</v>
-      </c>
-      <c r="K132" s="36">
-        <v>0</v>
-      </c>
-      <c r="L132" s="36">
-        <v>0</v>
-      </c>
-      <c r="M132" s="36">
-        <v>0</v>
-      </c>
-      <c r="N132" s="36">
-        <v>0</v>
-      </c>
-      <c r="O132" s="36">
-        <v>0</v>
-      </c>
-      <c r="P132" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="36">
-        <v>0</v>
-      </c>
-      <c r="R132" s="36">
-        <v>0</v>
-      </c>
-      <c r="S132" s="36">
-        <v>0</v>
-      </c>
-      <c r="T132" s="36">
-        <v>0</v>
-      </c>
-      <c r="U132" s="36">
-        <v>0</v>
-      </c>
-      <c r="V132" s="36">
-        <v>0</v>
-      </c>
-      <c r="W132" s="36" t="s">
+      <c r="J132" s="35">
+        <v>0</v>
+      </c>
+      <c r="K132" s="35">
+        <v>0</v>
+      </c>
+      <c r="L132" s="35">
+        <v>0</v>
+      </c>
+      <c r="M132" s="35">
+        <v>0</v>
+      </c>
+      <c r="N132" s="35">
+        <v>0</v>
+      </c>
+      <c r="O132" s="35">
+        <v>0</v>
+      </c>
+      <c r="P132" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="35">
+        <v>0</v>
+      </c>
+      <c r="R132" s="35">
+        <v>0</v>
+      </c>
+      <c r="S132" s="35">
+        <v>0</v>
+      </c>
+      <c r="T132" s="35">
+        <v>0</v>
+      </c>
+      <c r="U132" s="35">
+        <v>0</v>
+      </c>
+      <c r="V132" s="35">
+        <v>0</v>
+      </c>
+      <c r="W132" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X132" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y132" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z132" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA132" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB132" s="36">
+      <c r="X132" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="35">
         <v>85000500</v>
       </c>
-      <c r="AC132" s="36">
+      <c r="AC132" s="35">
         <v>0</v>
       </c>
       <c r="AD132" s="5">
@@ -15552,70 +15553,70 @@
       <c r="G133" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="H133" s="37" t="s">
+      <c r="H133" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I133" s="36" t="s">
+      <c r="I133" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="J133" s="36">
-        <v>0</v>
-      </c>
-      <c r="K133" s="36">
-        <v>0</v>
-      </c>
-      <c r="L133" s="36">
-        <v>0</v>
-      </c>
-      <c r="M133" s="36">
-        <v>0</v>
-      </c>
-      <c r="N133" s="36">
-        <v>0</v>
-      </c>
-      <c r="O133" s="36">
-        <v>0</v>
-      </c>
-      <c r="P133" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="36">
-        <v>0</v>
-      </c>
-      <c r="R133" s="36">
-        <v>0</v>
-      </c>
-      <c r="S133" s="36">
-        <v>0</v>
-      </c>
-      <c r="T133" s="36">
-        <v>0</v>
-      </c>
-      <c r="U133" s="36">
-        <v>0</v>
-      </c>
-      <c r="V133" s="36">
-        <v>0</v>
-      </c>
-      <c r="W133" s="36" t="s">
+      <c r="J133" s="35">
+        <v>0</v>
+      </c>
+      <c r="K133" s="35">
+        <v>0</v>
+      </c>
+      <c r="L133" s="35">
+        <v>0</v>
+      </c>
+      <c r="M133" s="35">
+        <v>0</v>
+      </c>
+      <c r="N133" s="35">
+        <v>0</v>
+      </c>
+      <c r="O133" s="35">
+        <v>0</v>
+      </c>
+      <c r="P133" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="35">
+        <v>0</v>
+      </c>
+      <c r="R133" s="35">
+        <v>0</v>
+      </c>
+      <c r="S133" s="35">
+        <v>0</v>
+      </c>
+      <c r="T133" s="35">
+        <v>0</v>
+      </c>
+      <c r="U133" s="35">
+        <v>0</v>
+      </c>
+      <c r="V133" s="35">
+        <v>0</v>
+      </c>
+      <c r="W133" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X133" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y133" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z133" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA133" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB133" s="36">
+      <c r="X133" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y133" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="35">
         <v>85000700</v>
       </c>
-      <c r="AC133" s="36">
+      <c r="AC133" s="35">
         <v>0</v>
       </c>
       <c r="AD133" s="5">
@@ -15653,70 +15654,70 @@
       <c r="G134" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="H134" s="37" t="s">
+      <c r="H134" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I134" s="36" t="s">
+      <c r="I134" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="J134" s="36">
-        <v>0</v>
-      </c>
-      <c r="K134" s="36">
-        <v>0</v>
-      </c>
-      <c r="L134" s="36">
-        <v>0</v>
-      </c>
-      <c r="M134" s="36">
-        <v>0</v>
-      </c>
-      <c r="N134" s="36">
-        <v>0</v>
-      </c>
-      <c r="O134" s="36">
-        <v>0</v>
-      </c>
-      <c r="P134" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q134" s="36">
-        <v>0</v>
-      </c>
-      <c r="R134" s="36">
-        <v>0</v>
-      </c>
-      <c r="S134" s="36">
-        <v>0</v>
-      </c>
-      <c r="T134" s="36">
-        <v>0</v>
-      </c>
-      <c r="U134" s="36">
-        <v>0</v>
-      </c>
-      <c r="V134" s="36">
-        <v>0</v>
-      </c>
-      <c r="W134" s="36" t="s">
+      <c r="J134" s="35">
+        <v>0</v>
+      </c>
+      <c r="K134" s="35">
+        <v>0</v>
+      </c>
+      <c r="L134" s="35">
+        <v>0</v>
+      </c>
+      <c r="M134" s="35">
+        <v>0</v>
+      </c>
+      <c r="N134" s="35">
+        <v>0</v>
+      </c>
+      <c r="O134" s="35">
+        <v>0</v>
+      </c>
+      <c r="P134" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="35">
+        <v>0</v>
+      </c>
+      <c r="R134" s="35">
+        <v>0</v>
+      </c>
+      <c r="S134" s="35">
+        <v>0</v>
+      </c>
+      <c r="T134" s="35">
+        <v>0</v>
+      </c>
+      <c r="U134" s="35">
+        <v>0</v>
+      </c>
+      <c r="V134" s="35">
+        <v>0</v>
+      </c>
+      <c r="W134" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X134" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y134" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z134" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA134" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB134" s="36">
+      <c r="X134" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y134" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB134" s="35">
         <v>85000900</v>
       </c>
-      <c r="AC134" s="36">
+      <c r="AC134" s="35">
         <v>0</v>
       </c>
       <c r="AD134" s="5">
@@ -15754,70 +15755,70 @@
       <c r="G135" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="H135" s="37" t="s">
+      <c r="H135" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I135" s="36" t="s">
+      <c r="I135" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="J135" s="36">
-        <v>0</v>
-      </c>
-      <c r="K135" s="36">
-        <v>0</v>
-      </c>
-      <c r="L135" s="36">
-        <v>0</v>
-      </c>
-      <c r="M135" s="36">
-        <v>0</v>
-      </c>
-      <c r="N135" s="36">
+      <c r="J135" s="35">
+        <v>0</v>
+      </c>
+      <c r="K135" s="35">
+        <v>0</v>
+      </c>
+      <c r="L135" s="35">
+        <v>0</v>
+      </c>
+      <c r="M135" s="35">
+        <v>0</v>
+      </c>
+      <c r="N135" s="35">
         <v>20000</v>
       </c>
-      <c r="O135" s="36">
-        <v>0</v>
-      </c>
-      <c r="P135" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q135" s="36">
+      <c r="O135" s="35">
+        <v>0</v>
+      </c>
+      <c r="P135" s="35">
+        <v>1</v>
+      </c>
+      <c r="Q135" s="35">
         <v>3</v>
       </c>
-      <c r="R135" s="36">
+      <c r="R135" s="35">
         <v>2</v>
       </c>
-      <c r="S135" s="36">
+      <c r="S135" s="35">
         <v>1400</v>
       </c>
-      <c r="T135" s="36">
-        <v>0</v>
-      </c>
-      <c r="U135" s="36">
-        <v>1</v>
-      </c>
-      <c r="V135" s="36">
-        <v>1</v>
-      </c>
-      <c r="W135" s="36" t="s">
+      <c r="T135" s="35">
+        <v>0</v>
+      </c>
+      <c r="U135" s="35">
+        <v>1</v>
+      </c>
+      <c r="V135" s="35">
+        <v>1</v>
+      </c>
+      <c r="W135" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X135" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y135" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z135" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA135" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB135" s="36">
+      <c r="X135" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y135" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB135" s="35">
         <v>85001300</v>
       </c>
-      <c r="AC135" s="36">
+      <c r="AC135" s="35">
         <v>0</v>
       </c>
       <c r="AD135" s="5">
@@ -15855,70 +15856,70 @@
       <c r="G136" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="H136" s="37" t="s">
+      <c r="H136" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I136" s="36" t="s">
+      <c r="I136" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="J136" s="36">
-        <v>0</v>
-      </c>
-      <c r="K136" s="36">
-        <v>0</v>
-      </c>
-      <c r="L136" s="36">
-        <v>0</v>
-      </c>
-      <c r="M136" s="36">
-        <v>0</v>
-      </c>
-      <c r="N136" s="36">
-        <v>0</v>
-      </c>
-      <c r="O136" s="36">
-        <v>0</v>
-      </c>
-      <c r="P136" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q136" s="36">
-        <v>1</v>
-      </c>
-      <c r="R136" s="36">
+      <c r="J136" s="35">
+        <v>0</v>
+      </c>
+      <c r="K136" s="35">
+        <v>0</v>
+      </c>
+      <c r="L136" s="35">
+        <v>0</v>
+      </c>
+      <c r="M136" s="35">
+        <v>0</v>
+      </c>
+      <c r="N136" s="35">
+        <v>0</v>
+      </c>
+      <c r="O136" s="35">
+        <v>0</v>
+      </c>
+      <c r="P136" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="35">
+        <v>1</v>
+      </c>
+      <c r="R136" s="35">
         <v>2</v>
       </c>
-      <c r="S136" s="36">
-        <v>0</v>
-      </c>
-      <c r="T136" s="36">
-        <v>0</v>
-      </c>
-      <c r="U136" s="36">
-        <v>0</v>
-      </c>
-      <c r="V136" s="36">
-        <v>0</v>
-      </c>
-      <c r="W136" s="36" t="s">
+      <c r="S136" s="35">
+        <v>0</v>
+      </c>
+      <c r="T136" s="35">
+        <v>0</v>
+      </c>
+      <c r="U136" s="35">
+        <v>0</v>
+      </c>
+      <c r="V136" s="35">
+        <v>0</v>
+      </c>
+      <c r="W136" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X136" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y136" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA136" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB136" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC136" s="36">
+      <c r="X136" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB136" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="35">
         <v>85001500</v>
       </c>
       <c r="AD136" s="5">
@@ -15956,70 +15957,70 @@
       <c r="G137" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="H137" s="37" t="s">
+      <c r="H137" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I137" s="36" t="s">
+      <c r="I137" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="J137" s="36">
-        <v>0</v>
-      </c>
-      <c r="K137" s="36">
-        <v>0</v>
-      </c>
-      <c r="L137" s="36">
-        <v>0</v>
-      </c>
-      <c r="M137" s="36">
-        <v>0</v>
-      </c>
-      <c r="N137" s="36">
-        <v>0</v>
-      </c>
-      <c r="O137" s="36">
-        <v>0</v>
-      </c>
-      <c r="P137" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q137" s="36">
-        <v>0</v>
-      </c>
-      <c r="R137" s="36">
-        <v>0</v>
-      </c>
-      <c r="S137" s="36">
-        <v>0</v>
-      </c>
-      <c r="T137" s="36">
-        <v>0</v>
-      </c>
-      <c r="U137" s="36">
-        <v>0</v>
-      </c>
-      <c r="V137" s="36">
-        <v>0</v>
-      </c>
-      <c r="W137" s="36" t="s">
+      <c r="J137" s="35">
+        <v>0</v>
+      </c>
+      <c r="K137" s="35">
+        <v>0</v>
+      </c>
+      <c r="L137" s="35">
+        <v>0</v>
+      </c>
+      <c r="M137" s="35">
+        <v>0</v>
+      </c>
+      <c r="N137" s="35">
+        <v>0</v>
+      </c>
+      <c r="O137" s="35">
+        <v>0</v>
+      </c>
+      <c r="P137" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="35">
+        <v>0</v>
+      </c>
+      <c r="R137" s="35">
+        <v>0</v>
+      </c>
+      <c r="S137" s="35">
+        <v>0</v>
+      </c>
+      <c r="T137" s="35">
+        <v>0</v>
+      </c>
+      <c r="U137" s="35">
+        <v>0</v>
+      </c>
+      <c r="V137" s="35">
+        <v>0</v>
+      </c>
+      <c r="W137" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X137" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y137" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z137" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA137" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB137" s="36">
+      <c r="X137" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="35">
         <v>85020300</v>
       </c>
-      <c r="AC137" s="36">
+      <c r="AC137" s="35">
         <v>0</v>
       </c>
       <c r="AD137" s="5">
@@ -16035,92 +16036,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A138" s="36">
+    <row r="138" spans="1:33" s="35" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="35">
         <v>95100100</v>
       </c>
-      <c r="B138" s="36">
+      <c r="B138" s="35">
         <v>4</v>
       </c>
-      <c r="C138" s="36">
+      <c r="C138" s="35">
         <v>0</v>
       </c>
       <c r="D138" s="5">
         <v>7012</v>
       </c>
-      <c r="E138" s="36">
-        <v>1</v>
-      </c>
-      <c r="F138" s="36" t="s">
+      <c r="E138" s="35">
+        <v>1</v>
+      </c>
+      <c r="F138" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="G138" s="36" t="s">
+      <c r="G138" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="H138" s="37" t="s">
+      <c r="H138" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I138" s="36" t="s">
+      <c r="I138" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="J138" s="36">
-        <v>0</v>
-      </c>
-      <c r="K138" s="36">
-        <v>0</v>
-      </c>
-      <c r="L138" s="36">
-        <v>0</v>
-      </c>
-      <c r="M138" s="36">
-        <v>0</v>
-      </c>
-      <c r="N138" s="36">
-        <v>0</v>
-      </c>
-      <c r="O138" s="36">
-        <v>0</v>
-      </c>
-      <c r="P138" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q138" s="36">
-        <v>0</v>
-      </c>
-      <c r="R138" s="36">
-        <v>0</v>
-      </c>
-      <c r="S138" s="36">
-        <v>0</v>
-      </c>
-      <c r="T138" s="36">
-        <v>0</v>
-      </c>
-      <c r="U138" s="36">
-        <v>0</v>
-      </c>
-      <c r="V138" s="36">
-        <v>0</v>
-      </c>
-      <c r="W138" s="36" t="s">
+      <c r="J138" s="35">
+        <v>0</v>
+      </c>
+      <c r="K138" s="35">
+        <v>0</v>
+      </c>
+      <c r="L138" s="35">
+        <v>0</v>
+      </c>
+      <c r="M138" s="35">
+        <v>0</v>
+      </c>
+      <c r="N138" s="35">
+        <v>0</v>
+      </c>
+      <c r="O138" s="35">
+        <v>0</v>
+      </c>
+      <c r="P138" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="35">
+        <v>0</v>
+      </c>
+      <c r="R138" s="35">
+        <v>0</v>
+      </c>
+      <c r="S138" s="35">
+        <v>0</v>
+      </c>
+      <c r="T138" s="35">
+        <v>0</v>
+      </c>
+      <c r="U138" s="35">
+        <v>0</v>
+      </c>
+      <c r="V138" s="35">
+        <v>0</v>
+      </c>
+      <c r="W138" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X138" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y138" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z138" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA138" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB138" s="36">
+      <c r="X138" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="35">
         <v>85100100</v>
       </c>
-      <c r="AC138" s="36">
+      <c r="AC138" s="35">
         <v>0</v>
       </c>
       <c r="AD138" s="5">
@@ -16136,92 +16137,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A139" s="36">
+    <row r="139" spans="1:33" s="35" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="35">
         <v>95100101</v>
       </c>
-      <c r="B139" s="36">
+      <c r="B139" s="35">
         <v>5</v>
       </c>
-      <c r="C139" s="36">
+      <c r="C139" s="35">
         <v>1</v>
       </c>
       <c r="D139" s="5">
         <v>7013</v>
       </c>
-      <c r="E139" s="36">
-        <v>1</v>
-      </c>
-      <c r="F139" s="36" t="s">
+      <c r="E139" s="35">
+        <v>1</v>
+      </c>
+      <c r="F139" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="G139" s="36" t="s">
+      <c r="G139" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="H139" s="37" t="s">
+      <c r="H139" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I139" s="36" t="s">
+      <c r="I139" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="J139" s="36">
-        <v>0</v>
-      </c>
-      <c r="K139" s="36">
-        <v>0</v>
-      </c>
-      <c r="L139" s="36">
+      <c r="J139" s="35">
+        <v>0</v>
+      </c>
+      <c r="K139" s="35">
+        <v>0</v>
+      </c>
+      <c r="L139" s="35">
         <v>7000</v>
       </c>
-      <c r="M139" s="36">
-        <v>0</v>
-      </c>
-      <c r="N139" s="36">
+      <c r="M139" s="35">
+        <v>0</v>
+      </c>
+      <c r="N139" s="35">
         <v>7500</v>
       </c>
-      <c r="O139" s="36">
-        <v>0</v>
-      </c>
-      <c r="P139" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q139" s="36">
+      <c r="O139" s="35">
+        <v>0</v>
+      </c>
+      <c r="P139" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="35">
         <v>3</v>
       </c>
-      <c r="R139" s="36">
+      <c r="R139" s="35">
         <v>2</v>
       </c>
-      <c r="S139" s="36">
+      <c r="S139" s="35">
         <v>2400</v>
       </c>
-      <c r="T139" s="36">
-        <v>0</v>
-      </c>
-      <c r="U139" s="36">
-        <v>1</v>
-      </c>
-      <c r="V139" s="36">
+      <c r="T139" s="35">
+        <v>0</v>
+      </c>
+      <c r="U139" s="35">
+        <v>1</v>
+      </c>
+      <c r="V139" s="35">
         <v>2</v>
       </c>
-      <c r="W139" s="36" t="s">
+      <c r="W139" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X139" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y139" s="36">
+      <c r="X139" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="35">
         <v>20000</v>
       </c>
-      <c r="Z139" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA139" s="36">
+      <c r="Z139" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="35">
         <v>20000</v>
       </c>
-      <c r="AB139" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC139" s="36">
+      <c r="AB139" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="35">
         <v>0</v>
       </c>
       <c r="AD139" s="5">
@@ -16259,70 +16260,70 @@
       <c r="G140" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="H140" s="37" t="s">
+      <c r="H140" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I140" s="36" t="s">
+      <c r="I140" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="J140" s="36">
-        <v>0</v>
-      </c>
-      <c r="K140" s="36">
-        <v>0</v>
-      </c>
-      <c r="L140" s="36">
-        <v>0</v>
-      </c>
-      <c r="M140" s="36">
-        <v>0</v>
-      </c>
-      <c r="N140" s="36">
-        <v>0</v>
-      </c>
-      <c r="O140" s="36">
-        <v>0</v>
-      </c>
-      <c r="P140" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="36">
-        <v>0</v>
-      </c>
-      <c r="R140" s="36">
-        <v>0</v>
-      </c>
-      <c r="S140" s="36">
-        <v>0</v>
-      </c>
-      <c r="T140" s="36">
-        <v>0</v>
-      </c>
-      <c r="U140" s="36">
-        <v>0</v>
-      </c>
-      <c r="V140" s="36">
-        <v>0</v>
-      </c>
-      <c r="W140" s="36" t="s">
+      <c r="J140" s="35">
+        <v>0</v>
+      </c>
+      <c r="K140" s="35">
+        <v>0</v>
+      </c>
+      <c r="L140" s="35">
+        <v>0</v>
+      </c>
+      <c r="M140" s="35">
+        <v>0</v>
+      </c>
+      <c r="N140" s="35">
+        <v>0</v>
+      </c>
+      <c r="O140" s="35">
+        <v>0</v>
+      </c>
+      <c r="P140" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="35">
+        <v>0</v>
+      </c>
+      <c r="R140" s="35">
+        <v>0</v>
+      </c>
+      <c r="S140" s="35">
+        <v>0</v>
+      </c>
+      <c r="T140" s="35">
+        <v>0</v>
+      </c>
+      <c r="U140" s="35">
+        <v>0</v>
+      </c>
+      <c r="V140" s="35">
+        <v>0</v>
+      </c>
+      <c r="W140" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X140" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y140" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z140" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA140" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB140" s="36">
+      <c r="X140" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y140" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB140" s="35">
         <v>85100300</v>
       </c>
-      <c r="AC140" s="36">
+      <c r="AC140" s="35">
         <v>0</v>
       </c>
       <c r="AD140" s="5">
@@ -16360,70 +16361,70 @@
       <c r="G141" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H141" s="37" t="s">
+      <c r="H141" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I141" s="36" t="s">
+      <c r="I141" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="J141" s="36">
-        <v>0</v>
-      </c>
-      <c r="K141" s="36">
-        <v>0</v>
-      </c>
-      <c r="L141" s="36">
-        <v>0</v>
-      </c>
-      <c r="M141" s="36">
-        <v>0</v>
-      </c>
-      <c r="N141" s="36">
-        <v>0</v>
-      </c>
-      <c r="O141" s="36">
-        <v>0</v>
-      </c>
-      <c r="P141" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q141" s="36">
-        <v>0</v>
-      </c>
-      <c r="R141" s="36">
-        <v>0</v>
-      </c>
-      <c r="S141" s="36">
-        <v>0</v>
-      </c>
-      <c r="T141" s="36">
-        <v>0</v>
-      </c>
-      <c r="U141" s="36">
-        <v>0</v>
-      </c>
-      <c r="V141" s="36">
-        <v>0</v>
-      </c>
-      <c r="W141" s="36" t="s">
+      <c r="J141" s="35">
+        <v>0</v>
+      </c>
+      <c r="K141" s="35">
+        <v>0</v>
+      </c>
+      <c r="L141" s="35">
+        <v>0</v>
+      </c>
+      <c r="M141" s="35">
+        <v>0</v>
+      </c>
+      <c r="N141" s="35">
+        <v>0</v>
+      </c>
+      <c r="O141" s="35">
+        <v>0</v>
+      </c>
+      <c r="P141" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="35">
+        <v>0</v>
+      </c>
+      <c r="R141" s="35">
+        <v>0</v>
+      </c>
+      <c r="S141" s="35">
+        <v>0</v>
+      </c>
+      <c r="T141" s="35">
+        <v>0</v>
+      </c>
+      <c r="U141" s="35">
+        <v>0</v>
+      </c>
+      <c r="V141" s="35">
+        <v>0</v>
+      </c>
+      <c r="W141" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X141" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y141" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z141" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA141" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB141" s="36">
+      <c r="X141" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="35">
         <v>85100500</v>
       </c>
-      <c r="AC141" s="36">
+      <c r="AC141" s="35">
         <v>0</v>
       </c>
       <c r="AD141" s="5">
@@ -16461,70 +16462,70 @@
       <c r="G142" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="H142" s="37" t="s">
+      <c r="H142" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I142" s="36" t="s">
+      <c r="I142" s="35" t="s">
         <v>339</v>
       </c>
-      <c r="J142" s="36">
-        <v>0</v>
-      </c>
-      <c r="K142" s="36">
-        <v>0</v>
-      </c>
-      <c r="L142" s="36">
-        <v>0</v>
-      </c>
-      <c r="M142" s="36">
-        <v>0</v>
-      </c>
-      <c r="N142" s="36">
-        <v>0</v>
-      </c>
-      <c r="O142" s="36">
-        <v>0</v>
-      </c>
-      <c r="P142" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="36">
-        <v>0</v>
-      </c>
-      <c r="R142" s="36">
-        <v>0</v>
-      </c>
-      <c r="S142" s="36">
-        <v>0</v>
-      </c>
-      <c r="T142" s="36">
-        <v>0</v>
-      </c>
-      <c r="U142" s="36">
-        <v>0</v>
-      </c>
-      <c r="V142" s="36">
-        <v>0</v>
-      </c>
-      <c r="W142" s="36" t="s">
+      <c r="J142" s="35">
+        <v>0</v>
+      </c>
+      <c r="K142" s="35">
+        <v>0</v>
+      </c>
+      <c r="L142" s="35">
+        <v>0</v>
+      </c>
+      <c r="M142" s="35">
+        <v>0</v>
+      </c>
+      <c r="N142" s="35">
+        <v>0</v>
+      </c>
+      <c r="O142" s="35">
+        <v>0</v>
+      </c>
+      <c r="P142" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="35">
+        <v>0</v>
+      </c>
+      <c r="R142" s="35">
+        <v>0</v>
+      </c>
+      <c r="S142" s="35">
+        <v>0</v>
+      </c>
+      <c r="T142" s="35">
+        <v>0</v>
+      </c>
+      <c r="U142" s="35">
+        <v>0</v>
+      </c>
+      <c r="V142" s="35">
+        <v>0</v>
+      </c>
+      <c r="W142" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X142" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y142" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z142" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA142" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB142" s="36">
+      <c r="X142" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="35">
         <v>85100700</v>
       </c>
-      <c r="AC142" s="36">
+      <c r="AC142" s="35">
         <v>0</v>
       </c>
       <c r="AD142" s="5">
@@ -16562,70 +16563,70 @@
       <c r="G143" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H143" s="37" t="s">
+      <c r="H143" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I143" s="36" t="s">
+      <c r="I143" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="J143" s="36">
-        <v>0</v>
-      </c>
-      <c r="K143" s="36">
-        <v>0</v>
-      </c>
-      <c r="L143" s="36">
-        <v>0</v>
-      </c>
-      <c r="M143" s="36">
-        <v>0</v>
-      </c>
-      <c r="N143" s="36">
+      <c r="J143" s="35">
+        <v>0</v>
+      </c>
+      <c r="K143" s="35">
+        <v>0</v>
+      </c>
+      <c r="L143" s="35">
+        <v>0</v>
+      </c>
+      <c r="M143" s="35">
+        <v>0</v>
+      </c>
+      <c r="N143" s="35">
         <v>20000</v>
       </c>
-      <c r="O143" s="36">
-        <v>0</v>
-      </c>
-      <c r="P143" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q143" s="36">
+      <c r="O143" s="35">
+        <v>0</v>
+      </c>
+      <c r="P143" s="35">
+        <v>1</v>
+      </c>
+      <c r="Q143" s="35">
         <v>3</v>
       </c>
-      <c r="R143" s="36">
+      <c r="R143" s="35">
         <v>2</v>
       </c>
-      <c r="S143" s="36">
+      <c r="S143" s="35">
         <v>2400</v>
       </c>
-      <c r="T143" s="36">
-        <v>0</v>
-      </c>
-      <c r="U143" s="36">
-        <v>1</v>
-      </c>
-      <c r="V143" s="36">
+      <c r="T143" s="35">
+        <v>0</v>
+      </c>
+      <c r="U143" s="35">
+        <v>1</v>
+      </c>
+      <c r="V143" s="35">
         <v>2</v>
       </c>
-      <c r="W143" s="36" t="s">
+      <c r="W143" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X143" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y143" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z143" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA143" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB143" s="36">
+      <c r="X143" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y143" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB143" s="35">
         <v>85100900</v>
       </c>
-      <c r="AC143" s="36">
+      <c r="AC143" s="35">
         <v>0</v>
       </c>
       <c r="AD143" s="5">
@@ -16663,70 +16664,70 @@
       <c r="G144" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H144" s="37" t="s">
+      <c r="H144" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I144" s="36" t="s">
+      <c r="I144" s="35" t="s">
         <v>348</v>
       </c>
-      <c r="J144" s="36">
-        <v>0</v>
-      </c>
-      <c r="K144" s="36">
-        <v>0</v>
-      </c>
-      <c r="L144" s="36">
-        <v>0</v>
-      </c>
-      <c r="M144" s="36">
-        <v>0</v>
-      </c>
-      <c r="N144" s="36">
-        <v>0</v>
-      </c>
-      <c r="O144" s="36">
-        <v>0</v>
-      </c>
-      <c r="P144" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q144" s="36">
-        <v>1</v>
-      </c>
-      <c r="R144" s="36">
+      <c r="J144" s="35">
+        <v>0</v>
+      </c>
+      <c r="K144" s="35">
+        <v>0</v>
+      </c>
+      <c r="L144" s="35">
+        <v>0</v>
+      </c>
+      <c r="M144" s="35">
+        <v>0</v>
+      </c>
+      <c r="N144" s="35">
+        <v>0</v>
+      </c>
+      <c r="O144" s="35">
+        <v>0</v>
+      </c>
+      <c r="P144" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="35">
+        <v>1</v>
+      </c>
+      <c r="R144" s="35">
         <v>2</v>
       </c>
-      <c r="S144" s="36">
-        <v>0</v>
-      </c>
-      <c r="T144" s="36">
-        <v>0</v>
-      </c>
-      <c r="U144" s="36">
-        <v>0</v>
-      </c>
-      <c r="V144" s="36">
-        <v>0</v>
-      </c>
-      <c r="W144" s="36" t="s">
+      <c r="S144" s="35">
+        <v>0</v>
+      </c>
+      <c r="T144" s="35">
+        <v>0</v>
+      </c>
+      <c r="U144" s="35">
+        <v>0</v>
+      </c>
+      <c r="V144" s="35">
+        <v>0</v>
+      </c>
+      <c r="W144" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X144" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y144" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z144" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB144" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC144" s="36">
+      <c r="X144" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB144" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="35">
         <v>85101100</v>
       </c>
       <c r="AD144" s="5">
@@ -16764,70 +16765,70 @@
       <c r="G145" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H145" s="37" t="s">
+      <c r="H145" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I145" s="36" t="s">
+      <c r="I145" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="J145" s="36">
-        <v>0</v>
-      </c>
-      <c r="K145" s="36">
-        <v>0</v>
-      </c>
-      <c r="L145" s="36">
-        <v>0</v>
-      </c>
-      <c r="M145" s="36">
-        <v>0</v>
-      </c>
-      <c r="N145" s="36">
-        <v>0</v>
-      </c>
-      <c r="O145" s="36">
-        <v>0</v>
-      </c>
-      <c r="P145" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q145" s="36">
-        <v>0</v>
-      </c>
-      <c r="R145" s="36">
-        <v>0</v>
-      </c>
-      <c r="S145" s="36">
-        <v>0</v>
-      </c>
-      <c r="T145" s="36">
-        <v>0</v>
-      </c>
-      <c r="U145" s="36">
-        <v>0</v>
-      </c>
-      <c r="V145" s="36">
-        <v>0</v>
-      </c>
-      <c r="W145" s="36" t="s">
+      <c r="J145" s="35">
+        <v>0</v>
+      </c>
+      <c r="K145" s="35">
+        <v>0</v>
+      </c>
+      <c r="L145" s="35">
+        <v>0</v>
+      </c>
+      <c r="M145" s="35">
+        <v>0</v>
+      </c>
+      <c r="N145" s="35">
+        <v>0</v>
+      </c>
+      <c r="O145" s="35">
+        <v>0</v>
+      </c>
+      <c r="P145" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="35">
+        <v>0</v>
+      </c>
+      <c r="R145" s="35">
+        <v>0</v>
+      </c>
+      <c r="S145" s="35">
+        <v>0</v>
+      </c>
+      <c r="T145" s="35">
+        <v>0</v>
+      </c>
+      <c r="U145" s="35">
+        <v>0</v>
+      </c>
+      <c r="V145" s="35">
+        <v>0</v>
+      </c>
+      <c r="W145" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X145" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y145" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z145" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB145" s="36">
+      <c r="X145" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="35">
         <v>85120300</v>
       </c>
-      <c r="AC145" s="36">
+      <c r="AC145" s="35">
         <v>0</v>
       </c>
       <c r="AD145" s="5">
@@ -16843,92 +16844,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A146" s="36">
+    <row r="146" spans="1:33" s="35" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="35">
         <v>95200100</v>
       </c>
-      <c r="B146" s="36">
+      <c r="B146" s="35">
         <v>4</v>
       </c>
-      <c r="C146" s="36">
+      <c r="C146" s="35">
         <v>0</v>
       </c>
       <c r="D146" s="5">
         <v>7020</v>
       </c>
-      <c r="E146" s="36">
-        <v>1</v>
-      </c>
-      <c r="F146" s="36" t="s">
+      <c r="E146" s="35">
+        <v>1</v>
+      </c>
+      <c r="F146" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="G146" s="36" t="s">
+      <c r="G146" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="H146" s="37" t="s">
+      <c r="H146" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I146" s="36" t="s">
+      <c r="I146" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="J146" s="36">
-        <v>0</v>
-      </c>
-      <c r="K146" s="36">
-        <v>0</v>
-      </c>
-      <c r="L146" s="36">
-        <v>0</v>
-      </c>
-      <c r="M146" s="36">
-        <v>0</v>
-      </c>
-      <c r="N146" s="36">
-        <v>0</v>
-      </c>
-      <c r="O146" s="36">
-        <v>0</v>
-      </c>
-      <c r="P146" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q146" s="36">
-        <v>0</v>
-      </c>
-      <c r="R146" s="36">
-        <v>0</v>
-      </c>
-      <c r="S146" s="36">
-        <v>0</v>
-      </c>
-      <c r="T146" s="36">
-        <v>0</v>
-      </c>
-      <c r="U146" s="36">
-        <v>0</v>
-      </c>
-      <c r="V146" s="36">
-        <v>0</v>
-      </c>
-      <c r="W146" s="36" t="s">
+      <c r="J146" s="35">
+        <v>0</v>
+      </c>
+      <c r="K146" s="35">
+        <v>0</v>
+      </c>
+      <c r="L146" s="35">
+        <v>0</v>
+      </c>
+      <c r="M146" s="35">
+        <v>0</v>
+      </c>
+      <c r="N146" s="35">
+        <v>0</v>
+      </c>
+      <c r="O146" s="35">
+        <v>0</v>
+      </c>
+      <c r="P146" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="35">
+        <v>0</v>
+      </c>
+      <c r="R146" s="35">
+        <v>0</v>
+      </c>
+      <c r="S146" s="35">
+        <v>0</v>
+      </c>
+      <c r="T146" s="35">
+        <v>0</v>
+      </c>
+      <c r="U146" s="35">
+        <v>0</v>
+      </c>
+      <c r="V146" s="35">
+        <v>0</v>
+      </c>
+      <c r="W146" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X146" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y146" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z146" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB146" s="36">
+      <c r="X146" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="35">
         <v>85200100</v>
       </c>
-      <c r="AC146" s="36">
+      <c r="AC146" s="35">
         <v>0</v>
       </c>
       <c r="AD146" s="5">
@@ -16944,92 +16945,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:33" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A147" s="36">
+    <row r="147" spans="1:33" s="35" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A147" s="35">
         <v>95200101</v>
       </c>
-      <c r="B147" s="36">
+      <c r="B147" s="35">
         <v>5</v>
       </c>
-      <c r="C147" s="36">
+      <c r="C147" s="35">
         <v>1</v>
       </c>
       <c r="D147" s="5">
         <v>7021</v>
       </c>
-      <c r="E147" s="36">
-        <v>1</v>
-      </c>
-      <c r="F147" s="36" t="s">
+      <c r="E147" s="35">
+        <v>1</v>
+      </c>
+      <c r="F147" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="G147" s="36" t="s">
+      <c r="G147" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="H147" s="37" t="s">
+      <c r="H147" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I147" s="36" t="s">
+      <c r="I147" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="J147" s="36">
-        <v>0</v>
-      </c>
-      <c r="K147" s="36">
-        <v>0</v>
-      </c>
-      <c r="L147" s="36">
+      <c r="J147" s="35">
+        <v>0</v>
+      </c>
+      <c r="K147" s="35">
+        <v>0</v>
+      </c>
+      <c r="L147" s="35">
         <v>6000</v>
       </c>
-      <c r="M147" s="36">
-        <v>0</v>
-      </c>
-      <c r="N147" s="36">
+      <c r="M147" s="35">
+        <v>0</v>
+      </c>
+      <c r="N147" s="35">
         <v>7500</v>
       </c>
-      <c r="O147" s="36">
-        <v>0</v>
-      </c>
-      <c r="P147" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q147" s="36">
+      <c r="O147" s="35">
+        <v>0</v>
+      </c>
+      <c r="P147" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="35">
         <v>4</v>
       </c>
-      <c r="R147" s="36">
+      <c r="R147" s="35">
         <v>2</v>
       </c>
-      <c r="S147" s="36">
+      <c r="S147" s="35">
         <v>5000</v>
       </c>
-      <c r="T147" s="36">
+      <c r="T147" s="35">
         <v>4</v>
       </c>
-      <c r="U147" s="36">
-        <v>1</v>
-      </c>
-      <c r="V147" s="36">
+      <c r="U147" s="35">
+        <v>1</v>
+      </c>
+      <c r="V147" s="35">
         <v>4</v>
       </c>
-      <c r="W147" s="36" t="s">
+      <c r="W147" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X147" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y147" s="36">
+      <c r="X147" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="35">
         <v>24000</v>
       </c>
-      <c r="Z147" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA147" s="36">
+      <c r="Z147" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="35">
         <v>24000</v>
       </c>
-      <c r="AB147" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC147" s="36">
+      <c r="AB147" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="35">
         <v>0</v>
       </c>
       <c r="AD147" s="5">
@@ -17067,70 +17068,70 @@
       <c r="G148" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H148" s="37" t="s">
+      <c r="H148" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I148" s="36" t="s">
+      <c r="I148" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="J148" s="36">
-        <v>0</v>
-      </c>
-      <c r="K148" s="36">
-        <v>0</v>
-      </c>
-      <c r="L148" s="36">
-        <v>0</v>
-      </c>
-      <c r="M148" s="36">
-        <v>0</v>
-      </c>
-      <c r="N148" s="36">
-        <v>0</v>
-      </c>
-      <c r="O148" s="36">
-        <v>0</v>
-      </c>
-      <c r="P148" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q148" s="36">
-        <v>0</v>
-      </c>
-      <c r="R148" s="36">
-        <v>0</v>
-      </c>
-      <c r="S148" s="36">
-        <v>0</v>
-      </c>
-      <c r="T148" s="36">
-        <v>0</v>
-      </c>
-      <c r="U148" s="36">
-        <v>0</v>
-      </c>
-      <c r="V148" s="36">
-        <v>0</v>
-      </c>
-      <c r="W148" s="36" t="s">
+      <c r="J148" s="35">
+        <v>0</v>
+      </c>
+      <c r="K148" s="35">
+        <v>0</v>
+      </c>
+      <c r="L148" s="35">
+        <v>0</v>
+      </c>
+      <c r="M148" s="35">
+        <v>0</v>
+      </c>
+      <c r="N148" s="35">
+        <v>0</v>
+      </c>
+      <c r="O148" s="35">
+        <v>0</v>
+      </c>
+      <c r="P148" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="35">
+        <v>0</v>
+      </c>
+      <c r="R148" s="35">
+        <v>0</v>
+      </c>
+      <c r="S148" s="35">
+        <v>0</v>
+      </c>
+      <c r="T148" s="35">
+        <v>0</v>
+      </c>
+      <c r="U148" s="35">
+        <v>0</v>
+      </c>
+      <c r="V148" s="35">
+        <v>0</v>
+      </c>
+      <c r="W148" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X148" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y148" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z148" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA148" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB148" s="36">
+      <c r="X148" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="35">
         <v>85200300</v>
       </c>
-      <c r="AC148" s="36">
+      <c r="AC148" s="35">
         <v>0</v>
       </c>
       <c r="AD148" s="5">
@@ -17168,70 +17169,70 @@
       <c r="G149" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="H149" s="37" t="s">
+      <c r="H149" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I149" s="36" t="s">
+      <c r="I149" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="J149" s="36">
-        <v>0</v>
-      </c>
-      <c r="K149" s="36">
-        <v>0</v>
-      </c>
-      <c r="L149" s="36">
-        <v>0</v>
-      </c>
-      <c r="M149" s="36">
-        <v>0</v>
-      </c>
-      <c r="N149" s="36">
-        <v>0</v>
-      </c>
-      <c r="O149" s="36">
-        <v>0</v>
-      </c>
-      <c r="P149" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q149" s="36">
-        <v>0</v>
-      </c>
-      <c r="R149" s="36">
-        <v>0</v>
-      </c>
-      <c r="S149" s="36">
-        <v>0</v>
-      </c>
-      <c r="T149" s="36">
-        <v>0</v>
-      </c>
-      <c r="U149" s="36">
-        <v>0</v>
-      </c>
-      <c r="V149" s="36">
-        <v>0</v>
-      </c>
-      <c r="W149" s="36" t="s">
+      <c r="J149" s="35">
+        <v>0</v>
+      </c>
+      <c r="K149" s="35">
+        <v>0</v>
+      </c>
+      <c r="L149" s="35">
+        <v>0</v>
+      </c>
+      <c r="M149" s="35">
+        <v>0</v>
+      </c>
+      <c r="N149" s="35">
+        <v>0</v>
+      </c>
+      <c r="O149" s="35">
+        <v>0</v>
+      </c>
+      <c r="P149" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="35">
+        <v>0</v>
+      </c>
+      <c r="R149" s="35">
+        <v>0</v>
+      </c>
+      <c r="S149" s="35">
+        <v>0</v>
+      </c>
+      <c r="T149" s="35">
+        <v>0</v>
+      </c>
+      <c r="U149" s="35">
+        <v>0</v>
+      </c>
+      <c r="V149" s="35">
+        <v>0</v>
+      </c>
+      <c r="W149" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X149" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y149" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z149" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA149" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB149" s="36">
+      <c r="X149" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="35">
         <v>85200500</v>
       </c>
-      <c r="AC149" s="36">
+      <c r="AC149" s="35">
         <v>0</v>
       </c>
       <c r="AD149" s="5">
@@ -17269,70 +17270,70 @@
       <c r="G150" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="H150" s="37" t="s">
+      <c r="H150" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I150" s="36" t="s">
+      <c r="I150" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="J150" s="36">
-        <v>0</v>
-      </c>
-      <c r="K150" s="36">
-        <v>0</v>
-      </c>
-      <c r="L150" s="36">
-        <v>0</v>
-      </c>
-      <c r="M150" s="36">
-        <v>0</v>
-      </c>
-      <c r="N150" s="36">
-        <v>0</v>
-      </c>
-      <c r="O150" s="36">
-        <v>0</v>
-      </c>
-      <c r="P150" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q150" s="36">
-        <v>1</v>
-      </c>
-      <c r="R150" s="36">
+      <c r="J150" s="35">
+        <v>0</v>
+      </c>
+      <c r="K150" s="35">
+        <v>0</v>
+      </c>
+      <c r="L150" s="35">
+        <v>0</v>
+      </c>
+      <c r="M150" s="35">
+        <v>0</v>
+      </c>
+      <c r="N150" s="35">
+        <v>0</v>
+      </c>
+      <c r="O150" s="35">
+        <v>0</v>
+      </c>
+      <c r="P150" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="35">
+        <v>1</v>
+      </c>
+      <c r="R150" s="35">
         <v>2</v>
       </c>
-      <c r="S150" s="36">
-        <v>0</v>
-      </c>
-      <c r="T150" s="36">
-        <v>0</v>
-      </c>
-      <c r="U150" s="36">
-        <v>0</v>
-      </c>
-      <c r="V150" s="36">
-        <v>0</v>
-      </c>
-      <c r="W150" s="36" t="s">
+      <c r="S150" s="35">
+        <v>0</v>
+      </c>
+      <c r="T150" s="35">
+        <v>0</v>
+      </c>
+      <c r="U150" s="35">
+        <v>0</v>
+      </c>
+      <c r="V150" s="35">
+        <v>0</v>
+      </c>
+      <c r="W150" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X150" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y150" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z150" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA150" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB150" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC150" s="36">
+      <c r="X150" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="35">
         <v>85200700</v>
       </c>
       <c r="AD150" s="5">
@@ -17370,70 +17371,70 @@
       <c r="G151" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="H151" s="37" t="s">
+      <c r="H151" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I151" s="36" t="s">
+      <c r="I151" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="J151" s="36">
-        <v>0</v>
-      </c>
-      <c r="K151" s="36">
-        <v>0</v>
-      </c>
-      <c r="L151" s="36">
-        <v>0</v>
-      </c>
-      <c r="M151" s="36">
-        <v>0</v>
-      </c>
-      <c r="N151" s="36">
-        <v>0</v>
-      </c>
-      <c r="O151" s="36">
-        <v>0</v>
-      </c>
-      <c r="P151" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q151" s="36">
-        <v>0</v>
-      </c>
-      <c r="R151" s="36">
-        <v>0</v>
-      </c>
-      <c r="S151" s="36">
-        <v>0</v>
-      </c>
-      <c r="T151" s="36">
-        <v>0</v>
-      </c>
-      <c r="U151" s="36">
-        <v>0</v>
-      </c>
-      <c r="V151" s="36">
-        <v>0</v>
-      </c>
-      <c r="W151" s="36" t="s">
+      <c r="J151" s="35">
+        <v>0</v>
+      </c>
+      <c r="K151" s="35">
+        <v>0</v>
+      </c>
+      <c r="L151" s="35">
+        <v>0</v>
+      </c>
+      <c r="M151" s="35">
+        <v>0</v>
+      </c>
+      <c r="N151" s="35">
+        <v>0</v>
+      </c>
+      <c r="O151" s="35">
+        <v>0</v>
+      </c>
+      <c r="P151" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q151" s="35">
+        <v>0</v>
+      </c>
+      <c r="R151" s="35">
+        <v>0</v>
+      </c>
+      <c r="S151" s="35">
+        <v>0</v>
+      </c>
+      <c r="T151" s="35">
+        <v>0</v>
+      </c>
+      <c r="U151" s="35">
+        <v>0</v>
+      </c>
+      <c r="V151" s="35">
+        <v>0</v>
+      </c>
+      <c r="W151" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X151" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y151" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z151" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA151" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB151" s="36">
+      <c r="X151" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="35">
         <v>85220300</v>
       </c>
-      <c r="AC151" s="36">
+      <c r="AC151" s="35">
         <v>0</v>
       </c>
       <c r="AD151" s="5">
@@ -17471,70 +17472,70 @@
       <c r="G152" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="H152" s="37" t="s">
+      <c r="H152" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I152" s="36" t="s">
+      <c r="I152" s="35" t="s">
         <v>345</v>
       </c>
-      <c r="J152" s="36">
-        <v>0</v>
-      </c>
-      <c r="K152" s="36">
-        <v>0</v>
-      </c>
-      <c r="L152" s="36">
-        <v>0</v>
-      </c>
-      <c r="M152" s="36">
-        <v>0</v>
-      </c>
-      <c r="N152" s="36">
-        <v>0</v>
-      </c>
-      <c r="O152" s="36">
-        <v>0</v>
-      </c>
-      <c r="P152" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q152" s="36">
-        <v>0</v>
-      </c>
-      <c r="R152" s="36">
-        <v>0</v>
-      </c>
-      <c r="S152" s="36">
-        <v>0</v>
-      </c>
-      <c r="T152" s="36">
-        <v>0</v>
-      </c>
-      <c r="U152" s="36">
-        <v>0</v>
-      </c>
-      <c r="V152" s="36">
-        <v>0</v>
-      </c>
-      <c r="W152" s="36" t="s">
+      <c r="J152" s="35">
+        <v>0</v>
+      </c>
+      <c r="K152" s="35">
+        <v>0</v>
+      </c>
+      <c r="L152" s="35">
+        <v>0</v>
+      </c>
+      <c r="M152" s="35">
+        <v>0</v>
+      </c>
+      <c r="N152" s="35">
+        <v>0</v>
+      </c>
+      <c r="O152" s="35">
+        <v>0</v>
+      </c>
+      <c r="P152" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q152" s="35">
+        <v>0</v>
+      </c>
+      <c r="R152" s="35">
+        <v>0</v>
+      </c>
+      <c r="S152" s="35">
+        <v>0</v>
+      </c>
+      <c r="T152" s="35">
+        <v>0</v>
+      </c>
+      <c r="U152" s="35">
+        <v>0</v>
+      </c>
+      <c r="V152" s="35">
+        <v>0</v>
+      </c>
+      <c r="W152" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="X152" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y152" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z152" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA152" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB152" s="36">
+      <c r="X152" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="35">
         <v>87000100</v>
       </c>
-      <c r="AC152" s="36">
+      <c r="AC152" s="35">
         <v>0</v>
       </c>
       <c r="AD152" s="5">

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837022DA-D3CB-4597-AA8A-0A1F7EC2F3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC03F38F-463A-4F9D-8BC2-A051782E7BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -15326,7 +15326,7 @@
         <v>0</v>
       </c>
       <c r="AG130" s="5">
-        <v>95001500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.15">
@@ -16235,7 +16235,7 @@
         <v>0</v>
       </c>
       <c r="AG139" s="5">
-        <v>95101100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.15">
@@ -17043,7 +17043,7 @@
         <v>0</v>
       </c>
       <c r="AG147" s="5">
-        <v>95200700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC03F38F-463A-4F9D-8BC2-A051782E7BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF922C7E-6F80-4567-B1EE-E60FC4CEFB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="357">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1583,6 +1583,10 @@
   </si>
   <si>
     <t>0,1,2,3,4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>95001500,95101100,95200700</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1913,7 +1917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1996,6 +2000,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2733,8 +2740,8 @@
       <c r="AF5" s="5">
         <v>0</v>
       </c>
-      <c r="AG5" s="5">
-        <v>0</v>
+      <c r="AG5" s="40" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
@@ -2832,8 +2839,8 @@
       <c r="AF6" s="5">
         <v>0</v>
       </c>
-      <c r="AG6" s="5">
-        <v>0</v>
+      <c r="AG6" s="40" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
@@ -2931,8 +2938,8 @@
       <c r="AF7" s="5">
         <v>0</v>
       </c>
-      <c r="AG7" s="5">
-        <v>0</v>
+      <c r="AG7" s="40" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
@@ -3030,8 +3037,8 @@
       <c r="AF8" s="5">
         <v>0</v>
       </c>
-      <c r="AG8" s="5">
-        <v>0</v>
+      <c r="AG8" s="40" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
@@ -3129,8 +3136,8 @@
       <c r="AF9" s="5">
         <v>0</v>
       </c>
-      <c r="AG9" s="5">
-        <v>0</v>
+      <c r="AG9" s="40" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
@@ -3228,8 +3235,8 @@
       <c r="AF10" s="5">
         <v>0</v>
       </c>
-      <c r="AG10" s="5">
-        <v>0</v>
+      <c r="AG10" s="40" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF922C7E-6F80-4567-B1EE-E60FC4CEFB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D099D258-4694-4ADD-AE41-5087601AE0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -16200,7 +16200,7 @@
         <v>2</v>
       </c>
       <c r="S139" s="35">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="T139" s="35">
         <v>0</v>
@@ -17008,7 +17008,7 @@
         <v>2</v>
       </c>
       <c r="S147" s="35">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="T147" s="35">
         <v>4</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\新技能配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F55147-9040-4DAC-848B-58B601EF51CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A22488-BA42-4848-9321-36CADEE07292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$Z$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +72,28 @@
         </r>
       </text>
     </comment>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I4" authorId="1" shapeId="0" xr:uid="{051313A9-A9F3-47D0-8025-83ECAEF4180F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1 攻击命中造成伤害前
+2 攻击命中造成伤害后
+3 受到攻击伤害前
+4 受到攻击伤害后
+5 击杀目标前
+6 击杀目标后
+7 自身死亡前
+8 自身死亡后</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -89,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J4" authorId="1" shapeId="0" xr:uid="{0EDCE646-B10B-4F69-BE67-60929A0CAD6F}">
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{0EDCE646-B10B-4F69-BE67-60929A0CAD6F}">
       <text>
         <r>
           <rPr>
@@ -115,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="M4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -141,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -169,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -197,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -222,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
+    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
       <text>
         <r>
           <rPr>
@@ -236,7 +257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="T4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -253,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
+    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
       <text>
         <r>
           <rPr>
@@ -270,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="2" shapeId="0" xr:uid="{3BCFFE37-A88F-4166-8915-9D540B7CC094}">
+    <comment ref="V4" authorId="2" shapeId="0" xr:uid="{3BCFFE37-A88F-4166-8915-9D540B7CC094}">
       <text>
         <r>
           <rPr>
@@ -302,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="177">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -860,13 +881,37 @@
   </si>
   <si>
     <t>1:995200101</t>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRING_S</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放时机</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放条件</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>auto_release_condition</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>auto_release_time</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,6 +1012,12 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1056,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1110,6 +1161,7 @@
     <xf numFmtId="20" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1407,7 +1459,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -1417,32 +1469,32 @@
     <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="22.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="58" style="2" customWidth="1"/>
-    <col min="20" max="20" width="61" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="2"/>
+    <col min="8" max="10" width="17.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="22.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="58" style="2" customWidth="1"/>
+    <col min="22" max="22" width="61" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1467,20 +1519,20 @@
       <c r="H2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>85</v>
+      <c r="I2" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>172</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>85</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>55</v>
@@ -1489,25 +1541,25 @@
         <v>55</v>
       </c>
       <c r="P2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>85</v>
@@ -1516,13 +1568,19 @@
         <v>85</v>
       </c>
       <c r="Y2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1547,62 +1605,68 @@
       <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="L3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="M3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="U3" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="V3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="W3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="X3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1627,62 +1691,68 @@
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="K4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="L4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="M4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="R4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="S4" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="U4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="V4" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="W4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="X4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="15" t="s">
+      <c r="Y4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="X4" s="15" t="s">
+      <c r="Z4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10101</v>
       </c>
@@ -1705,62 +1775,68 @@
         <v>32</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
       <c r="N5" s="6">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6">
         <v>3</v>
       </c>
-      <c r="O5" s="6">
+      <c r="Q5" s="6">
         <v>2</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="R5" s="6">
-        <v>1</v>
-      </c>
-      <c r="S5" s="14" t="s">
+      <c r="T5" s="6">
+        <v>1</v>
+      </c>
+      <c r="U5" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="T5" s="14" t="s">
+      <c r="V5" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="Y5" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="7">
+      <c r="AA5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10102</v>
       </c>
@@ -1783,62 +1859,68 @@
         <v>32</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
       <c r="N6" s="6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
         <v>3</v>
       </c>
-      <c r="O6" s="6">
+      <c r="Q6" s="6">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="R6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="S6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="R6" s="6">
-        <v>1</v>
-      </c>
-      <c r="S6" s="14" t="s">
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="T6" s="14" t="s">
+      <c r="V6" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U6" s="6" t="s">
+      <c r="W6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="V6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="Y6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="7">
+      <c r="AA6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10201</v>
       </c>
@@ -1861,62 +1943,68 @@
         <v>32</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="M7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
       <c r="N7" s="6">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6">
         <v>3</v>
       </c>
-      <c r="O7" s="6">
+      <c r="Q7" s="6">
         <v>2</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="R7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="S7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="R7" s="6">
-        <v>1</v>
-      </c>
-      <c r="S7" s="14" t="s">
+      <c r="T7" s="6">
+        <v>1</v>
+      </c>
+      <c r="U7" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="T7" s="14" t="s">
+      <c r="V7" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="W7" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="V7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="Y7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="7">
+      <c r="AA7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10202</v>
       </c>
@@ -1939,62 +2027,68 @@
         <v>32</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="M8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
       <c r="N8" s="6">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6">
         <v>3</v>
       </c>
-      <c r="O8" s="6">
+      <c r="Q8" s="6">
         <v>2</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="R8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="Q8" s="6" t="s">
+      <c r="S8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="R8" s="6">
-        <v>1</v>
-      </c>
-      <c r="S8" s="14" t="s">
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="T8" s="14" t="s">
+      <c r="V8" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="W8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="V8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="Y8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="7">
+      <c r="AA8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10301</v>
       </c>
@@ -2017,62 +2111,68 @@
         <v>32</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="M9" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
       <c r="N9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
         <v>3</v>
       </c>
-      <c r="O9" s="6">
+      <c r="Q9" s="6">
         <v>2</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="R9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="S9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="R9" s="6">
-        <v>1</v>
-      </c>
-      <c r="S9" s="14" t="s">
+      <c r="T9" s="6">
+        <v>1</v>
+      </c>
+      <c r="U9" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="T9" s="14" t="s">
+      <c r="V9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="W9" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Z9" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="Y9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="7">
+      <c r="AA9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10302</v>
       </c>
@@ -2095,62 +2195,68 @@
         <v>32</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="M10" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
       <c r="N10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
         <v>3</v>
       </c>
-      <c r="O10" s="6">
+      <c r="Q10" s="6">
         <v>2</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="R10" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="S10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="R10" s="6">
-        <v>1</v>
-      </c>
-      <c r="S10" s="14" t="s">
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="T10" s="14" t="s">
+      <c r="V10" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U10" s="6" t="s">
+      <c r="W10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="V10" s="6" t="s">
+      <c r="X10" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="W10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Z10" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Y10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="7">
+      <c r="AA10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>201001011</v>
       </c>
@@ -2175,47 +2281,47 @@
       <c r="H11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>28</v>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
       <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
         <v>3</v>
       </c>
-      <c r="O11" s="1">
+      <c r="Q11" s="1">
         <v>2</v>
       </c>
-      <c r="P11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" s="18" t="s">
+      <c r="R11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S11" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="R11" s="1">
-        <v>1</v>
-      </c>
-      <c r="S11" s="12">
-        <v>0</v>
-      </c>
-      <c r="T11" s="12" t="s">
+      <c r="T11" s="1">
+        <v>1</v>
+      </c>
+      <c r="U11" s="12">
+        <v>0</v>
+      </c>
+      <c r="V11" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>28</v>
@@ -2223,14 +2329,20 @@
       <c r="X11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Y11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="1">
+      <c r="Y11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>201002011</v>
       </c>
@@ -2255,47 +2367,47 @@
       <c r="H12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>28</v>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
       <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
         <v>3</v>
       </c>
-      <c r="O12" s="1">
+      <c r="Q12" s="1">
         <v>2</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R12" s="1">
-        <v>1</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12" t="s">
+      <c r="T12" s="1">
+        <v>1</v>
+      </c>
+      <c r="U12" s="12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>28</v>
@@ -2303,14 +2415,20 @@
       <c r="X12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Y12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="1">
+      <c r="Y12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>201004011</v>
       </c>
@@ -2335,47 +2453,47 @@
       <c r="H13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>28</v>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
       <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
         <v>3</v>
       </c>
-      <c r="O13" s="1">
+      <c r="Q13" s="1">
         <v>2</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R13" s="1">
-        <v>1</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12" t="s">
+      <c r="T13" s="1">
+        <v>1</v>
+      </c>
+      <c r="U13" s="12">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>28</v>
@@ -2383,14 +2501,20 @@
       <c r="X13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="1">
+      <c r="Y13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>214001011</v>
       </c>
@@ -2415,47 +2539,47 @@
       <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>28</v>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>1</v>
-      </c>
       <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
         <v>3</v>
       </c>
-      <c r="O14" s="1">
+      <c r="Q14" s="1">
         <v>2</v>
       </c>
-      <c r="P14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="1" t="s">
+      <c r="R14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R14" s="1">
-        <v>1</v>
-      </c>
-      <c r="S14" s="12">
-        <v>0</v>
-      </c>
-      <c r="T14" s="12" t="s">
+      <c r="T14" s="1">
+        <v>1</v>
+      </c>
+      <c r="U14" s="12">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>28</v>
@@ -2463,14 +2587,20 @@
       <c r="X14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Y14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="1">
+      <c r="Y14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>203002011</v>
       </c>
@@ -2495,47 +2625,47 @@
       <c r="H15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>28</v>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>1</v>
-      </c>
       <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
         <v>3</v>
       </c>
-      <c r="O15" s="1">
+      <c r="Q15" s="1">
         <v>2</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q15" s="1" t="s">
+      <c r="R15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R15" s="1">
-        <v>1</v>
-      </c>
-      <c r="S15" s="12">
-        <v>0</v>
-      </c>
-      <c r="T15" s="12" t="s">
+      <c r="T15" s="1">
+        <v>1</v>
+      </c>
+      <c r="U15" s="12">
+        <v>0</v>
+      </c>
+      <c r="V15" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>28</v>
@@ -2543,14 +2673,20 @@
       <c r="X15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="1">
+      <c r="Y15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A16" s="10">
         <v>25010001</v>
       </c>
@@ -2575,62 +2711,68 @@
       <c r="H16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>28</v>
+      <c r="I16" s="10">
+        <v>0</v>
+      </c>
+      <c r="J16" s="10">
+        <v>0</v>
       </c>
       <c r="K16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="10">
-        <v>0</v>
-      </c>
-      <c r="M16" s="10">
-        <v>0</v>
-      </c>
       <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>0</v>
+      </c>
+      <c r="P16" s="10">
         <v>2</v>
       </c>
-      <c r="O16" s="10">
-        <v>1</v>
-      </c>
-      <c r="P16" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q16" s="10" t="s">
+      <c r="Q16" s="10">
+        <v>1</v>
+      </c>
+      <c r="R16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S16" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="R16" s="10">
-        <v>1</v>
-      </c>
-      <c r="S16" s="10">
-        <v>0</v>
-      </c>
-      <c r="T16" s="10" t="s">
+      <c r="T16" s="10">
+        <v>1</v>
+      </c>
+      <c r="U16" s="10">
+        <v>0</v>
+      </c>
+      <c r="V16" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="U16" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="V16" s="10" t="s">
-        <v>28</v>
-      </c>
       <c r="W16" s="10" t="s">
         <v>28</v>
       </c>
       <c r="X16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Y16" s="10">
+      <c r="Y16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA16" s="10">
         <v>54150001</v>
       </c>
-      <c r="Z16" s="10">
+      <c r="AB16" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13">
         <v>95000101</v>
       </c>
@@ -2655,62 +2797,68 @@
       <c r="H17" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="13">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13">
+        <v>0</v>
+      </c>
+      <c r="K17" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="L17" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="M17" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0</v>
-      </c>
       <c r="N17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="13">
+        <v>0</v>
+      </c>
+      <c r="P17" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="13">
         <v>2</v>
       </c>
-      <c r="P17" s="13" t="s">
+      <c r="R17" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="Q17" s="13" t="s">
+      <c r="S17" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="R17" s="13">
-        <v>1</v>
-      </c>
-      <c r="S17" s="13">
-        <v>1</v>
-      </c>
-      <c r="T17" s="13" t="s">
+      <c r="T17" s="13">
+        <v>1</v>
+      </c>
+      <c r="U17" s="13">
+        <v>1</v>
+      </c>
+      <c r="V17" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="U17" s="13" t="s">
+      <c r="W17" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="V17" s="13" t="s">
+      <c r="X17" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="W17" s="13" t="s">
+      <c r="Y17" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="X17" s="13" t="s">
+      <c r="Z17" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="Y17" s="13">
+      <c r="AA17" s="13">
         <v>85001100</v>
       </c>
-      <c r="Z17" s="13">
+      <c r="AB17" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:26" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
         <v>95100101</v>
       </c>
@@ -2735,62 +2883,68 @@
       <c r="H18" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="13">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13">
+        <v>0</v>
+      </c>
+      <c r="K18" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="L18" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="M18" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="L18" s="13">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0</v>
-      </c>
       <c r="N18" s="13">
+        <v>0</v>
+      </c>
+      <c r="O18" s="13">
+        <v>0</v>
+      </c>
+      <c r="P18" s="13">
         <v>3</v>
       </c>
-      <c r="O18" s="13">
+      <c r="Q18" s="13">
         <v>2</v>
       </c>
-      <c r="P18" s="13" t="s">
+      <c r="R18" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="Q18" s="13" t="s">
+      <c r="S18" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="R18" s="13">
-        <v>1</v>
-      </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
+        <v>1</v>
+      </c>
+      <c r="U18" s="13">
         <v>2</v>
       </c>
-      <c r="T18" s="13" t="s">
+      <c r="V18" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="U18" s="13" t="s">
+      <c r="W18" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="V18" s="13" t="s">
+      <c r="X18" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="W18" s="13" t="s">
+      <c r="Y18" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="X18" s="13" t="s">
+      <c r="Z18" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="Y18" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="13">
+      <c r="AA18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:26" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
         <v>95200101</v>
       </c>
@@ -2815,58 +2969,64 @@
       <c r="H19" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="13">
+        <v>0</v>
+      </c>
+      <c r="J19" s="13">
+        <v>0</v>
+      </c>
+      <c r="K19" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="L19" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="M19" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="L19" s="13">
-        <v>0</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0</v>
-      </c>
       <c r="N19" s="13">
+        <v>0</v>
+      </c>
+      <c r="O19" s="13">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13">
         <v>4</v>
       </c>
-      <c r="O19" s="13">
+      <c r="Q19" s="13">
         <v>2</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="R19" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="Q19" s="13" t="s">
+      <c r="S19" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="R19" s="13">
-        <v>1</v>
-      </c>
-      <c r="S19" s="13">
+      <c r="T19" s="13">
+        <v>1</v>
+      </c>
+      <c r="U19" s="13">
         <v>4</v>
       </c>
-      <c r="T19" s="13" t="s">
+      <c r="V19" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="U19" s="13" t="s">
+      <c r="W19" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="V19" s="13" t="s">
+      <c r="X19" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="W19" s="13" t="s">
+      <c r="Y19" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="X19" s="13" t="s">
+      <c r="Z19" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="Y19" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="13">
+      <c r="AA19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="13">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D099D258-4694-4ADD-AE41-5087601AE0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050D6C8F-CEF8-40CB-942A-448DA707A20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4991,7 +4991,7 @@
         <v>500</v>
       </c>
       <c r="L28" s="2">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="M28" s="2">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>500</v>
       </c>
       <c r="L29" s="2">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="M29" s="2">
         <v>0</v>
@@ -5193,7 +5193,7 @@
         <v>500</v>
       </c>
       <c r="L30" s="2">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="M30" s="2">
         <v>0</v>
@@ -5294,7 +5294,7 @@
         <v>800</v>
       </c>
       <c r="L31" s="2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M31" s="2">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>500</v>
       </c>
       <c r="L32" s="2">
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="M32" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050D6C8F-CEF8-40CB-942A-448DA707A20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D099D258-4694-4ADD-AE41-5087601AE0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4991,7 +4991,7 @@
         <v>500</v>
       </c>
       <c r="L28" s="2">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>500</v>
       </c>
       <c r="L29" s="2">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2">
         <v>0</v>
@@ -5193,7 +5193,7 @@
         <v>500</v>
       </c>
       <c r="L30" s="2">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2">
         <v>0</v>
@@ -5294,7 +5294,7 @@
         <v>800</v>
       </c>
       <c r="L31" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>500</v>
       </c>
       <c r="L32" s="2">
-        <v>830</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\新技能配置\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A22488-BA42-4848-9321-36CADEE07292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF23FE8-0DD0-4785-AFB5-AD3C4F81E0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="192">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -904,6 +904,66 @@
   </si>
   <si>
     <t>auto_release_time</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:550</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:525</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:435</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:450</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域内每秒造成燃烧伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:8920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9920001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1107,7 +1167,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1162,6 +1222,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1459,7 +1522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -2287,8 +2350,8 @@
       <c r="J11" s="1">
         <v>0</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>28</v>
+      <c r="K11" s="20" t="s">
+        <v>177</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>28</v>
@@ -2373,8 +2436,8 @@
       <c r="J12" s="1">
         <v>0</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>28</v>
+      <c r="K12" s="20" t="s">
+        <v>178</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>28</v>
@@ -2459,8 +2522,8 @@
       <c r="J13" s="1">
         <v>0</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>28</v>
+      <c r="K13" s="20" t="s">
+        <v>179</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>28</v>
@@ -2545,8 +2608,8 @@
       <c r="J14" s="1">
         <v>0</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>28</v>
+      <c r="K14" s="20" t="s">
+        <v>180</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>28</v>
@@ -2631,8 +2694,8 @@
       <c r="J15" s="1">
         <v>0</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>28</v>
+      <c r="K15" s="20" t="s">
+        <v>180</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>28</v>
@@ -3028,6 +3091,92 @@
       </c>
       <c r="AB19" s="13">
         <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>20001</v>
+      </c>
+      <c r="B20" s="2">
+        <v>920001</v>
+      </c>
+      <c r="C20" s="2">
+        <v>5</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>2</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="T20" s="2">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W20" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="X20" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y20" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z20" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>85101100</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF23FE8-0DD0-4785-AFB5-AD3C4F81E0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6717778A-9501-4C63-9CE0-A2D6796620EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,21 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{1470E070-7A06-4482-BB77-BBC87D296DF9}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0-没有额外释放条件
-1-只有进入战斗才会释放技能</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="1" shapeId="0" xr:uid="{051313A9-A9F3-47D0-8025-83ECAEF4180F}">
+    <comment ref="H4" authorId="1" shapeId="0" xr:uid="{051313A9-A9F3-47D0-8025-83ECAEF4180F}">
       <text>
         <r>
           <rPr>
@@ -93,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -110,7 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{0EDCE646-B10B-4F69-BE67-60929A0CAD6F}">
+    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{0EDCE646-B10B-4F69-BE67-60929A0CAD6F}">
       <text>
         <r>
           <rPr>
@@ -136,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -162,7 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -190,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -218,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -243,7 +229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
+    <comment ref="R4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
       <text>
         <r>
           <rPr>
@@ -257,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -274,7 +260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
+    <comment ref="T4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
       <text>
         <r>
           <rPr>
@@ -291,7 +277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="2" shapeId="0" xr:uid="{3BCFFE37-A88F-4166-8915-9D540B7CC094}">
+    <comment ref="U4" authorId="2" shapeId="0" xr:uid="{3BCFFE37-A88F-4166-8915-9D540B7CC094}">
       <text>
         <r>
           <rPr>
@@ -323,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="190">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -580,14 +566,6 @@
   </si>
   <si>
     <t>僵尸等级2精英</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能释放条件</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>release_condition</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1522,42 +1500,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="17.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="22.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19" style="2" customWidth="1"/>
-    <col min="16" max="16" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="58" style="2" customWidth="1"/>
-    <col min="22" max="22" width="61" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="17.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="58" style="2" customWidth="1"/>
+    <col min="21" max="21" width="61" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1567,35 +1543,35 @@
       <c r="C2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>55</v>
@@ -1607,215 +1583,206 @@
         <v>55</v>
       </c>
       <c r="Q2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>55</v>
+      <c r="T2" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="U2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="V2" s="11" t="s">
-        <v>62</v>
+      <c r="V2" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AB2" s="2" t="s">
-        <v>56</v>
-      </c>
     </row>
-    <row r="3" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="H3" s="19" t="s">
+        <v>174</v>
+      </c>
       <c r="I3" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>175</v>
+        <v>173</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="15" t="s">
         <v>38</v>
       </c>
+      <c r="M3" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="N3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q3" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="Q3" s="16" t="s">
+        <v>44</v>
+      </c>
       <c r="R3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="T3" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="U3" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" s="15" t="s">
         <v>13</v>
       </c>
+      <c r="X3" s="16" t="s">
+        <v>33</v>
+      </c>
       <c r="Y3" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z3" s="16" t="s">
         <v>35</v>
       </c>
+      <c r="Z3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="AA3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="H4" s="19" t="s">
+        <v>171</v>
+      </c>
       <c r="I4" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="15" t="s">
         <v>39</v>
       </c>
+      <c r="M4" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="N4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="Q4" s="15" t="s">
+        <v>41</v>
+      </c>
       <c r="R4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="T4" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="U4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="Y4" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z4" s="15" t="s">
         <v>36</v>
       </c>
+      <c r="Z4" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="AA4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10101</v>
       </c>
@@ -1826,80 +1793,77 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
       <c r="I5" s="6">
         <v>0</v>
       </c>
-      <c r="J5" s="6">
-        <v>0</v>
+      <c r="J5" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <v>3</v>
+      </c>
+      <c r="P5" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="N5" s="6">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>2</v>
-      </c>
-      <c r="R5" s="6" t="s">
+      <c r="S5" s="6">
+        <v>1</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="T5" s="6">
-        <v>1</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X5" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="Y5" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="7">
+        <v>88</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10102</v>
       </c>
@@ -1910,80 +1874,77 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
-      <c r="J6" s="6">
-        <v>0</v>
+      <c r="J6" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <v>3</v>
+      </c>
+      <c r="P6" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="R6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>2</v>
-      </c>
-      <c r="R6" s="6" t="s">
+      <c r="S6" s="6">
+        <v>1</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="W6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="T6" s="6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="V6" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="Y6" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="7">
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10201</v>
       </c>
@@ -1994,80 +1955,77 @@
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
         <v>2</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
       <c r="I7" s="6">
         <v>0</v>
       </c>
-      <c r="J7" s="6">
-        <v>0</v>
+      <c r="J7" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="L7" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>3</v>
+      </c>
+      <c r="P7" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="R7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>2</v>
-      </c>
-      <c r="R7" s="6" t="s">
+      <c r="S7" s="6">
+        <v>1</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="W7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="T7" s="6">
-        <v>1</v>
-      </c>
-      <c r="U7" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="V7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="Y7" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="7">
+      <c r="Z7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10202</v>
       </c>
@@ -2078,80 +2036,77 @@
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
         <v>2</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
       <c r="I8" s="6">
         <v>0</v>
       </c>
-      <c r="J8" s="6">
-        <v>0</v>
+      <c r="J8" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="K8" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6">
+        <v>3</v>
+      </c>
+      <c r="P8" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="R8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>2</v>
-      </c>
-      <c r="R8" s="6" t="s">
+      <c r="S8" s="6">
+        <v>1</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="W8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T8" s="6">
-        <v>1</v>
-      </c>
-      <c r="U8" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="V8" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="Y8" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="7">
+      <c r="Z8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10301</v>
       </c>
@@ -2162,80 +2117,77 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
         <v>3</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
       <c r="I9" s="6">
         <v>0</v>
       </c>
-      <c r="J9" s="6">
-        <v>0</v>
+      <c r="J9" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="K9" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <v>3</v>
+      </c>
+      <c r="P9" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="R9" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="N9" s="6">
-        <v>0</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>2</v>
-      </c>
-      <c r="R9" s="6" t="s">
+      <c r="S9" s="6">
+        <v>1</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="W9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="6">
-        <v>1</v>
-      </c>
-      <c r="U9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="V9" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="Y9" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="7">
+      <c r="Z9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10302</v>
       </c>
@@ -2246,80 +2198,77 @@
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
         <v>3</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
       <c r="I10" s="6">
         <v>0</v>
       </c>
-      <c r="J10" s="6">
-        <v>0</v>
+      <c r="J10" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="K10" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>3</v>
+      </c>
+      <c r="P10" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="R10" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="N10" s="6">
-        <v>0</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>2</v>
-      </c>
-      <c r="R10" s="6" t="s">
+      <c r="S10" s="6">
+        <v>1</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V10" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="W10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="T10" s="6">
-        <v>1</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W10" s="6" t="s">
+      <c r="X10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Y10" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="7">
+      <c r="Z10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>201001011</v>
       </c>
@@ -2330,82 +2279,79 @@
         <v>2</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>70</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>177</v>
+      <c r="J11" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>3</v>
+      </c>
+      <c r="P11" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="R11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>1</v>
-      </c>
-      <c r="P11" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>2</v>
-      </c>
-      <c r="R11" s="1" t="s">
+      <c r="S11" s="1">
+        <v>1</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S11" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="T11" s="1">
-        <v>1</v>
-      </c>
-      <c r="U11" s="12">
-        <v>0</v>
-      </c>
-      <c r="V11" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="W11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="X11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X11" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="Y11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
       </c>
       <c r="AA11" s="1">
         <v>0</v>
       </c>
-      <c r="AB11" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>201002011</v>
       </c>
@@ -2416,82 +2362,79 @@
         <v>2</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>71</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>178</v>
+      <c r="J12" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="L12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>2</v>
-      </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="T12" s="1">
-        <v>1</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="W12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X12" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="Y12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
       </c>
-      <c r="AB12" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>201004011</v>
       </c>
@@ -2502,82 +2445,79 @@
         <v>2</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>72</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="20" t="s">
-        <v>179</v>
+      <c r="J13" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>3</v>
+      </c>
+      <c r="P13" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>1</v>
-      </c>
-      <c r="P13" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>2</v>
-      </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1">
+        <v>1</v>
+      </c>
+      <c r="T13" s="12">
+        <v>0</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="T13" s="1">
-        <v>1</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="W13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X13" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="Y13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
       </c>
-      <c r="AB13" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>214001011</v>
       </c>
@@ -2588,82 +2528,79 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>73</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>180</v>
+      <c r="J14" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>3</v>
+      </c>
+      <c r="P14" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>1</v>
-      </c>
-      <c r="P14" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>2</v>
-      </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+      <c r="T14" s="12">
+        <v>0</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="T14" s="1">
-        <v>1</v>
-      </c>
-      <c r="U14" s="12">
-        <v>0</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="W14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X14" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="Y14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
       </c>
       <c r="AA14" s="1">
         <v>0</v>
       </c>
-      <c r="AB14" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>203002011</v>
       </c>
@@ -2674,82 +2611,79 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>74</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>180</v>
+      <c r="J15" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
+        <v>3</v>
+      </c>
+      <c r="P15" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="R15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>1</v>
-      </c>
-      <c r="P15" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>2</v>
-      </c>
-      <c r="R15" s="1" t="s">
+      <c r="S15" s="1">
+        <v>1</v>
+      </c>
+      <c r="T15" s="12">
+        <v>0</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="T15" s="1">
-        <v>1</v>
-      </c>
-      <c r="U15" s="12">
-        <v>0</v>
-      </c>
-      <c r="V15" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="W15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X15" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="Y15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>0</v>
       </c>
       <c r="AA15" s="1">
         <v>0</v>
       </c>
-      <c r="AB15" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A16" s="10">
         <v>25010001</v>
       </c>
@@ -2760,61 +2694,61 @@
         <v>2</v>
       </c>
       <c r="D16" s="10">
-        <v>0</v>
-      </c>
-      <c r="E16" s="10">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="F16" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="G16" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="10" t="s">
         <v>60</v>
       </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
       <c r="I16" s="10">
         <v>0</v>
       </c>
-      <c r="J16" s="10">
-        <v>0</v>
+      <c r="J16" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="K16" s="10" t="s">
         <v>28</v>
       </c>
       <c r="L16" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="M16" s="10">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>2</v>
+      </c>
+      <c r="P16" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="R16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="N16" s="10">
-        <v>0</v>
-      </c>
-      <c r="O16" s="10">
-        <v>0</v>
-      </c>
-      <c r="P16" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>1</v>
-      </c>
-      <c r="R16" s="10" t="s">
+      <c r="S16" s="10">
+        <v>1</v>
+      </c>
+      <c r="T16" s="10">
+        <v>0</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="V16" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="S16" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="T16" s="10">
-        <v>1</v>
-      </c>
-      <c r="U16" s="10">
-        <v>0</v>
-      </c>
-      <c r="V16" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="W16" s="10" t="s">
         <v>28</v>
@@ -2825,17 +2759,14 @@
       <c r="Y16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="10" t="s">
-        <v>28</v>
+      <c r="Z16" s="10">
+        <v>54150001</v>
       </c>
       <c r="AA16" s="10">
-        <v>54150001</v>
-      </c>
-      <c r="AB16" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13">
         <v>95000101</v>
       </c>
@@ -2848,80 +2779,77 @@
       <c r="D17" s="13">
         <v>1</v>
       </c>
-      <c r="E17" s="13">
-        <v>1</v>
+      <c r="E17" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>66</v>
+      <c r="H17" s="13">
+        <v>0</v>
       </c>
       <c r="I17" s="13">
         <v>0</v>
       </c>
-      <c r="J17" s="13">
-        <v>0</v>
+      <c r="J17" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="K17" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="L17" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="M17" s="13">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13">
+        <v>0</v>
+      </c>
+      <c r="O17" s="13">
+        <v>1</v>
+      </c>
+      <c r="P17" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M17" s="13" t="s">
+      <c r="R17" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N17" s="13">
-        <v>0</v>
-      </c>
-      <c r="O17" s="13">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>2</v>
-      </c>
-      <c r="R17" s="13" t="s">
+      <c r="S17" s="13">
+        <v>1</v>
+      </c>
+      <c r="T17" s="13">
+        <v>1</v>
+      </c>
+      <c r="U17" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="V17" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="S17" s="13" t="s">
+      <c r="W17" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="T17" s="13">
-        <v>1</v>
-      </c>
-      <c r="U17" s="13">
-        <v>1</v>
-      </c>
-      <c r="V17" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="W17" s="13" t="s">
+      <c r="X17" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="X17" s="13" t="s">
+      <c r="Y17" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="Y17" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z17" s="13" t="s">
-        <v>152</v>
+      <c r="Z17" s="13">
+        <v>85001100</v>
       </c>
       <c r="AA17" s="13">
-        <v>85001100</v>
-      </c>
-      <c r="AB17" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
         <v>95100101</v>
       </c>
@@ -2934,80 +2862,77 @@
       <c r="D18" s="13">
         <v>1</v>
       </c>
-      <c r="E18" s="13">
-        <v>1</v>
+      <c r="E18" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H18" s="13" t="s">
-        <v>67</v>
+      <c r="H18" s="13">
+        <v>0</v>
       </c>
       <c r="I18" s="13">
         <v>0</v>
       </c>
-      <c r="J18" s="13">
-        <v>0</v>
+      <c r="J18" s="13" t="s">
+        <v>151</v>
       </c>
       <c r="K18" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="L18" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="M18" s="13">
+        <v>0</v>
+      </c>
+      <c r="N18" s="13">
+        <v>0</v>
+      </c>
+      <c r="O18" s="13">
+        <v>3</v>
+      </c>
+      <c r="P18" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="M18" s="13" t="s">
+      <c r="R18" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="N18" s="13">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="13">
+      <c r="S18" s="13">
+        <v>1</v>
+      </c>
+      <c r="T18" s="13">
         <v>2</v>
       </c>
-      <c r="R18" s="13" t="s">
+      <c r="U18" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="V18" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="S18" s="13" t="s">
+      <c r="W18" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="T18" s="13">
-        <v>1</v>
-      </c>
-      <c r="U18" s="13">
-        <v>2</v>
-      </c>
-      <c r="V18" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="W18" s="13" t="s">
+      <c r="X18" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="X18" s="13" t="s">
+      <c r="Y18" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="Y18" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z18" s="13" t="s">
-        <v>161</v>
+      <c r="Z18" s="13">
+        <v>0</v>
       </c>
       <c r="AA18" s="13">
         <v>0</v>
       </c>
-      <c r="AB18" s="13">
-        <v>0</v>
-      </c>
     </row>
-    <row r="19" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
         <v>95200101</v>
       </c>
@@ -3020,80 +2945,77 @@
       <c r="D19" s="13">
         <v>1</v>
       </c>
-      <c r="E19" s="13">
-        <v>1</v>
+      <c r="E19" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>65</v>
+      <c r="H19" s="13">
+        <v>0</v>
       </c>
       <c r="I19" s="13">
         <v>0</v>
       </c>
-      <c r="J19" s="13">
-        <v>0</v>
+      <c r="J19" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="K19" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L19" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="M19" s="13">
+        <v>0</v>
+      </c>
+      <c r="N19" s="13">
+        <v>0</v>
+      </c>
+      <c r="O19" s="13">
+        <v>4</v>
+      </c>
+      <c r="P19" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="M19" s="13" t="s">
+      <c r="R19" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="N19" s="13">
-        <v>0</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
+      <c r="S19" s="13">
+        <v>1</v>
+      </c>
+      <c r="T19" s="13">
         <v>4</v>
       </c>
-      <c r="Q19" s="13">
-        <v>2</v>
-      </c>
-      <c r="R19" s="13" t="s">
+      <c r="U19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="V19" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="S19" s="13" t="s">
+      <c r="W19" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="T19" s="13">
-        <v>1</v>
-      </c>
-      <c r="U19" s="13">
-        <v>4</v>
-      </c>
-      <c r="V19" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="W19" s="13" t="s">
+      <c r="X19" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="X19" s="13" t="s">
+      <c r="Y19" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="Y19" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="Z19" s="13" t="s">
-        <v>170</v>
+      <c r="Z19" s="13">
+        <v>0</v>
       </c>
       <c r="AA19" s="13">
         <v>0</v>
       </c>
-      <c r="AB19" s="13">
-        <v>0</v>
-      </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20001</v>
       </c>
@@ -3106,77 +3028,74 @@
       <c r="D20" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="2">
-        <v>1</v>
+      <c r="E20" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>720001</v>
+      </c>
+      <c r="J20" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="K20" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13" t="s">
+      <c r="L20" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2">
+        <v>4</v>
+      </c>
+      <c r="P20" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="M20" s="13" t="s">
+      <c r="R20" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="N20" s="2">
-        <v>0</v>
-      </c>
-      <c r="O20" s="2">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="2">
+      <c r="S20" s="2">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2">
         <v>2</v>
       </c>
-      <c r="R20" s="13" t="s">
+      <c r="U20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V20" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="S20" s="13" t="s">
+      <c r="W20" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="T20" s="2">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="W20" s="13" t="s">
+      <c r="X20" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="Y20" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="Y20" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z20" s="13" t="s">
-        <v>191</v>
+      <c r="Z20" s="2">
+        <v>0</v>
       </c>
       <c r="AA20" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="2">
-        <v>85101100</v>
+        <v>820001</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6717778A-9501-4C63-9CE0-A2D6796620EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ED7F29-B55E-44AC-8564-4C8E1AFD91A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="200">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -942,6 +942,45 @@
   </si>
   <si>
     <t>1:9920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血</t>
+  </si>
+  <si>
+    <t>1:159260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:259260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:359260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:459260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:559260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:659260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:759260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:859260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:959260001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1500,7 +1539,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -2683,178 +2722,174 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A16" s="10">
+    <row r="16" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>59260001</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3592200</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
+      <c r="I16" s="1">
+        <v>26010001</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>2</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="S16" s="1">
+        <v>1</v>
+      </c>
+      <c r="T16" s="12">
+        <v>0</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>59260001</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A17" s="10">
         <v>25010001</v>
       </c>
-      <c r="B16" s="10">
-        <v>0</v>
-      </c>
-      <c r="C16" s="10">
+      <c r="B17" s="10">
+        <v>0</v>
+      </c>
+      <c r="C17" s="10">
         <v>2</v>
       </c>
-      <c r="D16" s="10">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F17" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G17" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H16" s="10">
-        <v>0</v>
-      </c>
-      <c r="I16" s="10">
-        <v>0</v>
-      </c>
-      <c r="J16" s="10" t="s">
+      <c r="H17" s="10">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="M16" s="10">
-        <v>0</v>
-      </c>
-      <c r="N16" s="10">
-        <v>0</v>
-      </c>
-      <c r="O16" s="10">
+      <c r="M17" s="10">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
         <v>2</v>
       </c>
-      <c r="P16" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="10" t="s">
+      <c r="P17" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="R16" s="10" t="s">
+      <c r="R17" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="S16" s="10">
-        <v>1</v>
-      </c>
-      <c r="T16" s="10">
-        <v>0</v>
-      </c>
-      <c r="U16" s="10" t="s">
+      <c r="S17" s="10">
+        <v>1</v>
+      </c>
+      <c r="T17" s="10">
+        <v>0</v>
+      </c>
+      <c r="U17" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="V16" s="10" t="s">
+      <c r="V17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="W16" s="10" t="s">
+      <c r="W17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="X16" s="10" t="s">
+      <c r="X17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Y16" s="10" t="s">
+      <c r="Y17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="10">
+      <c r="Z17" s="10">
         <v>54150001</v>
       </c>
-      <c r="AA16" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13">
-        <v>95000101</v>
-      </c>
-      <c r="B17" s="13">
-        <v>95000101</v>
-      </c>
-      <c r="C17" s="13">
-        <v>5</v>
-      </c>
-      <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13">
-        <v>0</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0</v>
-      </c>
-      <c r="N17" s="13">
-        <v>0</v>
-      </c>
-      <c r="O17" s="13">
-        <v>1</v>
-      </c>
-      <c r="P17" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="S17" s="13">
-        <v>1</v>
-      </c>
-      <c r="T17" s="13">
-        <v>1</v>
-      </c>
-      <c r="U17" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="V17" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="W17" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="X17" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y17" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z17" s="13">
-        <v>85001100</v>
-      </c>
-      <c r="AA17" s="13">
+      <c r="AA17" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
-        <v>95100101</v>
+        <v>95000101</v>
       </c>
       <c r="B18" s="13">
-        <v>95100101</v>
+        <v>95000101</v>
       </c>
       <c r="C18" s="13">
         <v>5</v>
@@ -2863,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H18" s="13">
         <v>0</v>
@@ -2878,13 +2913,13 @@
         <v>0</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="M18" s="13">
         <v>0</v>
@@ -2893,40 +2928,40 @@
         <v>0</v>
       </c>
       <c r="O18" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" s="13">
         <v>2</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="S18" s="13">
         <v>1</v>
       </c>
       <c r="T18" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" s="13" t="s">
         <v>78</v>
       </c>
       <c r="V18" s="13" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="W18" s="13" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="X18" s="13" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="Z18" s="13">
-        <v>0</v>
+        <v>85001100</v>
       </c>
       <c r="AA18" s="13">
         <v>0</v>
@@ -2934,10 +2969,10 @@
     </row>
     <row r="19" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
-        <v>95200101</v>
+        <v>95100101</v>
       </c>
       <c r="B19" s="13">
-        <v>95200101</v>
+        <v>95100101</v>
       </c>
       <c r="C19" s="13">
         <v>5</v>
@@ -2946,13 +2981,13 @@
         <v>1</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H19" s="13">
         <v>0</v>
@@ -2961,13 +2996,13 @@
         <v>0</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="M19" s="13">
         <v>0</v>
@@ -2976,125 +3011,208 @@
         <v>0</v>
       </c>
       <c r="O19" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P19" s="13">
         <v>2</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="S19" s="13">
         <v>1</v>
       </c>
       <c r="T19" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U19" s="13" t="s">
         <v>78</v>
       </c>
       <c r="V19" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="W19" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="X19" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y19" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="13">
+        <v>95200101</v>
+      </c>
+      <c r="B20" s="13">
+        <v>95200101</v>
+      </c>
+      <c r="C20" s="13">
+        <v>5</v>
+      </c>
+      <c r="D20" s="13">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" s="13">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="M20" s="13">
+        <v>0</v>
+      </c>
+      <c r="N20" s="13">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13">
+        <v>4</v>
+      </c>
+      <c r="P20" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="S20" s="13">
+        <v>1</v>
+      </c>
+      <c r="T20" s="13">
+        <v>4</v>
+      </c>
+      <c r="U20" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="V20" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="W19" s="13" t="s">
+      <c r="W20" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="X19" s="13" t="s">
+      <c r="X20" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="Y19" s="13" t="s">
+      <c r="Y20" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="Z19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="13">
+      <c r="Z20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
         <v>20001</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B21" s="2">
         <v>920001</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C21" s="2">
         <v>5</v>
       </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
         <v>720001</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J21" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K21" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L21" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="M20" s="2">
-        <v>0</v>
-      </c>
-      <c r="N20" s="2">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2">
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2">
         <v>4</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P21" s="2">
         <v>2</v>
       </c>
-      <c r="Q20" s="13" t="s">
+      <c r="Q21" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="R20" s="13" t="s">
+      <c r="R21" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="S20" s="2">
-        <v>1</v>
-      </c>
-      <c r="T20" s="2">
+      <c r="S21" s="2">
+        <v>1</v>
+      </c>
+      <c r="T21" s="2">
         <v>2</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="U21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="V21" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="W20" s="13" t="s">
+      <c r="W21" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="X21" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="Y20" s="13" t="s">
+      <c r="Y21" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="Z20" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="2">
+      <c r="Z21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
         <v>820001</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ED7F29-B55E-44AC-8564-4C8E1AFD91A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A309C81E-102C-471B-90B3-288C6B33F8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -2795,7 +2795,7 @@
         <v>199</v>
       </c>
       <c r="Z16" s="1">
-        <v>59260001</v>
+        <v>59130001</v>
       </c>
       <c r="AA16" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A309C81E-102C-471B-90B3-288C6B33F8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E75DB63-13FF-482B-A456-8542A6113C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="221">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -981,6 +981,73 @@
   </si>
   <si>
     <t>1:959260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻附加毒爆</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920011</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2920011</t>
+  </si>
+  <si>
+    <t>1:3920011</t>
+  </si>
+  <si>
+    <t>1:4920011</t>
+  </si>
+  <si>
+    <t>1:5920011</t>
+  </si>
+  <si>
+    <t>1:6920011</t>
+  </si>
+  <si>
+    <t>1:7920011</t>
+  </si>
+  <si>
+    <t>1:8920011</t>
+  </si>
+  <si>
+    <t>1:9920011</t>
+  </si>
+  <si>
+    <t>1:1920012</t>
+  </si>
+  <si>
+    <t>1:2920012</t>
+  </si>
+  <si>
+    <t>1:3920012</t>
+  </si>
+  <si>
+    <t>1:4920012</t>
+  </si>
+  <si>
+    <t>1:5920012</t>
+  </si>
+  <si>
+    <t>1:6920012</t>
+  </si>
+  <si>
+    <t>1:7920012</t>
+  </si>
+  <si>
+    <t>1:8920012</t>
+  </si>
+  <si>
+    <t>1:9920012</t>
+  </si>
+  <si>
+    <t>毒爆</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒爆，小范围AOE伤害</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1539,7 +1606,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -1553,7 +1620,7 @@
     <col min="13" max="13" width="24.75" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" style="2" customWidth="1"/>
     <col min="15" max="15" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.75" style="2" customWidth="1"/>
     <col min="17" max="18" width="13.875" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="58" style="2" customWidth="1"/>
@@ -2901,7 +2968,7 @@
         <v>68</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>66</v>
@@ -2984,7 +3051,7 @@
         <v>69</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>67</v>
@@ -3067,7 +3134,7 @@
         <v>64</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>65</v>
@@ -3214,6 +3281,169 @@
       </c>
       <c r="AA21" s="2">
         <v>820001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>20011</v>
+      </c>
+      <c r="B22" s="2">
+        <v>920011</v>
+      </c>
+      <c r="C22" s="2">
+        <v>5</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2">
+        <v>720011</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="S22" s="2">
+        <v>1</v>
+      </c>
+      <c r="T22" s="2">
+        <v>3</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V22" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="W22" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="X22" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y22" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>820011</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>20012</v>
+      </c>
+      <c r="B23" s="2">
+        <v>920012</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
+        <v>3</v>
+      </c>
+      <c r="P23" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="S23" s="2">
+        <v>1</v>
+      </c>
+      <c r="T23" s="2">
+        <v>3</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V23" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="W23" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="X23" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y23" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>820011</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E75DB63-13FF-482B-A456-8542A6113C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B203D5E-6408-4264-9120-3B900E17268E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -148,34 +148,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>李强:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 目标单体
-2 自身单体
-3 目标为中心范围
-4 自身为中心范围
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
@@ -309,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="243">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1049,6 +1021,76 @@
   <si>
     <t>毒爆，小范围AOE伤害</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>向目标方向冲刺挥砍，刀锋划出烈火，对目标造成火属性伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920021</t>
+  </si>
+  <si>
+    <t>1:2920021</t>
+  </si>
+  <si>
+    <t>1:3920021</t>
+  </si>
+  <si>
+    <t>1:4920021</t>
+  </si>
+  <si>
+    <t>1:5920021</t>
+  </si>
+  <si>
+    <t>1:6920021</t>
+  </si>
+  <si>
+    <t>1:7920021</t>
+  </si>
+  <si>
+    <t>1:8920021</t>
+  </si>
+  <si>
+    <t>1:9920021</t>
+  </si>
+  <si>
+    <t>升龙击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺收招后追加释放升龙击，造成火属性伤害和击飞</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920022</t>
+  </si>
+  <si>
+    <t>1:2920022</t>
+  </si>
+  <si>
+    <t>1:3920022</t>
+  </si>
+  <si>
+    <t>1:4920022</t>
+  </si>
+  <si>
+    <t>1:5920022</t>
+  </si>
+  <si>
+    <t>1:6920022</t>
+  </si>
+  <si>
+    <t>1:7920022</t>
+  </si>
+  <si>
+    <t>1:8920022</t>
+  </si>
+  <si>
+    <t>1:9920022</t>
   </si>
 </sst>
 </file>
@@ -1606,7 +1648,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -1618,7 +1660,7 @@
     <col min="10" max="10" width="22.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="13.875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="2" customWidth="1"/>
+    <col min="14" max="14" width="31.375" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="27.75" style="2" customWidth="1"/>
     <col min="17" max="18" width="13.875" style="2" bestFit="1" customWidth="1"/>
@@ -3446,6 +3488,172 @@
         <v>820011</v>
       </c>
     </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>20021</v>
+      </c>
+      <c r="B24" s="2">
+        <v>930021</v>
+      </c>
+      <c r="C24" s="2">
+        <v>5</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="S24" s="2">
+        <v>1</v>
+      </c>
+      <c r="T24" s="2">
+        <v>2</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V24" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="W24" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="X24" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="Y24" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>820021</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>20022</v>
+      </c>
+      <c r="B25" s="2">
+        <v>930022</v>
+      </c>
+      <c r="C25" s="2">
+        <v>5</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2">
+        <v>1</v>
+      </c>
+      <c r="P25" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="R25" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1</v>
+      </c>
+      <c r="T25" s="2">
+        <v>2</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V25" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="W25" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="X25" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y25" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B203D5E-6408-4264-9120-3B900E17268E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD30D16-7C49-4D74-9010-009523BFC714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -3493,7 +3493,7 @@
         <v>20021</v>
       </c>
       <c r="B24" s="2">
-        <v>930021</v>
+        <v>920021</v>
       </c>
       <c r="C24" s="2">
         <v>5</v>
@@ -3576,7 +3576,7 @@
         <v>20022</v>
       </c>
       <c r="B25" s="2">
-        <v>930022</v>
+        <v>920022</v>
       </c>
       <c r="C25" s="2">
         <v>5</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD30D16-7C49-4D74-9010-009523BFC714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F29A22-EB0D-4B09-8D82-66E663A2A7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -53,8 +53,9 @@
           <t>1-玩家普攻
 2-怪物主动技能
 3-吃药回血
-4-属性id关联的被动
-5-玩家主动技能</t>
+4-玩家被动技能
+5-玩家主动技能
+6-由特殊方式触发的主动技能</t>
         </r>
       </text>
     </comment>
@@ -3413,7 +3414,7 @@
         <v>920012</v>
       </c>
       <c r="C23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F29A22-EB0D-4B09-8D82-66E663A2A7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CB84F7-70C5-426E-B94C-1302884888B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3566,7 +3566,7 @@
         <v>231</v>
       </c>
       <c r="Z24" s="2">
-        <v>820021</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CB84F7-70C5-426E-B94C-1302884888B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC6ACD9-E0BD-445B-AB0E-DC5AE6099B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2">
         <v>3</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2">
         <v>1</v>
@@ -3595,10 +3595,10 @@
         <v>233</v>
       </c>
       <c r="H25" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>720022</v>
       </c>
       <c r="J25" s="13" t="s">
         <v>234</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC6ACD9-E0BD-445B-AB0E-DC5AE6099B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60FA0B4-DBA2-47CB-A26F-EE0A3E2D816F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="1" shapeId="0" xr:uid="{051313A9-A9F3-47D0-8025-83ECAEF4180F}">
+    <comment ref="I4" authorId="1" shapeId="0" xr:uid="{051313A9-A9F3-47D0-8025-83ECAEF4180F}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -97,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{0EDCE646-B10B-4F69-BE67-60929A0CAD6F}">
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{0EDCE646-B10B-4F69-BE67-60929A0CAD6F}">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="M4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -149,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -177,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -202,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
+    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{554A3FFC-B100-4A02-BB96-0B2D26B82D13}">
       <text>
         <r>
           <rPr>
@@ -216,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="T4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -233,7 +233,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
+    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
       <text>
         <r>
           <rPr>
@@ -250,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="2" shapeId="0" xr:uid="{3BCFFE37-A88F-4166-8915-9D540B7CC094}">
+    <comment ref="V4" authorId="2" shapeId="0" xr:uid="{3BCFFE37-A88F-4166-8915-9D540B7CC094}">
       <text>
         <r>
           <rPr>
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="256">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1092,6 +1092,49 @@
   </si>
   <si>
     <t>1:9920022</t>
+  </si>
+  <si>
+    <t>1:1920023</t>
+  </si>
+  <si>
+    <t>1:2920023</t>
+  </si>
+  <si>
+    <t>1:3920023</t>
+  </si>
+  <si>
+    <t>1:4920023</t>
+  </si>
+  <si>
+    <t>1:5920023</t>
+  </si>
+  <si>
+    <t>1:6920023</t>
+  </si>
+  <si>
+    <t>1:7920023</t>
+  </si>
+  <si>
+    <t>1:8920023</t>
+  </si>
+  <si>
+    <t>1:9920023</t>
+  </si>
+  <si>
+    <t>爆炎砸地</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放爆炎冲刺3次后，接1次大范围砸地造成火属性伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>priority</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>动作技能释放优先级</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1649,40 +1692,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="17.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.75" style="2" customWidth="1"/>
-    <col min="17" max="18" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="58" style="2" customWidth="1"/>
-    <col min="21" max="21" width="61" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="17.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="22.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.75" style="2" customWidth="1"/>
+    <col min="18" max="19" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="58" style="2" customWidth="1"/>
+    <col min="22" max="22" width="61" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1692,26 +1737,26 @@
       <c r="C2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>81</v>
+      <c r="E2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="J2" s="19" t="s">
         <v>170</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>83</v>
@@ -1720,7 +1765,7 @@
         <v>83</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>55</v>
@@ -1732,22 +1777,22 @@
         <v>55</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>62</v>
       </c>
       <c r="U2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>83</v>
+      <c r="V2" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>83</v>
@@ -1759,13 +1804,16 @@
         <v>83</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="AB2" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="3" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1775,80 +1823,83 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="I3" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="J3" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="L3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="M3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="U3" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="V3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="W3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="X3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1858,80 +1909,83 @@
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="I4" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="J4" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="K4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="L4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="M4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="R4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="S4" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="U4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="11" t="s">
+      <c r="V4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="W4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="W4" s="15" t="s">
+      <c r="X4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="X4" s="15" t="s">
+      <c r="Y4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="Y4" s="15" t="s">
+      <c r="Z4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10101</v>
       </c>
@@ -1944,75 +1998,78 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
+      <c r="H5" s="6"/>
       <c r="I5" s="6">
         <v>0</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
       <c r="N5" s="6">
         <v>0</v>
       </c>
       <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6">
         <v>3</v>
       </c>
-      <c r="P5" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="6">
+        <v>2</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="S5" s="6">
-        <v>1</v>
-      </c>
-      <c r="T5" s="14" t="s">
+      <c r="T5" s="6">
+        <v>1</v>
+      </c>
+      <c r="U5" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U5" s="14" t="s">
+      <c r="V5" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="Z5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="7">
+      <c r="AA5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10102</v>
       </c>
@@ -2025,75 +2082,78 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
+      <c r="H6" s="6"/>
       <c r="I6" s="6">
         <v>0</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
       <c r="N6" s="6">
         <v>0</v>
       </c>
       <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
         <v>3</v>
       </c>
-      <c r="P6" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="6" t="s">
+      <c r="Q6" s="6">
+        <v>2</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="S6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="S6" s="6">
-        <v>1</v>
-      </c>
-      <c r="T6" s="14" t="s">
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U6" s="14" t="s">
+      <c r="V6" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="V6" s="6" t="s">
+      <c r="W6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="7">
+      <c r="AA6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10201</v>
       </c>
@@ -2104,77 +2164,80 @@
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
+      <c r="H7" s="6"/>
       <c r="I7" s="6">
         <v>0</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="M7" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
       <c r="N7" s="6">
         <v>0</v>
       </c>
       <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6">
         <v>3</v>
       </c>
-      <c r="P7" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="6" t="s">
+      <c r="Q7" s="6">
+        <v>2</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="S7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="S7" s="6">
-        <v>1</v>
-      </c>
-      <c r="T7" s="14" t="s">
+      <c r="T7" s="6">
+        <v>1</v>
+      </c>
+      <c r="U7" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="V7" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="V7" s="6" t="s">
+      <c r="W7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="Z7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="7">
+      <c r="AA7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10202</v>
       </c>
@@ -2185,77 +2248,80 @@
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="6">
         <v>0</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="M8" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
       <c r="N8" s="6">
         <v>0</v>
       </c>
       <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6">
         <v>3</v>
       </c>
-      <c r="P8" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="6" t="s">
+      <c r="Q8" s="6">
+        <v>2</v>
+      </c>
+      <c r="R8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="R8" s="6" t="s">
+      <c r="S8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="S8" s="6">
-        <v>1</v>
-      </c>
-      <c r="T8" s="14" t="s">
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="14" t="s">
+      <c r="V8" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="V8" s="6" t="s">
+      <c r="W8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="7">
+      <c r="AA8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10301</v>
       </c>
@@ -2266,77 +2332,80 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
         <v>3</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
+      <c r="H9" s="6"/>
       <c r="I9" s="6">
         <v>0</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="M9" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
       <c r="N9" s="6">
         <v>0</v>
       </c>
       <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
         <v>3</v>
       </c>
-      <c r="P9" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="6" t="s">
+      <c r="Q9" s="6">
+        <v>2</v>
+      </c>
+      <c r="R9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="S9" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="S9" s="6">
-        <v>1</v>
-      </c>
-      <c r="T9" s="14" t="s">
+      <c r="T9" s="6">
+        <v>1</v>
+      </c>
+      <c r="U9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="V9" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="W9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Z9" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="Z9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="7">
+      <c r="AA9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10302</v>
       </c>
@@ -2347,77 +2416,80 @@
         <v>1</v>
       </c>
       <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
         <v>3</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
+      <c r="H10" s="6"/>
       <c r="I10" s="6">
         <v>0</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="M10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
       <c r="N10" s="6">
         <v>0</v>
       </c>
       <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
         <v>3</v>
       </c>
-      <c r="P10" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="6" t="s">
+      <c r="Q10" s="6">
+        <v>2</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="R10" s="6" t="s">
+      <c r="S10" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="S10" s="6">
-        <v>1</v>
-      </c>
-      <c r="T10" s="14" t="s">
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U10" s="14" t="s">
+      <c r="V10" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="V10" s="6" t="s">
+      <c r="W10" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="W10" s="6" t="s">
+      <c r="X10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Z10" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="7">
+      <c r="AA10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>201001011</v>
       </c>
@@ -2430,77 +2502,80 @@
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
       <c r="N11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
         <v>3</v>
       </c>
-      <c r="P11" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="1" t="s">
+      <c r="Q11" s="1">
+        <v>2</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R11" s="18" t="s">
+      <c r="S11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="S11" s="1">
-        <v>1</v>
-      </c>
-      <c r="T11" s="12">
-        <v>0</v>
-      </c>
-      <c r="U11" s="12" t="s">
+      <c r="T11" s="1">
+        <v>1</v>
+      </c>
+      <c r="U11" s="12">
+        <v>0</v>
+      </c>
+      <c r="V11" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V11" s="1" t="s">
+      <c r="W11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="X11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="X11" s="1" t="s">
+      <c r="Y11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="Z11" s="1">
-        <v>0</v>
-      </c>
       <c r="AA11" s="1">
         <v>0</v>
       </c>
+      <c r="AB11" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>201002011</v>
       </c>
@@ -2513,77 +2588,80 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
         <v>3</v>
       </c>
-      <c r="P12" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="1" t="s">
+      <c r="Q12" s="1">
+        <v>2</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S12" s="1">
-        <v>1</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12" t="s">
+      <c r="T12" s="1">
+        <v>1</v>
+      </c>
+      <c r="U12" s="12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V12" s="1" t="s">
+      <c r="W12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W12" s="1" t="s">
+      <c r="X12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X12" s="1" t="s">
+      <c r="Y12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y12" s="1" t="s">
+      <c r="Z12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
       <c r="AA12" s="1">
         <v>0</v>
       </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>201004011</v>
       </c>
@@ -2596,77 +2674,80 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
       <c r="N13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
         <v>3</v>
       </c>
-      <c r="P13" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="1" t="s">
+      <c r="Q13" s="1">
+        <v>2</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S13" s="1">
-        <v>1</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12" t="s">
+      <c r="T13" s="1">
+        <v>1</v>
+      </c>
+      <c r="U13" s="12">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V13" s="1" t="s">
+      <c r="W13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W13" s="1" t="s">
+      <c r="X13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X13" s="1" t="s">
+      <c r="Y13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y13" s="1" t="s">
+      <c r="Z13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
       <c r="AA13" s="1">
         <v>0</v>
       </c>
+      <c r="AB13" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>214001011</v>
       </c>
@@ -2679,77 +2760,80 @@
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
       <c r="N14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
         <v>3</v>
       </c>
-      <c r="P14" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="1" t="s">
+      <c r="Q14" s="1">
+        <v>2</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S14" s="1">
-        <v>1</v>
-      </c>
-      <c r="T14" s="12">
-        <v>0</v>
-      </c>
-      <c r="U14" s="12" t="s">
+      <c r="T14" s="1">
+        <v>1</v>
+      </c>
+      <c r="U14" s="12">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V14" s="1" t="s">
+      <c r="W14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W14" s="1" t="s">
+      <c r="X14" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X14" s="1" t="s">
+      <c r="Y14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y14" s="1" t="s">
+      <c r="Z14" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
       <c r="AA14" s="1">
         <v>0</v>
       </c>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>203002011</v>
       </c>
@@ -2762,77 +2846,80 @@
       <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
       <c r="N15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
         <v>3</v>
       </c>
-      <c r="P15" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="1" t="s">
+      <c r="Q15" s="1">
+        <v>2</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S15" s="1">
-        <v>1</v>
-      </c>
-      <c r="T15" s="12">
-        <v>0</v>
-      </c>
-      <c r="U15" s="12" t="s">
+      <c r="T15" s="1">
+        <v>1</v>
+      </c>
+      <c r="U15" s="12">
+        <v>0</v>
+      </c>
+      <c r="V15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V15" s="1" t="s">
+      <c r="W15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W15" s="1" t="s">
+      <c r="X15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X15" s="1" t="s">
+      <c r="Y15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y15" s="1" t="s">
+      <c r="Z15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
       <c r="AA15" s="1">
         <v>0</v>
       </c>
+      <c r="AB15" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>59260001</v>
       </c>
@@ -2845,73 +2932,76 @@
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1">
-        <v>2</v>
-      </c>
+      <c r="H16" s="1"/>
       <c r="I16" s="1">
+        <v>2</v>
+      </c>
+      <c r="J16" s="1">
         <v>26010001</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
       <c r="N16" s="1">
         <v>0</v>
       </c>
       <c r="O16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="S16" s="1">
-        <v>1</v>
-      </c>
-      <c r="T16" s="12">
-        <v>0</v>
-      </c>
-      <c r="U16" s="12" t="s">
+      <c r="T16" s="1">
+        <v>1</v>
+      </c>
+      <c r="U16" s="12">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V16" s="1" t="s">
+      <c r="W16" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="W16" s="1" t="s">
+      <c r="X16" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="X16" s="1" t="s">
+      <c r="Y16" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="Y16" s="1" t="s">
+      <c r="Z16" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="Z16" s="1">
+      <c r="AA16" s="1">
         <v>59130001</v>
       </c>
-      <c r="AA16" s="1">
+      <c r="AB16" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A17" s="10">
         <v>25010001</v>
       </c>
@@ -2924,59 +3014,59 @@
       <c r="D17" s="10">
         <v>1</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="G17" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="H17" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="10">
-        <v>0</v>
-      </c>
       <c r="I17" s="10">
         <v>0</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>28</v>
+      <c r="J17" s="10">
+        <v>0</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>28</v>
       </c>
       <c r="L17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="M17" s="10">
-        <v>0</v>
-      </c>
       <c r="N17" s="10">
         <v>0</v>
       </c>
       <c r="O17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>1</v>
+      </c>
+      <c r="R17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="R17" s="10" t="s">
+      <c r="S17" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="S17" s="10">
-        <v>1</v>
-      </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="10">
+        <v>0</v>
+      </c>
+      <c r="V17" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="V17" s="10" t="s">
-        <v>28</v>
       </c>
       <c r="W17" s="10" t="s">
         <v>28</v>
@@ -2987,14 +3077,17 @@
       <c r="Y17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Z17" s="10">
+      <c r="Z17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA17" s="10">
         <v>54150001</v>
       </c>
-      <c r="AA17" s="10">
+      <c r="AB17" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
         <v>95000101</v>
       </c>
@@ -3007,77 +3100,80 @@
       <c r="D18" s="13">
         <v>1</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>68</v>
+      <c r="E18" s="13">
+        <v>1</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="13">
-        <v>0</v>
-      </c>
       <c r="I18" s="13">
         <v>0</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="13">
+        <v>0</v>
+      </c>
+      <c r="K18" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="L18" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="M18" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="M18" s="13">
-        <v>0</v>
-      </c>
       <c r="N18" s="13">
         <v>0</v>
       </c>
       <c r="O18" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>2</v>
+      </c>
+      <c r="R18" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="R18" s="13" t="s">
+      <c r="S18" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="S18" s="13">
-        <v>1</v>
-      </c>
       <c r="T18" s="13">
         <v>1</v>
       </c>
-      <c r="U18" s="13" t="s">
+      <c r="U18" s="13">
+        <v>1</v>
+      </c>
+      <c r="V18" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="V18" s="13" t="s">
+      <c r="W18" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="W18" s="13" t="s">
+      <c r="X18" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="X18" s="13" t="s">
+      <c r="Y18" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="Y18" s="13" t="s">
+      <c r="Z18" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AA18" s="13">
         <v>85001100</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AB18" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
         <v>95100101</v>
       </c>
@@ -3090,77 +3186,80 @@
       <c r="D19" s="13">
         <v>1</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>69</v>
+      <c r="E19" s="13">
+        <v>1</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="13">
-        <v>0</v>
-      </c>
       <c r="I19" s="13">
         <v>0</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="13">
+        <v>0</v>
+      </c>
+      <c r="K19" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="L19" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="M19" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M19" s="13">
-        <v>0</v>
-      </c>
       <c r="N19" s="13">
         <v>0</v>
       </c>
       <c r="O19" s="13">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13">
         <v>3</v>
       </c>
-      <c r="P19" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="13" t="s">
+      <c r="Q19" s="13">
+        <v>2</v>
+      </c>
+      <c r="R19" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="R19" s="13" t="s">
+      <c r="S19" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="S19" s="13">
-        <v>1</v>
-      </c>
       <c r="T19" s="13">
-        <v>2</v>
-      </c>
-      <c r="U19" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="U19" s="13">
+        <v>2</v>
+      </c>
+      <c r="V19" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="V19" s="13" t="s">
+      <c r="W19" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="W19" s="13" t="s">
+      <c r="X19" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="X19" s="13" t="s">
+      <c r="Y19" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="Y19" s="13" t="s">
+      <c r="Z19" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="Z19" s="13">
-        <v>0</v>
-      </c>
       <c r="AA19" s="13">
         <v>0</v>
       </c>
+      <c r="AB19" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13">
         <v>95200101</v>
       </c>
@@ -3173,77 +3272,80 @@
       <c r="D20" s="13">
         <v>1</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>64</v>
+      <c r="E20" s="13">
+        <v>1</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>64</v>
       </c>
       <c r="G20" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
       <c r="I20" s="13">
         <v>0</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="13">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="L20" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="M20" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="M20" s="13">
-        <v>0</v>
-      </c>
       <c r="N20" s="13">
         <v>0</v>
       </c>
       <c r="O20" s="13">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13">
         <v>4</v>
       </c>
-      <c r="P20" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="13" t="s">
+      <c r="Q20" s="13">
+        <v>2</v>
+      </c>
+      <c r="R20" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="R20" s="13" t="s">
+      <c r="S20" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="S20" s="13">
-        <v>1</v>
-      </c>
       <c r="T20" s="13">
+        <v>1</v>
+      </c>
+      <c r="U20" s="13">
         <v>4</v>
       </c>
-      <c r="U20" s="13" t="s">
+      <c r="V20" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="W20" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="W20" s="13" t="s">
+      <c r="X20" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="Y20" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="Y20" s="13" t="s">
+      <c r="Z20" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="Z20" s="13">
-        <v>0</v>
-      </c>
       <c r="AA20" s="13">
         <v>0</v>
       </c>
+      <c r="AB20" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20001</v>
       </c>
@@ -3256,77 +3358,80 @@
       <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>179</v>
+      <c r="E21" s="2">
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>179</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
       <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
         <v>720001</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="K21" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="L21" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="M21" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="M21" s="2">
-        <v>0</v>
-      </c>
       <c r="N21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2">
         <v>4</v>
       </c>
-      <c r="P21" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="13" t="s">
+      <c r="Q21" s="2">
+        <v>2</v>
+      </c>
+      <c r="R21" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="R21" s="13" t="s">
+      <c r="S21" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="S21" s="2">
-        <v>1</v>
-      </c>
       <c r="T21" s="2">
-        <v>2</v>
-      </c>
-      <c r="U21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U21" s="2">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V21" s="13" t="s">
+      <c r="W21" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="W21" s="13" t="s">
+      <c r="X21" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="X21" s="13" t="s">
+      <c r="Y21" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="Y21" s="13" t="s">
+      <c r="Z21" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="Z21" s="2">
-        <v>0</v>
-      </c>
       <c r="AA21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2">
         <v>820001</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20011</v>
       </c>
@@ -3339,74 +3444,77 @@
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>200</v>
+      <c r="E22" s="2">
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="H22" s="2">
-        <v>1</v>
+      <c r="G22" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
         <v>720011</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="K22" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="L22" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="L22" s="13" t="s">
+      <c r="M22" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="M22" s="2">
-        <v>0</v>
-      </c>
       <c r="N22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2">
         <v>1</v>
       </c>
       <c r="P22" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>2</v>
+      </c>
+      <c r="R22" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="R22" s="13" t="s">
+      <c r="S22" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="S22" s="2">
-        <v>1</v>
-      </c>
       <c r="T22" s="2">
+        <v>1</v>
+      </c>
+      <c r="U22" s="2">
         <v>3</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="V22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V22" s="13" t="s">
+      <c r="W22" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="W22" s="13" t="s">
+      <c r="X22" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="X22" s="13" t="s">
+      <c r="Y22" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="Y22" s="13" t="s">
+      <c r="Z22" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="Z22" s="2">
-        <v>0</v>
-      </c>
       <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
         <v>820011</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20012</v>
       </c>
@@ -3419,77 +3527,80 @@
       <c r="D23" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>219</v>
+      <c r="E23" s="2">
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>219</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="13" t="s">
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="L23" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="L23" s="13" t="s">
+      <c r="M23" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="M23" s="2">
-        <v>0</v>
-      </c>
       <c r="N23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2">
         <v>3</v>
       </c>
-      <c r="P23" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="13" t="s">
+      <c r="Q23" s="2">
+        <v>2</v>
+      </c>
+      <c r="R23" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="R23" s="13" t="s">
+      <c r="S23" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="S23" s="2">
-        <v>1</v>
-      </c>
       <c r="T23" s="2">
+        <v>1</v>
+      </c>
+      <c r="U23" s="2">
         <v>3</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="V23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V23" s="13" t="s">
+      <c r="W23" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="W23" s="13" t="s">
+      <c r="X23" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="X23" s="13" t="s">
+      <c r="Y23" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="Y23" s="13" t="s">
+      <c r="Z23" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="Z23" s="2">
-        <v>0</v>
-      </c>
       <c r="AA23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="2">
         <v>820011</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20021</v>
       </c>
@@ -3500,79 +3611,82 @@
         <v>5</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>221</v>
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>221</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="L24" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="M24" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="M24" s="2">
-        <v>0</v>
-      </c>
       <c r="N24" s="2">
         <v>0</v>
       </c>
       <c r="O24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>2</v>
+      </c>
+      <c r="R24" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="R24" s="13" t="s">
+      <c r="S24" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="S24" s="2">
-        <v>1</v>
-      </c>
       <c r="T24" s="2">
-        <v>2</v>
-      </c>
-      <c r="U24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U24" s="2">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V24" s="13" t="s">
+      <c r="W24" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W24" s="13" t="s">
+      <c r="X24" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="X24" s="13" t="s">
+      <c r="Y24" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="Y24" s="13" t="s">
+      <c r="Z24" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="Z24" s="2">
-        <v>0</v>
-      </c>
       <c r="AA24" s="2">
         <v>0</v>
       </c>
+      <c r="AB24" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20022</v>
       </c>
@@ -3583,75 +3697,164 @@
         <v>5</v>
       </c>
       <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>232</v>
+        <v>4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>232</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="H25" s="2">
-        <v>2</v>
-      </c>
       <c r="I25" s="2">
+        <v>2</v>
+      </c>
+      <c r="J25" s="2">
         <v>720022</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="K25" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="L25" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="L25" s="13" t="s">
+      <c r="M25" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="M25" s="2">
-        <v>0</v>
-      </c>
       <c r="N25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2">
         <v>1</v>
       </c>
       <c r="P25" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>2</v>
+      </c>
+      <c r="R25" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="R25" s="13" t="s">
+      <c r="S25" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="S25" s="2">
-        <v>1</v>
-      </c>
       <c r="T25" s="2">
-        <v>2</v>
-      </c>
-      <c r="U25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U25" s="2">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V25" s="13" t="s">
+      <c r="W25" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W25" s="13" t="s">
+      <c r="X25" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X25" s="13" t="s">
+      <c r="Y25" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="Y25" s="13" t="s">
+      <c r="Z25" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="Z25" s="2">
-        <v>0</v>
-      </c>
       <c r="AA25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>20023</v>
+      </c>
+      <c r="B26" s="2">
+        <v>920023</v>
+      </c>
+      <c r="C26" s="2">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2">
+        <v>720023</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>2</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="S26" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="T26" s="2">
+        <v>1</v>
+      </c>
+      <c r="U26" s="2">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W26" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="X26" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y26" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z26" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="2">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60FA0B4-DBA2-47CB-A26F-EE0A3E2D816F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41A7452-DEC3-4EE4-BD1B-802F27CB489F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="267">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1134,6 +1134,41 @@
   </si>
   <si>
     <t>动作技能释放优先级</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920031</t>
+  </si>
+  <si>
+    <t>1:2920031</t>
+  </si>
+  <si>
+    <t>1:3920031</t>
+  </si>
+  <si>
+    <t>1:4920031</t>
+  </si>
+  <si>
+    <t>1:5920031</t>
+  </si>
+  <si>
+    <t>1:6920031</t>
+  </si>
+  <si>
+    <t>1:7920031</t>
+  </si>
+  <si>
+    <t>1:8920031</t>
+  </si>
+  <si>
+    <t>1:9920031</t>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链，可弹射3次</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1692,7 +1727,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -3858,6 +3893,92 @@
         <v>0</v>
       </c>
     </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>20031</v>
+      </c>
+      <c r="B27" s="2">
+        <v>920031</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>2</v>
+      </c>
+      <c r="R27" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="S27" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="T27" s="2">
+        <v>1</v>
+      </c>
+      <c r="U27" s="2">
+        <v>4</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W27" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="X27" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y27" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z27" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41A7452-DEC3-4EE4-BD1B-802F27CB489F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F98FE89-BDBC-427C-862F-BC93972FABD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="269">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -538,10 +538,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>僵尸等级2精英</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>damage_element_adjust</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1169,6 +1165,18 @@
   </si>
   <si>
     <t>闪电链，可弹射3次</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>石像鬼精英</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:500</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1727,7 +1735,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -1782,25 +1790,25 @@
         <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I2" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="J2" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="J2" s="19" t="s">
-        <v>170</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>55</v>
@@ -1815,10 +1823,10 @@
         <v>55</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>55</v>
@@ -1830,16 +1838,16 @@
         <v>62</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>56</v>
@@ -1853,13 +1861,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>46</v>
@@ -1874,10 +1882,10 @@
         <v>7</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>8</v>
@@ -1913,7 +1921,7 @@
         <v>61</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>30</v>
@@ -1939,13 +1947,13 @@
         <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>47</v>
@@ -1960,10 +1968,10 @@
         <v>19</v>
       </c>
       <c r="I4" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="J4" s="19" t="s">
         <v>171</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>172</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>20</v>
@@ -1999,7 +2007,7 @@
         <v>63</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W4" s="15" t="s">
         <v>31</v>
@@ -2050,13 +2058,13 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="N5" s="6">
         <v>0</v>
@@ -2071,31 +2079,31 @@
         <v>2</v>
       </c>
       <c r="R5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="S5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6">
+        <v>1</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="W5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="T5" s="6">
-        <v>1</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="Y5" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="Z5" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA5" s="6">
         <v>0</v>
@@ -2134,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="N6" s="6">
         <v>0</v>
@@ -2155,31 +2163,31 @@
         <v>2</v>
       </c>
       <c r="R6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="V6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="W6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="T6" s="6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="V6" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="AA6" s="6">
         <v>0</v>
@@ -2218,13 +2226,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="N7" s="6">
         <v>0</v>
@@ -2239,31 +2247,31 @@
         <v>2</v>
       </c>
       <c r="R7" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S7" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="T7" s="6">
+        <v>1</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="W7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="T7" s="6">
-        <v>1</v>
-      </c>
-      <c r="U7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="V7" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="AA7" s="6">
         <v>0</v>
@@ -2302,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="N8" s="6">
         <v>0</v>
@@ -2323,31 +2331,31 @@
         <v>2</v>
       </c>
       <c r="R8" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="S8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="W8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="T8" s="6">
-        <v>1</v>
-      </c>
-      <c r="U8" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="V8" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="AA8" s="6">
         <v>0</v>
@@ -2386,13 +2394,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="N9" s="6">
         <v>0</v>
@@ -2407,31 +2415,31 @@
         <v>2</v>
       </c>
       <c r="R9" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="S9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="T9" s="6">
+        <v>1</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="W9" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="T9" s="6">
-        <v>1</v>
-      </c>
-      <c r="U9" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="V9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Z9" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="AA9" s="6">
         <v>0</v>
@@ -2470,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="K10" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="N10" s="6">
         <v>0</v>
@@ -2491,31 +2499,31 @@
         <v>2</v>
       </c>
       <c r="R10" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="S10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="V10" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="W10" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="T10" s="6">
-        <v>1</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W10" s="6" t="s">
+      <c r="X10" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Z10" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="AA10" s="6">
         <v>0</v>
@@ -2556,13 +2564,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N11" s="1">
         <v>0</v>
@@ -2580,7 +2588,7 @@
         <v>28</v>
       </c>
       <c r="S11" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T11" s="1">
         <v>1</v>
@@ -2589,19 +2597,19 @@
         <v>0</v>
       </c>
       <c r="V11" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA11" s="1">
         <v>0</v>
@@ -2642,13 +2650,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N12" s="1">
         <v>0</v>
@@ -2666,7 +2674,7 @@
         <v>28</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T12" s="1">
         <v>1</v>
@@ -2675,19 +2683,19 @@
         <v>0</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
@@ -2728,13 +2736,13 @@
         <v>0</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
@@ -2752,7 +2760,7 @@
         <v>28</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T13" s="1">
         <v>1</v>
@@ -2761,19 +2769,19 @@
         <v>0</v>
       </c>
       <c r="V13" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
@@ -2814,13 +2822,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N14" s="1">
         <v>0</v>
@@ -2838,7 +2846,7 @@
         <v>28</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T14" s="1">
         <v>1</v>
@@ -2847,19 +2855,19 @@
         <v>0</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA14" s="1">
         <v>0</v>
@@ -2885,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>57</v>
@@ -2900,13 +2908,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
@@ -2924,7 +2932,7 @@
         <v>28</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T15" s="1">
         <v>1</v>
@@ -2933,19 +2941,19 @@
         <v>0</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA15" s="1">
         <v>0</v>
@@ -2956,264 +2964,264 @@
     </row>
     <row r="16" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
+        <v>216001001</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>2</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T16" s="1">
+        <v>1</v>
+      </c>
+      <c r="U16" s="12">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>59260001</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B17" s="1">
         <v>3592200</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C17" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="1" t="s">
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>26010001</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1">
-        <v>2</v>
-      </c>
-      <c r="J16" s="1">
-        <v>26010001</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>1</v>
-      </c>
-      <c r="R16" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="T17" s="1">
+        <v>1</v>
+      </c>
+      <c r="U17" s="12">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W17" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="T16" s="1">
-        <v>1</v>
-      </c>
-      <c r="U16" s="12">
-        <v>0</v>
-      </c>
-      <c r="V16" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="W16" s="1" t="s">
+      <c r="X17" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="X16" s="1" t="s">
+      <c r="Y17" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Y16" s="1" t="s">
+      <c r="Z17" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="Z16" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA16" s="1">
+      <c r="AA17" s="1">
         <v>59130001</v>
       </c>
-      <c r="AB16" s="1">
+      <c r="AB17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A17" s="10">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.15">
+      <c r="A18" s="10">
         <v>25010001</v>
       </c>
-      <c r="B17" s="10">
-        <v>0</v>
-      </c>
-      <c r="C17" s="10">
-        <v>2</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="B18" s="10">
+        <v>0</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G18" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H18" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="10">
-        <v>0</v>
-      </c>
-      <c r="J17" s="10">
-        <v>0</v>
-      </c>
-      <c r="K17" s="10" t="s">
+      <c r="I18" s="10">
+        <v>0</v>
+      </c>
+      <c r="J18" s="10">
+        <v>0</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="N17" s="10">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10">
-        <v>0</v>
-      </c>
-      <c r="P17" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>1</v>
-      </c>
-      <c r="R17" s="10" t="s">
+      <c r="M18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10">
+        <v>0</v>
+      </c>
+      <c r="P18" s="10">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>1</v>
+      </c>
+      <c r="R18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="S17" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="T17" s="10">
-        <v>1</v>
-      </c>
-      <c r="U17" s="10">
-        <v>0</v>
-      </c>
-      <c r="V17" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="W17" s="10" t="s">
+      <c r="S18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="T18" s="10">
+        <v>1</v>
+      </c>
+      <c r="U18" s="10">
+        <v>0</v>
+      </c>
+      <c r="V18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="W18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="X17" s="10" t="s">
+      <c r="X18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Y17" s="10" t="s">
+      <c r="Y18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Z17" s="10" t="s">
+      <c r="Z18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AA17" s="10">
+      <c r="AA18" s="10">
         <v>54150001</v>
       </c>
-      <c r="AB17" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13">
-        <v>95000101</v>
-      </c>
-      <c r="B18" s="13">
-        <v>95000101</v>
-      </c>
-      <c r="C18" s="13">
-        <v>5</v>
-      </c>
-      <c r="D18" s="13">
-        <v>1</v>
-      </c>
-      <c r="E18" s="13">
-        <v>1</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="N18" s="13">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>2</v>
-      </c>
-      <c r="R18" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="S18" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="T18" s="13">
-        <v>1</v>
-      </c>
-      <c r="U18" s="13">
-        <v>1</v>
-      </c>
-      <c r="V18" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="W18" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="X18" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y18" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z18" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>85001100</v>
-      </c>
-      <c r="AB18" s="13">
+      <c r="AB18" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
-        <v>95100101</v>
+        <v>95000101</v>
       </c>
       <c r="B19" s="13">
-        <v>95100101</v>
+        <v>95000101</v>
       </c>
       <c r="C19" s="13">
         <v>5</v>
@@ -3225,13 +3233,13 @@
         <v>1</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="13">
         <v>0</v>
@@ -3240,13 +3248,13 @@
         <v>0</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N19" s="13">
         <v>0</v>
@@ -3255,40 +3263,40 @@
         <v>0</v>
       </c>
       <c r="P19" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="13">
         <v>2</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="T19" s="13">
         <v>1</v>
       </c>
       <c r="U19" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="AA19" s="13">
-        <v>0</v>
+        <v>85001100</v>
       </c>
       <c r="AB19" s="13">
         <v>0</v>
@@ -3296,10 +3304,10 @@
     </row>
     <row r="20" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13">
-        <v>95200101</v>
+        <v>95100101</v>
       </c>
       <c r="B20" s="13">
-        <v>95200101</v>
+        <v>95100101</v>
       </c>
       <c r="C20" s="13">
         <v>5</v>
@@ -3311,167 +3319,167 @@
         <v>1</v>
       </c>
       <c r="F20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="N20" s="13">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>2</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="T20" s="13">
+        <v>1</v>
+      </c>
+      <c r="U20" s="13">
+        <v>2</v>
+      </c>
+      <c r="V20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="W20" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="X20" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y20" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z20" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="13">
+        <v>95200101</v>
+      </c>
+      <c r="B21" s="13">
+        <v>95200101</v>
+      </c>
+      <c r="C21" s="13">
+        <v>5</v>
+      </c>
+      <c r="D21" s="13">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G21" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H21" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I20" s="13">
-        <v>0</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13" t="s">
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13">
+        <v>0</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="L21" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="M21" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="M20" s="13" t="s">
+      <c r="N21" s="13">
+        <v>0</v>
+      </c>
+      <c r="O21" s="13">
+        <v>0</v>
+      </c>
+      <c r="P21" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>2</v>
+      </c>
+      <c r="R21" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="N20" s="13">
-        <v>0</v>
-      </c>
-      <c r="O20" s="13">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="S21" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="T21" s="13">
+        <v>1</v>
+      </c>
+      <c r="U21" s="13">
         <v>4</v>
       </c>
-      <c r="Q20" s="13">
-        <v>2</v>
-      </c>
-      <c r="R20" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="S20" s="13" t="s">
+      <c r="V21" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="W21" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="T20" s="13">
-        <v>1</v>
-      </c>
-      <c r="U20" s="13">
-        <v>4</v>
-      </c>
-      <c r="V20" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="W20" s="13" t="s">
+      <c r="X21" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="Y21" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="Y20" s="13" t="s">
+      <c r="Z21" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="Z20" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>20001</v>
-      </c>
-      <c r="B21" s="2">
-        <v>920001</v>
-      </c>
-      <c r="C21" s="2">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>720001</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="M21" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="N21" s="2">
-        <v>0</v>
-      </c>
-      <c r="O21" s="2">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>2</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="S21" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="T21" s="2">
-        <v>1</v>
-      </c>
-      <c r="U21" s="2">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W21" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="X21" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y21" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z21" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="2">
-        <v>820001</v>
+      <c r="AA21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>20011</v>
+        <v>20001</v>
       </c>
       <c r="B22" s="2">
-        <v>920011</v>
+        <v>920001</v>
       </c>
       <c r="C22" s="2">
         <v>5</v>
@@ -3483,25 +3491,28 @@
         <v>1</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>200</v>
+        <v>178</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="I22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2">
-        <v>720011</v>
+        <v>720001</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="N22" s="2">
         <v>0</v>
@@ -3510,54 +3521,54 @@
         <v>1</v>
       </c>
       <c r="P22" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="2">
         <v>2</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="T22" s="2">
         <v>1</v>
       </c>
       <c r="U22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W22" s="13" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="X22" s="13" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="Z22" s="13" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="AA22" s="2">
         <v>0</v>
       </c>
       <c r="AB22" s="2">
-        <v>820011</v>
+        <v>820001</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>20012</v>
+        <v>20011</v>
       </c>
       <c r="B23" s="2">
-        <v>920012</v>
+        <v>920011</v>
       </c>
       <c r="C23" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -3566,28 +3577,25 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2">
-        <v>0</v>
+        <v>720011</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="N23" s="2">
         <v>0</v>
@@ -3596,16 +3604,16 @@
         <v>1</v>
       </c>
       <c r="P23" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="2">
         <v>2</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="T23" s="2">
         <v>1</v>
@@ -3614,19 +3622,19 @@
         <v>3</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W23" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="X23" s="13" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="Y23" s="13" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="Z23" s="13" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="AA23" s="2">
         <v>0</v>
@@ -3637,28 +3645,28 @@
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>20021</v>
+        <v>20012</v>
       </c>
       <c r="B24" s="2">
-        <v>920021</v>
+        <v>920012</v>
       </c>
       <c r="C24" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
@@ -3667,105 +3675,105 @@
         <v>0</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="N24" s="2">
         <v>0</v>
       </c>
       <c r="O24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="2">
         <v>2</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="T24" s="2">
         <v>1</v>
       </c>
       <c r="U24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W24" s="13" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="X24" s="13" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="Z24" s="13" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="AA24" s="2">
         <v>0</v>
       </c>
       <c r="AB24" s="2">
-        <v>0</v>
+        <v>820011</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>20022</v>
+        <v>20021</v>
       </c>
       <c r="B25" s="2">
-        <v>920022</v>
+        <v>920021</v>
       </c>
       <c r="C25" s="2">
         <v>5</v>
       </c>
       <c r="D25" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="I25" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2">
-        <v>720022</v>
+        <v>0</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="N25" s="2">
         <v>0</v>
       </c>
       <c r="O25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="2">
         <v>1</v>
@@ -3774,10 +3782,10 @@
         <v>2</v>
       </c>
       <c r="R25" s="13" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="S25" s="13" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="T25" s="2">
         <v>1</v>
@@ -3786,19 +3794,19 @@
         <v>2</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W25" s="13" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="X25" s="13" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="Y25" s="13" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="Z25" s="13" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="AA25" s="2">
         <v>0</v>
@@ -3809,43 +3817,43 @@
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>20023</v>
+        <v>20022</v>
       </c>
       <c r="B26" s="2">
-        <v>920023</v>
+        <v>920022</v>
       </c>
       <c r="C26" s="2">
         <v>5</v>
       </c>
       <c r="D26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="I26" s="2">
         <v>2</v>
       </c>
       <c r="J26" s="2">
-        <v>720023</v>
+        <v>720022</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="N26" s="2">
         <v>0</v>
@@ -3854,16 +3862,16 @@
         <v>1</v>
       </c>
       <c r="P26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="2">
         <v>2</v>
       </c>
       <c r="R26" s="13" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="S26" s="13" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="T26" s="2">
         <v>1</v>
@@ -3872,19 +3880,19 @@
         <v>2</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W26" s="13" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="X26" s="13" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="Y26" s="13" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Z26" s="13" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="AA26" s="2">
         <v>0</v>
@@ -3895,87 +3903,173 @@
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>20031</v>
+        <v>20023</v>
       </c>
       <c r="B27" s="2">
-        <v>920031</v>
+        <v>920023</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
       </c>
       <c r="D27" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>720023</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <v>1</v>
+      </c>
+      <c r="P27" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>2</v>
+      </c>
+      <c r="R27" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="S27" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="T27" s="2">
+        <v>1</v>
+      </c>
+      <c r="U27" s="2">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W27" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="X27" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y27" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z27" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>20031</v>
+      </c>
+      <c r="B28" s="2">
+        <v>920031</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
-      <c r="K27" s="13" t="s">
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="L28" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="L27" s="13" t="s">
+      <c r="M28" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="M27" s="13" t="s">
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>2</v>
+      </c>
+      <c r="R28" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>2</v>
-      </c>
-      <c r="R27" s="13" t="s">
+      <c r="S28" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="S27" s="13" t="s">
+      <c r="T28" s="2">
+        <v>1</v>
+      </c>
+      <c r="U28" s="2">
+        <v>4</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W28" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="T27" s="2">
-        <v>1</v>
-      </c>
-      <c r="U27" s="2">
-        <v>4</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W27" s="13" t="s">
+      <c r="X28" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="X27" s="13" t="s">
+      <c r="Y28" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="Y27" s="13" t="s">
+      <c r="Z28" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="Z27" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="2">
+      <c r="AA28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F98FE89-BDBC-427C-862F-BC93972FABD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE44191-836E-49DC-B911-31BD6E9FB314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="278">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1177,6 +1177,42 @@
   </si>
   <si>
     <t>0:500</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼等级2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉沦魔等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉沦魔等级2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:400</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺_升龙击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺_爆炎砸地</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1735,7 +1771,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -2822,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>28</v>
@@ -2878,7 +2914,7 @@
     </row>
     <row r="15" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>203002011</v>
+        <v>203001001</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
@@ -2893,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>57</v>
@@ -2908,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>28</v>
@@ -2964,7 +3000,7 @@
     </row>
     <row r="16" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>216001001</v>
+        <v>203002011</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
@@ -2979,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>57</v>
@@ -2994,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>268</v>
+        <v>177</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>28</v>
@@ -3050,13 +3086,13 @@
     </row>
     <row r="17" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>59260001</v>
+        <v>203003001</v>
       </c>
       <c r="B17" s="1">
-        <v>3592200</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -3064,43 +3100,47 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="8"/>
+      <c r="F17" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="G17" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H17" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="I17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>26010001</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>190</v>
+        <v>0</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>174</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>191</v>
+        <v>28</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
       </c>
       <c r="O17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="T17" s="1">
         <v>1</v>
@@ -3112,887 +3152,886 @@
         <v>77</v>
       </c>
       <c r="W17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>204001001</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>2</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T18" s="1">
+        <v>1</v>
+      </c>
+      <c r="U18" s="12">
+        <v>0</v>
+      </c>
+      <c r="V18" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>204002001</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>2</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T19" s="1">
+        <v>1</v>
+      </c>
+      <c r="U19" s="12">
+        <v>0</v>
+      </c>
+      <c r="V19" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>211001001</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1</v>
+      </c>
+      <c r="P20" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>2</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T20" s="1">
+        <v>1</v>
+      </c>
+      <c r="U20" s="12">
+        <v>0</v>
+      </c>
+      <c r="V20" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>211002001</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>2</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T21" s="1">
+        <v>1</v>
+      </c>
+      <c r="U21" s="12">
+        <v>0</v>
+      </c>
+      <c r="V21" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>216001001</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>2</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T22" s="1">
+        <v>1</v>
+      </c>
+      <c r="U22" s="12">
+        <v>0</v>
+      </c>
+      <c r="V22" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>59260001</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3592200</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1">
+        <v>2</v>
+      </c>
+      <c r="J23" s="1">
+        <v>26010001</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>1</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="T23" s="1">
+        <v>1</v>
+      </c>
+      <c r="U23" s="12">
+        <v>0</v>
+      </c>
+      <c r="V23" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W23" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="X17" s="1" t="s">
+      <c r="X23" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="Y17" s="1" t="s">
+      <c r="Y23" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Z17" s="1" t="s">
+      <c r="Z23" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AA17" s="1">
+      <c r="AA23" s="1">
         <v>59130001</v>
       </c>
-      <c r="AB17" s="1">
+      <c r="AB23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A18" s="10">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.15">
+      <c r="A24" s="10">
         <v>25010001</v>
       </c>
-      <c r="B18" s="10">
-        <v>0</v>
-      </c>
-      <c r="C18" s="10">
-        <v>2</v>
-      </c>
-      <c r="D18" s="10">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="s">
+      <c r="B24" s="10">
+        <v>0</v>
+      </c>
+      <c r="C24" s="10">
+        <v>2</v>
+      </c>
+      <c r="D24" s="10">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G24" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H24" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I18" s="10">
-        <v>0</v>
-      </c>
-      <c r="J18" s="10">
-        <v>0</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="10" t="s">
+      <c r="I24" s="10">
+        <v>0</v>
+      </c>
+      <c r="J24" s="10">
+        <v>0</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="N18" s="10">
-        <v>0</v>
-      </c>
-      <c r="O18" s="10">
-        <v>0</v>
-      </c>
-      <c r="P18" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>1</v>
-      </c>
-      <c r="R18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="S18" s="10" t="s">
+      <c r="N24" s="10">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0</v>
+      </c>
+      <c r="P24" s="10">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>1</v>
+      </c>
+      <c r="R24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S24" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="T18" s="10">
-        <v>1</v>
-      </c>
-      <c r="U18" s="10">
-        <v>0</v>
-      </c>
-      <c r="V18" s="10" t="s">
+      <c r="T24" s="10">
+        <v>1</v>
+      </c>
+      <c r="U24" s="10">
+        <v>0</v>
+      </c>
+      <c r="V24" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="X18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA18" s="10">
+      <c r="W24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="X24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA24" s="10">
         <v>54150001</v>
       </c>
-      <c r="AB18" s="10">
+      <c r="AB24" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13">
+    <row r="25" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="13">
         <v>95000101</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B25" s="13">
         <v>95000101</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C25" s="13">
         <v>5</v>
       </c>
-      <c r="D19" s="13">
-        <v>1</v>
-      </c>
-      <c r="E19" s="13">
-        <v>1</v>
-      </c>
-      <c r="F19" s="13" t="s">
+      <c r="D25" s="13">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G25" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H25" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="I19" s="13">
-        <v>0</v>
-      </c>
-      <c r="J19" s="13">
-        <v>0</v>
-      </c>
-      <c r="K19" s="13" t="s">
+      <c r="I25" s="13">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13">
+        <v>0</v>
+      </c>
+      <c r="K25" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="L25" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="M19" s="13" t="s">
+      <c r="M25" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="N19" s="13">
-        <v>0</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>2</v>
-      </c>
-      <c r="R19" s="13" t="s">
+      <c r="N25" s="13">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13">
+        <v>0</v>
+      </c>
+      <c r="P25" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>2</v>
+      </c>
+      <c r="R25" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="S19" s="13" t="s">
+      <c r="S25" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="T19" s="13">
-        <v>1</v>
-      </c>
-      <c r="U19" s="13">
-        <v>1</v>
-      </c>
-      <c r="V19" s="13" t="s">
+      <c r="T25" s="13">
+        <v>1</v>
+      </c>
+      <c r="U25" s="13">
+        <v>1</v>
+      </c>
+      <c r="V25" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="W19" s="13" t="s">
+      <c r="W25" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="X19" s="13" t="s">
+      <c r="X25" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="Y19" s="13" t="s">
+      <c r="Y25" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="Z19" s="13" t="s">
+      <c r="Z25" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AA19" s="13">
+      <c r="AA25" s="13">
         <v>85001100</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AB25" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13">
+    <row r="26" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="13">
         <v>95100101</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B26" s="13">
         <v>95100101</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C26" s="13">
         <v>5</v>
       </c>
-      <c r="D20" s="13">
-        <v>1</v>
-      </c>
-      <c r="E20" s="13">
-        <v>1</v>
-      </c>
-      <c r="F20" s="13" t="s">
+      <c r="D26" s="13">
+        <v>1</v>
+      </c>
+      <c r="E26" s="13">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G26" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H26" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I20" s="13">
-        <v>0</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13" t="s">
+      <c r="I26" s="13">
+        <v>0</v>
+      </c>
+      <c r="J26" s="13">
+        <v>0</v>
+      </c>
+      <c r="K26" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L26" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="M20" s="13" t="s">
+      <c r="M26" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="N20" s="13">
-        <v>0</v>
-      </c>
-      <c r="O20" s="13">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="N26" s="13">
+        <v>0</v>
+      </c>
+      <c r="O26" s="13">
+        <v>0</v>
+      </c>
+      <c r="P26" s="13">
         <v>3</v>
       </c>
-      <c r="Q20" s="13">
-        <v>2</v>
-      </c>
-      <c r="R20" s="13" t="s">
+      <c r="Q26" s="13">
+        <v>2</v>
+      </c>
+      <c r="R26" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="S20" s="13" t="s">
+      <c r="S26" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="T20" s="13">
-        <v>1</v>
-      </c>
-      <c r="U20" s="13">
-        <v>2</v>
-      </c>
-      <c r="V20" s="13" t="s">
+      <c r="T26" s="13">
+        <v>1</v>
+      </c>
+      <c r="U26" s="13">
+        <v>2</v>
+      </c>
+      <c r="V26" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="W20" s="13" t="s">
+      <c r="W26" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="X26" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="Y20" s="13" t="s">
+      <c r="Y26" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="Z20" s="13" t="s">
+      <c r="Z26" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AA20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="13">
+      <c r="AA26" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="13">
+    <row r="27" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="13">
         <v>95200101</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B27" s="13">
         <v>95200101</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C27" s="13">
         <v>5</v>
       </c>
-      <c r="D21" s="13">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13">
-        <v>1</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="D27" s="13">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G27" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H27" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I21" s="13">
-        <v>0</v>
-      </c>
-      <c r="J21" s="13">
-        <v>0</v>
-      </c>
-      <c r="K21" s="13" t="s">
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="L27" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="M21" s="13" t="s">
+      <c r="M27" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="N21" s="13">
-        <v>0</v>
-      </c>
-      <c r="O21" s="13">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
+      <c r="N27" s="13">
+        <v>0</v>
+      </c>
+      <c r="O27" s="13">
+        <v>0</v>
+      </c>
+      <c r="P27" s="13">
         <v>4</v>
       </c>
-      <c r="Q21" s="13">
-        <v>2</v>
-      </c>
-      <c r="R21" s="13" t="s">
+      <c r="Q27" s="13">
+        <v>2</v>
+      </c>
+      <c r="R27" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="S21" s="13" t="s">
+      <c r="S27" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="T21" s="13">
-        <v>1</v>
-      </c>
-      <c r="U21" s="13">
+      <c r="T27" s="13">
+        <v>1</v>
+      </c>
+      <c r="U27" s="13">
         <v>4</v>
       </c>
-      <c r="V21" s="13" t="s">
+      <c r="V27" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="W21" s="13" t="s">
+      <c r="W27" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="X21" s="13" t="s">
+      <c r="X27" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="Y21" s="13" t="s">
+      <c r="Y27" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="Z21" s="13" t="s">
+      <c r="Z27" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="AA21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
-        <v>20001</v>
-      </c>
-      <c r="B22" s="2">
-        <v>920001</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>720001</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="N22" s="2">
-        <v>0</v>
-      </c>
-      <c r="O22" s="2">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="2">
-        <v>2</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="S22" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="T22" s="2">
-        <v>1</v>
-      </c>
-      <c r="U22" s="2">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W22" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="X22" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y22" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z22" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="AA22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="2">
-        <v>820001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <v>20011</v>
-      </c>
-      <c r="B23" s="2">
-        <v>920011</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2">
-        <v>720011</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="N23" s="2">
-        <v>0</v>
-      </c>
-      <c r="O23" s="2">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>2</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="S23" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="T23" s="2">
-        <v>1</v>
-      </c>
-      <c r="U23" s="2">
-        <v>3</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W23" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="X23" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y23" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z23" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="AA23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="2">
-        <v>820011</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>20012</v>
-      </c>
-      <c r="B24" s="2">
-        <v>920012</v>
-      </c>
-      <c r="C24" s="2">
-        <v>6</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="M24" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="N24" s="2">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2">
-        <v>1</v>
-      </c>
-      <c r="P24" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>2</v>
-      </c>
-      <c r="R24" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="S24" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="T24" s="2">
-        <v>1</v>
-      </c>
-      <c r="U24" s="2">
-        <v>3</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W24" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="X24" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y24" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z24" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="2">
-        <v>820011</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>20021</v>
-      </c>
-      <c r="B25" s="2">
-        <v>920021</v>
-      </c>
-      <c r="C25" s="2">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="N25" s="2">
-        <v>0</v>
-      </c>
-      <c r="O25" s="2">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>2</v>
-      </c>
-      <c r="R25" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="S25" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="T25" s="2">
-        <v>1</v>
-      </c>
-      <c r="U25" s="2">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W25" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="X25" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="Y25" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="Z25" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA25" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>20022</v>
-      </c>
-      <c r="B26" s="2">
-        <v>920022</v>
-      </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
-        <v>4</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I26" s="2">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2">
-        <v>720022</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="N26" s="2">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2">
-        <v>1</v>
-      </c>
-      <c r="P26" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>2</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="S26" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="T26" s="2">
-        <v>1</v>
-      </c>
-      <c r="U26" s="2">
-        <v>2</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W26" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="X26" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="Y26" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="Z26" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>20023</v>
-      </c>
-      <c r="B27" s="2">
-        <v>920023</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
-        <v>3</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I27" s="2">
-        <v>2</v>
-      </c>
-      <c r="J27" s="2">
-        <v>720023</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2">
-        <v>1</v>
-      </c>
-      <c r="P27" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>2</v>
-      </c>
-      <c r="R27" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="S27" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="T27" s="2">
-        <v>1</v>
-      </c>
-      <c r="U27" s="2">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W27" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="X27" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="Y27" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="Z27" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="2">
+      <c r="AA27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>20031</v>
+        <v>20001</v>
       </c>
       <c r="B28" s="2">
-        <v>920031</v>
+        <v>920001</v>
       </c>
       <c r="C28" s="2">
         <v>5</v>
@@ -4004,72 +4043,585 @@
         <v>1</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>264</v>
+        <v>178</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>264</v>
+        <v>178</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>265</v>
+        <v>179</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
       </c>
       <c r="J28" s="2">
-        <v>0</v>
+        <v>720001</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>257</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2">
         <v>0</v>
       </c>
       <c r="O28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q28" s="2">
         <v>2</v>
       </c>
       <c r="R28" s="13" t="s">
-        <v>258</v>
+        <v>183</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="T28" s="2">
         <v>1</v>
       </c>
       <c r="U28" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="W28" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="X28" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y28" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z28" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2">
+        <v>820001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>20011</v>
+      </c>
+      <c r="B29" s="2">
+        <v>920011</v>
+      </c>
+      <c r="C29" s="2">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>720011</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>2</v>
+      </c>
+      <c r="R29" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="S29" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="T29" s="2">
+        <v>1</v>
+      </c>
+      <c r="U29" s="2">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W29" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="X29" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y29" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z29" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>820011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>20012</v>
+      </c>
+      <c r="B30" s="2">
+        <v>920012</v>
+      </c>
+      <c r="C30" s="2">
+        <v>6</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="N30" s="2">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2">
+        <v>1</v>
+      </c>
+      <c r="P30" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>2</v>
+      </c>
+      <c r="R30" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="S30" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="T30" s="2">
+        <v>1</v>
+      </c>
+      <c r="U30" s="2">
+        <v>3</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W30" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="X30" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y30" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z30" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>820011</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>20021</v>
+      </c>
+      <c r="B31" s="2">
+        <v>920021</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="N31" s="2">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>2</v>
+      </c>
+      <c r="R31" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="S31" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="T31" s="2">
+        <v>1</v>
+      </c>
+      <c r="U31" s="2">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W31" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="X31" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y31" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z31" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>20022</v>
+      </c>
+      <c r="B32" s="2">
+        <v>920022</v>
+      </c>
+      <c r="C32" s="2">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I32" s="2">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2">
+        <v>720022</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="N32" s="2">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>2</v>
+      </c>
+      <c r="R32" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="S32" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="T32" s="2">
+        <v>1</v>
+      </c>
+      <c r="U32" s="2">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W32" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="X32" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y32" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z32" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>20023</v>
+      </c>
+      <c r="B33" s="2">
+        <v>920023</v>
+      </c>
+      <c r="C33" s="2">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I33" s="2">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>720023</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="L33" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="N33" s="2">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>2</v>
+      </c>
+      <c r="R33" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="S33" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="T33" s="2">
+        <v>1</v>
+      </c>
+      <c r="U33" s="2">
+        <v>2</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W33" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="X33" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y33" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z33" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>20031</v>
+      </c>
+      <c r="B34" s="2">
+        <v>920031</v>
+      </c>
+      <c r="C34" s="2">
+        <v>5</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="L34" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="N34" s="2">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>2</v>
+      </c>
+      <c r="R34" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="S34" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="T34" s="2">
+        <v>1</v>
+      </c>
+      <c r="U34" s="2">
+        <v>4</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W34" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="X28" s="13" t="s">
+      <c r="X34" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="Y28" s="13" t="s">
+      <c r="Y34" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="Z28" s="13" t="s">
+      <c r="Z34" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="AA28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="2">
+      <c r="AA34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="2">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE44191-836E-49DC-B911-31BD6E9FB314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630DF9C2-C579-4C00-A465-E3027B9974B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -3608,7 +3608,7 @@
         <v>3592200</v>
       </c>
       <c r="C23" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -3622,10 +3622,10 @@
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>26010001</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>190</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630DF9C2-C579-4C00-A465-E3027B9974B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC69110-B2BF-42C9-8870-20EFEFBA7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="280">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -299,920 +299,929 @@
     <t>type</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>skill_cool_time</t>
+  </si>
+  <si>
+    <t>is_break</t>
+  </si>
+  <si>
+    <t>is_no_target</t>
+  </si>
+  <si>
+    <t>target_type</t>
+  </si>
+  <si>
+    <t>damage_type</t>
+  </si>
+  <si>
+    <t>main_target_damage</t>
+  </si>
+  <si>
+    <t>self_effect</t>
+  </si>
+  <si>
+    <t>target_effect</t>
+  </si>
+  <si>
+    <t>技能id</t>
+  </si>
+  <si>
+    <t>技能类型</t>
+  </si>
+  <si>
+    <t>技能名</t>
+  </si>
+  <si>
+    <t>技能描述_文本</t>
+  </si>
+  <si>
+    <t>技能释放冷却时间（豪秒）</t>
+  </si>
+  <si>
+    <t>是否打断当前动作（0-不 1-打断</t>
+  </si>
+  <si>
+    <t>是否允许无目标释放（0-不允许 1-允许）</t>
+  </si>
+  <si>
+    <t>释放目标类型</t>
+  </si>
+  <si>
+    <t>伤害计算类型</t>
+  </si>
+  <si>
+    <t>主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>释放后自身效果</t>
+  </si>
+  <si>
+    <t>释放后对目标效果</t>
+  </si>
+  <si>
+    <t>0:0</t>
+  </si>
+  <si>
+    <t>单体伤害</t>
+  </si>
+  <si>
+    <t>main_target_damage_fix</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>主目标直接伤害固定值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>second_target_damage_fix</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>非主目标直接伤害固定值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>second_target_damage</t>
+  </si>
+  <si>
+    <t>非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>distance_min</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>distance_max</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>最远释放距离</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近释放距离</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果半径</t>
+  </si>
+  <si>
+    <t>target_num</t>
+  </si>
+  <si>
+    <t>目标数量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>scope_param1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>scope_type</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能等级</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家1档平A</t>
+  </si>
+  <si>
+    <t>玩家1档技能</t>
+  </si>
+  <si>
+    <t>玩家2档平A</t>
+  </si>
+  <si>
+    <t>玩家3平A</t>
+  </si>
+  <si>
+    <t>玩家2档技能1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家3档技能1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标阵营</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S_C</t>
+  </si>
+  <si>
+    <t>普通攻击</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成，永久</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage_element</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S_C</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参与伤害计算的攻击元素类型（0-物理、1-冰、2-火、3-毒、4-电）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放4道雷击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放冰弹攻击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放陨石攻击敌方</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级4远程</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜘蛛怪等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage_element_adjust</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素伤害系数调整关联属性id（按顺序：物理、冰、火、毒、电，万分比）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>7000305,7000301,7000302,7000303,7000304</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,2,3,4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得技能对应属性id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRING_S_C</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_attr_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S_C</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:10000</t>
+  </si>
+  <si>
+    <t>0:10000</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:1</t>
+  </si>
+  <si>
+    <t>0:1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:990010101</t>
+  </si>
+  <si>
+    <t>1:190010101</t>
+  </si>
+  <si>
+    <t>1:290010101</t>
+  </si>
+  <si>
+    <t>1:390010101</t>
+  </si>
+  <si>
+    <t>1:490010101</t>
+  </si>
+  <si>
+    <t>1:590010101</t>
+  </si>
+  <si>
+    <t>1:690010101</t>
+  </si>
+  <si>
+    <t>1:790010101</t>
+  </si>
+  <si>
+    <t>1:890010101</t>
+  </si>
+  <si>
+    <t>1:190010102</t>
+  </si>
+  <si>
+    <t>1:290010102</t>
+  </si>
+  <si>
+    <t>1:390010102</t>
+  </si>
+  <si>
+    <t>1:490010102</t>
+  </si>
+  <si>
+    <t>1:590010102</t>
+  </si>
+  <si>
+    <t>1:690010102</t>
+  </si>
+  <si>
+    <t>1:790010102</t>
+  </si>
+  <si>
+    <t>1:890010102</t>
+  </si>
+  <si>
+    <t>1:990010102</t>
+  </si>
+  <si>
+    <t>1:190010201</t>
+  </si>
+  <si>
+    <t>1:290010201</t>
+  </si>
+  <si>
+    <t>1:390010201</t>
+  </si>
+  <si>
+    <t>1:490010201</t>
+  </si>
+  <si>
+    <t>1:590010201</t>
+  </si>
+  <si>
+    <t>1:690010201</t>
+  </si>
+  <si>
+    <t>1:790010201</t>
+  </si>
+  <si>
+    <t>1:890010201</t>
+  </si>
+  <si>
+    <t>1:990010201</t>
+  </si>
+  <si>
+    <t>1:190010202</t>
+  </si>
+  <si>
+    <t>1:290010202</t>
+  </si>
+  <si>
+    <t>1:390010202</t>
+  </si>
+  <si>
+    <t>1:490010202</t>
+  </si>
+  <si>
+    <t>1:590010202</t>
+  </si>
+  <si>
+    <t>1:690010202</t>
+  </si>
+  <si>
+    <t>1:790010202</t>
+  </si>
+  <si>
+    <t>1:890010202</t>
+  </si>
+  <si>
+    <t>1:990010202</t>
+  </si>
+  <si>
+    <t>1:190010301</t>
+  </si>
+  <si>
+    <t>1:290010301</t>
+  </si>
+  <si>
+    <t>1:390010301</t>
+  </si>
+  <si>
+    <t>1:490010301</t>
+  </si>
+  <si>
+    <t>1:590010301</t>
+  </si>
+  <si>
+    <t>1:690010301</t>
+  </si>
+  <si>
+    <t>1:790010301</t>
+  </si>
+  <si>
+    <t>1:890010301</t>
+  </si>
+  <si>
+    <t>1:990010301</t>
+  </si>
+  <si>
+    <t>1:190010302</t>
+  </si>
+  <si>
+    <t>1:290010302</t>
+  </si>
+  <si>
+    <t>1:390010302</t>
+  </si>
+  <si>
+    <t>1:490010302</t>
+  </si>
+  <si>
+    <t>1:590010302</t>
+  </si>
+  <si>
+    <t>1:690010302</t>
+  </si>
+  <si>
+    <t>1:790010302</t>
+  </si>
+  <si>
+    <t>1:890010302</t>
+  </si>
+  <si>
+    <t>1:990010302</t>
+  </si>
+  <si>
+    <t>1:195000101</t>
+  </si>
+  <si>
+    <t>1:295000101</t>
+  </si>
+  <si>
+    <t>1:395000101</t>
+  </si>
+  <si>
+    <t>1:495000101</t>
+  </si>
+  <si>
+    <t>1:595000101</t>
+  </si>
+  <si>
+    <t>1:695000101</t>
+  </si>
+  <si>
+    <t>1:795000101</t>
+  </si>
+  <si>
+    <t>1:895000101</t>
+  </si>
+  <si>
+    <t>1:995000101</t>
+  </si>
+  <si>
+    <t>1:195100101</t>
+  </si>
+  <si>
+    <t>1:295100101</t>
+  </si>
+  <si>
+    <t>1:395100101</t>
+  </si>
+  <si>
+    <t>1:495100101</t>
+  </si>
+  <si>
+    <t>1:595100101</t>
+  </si>
+  <si>
+    <t>1:695100101</t>
+  </si>
+  <si>
+    <t>1:795100101</t>
+  </si>
+  <si>
+    <t>1:895100101</t>
+  </si>
+  <si>
+    <t>1:995100101</t>
+  </si>
+  <si>
+    <t>1:195200101</t>
+  </si>
+  <si>
+    <t>1:295200101</t>
+  </si>
+  <si>
+    <t>1:395200101</t>
+  </si>
+  <si>
+    <t>1:495200101</t>
+  </si>
+  <si>
+    <t>1:595200101</t>
+  </si>
+  <si>
+    <t>1:695200101</t>
+  </si>
+  <si>
+    <t>1:795200101</t>
+  </si>
+  <si>
+    <t>1:895200101</t>
+  </si>
+  <si>
+    <t>1:995200101</t>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRING_S</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放时机</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放条件</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>auto_release_condition</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>auto_release_time</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:550</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:525</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:435</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:450</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域内每秒造成燃烧伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:8920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血</t>
+  </si>
+  <si>
+    <t>1:159260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:259260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:359260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:459260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:559260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:659260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:759260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:859260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:959260001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻附加毒爆</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920011</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2920011</t>
+  </si>
+  <si>
+    <t>1:3920011</t>
+  </si>
+  <si>
+    <t>1:4920011</t>
+  </si>
+  <si>
+    <t>1:5920011</t>
+  </si>
+  <si>
+    <t>1:6920011</t>
+  </si>
+  <si>
+    <t>1:7920011</t>
+  </si>
+  <si>
+    <t>1:8920011</t>
+  </si>
+  <si>
+    <t>1:9920011</t>
+  </si>
+  <si>
+    <t>1:1920012</t>
+  </si>
+  <si>
+    <t>1:2920012</t>
+  </si>
+  <si>
+    <t>1:3920012</t>
+  </si>
+  <si>
+    <t>1:4920012</t>
+  </si>
+  <si>
+    <t>1:5920012</t>
+  </si>
+  <si>
+    <t>1:6920012</t>
+  </si>
+  <si>
+    <t>1:7920012</t>
+  </si>
+  <si>
+    <t>1:8920012</t>
+  </si>
+  <si>
+    <t>1:9920012</t>
+  </si>
+  <si>
+    <t>毒爆</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒爆，小范围AOE伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>向目标方向冲刺挥砍，刀锋划出烈火，对目标造成火属性伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920021</t>
+  </si>
+  <si>
+    <t>1:2920021</t>
+  </si>
+  <si>
+    <t>1:3920021</t>
+  </si>
+  <si>
+    <t>1:4920021</t>
+  </si>
+  <si>
+    <t>1:5920021</t>
+  </si>
+  <si>
+    <t>1:6920021</t>
+  </si>
+  <si>
+    <t>1:7920021</t>
+  </si>
+  <si>
+    <t>1:8920021</t>
+  </si>
+  <si>
+    <t>1:9920021</t>
+  </si>
+  <si>
+    <t>升龙击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺收招后追加释放升龙击，造成火属性伤害和击飞</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920022</t>
+  </si>
+  <si>
+    <t>1:2920022</t>
+  </si>
+  <si>
+    <t>1:3920022</t>
+  </si>
+  <si>
+    <t>1:4920022</t>
+  </si>
+  <si>
+    <t>1:5920022</t>
+  </si>
+  <si>
+    <t>1:6920022</t>
+  </si>
+  <si>
+    <t>1:7920022</t>
+  </si>
+  <si>
+    <t>1:8920022</t>
+  </si>
+  <si>
+    <t>1:9920022</t>
+  </si>
+  <si>
+    <t>1:1920023</t>
+  </si>
+  <si>
+    <t>1:2920023</t>
+  </si>
+  <si>
+    <t>1:3920023</t>
+  </si>
+  <si>
+    <t>1:4920023</t>
+  </si>
+  <si>
+    <t>1:5920023</t>
+  </si>
+  <si>
+    <t>1:6920023</t>
+  </si>
+  <si>
+    <t>1:7920023</t>
+  </si>
+  <si>
+    <t>1:8920023</t>
+  </si>
+  <si>
+    <t>1:9920023</t>
+  </si>
+  <si>
+    <t>爆炎砸地</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放爆炎冲刺3次后，接1次大范围砸地造成火属性伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>priority</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>动作技能释放优先级</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920031</t>
+  </si>
+  <si>
+    <t>1:2920031</t>
+  </si>
+  <si>
+    <t>1:3920031</t>
+  </si>
+  <si>
+    <t>1:4920031</t>
+  </si>
+  <si>
+    <t>1:5920031</t>
+  </si>
+  <si>
+    <t>1:6920031</t>
+  </si>
+  <si>
+    <t>1:7920031</t>
+  </si>
+  <si>
+    <t>1:8920031</t>
+  </si>
+  <si>
+    <t>1:9920031</t>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链，可弹射3次</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>石像鬼精英</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:500</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼等级2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉沦魔等级1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉沦魔等级2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:400</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺_升龙击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺_爆炎砸地</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>name_desc</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>skill_cool_time</t>
-  </si>
-  <si>
-    <t>is_break</t>
-  </si>
-  <si>
-    <t>is_no_target</t>
-  </si>
-  <si>
-    <t>target_type</t>
-  </si>
-  <si>
-    <t>damage_type</t>
-  </si>
-  <si>
-    <t>main_target_damage</t>
-  </si>
-  <si>
-    <t>self_effect</t>
-  </si>
-  <si>
-    <t>target_effect</t>
-  </si>
-  <si>
-    <t>技能id</t>
-  </si>
-  <si>
-    <t>技能类型</t>
-  </si>
-  <si>
-    <t>技能名</t>
-  </si>
-  <si>
-    <t>技能描述_文本</t>
-  </si>
-  <si>
-    <t>技能释放冷却时间（豪秒）</t>
-  </si>
-  <si>
-    <t>是否打断当前动作（0-不 1-打断</t>
-  </si>
-  <si>
-    <t>是否允许无目标释放（0-不允许 1-允许）</t>
-  </si>
-  <si>
-    <t>释放目标类型</t>
-  </si>
-  <si>
-    <t>伤害计算类型</t>
-  </si>
-  <si>
-    <t>主目标直接伤害系数</t>
-  </si>
-  <si>
-    <t>释放后自身效果</t>
-  </si>
-  <si>
-    <t>释放后对目标效果</t>
-  </si>
-  <si>
-    <t>0:0</t>
-  </si>
-  <si>
-    <t>单体伤害</t>
-  </si>
-  <si>
-    <t>main_target_damage_fix</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>主目标直接伤害固定值</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>second_target_damage_fix</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>非主目标直接伤害固定值</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>second_target_damage</t>
-  </si>
-  <si>
-    <t>非主目标直接伤害系数</t>
-  </si>
-  <si>
-    <t>distance_min</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>distance_max</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>最远释放距离</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>最近释放距离</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果半径</t>
-  </si>
-  <si>
-    <t>target_num</t>
-  </si>
-  <si>
-    <t>目标数量</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>scope_param1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>scope_type</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>level</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能等级</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家1档平A</t>
-  </si>
-  <si>
-    <t>玩家1档技能</t>
-  </si>
-  <si>
-    <t>玩家2档平A</t>
-  </si>
-  <si>
-    <t>玩家3平A</t>
-  </si>
-  <si>
-    <t>玩家2档技能1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家3档技能1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标阵营</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S_C</t>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S_C</t>
-  </si>
-  <si>
-    <t>普通攻击</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成，永久</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage_element</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S_C</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>参与伤害计算的攻击元素类型（0-物理、1-冰、2-火、3-毒、4-电）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷击</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放4道雷击敌方</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放冰弹攻击敌方</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放陨石攻击敌方</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰弹</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>骷髅怪等级1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>骷髅怪等级2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>骷髅怪等级4远程</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>蜘蛛怪等级1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage_element_adjust</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素伤害系数调整关联属性id（按顺序：物理、冰、火、毒、电，万分比）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>7000305,7000301,7000302,7000303,7000304</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0,0,0,0</t>
-  </si>
-  <si>
-    <t>0,1,2,3,4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得技能对应属性id</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING_S_C</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_attr_id</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S_C</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:10000</t>
-  </si>
-  <si>
-    <t>0:10000</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:1</t>
-  </si>
-  <si>
-    <t>0:1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:990010101</t>
-  </si>
-  <si>
-    <t>1:190010101</t>
-  </si>
-  <si>
-    <t>1:290010101</t>
-  </si>
-  <si>
-    <t>1:390010101</t>
-  </si>
-  <si>
-    <t>1:490010101</t>
-  </si>
-  <si>
-    <t>1:590010101</t>
-  </si>
-  <si>
-    <t>1:690010101</t>
-  </si>
-  <si>
-    <t>1:790010101</t>
-  </si>
-  <si>
-    <t>1:890010101</t>
-  </si>
-  <si>
-    <t>1:190010102</t>
-  </si>
-  <si>
-    <t>1:290010102</t>
-  </si>
-  <si>
-    <t>1:390010102</t>
-  </si>
-  <si>
-    <t>1:490010102</t>
-  </si>
-  <si>
-    <t>1:590010102</t>
-  </si>
-  <si>
-    <t>1:690010102</t>
-  </si>
-  <si>
-    <t>1:790010102</t>
-  </si>
-  <si>
-    <t>1:890010102</t>
-  </si>
-  <si>
-    <t>1:990010102</t>
-  </si>
-  <si>
-    <t>1:190010201</t>
-  </si>
-  <si>
-    <t>1:290010201</t>
-  </si>
-  <si>
-    <t>1:390010201</t>
-  </si>
-  <si>
-    <t>1:490010201</t>
-  </si>
-  <si>
-    <t>1:590010201</t>
-  </si>
-  <si>
-    <t>1:690010201</t>
-  </si>
-  <si>
-    <t>1:790010201</t>
-  </si>
-  <si>
-    <t>1:890010201</t>
-  </si>
-  <si>
-    <t>1:990010201</t>
-  </si>
-  <si>
-    <t>1:190010202</t>
-  </si>
-  <si>
-    <t>1:290010202</t>
-  </si>
-  <si>
-    <t>1:390010202</t>
-  </si>
-  <si>
-    <t>1:490010202</t>
-  </si>
-  <si>
-    <t>1:590010202</t>
-  </si>
-  <si>
-    <t>1:690010202</t>
-  </si>
-  <si>
-    <t>1:790010202</t>
-  </si>
-  <si>
-    <t>1:890010202</t>
-  </si>
-  <si>
-    <t>1:990010202</t>
-  </si>
-  <si>
-    <t>1:190010301</t>
-  </si>
-  <si>
-    <t>1:290010301</t>
-  </si>
-  <si>
-    <t>1:390010301</t>
-  </si>
-  <si>
-    <t>1:490010301</t>
-  </si>
-  <si>
-    <t>1:590010301</t>
-  </si>
-  <si>
-    <t>1:690010301</t>
-  </si>
-  <si>
-    <t>1:790010301</t>
-  </si>
-  <si>
-    <t>1:890010301</t>
-  </si>
-  <si>
-    <t>1:990010301</t>
-  </si>
-  <si>
-    <t>1:190010302</t>
-  </si>
-  <si>
-    <t>1:290010302</t>
-  </si>
-  <si>
-    <t>1:390010302</t>
-  </si>
-  <si>
-    <t>1:490010302</t>
-  </si>
-  <si>
-    <t>1:590010302</t>
-  </si>
-  <si>
-    <t>1:690010302</t>
-  </si>
-  <si>
-    <t>1:790010302</t>
-  </si>
-  <si>
-    <t>1:890010302</t>
-  </si>
-  <si>
-    <t>1:990010302</t>
-  </si>
-  <si>
-    <t>1:195000101</t>
-  </si>
-  <si>
-    <t>1:295000101</t>
-  </si>
-  <si>
-    <t>1:395000101</t>
-  </si>
-  <si>
-    <t>1:495000101</t>
-  </si>
-  <si>
-    <t>1:595000101</t>
-  </si>
-  <si>
-    <t>1:695000101</t>
-  </si>
-  <si>
-    <t>1:795000101</t>
-  </si>
-  <si>
-    <t>1:895000101</t>
-  </si>
-  <si>
-    <t>1:995000101</t>
-  </si>
-  <si>
-    <t>1:195100101</t>
-  </si>
-  <si>
-    <t>1:295100101</t>
-  </si>
-  <si>
-    <t>1:395100101</t>
-  </si>
-  <si>
-    <t>1:495100101</t>
-  </si>
-  <si>
-    <t>1:595100101</t>
-  </si>
-  <si>
-    <t>1:695100101</t>
-  </si>
-  <si>
-    <t>1:795100101</t>
-  </si>
-  <si>
-    <t>1:895100101</t>
-  </si>
-  <si>
-    <t>1:995100101</t>
-  </si>
-  <si>
-    <t>1:195200101</t>
-  </si>
-  <si>
-    <t>1:295200101</t>
-  </si>
-  <si>
-    <t>1:395200101</t>
-  </si>
-  <si>
-    <t>1:495200101</t>
-  </si>
-  <si>
-    <t>1:595200101</t>
-  </si>
-  <si>
-    <t>1:695200101</t>
-  </si>
-  <si>
-    <t>1:795200101</t>
-  </si>
-  <si>
-    <t>1:895200101</t>
-  </si>
-  <si>
-    <t>1:995200101</t>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING_S</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动释放时机</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动释放条件</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>auto_release_condition</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>auto_release_time</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:550</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:525</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:435</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:450</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>炎域</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>炎域内每秒造成燃烧伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:6920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:8920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:9920001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻击中回血</t>
-  </si>
-  <si>
-    <t>1:159260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:259260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:359260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:459260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:559260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:659260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:759260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:859260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:959260001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻附加毒爆</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1920011</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2920011</t>
-  </si>
-  <si>
-    <t>1:3920011</t>
-  </si>
-  <si>
-    <t>1:4920011</t>
-  </si>
-  <si>
-    <t>1:5920011</t>
-  </si>
-  <si>
-    <t>1:6920011</t>
-  </si>
-  <si>
-    <t>1:7920011</t>
-  </si>
-  <si>
-    <t>1:8920011</t>
-  </si>
-  <si>
-    <t>1:9920011</t>
-  </si>
-  <si>
-    <t>1:1920012</t>
-  </si>
-  <si>
-    <t>1:2920012</t>
-  </si>
-  <si>
-    <t>1:3920012</t>
-  </si>
-  <si>
-    <t>1:4920012</t>
-  </si>
-  <si>
-    <t>1:5920012</t>
-  </si>
-  <si>
-    <t>1:6920012</t>
-  </si>
-  <si>
-    <t>1:7920012</t>
-  </si>
-  <si>
-    <t>1:8920012</t>
-  </si>
-  <si>
-    <t>1:9920012</t>
-  </si>
-  <si>
-    <t>毒爆</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>毒爆，小范围AOE伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炎冲刺</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>向目标方向冲刺挥砍，刀锋划出烈火，对目标造成火属性伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1920021</t>
-  </si>
-  <si>
-    <t>1:2920021</t>
-  </si>
-  <si>
-    <t>1:3920021</t>
-  </si>
-  <si>
-    <t>1:4920021</t>
-  </si>
-  <si>
-    <t>1:5920021</t>
-  </si>
-  <si>
-    <t>1:6920021</t>
-  </si>
-  <si>
-    <t>1:7920021</t>
-  </si>
-  <si>
-    <t>1:8920021</t>
-  </si>
-  <si>
-    <t>1:9920021</t>
-  </si>
-  <si>
-    <t>升龙击</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炎冲刺收招后追加释放升龙击，造成火属性伤害和击飞</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1920022</t>
-  </si>
-  <si>
-    <t>1:2920022</t>
-  </si>
-  <si>
-    <t>1:3920022</t>
-  </si>
-  <si>
-    <t>1:4920022</t>
-  </si>
-  <si>
-    <t>1:5920022</t>
-  </si>
-  <si>
-    <t>1:6920022</t>
-  </si>
-  <si>
-    <t>1:7920022</t>
-  </si>
-  <si>
-    <t>1:8920022</t>
-  </si>
-  <si>
-    <t>1:9920022</t>
-  </si>
-  <si>
-    <t>1:1920023</t>
-  </si>
-  <si>
-    <t>1:2920023</t>
-  </si>
-  <si>
-    <t>1:3920023</t>
-  </si>
-  <si>
-    <t>1:4920023</t>
-  </si>
-  <si>
-    <t>1:5920023</t>
-  </si>
-  <si>
-    <t>1:6920023</t>
-  </si>
-  <si>
-    <t>1:7920023</t>
-  </si>
-  <si>
-    <t>1:8920023</t>
-  </si>
-  <si>
-    <t>1:9920023</t>
-  </si>
-  <si>
-    <t>爆炎砸地</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放爆炎冲刺3次后，接1次大范围砸地造成火属性伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>priority</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>动作技能释放优先级</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1920031</t>
-  </si>
-  <si>
-    <t>1:2920031</t>
-  </si>
-  <si>
-    <t>1:3920031</t>
-  </si>
-  <si>
-    <t>1:4920031</t>
-  </si>
-  <si>
-    <t>1:5920031</t>
-  </si>
-  <si>
-    <t>1:6920031</t>
-  </si>
-  <si>
-    <t>1:7920031</t>
-  </si>
-  <si>
-    <t>1:8920031</t>
-  </si>
-  <si>
-    <t>1:9920031</t>
-  </si>
-  <si>
-    <t>闪电链</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链，可弹射3次</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>僵尸等级2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>石像鬼精英</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:500</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>僵尸等级1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>僵尸等级3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>狼等级1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>狼等级2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>沉沦魔等级1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>沉沦魔等级2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:400</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炎冲刺_升龙击</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炎冲刺_爆炎砸地</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>summon_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物id（默认召唤1个）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1416,7 +1425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1473,6 +1482,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1771,7 +1783,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -1798,273 +1810,283 @@
     <col min="26" max="26" width="19.25" style="2" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="2"/>
+    <col min="29" max="29" width="19.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:29" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>56</v>
+      <c r="AC2" s="21" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:29" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y3" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="15" t="s">
+      <c r="F4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="16" t="s">
+      <c r="N4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="V3" s="11" t="s">
+      <c r="T4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="V4" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="W4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="X3" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y3" s="16" t="s">
+      <c r="X4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Z3" s="16" t="s">
+      <c r="Z4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AA3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>15</v>
+      <c r="AA4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC4" s="21" t="s">
+        <v>279</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W4" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="X4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y4" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10101</v>
       </c>
@@ -2081,10 +2103,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6">
@@ -2094,13 +2116,13 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="N5" s="6">
         <v>0</v>
@@ -2115,31 +2137,31 @@
         <v>2</v>
       </c>
       <c r="R5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="S5" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6">
+        <v>1</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="T5" s="6">
-        <v>1</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="Y5" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="Z5" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AA5" s="6">
         <v>0</v>
@@ -2147,8 +2169,11 @@
       <c r="AB5" s="7">
         <v>0</v>
       </c>
+      <c r="AC5" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10102</v>
       </c>
@@ -2165,10 +2190,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6">
@@ -2178,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="N6" s="6">
         <v>0</v>
@@ -2199,40 +2224,43 @@
         <v>2</v>
       </c>
       <c r="R6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="T6" s="6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="V6" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z6" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="AA6" s="6">
         <v>0</v>
       </c>
       <c r="AB6" s="7">
         <v>0</v>
       </c>
+      <c r="AC6" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10201</v>
       </c>
@@ -2249,10 +2277,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6">
@@ -2262,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="N7" s="6">
         <v>0</v>
@@ -2283,40 +2311,43 @@
         <v>2</v>
       </c>
       <c r="R7" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="S7" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="T7" s="6">
+        <v>1</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W7" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="T7" s="6">
-        <v>1</v>
-      </c>
-      <c r="U7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="V7" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="Z7" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="AA7" s="6">
         <v>0</v>
       </c>
       <c r="AB7" s="7">
         <v>0</v>
       </c>
+      <c r="AC7" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10202</v>
       </c>
@@ -2333,10 +2364,10 @@
         <v>2</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6">
@@ -2346,13 +2377,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="N8" s="6">
         <v>0</v>
@@ -2367,40 +2398,43 @@
         <v>2</v>
       </c>
       <c r="R8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="S8" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="T8" s="6">
-        <v>1</v>
-      </c>
-      <c r="U8" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="V8" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="Z8" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="AA8" s="6">
         <v>0</v>
       </c>
       <c r="AB8" s="7">
         <v>0</v>
       </c>
+      <c r="AC8" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10301</v>
       </c>
@@ -2417,10 +2451,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6">
@@ -2430,13 +2464,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="N9" s="6">
         <v>0</v>
@@ -2451,40 +2485,43 @@
         <v>2</v>
       </c>
       <c r="R9" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="S9" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="T9" s="6">
+        <v>1</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="T9" s="6">
-        <v>1</v>
-      </c>
-      <c r="U9" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="V9" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="W9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Z9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="Z9" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="AA9" s="6">
         <v>0</v>
       </c>
       <c r="AB9" s="7">
         <v>0</v>
       </c>
+      <c r="AC9" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10302</v>
       </c>
@@ -2501,10 +2538,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6">
@@ -2514,13 +2551,13 @@
         <v>0</v>
       </c>
       <c r="K10" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="N10" s="6">
         <v>0</v>
@@ -2535,40 +2572,43 @@
         <v>2</v>
       </c>
       <c r="R10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="S10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="V10" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="T10" s="6">
-        <v>1</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="W10" s="6" t="s">
+      <c r="X10" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Z10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="Z10" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="AA10" s="6">
         <v>0</v>
       </c>
       <c r="AB10" s="7">
         <v>0</v>
       </c>
+      <c r="AC10" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>201001011</v>
       </c>
@@ -2585,13 +2625,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -2600,13 +2640,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N11" s="1">
         <v>0</v>
@@ -2621,10 +2661,10 @@
         <v>2</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S11" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T11" s="1">
         <v>1</v>
@@ -2633,19 +2673,19 @@
         <v>0</v>
       </c>
       <c r="V11" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA11" s="1">
         <v>0</v>
@@ -2653,8 +2693,11 @@
       <c r="AB11" s="1">
         <v>0</v>
       </c>
+      <c r="AC11" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>201002011</v>
       </c>
@@ -2671,13 +2714,13 @@
         <v>1</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -2686,13 +2729,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N12" s="1">
         <v>0</v>
@@ -2707,10 +2750,10 @@
         <v>2</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T12" s="1">
         <v>1</v>
@@ -2719,19 +2762,19 @@
         <v>0</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
@@ -2739,8 +2782,11 @@
       <c r="AB12" s="1">
         <v>0</v>
       </c>
+      <c r="AC12" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>201004011</v>
       </c>
@@ -2757,13 +2803,13 @@
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
@@ -2772,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
@@ -2793,10 +2839,10 @@
         <v>2</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T13" s="1">
         <v>1</v>
@@ -2805,19 +2851,19 @@
         <v>0</v>
       </c>
       <c r="V13" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
@@ -2825,8 +2871,11 @@
       <c r="AB13" s="1">
         <v>0</v>
       </c>
+      <c r="AC13" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>214001011</v>
       </c>
@@ -2843,13 +2892,13 @@
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2858,13 +2907,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N14" s="1">
         <v>0</v>
@@ -2879,10 +2928,10 @@
         <v>2</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T14" s="1">
         <v>1</v>
@@ -2891,19 +2940,19 @@
         <v>0</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA14" s="1">
         <v>0</v>
@@ -2911,8 +2960,11 @@
       <c r="AB14" s="1">
         <v>0</v>
       </c>
+      <c r="AC14" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>203001001</v>
       </c>
@@ -2929,13 +2981,13 @@
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -2944,13 +2996,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
@@ -2965,10 +3017,10 @@
         <v>2</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T15" s="1">
         <v>1</v>
@@ -2977,19 +3029,19 @@
         <v>0</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA15" s="1">
         <v>0</v>
@@ -2997,8 +3049,11 @@
       <c r="AB15" s="1">
         <v>0</v>
       </c>
+      <c r="AC15" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>203002011</v>
       </c>
@@ -3015,13 +3070,13 @@
         <v>1</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -3030,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N16" s="1">
         <v>0</v>
@@ -3051,10 +3106,10 @@
         <v>2</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T16" s="1">
         <v>1</v>
@@ -3063,19 +3118,19 @@
         <v>0</v>
       </c>
       <c r="V16" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA16" s="1">
         <v>0</v>
@@ -3083,8 +3138,11 @@
       <c r="AB16" s="1">
         <v>0</v>
       </c>
+      <c r="AC16" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>203003001</v>
       </c>
@@ -3101,13 +3159,13 @@
         <v>1</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -3116,13 +3174,13 @@
         <v>0</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
@@ -3137,10 +3195,10 @@
         <v>2</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T17" s="1">
         <v>1</v>
@@ -3149,19 +3207,19 @@
         <v>0</v>
       </c>
       <c r="V17" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA17" s="1">
         <v>0</v>
@@ -3169,8 +3227,11 @@
       <c r="AB17" s="1">
         <v>0</v>
       </c>
+      <c r="AC17" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>204001001</v>
       </c>
@@ -3187,13 +3248,13 @@
         <v>1</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -3202,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N18" s="1">
         <v>0</v>
@@ -3223,10 +3284,10 @@
         <v>2</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T18" s="1">
         <v>1</v>
@@ -3235,19 +3296,19 @@
         <v>0</v>
       </c>
       <c r="V18" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA18" s="1">
         <v>0</v>
@@ -3255,8 +3316,11 @@
       <c r="AB18" s="1">
         <v>0</v>
       </c>
+      <c r="AC18" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>204002001</v>
       </c>
@@ -3273,13 +3337,13 @@
         <v>1</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -3288,13 +3352,13 @@
         <v>0</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N19" s="1">
         <v>0</v>
@@ -3309,10 +3373,10 @@
         <v>2</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T19" s="1">
         <v>1</v>
@@ -3321,19 +3385,19 @@
         <v>0</v>
       </c>
       <c r="V19" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA19" s="1">
         <v>0</v>
@@ -3341,8 +3405,11 @@
       <c r="AB19" s="1">
         <v>0</v>
       </c>
+      <c r="AC19" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>211001001</v>
       </c>
@@ -3359,13 +3426,13 @@
         <v>1</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -3374,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N20" s="1">
         <v>0</v>
@@ -3395,10 +3462,10 @@
         <v>2</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T20" s="1">
         <v>1</v>
@@ -3407,19 +3474,19 @@
         <v>0</v>
       </c>
       <c r="V20" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA20" s="1">
         <v>0</v>
@@ -3427,8 +3494,11 @@
       <c r="AB20" s="1">
         <v>0</v>
       </c>
+      <c r="AC20" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>211002001</v>
       </c>
@@ -3445,13 +3515,13 @@
         <v>1</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -3460,13 +3530,13 @@
         <v>0</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N21" s="1">
         <v>0</v>
@@ -3481,10 +3551,10 @@
         <v>2</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T21" s="1">
         <v>1</v>
@@ -3493,19 +3563,19 @@
         <v>0</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA21" s="1">
         <v>0</v>
@@ -3513,8 +3583,11 @@
       <c r="AB21" s="1">
         <v>0</v>
       </c>
+      <c r="AC21" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>216001001</v>
       </c>
@@ -3531,28 +3604,28 @@
         <v>1</v>
       </c>
       <c r="F22" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="20" t="s">
-        <v>268</v>
-      </c>
       <c r="L22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N22" s="1">
         <v>0</v>
@@ -3567,10 +3640,10 @@
         <v>2</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T22" s="1">
         <v>1</v>
@@ -3579,19 +3652,19 @@
         <v>0</v>
       </c>
       <c r="V22" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA22" s="1">
         <v>0</v>
@@ -3599,8 +3672,11 @@
       <c r="AB22" s="1">
         <v>0</v>
       </c>
+      <c r="AC22" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:28" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>59260001</v>
       </c>
@@ -3618,7 +3694,7 @@
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1">
@@ -3628,52 +3704,52 @@
         <v>0</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>1</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>1</v>
-      </c>
-      <c r="R23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="S23" s="1" t="s">
+      <c r="T23" s="1">
+        <v>1</v>
+      </c>
+      <c r="U23" s="12">
+        <v>0</v>
+      </c>
+      <c r="V23" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="W23" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="T23" s="1">
-        <v>1</v>
-      </c>
-      <c r="U23" s="12">
-        <v>0</v>
-      </c>
-      <c r="V23" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="W23" s="1" t="s">
+      <c r="X23" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="X23" s="1" t="s">
+      <c r="Y23" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="Y23" s="1" t="s">
+      <c r="Z23" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="AA23" s="1">
         <v>59130001</v>
@@ -3681,8 +3757,11 @@
       <c r="AB23" s="1">
         <v>0</v>
       </c>
+      <c r="AC23" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A24" s="10">
         <v>25010001</v>
       </c>
@@ -3699,14 +3778,14 @@
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="H24" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>60</v>
-      </c>
       <c r="I24" s="10">
         <v>0</v>
       </c>
@@ -3714,13 +3793,13 @@
         <v>0</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N24" s="10">
         <v>0</v>
@@ -3735,10 +3814,10 @@
         <v>1</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S24" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T24" s="10">
         <v>1</v>
@@ -3747,19 +3826,19 @@
         <v>0</v>
       </c>
       <c r="V24" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W24" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X24" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z24" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA24" s="10">
         <v>54150001</v>
@@ -3767,8 +3846,11 @@
       <c r="AB24" s="10">
         <v>0</v>
       </c>
+      <c r="AC24" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
         <v>95000101</v>
       </c>
@@ -3785,13 +3867,13 @@
         <v>1</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I25" s="13">
         <v>0</v>
@@ -3800,52 +3882,52 @@
         <v>0</v>
       </c>
       <c r="K25" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="L25" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="L25" s="13" t="s">
+      <c r="M25" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="M25" s="13" t="s">
+      <c r="N25" s="13">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13">
+        <v>0</v>
+      </c>
+      <c r="P25" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>2</v>
+      </c>
+      <c r="R25" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="N25" s="13">
-        <v>0</v>
-      </c>
-      <c r="O25" s="13">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>2</v>
-      </c>
-      <c r="R25" s="13" t="s">
+      <c r="S25" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="S25" s="13" t="s">
+      <c r="T25" s="13">
+        <v>1</v>
+      </c>
+      <c r="U25" s="13">
+        <v>1</v>
+      </c>
+      <c r="V25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="W25" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="T25" s="13">
-        <v>1</v>
-      </c>
-      <c r="U25" s="13">
-        <v>1</v>
-      </c>
-      <c r="V25" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="W25" s="13" t="s">
+      <c r="X25" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="X25" s="13" t="s">
+      <c r="Y25" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="Y25" s="13" t="s">
+      <c r="Z25" s="13" t="s">
         <v>148</v>
-      </c>
-      <c r="Z25" s="13" t="s">
-        <v>149</v>
       </c>
       <c r="AA25" s="13">
         <v>85001100</v>
@@ -3853,8 +3935,11 @@
       <c r="AB25" s="13">
         <v>0</v>
       </c>
+      <c r="AC25" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
         <v>95100101</v>
       </c>
@@ -3871,13 +3956,13 @@
         <v>1</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I26" s="13">
         <v>0</v>
@@ -3886,13 +3971,13 @@
         <v>0</v>
       </c>
       <c r="K26" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="L26" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="L26" s="13" t="s">
+      <c r="M26" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="N26" s="13">
         <v>0</v>
@@ -3907,40 +3992,43 @@
         <v>2</v>
       </c>
       <c r="R26" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="S26" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="S26" s="13" t="s">
+      <c r="T26" s="13">
+        <v>1</v>
+      </c>
+      <c r="U26" s="13">
+        <v>2</v>
+      </c>
+      <c r="V26" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="W26" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="T26" s="13">
-        <v>1</v>
-      </c>
-      <c r="U26" s="13">
-        <v>2</v>
-      </c>
-      <c r="V26" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="W26" s="13" t="s">
+      <c r="X26" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="X26" s="13" t="s">
+      <c r="Y26" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="Y26" s="13" t="s">
+      <c r="Z26" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="Z26" s="13" t="s">
-        <v>158</v>
-      </c>
       <c r="AA26" s="13">
         <v>0</v>
       </c>
       <c r="AB26" s="13">
         <v>0</v>
       </c>
+      <c r="AC26" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
         <v>95200101</v>
       </c>
@@ -3957,14 +4045,14 @@
         <v>1</v>
       </c>
       <c r="F27" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>65</v>
-      </c>
       <c r="I27" s="13">
         <v>0</v>
       </c>
@@ -3972,13 +4060,13 @@
         <v>0</v>
       </c>
       <c r="K27" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="L27" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="L27" s="13" t="s">
+      <c r="M27" s="13" t="s">
         <v>160</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>161</v>
       </c>
       <c r="N27" s="13">
         <v>0</v>
@@ -3993,10 +4081,10 @@
         <v>2</v>
       </c>
       <c r="R27" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="S27" s="13" t="s">
         <v>162</v>
-      </c>
-      <c r="S27" s="13" t="s">
-        <v>163</v>
       </c>
       <c r="T27" s="13">
         <v>1</v>
@@ -4005,28 +4093,31 @@
         <v>4</v>
       </c>
       <c r="V27" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W27" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="X27" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="X27" s="13" t="s">
+      <c r="Y27" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="Y27" s="13" t="s">
+      <c r="Z27" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="Z27" s="13" t="s">
-        <v>167</v>
-      </c>
       <c r="AA27" s="13">
         <v>0</v>
       </c>
       <c r="AB27" s="13">
         <v>0</v>
       </c>
+      <c r="AC27" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>20001</v>
       </c>
@@ -4043,13 +4134,13 @@
         <v>1</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
@@ -4058,13 +4149,13 @@
         <v>720001</v>
       </c>
       <c r="K28" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="L28" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="L28" s="13" t="s">
+      <c r="M28" s="13" t="s">
         <v>181</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>182</v>
       </c>
       <c r="N28" s="2">
         <v>0</v>
@@ -4079,31 +4170,31 @@
         <v>2</v>
       </c>
       <c r="R28" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="S28" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="S28" s="13" t="s">
+      <c r="T28" s="2">
+        <v>1</v>
+      </c>
+      <c r="U28" s="2">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W28" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="T28" s="2">
-        <v>1</v>
-      </c>
-      <c r="U28" s="2">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W28" s="13" t="s">
+      <c r="X28" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="X28" s="13" t="s">
+      <c r="Y28" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="Y28" s="13" t="s">
+      <c r="Z28" s="13" t="s">
         <v>187</v>
-      </c>
-      <c r="Z28" s="13" t="s">
-        <v>188</v>
       </c>
       <c r="AA28" s="2">
         <v>0</v>
@@ -4111,8 +4202,11 @@
       <c r="AB28" s="2">
         <v>820001</v>
       </c>
+      <c r="AC28" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>20011</v>
       </c>
@@ -4129,10 +4223,10 @@
         <v>1</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
@@ -4141,31 +4235,31 @@
         <v>720011</v>
       </c>
       <c r="K29" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="L29" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="L29" s="13" t="s">
+      <c r="M29" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="M29" s="13" t="s">
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>2</v>
+      </c>
+      <c r="R29" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="N29" s="2">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="2">
-        <v>2</v>
-      </c>
-      <c r="R29" s="13" t="s">
+      <c r="S29" s="13" t="s">
         <v>203</v>
-      </c>
-      <c r="S29" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="T29" s="2">
         <v>1</v>
@@ -4174,19 +4268,19 @@
         <v>3</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W29" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="X29" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="X29" s="13" t="s">
+      <c r="Y29" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="Y29" s="13" t="s">
+      <c r="Z29" s="13" t="s">
         <v>207</v>
-      </c>
-      <c r="Z29" s="13" t="s">
-        <v>208</v>
       </c>
       <c r="AA29" s="2">
         <v>0</v>
@@ -4194,8 +4288,11 @@
       <c r="AB29" s="2">
         <v>820011</v>
       </c>
+      <c r="AC29" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>20012</v>
       </c>
@@ -4212,14 +4309,14 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="I30" s="2">
         <v>0</v>
       </c>
@@ -4227,13 +4324,13 @@
         <v>0</v>
       </c>
       <c r="K30" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="L30" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="M30" s="13" t="s">
         <v>210</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>211</v>
       </c>
       <c r="N30" s="2">
         <v>0</v>
@@ -4248,10 +4345,10 @@
         <v>2</v>
       </c>
       <c r="R30" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="S30" s="13" t="s">
         <v>212</v>
-      </c>
-      <c r="S30" s="13" t="s">
-        <v>213</v>
       </c>
       <c r="T30" s="2">
         <v>1</v>
@@ -4260,19 +4357,19 @@
         <v>3</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W30" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="X30" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="X30" s="13" t="s">
+      <c r="Y30" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="Y30" s="13" t="s">
+      <c r="Z30" s="13" t="s">
         <v>216</v>
-      </c>
-      <c r="Z30" s="13" t="s">
-        <v>217</v>
       </c>
       <c r="AA30" s="2">
         <v>0</v>
@@ -4280,8 +4377,11 @@
       <c r="AB30" s="2">
         <v>820011</v>
       </c>
+      <c r="AC30" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>20021</v>
       </c>
@@ -4298,76 +4398,79 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0</v>
-      </c>
-      <c r="K31" s="13" t="s">
+      <c r="L31" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="L31" s="13" t="s">
+      <c r="M31" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="M31" s="13" t="s">
+      <c r="N31" s="2">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>2</v>
+      </c>
+      <c r="R31" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="N31" s="2">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>2</v>
-      </c>
-      <c r="R31" s="13" t="s">
+      <c r="S31" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="S31" s="13" t="s">
+      <c r="T31" s="2">
+        <v>1</v>
+      </c>
+      <c r="U31" s="2">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W31" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="T31" s="2">
-        <v>1</v>
-      </c>
-      <c r="U31" s="2">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W31" s="13" t="s">
+      <c r="X31" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X31" s="13" t="s">
+      <c r="Y31" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="Y31" s="13" t="s">
+      <c r="Z31" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="Z31" s="13" t="s">
-        <v>230</v>
-      </c>
       <c r="AA31" s="2">
         <v>0</v>
       </c>
       <c r="AB31" s="2">
         <v>0</v>
       </c>
+      <c r="AC31" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>20022</v>
       </c>
@@ -4384,13 +4487,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G32" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="I32" s="2">
         <v>2</v>
@@ -4399,61 +4502,64 @@
         <v>720022</v>
       </c>
       <c r="K32" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="L32" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="L32" s="13" t="s">
+      <c r="M32" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="M32" s="13" t="s">
+      <c r="N32" s="2">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>2</v>
+      </c>
+      <c r="R32" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="N32" s="2">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>1</v>
-      </c>
-      <c r="P32" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>2</v>
-      </c>
-      <c r="R32" s="13" t="s">
+      <c r="S32" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="S32" s="13" t="s">
+      <c r="T32" s="2">
+        <v>1</v>
+      </c>
+      <c r="U32" s="2">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W32" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="T32" s="2">
-        <v>1</v>
-      </c>
-      <c r="U32" s="2">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W32" s="13" t="s">
+      <c r="X32" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X32" s="13" t="s">
+      <c r="Y32" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="Y32" s="13" t="s">
+      <c r="Z32" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="Z32" s="13" t="s">
-        <v>241</v>
-      </c>
       <c r="AA32" s="2">
         <v>0</v>
       </c>
       <c r="AB32" s="2">
         <v>0</v>
       </c>
+      <c r="AC32" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>20023</v>
       </c>
@@ -4470,13 +4576,13 @@
         <v>1</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="I33" s="2">
         <v>2</v>
@@ -4485,13 +4591,13 @@
         <v>720023</v>
       </c>
       <c r="K33" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="L33" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="L33" s="13" t="s">
+      <c r="M33" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="M33" s="13" t="s">
-        <v>244</v>
       </c>
       <c r="N33" s="2">
         <v>0</v>
@@ -4506,40 +4612,43 @@
         <v>2</v>
       </c>
       <c r="R33" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="S33" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="S33" s="13" t="s">
+      <c r="T33" s="2">
+        <v>1</v>
+      </c>
+      <c r="U33" s="2">
+        <v>2</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W33" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="T33" s="2">
-        <v>1</v>
-      </c>
-      <c r="U33" s="2">
-        <v>2</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W33" s="13" t="s">
+      <c r="X33" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="X33" s="13" t="s">
+      <c r="Y33" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="Y33" s="13" t="s">
+      <c r="Z33" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="Z33" s="13" t="s">
-        <v>250</v>
-      </c>
       <c r="AA33" s="2">
         <v>0</v>
       </c>
       <c r="AB33" s="2">
         <v>0</v>
       </c>
+      <c r="AC33" s="21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>20031</v>
       </c>
@@ -4556,14 +4665,14 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="I34" s="2">
         <v>0</v>
       </c>
@@ -4571,31 +4680,31 @@
         <v>0</v>
       </c>
       <c r="K34" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="L34" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="L34" s="13" t="s">
+      <c r="M34" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="M34" s="13" t="s">
+      <c r="N34" s="2">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>2</v>
+      </c>
+      <c r="R34" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="N34" s="2">
-        <v>0</v>
-      </c>
-      <c r="O34" s="2">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="2">
-        <v>2</v>
-      </c>
-      <c r="R34" s="13" t="s">
+      <c r="S34" s="13" t="s">
         <v>258</v>
-      </c>
-      <c r="S34" s="13" t="s">
-        <v>259</v>
       </c>
       <c r="T34" s="2">
         <v>1</v>
@@ -4604,24 +4713,27 @@
         <v>4</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W34" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="X34" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="X34" s="13" t="s">
+      <c r="Y34" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="Y34" s="13" t="s">
+      <c r="Z34" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="Z34" s="13" t="s">
-        <v>263</v>
-      </c>
       <c r="AA34" s="2">
         <v>0</v>
       </c>
       <c r="AB34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="21">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC69110-B2BF-42C9-8870-20EFEFBA7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376BBF53-8FE4-4398-825B-B556FFB06360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="291">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1222,6 +1222,41 @@
   </si>
   <si>
     <t>召唤物id（默认召唤1个）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920041</t>
+  </si>
+  <si>
+    <t>1:2920041</t>
+  </si>
+  <si>
+    <t>1:3920041</t>
+  </si>
+  <si>
+    <t>1:4920041</t>
+  </si>
+  <si>
+    <t>1:5920041</t>
+  </si>
+  <si>
+    <t>1:6920041</t>
+  </si>
+  <si>
+    <t>1:7920041</t>
+  </si>
+  <si>
+    <t>1:8920041</t>
+  </si>
+  <si>
+    <t>1:9920041</t>
+  </si>
+  <si>
+    <t>召唤守卫</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤一个不承伤只会普攻的守卫，继承自身100%攻击</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1783,7 +1818,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -4737,6 +4772,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>20041</v>
+      </c>
+      <c r="B35" s="2">
+        <v>920041</v>
+      </c>
+      <c r="C35" s="2">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>1</v>
+      </c>
+      <c r="R35" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="S35" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="T35" s="2">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W35" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="X35" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y35" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z35" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="21">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376BBF53-8FE4-4398-825B-B556FFB06360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DFB51F-6E53-4BBC-9AE2-58B024B344F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4780,7 +4780,7 @@
         <v>920041</v>
       </c>
       <c r="C35" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DFB51F-6E53-4BBC-9AE2-58B024B344F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C637EEE-34E9-4FC6-8AAC-FB0E28B33CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
+    <sheet name="自动释放时机备注" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$27</definedName>
@@ -56,27 +57,6 @@
 4-玩家被动技能
 5-玩家主动技能
 6-由特殊方式触发的主动技能</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="1" shapeId="0" xr:uid="{051313A9-A9F3-47D0-8025-83ECAEF4180F}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1 攻击命中造成伤害前
-2 攻击命中造成伤害后
-3 受到攻击伤害前
-4 受到攻击伤害后
-5 击杀目标前
-6 击杀目标后
-7 自身死亡前
-8 自身死亡后</t>
         </r>
       </text>
     </comment>
@@ -282,7 +262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="310">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1257,6 +1237,82 @@
   </si>
   <si>
     <t>召唤一个不承伤只会普攻的守卫，继承自身100%攻击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻攻击命中造成伤害前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻攻击命中造成伤害后</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击伤害前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>预留</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中造成伤害前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能变更</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>动作技能动作开始前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击伤害后</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀目标前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀目标后</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身死亡前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>非动作技能释放技能前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>非动作技能释放技能后</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中造成伤害后</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果命中前</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果命中后</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>动作技能动作结束后</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1264,7 +1320,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1371,6 +1427,22 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1460,7 +1532,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1520,6 +1592,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4531,7 +4612,7 @@
         <v>231</v>
       </c>
       <c r="I32" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2">
         <v>720022</v>
@@ -4620,7 +4701,7 @@
         <v>251</v>
       </c>
       <c r="I33" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J33" s="2">
         <v>720023</v>
@@ -4867,4 +4948,170 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C36878A-E4DD-44BC-97EB-F8B80B2F3EC3}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="4" width="9" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="22">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="22">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="22">
+        <v>5</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="22">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="22">
+        <v>8</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="22">
+        <v>9</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="22">
+        <v>10</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="22">
+        <v>11</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="22">
+        <v>12</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="22">
+        <v>13</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="22">
+        <v>14</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="22">
+        <v>15</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="22">
+        <v>16</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="22">
+        <v>17</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="22">
+        <v>18</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C637EEE-34E9-4FC6-8AAC-FB0E28B33CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C165E5C-8FFF-4F3C-A8E0-F117BFDE82CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -153,6 +153,7 @@
 2 自身单体
 3 目标为中心范围
 4 自身为中心范围
+5 以固定点为中心范围
 </t>
         </r>
       </text>
@@ -262,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="316">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1313,6 +1314,30 @@
   </si>
   <si>
     <t>动作技能动作结束后</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能持续时间（毫秒）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害\效果生效间隔（毫秒）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>interval</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:11920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:10920001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1532,7 +1557,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1601,6 +1626,15 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1899,7 +1933,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AE35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -1927,15 +1961,17 @@
     <col min="27" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="15.875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="19.75" style="21" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="2"/>
+    <col min="30" max="30" width="20.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="24.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2023,8 +2059,14 @@
       <c r="AC2" s="21" t="s">
         <v>54</v>
       </c>
+      <c r="AD2" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE2" s="21" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2112,8 +2154,14 @@
       <c r="AC3" s="21" t="s">
         <v>278</v>
       </c>
+      <c r="AD3" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="AE3" s="25" t="s">
+        <v>313</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -2201,8 +2249,14 @@
       <c r="AC4" s="21" t="s">
         <v>279</v>
       </c>
+      <c r="AD4" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="AE4" s="26" t="s">
+        <v>311</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10101</v>
       </c>
@@ -2288,8 +2342,14 @@
       <c r="AC5" s="21">
         <v>0</v>
       </c>
+      <c r="AD5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE5" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10102</v>
       </c>
@@ -2375,8 +2435,14 @@
       <c r="AC6" s="21">
         <v>0</v>
       </c>
+      <c r="AD6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE6" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10201</v>
       </c>
@@ -2462,8 +2528,14 @@
       <c r="AC7" s="21">
         <v>0</v>
       </c>
+      <c r="AD7" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE7" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10202</v>
       </c>
@@ -2549,8 +2621,14 @@
       <c r="AC8" s="21">
         <v>0</v>
       </c>
+      <c r="AD8" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE8" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10301</v>
       </c>
@@ -2636,8 +2714,14 @@
       <c r="AC9" s="21">
         <v>0</v>
       </c>
+      <c r="AD9" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE9" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10302</v>
       </c>
@@ -2723,8 +2807,14 @@
       <c r="AC10" s="21">
         <v>0</v>
       </c>
+      <c r="AD10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE10" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>201001011</v>
       </c>
@@ -2812,8 +2902,14 @@
       <c r="AC11" s="21">
         <v>0</v>
       </c>
+      <c r="AD11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>201002011</v>
       </c>
@@ -2901,8 +2997,14 @@
       <c r="AC12" s="21">
         <v>0</v>
       </c>
+      <c r="AD12" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>201004011</v>
       </c>
@@ -2990,8 +3092,14 @@
       <c r="AC13" s="21">
         <v>0</v>
       </c>
+      <c r="AD13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE13" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>214001011</v>
       </c>
@@ -3079,8 +3187,14 @@
       <c r="AC14" s="21">
         <v>0</v>
       </c>
+      <c r="AD14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE14" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>203001001</v>
       </c>
@@ -3168,8 +3282,14 @@
       <c r="AC15" s="21">
         <v>0</v>
       </c>
+      <c r="AD15" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE15" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>203002011</v>
       </c>
@@ -3257,8 +3377,14 @@
       <c r="AC16" s="21">
         <v>0</v>
       </c>
+      <c r="AD16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE16" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>203003001</v>
       </c>
@@ -3346,8 +3472,14 @@
       <c r="AC17" s="21">
         <v>0</v>
       </c>
+      <c r="AD17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE17" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>204001001</v>
       </c>
@@ -3435,8 +3567,14 @@
       <c r="AC18" s="21">
         <v>0</v>
       </c>
+      <c r="AD18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE18" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>204002001</v>
       </c>
@@ -3524,8 +3662,14 @@
       <c r="AC19" s="21">
         <v>0</v>
       </c>
+      <c r="AD19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>211001001</v>
       </c>
@@ -3613,8 +3757,14 @@
       <c r="AC20" s="21">
         <v>0</v>
       </c>
+      <c r="AD20" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE20" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>211002001</v>
       </c>
@@ -3702,8 +3852,14 @@
       <c r="AC21" s="21">
         <v>0</v>
       </c>
+      <c r="AD21" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE21" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>216001001</v>
       </c>
@@ -3791,8 +3947,14 @@
       <c r="AC22" s="21">
         <v>0</v>
       </c>
+      <c r="AD22" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE22" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>59260001</v>
       </c>
@@ -3876,8 +4038,14 @@
       <c r="AC23" s="21">
         <v>0</v>
       </c>
+      <c r="AD23" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A24" s="10">
         <v>25010001</v>
       </c>
@@ -3965,8 +4133,14 @@
       <c r="AC24" s="21">
         <v>0</v>
       </c>
+      <c r="AD24" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
         <v>95000101</v>
       </c>
@@ -4054,8 +4228,14 @@
       <c r="AC25" s="21">
         <v>0</v>
       </c>
+      <c r="AD25" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="27" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
         <v>95100101</v>
       </c>
@@ -4143,8 +4323,14 @@
       <c r="AC26" s="21">
         <v>0</v>
       </c>
+      <c r="AD26" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE26" s="27" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
         <v>95200101</v>
       </c>
@@ -4232,8 +4418,14 @@
       <c r="AC27" s="21">
         <v>0</v>
       </c>
+      <c r="AD27" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE27" s="27" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>20001</v>
       </c>
@@ -4280,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="P28" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q28" s="2">
         <v>2</v>
@@ -4321,8 +4513,14 @@
       <c r="AC28" s="21">
         <v>0</v>
       </c>
+      <c r="AD28" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="AE28" s="27" t="s">
+        <v>314</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>20011</v>
       </c>
@@ -4407,8 +4605,14 @@
       <c r="AC29" s="21">
         <v>0</v>
       </c>
+      <c r="AD29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE29" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>20012</v>
       </c>
@@ -4496,8 +4700,14 @@
       <c r="AC30" s="21">
         <v>0</v>
       </c>
+      <c r="AD30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE30" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>20021</v>
       </c>
@@ -4585,8 +4795,14 @@
       <c r="AC31" s="21">
         <v>0</v>
       </c>
+      <c r="AD31" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE31" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>20022</v>
       </c>
@@ -4674,8 +4890,14 @@
       <c r="AC32" s="21">
         <v>0</v>
       </c>
+      <c r="AD32" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE32" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>20023</v>
       </c>
@@ -4763,8 +4985,14 @@
       <c r="AC33" s="21">
         <v>0</v>
       </c>
+      <c r="AD33" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE33" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>20031</v>
       </c>
@@ -4852,8 +5080,14 @@
       <c r="AC34" s="21">
         <v>0</v>
       </c>
+      <c r="AD34" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE34" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>20041</v>
       </c>
@@ -4940,6 +5174,12 @@
       </c>
       <c r="AC35" s="21">
         <v>1</v>
+      </c>
+      <c r="AD35" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE35" s="21" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C165E5C-8FFF-4F3C-A8E0-F117BFDE82CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6C3557-1E72-443D-9AB4-2A0A8638B0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
     <sheet name="自动释放时机备注" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -263,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="326">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -508,10 +508,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>骷髅怪等级4远程</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>蜘蛛怪等级1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -832,22 +828,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>0:550</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:525</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:435</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:450</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>炎域</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1182,10 +1162,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>0:400</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>爆炎冲刺_升龙击</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1321,10 +1297,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>技能伤害\效果生效间隔（毫秒）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>duration</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1338,6 +1310,72 @@
   </si>
   <si>
     <t>1:10920001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害或效果生效间隔（毫秒）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅射手1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅射手2</t>
+  </si>
+  <si>
+    <t>骷髅射手3</t>
+  </si>
+  <si>
+    <t>狼等级3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>女妖精英</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血鬼3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:865</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:625</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:1040</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:830</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:660</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:665</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:785</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:1035</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:1080</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1933,7 +1971,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AE35"/>
+  <dimension ref="A1:AE41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -1991,25 +2029,25 @@
         <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I2" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="J2" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="J2" s="19" t="s">
-        <v>168</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>54</v>
@@ -2024,10 +2062,10 @@
         <v>54</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>54</v>
@@ -2039,16 +2077,16 @@
         <v>61</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>55</v>
@@ -2060,10 +2098,10 @@
         <v>54</v>
       </c>
       <c r="AD2" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AE2" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
@@ -2071,19 +2109,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>5</v>
@@ -2092,10 +2130,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>7</v>
@@ -2131,7 +2169,7 @@
         <v>60</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>29</v>
@@ -2152,13 +2190,13 @@
         <v>14</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AD3" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="AE3" s="25" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
@@ -2166,13 +2204,13 @@
         <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>46</v>
@@ -2187,10 +2225,10 @@
         <v>18</v>
       </c>
       <c r="I4" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="19" t="s">
         <v>169</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>170</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>19</v>
@@ -2226,7 +2264,7 @@
         <v>62</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="W4" s="15" t="s">
         <v>30</v>
@@ -2247,13 +2285,13 @@
         <v>26</v>
       </c>
       <c r="AC4" s="21" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AD4" s="26" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AE4" s="26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
@@ -2286,13 +2324,13 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="N5" s="6">
         <v>0</v>
@@ -2307,31 +2345,31 @@
         <v>2</v>
       </c>
       <c r="R5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="S5" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6">
+        <v>1</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="W5" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="T5" s="6">
-        <v>1</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="Y5" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="Z5" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AA5" s="6">
         <v>0</v>
@@ -2379,13 +2417,13 @@
         <v>0</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="N6" s="6">
         <v>0</v>
@@ -2400,31 +2438,31 @@
         <v>2</v>
       </c>
       <c r="R6" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="W6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="T6" s="6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="V6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="AA6" s="6">
         <v>0</v>
@@ -2472,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="N7" s="6">
         <v>0</v>
@@ -2493,31 +2531,31 @@
         <v>2</v>
       </c>
       <c r="R7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="S7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="T7" s="6">
+        <v>1</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="W7" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="T7" s="6">
-        <v>1</v>
-      </c>
-      <c r="U7" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="V7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="AA7" s="6">
         <v>0</v>
@@ -2565,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="N8" s="6">
         <v>0</v>
@@ -2586,31 +2624,31 @@
         <v>2</v>
       </c>
       <c r="R8" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="S8" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="W8" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="6">
-        <v>1</v>
-      </c>
-      <c r="U8" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="V8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="AA8" s="6">
         <v>0</v>
@@ -2658,13 +2696,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="N9" s="6">
         <v>0</v>
@@ -2679,31 +2717,31 @@
         <v>2</v>
       </c>
       <c r="R9" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="S9" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="T9" s="6">
+        <v>1</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="W9" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="T9" s="6">
-        <v>1</v>
-      </c>
-      <c r="U9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="V9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Z9" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="AA9" s="6">
         <v>0</v>
@@ -2751,13 +2789,13 @@
         <v>0</v>
       </c>
       <c r="K10" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="N10" s="6">
         <v>0</v>
@@ -2772,31 +2810,31 @@
         <v>2</v>
       </c>
       <c r="R10" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="S10" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="V10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="W10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="T10" s="6">
-        <v>1</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W10" s="6" t="s">
+      <c r="X10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Z10" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="AA10" s="6">
         <v>0</v>
@@ -2846,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N11" s="1">
         <v>0</v>
@@ -2870,7 +2908,7 @@
         <v>27</v>
       </c>
       <c r="S11" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T11" s="1">
         <v>1</v>
@@ -2879,19 +2917,19 @@
         <v>0</v>
       </c>
       <c r="V11" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA11" s="1">
         <v>0</v>
@@ -2941,13 +2979,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N12" s="1">
         <v>0</v>
@@ -2965,7 +3003,7 @@
         <v>27</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T12" s="1">
         <v>1</v>
@@ -2974,19 +3012,19 @@
         <v>0</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
@@ -3006,7 +3044,7 @@
     </row>
     <row r="13" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>201004011</v>
+        <v>201003001</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
@@ -3021,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>71</v>
+        <v>311</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>56</v>
@@ -3036,13 +3074,13 @@
         <v>0</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>175</v>
+        <v>317</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
@@ -3060,7 +3098,7 @@
         <v>27</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T13" s="1">
         <v>1</v>
@@ -3069,19 +3107,19 @@
         <v>0</v>
       </c>
       <c r="V13" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
@@ -3101,7 +3139,7 @@
     </row>
     <row r="14" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>214001011</v>
+        <v>201004011</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -3116,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>72</v>
+        <v>310</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>56</v>
@@ -3131,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N14" s="1">
         <v>0</v>
@@ -3155,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T14" s="1">
         <v>1</v>
@@ -3164,19 +3202,19 @@
         <v>0</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA14" s="1">
         <v>0</v>
@@ -3196,7 +3234,7 @@
     </row>
     <row r="15" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>203001001</v>
+        <v>201005001</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
@@ -3211,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>56</v>
@@ -3226,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>173</v>
+        <v>318</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
@@ -3250,7 +3288,7 @@
         <v>27</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T15" s="1">
         <v>1</v>
@@ -3259,19 +3297,19 @@
         <v>0</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA15" s="1">
         <v>0</v>
@@ -3291,7 +3329,7 @@
     </row>
     <row r="16" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>203002011</v>
+        <v>201006001</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
@@ -3306,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>56</v>
@@ -3321,13 +3359,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>176</v>
+        <v>318</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N16" s="1">
         <v>0</v>
@@ -3345,7 +3383,7 @@
         <v>27</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T16" s="1">
         <v>1</v>
@@ -3354,19 +3392,19 @@
         <v>0</v>
       </c>
       <c r="V16" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA16" s="1">
         <v>0</v>
@@ -3386,7 +3424,7 @@
     </row>
     <row r="17" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>203003001</v>
+        <v>214001011</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
@@ -3401,7 +3439,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>269</v>
+        <v>71</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>56</v>
@@ -3416,13 +3454,13 @@
         <v>0</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
@@ -3440,7 +3478,7 @@
         <v>27</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T17" s="1">
         <v>1</v>
@@ -3449,19 +3487,19 @@
         <v>0</v>
       </c>
       <c r="V17" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA17" s="1">
         <v>0</v>
@@ -3481,7 +3519,7 @@
     </row>
     <row r="18" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>204001001</v>
+        <v>203001001</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -3496,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>56</v>
@@ -3511,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>175</v>
+        <v>319</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N18" s="1">
         <v>0</v>
@@ -3535,7 +3573,7 @@
         <v>27</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T18" s="1">
         <v>1</v>
@@ -3544,19 +3582,19 @@
         <v>0</v>
       </c>
       <c r="V18" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA18" s="1">
         <v>0</v>
@@ -3576,7 +3614,7 @@
     </row>
     <row r="19" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>204002001</v>
+        <v>203002011</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
@@ -3591,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>56</v>
@@ -3606,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N19" s="1">
         <v>0</v>
@@ -3630,7 +3668,7 @@
         <v>27</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T19" s="1">
         <v>1</v>
@@ -3639,19 +3677,19 @@
         <v>0</v>
       </c>
       <c r="V19" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y19" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA19" s="1">
         <v>0</v>
@@ -3671,7 +3709,7 @@
     </row>
     <row r="20" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>211001001</v>
+        <v>203003001</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
@@ -3686,7 +3724,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>56</v>
@@ -3701,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>173</v>
+        <v>319</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N20" s="1">
         <v>0</v>
@@ -3725,7 +3763,7 @@
         <v>27</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T20" s="1">
         <v>1</v>
@@ -3734,19 +3772,19 @@
         <v>0</v>
       </c>
       <c r="V20" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA20" s="1">
         <v>0</v>
@@ -3766,7 +3804,7 @@
     </row>
     <row r="21" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>211002001</v>
+        <v>204001001</v>
       </c>
       <c r="B21" s="1">
         <v>0</v>
@@ -3781,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>56</v>
@@ -3796,13 +3834,13 @@
         <v>0</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>173</v>
+        <v>321</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N21" s="1">
         <v>0</v>
@@ -3820,7 +3858,7 @@
         <v>27</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T21" s="1">
         <v>1</v>
@@ -3829,19 +3867,19 @@
         <v>0</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA21" s="1">
         <v>0</v>
@@ -3861,7 +3899,7 @@
     </row>
     <row r="22" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>216001001</v>
+        <v>204002001</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
@@ -3891,13 +3929,13 @@
         <v>0</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N22" s="1">
         <v>0</v>
@@ -3915,7 +3953,7 @@
         <v>27</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T22" s="1">
         <v>1</v>
@@ -3924,19 +3962,19 @@
         <v>0</v>
       </c>
       <c r="V22" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA22" s="1">
         <v>0</v>
@@ -3956,1048 +3994,1051 @@
     </row>
     <row r="23" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
+        <v>204003001</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1</v>
+      </c>
+      <c r="P23" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>2</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T23" s="1">
+        <v>1</v>
+      </c>
+      <c r="U23" s="12">
+        <v>0</v>
+      </c>
+      <c r="V23" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>208001001</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>1</v>
+      </c>
+      <c r="P24" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>2</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T24" s="1">
+        <v>1</v>
+      </c>
+      <c r="U24" s="12">
+        <v>0</v>
+      </c>
+      <c r="V24" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>211001001</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1</v>
+      </c>
+      <c r="P25" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>2</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T25" s="1">
+        <v>1</v>
+      </c>
+      <c r="U25" s="12">
+        <v>0</v>
+      </c>
+      <c r="V25" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>211002001</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>1</v>
+      </c>
+      <c r="P26" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>2</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T26" s="1">
+        <v>1</v>
+      </c>
+      <c r="U26" s="12">
+        <v>0</v>
+      </c>
+      <c r="V26" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE26" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>213003001</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1</v>
+      </c>
+      <c r="P27" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>2</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T27" s="1">
+        <v>1</v>
+      </c>
+      <c r="U27" s="12">
+        <v>0</v>
+      </c>
+      <c r="V27" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE27" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>216001001</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>1</v>
+      </c>
+      <c r="P28" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>2</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T28" s="1">
+        <v>1</v>
+      </c>
+      <c r="U28" s="12">
+        <v>0</v>
+      </c>
+      <c r="V28" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE28" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>59260001</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B29" s="1">
         <v>3592200</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C29" s="1">
         <v>4</v>
       </c>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="1" t="s">
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>1</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1" t="s">
+      <c r="T29" s="1">
+        <v>1</v>
+      </c>
+      <c r="U29" s="12">
+        <v>0</v>
+      </c>
+      <c r="V29" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W29" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="X29" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="Y29" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>1</v>
-      </c>
-      <c r="R23" s="1" t="s">
+      <c r="Z29" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="T23" s="1">
-        <v>1</v>
-      </c>
-      <c r="U23" s="12">
-        <v>0</v>
-      </c>
-      <c r="V23" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA23" s="1">
+      <c r="AA29" s="1">
         <v>59130001</v>
       </c>
-      <c r="AB23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE23" s="21" t="s">
+      <c r="AB29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE29" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A24" s="10">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A30" s="10">
         <v>25010001</v>
       </c>
-      <c r="B24" s="10">
-        <v>0</v>
-      </c>
-      <c r="C24" s="10">
-        <v>2</v>
-      </c>
-      <c r="D24" s="10">
-        <v>1</v>
-      </c>
-      <c r="E24" s="10">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="B30" s="10">
+        <v>0</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G30" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H30" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="10">
-        <v>0</v>
-      </c>
-      <c r="J24" s="10">
-        <v>0</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="N24" s="10">
-        <v>0</v>
-      </c>
-      <c r="O24" s="10">
-        <v>0</v>
-      </c>
-      <c r="P24" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="10">
-        <v>1</v>
-      </c>
-      <c r="R24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="S24" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="T24" s="10">
-        <v>1</v>
-      </c>
-      <c r="U24" s="10">
-        <v>0</v>
-      </c>
-      <c r="V24" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="W24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="X24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA24" s="10">
+      <c r="I30" s="10">
+        <v>0</v>
+      </c>
+      <c r="J30" s="10">
+        <v>0</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N30" s="10">
+        <v>0</v>
+      </c>
+      <c r="O30" s="10">
+        <v>0</v>
+      </c>
+      <c r="P30" s="10">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>1</v>
+      </c>
+      <c r="R30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="S30" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="T30" s="10">
+        <v>1</v>
+      </c>
+      <c r="U30" s="10">
+        <v>0</v>
+      </c>
+      <c r="V30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="W30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="X30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA30" s="10">
         <v>54150001</v>
       </c>
-      <c r="AB24" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE24" s="21" t="s">
+      <c r="AB30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE30" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="13">
+    <row r="31" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="13">
         <v>95000101</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B31" s="13">
         <v>95000101</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C31" s="13">
         <v>5</v>
       </c>
-      <c r="D25" s="13">
-        <v>1</v>
-      </c>
-      <c r="E25" s="13">
-        <v>1</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="D31" s="13">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13">
+        <v>1</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G31" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H31" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I25" s="13">
-        <v>0</v>
-      </c>
-      <c r="J25" s="13">
-        <v>0</v>
-      </c>
-      <c r="K25" s="13" t="s">
+      <c r="I31" s="13">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13">
+        <v>0</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="L31" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="L25" s="13" t="s">
+      <c r="M31" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="M25" s="13" t="s">
+      <c r="N31" s="13">
+        <v>0</v>
+      </c>
+      <c r="O31" s="13">
+        <v>0</v>
+      </c>
+      <c r="P31" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>2</v>
+      </c>
+      <c r="R31" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="N25" s="13">
-        <v>0</v>
-      </c>
-      <c r="O25" s="13">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>2</v>
-      </c>
-      <c r="R25" s="13" t="s">
+      <c r="S31" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="S25" s="13" t="s">
+      <c r="T31" s="13">
+        <v>1</v>
+      </c>
+      <c r="U31" s="13">
+        <v>1</v>
+      </c>
+      <c r="V31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="W31" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="T25" s="13">
-        <v>1</v>
-      </c>
-      <c r="U25" s="13">
-        <v>1</v>
-      </c>
-      <c r="V25" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="W25" s="13" t="s">
+      <c r="X31" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="X25" s="13" t="s">
+      <c r="Y31" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="Y25" s="13" t="s">
+      <c r="Z31" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="Z25" s="13" t="s">
+      <c r="AA31" s="13">
+        <v>85001100</v>
+      </c>
+      <c r="AB31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE31" s="27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="13">
+        <v>95100101</v>
+      </c>
+      <c r="B32" s="13">
+        <v>95100101</v>
+      </c>
+      <c r="C32" s="13">
+        <v>5</v>
+      </c>
+      <c r="D32" s="13">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13">
+        <v>1</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" s="13">
+        <v>0</v>
+      </c>
+      <c r="J32" s="13">
+        <v>0</v>
+      </c>
+      <c r="K32" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AA25" s="13">
-        <v>85001100</v>
-      </c>
-      <c r="AB25" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE25" s="27" t="s">
+      <c r="L32" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="N32" s="13">
+        <v>0</v>
+      </c>
+      <c r="O32" s="13">
+        <v>0</v>
+      </c>
+      <c r="P32" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="13">
+        <v>2</v>
+      </c>
+      <c r="R32" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="S32" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="T32" s="13">
+        <v>1</v>
+      </c>
+      <c r="U32" s="13">
+        <v>2</v>
+      </c>
+      <c r="V32" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="W32" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="X32" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y32" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z32" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE32" s="27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13">
-        <v>95100101</v>
-      </c>
-      <c r="B26" s="13">
-        <v>95100101</v>
-      </c>
-      <c r="C26" s="13">
+    <row r="33" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="13">
+        <v>95200101</v>
+      </c>
+      <c r="B33" s="13">
+        <v>95200101</v>
+      </c>
+      <c r="C33" s="13">
         <v>5</v>
       </c>
-      <c r="D26" s="13">
-        <v>1</v>
-      </c>
-      <c r="E26" s="13">
-        <v>1</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I26" s="13">
-        <v>0</v>
-      </c>
-      <c r="J26" s="13">
-        <v>0</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="N26" s="13">
-        <v>0</v>
-      </c>
-      <c r="O26" s="13">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>2</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="S26" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="T26" s="13">
-        <v>1</v>
-      </c>
-      <c r="U26" s="13">
-        <v>2</v>
-      </c>
-      <c r="V26" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="W26" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="X26" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y26" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z26" s="13" t="s">
+      <c r="D33" s="13">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="13">
+        <v>0</v>
+      </c>
+      <c r="J33" s="13">
+        <v>0</v>
+      </c>
+      <c r="K33" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AA26" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE26" s="27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="13">
-        <v>95200101</v>
-      </c>
-      <c r="B27" s="13">
-        <v>95200101</v>
-      </c>
-      <c r="C27" s="13">
-        <v>5</v>
-      </c>
-      <c r="D27" s="13">
-        <v>1</v>
-      </c>
-      <c r="E27" s="13">
-        <v>1</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="13">
-        <v>0</v>
-      </c>
-      <c r="J27" s="13">
-        <v>0</v>
-      </c>
-      <c r="K27" s="13" t="s">
+      <c r="L33" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="L27" s="13" t="s">
+      <c r="M33" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="M27" s="13" t="s">
+      <c r="N33" s="13">
+        <v>0</v>
+      </c>
+      <c r="O33" s="13">
+        <v>0</v>
+      </c>
+      <c r="P33" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>2</v>
+      </c>
+      <c r="R33" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="N27" s="13">
-        <v>0</v>
-      </c>
-      <c r="O27" s="13">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13">
+      <c r="S33" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="T33" s="13">
+        <v>1</v>
+      </c>
+      <c r="U33" s="13">
         <v>4</v>
       </c>
-      <c r="Q27" s="13">
-        <v>2</v>
-      </c>
-      <c r="R27" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="S27" s="13" t="s">
+      <c r="V33" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="W33" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="T27" s="13">
-        <v>1</v>
-      </c>
-      <c r="U27" s="13">
-        <v>4</v>
-      </c>
-      <c r="V27" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="W27" s="13" t="s">
+      <c r="X33" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="X27" s="13" t="s">
+      <c r="Y33" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="Y27" s="13" t="s">
+      <c r="Z33" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="Z27" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA27" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE27" s="27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>20001</v>
-      </c>
-      <c r="B28" s="2">
-        <v>920001</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
-        <v>720001</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="N28" s="2">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2">
-        <v>1</v>
-      </c>
-      <c r="P28" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>2</v>
-      </c>
-      <c r="R28" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="S28" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="T28" s="2">
-        <v>1</v>
-      </c>
-      <c r="U28" s="2">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W28" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="X28" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="Y28" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z28" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="2">
-        <v>820001</v>
-      </c>
-      <c r="AC28" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="AE28" s="27" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>20011</v>
-      </c>
-      <c r="B29" s="2">
-        <v>920011</v>
-      </c>
-      <c r="C29" s="2">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2">
-        <v>1</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2">
-        <v>720011</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="N29" s="2">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="2">
-        <v>2</v>
-      </c>
-      <c r="R29" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="S29" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="T29" s="2">
-        <v>1</v>
-      </c>
-      <c r="U29" s="2">
-        <v>3</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W29" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="X29" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y29" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z29" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="2">
-        <v>820011</v>
-      </c>
-      <c r="AC29" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE29" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>20012</v>
-      </c>
-      <c r="B30" s="2">
-        <v>920012</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="N30" s="2">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q30" s="2">
-        <v>2</v>
-      </c>
-      <c r="R30" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="S30" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="T30" s="2">
-        <v>1</v>
-      </c>
-      <c r="U30" s="2">
-        <v>3</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W30" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="X30" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y30" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z30" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="AA30" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="2">
-        <v>820011</v>
-      </c>
-      <c r="AC30" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE30" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>20021</v>
-      </c>
-      <c r="B31" s="2">
-        <v>920021</v>
-      </c>
-      <c r="C31" s="2">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="M31" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="N31" s="2">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>2</v>
-      </c>
-      <c r="R31" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="S31" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="T31" s="2">
-        <v>1</v>
-      </c>
-      <c r="U31" s="2">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W31" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="X31" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="Y31" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z31" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA31" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE31" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>20022</v>
-      </c>
-      <c r="B32" s="2">
-        <v>920022</v>
-      </c>
-      <c r="C32" s="2">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2">
-        <v>4</v>
-      </c>
-      <c r="E32" s="2">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I32" s="2">
-        <v>18</v>
-      </c>
-      <c r="J32" s="2">
-        <v>720022</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="L32" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="M32" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="N32" s="2">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>1</v>
-      </c>
-      <c r="P32" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>2</v>
-      </c>
-      <c r="R32" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="S32" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="T32" s="2">
-        <v>1</v>
-      </c>
-      <c r="U32" s="2">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W32" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="X32" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="Y32" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z32" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE32" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>20023</v>
-      </c>
-      <c r="B33" s="2">
-        <v>920023</v>
-      </c>
-      <c r="C33" s="2">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2">
-        <v>3</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I33" s="2">
-        <v>18</v>
-      </c>
-      <c r="J33" s="2">
-        <v>720023</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="L33" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="M33" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="N33" s="2">
-        <v>0</v>
-      </c>
-      <c r="O33" s="2">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>2</v>
-      </c>
-      <c r="R33" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="S33" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="T33" s="2">
-        <v>1</v>
-      </c>
-      <c r="U33" s="2">
-        <v>2</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W33" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="X33" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y33" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="Z33" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA33" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="2">
+      <c r="AA33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="13">
         <v>0</v>
       </c>
       <c r="AC33" s="21">
         <v>0</v>
       </c>
-      <c r="AD33" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE33" s="21" t="s">
+      <c r="AD33" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE33" s="27" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>20031</v>
+        <v>20001</v>
       </c>
       <c r="B34" s="2">
-        <v>920031</v>
+        <v>920001</v>
       </c>
       <c r="C34" s="2">
         <v>5</v>
@@ -5009,176 +5050,743 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>264</v>
+        <v>173</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
       </c>
       <c r="J34" s="2">
-        <v>0</v>
+        <v>720001</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="M34" s="13" t="s">
-        <v>256</v>
+        <v>176</v>
       </c>
       <c r="N34" s="2">
         <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q34" s="2">
         <v>2</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="S34" s="13" t="s">
-        <v>258</v>
+        <v>178</v>
       </c>
       <c r="T34" s="2">
         <v>1</v>
       </c>
       <c r="U34" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W34" s="13" t="s">
-        <v>259</v>
+        <v>179</v>
       </c>
       <c r="X34" s="13" t="s">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="Y34" s="13" t="s">
-        <v>261</v>
+        <v>181</v>
       </c>
       <c r="Z34" s="13" t="s">
-        <v>262</v>
+        <v>182</v>
       </c>
       <c r="AA34" s="2">
         <v>0</v>
       </c>
       <c r="AB34" s="2">
-        <v>0</v>
+        <v>820001</v>
       </c>
       <c r="AC34" s="21">
         <v>0</v>
       </c>
-      <c r="AD34" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE34" s="21" t="s">
-        <v>27</v>
+      <c r="AD34" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="AE34" s="27" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
+        <v>20011</v>
+      </c>
+      <c r="B35" s="2">
+        <v>920011</v>
+      </c>
+      <c r="C35" s="2">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>720011</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>2</v>
+      </c>
+      <c r="R35" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="S35" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="T35" s="2">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2">
+        <v>3</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W35" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="X35" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y35" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z35" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="2">
+        <v>820011</v>
+      </c>
+      <c r="AC35" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE35" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>20012</v>
+      </c>
+      <c r="B36" s="2">
+        <v>920012</v>
+      </c>
+      <c r="C36" s="2">
+        <v>6</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="L36" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>2</v>
+      </c>
+      <c r="R36" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="S36" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="T36" s="2">
+        <v>1</v>
+      </c>
+      <c r="U36" s="2">
+        <v>3</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W36" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="X36" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y36" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z36" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="2">
+        <v>820011</v>
+      </c>
+      <c r="AC36" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE36" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>20021</v>
+      </c>
+      <c r="B37" s="2">
+        <v>920021</v>
+      </c>
+      <c r="C37" s="2">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>2</v>
+      </c>
+      <c r="R37" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="S37" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="T37" s="2">
+        <v>1</v>
+      </c>
+      <c r="U37" s="2">
+        <v>2</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W37" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="X37" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y37" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z37" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE37" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>20022</v>
+      </c>
+      <c r="B38" s="2">
+        <v>920022</v>
+      </c>
+      <c r="C38" s="2">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I38" s="2">
+        <v>18</v>
+      </c>
+      <c r="J38" s="2">
+        <v>720022</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2">
+        <v>1</v>
+      </c>
+      <c r="P38" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>2</v>
+      </c>
+      <c r="R38" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="S38" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="T38" s="2">
+        <v>1</v>
+      </c>
+      <c r="U38" s="2">
+        <v>2</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W38" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="X38" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="Y38" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z38" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA38" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE38" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>20023</v>
+      </c>
+      <c r="B39" s="2">
+        <v>920023</v>
+      </c>
+      <c r="C39" s="2">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2">
+        <v>3</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I39" s="2">
+        <v>18</v>
+      </c>
+      <c r="J39" s="2">
+        <v>720023</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="N39" s="2">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2">
+        <v>1</v>
+      </c>
+      <c r="P39" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>2</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="S39" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="T39" s="2">
+        <v>1</v>
+      </c>
+      <c r="U39" s="2">
+        <v>2</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W39" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="X39" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y39" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z39" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE39" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>20031</v>
+      </c>
+      <c r="B40" s="2">
+        <v>920031</v>
+      </c>
+      <c r="C40" s="2">
+        <v>5</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="N40" s="2">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>2</v>
+      </c>
+      <c r="R40" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="S40" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="T40" s="2">
+        <v>1</v>
+      </c>
+      <c r="U40" s="2">
+        <v>4</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W40" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="X40" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y40" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z40" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE40" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
         <v>20041</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B41" s="2">
         <v>920041</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C41" s="2">
         <v>7</v>
       </c>
-      <c r="D35" s="2">
-        <v>1</v>
-      </c>
-      <c r="E35" s="2">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2">
-        <v>0</v>
-      </c>
-      <c r="K35" s="13" t="s">
+      <c r="D41" s="2">
+        <v>1</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="M41" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2">
+        <v>1</v>
+      </c>
+      <c r="P41" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>1</v>
+      </c>
+      <c r="R41" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="S41" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="T41" s="2">
+        <v>1</v>
+      </c>
+      <c r="U41" s="2">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W41" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="X41" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="L35" s="13" t="s">
+      <c r="Y41" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="M35" s="13" t="s">
+      <c r="Z41" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="N35" s="2">
-        <v>0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>1</v>
-      </c>
-      <c r="P35" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>1</v>
-      </c>
-      <c r="R35" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="S35" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="T35" s="2">
-        <v>1</v>
-      </c>
-      <c r="U35" s="2">
-        <v>0</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W35" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="X35" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="Y35" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z35" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="AA35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="21">
-        <v>1</v>
-      </c>
-      <c r="AD35" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE35" s="21" t="s">
+      <c r="AA41" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="21">
+        <v>1</v>
+      </c>
+      <c r="AD41" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE41" s="21" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5203,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5211,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -5219,7 +5827,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -5227,7 +5835,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -5235,7 +5843,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -5243,7 +5851,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -5251,7 +5859,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -5259,7 +5867,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -5267,7 +5875,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -5275,7 +5883,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -5283,7 +5891,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -5291,7 +5899,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -5299,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -5307,7 +5915,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -5315,7 +5923,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -5323,7 +5931,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -5331,7 +5939,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -5339,7 +5947,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -5347,7 +5955,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6C3557-1E72-443D-9AB4-2A0A8638B0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DC5769-C0BA-4BD5-A011-4B95EE827B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,10 @@
 3-吃药回血
 4-玩家被动技能
 5-玩家主动技能
-6-由特殊方式触发的主动技能</t>
+6-由特殊方式触发的主动技能
+7-召唤技能
+8-弹道技能
+9-由特殊方式触发的动作技能</t>
         </r>
       </text>
     </comment>
@@ -263,7 +266,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="355">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1376,6 +1379,103 @@
   </si>
   <si>
     <t>0:1080</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920032</t>
+  </si>
+  <si>
+    <t>1:2920032</t>
+  </si>
+  <si>
+    <t>1:3920032</t>
+  </si>
+  <si>
+    <t>1:4920032</t>
+  </si>
+  <si>
+    <t>1:5920032</t>
+  </si>
+  <si>
+    <t>1:6920032</t>
+  </si>
+  <si>
+    <t>1:7920032</t>
+  </si>
+  <si>
+    <t>1:8920032</t>
+  </si>
+  <si>
+    <t>1:9920032</t>
+  </si>
+  <si>
+    <t>电环</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放一圈电环</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920033</t>
+  </si>
+  <si>
+    <t>1:2920033</t>
+  </si>
+  <si>
+    <t>1:3920033</t>
+  </si>
+  <si>
+    <t>1:4920033</t>
+  </si>
+  <si>
+    <t>1:5920033</t>
+  </si>
+  <si>
+    <t>1:6920033</t>
+  </si>
+  <si>
+    <t>1:7920033</t>
+  </si>
+  <si>
+    <t>1:8920033</t>
+  </si>
+  <si>
+    <t>1:9920033</t>
+  </si>
+  <si>
+    <t>雷暴云</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤持续6秒的雷暴云，每秒随机劈下闪电对敌人造成伤害</t>
+  </si>
+  <si>
+    <t>1:10920033</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:11920033</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage_adjustment</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次造成伤害后的伤害调整系数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:12920031</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>连环闪电</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人后释放闪电链</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1595,7 +1695,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1674,6 +1774,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1971,7 +2072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AE41"/>
+  <dimension ref="A1:AF44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
@@ -2001,15 +2102,16 @@
     <col min="29" max="29" width="19.75" style="21" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="20.5" style="21" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="24.75" style="21" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9" style="2"/>
+    <col min="32" max="32" width="23.875" style="21" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:32" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2103,8 +2205,11 @@
       <c r="AE2" s="21" t="s">
         <v>80</v>
       </c>
+      <c r="AF2" s="21" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:32" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2198,8 +2303,11 @@
       <c r="AE3" s="25" t="s">
         <v>306</v>
       </c>
+      <c r="AF3" s="21" t="s">
+        <v>350</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:32" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -2293,8 +2401,11 @@
       <c r="AE4" s="26" t="s">
         <v>309</v>
       </c>
+      <c r="AF4" s="21" t="s">
+        <v>351</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10101</v>
       </c>
@@ -2386,8 +2497,11 @@
       <c r="AE5" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF5" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10102</v>
       </c>
@@ -2479,8 +2593,11 @@
       <c r="AE6" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF6" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10201</v>
       </c>
@@ -2572,8 +2689,11 @@
       <c r="AE7" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF7" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10202</v>
       </c>
@@ -2665,8 +2785,11 @@
       <c r="AE8" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF8" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10301</v>
       </c>
@@ -2758,8 +2881,11 @@
       <c r="AE9" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF9" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10302</v>
       </c>
@@ -2851,8 +2977,11 @@
       <c r="AE10" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF10" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>201001011</v>
       </c>
@@ -2946,8 +3075,11 @@
       <c r="AE11" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF11" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>201002011</v>
       </c>
@@ -3041,8 +3173,11 @@
       <c r="AE12" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF12" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>201003001</v>
       </c>
@@ -3136,8 +3271,11 @@
       <c r="AE13" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF13" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>201004011</v>
       </c>
@@ -3231,8 +3369,11 @@
       <c r="AE14" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF14" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>201005001</v>
       </c>
@@ -3326,8 +3467,11 @@
       <c r="AE15" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF15" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>201006001</v>
       </c>
@@ -3421,8 +3565,11 @@
       <c r="AE16" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF16" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>214001011</v>
       </c>
@@ -3516,8 +3663,11 @@
       <c r="AE17" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF17" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>203001001</v>
       </c>
@@ -3611,8 +3761,11 @@
       <c r="AE18" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF18" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>203002011</v>
       </c>
@@ -3706,8 +3859,11 @@
       <c r="AE19" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF19" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>203003001</v>
       </c>
@@ -3801,8 +3957,11 @@
       <c r="AE20" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF20" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>204001001</v>
       </c>
@@ -3896,8 +4055,11 @@
       <c r="AE21" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF21" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>204002001</v>
       </c>
@@ -3991,8 +4153,11 @@
       <c r="AE22" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF22" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>204003001</v>
       </c>
@@ -4086,8 +4251,11 @@
       <c r="AE23" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF23" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>208001001</v>
       </c>
@@ -4181,8 +4349,11 @@
       <c r="AE24" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF24" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>211001001</v>
       </c>
@@ -4276,8 +4447,11 @@
       <c r="AE25" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF25" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>211002001</v>
       </c>
@@ -4371,8 +4545,11 @@
       <c r="AE26" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF26" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="27" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>213003001</v>
       </c>
@@ -4466,8 +4643,11 @@
       <c r="AE27" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF27" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>216001001</v>
       </c>
@@ -4561,8 +4741,11 @@
       <c r="AE28" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF28" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="29" spans="1:31" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>59260001</v>
       </c>
@@ -4652,8 +4835,11 @@
       <c r="AE29" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF29" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A30" s="10">
         <v>25010001</v>
       </c>
@@ -4747,8 +4933,11 @@
       <c r="AE30" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF30" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="31" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="13">
         <v>95000101</v>
       </c>
@@ -4842,8 +5031,11 @@
       <c r="AE31" s="27" t="s">
         <v>27</v>
       </c>
+      <c r="AF31" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="32" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="13">
         <v>95100101</v>
       </c>
@@ -4937,8 +5129,11 @@
       <c r="AE32" s="27" t="s">
         <v>27</v>
       </c>
+      <c r="AF32" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="33" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="13">
         <v>95200101</v>
       </c>
@@ -5032,8 +5227,11 @@
       <c r="AE33" s="27" t="s">
         <v>27</v>
       </c>
+      <c r="AF33" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>20001</v>
       </c>
@@ -5127,8 +5325,11 @@
       <c r="AE34" s="27" t="s">
         <v>307</v>
       </c>
+      <c r="AF34" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>20011</v>
       </c>
@@ -5219,8 +5420,11 @@
       <c r="AE35" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF35" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>20012</v>
       </c>
@@ -5314,8 +5518,11 @@
       <c r="AE36" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF36" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>20021</v>
       </c>
@@ -5409,8 +5616,11 @@
       <c r="AE37" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF37" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>20022</v>
       </c>
@@ -5504,8 +5714,11 @@
       <c r="AE38" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF38" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>20023</v>
       </c>
@@ -5599,8 +5812,11 @@
       <c r="AE39" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF39" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A40" s="2">
         <v>20031</v>
       </c>
@@ -5682,8 +5898,8 @@
       <c r="AA40" s="2">
         <v>0</v>
       </c>
-      <c r="AB40" s="2">
-        <v>0</v>
+      <c r="AB40" s="28">
+        <v>820031</v>
       </c>
       <c r="AC40" s="21">
         <v>0</v>
@@ -5694,16 +5910,19 @@
       <c r="AE40" s="21" t="s">
         <v>27</v>
       </c>
+      <c r="AF40" s="21" t="s">
+        <v>352</v>
+      </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A41" s="2">
-        <v>20041</v>
+        <v>20032</v>
       </c>
       <c r="B41" s="2">
-        <v>920041</v>
+        <v>920032</v>
       </c>
       <c r="C41" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D41" s="2">
         <v>1</v>
@@ -5712,13 +5931,13 @@
         <v>1</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>283</v>
+        <v>335</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>283</v>
+        <v>335</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>284</v>
+        <v>336</v>
       </c>
       <c r="I41" s="2">
         <v>0</v>
@@ -5727,13 +5946,13 @@
         <v>0</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="L41" s="13" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="M41" s="13" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="N41" s="2">
         <v>0</v>
@@ -5742,51 +5961,348 @@
         <v>1</v>
       </c>
       <c r="P41" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" s="13" t="s">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="S41" s="13" t="s">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="T41" s="2">
         <v>1</v>
       </c>
       <c r="U41" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>75</v>
       </c>
       <c r="W41" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="X41" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="Y41" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="Z41" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA41" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="28">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE41" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF41" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>20033</v>
+      </c>
+      <c r="B42" s="2">
+        <v>920033</v>
+      </c>
+      <c r="C42" s="2">
+        <v>5</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2">
+        <v>1</v>
+      </c>
+      <c r="P42" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>2</v>
+      </c>
+      <c r="R42" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="S42" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="T42" s="2">
+        <v>1</v>
+      </c>
+      <c r="U42" s="2">
+        <v>4</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W42" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="X42" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="Y42" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="Z42" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="28">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="AE42" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="AF42" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>20034</v>
+      </c>
+      <c r="B43" s="2">
+        <v>920034</v>
+      </c>
+      <c r="C43" s="2">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>1</v>
+      </c>
+      <c r="R43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="T43" s="2">
+        <v>1</v>
+      </c>
+      <c r="U43" s="2">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="X43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z43" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="28">
+        <v>820034</v>
+      </c>
+      <c r="AC43" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE43" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF43" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>20041</v>
+      </c>
+      <c r="B44" s="2">
+        <v>920041</v>
+      </c>
+      <c r="C44" s="2">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2">
+        <v>0</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2">
+        <v>1</v>
+      </c>
+      <c r="P44" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>1</v>
+      </c>
+      <c r="R44" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="S44" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="T44" s="2">
+        <v>1</v>
+      </c>
+      <c r="U44" s="2">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W44" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="X41" s="13" t="s">
+      <c r="X44" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="Y41" s="13" t="s">
+      <c r="Y44" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="Z41" s="13" t="s">
+      <c r="Z44" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="AA41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="21">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE41" s="21" t="s">
+      <c r="AA44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="21">
+        <v>1</v>
+      </c>
+      <c r="AD44" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE44" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF44" s="21" t="s">
         <v>27</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DC5769-C0BA-4BD5-A011-4B95EE827B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA9932D-7D22-4055-BE8B-F85DFD41B661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,7 +266,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="374">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1476,6 +1476,73 @@
   </si>
   <si>
     <t>击杀敌人后释放闪电链</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>电刃</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻有概率使目标麻痹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>超强电刃</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每攻击3次，向前方劈出一道超强电刃</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1920053</t>
+  </si>
+  <si>
+    <t>1:2920053</t>
+  </si>
+  <si>
+    <t>1:3920053</t>
+  </si>
+  <si>
+    <t>1:4920053</t>
+  </si>
+  <si>
+    <t>1:5920053</t>
+  </si>
+  <si>
+    <t>1:6920053</t>
+  </si>
+  <si>
+    <t>1:7920053</t>
+  </si>
+  <si>
+    <t>1:8920053</t>
+  </si>
+  <si>
+    <t>1:9920053</t>
+  </si>
+  <si>
+    <t>天罚</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人后释放超强电刃</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:13920031</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:13920032</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1695,7 +1762,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1775,6 +1842,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2072,14 +2148,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AF44"/>
+  <dimension ref="A1:AF47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.5" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.5" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="17.625" style="2" customWidth="1"/>
@@ -2124,8 +2200,8 @@
       <c r="D2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>54</v>
+      <c r="E2" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>2</v>
@@ -2418,8 +2494,8 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="4">
-        <v>1</v>
+      <c r="E5" s="31" t="s">
+        <v>84</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>47</v>
@@ -2514,8 +2590,8 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
-        <v>1</v>
+      <c r="E6" s="31" t="s">
+        <v>84</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>48</v>
@@ -2610,8 +2686,8 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
-        <v>2</v>
+      <c r="E7" s="31" t="s">
+        <v>371</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>49</v>
@@ -2706,8 +2782,8 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
-        <v>2</v>
+      <c r="E8" s="31" t="s">
+        <v>371</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>51</v>
@@ -2802,8 +2878,8 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="4">
-        <v>3</v>
+      <c r="E9" s="31" t="s">
+        <v>370</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>50</v>
@@ -2898,8 +2974,8 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="4">
-        <v>3</v>
+      <c r="E10" s="31" t="s">
+        <v>370</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>52</v>
@@ -2994,8 +3070,8 @@
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
+      <c r="E11" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>69</v>
@@ -3092,8 +3168,8 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="1">
-        <v>1</v>
+      <c r="E12" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>70</v>
@@ -3190,8 +3266,8 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
+      <c r="E13" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>311</v>
@@ -3288,8 +3364,8 @@
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
+      <c r="E14" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>310</v>
@@ -3386,8 +3462,8 @@
       <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
+      <c r="E15" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>312</v>
@@ -3484,8 +3560,8 @@
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="1">
-        <v>1</v>
+      <c r="E16" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>313</v>
@@ -3582,8 +3658,8 @@
       <c r="D17" s="1">
         <v>1</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
+      <c r="E17" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>71</v>
@@ -3680,8 +3756,8 @@
       <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="1">
-        <v>1</v>
+      <c r="E18" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>263</v>
@@ -3778,8 +3854,8 @@
       <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
+      <c r="E19" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>260</v>
@@ -3876,8 +3952,8 @@
       <c r="D20" s="1">
         <v>1</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
+      <c r="E20" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>264</v>
@@ -3974,8 +4050,8 @@
       <c r="D21" s="1">
         <v>1</v>
       </c>
-      <c r="E21" s="1">
-        <v>1</v>
+      <c r="E21" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>265</v>
@@ -4072,8 +4148,8 @@
       <c r="D22" s="1">
         <v>1</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
+      <c r="E22" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>266</v>
@@ -4170,8 +4246,8 @@
       <c r="D23" s="1">
         <v>1</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
+      <c r="E23" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>314</v>
@@ -4268,8 +4344,8 @@
       <c r="D24" s="1">
         <v>1</v>
       </c>
-      <c r="E24" s="1">
-        <v>1</v>
+      <c r="E24" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>315</v>
@@ -4366,8 +4442,8 @@
       <c r="D25" s="1">
         <v>1</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
+      <c r="E25" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>267</v>
@@ -4464,8 +4540,8 @@
       <c r="D26" s="1">
         <v>1</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
+      <c r="E26" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>268</v>
@@ -4562,8 +4638,8 @@
       <c r="D27" s="1">
         <v>1</v>
       </c>
-      <c r="E27" s="1">
-        <v>1</v>
+      <c r="E27" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>316</v>
@@ -4660,8 +4736,8 @@
       <c r="D28" s="1">
         <v>1</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
+      <c r="E28" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>261</v>
@@ -4758,8 +4834,8 @@
       <c r="D29" s="1">
         <v>1</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
+      <c r="E29" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="1" t="s">
@@ -4852,8 +4928,8 @@
       <c r="D30" s="10">
         <v>1</v>
       </c>
-      <c r="E30" s="10">
-        <v>1</v>
+      <c r="E30" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>57</v>
@@ -4950,8 +5026,8 @@
       <c r="D31" s="13">
         <v>1</v>
       </c>
-      <c r="E31" s="13">
-        <v>1</v>
+      <c r="E31" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>67</v>
@@ -5048,8 +5124,8 @@
       <c r="D32" s="13">
         <v>1</v>
       </c>
-      <c r="E32" s="13">
-        <v>1</v>
+      <c r="E32" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>68</v>
@@ -5146,8 +5222,8 @@
       <c r="D33" s="13">
         <v>1</v>
       </c>
-      <c r="E33" s="13">
-        <v>1</v>
+      <c r="E33" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>63</v>
@@ -5231,588 +5307,588 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
+    <row r="34" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="29">
         <v>20001</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="29">
         <v>920001</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="29">
         <v>5</v>
       </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="D34" s="29">
+        <v>1</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="I34" s="2">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
+      <c r="I34" s="29">
+        <v>0</v>
+      </c>
+      <c r="J34" s="29">
         <v>720001</v>
       </c>
-      <c r="K34" s="13" t="s">
+      <c r="K34" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="L34" s="13" t="s">
+      <c r="L34" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="M34" s="13" t="s">
+      <c r="M34" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="N34" s="2">
-        <v>0</v>
-      </c>
-      <c r="O34" s="2">
-        <v>1</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="N34" s="29">
+        <v>0</v>
+      </c>
+      <c r="O34" s="29">
+        <v>1</v>
+      </c>
+      <c r="P34" s="29">
         <v>5</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="29">
         <v>2</v>
       </c>
-      <c r="R34" s="13" t="s">
+      <c r="R34" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="S34" s="13" t="s">
+      <c r="S34" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="T34" s="2">
-        <v>1</v>
-      </c>
-      <c r="U34" s="2">
+      <c r="T34" s="29">
+        <v>1</v>
+      </c>
+      <c r="U34" s="29">
         <v>2</v>
       </c>
-      <c r="V34" s="2" t="s">
+      <c r="V34" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="W34" s="13" t="s">
+      <c r="W34" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="X34" s="13" t="s">
+      <c r="X34" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="Y34" s="13" t="s">
+      <c r="Y34" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="Z34" s="13" t="s">
+      <c r="Z34" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="AA34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="2">
+      <c r="AA34" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="29">
         <v>820001</v>
       </c>
-      <c r="AC34" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="27" t="s">
+      <c r="AC34" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="AE34" s="27" t="s">
+      <c r="AE34" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="AF34" s="21" t="s">
+      <c r="AF34" s="30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
+    <row r="35" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="29">
         <v>20011</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="29">
         <v>920011</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="29">
         <v>5</v>
       </c>
-      <c r="D35" s="2">
-        <v>1</v>
-      </c>
-      <c r="E35" s="2">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="D35" s="29">
+        <v>1</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F35" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2">
+      <c r="I35" s="29">
+        <v>1</v>
+      </c>
+      <c r="J35" s="29">
         <v>720011</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="K35" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="L35" s="13" t="s">
+      <c r="L35" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="M35" s="13" t="s">
+      <c r="M35" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="N35" s="2">
-        <v>0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>1</v>
-      </c>
-      <c r="P35" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="2">
+      <c r="N35" s="29">
+        <v>0</v>
+      </c>
+      <c r="O35" s="29">
+        <v>1</v>
+      </c>
+      <c r="P35" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="29">
         <v>2</v>
       </c>
-      <c r="R35" s="13" t="s">
+      <c r="R35" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="S35" s="13" t="s">
+      <c r="S35" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="T35" s="2">
-        <v>1</v>
-      </c>
-      <c r="U35" s="2">
+      <c r="T35" s="29">
+        <v>1</v>
+      </c>
+      <c r="U35" s="29">
         <v>3</v>
       </c>
-      <c r="V35" s="2" t="s">
+      <c r="V35" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="W35" s="13" t="s">
+      <c r="W35" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="X35" s="13" t="s">
+      <c r="X35" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="Y35" s="13" t="s">
+      <c r="Y35" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="Z35" s="13" t="s">
+      <c r="Z35" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="AA35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="2">
+      <c r="AA35" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="29">
         <v>820011</v>
       </c>
-      <c r="AC35" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE35" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF35" s="21" t="s">
+      <c r="AC35" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE35" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF35" s="30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
+    <row r="36" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="29">
         <v>20012</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="29">
         <v>920012</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="29">
         <v>6</v>
       </c>
-      <c r="D36" s="2">
-        <v>1</v>
-      </c>
-      <c r="E36" s="2">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="D36" s="29">
+        <v>1</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="13" t="s">
+      <c r="I36" s="29">
+        <v>0</v>
+      </c>
+      <c r="J36" s="29">
+        <v>0</v>
+      </c>
+      <c r="K36" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="L36" s="13" t="s">
+      <c r="L36" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="M36" s="13" t="s">
+      <c r="M36" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="N36" s="2">
-        <v>0</v>
-      </c>
-      <c r="O36" s="2">
-        <v>1</v>
-      </c>
-      <c r="P36" s="2">
+      <c r="N36" s="29">
+        <v>0</v>
+      </c>
+      <c r="O36" s="29">
+        <v>1</v>
+      </c>
+      <c r="P36" s="29">
         <v>3</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="29">
         <v>2</v>
       </c>
-      <c r="R36" s="13" t="s">
+      <c r="R36" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="S36" s="13" t="s">
+      <c r="S36" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="T36" s="2">
-        <v>1</v>
-      </c>
-      <c r="U36" s="2">
+      <c r="T36" s="29">
+        <v>1</v>
+      </c>
+      <c r="U36" s="29">
         <v>3</v>
       </c>
-      <c r="V36" s="2" t="s">
+      <c r="V36" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="W36" s="13" t="s">
+      <c r="W36" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="X36" s="13" t="s">
+      <c r="X36" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="Y36" s="13" t="s">
+      <c r="Y36" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="Z36" s="13" t="s">
+      <c r="Z36" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="AA36" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="2">
+      <c r="AA36" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="29">
         <v>820011</v>
       </c>
-      <c r="AC36" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE36" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF36" s="21" t="s">
+      <c r="AC36" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE36" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF36" s="30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
+    <row r="37" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="29">
         <v>20021</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="29">
         <v>920021</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="29">
         <v>5</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="29">
         <v>2</v>
       </c>
-      <c r="E37" s="2">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="E37" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
-        <v>0</v>
-      </c>
-      <c r="K37" s="13" t="s">
+      <c r="I37" s="29">
+        <v>0</v>
+      </c>
+      <c r="J37" s="29">
+        <v>0</v>
+      </c>
+      <c r="K37" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="L37" s="13" t="s">
+      <c r="L37" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="M37" s="13" t="s">
+      <c r="M37" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="N37" s="2">
-        <v>0</v>
-      </c>
-      <c r="O37" s="2">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="2">
+      <c r="N37" s="29">
+        <v>0</v>
+      </c>
+      <c r="O37" s="29">
+        <v>0</v>
+      </c>
+      <c r="P37" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="29">
         <v>2</v>
       </c>
-      <c r="R37" s="13" t="s">
+      <c r="R37" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="S37" s="13" t="s">
+      <c r="S37" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="T37" s="2">
-        <v>1</v>
-      </c>
-      <c r="U37" s="2">
+      <c r="T37" s="29">
+        <v>1</v>
+      </c>
+      <c r="U37" s="29">
         <v>2</v>
       </c>
-      <c r="V37" s="2" t="s">
+      <c r="V37" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="W37" s="13" t="s">
+      <c r="W37" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="X37" s="13" t="s">
+      <c r="X37" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="Y37" s="13" t="s">
+      <c r="Y37" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="Z37" s="13" t="s">
+      <c r="Z37" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="AA37" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE37" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF37" s="21" t="s">
+      <c r="AA37" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="29">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE37" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF37" s="30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
+    <row r="38" spans="1:32" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="29">
         <v>20022</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="29">
         <v>920022</v>
       </c>
-      <c r="C